--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -268,7 +268,7 @@
     <t xml:space="preserve">Days: interview → written offer</t>
   </si>
   <si>
-    <t xml:space="preserve">Tesla is known for fast decisions; assumes offer approval within 3 days (client to confirm).</t>
+    <t xml:space="preserve">Assumes offer approval within 3 working days of the interview (client to confirm; it is one of the asks).</t>
   </si>
   <si>
     <t xml:space="preserve">T5</t>
@@ -370,13 +370,13 @@
     <t xml:space="preserve">Offer → signed contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Engpassberuf with counter-offers from energy/grid, rail, aerospace; Tesla shift work and IG Metall disputes are known. Tesla pays above Brandenburg trade median (€3,030/month, WSI https://www.lohnspiegel.de/gehaltsinfos/elektroniker_in_fuer_betriebstechnik_26252114.html) which helps.</t>
+    <t xml:space="preserve">Engpassberuf with counter-offers from energy/grid, rail, aerospace; Tesla shift work and IG Metall disputes are known. Acceptance improves if Tesla's offer beats the Brandenburg trade median (€3,030/month at 10 yrs, WSI https://www.lohnspiegel.de/gehaltsinfos/elektroniker_in_fuer_betriebstechnik_26252114.html); client to confirm pay band.</t>
   </si>
   <si>
     <t xml:space="preserve">AM</t>
   </si>
   <si>
-    <t xml:space="preserve">Bigger pool, fewer counter-offers; pay premium vs Brandenburg/Polish wages is strong for border commuters.</t>
+    <t xml:space="preserve">Bigger pool, fewer counter-offers; German pay vs Polish wages is a strong pull for border commuters.</t>
   </si>
   <si>
     <t xml:space="preserve">AA</t>
@@ -400,7 +400,7 @@
     <t xml:space="preserve">Reserve held back (share of total budget)</t>
   </si>
   <si>
-    <t xml:space="preserve">Covers ±30% error on the conversion that matters most (Part 1.4) for the cheapest channels; released from week 3 only on the rules in Part 4.</t>
+    <t xml:space="preserve">Buffer for estimate error: at €50k (incl. rounding) funds about half of the extra media a 30% miss on share qualified would need (Funnel F45 – F42). Beyond that the binding limit is assessment slots, not money. Released from week 3 only on the Tracker rules.</t>
   </si>
   <si>
     <t xml:space="preserve">B2</t>
@@ -535,7 +535,7 @@
     <t xml:space="preserve">people</t>
   </si>
   <si>
-    <t xml:space="preserve">≈7% of German employment is in Berlin+Brandenburg (BA statistics); assumed ~150–200k industrial electricians in DE, lower industrial density in the East → ~7,000 within 75 km of Grünheide. Order of magnitude only.</t>
+    <t xml:space="preserve">Berlin+Brandenburg hold roughly 7% of German employment (approx. 2.6M of ~35M employees subject to social insurance, from memory of BA figures); assumed ~150–200k industrial electricians in DE, lower industrial density in the East → ~7,000 within 75 km of Grünheide. Order of magnitude only.</t>
   </si>
   <si>
     <t xml:space="preserve">PSM</t>
@@ -955,7 +955,7 @@
     <t xml:space="preserve">I2: construction/Handwerk electricians (Elektroniker Energie- und Gebäudetechnik) within 75 km</t>
   </si>
   <si>
-    <t xml:space="preserve">Bauelektrik is a larger occupation than industrial electrics and is itself an Engpassberuf (BA Engpassanalyse https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html); Berlin construction boom → large local pool.</t>
+    <t xml:space="preserve">Bauelektrik is a larger occupation than industrial electrics and is itself an Engpassberuf (BA Engpassanalyse 2024: KldB 2621 Bauelektrik scores 2.7, threshold 2.0 – https://www.vbw-bayern.de/Redaktion/Frei-zugaengliche-Medien/Abteilungen-GS/Bildung/2025/Downloads/2024_BA-FK-Engpassanalyse.pdf); Berlin construction boom → large local pool.</t>
   </si>
   <si>
     <t xml:space="preserve">I2S</t>
@@ -1009,7 +1009,7 @@
     <t xml:space="preserve">I3: blended cost per application, Pracuj.pl + OLX Praca + Polish-geo Meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Pracuj.pl 30-day ad 1,499 PLN ≈ €350 (https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen) ÷ ~25 apps ≈ €14; PL Meta leads ~€8–10.</t>
+    <t xml:space="preserve">Pracuj.pl 30-day ad indicatively 1,499 PLN ≈ €350 (package page https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen; exact price is quoted per role/location in their calculator) ÷ ~25 apps ≈ €14; PL Meta leads ~€8–10 (own estimate).</t>
   </si>
   <si>
     <t xml:space="preserve">I3Q</t>
@@ -1471,7 +1471,7 @@
     <t xml:space="preserve">≥15 qualified re-applicants + referrals across roles by day 14, ≥5 of them electricians</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;5 qualified by day 14 → stop re-contact waves (cost is tiny, so mostly a signal that the ATS data is stale); referral bonus stays live because it only costs on a hire</t>
+    <t xml:space="preserve">&lt;5 qualified by day 14 → stop re-contact waves (cost is tiny, so mostly a signal that the ATS data is stale); referral bonus stays live because it is paid only on a signed hire (from week 4)</t>
   </si>
   <si>
     <t xml:space="preserve">I2 Handwerk → Industrie</t>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">Budget!H47</f>
-        <v>87.4362783297683</v>
+        <v>88.0409219542276</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6101,7 +6101,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>111</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>114</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>121</v>
       </c>
@@ -8258,7 +8258,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
         <v>306</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
         <v>324</v>
       </c>
@@ -10558,8 +10558,8 @@
         <v>478</v>
       </c>
       <c r="B53" s="35" t="n">
-        <f aca="false">F10+F16*(Assumptions!$D$51+Assumptions!$D$52)</f>
-        <v>4402.45581875</v>
+        <f aca="false">F10</f>
+        <v>350</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>479</v>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C45" s="35" t="n">
         <f aca="false">Scenarios!F4</f>
-        <v>49169.764891993</v>
+        <v>50000</v>
       </c>
       <c r="D45" s="26" t="n">
         <f aca="false">Scenarios!F39</f>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="I45" s="35" t="n">
         <f aca="false">C45/H45</f>
-        <v>491.69764891993</v>
+        <v>500</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15122,11 +15122,11 @@
       </c>
       <c r="C46" s="35" t="n">
         <f aca="false">Scenarios!G4</f>
-        <v>41794.3001581941</v>
+        <v>42500</v>
       </c>
       <c r="D46" s="26" t="n">
         <f aca="false">Scenarios!G39</f>
-        <v>25.4545656012709</v>
+        <v>26.0544104668059</v>
       </c>
       <c r="E46" s="26" t="n">
         <f aca="false">Scenarios!G40</f>
@@ -15142,11 +15142,11 @@
       </c>
       <c r="H46" s="29" t="n">
         <f aca="false">SUM(D46:G46)</f>
-        <v>94.5366456012709</v>
+        <v>95.1364904668059</v>
       </c>
       <c r="I46" s="35" t="n">
         <f aca="false">C46/H46</f>
-        <v>442.096288612468</v>
+        <v>446.726590306888</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="C47" s="35" t="n">
         <f aca="false">Scenarios!H4</f>
-        <v>34418.8354243951</v>
+        <v>35000</v>
       </c>
       <c r="D47" s="26" t="n">
         <f aca="false">Scenarios!H39</f>
@@ -15172,15 +15172,15 @@
       </c>
       <c r="G47" s="26" t="n">
         <f aca="false">Scenarios!H42</f>
-        <v>3.69112832976827</v>
+        <v>4.2957719542276</v>
       </c>
       <c r="H47" s="29" t="n">
         <f aca="false">SUM(D47:G47)</f>
-        <v>87.4362783297683</v>
+        <v>88.0409219542276</v>
       </c>
       <c r="I47" s="35" t="n">
         <f aca="false">C47/H47</f>
-        <v>393.644790033075</v>
+        <v>397.54240667989</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15190,11 +15190,11 @@
       </c>
       <c r="C48" s="35" t="n">
         <f aca="false">Scenarios!I4</f>
-        <v>24584.8824459965</v>
+        <v>25000</v>
       </c>
       <c r="D48" s="26" t="n">
         <f aca="false">Scenarios!I39</f>
-        <v>13.9630075154343</v>
+        <v>14.4171253636364</v>
       </c>
       <c r="E48" s="26" t="n">
         <f aca="false">Scenarios!I40</f>
@@ -15210,11 +15210,11 @@
       </c>
       <c r="H48" s="29" t="n">
         <f aca="false">SUM(D48:G48)</f>
-        <v>76.7261875154343</v>
+        <v>77.1803053636364</v>
       </c>
       <c r="I48" s="35" t="n">
         <f aca="false">C48/H48</f>
-        <v>320.423616005305</v>
+        <v>323.916831919906</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15299,20 +15299,20 @@
         <v>550</v>
       </c>
       <c r="F4" s="35" t="n">
-        <f aca="false">Budget!$C$11*F3</f>
-        <v>49169.764891993</v>
+        <f aca="false">Budget!$C$12*F3</f>
+        <v>50000</v>
       </c>
       <c r="G4" s="35" t="n">
-        <f aca="false">Budget!$C$11*G3</f>
-        <v>41794.3001581941</v>
+        <f aca="false">Budget!$C$12*G3</f>
+        <v>42500</v>
       </c>
       <c r="H4" s="35" t="n">
-        <f aca="false">Budget!$C$11*H3</f>
-        <v>34418.8354243951</v>
+        <f aca="false">Budget!$C$12*H3</f>
+        <v>35000</v>
       </c>
       <c r="I4" s="35" t="n">
-        <f aca="false">Budget!$C$11*I3</f>
-        <v>24584.8824459965</v>
+        <f aca="false">Budget!$C$12*I3</f>
+        <v>25000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15321,19 +15321,19 @@
       </c>
       <c r="F5" s="35" t="n">
         <f aca="false">F4*(1-Assumptions!$D$48)-Budget!$C$6-Budget!$C$8</f>
-        <v>34486.5858724798</v>
+        <v>35192.2857142857</v>
       </c>
       <c r="G5" s="35" t="n">
         <f aca="false">G4*(1-Assumptions!$D$48)-Budget!$C$6-Budget!$C$8</f>
-        <v>28217.4408487507</v>
+        <v>28817.2857142857</v>
       </c>
       <c r="H5" s="35" t="n">
         <f aca="false">H4*(1-Assumptions!$D$48)-Budget!$C$6-Budget!$C$8</f>
-        <v>21948.2958250216</v>
+        <v>22442.2857142857</v>
       </c>
       <c r="I5" s="35" t="n">
         <f aca="false">I4*(1-Assumptions!$D$48)-Budget!$C$6-Budget!$C$8</f>
-        <v>13589.4357933827</v>
+        <v>13942.2857142857</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15346,15 +15346,15 @@
       </c>
       <c r="G6" s="35" t="n">
         <f aca="false">MAX(0,(Budget!$C$4+Budget!$C$5)-G5)</f>
-        <v>6269.14502372912</v>
+        <v>5669.30015819407</v>
       </c>
       <c r="H6" s="35" t="n">
         <f aca="false">MAX(0,(Budget!$C$4+Budget!$C$5)-H5)</f>
-        <v>12538.2900474582</v>
+        <v>12044.3001581941</v>
       </c>
       <c r="I6" s="35" t="n">
         <f aca="false">MAX(0,(Budget!$C$4+Budget!$C$5)-I5)</f>
-        <v>20897.150079097</v>
+        <v>20544.3001581941</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="H21" s="26" t="n">
         <f aca="false">IF(C21&gt;0,E21*(1-L21/C21),E21)</f>
-        <v>0.927948329768269</v>
+        <v>1.5325919542276</v>
       </c>
       <c r="I21" s="26" t="n">
         <f aca="false">IF(C21&gt;0,E21*(1-M21/C21),E21)</f>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="L21" s="35" t="n">
         <f aca="false">MIN(C21,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
-        <v>3616.87227960109</v>
+        <v>3122.88239033693</v>
       </c>
       <c r="M21" s="35" t="n">
         <f aca="false">MIN(C21,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="G32" s="26" t="n">
         <f aca="false">IF(C32&gt;0,E32*(1-K32/C32),E32)</f>
-        <v>1.70941560127088</v>
+        <v>2.30926046680593</v>
       </c>
       <c r="H32" s="26" t="n">
         <f aca="false">IF(C32&gt;0,E32*(1-L32/C32),E32)</f>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="K32" s="35" t="n">
         <f aca="false">MIN(C32,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
-        <v>2453.22502372912</v>
+        <v>1853.38015819407</v>
       </c>
       <c r="L32" s="35" t="n">
         <f aca="false">MIN(C32,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="I36" s="26" t="n">
         <f aca="false">IF(C36&gt;0,E36*(1-M36/C36),E36)</f>
-        <v>1.80085751543425</v>
+        <v>2.25497536363637</v>
       </c>
       <c r="J36" s="35" t="n">
         <f aca="false">MIN(C36,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
@@ -16961,7 +16961,7 @@
       </c>
       <c r="M36" s="35" t="n">
         <f aca="false">MIN(C36,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
-        <v>7600.7323112399</v>
+        <v>7247.88239033693</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17033,7 +17033,7 @@
       </c>
       <c r="G39" s="26" t="n">
         <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E39)</f>
-        <v>25.4545656012709</v>
+        <v>26.0544104668059</v>
       </c>
       <c r="H39" s="26" t="n">
         <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E39)</f>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="I39" s="26" t="n">
         <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E39)</f>
-        <v>13.9630075154343</v>
+        <v>14.4171253636364</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="H42" s="26" t="n">
         <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E42)</f>
-        <v>3.69112832976827</v>
+        <v>4.2957719542276</v>
       </c>
       <c r="I42" s="26" t="n">
         <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E42)</f>
@@ -17117,15 +17117,15 @@
       </c>
       <c r="G43" s="29" t="n">
         <f aca="false">SUM(G39:G42)</f>
-        <v>94.5366456012709</v>
+        <v>95.1364904668059</v>
       </c>
       <c r="H43" s="29" t="n">
         <f aca="false">SUM(H39:H42)</f>
-        <v>87.4362783297683</v>
+        <v>88.0409219542276</v>
       </c>
       <c r="I43" s="29" t="n">
         <f aca="false">SUM(I39:I42)</f>
-        <v>76.7261875154343</v>
+        <v>77.1803053636364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17134,19 +17134,19 @@
       </c>
       <c r="F44" s="35" t="n">
         <f aca="false">F4/F43</f>
-        <v>491.69764891993</v>
+        <v>500</v>
       </c>
       <c r="G44" s="35" t="n">
         <f aca="false">G4/G43</f>
-        <v>442.096288612468</v>
+        <v>446.726590306888</v>
       </c>
       <c r="H44" s="35" t="n">
         <f aca="false">H4/H43</f>
-        <v>393.644790033075</v>
+        <v>397.54240667989</v>
       </c>
       <c r="I44" s="35" t="n">
         <f aca="false">I4/I43</f>
-        <v>320.423616005305</v>
+        <v>323.916831919906</v>
       </c>
     </row>
   </sheetData>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="751">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -616,7 +616,10 @@
     <t xml:space="preserve">Qualified people elsewhere in Germany willing to relocate in the window</t>
   </si>
   <si>
-    <t xml:space="preserve">East-German trade wages are below West (WSI: Brandenburg €3,030 vs West €3,600) so relocation pull is weak for trades, stronger for automation specialists.</t>
+    <t xml:space="preserve">Researched + Own estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">East-German trade wages are below West (WSI, https://www.lohnspiegel.de/gehaltsinfos/elektroniker_in_fuer_betriebstechnik_26252114.html: Brandenburg €3,030 vs West €3,600, both standardised to 10 years) so relocation pull is weak for trades, stronger for automation specialists.</t>
   </si>
   <si>
     <t xml:space="preserve">PRM</t>
@@ -865,6 +868,18 @@
     <t xml:space="preserve">Week is effectively full.</t>
   </si>
   <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacing floor: release reserve to the cheapest cells with capacity when next week's forecast qualified falls below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qualified/wk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~80% of the 55 weekly slots; below this, slots would go unused.</t>
+  </si>
+  <si>
     <t xml:space="preserve">R8</t>
   </si>
   <si>
@@ -940,9 +955,6 @@
     <t xml:space="preserve">CPC</t>
   </si>
   <si>
-    <t xml:space="preserve">Researched + Own estimate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Indeed CPCs €0.10–5+ by competition (https://www.pin.com/blog/indeed-pricing/); Engpass trade in a contested market → €2.00. Apply rate: Appcast 6.1% overall, trades lower (https://www.prnewswire.com/news-releases/appcast-releases-2025-recruitment-marketing-benchmark-report-302372820.html) → 3.5%.</t>
   </si>
   <si>
@@ -1372,7 +1384,7 @@
     <t xml:space="preserve">Reachable qualified pool (Pool tab)</t>
   </si>
   <si>
-    <t xml:space="preserve">Qualified needed ÷ reachable pool</t>
+    <t xml:space="preserve">Qualified needed ÷ reachable pool (excl. I2, Pool tab)</t>
   </si>
   <si>
     <t xml:space="preserve">Highest cost per hire we must buy (beyond tests)</t>
@@ -1648,7 +1660,7 @@
     <t xml:space="preserve">Test window (14 days from launch)</t>
   </si>
   <si>
-    <t xml:space="preserve">Share of planned volume in window</t>
+    <t xml:space="preserve">Share of planned volume in window (days of each spend week inside the window)</t>
   </si>
   <si>
     <t xml:space="preserve">Test budget €</t>
@@ -1678,7 +1690,7 @@
     <t xml:space="preserve">I1 Rediscovery + referrals</t>
   </si>
   <si>
-    <t xml:space="preserve">Wed 21 Oct – Tue 3 Nov (waves 1–2)</t>
+    <t xml:space="preserve">Wed 21 Oct – Tue 3 Nov (waves 1–3)</t>
   </si>
   <si>
     <t xml:space="preserve">n/a (≈€8)</t>
@@ -1687,7 +1699,7 @@
     <t xml:space="preserve">–</t>
   </si>
   <si>
-    <t xml:space="preserve">Also ≥ a third of the qualified are electricians. Referral bonus stays live after a kill: it is paid only on a signed hire (from week 4). A kill mainly signals stale ATS data.</t>
+    <t xml:space="preserve">Also ≥ a third of the qualified are electricians. All three waves have gone out by day 14, so a kill means no further re-contacts and the I1a share of the plan is re-allocated. Referral bonus stays live: it is paid only on a signed hire (from week 4). A kill mainly signals stale ATS data.</t>
   </si>
   <si>
     <t xml:space="preserve">I2 Handwerk → Industrie</t>
@@ -1931,9 +1943,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total hires</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Above the recommended budget, extra money buys almost nothing before 31 Dec: hires are capped by 55 assessments/week (Funnel B26), not by media.</t>
   </si>
   <si>
     <t xml:space="preserve">Budget scenarios: cut the most expensive cost-per-hire cells first</t>
@@ -3075,12 +3084,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3088,73 +3097,73 @@
         <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3212,7 +3221,7 @@
         <v/>
       </c>
       <c r="U5" s="24" t="n">
-        <f aca="false">(R5+Assumptions!$D$107*E5)/(Q5+Assumptions!$D$107)</f>
+        <f aca="false">(R5+Assumptions!$D$108*E5)/(Q5+Assumptions!$D$108)</f>
         <v>0.08</v>
       </c>
       <c r="V5" s="35" t="n">
@@ -3283,7 +3292,7 @@
         <v/>
       </c>
       <c r="U6" s="24" t="n">
-        <f aca="false">(R6+Assumptions!$D$107*E6)/(Q6+Assumptions!$D$107)</f>
+        <f aca="false">(R6+Assumptions!$D$108*E6)/(Q6+Assumptions!$D$108)</f>
         <v>0.18</v>
       </c>
       <c r="V6" s="35" t="n">
@@ -3354,7 +3363,7 @@
         <v/>
       </c>
       <c r="U7" s="24" t="n">
-        <f aca="false">(R7+Assumptions!$D$107*E7)/(Q7+Assumptions!$D$107)</f>
+        <f aca="false">(R7+Assumptions!$D$108*E7)/(Q7+Assumptions!$D$108)</f>
         <v>0.1</v>
       </c>
       <c r="V7" s="35" t="n">
@@ -3425,7 +3434,7 @@
         <v/>
       </c>
       <c r="U8" s="24" t="n">
-        <f aca="false">(R8+Assumptions!$D$107*E8)/(Q8+Assumptions!$D$107)</f>
+        <f aca="false">(R8+Assumptions!$D$108*E8)/(Q8+Assumptions!$D$108)</f>
         <v>0.08</v>
       </c>
       <c r="V8" s="35" t="n">
@@ -3496,7 +3505,7 @@
         <v/>
       </c>
       <c r="U9" s="24" t="n">
-        <f aca="false">(R9+Assumptions!$D$107*E9)/(Q9+Assumptions!$D$107)</f>
+        <f aca="false">(R9+Assumptions!$D$108*E9)/(Q9+Assumptions!$D$108)</f>
         <v>0.12</v>
       </c>
       <c r="V9" s="35" t="n">
@@ -3567,7 +3576,7 @@
         <v/>
       </c>
       <c r="U10" s="24" t="n">
-        <f aca="false">(R10+Assumptions!$D$107*E10)/(Q10+Assumptions!$D$107)</f>
+        <f aca="false">(R10+Assumptions!$D$108*E10)/(Q10+Assumptions!$D$108)</f>
         <v>0.22</v>
       </c>
       <c r="V10" s="35" t="n">
@@ -3638,7 +3647,7 @@
         <v/>
       </c>
       <c r="U11" s="24" t="n">
-        <f aca="false">(R11+Assumptions!$D$107*E11)/(Q11+Assumptions!$D$107)</f>
+        <f aca="false">(R11+Assumptions!$D$108*E11)/(Q11+Assumptions!$D$108)</f>
         <v>0.12</v>
       </c>
       <c r="V11" s="35" t="n">
@@ -3709,7 +3718,7 @@
         <v/>
       </c>
       <c r="U12" s="24" t="n">
-        <f aca="false">(R12+Assumptions!$D$107*E12)/(Q12+Assumptions!$D$107)</f>
+        <f aca="false">(R12+Assumptions!$D$108*E12)/(Q12+Assumptions!$D$108)</f>
         <v>0.1</v>
       </c>
       <c r="V12" s="35" t="n">
@@ -3780,7 +3789,7 @@
         <v/>
       </c>
       <c r="U13" s="24" t="n">
-        <f aca="false">(R13+Assumptions!$D$107*E13)/(Q13+Assumptions!$D$107)</f>
+        <f aca="false">(R13+Assumptions!$D$108*E13)/(Q13+Assumptions!$D$108)</f>
         <v>0.3</v>
       </c>
       <c r="V13" s="35" t="n">
@@ -3851,7 +3860,7 @@
         <v/>
       </c>
       <c r="U14" s="24" t="n">
-        <f aca="false">(R14+Assumptions!$D$107*E14)/(Q14+Assumptions!$D$107)</f>
+        <f aca="false">(R14+Assumptions!$D$108*E14)/(Q14+Assumptions!$D$108)</f>
         <v>0.35</v>
       </c>
       <c r="V14" s="35" t="n">
@@ -3922,7 +3931,7 @@
         <v/>
       </c>
       <c r="U15" s="24" t="n">
-        <f aca="false">(R15+Assumptions!$D$107*E15)/(Q15+Assumptions!$D$107)</f>
+        <f aca="false">(R15+Assumptions!$D$108*E15)/(Q15+Assumptions!$D$108)</f>
         <v>0.25</v>
       </c>
       <c r="V15" s="35" t="n">
@@ -3993,7 +4002,7 @@
         <v/>
       </c>
       <c r="U16" s="24" t="n">
-        <f aca="false">(R16+Assumptions!$D$107*E16)/(Q16+Assumptions!$D$107)</f>
+        <f aca="false">(R16+Assumptions!$D$108*E16)/(Q16+Assumptions!$D$108)</f>
         <v>0.25</v>
       </c>
       <c r="V16" s="35" t="n">
@@ -4064,7 +4073,7 @@
         <v/>
       </c>
       <c r="U17" s="24" t="n">
-        <f aca="false">(R17+Assumptions!$D$107*E17)/(Q17+Assumptions!$D$107)</f>
+        <f aca="false">(R17+Assumptions!$D$108*E17)/(Q17+Assumptions!$D$108)</f>
         <v>0.25</v>
       </c>
       <c r="V17" s="35" t="n">
@@ -4135,7 +4144,7 @@
         <v/>
       </c>
       <c r="U18" s="24" t="n">
-        <f aca="false">(R18+Assumptions!$D$107*E18)/(Q18+Assumptions!$D$107)</f>
+        <f aca="false">(R18+Assumptions!$D$108*E18)/(Q18+Assumptions!$D$108)</f>
         <v>0.2</v>
       </c>
       <c r="V18" s="35" t="n">
@@ -4206,7 +4215,7 @@
         <v/>
       </c>
       <c r="U19" s="24" t="n">
-        <f aca="false">(R19+Assumptions!$D$107*E19)/(Q19+Assumptions!$D$107)</f>
+        <f aca="false">(R19+Assumptions!$D$108*E19)/(Q19+Assumptions!$D$108)</f>
         <v>0.05</v>
       </c>
       <c r="V19" s="35" t="n">
@@ -4277,7 +4286,7 @@
         <v/>
       </c>
       <c r="U20" s="24" t="n">
-        <f aca="false">(R20+Assumptions!$D$107*E20)/(Q20+Assumptions!$D$107)</f>
+        <f aca="false">(R20+Assumptions!$D$108*E20)/(Q20+Assumptions!$D$108)</f>
         <v>0.12</v>
       </c>
       <c r="V20" s="35" t="n">
@@ -4348,7 +4357,7 @@
         <v/>
       </c>
       <c r="U21" s="24" t="n">
-        <f aca="false">(R21+Assumptions!$D$107*E21)/(Q21+Assumptions!$D$107)</f>
+        <f aca="false">(R21+Assumptions!$D$108*E21)/(Q21+Assumptions!$D$108)</f>
         <v>0.15</v>
       </c>
       <c r="V21" s="35" t="n">
@@ -4419,7 +4428,7 @@
         <v/>
       </c>
       <c r="U22" s="24" t="n">
-        <f aca="false">(R22+Assumptions!$D$107*E22)/(Q22+Assumptions!$D$107)</f>
+        <f aca="false">(R22+Assumptions!$D$108*E22)/(Q22+Assumptions!$D$108)</f>
         <v>0.25</v>
       </c>
       <c r="V22" s="35" t="n">
@@ -4490,7 +4499,7 @@
         <v/>
       </c>
       <c r="U23" s="24" t="n">
-        <f aca="false">(R23+Assumptions!$D$107*E23)/(Q23+Assumptions!$D$107)</f>
+        <f aca="false">(R23+Assumptions!$D$108*E23)/(Q23+Assumptions!$D$108)</f>
         <v>0.15</v>
       </c>
       <c r="V23" s="35" t="n">
@@ -4561,7 +4570,7 @@
         <v/>
       </c>
       <c r="U24" s="24" t="n">
-        <f aca="false">(R24+Assumptions!$D$107*E24)/(Q24+Assumptions!$D$107)</f>
+        <f aca="false">(R24+Assumptions!$D$108*E24)/(Q24+Assumptions!$D$108)</f>
         <v>0.12</v>
       </c>
       <c r="V24" s="35" t="n">
@@ -4632,7 +4641,7 @@
         <v/>
       </c>
       <c r="U25" s="24" t="n">
-        <f aca="false">(R25+Assumptions!$D$107*E25)/(Q25+Assumptions!$D$107)</f>
+        <f aca="false">(R25+Assumptions!$D$108*E25)/(Q25+Assumptions!$D$108)</f>
         <v>0.5</v>
       </c>
       <c r="V25" s="35" t="n">
@@ -4703,7 +4712,7 @@
         <v/>
       </c>
       <c r="U26" s="24" t="n">
-        <f aca="false">(R26+Assumptions!$D$107*E26)/(Q26+Assumptions!$D$107)</f>
+        <f aca="false">(R26+Assumptions!$D$108*E26)/(Q26+Assumptions!$D$108)</f>
         <v>0.5</v>
       </c>
       <c r="V26" s="35" t="n">
@@ -4774,7 +4783,7 @@
         <v/>
       </c>
       <c r="U27" s="24" t="n">
-        <f aca="false">(R27+Assumptions!$D$107*E27)/(Q27+Assumptions!$D$107)</f>
+        <f aca="false">(R27+Assumptions!$D$108*E27)/(Q27+Assumptions!$D$108)</f>
         <v>0.5</v>
       </c>
       <c r="V27" s="35" t="n">
@@ -4845,7 +4854,7 @@
         <v/>
       </c>
       <c r="U28" s="24" t="n">
-        <f aca="false">(R28+Assumptions!$D$107*E28)/(Q28+Assumptions!$D$107)</f>
+        <f aca="false">(R28+Assumptions!$D$108*E28)/(Q28+Assumptions!$D$108)</f>
         <v>0.5</v>
       </c>
       <c r="V28" s="35" t="n">
@@ -4916,7 +4925,7 @@
         <v/>
       </c>
       <c r="U29" s="24" t="n">
-        <f aca="false">(R29+Assumptions!$D$107*E29)/(Q29+Assumptions!$D$107)</f>
+        <f aca="false">(R29+Assumptions!$D$108*E29)/(Q29+Assumptions!$D$108)</f>
         <v>0.45</v>
       </c>
       <c r="V29" s="35" t="n">
@@ -4987,7 +4996,7 @@
         <v/>
       </c>
       <c r="U30" s="24" t="n">
-        <f aca="false">(R30+Assumptions!$D$107*E30)/(Q30+Assumptions!$D$107)</f>
+        <f aca="false">(R30+Assumptions!$D$108*E30)/(Q30+Assumptions!$D$108)</f>
         <v>0.45</v>
       </c>
       <c r="V30" s="35" t="n">
@@ -5058,7 +5067,7 @@
         <v/>
       </c>
       <c r="U31" s="24" t="n">
-        <f aca="false">(R31+Assumptions!$D$107*E31)/(Q31+Assumptions!$D$107)</f>
+        <f aca="false">(R31+Assumptions!$D$108*E31)/(Q31+Assumptions!$D$108)</f>
         <v>0.45</v>
       </c>
       <c r="V31" s="35" t="n">
@@ -5129,7 +5138,7 @@
         <v/>
       </c>
       <c r="U32" s="24" t="n">
-        <f aca="false">(R32+Assumptions!$D$107*E32)/(Q32+Assumptions!$D$107)</f>
+        <f aca="false">(R32+Assumptions!$D$108*E32)/(Q32+Assumptions!$D$108)</f>
         <v>0.45</v>
       </c>
       <c r="V32" s="35" t="n">
@@ -5200,7 +5209,7 @@
         <v/>
       </c>
       <c r="U33" s="24" t="n">
-        <f aca="false">(R33+Assumptions!$D$107*E33)/(Q33+Assumptions!$D$107)</f>
+        <f aca="false">(R33+Assumptions!$D$108*E33)/(Q33+Assumptions!$D$108)</f>
         <v>0.15</v>
       </c>
       <c r="V33" s="35" t="n">
@@ -5271,7 +5280,7 @@
         <v/>
       </c>
       <c r="U34" s="24" t="n">
-        <f aca="false">(R34+Assumptions!$D$107*E34)/(Q34+Assumptions!$D$107)</f>
+        <f aca="false">(R34+Assumptions!$D$108*E34)/(Q34+Assumptions!$D$108)</f>
         <v>0.22</v>
       </c>
       <c r="V34" s="35" t="n">
@@ -5289,7 +5298,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="G35" s="36" t="n">
         <f aca="false">SUM(G5:G34)</f>
@@ -5342,55 +5351,55 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
       <c r="B39" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5579,7 +5588,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C44" s="29" t="n">
         <f aca="false">SUM(C40:C43)</f>
@@ -5620,7 +5629,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -5694,7 +5703,7 @@
     <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -7247,7 +7256,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>193</v>
       </c>
@@ -7264,15 +7273,15 @@
         <v>179</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>194</v>
@@ -7287,15 +7296,15 @@
         <v>179</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B80" s="13" t="s">
         <v>194</v>
@@ -7310,15 +7319,15 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>194</v>
@@ -7333,15 +7342,15 @@
         <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -7375,13 +7384,13 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D85" s="17" t="n">
         <v>500</v>
@@ -7393,110 +7402,110 @@
         <v>66</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D86" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D89" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D90" s="17" t="n">
         <v>750</v>
@@ -7508,41 +7517,41 @@
         <v>66</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D91" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>0.5</v>
@@ -7554,18 +7563,18 @@
         <v>66</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D93" s="16" t="n">
         <v>0.6</v>
@@ -7577,41 +7586,41 @@
         <v>66</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D95" s="16" t="n">
         <v>0.3</v>
@@ -7623,41 +7632,41 @@
         <v>66</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D96" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>0.35</v>
@@ -7669,18 +7678,18 @@
         <v>66</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>0.4</v>
@@ -7692,18 +7701,18 @@
         <v>66</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>0.25</v>
@@ -7715,18 +7724,18 @@
         <v>66</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>0.25</v>
@@ -7738,64 +7747,64 @@
         <v>66</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D101" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D102" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>0.25</v>
@@ -7807,18 +7816,18 @@
         <v>66</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>0.12</v>
@@ -7830,18 +7839,18 @@
         <v>66</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>0.85</v>
@@ -7853,18 +7862,18 @@
         <v>66</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>0.9</v>
@@ -7876,144 +7885,131 @@
         <v>66</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>202</v>
+        <v>40</v>
       </c>
       <c r="D107" s="15" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-      <c r="H109" s="11"/>
-      <c r="I109" s="11"/>
-      <c r="J109" s="11"/>
-      <c r="K109" s="11"/>
-      <c r="L109" s="11"/>
-    </row>
-    <row r="110" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D108" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G108" s="13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+      <c r="H110" s="11"/>
+      <c r="I110" s="11"/>
+      <c r="J110" s="11"/>
+      <c r="K110" s="11"/>
+      <c r="L110" s="11"/>
+    </row>
+    <row r="111" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B110" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="E110" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="F110" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="G110" s="12" t="s">
+      <c r="B111" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="H110" s="12" t="s">
+      <c r="C111" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="I110" s="12" t="s">
+      <c r="D111" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="J110" s="12" t="s">
+      <c r="E111" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="K110" s="12" t="s">
+      <c r="F111" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="J111" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="K111" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L110" s="12" t="s">
+      <c r="L111" s="12" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B111" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E111" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="15"/>
-      <c r="G111" s="16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="I111" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L111" s="13" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E112" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="15"/>
       <c r="G112" s="16" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I112" s="20" t="n">
         <v>1</v>
@@ -8025,31 +8021,31 @@
         <v>66</v>
       </c>
       <c r="L112" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B113" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="B113" s="13" t="s">
-        <v>292</v>
-      </c>
       <c r="C113" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E113" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F113" s="15"/>
       <c r="G113" s="16" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I113" s="20" t="n">
         <v>1</v>
@@ -8061,31 +8057,31 @@
         <v>66</v>
       </c>
       <c r="L113" s="13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E114" s="19" t="n">
         <v>0</v>
       </c>
       <c r="F114" s="15"/>
       <c r="G114" s="16" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I114" s="20" t="n">
         <v>1</v>
@@ -8097,33 +8093,31 @@
         <v>66</v>
       </c>
       <c r="L114" s="13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B115" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="E115" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F115" s="21" t="n">
-        <v>0.035</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F115" s="15"/>
       <c r="G115" s="16" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="I115" s="20" t="n">
         <v>1</v>
@@ -8132,36 +8126,36 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L115" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="L115" s="13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="116" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
         <v>305</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E116" s="19" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="F116" s="21" t="n">
-        <v>0.05</v>
+        <v>0.035</v>
       </c>
       <c r="G116" s="16" t="n">
-        <v>0.22</v>
+        <v>0.12</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="I116" s="20" t="n">
         <v>1</v>
@@ -8170,36 +8164,36 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L116" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B117" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="E117" s="19" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="F117" s="21" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G117" s="16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="I117" s="20" t="n">
         <v>1</v>
@@ -8208,36 +8202,36 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L117" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E118" s="19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F118" s="21" t="n">
         <v>0.04</v>
       </c>
       <c r="G118" s="16" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="I118" s="20" t="n">
         <v>1</v>
@@ -8246,36 +8240,36 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L118" s="13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E119" s="19" t="n">
-        <v>1449</v>
-      </c>
-      <c r="F119" s="15" t="n">
-        <v>15</v>
+        <v>1.7</v>
+      </c>
+      <c r="F119" s="21" t="n">
+        <v>0.04</v>
       </c>
       <c r="G119" s="16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="I119" s="20" t="n">
         <v>1</v>
@@ -8284,33 +8278,33 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L119" s="13" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E120" s="19" t="n">
         <v>1449</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G120" s="16" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>3</v>
@@ -8322,36 +8316,36 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L120" s="13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B121" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="E121" s="19" t="n">
         <v>1449</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G121" s="16" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I121" s="20" t="n">
         <v>1</v>
@@ -8360,24 +8354,24 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L121" s="13" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E122" s="19" t="n">
         <v>1449</v>
@@ -8398,36 +8392,36 @@
         <v>0</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L122" s="13" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="E123" s="19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F123" s="21" t="n">
-        <v>0.08</v>
+        <v>1449</v>
+      </c>
+      <c r="F123" s="15" t="n">
+        <v>15</v>
       </c>
       <c r="G123" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="I123" s="20" t="n">
         <v>1</v>
@@ -8436,24 +8430,24 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L123" s="13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E124" s="19" t="n">
         <v>3.5</v>
@@ -8462,10 +8456,10 @@
         <v>0.08</v>
       </c>
       <c r="G124" s="16" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I124" s="20" t="n">
         <v>1</v>
@@ -8474,34 +8468,36 @@
         <v>0</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>303</v>
+        <v>195</v>
       </c>
       <c r="L124" s="13" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B125" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B125" s="13" t="s">
-        <v>327</v>
-      </c>
       <c r="C125" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="E125" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="F125" s="15"/>
+        <v>3.5</v>
+      </c>
+      <c r="F125" s="21" t="n">
+        <v>0.08</v>
+      </c>
       <c r="G125" s="16" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I125" s="20" t="n">
         <v>1</v>
@@ -8510,34 +8506,34 @@
         <v>0</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="L125" s="13" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E126" s="19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F126" s="15"/>
       <c r="G126" s="16" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I126" s="20" t="n">
         <v>1</v>
@@ -8549,33 +8545,31 @@
         <v>66</v>
       </c>
       <c r="L126" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B127" s="13" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
+      <c r="C127" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B127" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="E127" s="19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F127" s="21" t="n">
-        <v>0.07</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F127" s="15"/>
       <c r="G127" s="16" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="I127" s="20" t="n">
         <v>1</v>
@@ -8587,21 +8581,21 @@
         <v>66</v>
       </c>
       <c r="L127" s="13" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E128" s="19" t="n">
         <v>2.2</v>
@@ -8610,10 +8604,10 @@
         <v>0.07</v>
       </c>
       <c r="G128" s="16" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I128" s="20" t="n">
         <v>1</v>
@@ -8625,21 +8619,21 @@
         <v>66</v>
       </c>
       <c r="L128" s="13" t="s">
-        <v>298</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E129" s="19" t="n">
         <v>2.2</v>
@@ -8648,10 +8642,10 @@
         <v>0.07</v>
       </c>
       <c r="G129" s="16" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I129" s="20" t="n">
         <v>1</v>
@@ -8663,21 +8657,21 @@
         <v>66</v>
       </c>
       <c r="L129" s="13" t="s">
-        <v>337</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E130" s="19" t="n">
         <v>2.2</v>
@@ -8686,10 +8680,10 @@
         <v>0.07</v>
       </c>
       <c r="G130" s="16" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I130" s="20" t="n">
         <v>1</v>
@@ -8701,64 +8695,79 @@
         <v>66</v>
       </c>
       <c r="L130" s="13" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="11"/>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E131" s="19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F131" s="21" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="G131" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L131" s="13" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12" t="s">
+      <c r="A133" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B133" s="12" t="s">
+      <c r="B134" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C134" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D134" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E133" s="12" t="s">
+      <c r="E134" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F133" s="12" t="s">
+      <c r="F134" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G133" s="12" t="s">
+      <c r="G134" s="12" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B134" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D134" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G134" s="13" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8766,105 +8775,105 @@
         <v>344</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D135" s="15" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B136" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B136" s="13" t="s">
-        <v>341</v>
-      </c>
       <c r="C136" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D136" s="15" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D137" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="B137" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D137" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138" s="16" t="n">
-        <v>0.12</v>
+        <v>57</v>
+      </c>
+      <c r="D138" s="15" t="n">
+        <v>80</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D139" s="16" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>46</v>
@@ -8873,159 +8882,159 @@
         <v>66</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D140" s="15" t="n">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="D140" s="16" t="n">
+        <v>0.5</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D141" s="15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D142" s="15" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B143" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B143" s="13" t="s">
-        <v>354</v>
-      </c>
       <c r="C143" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D143" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D144" s="16" t="n">
-        <v>0.45</v>
+        <v>57</v>
+      </c>
+      <c r="D144" s="15" t="n">
+        <v>8</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>46</v>
+        <v>207</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D145" s="19" t="n">
-        <v>0.5</v>
+      <c r="D145" s="16" t="n">
+        <v>0.45</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D146" s="17" t="n">
-        <v>1000</v>
+      <c r="D146" s="19" t="n">
+        <v>0.5</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>127</v>
@@ -9034,24 +9043,24 @@
         <v>66</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D147" s="20" t="n">
-        <v>1.15</v>
+      <c r="D147" s="17" t="n">
+        <v>1000</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>66</v>
@@ -9060,7 +9069,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>372</v>
       </c>
@@ -9068,243 +9077,243 @@
         <v>373</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D148" s="15" t="n">
-        <v>12000</v>
+        <v>31</v>
+      </c>
+      <c r="D148" s="20" t="n">
+        <v>1.15</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>179</v>
+        <v>374</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D149" s="21" t="n">
-        <v>0.025</v>
+      <c r="D149" s="15" t="n">
+        <v>12000</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>46</v>
+        <v>179</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D150" s="17" t="n">
-        <v>30</v>
+      <c r="D150" s="21" t="n">
+        <v>0.025</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D151" s="16" t="n">
-        <v>0.15</v>
+      <c r="D151" s="17" t="n">
+        <v>30</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D152" s="20" t="n">
-        <v>0.8</v>
+      <c r="D152" s="16" t="n">
+        <v>0.15</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>370</v>
+        <v>46</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D153" s="17" t="n">
-        <v>1200</v>
+      <c r="D153" s="20" t="n">
+        <v>0.8</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>127</v>
+        <v>374</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D154" s="17" t="n">
-        <v>12</v>
+        <v>1200</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>303</v>
+        <v>66</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D155" s="16" t="n">
-        <v>0.22</v>
+      <c r="D155" s="17" t="n">
+        <v>12</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>66</v>
+        <v>195</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D156" s="15" t="n">
-        <v>450</v>
+      <c r="D156" s="16" t="n">
+        <v>0.22</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>206</v>
+        <v>46</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D157" s="20" t="n">
-        <v>1.1</v>
+      <c r="D157" s="15" t="n">
+        <v>450</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>370</v>
+        <v>207</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D158" s="15" t="n">
-        <v>15</v>
+      <c r="D158" s="20" t="n">
+        <v>1.1</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>66</v>
@@ -9313,7 +9322,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>406</v>
       </c>
@@ -9323,31 +9332,31 @@
       <c r="C159" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D159" s="17" t="n">
-        <v>30</v>
+      <c r="D159" s="15" t="n">
+        <v>15</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>127</v>
+        <v>408</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D160" s="17" t="n">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>127</v>
@@ -9356,7 +9365,30 @@
         <v>66</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D161" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G161" s="13" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -9387,62 +9419,62 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>49</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9707,7 +9739,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -9752,17 +9784,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">Assumptions!$D$7+Assumptions!$D$19</f>
@@ -9771,7 +9803,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">Assumptions!$D$20</f>
@@ -9780,7 +9812,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">Assumptions!$D$22+Assumptions!$D$23+Assumptions!$D$24</f>
@@ -9789,7 +9821,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">B15+Assumptions!$D$25</f>
@@ -9798,7 +9830,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B14-B15</f>
@@ -9807,7 +9839,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B18" s="30" t="n">
         <f aca="false">B14-B16</f>
@@ -9834,7 +9866,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">B17-B13+1</f>
@@ -9852,7 +9884,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">O9</f>
@@ -9874,7 +9906,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B9/O9</f>
@@ -9883,54 +9915,54 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">B22*B25</f>
         <v>110.823976181854</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9958,18 +9990,18 @@
         <v>570</v>
       </c>
       <c r="G30" s="25" t="n">
-        <f aca="false">C30/F30</f>
-        <v>0.173250163579111</v>
+        <f aca="false">Pool!H5</f>
+        <v>0.0943027951580583</v>
       </c>
       <c r="H30" s="35" t="n">
         <f aca="false">_xlfn.MAXIFS(Channels!$P:$P,Channels!$C:$C,A30,Channels!$AI:$AI,"&gt;0")</f>
         <v>1000.777000777</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="K30" s="34" t="n">
         <f aca="false">(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30</f>
@@ -10001,7 +10033,7 @@
         <v>1920</v>
       </c>
       <c r="G31" s="25" t="n">
-        <f aca="false">C31/F31</f>
+        <f aca="false">Pool!H6</f>
         <v>0.054850947926232</v>
       </c>
       <c r="H31" s="35" t="n">
@@ -10009,10 +10041,10 @@
         <v>221.181512090603</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K31" s="34" t="n">
         <f aca="false">(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31</f>
@@ -10044,7 +10076,7 @@
         <v>550</v>
       </c>
       <c r="G32" s="25" t="n">
-        <f aca="false">C32/F32</f>
+        <f aca="false">Pool!H7</f>
         <v>0.0912764568764569</v>
       </c>
       <c r="H32" s="35" t="n">
@@ -10052,10 +10084,10 @@
         <v>598.290598290598</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K32" s="34" t="n">
         <f aca="false">(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32</f>
@@ -10087,7 +10119,7 @@
         <v>220</v>
       </c>
       <c r="G33" s="25" t="n">
-        <f aca="false">C33/F33</f>
+        <f aca="false">Pool!H8</f>
         <v>0.165505843971317</v>
       </c>
       <c r="H33" s="35" t="n">
@@ -10095,10 +10127,10 @@
         <v>1000</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K33" s="34" t="n">
         <f aca="false">(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33</f>
@@ -10107,7 +10139,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -10145,12 +10177,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">Assumptions!$D$66</f>
@@ -10159,33 +10191,33 @@
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">O9</f>
@@ -10212,12 +10244,12 @@
         <v>0</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B43" s="23" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -10244,12 +10276,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B44" s="23" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -10276,12 +10308,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B45" s="23" t="n">
         <f aca="false">O9</f>
@@ -10308,12 +10340,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B46" s="23" t="n">
         <f aca="false">O9</f>
@@ -10340,12 +10372,12 @@
         <v>0.3</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">O9</f>
@@ -10372,12 +10404,12 @@
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="22" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D49" s="8" t="str">
         <f aca="false">INDEX(A43:A47,MATCH(MAX(E43:E47),E43:E47,0))</f>
@@ -10386,7 +10418,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -10435,42 +10467,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10655,7 +10687,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -10713,17 +10745,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>50</v>
@@ -10738,27 +10770,27 @@
         <v>57</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B5" s="23" t="n">
-        <f aca="false">Assumptions!$D$134</f>
+        <f aca="false">Assumptions!$D$135</f>
         <v>200</v>
       </c>
       <c r="C5" s="23" t="n">
-        <f aca="false">Assumptions!$D$135</f>
+        <f aca="false">Assumptions!$D$136</f>
         <v>300</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">Assumptions!$D$136</f>
+        <f aca="false">Assumptions!$D$137</f>
         <v>120</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">Assumptions!$D$137</f>
+        <f aca="false">Assumptions!$D$138</f>
         <v>80</v>
       </c>
       <c r="F5" s="27" t="n">
@@ -10768,28 +10800,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B6" s="24" t="n">
-        <f aca="false">Assumptions!$D$138</f>
+        <f aca="false">Assumptions!$D$139</f>
         <v>0.12</v>
       </c>
       <c r="C6" s="24" t="n">
-        <f aca="false">Assumptions!$D$138</f>
+        <f aca="false">Assumptions!$D$139</f>
         <v>0.12</v>
       </c>
       <c r="D6" s="24" t="n">
-        <f aca="false">Assumptions!$D$138</f>
+        <f aca="false">Assumptions!$D$139</f>
         <v>0.12</v>
       </c>
       <c r="E6" s="24" t="n">
-        <f aca="false">Assumptions!$D$138</f>
+        <f aca="false">Assumptions!$D$139</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">B5*B6</f>
@@ -10814,64 +10846,64 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B8" s="24" t="n">
-        <f aca="false">Assumptions!$D$139</f>
+        <f aca="false">Assumptions!$D$140</f>
         <v>0.5</v>
       </c>
       <c r="C8" s="24" t="n">
-        <f aca="false">Assumptions!$D$139</f>
+        <f aca="false">Assumptions!$D$140</f>
         <v>0.5</v>
       </c>
       <c r="D8" s="24" t="n">
-        <f aca="false">Assumptions!$D$139</f>
+        <f aca="false">Assumptions!$D$140</f>
         <v>0.5</v>
       </c>
       <c r="E8" s="24" t="n">
-        <f aca="false">Assumptions!$D$139</f>
+        <f aca="false">Assumptions!$D$140</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B9" s="25" t="n">
-        <f aca="false">Funnel!$G$5*Assumptions!$D$147</f>
+        <f aca="false">Funnel!$G$5*Assumptions!$D$148</f>
         <v>0.3700125</v>
       </c>
       <c r="C9" s="25" t="n">
-        <f aca="false">Funnel!$G$6*Assumptions!$D$147</f>
+        <f aca="false">Funnel!$G$6*Assumptions!$D$148</f>
         <v>0.46575</v>
       </c>
       <c r="D9" s="25" t="n">
-        <f aca="false">Funnel!$G$7*Assumptions!$D$147</f>
+        <f aca="false">Funnel!$G$7*Assumptions!$D$148</f>
         <v>0.336375</v>
       </c>
       <c r="E9" s="25" t="n">
-        <f aca="false">Funnel!$G$8*Assumptions!$D$147</f>
+        <f aca="false">Funnel!$G$8*Assumptions!$D$148</f>
         <v>0.3079125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B10" s="35" t="n">
-        <f aca="false">B5*Assumptions!$D$145</f>
+        <f aca="false">B5*Assumptions!$D$146</f>
         <v>100</v>
       </c>
       <c r="C10" s="35" t="n">
-        <f aca="false">C5*Assumptions!$D$145</f>
+        <f aca="false">C5*Assumptions!$D$146</f>
         <v>150</v>
       </c>
       <c r="D10" s="35" t="n">
-        <f aca="false">D5*Assumptions!$D$145</f>
+        <f aca="false">D5*Assumptions!$D$146</f>
         <v>60</v>
       </c>
       <c r="E10" s="35" t="n">
-        <f aca="false">E5*Assumptions!$D$145</f>
+        <f aca="false">E5*Assumptions!$D$146</f>
         <v>40</v>
       </c>
       <c r="F10" s="36" t="n">
@@ -10881,7 +10913,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B11" s="37" t="n">
         <f aca="false">B10/B7</f>
@@ -10900,12 +10932,12 @@
         <v>4.16666666666667</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B7*B8*B9</f>
@@ -10930,22 +10962,22 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B13" s="26" t="n">
-        <f aca="false">Assumptions!$D$140</f>
+        <f aca="false">Assumptions!$D$141</f>
         <v>25</v>
       </c>
       <c r="C13" s="26" t="n">
-        <f aca="false">Assumptions!$D$141</f>
+        <f aca="false">Assumptions!$D$142</f>
         <v>30</v>
       </c>
       <c r="D13" s="26" t="n">
-        <f aca="false">Assumptions!$D$142</f>
+        <f aca="false">Assumptions!$D$143</f>
         <v>10</v>
       </c>
       <c r="E13" s="26" t="n">
-        <f aca="false">Assumptions!$D$143</f>
+        <f aca="false">Assumptions!$D$144</f>
         <v>8</v>
       </c>
       <c r="F13" s="29" t="n">
@@ -10955,28 +10987,28 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B14" s="24" t="n">
-        <f aca="false">Assumptions!$D$144</f>
+        <f aca="false">Assumptions!$D$145</f>
         <v>0.45</v>
       </c>
       <c r="C14" s="24" t="n">
-        <f aca="false">Assumptions!$D$144</f>
+        <f aca="false">Assumptions!$D$145</f>
         <v>0.45</v>
       </c>
       <c r="D14" s="24" t="n">
-        <f aca="false">Assumptions!$D$144</f>
+        <f aca="false">Assumptions!$D$145</f>
         <v>0.45</v>
       </c>
       <c r="E14" s="24" t="n">
-        <f aca="false">Assumptions!$D$144</f>
+        <f aca="false">Assumptions!$D$145</f>
         <v>0.45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B13*B14*B9</f>
@@ -11001,22 +11033,22 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B16" s="35" t="n">
-        <f aca="false">B15*Assumptions!$D$146</f>
+        <f aca="false">B15*Assumptions!$D$147</f>
         <v>4162.640625</v>
       </c>
       <c r="C16" s="35" t="n">
-        <f aca="false">C15*Assumptions!$D$146</f>
+        <f aca="false">C15*Assumptions!$D$147</f>
         <v>6287.625</v>
       </c>
       <c r="D16" s="35" t="n">
-        <f aca="false">D15*Assumptions!$D$146</f>
+        <f aca="false">D15*Assumptions!$D$147</f>
         <v>1513.6875</v>
       </c>
       <c r="E16" s="35" t="n">
-        <f aca="false">E15*Assumptions!$D$146</f>
+        <f aca="false">E15*Assumptions!$D$147</f>
         <v>1108.485</v>
       </c>
       <c r="F16" s="36" t="n">
@@ -11026,7 +11058,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B17" s="37" t="n">
         <f aca="false">B16/B13</f>
@@ -11045,12 +11077,12 @@
         <v>138.560625</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B12+B15</f>
@@ -11075,7 +11107,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">B10+B16</f>
@@ -11100,7 +11132,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B20" s="35" t="n">
         <f aca="false">B19/B18</f>
@@ -11125,30 +11157,30 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B24" s="23" t="n">
-        <f aca="false">Assumptions!$D$148</f>
+        <f aca="false">Assumptions!$D$149</f>
         <v>12000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B25" s="25" t="n">
-        <f aca="false">Assumptions!$D$149</f>
+        <f aca="false">Assumptions!$D$150</f>
         <v>0.025</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">B24*B25</f>
@@ -11157,25 +11189,25 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B27" s="35" t="n">
-        <f aca="false">Assumptions!$D$150</f>
+        <f aca="false">Assumptions!$D$151</f>
         <v>30</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B28" s="24" t="n">
-        <f aca="false">Assumptions!$D$151</f>
+        <f aca="false">Assumptions!$D$152</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B26*B28</f>
@@ -11184,16 +11216,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B30" s="25" t="n">
-        <f aca="false">Funnel!$G$5*Assumptions!$D$152</f>
+        <f aca="false">Funnel!$G$5*Assumptions!$D$153</f>
         <v>0.2574</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B31" s="26" t="n">
         <f aca="false">B29*B30</f>
@@ -11202,7 +11234,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B32" s="35" t="n">
         <f aca="false">B26*B27</f>
@@ -11211,16 +11243,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B33" s="35" t="n">
-        <f aca="false">Assumptions!$D$153</f>
+        <f aca="false">Assumptions!$D$154</f>
         <v>1200</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B34" s="35" t="n">
         <f aca="false">(B32+B33)/B31</f>
@@ -11229,12 +11261,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B38" s="37" t="n">
         <f aca="false">B44+B45</f>
@@ -11243,34 +11275,34 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B39" s="24" t="n">
-        <f aca="false">Assumptions!$D$155</f>
+        <f aca="false">Assumptions!$D$156</f>
         <v>0.22</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B40" s="23" t="n">
-        <f aca="false">Assumptions!$D$156</f>
+        <f aca="false">Assumptions!$D$157</f>
         <v>450</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B41" s="25" t="n">
-        <f aca="false">Funnel!$G$6*Assumptions!$D$157</f>
+        <f aca="false">Funnel!$G$6*Assumptions!$D$158</f>
         <v>0.4455</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">Assumptions!$D$10*Assumptions!$D$12</f>
@@ -11279,7 +11311,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B43" s="26" t="n">
         <f aca="false">MIN(B40*B39*B41,B42)</f>
@@ -11288,34 +11320,34 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B44" s="37" t="n">
-        <f aca="false">Assumptions!$D$154</f>
+        <f aca="false">Assumptions!$D$155</f>
         <v>12</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B45" s="37" t="n">
-        <f aca="false">Assumptions!$D$158/60*Assumptions!$D$159</f>
+        <f aca="false">Assumptions!$D$159/60*Assumptions!$D$160</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B46" s="35" t="n">
-        <f aca="false">Assumptions!$D$160</f>
+        <f aca="false">Assumptions!$D$161</f>
         <v>400</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">B43/B41/B39</f>
@@ -11324,7 +11356,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B48" s="35" t="n">
         <f aca="false">(B47*B38+B46)/B43</f>
@@ -11333,50 +11365,50 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">(Assumptions!$D$97+Assumptions!$D$98)</f>
@@ -11391,44 +11423,44 @@
         <v>32.515726383307</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="G53" s="23" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E53*Assumptions!$D$93,0))</f>
         <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="I53" s="23" t="n">
         <f aca="false">MAX(1,ROUNDUP(E53*Assumptions!$D$95,0))</f>
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C54" s="24" t="n">
-        <f aca="false">(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>0.28</v>
+        <f aca="false">(Assumptions!$D$55*4/7+Assumptions!$D$56+Assumptions!$D$57*4/7)</f>
+        <v>0.181428571428571</v>
       </c>
       <c r="D54" s="35" t="n">
-        <f aca="false">B33+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I2-E")*(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>3720</v>
+        <f aca="false">B33+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I2-E")*C54</f>
+        <v>2832.85714285714</v>
       </c>
       <c r="E54" s="26" t="n">
-        <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E")*(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>12.6</v>
+        <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E")*C54</f>
+        <v>8.16428571428572</v>
       </c>
       <c r="F54" s="35" t="n">
         <f aca="false">B27/B28</f>
@@ -11436,7 +11468,7 @@
       </c>
       <c r="G54" s="23" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E54*Assumptions!$D$93,0))</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H54" s="35" t="n">
         <f aca="false">ROUND(F54*Assumptions!$D$94/10,0)*10</f>
@@ -11444,34 +11476,34 @@
       </c>
       <c r="I54" s="23" t="n">
         <f aca="false">MAX(1,ROUNDUP(E54*Assumptions!$D$95,0))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J54" s="35" t="n">
         <f aca="false">ROUND(F54*Assumptions!$D$96/10,0)*10</f>
         <v>300</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C55" s="24" t="n">
-        <f aca="false">(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>0.28</v>
+        <f aca="false">(Assumptions!$D$56+Assumptions!$D$57)</f>
+        <v>0.25</v>
       </c>
       <c r="D55" s="35" t="n">
-        <f aca="false">B46+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I3-M")*(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>1168.69133483596</v>
+        <f aca="false">B46+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I3-M")*C55</f>
+        <v>1086.33154896068</v>
       </c>
       <c r="E55" s="26" t="n">
-        <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I3-M")*(Assumptions!$D$55+Assumptions!$D$56+Assumptions!$D$57)</f>
-        <v>8.67241505968779</v>
+        <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I3-M")*C55</f>
+        <v>7.7432277318641</v>
       </c>
       <c r="F55" s="35" t="n">
         <f aca="false">B38/B39</f>
@@ -11479,7 +11511,7 @@
       </c>
       <c r="G55" s="23" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E55*Assumptions!$D$93,0))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H55" s="35" t="n">
         <f aca="false">ROUND(F55*Assumptions!$D$94/10,0)*10</f>
@@ -11494,12 +11526,12 @@
         <v>130</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -11533,17 +11565,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11551,134 +11583,134 @@
         <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AI4" s="12" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="str">
-        <f aca="false">Assumptions!A111</f>
+        <f aca="false">Assumptions!A112</f>
         <v>C01</v>
       </c>
       <c r="B5" s="2" t="str">
-        <f aca="false">Assumptions!B111</f>
+        <f aca="false">Assumptions!B112</f>
         <v>Organic (Tesla careers, BA Jobbörse, Google for Jobs)</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f aca="false">Assumptions!C111</f>
+        <f aca="false">Assumptions!C112</f>
         <v>Electricians</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f aca="false">Assumptions!D111</f>
+        <f aca="false">Assumptions!D112</f>
         <v>Free</v>
       </c>
       <c r="F5" s="37" t="n">
-        <f aca="false">Assumptions!E111</f>
+        <f aca="false">Assumptions!E112</f>
         <v>0</v>
       </c>
       <c r="G5" s="23" t="str">
-        <f aca="false">IF(E5="Free","",Assumptions!F111)</f>
+        <f aca="false">IF(E5="Free","",Assumptions!F112)</f>
         <v/>
       </c>
       <c r="H5" s="37" t="n">
@@ -11686,11 +11718,11 @@
         <v>0</v>
       </c>
       <c r="I5" s="24" t="n">
-        <f aca="false">Assumptions!G111</f>
+        <f aca="false">Assumptions!G112</f>
         <v>0.08</v>
       </c>
       <c r="J5" s="23" t="n">
-        <f aca="false">IF(E5="Slot",Assumptions!H111*G5,Assumptions!H111)</f>
+        <f aca="false">IF(E5="Slot",Assumptions!H112*G5,Assumptions!H112)</f>
         <v>150</v>
       </c>
       <c r="K5" s="26" t="n">
@@ -11702,7 +11734,7 @@
         <v>0.32175</v>
       </c>
       <c r="M5" s="38" t="n">
-        <f aca="false">Assumptions!I111</f>
+        <f aca="false">Assumptions!I112</f>
         <v>1</v>
       </c>
       <c r="N5" s="26" t="n">
@@ -11714,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="35" t="n">
-        <f aca="false">IF(N5&gt;0,(N5/L5/I5*H5+Assumptions!J111)/N5,0)</f>
+        <f aca="false">IF(N5&gt;0,(N5/L5/I5*H5+Assumptions!J112)/N5,0)</f>
         <v>0</v>
       </c>
       <c r="Q5" s="39" t="n">
@@ -11750,7 +11782,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="35" t="n">
-        <f aca="false">IF(U5&gt;0,Assumptions!J111,0)</f>
+        <f aca="false">IF(U5&gt;0,Assumptions!J112,0)</f>
         <v>0</v>
       </c>
       <c r="Z5" s="35" t="n">
@@ -11796,30 +11828,30 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="str">
-        <f aca="false">Assumptions!A112</f>
+        <f aca="false">Assumptions!A113</f>
         <v>C02</v>
       </c>
       <c r="B6" s="2" t="str">
-        <f aca="false">Assumptions!B112</f>
+        <f aca="false">Assumptions!B113</f>
         <v>Organic (Tesla careers, BA Jobbörse, Google for Jobs)</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f aca="false">Assumptions!C112</f>
+        <f aca="false">Assumptions!C113</f>
         <v>Mechatronics</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E6" s="2" t="str">
-        <f aca="false">Assumptions!D112</f>
+        <f aca="false">Assumptions!D113</f>
         <v>Free</v>
       </c>
       <c r="F6" s="37" t="n">
-        <f aca="false">Assumptions!E112</f>
+        <f aca="false">Assumptions!E113</f>
         <v>0</v>
       </c>
       <c r="G6" s="23" t="str">
-        <f aca="false">IF(E6="Free","",Assumptions!F112)</f>
+        <f aca="false">IF(E6="Free","",Assumptions!F113)</f>
         <v/>
       </c>
       <c r="H6" s="37" t="n">
@@ -11827,11 +11859,11 @@
         <v>0</v>
       </c>
       <c r="I6" s="24" t="n">
-        <f aca="false">Assumptions!G112</f>
+        <f aca="false">Assumptions!G113</f>
         <v>0.18</v>
       </c>
       <c r="J6" s="23" t="n">
-        <f aca="false">IF(E6="Slot",Assumptions!H112*G6,Assumptions!H112)</f>
+        <f aca="false">IF(E6="Slot",Assumptions!H113*G6,Assumptions!H113)</f>
         <v>200</v>
       </c>
       <c r="K6" s="26" t="n">
@@ -11843,7 +11875,7 @@
         <v>0.405</v>
       </c>
       <c r="M6" s="38" t="n">
-        <f aca="false">Assumptions!I112</f>
+        <f aca="false">Assumptions!I113</f>
         <v>1</v>
       </c>
       <c r="N6" s="26" t="n">
@@ -11855,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="35" t="n">
-        <f aca="false">IF(N6&gt;0,(N6/L6/I6*H6+Assumptions!J112)/N6,0)</f>
+        <f aca="false">IF(N6&gt;0,(N6/L6/I6*H6+Assumptions!J113)/N6,0)</f>
         <v>0</v>
       </c>
       <c r="Q6" s="39" t="n">
@@ -11891,7 +11923,7 @@
         <v>0</v>
       </c>
       <c r="Y6" s="35" t="n">
-        <f aca="false">IF(U6&gt;0,Assumptions!J112,0)</f>
+        <f aca="false">IF(U6&gt;0,Assumptions!J113,0)</f>
         <v>0</v>
       </c>
       <c r="Z6" s="35" t="n">
@@ -11937,30 +11969,30 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="str">
-        <f aca="false">Assumptions!A113</f>
+        <f aca="false">Assumptions!A114</f>
         <v>C03</v>
       </c>
       <c r="B7" s="2" t="str">
-        <f aca="false">Assumptions!B113</f>
+        <f aca="false">Assumptions!B114</f>
         <v>Organic (Tesla careers, BA Jobbörse, Google for Jobs)</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f aca="false">Assumptions!C113</f>
+        <f aca="false">Assumptions!C114</f>
         <v>Automation</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f aca="false">Assumptions!D113</f>
+        <f aca="false">Assumptions!D114</f>
         <v>Free</v>
       </c>
       <c r="F7" s="37" t="n">
-        <f aca="false">Assumptions!E113</f>
+        <f aca="false">Assumptions!E114</f>
         <v>0</v>
       </c>
       <c r="G7" s="23" t="str">
-        <f aca="false">IF(E7="Free","",Assumptions!F113)</f>
+        <f aca="false">IF(E7="Free","",Assumptions!F114)</f>
         <v/>
       </c>
       <c r="H7" s="37" t="n">
@@ -11968,11 +12000,11 @@
         <v>0</v>
       </c>
       <c r="I7" s="24" t="n">
-        <f aca="false">Assumptions!G113</f>
+        <f aca="false">Assumptions!G114</f>
         <v>0.1</v>
       </c>
       <c r="J7" s="23" t="n">
-        <f aca="false">IF(E7="Slot",Assumptions!H113*G7,Assumptions!H113)</f>
+        <f aca="false">IF(E7="Slot",Assumptions!H114*G7,Assumptions!H114)</f>
         <v>80</v>
       </c>
       <c r="K7" s="26" t="n">
@@ -11984,7 +12016,7 @@
         <v>0.2925</v>
       </c>
       <c r="M7" s="38" t="n">
-        <f aca="false">Assumptions!I113</f>
+        <f aca="false">Assumptions!I114</f>
         <v>1</v>
       </c>
       <c r="N7" s="26" t="n">
@@ -11996,7 +12028,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="35" t="n">
-        <f aca="false">IF(N7&gt;0,(N7/L7/I7*H7+Assumptions!J113)/N7,0)</f>
+        <f aca="false">IF(N7&gt;0,(N7/L7/I7*H7+Assumptions!J114)/N7,0)</f>
         <v>0</v>
       </c>
       <c r="Q7" s="39" t="n">
@@ -12032,7 +12064,7 @@
         <v>0</v>
       </c>
       <c r="Y7" s="35" t="n">
-        <f aca="false">IF(U7&gt;0,Assumptions!J113,0)</f>
+        <f aca="false">IF(U7&gt;0,Assumptions!J114,0)</f>
         <v>0</v>
       </c>
       <c r="Z7" s="35" t="n">
@@ -12078,30 +12110,30 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="str">
-        <f aca="false">Assumptions!A114</f>
+        <f aca="false">Assumptions!A115</f>
         <v>C04</v>
       </c>
       <c r="B8" s="2" t="str">
-        <f aca="false">Assumptions!B114</f>
+        <f aca="false">Assumptions!B115</f>
         <v>Organic (Tesla careers, BA Jobbörse, Google for Jobs)</v>
       </c>
       <c r="C8" s="2" t="str">
-        <f aca="false">Assumptions!C114</f>
+        <f aca="false">Assumptions!C115</f>
         <v>Supervisors</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f aca="false">Assumptions!D114</f>
+        <f aca="false">Assumptions!D115</f>
         <v>Free</v>
       </c>
       <c r="F8" s="37" t="n">
-        <f aca="false">Assumptions!E114</f>
+        <f aca="false">Assumptions!E115</f>
         <v>0</v>
       </c>
       <c r="G8" s="23" t="str">
-        <f aca="false">IF(E8="Free","",Assumptions!F114)</f>
+        <f aca="false">IF(E8="Free","",Assumptions!F115)</f>
         <v/>
       </c>
       <c r="H8" s="37" t="n">
@@ -12109,11 +12141,11 @@
         <v>0</v>
       </c>
       <c r="I8" s="24" t="n">
-        <f aca="false">Assumptions!G114</f>
+        <f aca="false">Assumptions!G115</f>
         <v>0.08</v>
       </c>
       <c r="J8" s="23" t="n">
-        <f aca="false">IF(E8="Slot",Assumptions!H114*G8,Assumptions!H114)</f>
+        <f aca="false">IF(E8="Slot",Assumptions!H115*G8,Assumptions!H115)</f>
         <v>60</v>
       </c>
       <c r="K8" s="26" t="n">
@@ -12125,7 +12157,7 @@
         <v>0.26775</v>
       </c>
       <c r="M8" s="38" t="n">
-        <f aca="false">Assumptions!I114</f>
+        <f aca="false">Assumptions!I115</f>
         <v>1</v>
       </c>
       <c r="N8" s="26" t="n">
@@ -12137,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="35" t="n">
-        <f aca="false">IF(N8&gt;0,(N8/L8/I8*H8+Assumptions!J114)/N8,0)</f>
+        <f aca="false">IF(N8&gt;0,(N8/L8/I8*H8+Assumptions!J115)/N8,0)</f>
         <v>0</v>
       </c>
       <c r="Q8" s="39" t="n">
@@ -12173,7 +12205,7 @@
         <v>0</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <f aca="false">IF(U8&gt;0,Assumptions!J114,0)</f>
+        <f aca="false">IF(U8&gt;0,Assumptions!J115,0)</f>
         <v>0</v>
       </c>
       <c r="Z8" s="35" t="n">
@@ -12219,30 +12251,30 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="str">
-        <f aca="false">Assumptions!A115</f>
+        <f aca="false">Assumptions!A116</f>
         <v>C05</v>
       </c>
       <c r="B9" s="2" t="str">
-        <f aca="false">Assumptions!B115</f>
+        <f aca="false">Assumptions!B116</f>
         <v>Programmatic job ads (Joveo: Indeed, Jooble, Talent.com, Kimeta, meinestadt…)</v>
       </c>
       <c r="C9" s="2" t="str">
-        <f aca="false">Assumptions!C115</f>
+        <f aca="false">Assumptions!C116</f>
         <v>Electricians</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f aca="false">Assumptions!D115</f>
+        <f aca="false">Assumptions!D116</f>
         <v>CPC</v>
       </c>
       <c r="F9" s="37" t="n">
-        <f aca="false">Assumptions!E115</f>
+        <f aca="false">Assumptions!E116</f>
         <v>2</v>
       </c>
       <c r="G9" s="25" t="n">
-        <f aca="false">IF(E9="Free","",Assumptions!F115)</f>
+        <f aca="false">IF(E9="Free","",Assumptions!F116)</f>
         <v>0.035</v>
       </c>
       <c r="H9" s="37" t="n">
@@ -12250,11 +12282,11 @@
         <v>57.1428571428571</v>
       </c>
       <c r="I9" s="24" t="n">
-        <f aca="false">Assumptions!G115</f>
+        <f aca="false">Assumptions!G116</f>
         <v>0.12</v>
       </c>
       <c r="J9" s="23" t="n">
-        <f aca="false">IF(E9="Slot",Assumptions!H115*G9,Assumptions!H115)</f>
+        <f aca="false">IF(E9="Slot",Assumptions!H116*G9,Assumptions!H116)</f>
         <v>450</v>
       </c>
       <c r="K9" s="26" t="n">
@@ -12266,7 +12298,7 @@
         <v>0.32175</v>
       </c>
       <c r="M9" s="38" t="n">
-        <f aca="false">Assumptions!I115</f>
+        <f aca="false">Assumptions!I116</f>
         <v>1</v>
       </c>
       <c r="N9" s="26" t="n">
@@ -12278,7 +12310,7 @@
         <v>476.190476190476</v>
       </c>
       <c r="P9" s="35" t="n">
-        <f aca="false">IF(N9&gt;0,(N9/L9/I9*H9+Assumptions!J115)/N9,0)</f>
+        <f aca="false">IF(N9&gt;0,(N9/L9/I9*H9+Assumptions!J116)/N9,0)</f>
         <v>1480.00148000148</v>
       </c>
       <c r="Q9" s="39" t="n">
@@ -12314,7 +12346,7 @@
         <v>750</v>
       </c>
       <c r="Y9" s="35" t="n">
-        <f aca="false">IF(U9&gt;0,Assumptions!J115,0)</f>
+        <f aca="false">IF(U9&gt;0,Assumptions!J116,0)</f>
         <v>0</v>
       </c>
       <c r="Z9" s="35" t="n">
@@ -12360,30 +12392,30 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="str">
-        <f aca="false">Assumptions!A116</f>
+        <f aca="false">Assumptions!A117</f>
         <v>C06</v>
       </c>
       <c r="B10" s="2" t="str">
-        <f aca="false">Assumptions!B116</f>
+        <f aca="false">Assumptions!B117</f>
         <v>Programmatic job ads (Joveo: Indeed, Jooble, Talent.com, Kimeta, meinestadt…)</v>
       </c>
       <c r="C10" s="2" t="str">
-        <f aca="false">Assumptions!C116</f>
+        <f aca="false">Assumptions!C117</f>
         <v>Mechatronics</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f aca="false">Assumptions!D116</f>
+        <f aca="false">Assumptions!D117</f>
         <v>CPC</v>
       </c>
       <c r="F10" s="37" t="n">
-        <f aca="false">Assumptions!E116</f>
+        <f aca="false">Assumptions!E117</f>
         <v>1.2</v>
       </c>
       <c r="G10" s="25" t="n">
-        <f aca="false">IF(E10="Free","",Assumptions!F116)</f>
+        <f aca="false">IF(E10="Free","",Assumptions!F117)</f>
         <v>0.05</v>
       </c>
       <c r="H10" s="37" t="n">
@@ -12391,11 +12423,11 @@
         <v>24</v>
       </c>
       <c r="I10" s="24" t="n">
-        <f aca="false">Assumptions!G116</f>
+        <f aca="false">Assumptions!G117</f>
         <v>0.22</v>
       </c>
       <c r="J10" s="23" t="n">
-        <f aca="false">IF(E10="Slot",Assumptions!H116*G10,Assumptions!H116)</f>
+        <f aca="false">IF(E10="Slot",Assumptions!H117*G10,Assumptions!H117)</f>
         <v>600</v>
       </c>
       <c r="K10" s="26" t="n">
@@ -12407,7 +12439,7 @@
         <v>0.405</v>
       </c>
       <c r="M10" s="38" t="n">
-        <f aca="false">Assumptions!I116</f>
+        <f aca="false">Assumptions!I117</f>
         <v>1</v>
       </c>
       <c r="N10" s="26" t="n">
@@ -12419,7 +12451,7 @@
         <v>109.090909090909</v>
       </c>
       <c r="P10" s="35" t="n">
-        <f aca="false">IF(N10&gt;0,(N10/L10/I10*H10+Assumptions!J116)/N10,0)</f>
+        <f aca="false">IF(N10&gt;0,(N10/L10/I10*H10+Assumptions!J117)/N10,0)</f>
         <v>269.360269360269</v>
       </c>
       <c r="Q10" s="39" t="n">
@@ -12455,7 +12487,7 @@
         <v>750</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <f aca="false">IF(U10&gt;0,Assumptions!J116,0)</f>
+        <f aca="false">IF(U10&gt;0,Assumptions!J117,0)</f>
         <v>0</v>
       </c>
       <c r="Z10" s="35" t="n">
@@ -12501,30 +12533,30 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="str">
-        <f aca="false">Assumptions!A117</f>
+        <f aca="false">Assumptions!A118</f>
         <v>C07</v>
       </c>
       <c r="B11" s="2" t="str">
-        <f aca="false">Assumptions!B117</f>
+        <f aca="false">Assumptions!B118</f>
         <v>Programmatic job ads (Joveo: Indeed, Jooble, Talent.com, Kimeta, meinestadt…)</v>
       </c>
       <c r="C11" s="2" t="str">
-        <f aca="false">Assumptions!C117</f>
+        <f aca="false">Assumptions!C118</f>
         <v>Automation</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f aca="false">Assumptions!D117</f>
+        <f aca="false">Assumptions!D118</f>
         <v>CPC</v>
       </c>
       <c r="F11" s="37" t="n">
-        <f aca="false">Assumptions!E117</f>
+        <f aca="false">Assumptions!E118</f>
         <v>1.8</v>
       </c>
       <c r="G11" s="25" t="n">
-        <f aca="false">IF(E11="Free","",Assumptions!F117)</f>
+        <f aca="false">IF(E11="Free","",Assumptions!F118)</f>
         <v>0.04</v>
       </c>
       <c r="H11" s="37" t="n">
@@ -12532,11 +12564,11 @@
         <v>45</v>
       </c>
       <c r="I11" s="24" t="n">
-        <f aca="false">Assumptions!G117</f>
+        <f aca="false">Assumptions!G118</f>
         <v>0.12</v>
       </c>
       <c r="J11" s="23" t="n">
-        <f aca="false">IF(E11="Slot",Assumptions!H117*G11,Assumptions!H117)</f>
+        <f aca="false">IF(E11="Slot",Assumptions!H118*G11,Assumptions!H118)</f>
         <v>250</v>
       </c>
       <c r="K11" s="26" t="n">
@@ -12548,7 +12580,7 @@
         <v>0.2925</v>
       </c>
       <c r="M11" s="38" t="n">
-        <f aca="false">Assumptions!I117</f>
+        <f aca="false">Assumptions!I118</f>
         <v>1</v>
       </c>
       <c r="N11" s="26" t="n">
@@ -12560,7 +12592,7 @@
         <v>375</v>
       </c>
       <c r="P11" s="35" t="n">
-        <f aca="false">IF(N11&gt;0,(N11/L11/I11*H11+Assumptions!J117)/N11,0)</f>
+        <f aca="false">IF(N11&gt;0,(N11/L11/I11*H11+Assumptions!J118)/N11,0)</f>
         <v>1282.05128205128</v>
       </c>
       <c r="Q11" s="39" t="n">
@@ -12596,7 +12628,7 @@
         <v>750</v>
       </c>
       <c r="Y11" s="35" t="n">
-        <f aca="false">IF(U11&gt;0,Assumptions!J117,0)</f>
+        <f aca="false">IF(U11&gt;0,Assumptions!J118,0)</f>
         <v>0</v>
       </c>
       <c r="Z11" s="35" t="n">
@@ -12642,30 +12674,30 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="str">
-        <f aca="false">Assumptions!A118</f>
+        <f aca="false">Assumptions!A119</f>
         <v>C08</v>
       </c>
       <c r="B12" s="2" t="str">
-        <f aca="false">Assumptions!B118</f>
+        <f aca="false">Assumptions!B119</f>
         <v>Programmatic job ads (Joveo: Indeed, Jooble, Talent.com, Kimeta, meinestadt…)</v>
       </c>
       <c r="C12" s="2" t="str">
-        <f aca="false">Assumptions!C118</f>
+        <f aca="false">Assumptions!C119</f>
         <v>Supervisors</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f aca="false">Assumptions!D118</f>
+        <f aca="false">Assumptions!D119</f>
         <v>CPC</v>
       </c>
       <c r="F12" s="37" t="n">
-        <f aca="false">Assumptions!E118</f>
+        <f aca="false">Assumptions!E119</f>
         <v>1.7</v>
       </c>
       <c r="G12" s="25" t="n">
-        <f aca="false">IF(E12="Free","",Assumptions!F118)</f>
+        <f aca="false">IF(E12="Free","",Assumptions!F119)</f>
         <v>0.04</v>
       </c>
       <c r="H12" s="37" t="n">
@@ -12673,11 +12705,11 @@
         <v>42.5</v>
       </c>
       <c r="I12" s="24" t="n">
-        <f aca="false">Assumptions!G118</f>
+        <f aca="false">Assumptions!G119</f>
         <v>0.1</v>
       </c>
       <c r="J12" s="23" t="n">
-        <f aca="false">IF(E12="Slot",Assumptions!H118*G12,Assumptions!H118)</f>
+        <f aca="false">IF(E12="Slot",Assumptions!H119*G12,Assumptions!H119)</f>
         <v>200</v>
       </c>
       <c r="K12" s="26" t="n">
@@ -12689,7 +12721,7 @@
         <v>0.26775</v>
       </c>
       <c r="M12" s="38" t="n">
-        <f aca="false">Assumptions!I118</f>
+        <f aca="false">Assumptions!I119</f>
         <v>1</v>
       </c>
       <c r="N12" s="26" t="n">
@@ -12701,7 +12733,7 @@
         <v>425</v>
       </c>
       <c r="P12" s="35" t="n">
-        <f aca="false">IF(N12&gt;0,(N12/L12/I12*H12+Assumptions!J118)/N12,0)</f>
+        <f aca="false">IF(N12&gt;0,(N12/L12/I12*H12+Assumptions!J119)/N12,0)</f>
         <v>1587.30158730159</v>
       </c>
       <c r="Q12" s="39" t="n">
@@ -12737,7 +12769,7 @@
         <v>750</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <f aca="false">IF(U12&gt;0,Assumptions!J118,0)</f>
+        <f aca="false">IF(U12&gt;0,Assumptions!J119,0)</f>
         <v>0</v>
       </c>
       <c r="Z12" s="35" t="n">
@@ -12783,30 +12815,30 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="str">
-        <f aca="false">Assumptions!A119</f>
+        <f aca="false">Assumptions!A120</f>
         <v>C09</v>
       </c>
       <c r="B13" s="2" t="str">
-        <f aca="false">Assumptions!B119</f>
+        <f aca="false">Assumptions!B120</f>
         <v>StepStone (30-day single ad)</v>
       </c>
       <c r="C13" s="2" t="str">
-        <f aca="false">Assumptions!C119</f>
+        <f aca="false">Assumptions!C120</f>
         <v>Electricians</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f aca="false">Assumptions!D119</f>
+        <f aca="false">Assumptions!D120</f>
         <v>Slot</v>
       </c>
       <c r="F13" s="37" t="n">
-        <f aca="false">Assumptions!E119</f>
+        <f aca="false">Assumptions!E120</f>
         <v>1449</v>
       </c>
       <c r="G13" s="23" t="n">
-        <f aca="false">IF(E13="Free","",Assumptions!F119)</f>
+        <f aca="false">IF(E13="Free","",Assumptions!F120)</f>
         <v>15</v>
       </c>
       <c r="H13" s="37" t="n">
@@ -12814,11 +12846,11 @@
         <v>96.6</v>
       </c>
       <c r="I13" s="24" t="n">
-        <f aca="false">Assumptions!G119</f>
+        <f aca="false">Assumptions!G120</f>
         <v>0.3</v>
       </c>
       <c r="J13" s="23" t="n">
-        <f aca="false">IF(E13="Slot",Assumptions!H119*G13,Assumptions!H119)</f>
+        <f aca="false">IF(E13="Slot",Assumptions!H120*G13,Assumptions!H120)</f>
         <v>45</v>
       </c>
       <c r="K13" s="26" t="n">
@@ -12830,7 +12862,7 @@
         <v>0.32175</v>
       </c>
       <c r="M13" s="38" t="n">
-        <f aca="false">Assumptions!I119</f>
+        <f aca="false">Assumptions!I120</f>
         <v>1</v>
       </c>
       <c r="N13" s="26" t="n">
@@ -12842,7 +12874,7 @@
         <v>322</v>
       </c>
       <c r="P13" s="35" t="n">
-        <f aca="false">IF(N13&gt;0,(N13/L13/I13*H13+Assumptions!J119)/N13,0)</f>
+        <f aca="false">IF(N13&gt;0,(N13/L13/I13*H13+Assumptions!J120)/N13,0)</f>
         <v>1000.777000777</v>
       </c>
       <c r="Q13" s="39" t="n">
@@ -12878,7 +12910,7 @@
         <v>1449</v>
       </c>
       <c r="Y13" s="35" t="n">
-        <f aca="false">IF(U13&gt;0,Assumptions!J119,0)</f>
+        <f aca="false">IF(U13&gt;0,Assumptions!J120,0)</f>
         <v>0</v>
       </c>
       <c r="Z13" s="35" t="n">
@@ -12924,30 +12956,30 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="str">
-        <f aca="false">Assumptions!A120</f>
+        <f aca="false">Assumptions!A121</f>
         <v>C10</v>
       </c>
       <c r="B14" s="2" t="str">
-        <f aca="false">Assumptions!B120</f>
+        <f aca="false">Assumptions!B121</f>
         <v>StepStone (30-day single ad)</v>
       </c>
       <c r="C14" s="2" t="str">
-        <f aca="false">Assumptions!C120</f>
+        <f aca="false">Assumptions!C121</f>
         <v>Mechatronics</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f aca="false">Assumptions!D120</f>
+        <f aca="false">Assumptions!D121</f>
         <v>Slot</v>
       </c>
       <c r="F14" s="37" t="n">
-        <f aca="false">Assumptions!E120</f>
+        <f aca="false">Assumptions!E121</f>
         <v>1449</v>
       </c>
       <c r="G14" s="23" t="n">
-        <f aca="false">IF(E14="Free","",Assumptions!F120)</f>
+        <f aca="false">IF(E14="Free","",Assumptions!F121)</f>
         <v>25</v>
       </c>
       <c r="H14" s="37" t="n">
@@ -12955,11 +12987,11 @@
         <v>57.96</v>
       </c>
       <c r="I14" s="24" t="n">
-        <f aca="false">Assumptions!G120</f>
+        <f aca="false">Assumptions!G121</f>
         <v>0.35</v>
       </c>
       <c r="J14" s="23" t="n">
-        <f aca="false">IF(E14="Slot",Assumptions!H120*G14,Assumptions!H120)</f>
+        <f aca="false">IF(E14="Slot",Assumptions!H121*G14,Assumptions!H121)</f>
         <v>75</v>
       </c>
       <c r="K14" s="26" t="n">
@@ -12971,7 +13003,7 @@
         <v>0.405</v>
       </c>
       <c r="M14" s="38" t="n">
-        <f aca="false">Assumptions!I120</f>
+        <f aca="false">Assumptions!I121</f>
         <v>1</v>
       </c>
       <c r="N14" s="26" t="n">
@@ -12983,7 +13015,7 @@
         <v>165.6</v>
       </c>
       <c r="P14" s="35" t="n">
-        <f aca="false">IF(N14&gt;0,(N14/L14/I14*H14+Assumptions!J120)/N14,0)</f>
+        <f aca="false">IF(N14&gt;0,(N14/L14/I14*H14+Assumptions!J121)/N14,0)</f>
         <v>408.888888888889</v>
       </c>
       <c r="Q14" s="39" t="n">
@@ -13019,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <f aca="false">IF(U14&gt;0,Assumptions!J120,0)</f>
+        <f aca="false">IF(U14&gt;0,Assumptions!J121,0)</f>
         <v>0</v>
       </c>
       <c r="Z14" s="35" t="n">
@@ -13065,30 +13097,30 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="str">
-        <f aca="false">Assumptions!A121</f>
+        <f aca="false">Assumptions!A122</f>
         <v>C11</v>
       </c>
       <c r="B15" s="2" t="str">
-        <f aca="false">Assumptions!B121</f>
+        <f aca="false">Assumptions!B122</f>
         <v>StepStone (30-day single ad)</v>
       </c>
       <c r="C15" s="2" t="str">
-        <f aca="false">Assumptions!C121</f>
+        <f aca="false">Assumptions!C122</f>
         <v>Automation</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f aca="false">Assumptions!D121</f>
+        <f aca="false">Assumptions!D122</f>
         <v>Slot</v>
       </c>
       <c r="F15" s="37" t="n">
-        <f aca="false">Assumptions!E121</f>
+        <f aca="false">Assumptions!E122</f>
         <v>1449</v>
       </c>
       <c r="G15" s="23" t="n">
-        <f aca="false">IF(E15="Free","",Assumptions!F121)</f>
+        <f aca="false">IF(E15="Free","",Assumptions!F122)</f>
         <v>15</v>
       </c>
       <c r="H15" s="37" t="n">
@@ -13096,11 +13128,11 @@
         <v>96.6</v>
       </c>
       <c r="I15" s="24" t="n">
-        <f aca="false">Assumptions!G121</f>
+        <f aca="false">Assumptions!G122</f>
         <v>0.25</v>
       </c>
       <c r="J15" s="23" t="n">
-        <f aca="false">IF(E15="Slot",Assumptions!H121*G15,Assumptions!H121)</f>
+        <f aca="false">IF(E15="Slot",Assumptions!H122*G15,Assumptions!H122)</f>
         <v>30</v>
       </c>
       <c r="K15" s="26" t="n">
@@ -13112,7 +13144,7 @@
         <v>0.2925</v>
       </c>
       <c r="M15" s="38" t="n">
-        <f aca="false">Assumptions!I121</f>
+        <f aca="false">Assumptions!I122</f>
         <v>1</v>
       </c>
       <c r="N15" s="26" t="n">
@@ -13124,7 +13156,7 @@
         <v>386.4</v>
       </c>
       <c r="P15" s="35" t="n">
-        <f aca="false">IF(N15&gt;0,(N15/L15/I15*H15+Assumptions!J121)/N15,0)</f>
+        <f aca="false">IF(N15&gt;0,(N15/L15/I15*H15+Assumptions!J122)/N15,0)</f>
         <v>1321.02564102564</v>
       </c>
       <c r="Q15" s="39" t="n">
@@ -13160,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="35" t="n">
-        <f aca="false">IF(U15&gt;0,Assumptions!J121,0)</f>
+        <f aca="false">IF(U15&gt;0,Assumptions!J122,0)</f>
         <v>0</v>
       </c>
       <c r="Z15" s="35" t="n">
@@ -13206,30 +13238,30 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="str">
-        <f aca="false">Assumptions!A122</f>
+        <f aca="false">Assumptions!A123</f>
         <v>C12</v>
       </c>
       <c r="B16" s="2" t="str">
-        <f aca="false">Assumptions!B122</f>
+        <f aca="false">Assumptions!B123</f>
         <v>StepStone (30-day single ad)</v>
       </c>
       <c r="C16" s="2" t="str">
-        <f aca="false">Assumptions!C122</f>
+        <f aca="false">Assumptions!C123</f>
         <v>Supervisors</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f aca="false">Assumptions!D122</f>
+        <f aca="false">Assumptions!D123</f>
         <v>Slot</v>
       </c>
       <c r="F16" s="37" t="n">
-        <f aca="false">Assumptions!E122</f>
+        <f aca="false">Assumptions!E123</f>
         <v>1449</v>
       </c>
       <c r="G16" s="23" t="n">
-        <f aca="false">IF(E16="Free","",Assumptions!F122)</f>
+        <f aca="false">IF(E16="Free","",Assumptions!F123)</f>
         <v>15</v>
       </c>
       <c r="H16" s="37" t="n">
@@ -13237,11 +13269,11 @@
         <v>96.6</v>
       </c>
       <c r="I16" s="24" t="n">
-        <f aca="false">Assumptions!G122</f>
+        <f aca="false">Assumptions!G123</f>
         <v>0.25</v>
       </c>
       <c r="J16" s="23" t="n">
-        <f aca="false">IF(E16="Slot",Assumptions!H122*G16,Assumptions!H122)</f>
+        <f aca="false">IF(E16="Slot",Assumptions!H123*G16,Assumptions!H123)</f>
         <v>30</v>
       </c>
       <c r="K16" s="26" t="n">
@@ -13253,7 +13285,7 @@
         <v>0.26775</v>
       </c>
       <c r="M16" s="38" t="n">
-        <f aca="false">Assumptions!I122</f>
+        <f aca="false">Assumptions!I123</f>
         <v>1</v>
       </c>
       <c r="N16" s="26" t="n">
@@ -13265,7 +13297,7 @@
         <v>386.4</v>
       </c>
       <c r="P16" s="35" t="n">
-        <f aca="false">IF(N16&gt;0,(N16/L16/I16*H16+Assumptions!J122)/N16,0)</f>
+        <f aca="false">IF(N16&gt;0,(N16/L16/I16*H16+Assumptions!J123)/N16,0)</f>
         <v>1443.13725490196</v>
       </c>
       <c r="Q16" s="39" t="n">
@@ -13301,7 +13333,7 @@
         <v>0</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <f aca="false">IF(U16&gt;0,Assumptions!J122,0)</f>
+        <f aca="false">IF(U16&gt;0,Assumptions!J123,0)</f>
         <v>0</v>
       </c>
       <c r="Z16" s="35" t="n">
@@ -13347,30 +13379,30 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="str">
-        <f aca="false">Assumptions!A123</f>
+        <f aca="false">Assumptions!A124</f>
         <v>C13</v>
       </c>
       <c r="B17" s="2" t="str">
-        <f aca="false">Assumptions!B123</f>
+        <f aca="false">Assumptions!B124</f>
         <v>LinkedIn (promoted jobs + InMail)</v>
       </c>
       <c r="C17" s="2" t="str">
-        <f aca="false">Assumptions!C123</f>
+        <f aca="false">Assumptions!C124</f>
         <v>Automation</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f aca="false">Assumptions!D123</f>
+        <f aca="false">Assumptions!D124</f>
         <v>CPC</v>
       </c>
       <c r="F17" s="37" t="n">
-        <f aca="false">Assumptions!E123</f>
+        <f aca="false">Assumptions!E124</f>
         <v>3.5</v>
       </c>
       <c r="G17" s="25" t="n">
-        <f aca="false">IF(E17="Free","",Assumptions!F123)</f>
+        <f aca="false">IF(E17="Free","",Assumptions!F124)</f>
         <v>0.08</v>
       </c>
       <c r="H17" s="37" t="n">
@@ -13378,11 +13410,11 @@
         <v>43.75</v>
       </c>
       <c r="I17" s="24" t="n">
-        <f aca="false">Assumptions!G123</f>
+        <f aca="false">Assumptions!G124</f>
         <v>0.25</v>
       </c>
       <c r="J17" s="23" t="n">
-        <f aca="false">IF(E17="Slot",Assumptions!H123*G17,Assumptions!H123)</f>
+        <f aca="false">IF(E17="Slot",Assumptions!H124*G17,Assumptions!H124)</f>
         <v>150</v>
       </c>
       <c r="K17" s="26" t="n">
@@ -13394,7 +13426,7 @@
         <v>0.2925</v>
       </c>
       <c r="M17" s="38" t="n">
-        <f aca="false">Assumptions!I123</f>
+        <f aca="false">Assumptions!I124</f>
         <v>1</v>
       </c>
       <c r="N17" s="26" t="n">
@@ -13406,7 +13438,7 @@
         <v>175</v>
       </c>
       <c r="P17" s="35" t="n">
-        <f aca="false">IF(N17&gt;0,(N17/L17/I17*H17+Assumptions!J123)/N17,0)</f>
+        <f aca="false">IF(N17&gt;0,(N17/L17/I17*H17+Assumptions!J124)/N17,0)</f>
         <v>598.290598290598</v>
       </c>
       <c r="Q17" s="39" t="n">
@@ -13442,7 +13474,7 @@
         <v>5148.93851981352</v>
       </c>
       <c r="Y17" s="35" t="n">
-        <f aca="false">IF(U17&gt;0,Assumptions!J123,0)</f>
+        <f aca="false">IF(U17&gt;0,Assumptions!J124,0)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="35" t="n">
@@ -13488,30 +13520,30 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="str">
-        <f aca="false">Assumptions!A124</f>
+        <f aca="false">Assumptions!A125</f>
         <v>C14</v>
       </c>
       <c r="B18" s="2" t="str">
-        <f aca="false">Assumptions!B124</f>
+        <f aca="false">Assumptions!B125</f>
         <v>LinkedIn (promoted jobs + InMail)</v>
       </c>
       <c r="C18" s="2" t="str">
-        <f aca="false">Assumptions!C124</f>
+        <f aca="false">Assumptions!C125</f>
         <v>Supervisors</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f aca="false">Assumptions!D124</f>
+        <f aca="false">Assumptions!D125</f>
         <v>CPC</v>
       </c>
       <c r="F18" s="37" t="n">
-        <f aca="false">Assumptions!E124</f>
+        <f aca="false">Assumptions!E125</f>
         <v>3.5</v>
       </c>
       <c r="G18" s="25" t="n">
-        <f aca="false">IF(E18="Free","",Assumptions!F124)</f>
+        <f aca="false">IF(E18="Free","",Assumptions!F125)</f>
         <v>0.08</v>
       </c>
       <c r="H18" s="37" t="n">
@@ -13519,11 +13551,11 @@
         <v>43.75</v>
       </c>
       <c r="I18" s="24" t="n">
-        <f aca="false">Assumptions!G124</f>
+        <f aca="false">Assumptions!G125</f>
         <v>0.2</v>
       </c>
       <c r="J18" s="23" t="n">
-        <f aca="false">IF(E18="Slot",Assumptions!H124*G18,Assumptions!H124)</f>
+        <f aca="false">IF(E18="Slot",Assumptions!H125*G18,Assumptions!H125)</f>
         <v>100</v>
       </c>
       <c r="K18" s="26" t="n">
@@ -13535,7 +13567,7 @@
         <v>0.26775</v>
       </c>
       <c r="M18" s="38" t="n">
-        <f aca="false">Assumptions!I124</f>
+        <f aca="false">Assumptions!I125</f>
         <v>1</v>
       </c>
       <c r="N18" s="26" t="n">
@@ -13547,7 +13579,7 @@
         <v>218.75</v>
       </c>
       <c r="P18" s="35" t="n">
-        <f aca="false">IF(N18&gt;0,(N18/L18/I18*H18+Assumptions!J124)/N18,0)</f>
+        <f aca="false">IF(N18&gt;0,(N18/L18/I18*H18+Assumptions!J125)/N18,0)</f>
         <v>816.993464052288</v>
       </c>
       <c r="Q18" s="39" t="n">
@@ -13583,7 +13615,7 @@
         <v>4375</v>
       </c>
       <c r="Y18" s="35" t="n">
-        <f aca="false">IF(U18&gt;0,Assumptions!J124,0)</f>
+        <f aca="false">IF(U18&gt;0,Assumptions!J125,0)</f>
         <v>0</v>
       </c>
       <c r="Z18" s="35" t="n">
@@ -13629,30 +13661,30 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="str">
-        <f aca="false">Assumptions!A125</f>
+        <f aca="false">Assumptions!A126</f>
         <v>C15</v>
       </c>
       <c r="B19" s="2" t="str">
-        <f aca="false">Assumptions!B125</f>
+        <f aca="false">Assumptions!B126</f>
         <v>Meta social (FB/IG lead ads, 75 km geo)</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f aca="false">Assumptions!C125</f>
+        <f aca="false">Assumptions!C126</f>
         <v>Electricians</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E19" s="2" t="str">
-        <f aca="false">Assumptions!D125</f>
+        <f aca="false">Assumptions!D126</f>
         <v>CPA</v>
       </c>
       <c r="F19" s="37" t="n">
-        <f aca="false">Assumptions!E125</f>
+        <f aca="false">Assumptions!E126</f>
         <v>18</v>
       </c>
       <c r="G19" s="23" t="n">
-        <f aca="false">IF(E19="Free","",Assumptions!F125)</f>
+        <f aca="false">IF(E19="Free","",Assumptions!F126)</f>
         <v>0</v>
       </c>
       <c r="H19" s="37" t="n">
@@ -13660,11 +13692,11 @@
         <v>18</v>
       </c>
       <c r="I19" s="24" t="n">
-        <f aca="false">Assumptions!G125</f>
+        <f aca="false">Assumptions!G126</f>
         <v>0.05</v>
       </c>
       <c r="J19" s="23" t="n">
-        <f aca="false">IF(E19="Slot",Assumptions!H125*G19,Assumptions!H125)</f>
+        <f aca="false">IF(E19="Slot",Assumptions!H126*G19,Assumptions!H126)</f>
         <v>400</v>
       </c>
       <c r="K19" s="26" t="n">
@@ -13676,7 +13708,7 @@
         <v>0.32175</v>
       </c>
       <c r="M19" s="38" t="n">
-        <f aca="false">Assumptions!I125</f>
+        <f aca="false">Assumptions!I126</f>
         <v>1</v>
       </c>
       <c r="N19" s="26" t="n">
@@ -13688,7 +13720,7 @@
         <v>360</v>
       </c>
       <c r="P19" s="35" t="n">
-        <f aca="false">IF(N19&gt;0,(N19/L19/I19*H19+Assumptions!J125)/N19,0)</f>
+        <f aca="false">IF(N19&gt;0,(N19/L19/I19*H19+Assumptions!J126)/N19,0)</f>
         <v>1118.88111888112</v>
       </c>
       <c r="Q19" s="39" t="n">
@@ -13724,7 +13756,7 @@
         <v>750</v>
       </c>
       <c r="Y19" s="35" t="n">
-        <f aca="false">IF(U19&gt;0,Assumptions!J125,0)</f>
+        <f aca="false">IF(U19&gt;0,Assumptions!J126,0)</f>
         <v>0</v>
       </c>
       <c r="Z19" s="35" t="n">
@@ -13770,30 +13802,30 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="str">
-        <f aca="false">Assumptions!A126</f>
+        <f aca="false">Assumptions!A127</f>
         <v>C16</v>
       </c>
       <c r="B20" s="2" t="str">
-        <f aca="false">Assumptions!B126</f>
+        <f aca="false">Assumptions!B127</f>
         <v>Meta social (FB/IG lead ads, 75 km geo)</v>
       </c>
       <c r="C20" s="2" t="str">
-        <f aca="false">Assumptions!C126</f>
+        <f aca="false">Assumptions!C127</f>
         <v>Mechatronics</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f aca="false">Assumptions!D126</f>
+        <f aca="false">Assumptions!D127</f>
         <v>CPA</v>
       </c>
       <c r="F20" s="37" t="n">
-        <f aca="false">Assumptions!E126</f>
+        <f aca="false">Assumptions!E127</f>
         <v>12</v>
       </c>
       <c r="G20" s="23" t="n">
-        <f aca="false">IF(E20="Free","",Assumptions!F126)</f>
+        <f aca="false">IF(E20="Free","",Assumptions!F127)</f>
         <v>0</v>
       </c>
       <c r="H20" s="37" t="n">
@@ -13801,11 +13833,11 @@
         <v>12</v>
       </c>
       <c r="I20" s="24" t="n">
-        <f aca="false">Assumptions!G126</f>
+        <f aca="false">Assumptions!G127</f>
         <v>0.12</v>
       </c>
       <c r="J20" s="23" t="n">
-        <f aca="false">IF(E20="Slot",Assumptions!H126*G20,Assumptions!H126)</f>
+        <f aca="false">IF(E20="Slot",Assumptions!H127*G20,Assumptions!H127)</f>
         <v>500</v>
       </c>
       <c r="K20" s="26" t="n">
@@ -13817,7 +13849,7 @@
         <v>0.405</v>
       </c>
       <c r="M20" s="38" t="n">
-        <f aca="false">Assumptions!I126</f>
+        <f aca="false">Assumptions!I127</f>
         <v>1</v>
       </c>
       <c r="N20" s="26" t="n">
@@ -13829,7 +13861,7 @@
         <v>100</v>
       </c>
       <c r="P20" s="35" t="n">
-        <f aca="false">IF(N20&gt;0,(N20/L20/I20*H20+Assumptions!J126)/N20,0)</f>
+        <f aca="false">IF(N20&gt;0,(N20/L20/I20*H20+Assumptions!J127)/N20,0)</f>
         <v>246.913580246914</v>
       </c>
       <c r="Q20" s="39" t="n">
@@ -13865,7 +13897,7 @@
         <v>750</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <f aca="false">IF(U20&gt;0,Assumptions!J126,0)</f>
+        <f aca="false">IF(U20&gt;0,Assumptions!J127,0)</f>
         <v>0</v>
       </c>
       <c r="Z20" s="35" t="n">
@@ -13911,30 +13943,30 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="str">
-        <f aca="false">Assumptions!A127</f>
+        <f aca="false">Assumptions!A128</f>
         <v>C17</v>
       </c>
       <c r="B21" s="2" t="str">
-        <f aca="false">Assumptions!B127</f>
+        <f aca="false">Assumptions!B128</f>
         <v>Google Search ads (job-intent keywords)</v>
       </c>
       <c r="C21" s="2" t="str">
-        <f aca="false">Assumptions!C127</f>
+        <f aca="false">Assumptions!C128</f>
         <v>Electricians</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f aca="false">Assumptions!D127</f>
+        <f aca="false">Assumptions!D128</f>
         <v>CPC</v>
       </c>
       <c r="F21" s="37" t="n">
-        <f aca="false">Assumptions!E127</f>
+        <f aca="false">Assumptions!E128</f>
         <v>2.2</v>
       </c>
       <c r="G21" s="25" t="n">
-        <f aca="false">IF(E21="Free","",Assumptions!F127)</f>
+        <f aca="false">IF(E21="Free","",Assumptions!F128)</f>
         <v>0.07</v>
       </c>
       <c r="H21" s="37" t="n">
@@ -13942,11 +13974,11 @@
         <v>31.4285714285714</v>
       </c>
       <c r="I21" s="24" t="n">
-        <f aca="false">Assumptions!G127</f>
+        <f aca="false">Assumptions!G128</f>
         <v>0.15</v>
       </c>
       <c r="J21" s="23" t="n">
-        <f aca="false">IF(E21="Slot",Assumptions!H127*G21,Assumptions!H127)</f>
+        <f aca="false">IF(E21="Slot",Assumptions!H128*G21,Assumptions!H128)</f>
         <v>80</v>
       </c>
       <c r="K21" s="26" t="n">
@@ -13958,7 +13990,7 @@
         <v>0.32175</v>
       </c>
       <c r="M21" s="38" t="n">
-        <f aca="false">Assumptions!I127</f>
+        <f aca="false">Assumptions!I128</f>
         <v>1</v>
       </c>
       <c r="N21" s="26" t="n">
@@ -13970,7 +14002,7 @@
         <v>209.52380952381</v>
       </c>
       <c r="P21" s="35" t="n">
-        <f aca="false">IF(N21&gt;0,(N21/L21/I21*H21+Assumptions!J127)/N21,0)</f>
+        <f aca="false">IF(N21&gt;0,(N21/L21/I21*H21+Assumptions!J128)/N21,0)</f>
         <v>651.200651200651</v>
       </c>
       <c r="Q21" s="39" t="n">
@@ -14006,7 +14038,7 @@
         <v>2514.28571428571</v>
       </c>
       <c r="Y21" s="35" t="n">
-        <f aca="false">IF(U21&gt;0,Assumptions!J127,0)</f>
+        <f aca="false">IF(U21&gt;0,Assumptions!J128,0)</f>
         <v>0</v>
       </c>
       <c r="Z21" s="35" t="n">
@@ -14052,30 +14084,30 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="str">
-        <f aca="false">Assumptions!A128</f>
+        <f aca="false">Assumptions!A129</f>
         <v>C18</v>
       </c>
       <c r="B22" s="2" t="str">
-        <f aca="false">Assumptions!B128</f>
+        <f aca="false">Assumptions!B129</f>
         <v>Google Search ads (job-intent keywords)</v>
       </c>
       <c r="C22" s="2" t="str">
-        <f aca="false">Assumptions!C128</f>
+        <f aca="false">Assumptions!C129</f>
         <v>Mechatronics</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f aca="false">Assumptions!D128</f>
+        <f aca="false">Assumptions!D129</f>
         <v>CPC</v>
       </c>
       <c r="F22" s="37" t="n">
-        <f aca="false">Assumptions!E128</f>
+        <f aca="false">Assumptions!E129</f>
         <v>2.2</v>
       </c>
       <c r="G22" s="25" t="n">
-        <f aca="false">IF(E22="Free","",Assumptions!F128)</f>
+        <f aca="false">IF(E22="Free","",Assumptions!F129)</f>
         <v>0.07</v>
       </c>
       <c r="H22" s="37" t="n">
@@ -14083,11 +14115,11 @@
         <v>31.4285714285714</v>
       </c>
       <c r="I22" s="24" t="n">
-        <f aca="false">Assumptions!G128</f>
+        <f aca="false">Assumptions!G129</f>
         <v>0.25</v>
       </c>
       <c r="J22" s="23" t="n">
-        <f aca="false">IF(E22="Slot",Assumptions!H128*G22,Assumptions!H128)</f>
+        <f aca="false">IF(E22="Slot",Assumptions!H129*G22,Assumptions!H129)</f>
         <v>100</v>
       </c>
       <c r="K22" s="26" t="n">
@@ -14099,7 +14131,7 @@
         <v>0.405</v>
       </c>
       <c r="M22" s="38" t="n">
-        <f aca="false">Assumptions!I128</f>
+        <f aca="false">Assumptions!I129</f>
         <v>1</v>
       </c>
       <c r="N22" s="26" t="n">
@@ -14111,7 +14143,7 @@
         <v>125.714285714286</v>
       </c>
       <c r="P22" s="35" t="n">
-        <f aca="false">IF(N22&gt;0,(N22/L22/I22*H22+Assumptions!J128)/N22,0)</f>
+        <f aca="false">IF(N22&gt;0,(N22/L22/I22*H22+Assumptions!J129)/N22,0)</f>
         <v>310.405643738977</v>
       </c>
       <c r="Q22" s="39" t="n">
@@ -14147,7 +14179,7 @@
         <v>750</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <f aca="false">IF(U22&gt;0,Assumptions!J128,0)</f>
+        <f aca="false">IF(U22&gt;0,Assumptions!J129,0)</f>
         <v>0</v>
       </c>
       <c r="Z22" s="35" t="n">
@@ -14193,30 +14225,30 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="str">
-        <f aca="false">Assumptions!A129</f>
+        <f aca="false">Assumptions!A130</f>
         <v>C19</v>
       </c>
       <c r="B23" s="2" t="str">
-        <f aca="false">Assumptions!B129</f>
+        <f aca="false">Assumptions!B130</f>
         <v>Google Search ads (job-intent keywords)</v>
       </c>
       <c r="C23" s="2" t="str">
-        <f aca="false">Assumptions!C129</f>
+        <f aca="false">Assumptions!C130</f>
         <v>Automation</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f aca="false">Assumptions!D129</f>
+        <f aca="false">Assumptions!D130</f>
         <v>CPC</v>
       </c>
       <c r="F23" s="37" t="n">
-        <f aca="false">Assumptions!E129</f>
+        <f aca="false">Assumptions!E130</f>
         <v>2.2</v>
       </c>
       <c r="G23" s="25" t="n">
-        <f aca="false">IF(E23="Free","",Assumptions!F129)</f>
+        <f aca="false">IF(E23="Free","",Assumptions!F130)</f>
         <v>0.07</v>
       </c>
       <c r="H23" s="37" t="n">
@@ -14224,11 +14256,11 @@
         <v>31.4285714285714</v>
       </c>
       <c r="I23" s="24" t="n">
-        <f aca="false">Assumptions!G129</f>
+        <f aca="false">Assumptions!G130</f>
         <v>0.15</v>
       </c>
       <c r="J23" s="23" t="n">
-        <f aca="false">IF(E23="Slot",Assumptions!H129*G23,Assumptions!H129)</f>
+        <f aca="false">IF(E23="Slot",Assumptions!H130*G23,Assumptions!H130)</f>
         <v>40</v>
       </c>
       <c r="K23" s="26" t="n">
@@ -14240,7 +14272,7 @@
         <v>0.2925</v>
       </c>
       <c r="M23" s="38" t="n">
-        <f aca="false">Assumptions!I129</f>
+        <f aca="false">Assumptions!I130</f>
         <v>1</v>
       </c>
       <c r="N23" s="26" t="n">
@@ -14252,7 +14284,7 @@
         <v>209.52380952381</v>
       </c>
       <c r="P23" s="35" t="n">
-        <f aca="false">IF(N23&gt;0,(N23/L23/I23*H23+Assumptions!J129)/N23,0)</f>
+        <f aca="false">IF(N23&gt;0,(N23/L23/I23*H23+Assumptions!J130)/N23,0)</f>
         <v>716.320716320716</v>
       </c>
       <c r="Q23" s="39" t="n">
@@ -14288,7 +14320,7 @@
         <v>750</v>
       </c>
       <c r="Y23" s="35" t="n">
-        <f aca="false">IF(U23&gt;0,Assumptions!J129,0)</f>
+        <f aca="false">IF(U23&gt;0,Assumptions!J130,0)</f>
         <v>0</v>
       </c>
       <c r="Z23" s="35" t="n">
@@ -14334,30 +14366,30 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="str">
-        <f aca="false">Assumptions!A130</f>
+        <f aca="false">Assumptions!A131</f>
         <v>C20</v>
       </c>
       <c r="B24" s="2" t="str">
-        <f aca="false">Assumptions!B130</f>
+        <f aca="false">Assumptions!B131</f>
         <v>Google Search ads (job-intent keywords)</v>
       </c>
       <c r="C24" s="2" t="str">
-        <f aca="false">Assumptions!C130</f>
+        <f aca="false">Assumptions!C131</f>
         <v>Supervisors</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f aca="false">Assumptions!D130</f>
+        <f aca="false">Assumptions!D131</f>
         <v>CPC</v>
       </c>
       <c r="F24" s="37" t="n">
-        <f aca="false">Assumptions!E130</f>
+        <f aca="false">Assumptions!E131</f>
         <v>2.2</v>
       </c>
       <c r="G24" s="25" t="n">
-        <f aca="false">IF(E24="Free","",Assumptions!F130)</f>
+        <f aca="false">IF(E24="Free","",Assumptions!F131)</f>
         <v>0.07</v>
       </c>
       <c r="H24" s="37" t="n">
@@ -14365,11 +14397,11 @@
         <v>31.4285714285714</v>
       </c>
       <c r="I24" s="24" t="n">
-        <f aca="false">Assumptions!G130</f>
+        <f aca="false">Assumptions!G131</f>
         <v>0.12</v>
       </c>
       <c r="J24" s="23" t="n">
-        <f aca="false">IF(E24="Slot",Assumptions!H130*G24,Assumptions!H130)</f>
+        <f aca="false">IF(E24="Slot",Assumptions!H131*G24,Assumptions!H131)</f>
         <v>30</v>
       </c>
       <c r="K24" s="26" t="n">
@@ -14381,7 +14413,7 @@
         <v>0.26775</v>
       </c>
       <c r="M24" s="38" t="n">
-        <f aca="false">Assumptions!I130</f>
+        <f aca="false">Assumptions!I131</f>
         <v>1</v>
       </c>
       <c r="N24" s="26" t="n">
@@ -14393,7 +14425,7 @@
         <v>261.904761904762</v>
       </c>
       <c r="P24" s="35" t="n">
-        <f aca="false">IF(N24&gt;0,(N24/L24/I24*H24+Assumptions!J130)/N24,0)</f>
+        <f aca="false">IF(N24&gt;0,(N24/L24/I24*H24+Assumptions!J131)/N24,0)</f>
         <v>978.169045395936</v>
       </c>
       <c r="Q24" s="39" t="n">
@@ -14429,7 +14461,7 @@
         <v>942.857142857143</v>
       </c>
       <c r="Y24" s="35" t="n">
-        <f aca="false">IF(U24&gt;0,Assumptions!J130,0)</f>
+        <f aca="false">IF(U24&gt;0,Assumptions!J131,0)</f>
         <v>0</v>
       </c>
       <c r="Z24" s="35" t="n">
@@ -14475,19 +14507,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F25" s="37" t="n">
         <f aca="false">Initiatives!B11</f>
@@ -14515,7 +14547,7 @@
         <v>0.3700125</v>
       </c>
       <c r="M25" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N25" s="26" t="n">
@@ -14609,19 +14641,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">Initiatives!C11</f>
@@ -14649,7 +14681,7 @@
         <v>0.46575</v>
       </c>
       <c r="M26" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N26" s="26" t="n">
@@ -14743,19 +14775,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">Initiatives!D11</f>
@@ -14783,7 +14815,7 @@
         <v>0.336375</v>
       </c>
       <c r="M27" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N27" s="26" t="n">
@@ -14877,19 +14909,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F28" s="37" t="n">
         <f aca="false">Initiatives!E11</f>
@@ -14917,7 +14949,7 @@
         <v>0.3079125</v>
       </c>
       <c r="M28" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N28" s="26" t="n">
@@ -15011,19 +15043,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F29" s="37" t="n">
         <f aca="false">Initiatives!B17</f>
@@ -15051,7 +15083,7 @@
         <v>0.3700125</v>
       </c>
       <c r="M29" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N29" s="26" t="n">
@@ -15145,19 +15177,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F30" s="37" t="n">
         <f aca="false">Initiatives!C17</f>
@@ -15185,7 +15217,7 @@
         <v>0.46575</v>
       </c>
       <c r="M30" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N30" s="26" t="n">
@@ -15279,19 +15311,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">Initiatives!D17</f>
@@ -15319,7 +15351,7 @@
         <v>0.336375</v>
       </c>
       <c r="M31" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N31" s="26" t="n">
@@ -15413,19 +15445,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F32" s="37" t="n">
         <f aca="false">Initiatives!E17</f>
@@ -15453,7 +15485,7 @@
         <v>0.3079125</v>
       </c>
       <c r="M32" s="38" t="n">
-        <f aca="false">Assumptions!$D$147</f>
+        <f aca="false">Assumptions!$D$148</f>
         <v>1.15</v>
       </c>
       <c r="N32" s="26" t="n">
@@ -15547,19 +15579,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F33" s="37" t="n">
         <f aca="false">Initiatives!B27</f>
@@ -15587,7 +15619,7 @@
         <v>0.2574</v>
       </c>
       <c r="M33" s="38" t="n">
-        <f aca="false">Assumptions!$D$152</f>
+        <f aca="false">Assumptions!$D$153</f>
         <v>0.8</v>
       </c>
       <c r="N33" s="26" t="n">
@@ -15681,19 +15713,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F34" s="37" t="n">
         <f aca="false">Initiatives!B38</f>
@@ -15721,7 +15753,7 @@
         <v>0.4455</v>
       </c>
       <c r="M34" s="38" t="n">
-        <f aca="false">Assumptions!$D$157</f>
+        <f aca="false">Assumptions!$D$158</f>
         <v>1.1</v>
       </c>
       <c r="N34" s="26" t="n">
@@ -15815,7 +15847,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="J35" s="27" t="n">
         <f aca="false">SUM(J5:J34)</f>
@@ -15880,22 +15912,22 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
       <c r="B38" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15993,12 +16025,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C4" s="35" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Channel")</f>
@@ -16007,7 +16039,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C5" s="35" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Initiative")</f>
@@ -16016,7 +16048,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">Channels!Y35</f>
@@ -16025,7 +16057,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">C4+C5+C6</f>
@@ -16034,7 +16066,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">Channels!Z35</f>
@@ -16043,7 +16075,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C9" s="35" t="n">
         <f aca="false">C7</f>
@@ -16052,7 +16084,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">C9/(1-Assumptions!$D$48)*Assumptions!$D$48</f>
@@ -16061,7 +16093,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">C9+C10</f>
@@ -16070,7 +16102,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51</f>
@@ -16079,7 +16111,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C13" s="40" t="n">
         <f aca="false">MIN(Channels!U35,Funnel!B26)</f>
@@ -16088,7 +16120,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C14" s="41" t="n">
         <f aca="false">C9/C13</f>
@@ -16097,7 +16129,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C15" s="35" t="n">
         <f aca="false">C12/C13</f>
@@ -16106,7 +16138,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">Weekly!N5/C12</f>
@@ -16115,34 +16147,34 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16279,7 +16311,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C25" s="36" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -16312,30 +16344,30 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C29" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B29)</f>
@@ -16356,7 +16388,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B30)</f>
@@ -16377,7 +16409,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B31)</f>
@@ -16398,7 +16430,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C32" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B32)</f>
@@ -16419,7 +16451,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C33" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B33)</f>
@@ -16440,7 +16472,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C34" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B34)</f>
@@ -16461,7 +16493,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C35" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B35)</f>
@@ -16482,7 +16514,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C36" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B36)</f>
@@ -16503,7 +16535,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C37" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B37)</f>
@@ -16524,7 +16556,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C38" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B38)</f>
@@ -16545,7 +16577,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C39" s="36" t="n">
         <f aca="false">SUM(C29:C38)</f>
@@ -16564,21 +16596,21 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>50</v>
@@ -16593,10 +16625,10 @@
         <v>57</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16735,9 +16767,10 @@
         <v>295.841171574422</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="9" t="s">
-        <v>634</v>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="9" t="str">
+        <f aca="false">"Above the recommended budget, extra money can buy at most ~"&amp;TEXT(MAX(0,Funnel!B26-Funnel!B9),"0")&amp;" more hires before 31 Dec (the "&amp;TEXT(MAX(0,Funnel!B22-Funnel!B23),"0")&amp;" spare assessment slots at plan conversion); after that the "&amp;Assumptions!$D$9&amp;"/week limit binds."</f>
+        <v>Above the recommended budget, extra money can buy at most ~11 more hires before 31 Dec (the 31 spare assessment slots at plan conversion); after that the 55/week limit binds.</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
@@ -16788,17 +16821,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E3" s="22" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F3" s="42" t="n">
         <f aca="false">1</f>
@@ -16819,7 +16852,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E4" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F4" s="35" t="n">
         <f aca="false">Budget!$C$12*F3</f>
@@ -16840,7 +16873,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E5" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F5" s="35" t="n">
         <f aca="false">F4*(1-Assumptions!$D$48)</f>
@@ -16861,7 +16894,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E6" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F6" s="35" t="n">
         <f aca="false">MAX(0,Budget!$C$9-F5)</f>
@@ -16885,43 +16918,43 @@
         <v>22</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18666,7 +18699,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="22" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18755,7 +18788,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F43" s="29" t="n">
         <f aca="false">SUM(F39:F42)</f>
@@ -18776,7 +18809,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="F44" s="35" t="n">
         <f aca="false">F4/F43</f>
@@ -18824,89 +18857,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20022,7 +20055,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D15" s="44" t="n">
         <f aca="false">SUM(D4:D14)</f>
@@ -20103,7 +20136,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -20155,12 +20188,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="F19" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20169,7 +20202,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F20" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20178,7 +20211,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F21" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -20187,7 +20220,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="F22" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20196,7 +20229,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="F23" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20205,7 +20238,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F24" s="35" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -20214,7 +20247,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F25" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20223,7 +20256,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="F26" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20232,7 +20265,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F27" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20241,7 +20274,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F28" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20250,7 +20283,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F29" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20259,7 +20292,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F30" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20268,7 +20301,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="F31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -20277,7 +20310,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20286,7 +20319,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20295,7 +20328,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F34" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20304,7 +20337,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20313,7 +20346,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="F36" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20322,7 +20355,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F37" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20331,7 +20364,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="F38" s="24" t="n">
         <f aca="false">MIN(1,Funnel!B22/Funnel!B23)</f>
@@ -20340,43 +20373,43 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20841,7 +20874,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C54" s="36" t="n">
         <f aca="false">SUM(C44:C53)</f>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="753">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -877,7 +877,7 @@
     <t xml:space="preserve">qualified/wk</t>
   </si>
   <si>
-    <t xml:space="preserve">~80% of the 55 weekly slots; below this, slots would go unused.</t>
+    <t xml:space="preserve">~80% of the 55 weekly slots; below this, slots would go unused. Flagged automatically per week on the Weekly tab (col S).</t>
   </si>
   <si>
     <t xml:space="preserve">R8</t>
@@ -1705,7 +1705,7 @@
     <t xml:space="preserve">I2 Handwerk → Industrie</t>
   </si>
   <si>
-    <t xml:space="preserve">Fri 23 Oct – Fri 6 Nov (read Mon 9 Nov)</t>
+    <t xml:space="preserve">Fri 23 Oct – Thu 5 Nov (read Mon 9 Nov)</t>
   </si>
   <si>
     <t xml:space="preserve">Also kill at once if the client rejects the EGT profile. Week-4 quality check: ≥50% of the first 6 interviewed pass (kill below 40%). Money then moves to Meta, StepStone and programmatic electricians.</t>
@@ -2168,6 +2168,12 @@
   </si>
   <si>
     <t xml:space="preserve">Wk 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wk 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wk 11</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly tracker — type actuals in the yellow cells; decisions and re-forecast update live</t>
@@ -3084,12 +3090,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3103,67 +3109,67 @@
         <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3225,7 +3231,7 @@
         <v>0.08</v>
       </c>
       <c r="V5" s="35" t="n">
-        <f aca="false">IF(Q5&gt;=Assumptions!$D$86,S5,D5)/U5</f>
+        <f aca="false">IF(U5&gt;0,IF(Q5&gt;=Assumptions!$D$86,S5,D5)/U5,0)</f>
         <v>0</v>
       </c>
       <c r="W5" s="45" t="str">
@@ -3296,7 +3302,7 @@
         <v>0.18</v>
       </c>
       <c r="V6" s="35" t="n">
-        <f aca="false">IF(Q6&gt;=Assumptions!$D$86,S6,D6)/U6</f>
+        <f aca="false">IF(U6&gt;0,IF(Q6&gt;=Assumptions!$D$86,S6,D6)/U6,0)</f>
         <v>0</v>
       </c>
       <c r="W6" s="45" t="str">
@@ -3367,7 +3373,7 @@
         <v>0.1</v>
       </c>
       <c r="V7" s="35" t="n">
-        <f aca="false">IF(Q7&gt;=Assumptions!$D$86,S7,D7)/U7</f>
+        <f aca="false">IF(U7&gt;0,IF(Q7&gt;=Assumptions!$D$86,S7,D7)/U7,0)</f>
         <v>0</v>
       </c>
       <c r="W7" s="45" t="str">
@@ -3438,7 +3444,7 @@
         <v>0.08</v>
       </c>
       <c r="V8" s="35" t="n">
-        <f aca="false">IF(Q8&gt;=Assumptions!$D$86,S8,D8)/U8</f>
+        <f aca="false">IF(U8&gt;0,IF(Q8&gt;=Assumptions!$D$86,S8,D8)/U8,0)</f>
         <v>0</v>
       </c>
       <c r="W8" s="45" t="str">
@@ -3509,7 +3515,7 @@
         <v>0.12</v>
       </c>
       <c r="V9" s="35" t="n">
-        <f aca="false">IF(Q9&gt;=Assumptions!$D$86,S9,D9)/U9</f>
+        <f aca="false">IF(U9&gt;0,IF(Q9&gt;=Assumptions!$D$86,S9,D9)/U9,0)</f>
         <v>476.190476190476</v>
       </c>
       <c r="W9" s="45" t="n">
@@ -3580,7 +3586,7 @@
         <v>0.22</v>
       </c>
       <c r="V10" s="35" t="n">
-        <f aca="false">IF(Q10&gt;=Assumptions!$D$86,S10,D10)/U10</f>
+        <f aca="false">IF(U10&gt;0,IF(Q10&gt;=Assumptions!$D$86,S10,D10)/U10,0)</f>
         <v>109.090909090909</v>
       </c>
       <c r="W10" s="45" t="n">
@@ -3651,7 +3657,7 @@
         <v>0.12</v>
       </c>
       <c r="V11" s="35" t="n">
-        <f aca="false">IF(Q11&gt;=Assumptions!$D$86,S11,D11)/U11</f>
+        <f aca="false">IF(U11&gt;0,IF(Q11&gt;=Assumptions!$D$86,S11,D11)/U11,0)</f>
         <v>375</v>
       </c>
       <c r="W11" s="45" t="n">
@@ -3722,7 +3728,7 @@
         <v>0.1</v>
       </c>
       <c r="V12" s="35" t="n">
-        <f aca="false">IF(Q12&gt;=Assumptions!$D$86,S12,D12)/U12</f>
+        <f aca="false">IF(U12&gt;0,IF(Q12&gt;=Assumptions!$D$86,S12,D12)/U12,0)</f>
         <v>425</v>
       </c>
       <c r="W12" s="45" t="n">
@@ -3793,7 +3799,7 @@
         <v>0.3</v>
       </c>
       <c r="V13" s="35" t="n">
-        <f aca="false">IF(Q13&gt;=Assumptions!$D$86,S13,D13)/U13</f>
+        <f aca="false">IF(U13&gt;0,IF(Q13&gt;=Assumptions!$D$86,S13,D13)/U13,0)</f>
         <v>322</v>
       </c>
       <c r="W13" s="45" t="n">
@@ -3864,7 +3870,7 @@
         <v>0.35</v>
       </c>
       <c r="V14" s="35" t="n">
-        <f aca="false">IF(Q14&gt;=Assumptions!$D$86,S14,D14)/U14</f>
+        <f aca="false">IF(U14&gt;0,IF(Q14&gt;=Assumptions!$D$86,S14,D14)/U14,0)</f>
         <v>165.6</v>
       </c>
       <c r="W14" s="45" t="n">
@@ -3935,7 +3941,7 @@
         <v>0.25</v>
       </c>
       <c r="V15" s="35" t="n">
-        <f aca="false">IF(Q15&gt;=Assumptions!$D$86,S15,D15)/U15</f>
+        <f aca="false">IF(U15&gt;0,IF(Q15&gt;=Assumptions!$D$86,S15,D15)/U15,0)</f>
         <v>386.4</v>
       </c>
       <c r="W15" s="45" t="n">
@@ -4006,7 +4012,7 @@
         <v>0.25</v>
       </c>
       <c r="V16" s="35" t="n">
-        <f aca="false">IF(Q16&gt;=Assumptions!$D$86,S16,D16)/U16</f>
+        <f aca="false">IF(U16&gt;0,IF(Q16&gt;=Assumptions!$D$86,S16,D16)/U16,0)</f>
         <v>386.4</v>
       </c>
       <c r="W16" s="45" t="n">
@@ -4077,7 +4083,7 @@
         <v>0.25</v>
       </c>
       <c r="V17" s="35" t="n">
-        <f aca="false">IF(Q17&gt;=Assumptions!$D$86,S17,D17)/U17</f>
+        <f aca="false">IF(U17&gt;0,IF(Q17&gt;=Assumptions!$D$86,S17,D17)/U17,0)</f>
         <v>175</v>
       </c>
       <c r="W17" s="45" t="n">
@@ -4148,7 +4154,7 @@
         <v>0.2</v>
       </c>
       <c r="V18" s="35" t="n">
-        <f aca="false">IF(Q18&gt;=Assumptions!$D$86,S18,D18)/U18</f>
+        <f aca="false">IF(U18&gt;0,IF(Q18&gt;=Assumptions!$D$86,S18,D18)/U18,0)</f>
         <v>218.75</v>
       </c>
       <c r="W18" s="45" t="n">
@@ -4219,7 +4225,7 @@
         <v>0.05</v>
       </c>
       <c r="V19" s="35" t="n">
-        <f aca="false">IF(Q19&gt;=Assumptions!$D$86,S19,D19)/U19</f>
+        <f aca="false">IF(U19&gt;0,IF(Q19&gt;=Assumptions!$D$86,S19,D19)/U19,0)</f>
         <v>360</v>
       </c>
       <c r="W19" s="45" t="n">
@@ -4290,7 +4296,7 @@
         <v>0.12</v>
       </c>
       <c r="V20" s="35" t="n">
-        <f aca="false">IF(Q20&gt;=Assumptions!$D$86,S20,D20)/U20</f>
+        <f aca="false">IF(U20&gt;0,IF(Q20&gt;=Assumptions!$D$86,S20,D20)/U20,0)</f>
         <v>100</v>
       </c>
       <c r="W20" s="45" t="n">
@@ -4361,7 +4367,7 @@
         <v>0.15</v>
       </c>
       <c r="V21" s="35" t="n">
-        <f aca="false">IF(Q21&gt;=Assumptions!$D$86,S21,D21)/U21</f>
+        <f aca="false">IF(U21&gt;0,IF(Q21&gt;=Assumptions!$D$86,S21,D21)/U21,0)</f>
         <v>209.52380952381</v>
       </c>
       <c r="W21" s="45" t="n">
@@ -4432,7 +4438,7 @@
         <v>0.25</v>
       </c>
       <c r="V22" s="35" t="n">
-        <f aca="false">IF(Q22&gt;=Assumptions!$D$86,S22,D22)/U22</f>
+        <f aca="false">IF(U22&gt;0,IF(Q22&gt;=Assumptions!$D$86,S22,D22)/U22,0)</f>
         <v>125.714285714286</v>
       </c>
       <c r="W22" s="45" t="n">
@@ -4503,7 +4509,7 @@
         <v>0.15</v>
       </c>
       <c r="V23" s="35" t="n">
-        <f aca="false">IF(Q23&gt;=Assumptions!$D$86,S23,D23)/U23</f>
+        <f aca="false">IF(U23&gt;0,IF(Q23&gt;=Assumptions!$D$86,S23,D23)/U23,0)</f>
         <v>209.52380952381</v>
       </c>
       <c r="W23" s="45" t="n">
@@ -4574,7 +4580,7 @@
         <v>0.12</v>
       </c>
       <c r="V24" s="35" t="n">
-        <f aca="false">IF(Q24&gt;=Assumptions!$D$86,S24,D24)/U24</f>
+        <f aca="false">IF(U24&gt;0,IF(Q24&gt;=Assumptions!$D$86,S24,D24)/U24,0)</f>
         <v>261.904761904762</v>
       </c>
       <c r="W24" s="45" t="n">
@@ -4645,7 +4651,7 @@
         <v>0.5</v>
       </c>
       <c r="V25" s="35" t="n">
-        <f aca="false">IF(Q25&gt;=Assumptions!$D$86,S25,D25)/U25</f>
+        <f aca="false">IF(U25&gt;0,IF(Q25&gt;=Assumptions!$D$86,S25,D25)/U25,0)</f>
         <v>8.33333333333333</v>
       </c>
       <c r="W25" s="45" t="n">
@@ -4716,7 +4722,7 @@
         <v>0.5</v>
       </c>
       <c r="V26" s="35" t="n">
-        <f aca="false">IF(Q26&gt;=Assumptions!$D$86,S26,D26)/U26</f>
+        <f aca="false">IF(U26&gt;0,IF(Q26&gt;=Assumptions!$D$86,S26,D26)/U26,0)</f>
         <v>8.33333333333333</v>
       </c>
       <c r="W26" s="45" t="n">
@@ -4787,7 +4793,7 @@
         <v>0.5</v>
       </c>
       <c r="V27" s="35" t="n">
-        <f aca="false">IF(Q27&gt;=Assumptions!$D$86,S27,D27)/U27</f>
+        <f aca="false">IF(U27&gt;0,IF(Q27&gt;=Assumptions!$D$86,S27,D27)/U27,0)</f>
         <v>8.33333333333333</v>
       </c>
       <c r="W27" s="45" t="n">
@@ -4858,7 +4864,7 @@
         <v>0.5</v>
       </c>
       <c r="V28" s="35" t="n">
-        <f aca="false">IF(Q28&gt;=Assumptions!$D$86,S28,D28)/U28</f>
+        <f aca="false">IF(U28&gt;0,IF(Q28&gt;=Assumptions!$D$86,S28,D28)/U28,0)</f>
         <v>8.33333333333333</v>
       </c>
       <c r="W28" s="45" t="n">
@@ -4929,7 +4935,7 @@
         <v>0.45</v>
       </c>
       <c r="V29" s="35" t="n">
-        <f aca="false">IF(Q29&gt;=Assumptions!$D$86,S29,D29)/U29</f>
+        <f aca="false">IF(U29&gt;0,IF(Q29&gt;=Assumptions!$D$86,S29,D29)/U29,0)</f>
         <v>370.0125</v>
       </c>
       <c r="W29" s="45" t="n">
@@ -5000,7 +5006,7 @@
         <v>0.45</v>
       </c>
       <c r="V30" s="35" t="n">
-        <f aca="false">IF(Q30&gt;=Assumptions!$D$86,S30,D30)/U30</f>
+        <f aca="false">IF(U30&gt;0,IF(Q30&gt;=Assumptions!$D$86,S30,D30)/U30,0)</f>
         <v>465.75</v>
       </c>
       <c r="W30" s="45" t="n">
@@ -5071,7 +5077,7 @@
         <v>0.45</v>
       </c>
       <c r="V31" s="35" t="n">
-        <f aca="false">IF(Q31&gt;=Assumptions!$D$86,S31,D31)/U31</f>
+        <f aca="false">IF(U31&gt;0,IF(Q31&gt;=Assumptions!$D$86,S31,D31)/U31,0)</f>
         <v>336.375</v>
       </c>
       <c r="W31" s="45" t="n">
@@ -5142,7 +5148,7 @@
         <v>0.45</v>
       </c>
       <c r="V32" s="35" t="n">
-        <f aca="false">IF(Q32&gt;=Assumptions!$D$86,S32,D32)/U32</f>
+        <f aca="false">IF(U32&gt;0,IF(Q32&gt;=Assumptions!$D$86,S32,D32)/U32,0)</f>
         <v>307.9125</v>
       </c>
       <c r="W32" s="45" t="n">
@@ -5213,7 +5219,7 @@
         <v>0.15</v>
       </c>
       <c r="V33" s="35" t="n">
-        <f aca="false">IF(Q33&gt;=Assumptions!$D$86,S33,D33)/U33</f>
+        <f aca="false">IF(U33&gt;0,IF(Q33&gt;=Assumptions!$D$86,S33,D33)/U33,0)</f>
         <v>200</v>
       </c>
       <c r="W33" s="45" t="n">
@@ -5284,7 +5290,7 @@
         <v>0.22</v>
       </c>
       <c r="V34" s="35" t="n">
-        <f aca="false">IF(Q34&gt;=Assumptions!$D$86,S34,D34)/U34</f>
+        <f aca="false">IF(U34&gt;0,IF(Q34&gt;=Assumptions!$D$86,S34,D34)/U34,0)</f>
         <v>88.6363636363636</v>
       </c>
       <c r="W34" s="45" t="n">
@@ -5351,7 +5357,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5360,46 +5366,46 @@
         <v>288</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5428,7 +5434,7 @@
         <v>0.65</v>
       </c>
       <c r="L40" s="25" t="n">
-        <f aca="false">I40*Assumptions!$D$37*K40*Funnel!B5/(Funnel!O5*Funnel!G5)</f>
+        <f aca="false">IF(Funnel!O5*Funnel!G5&gt;0,I40*Assumptions!$D$37*K40*Budget!G21/(Funnel!O5*Funnel!G5),0)</f>
         <v>0.303789490642157</v>
       </c>
       <c r="M40" s="26" t="n">
@@ -5474,7 +5480,7 @@
         <v>0.75</v>
       </c>
       <c r="L41" s="25" t="n">
-        <f aca="false">I41*Assumptions!$D$38*K41*Funnel!B6/(Funnel!O6*Funnel!G6)</f>
+        <f aca="false">IF(Funnel!O6*Funnel!G6&gt;0,I41*Assumptions!$D$38*K41*Budget!G22/(Funnel!O6*Funnel!G6),0)</f>
         <v>0.427294347428975</v>
       </c>
       <c r="M41" s="26" t="n">
@@ -5520,7 +5526,7 @@
         <v>0.65</v>
       </c>
       <c r="L42" s="25" t="n">
-        <f aca="false">I42*Assumptions!$D$39*K42*Funnel!B7/(Funnel!O7*Funnel!G7)</f>
+        <f aca="false">IF(Funnel!O7*Funnel!G7&gt;0,I42*Assumptions!$D$39*K42*Budget!G23/(Funnel!O7*Funnel!G7),0)</f>
         <v>0.29879257155699</v>
       </c>
       <c r="M42" s="26" t="n">
@@ -5566,7 +5572,7 @@
         <v>0.7</v>
       </c>
       <c r="L43" s="25" t="n">
-        <f aca="false">I43*Assumptions!$D$40*K43*Funnel!B8/(Funnel!O8*Funnel!G8)</f>
+        <f aca="false">IF(Funnel!O8*Funnel!G8&gt;0,I43*Assumptions!$D$40*K43*Budget!G24/(Funnel!O8*Funnel!G8),0)</f>
         <v>0.274640123658854</v>
       </c>
       <c r="M43" s="26" t="n">
@@ -5629,7 +5635,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -9510,19 +9516,19 @@
         <v>0.0482625</v>
       </c>
       <c r="I5" s="26" t="n">
-        <f aca="false">B5/F5</f>
+        <f aca="false">IF(F5&gt;0,B5/F5,0)</f>
         <v>46.1538461538462</v>
       </c>
       <c r="J5" s="26" t="n">
-        <f aca="false">I5/E5</f>
+        <f aca="false">IF(E5&gt;0,I5/E5,0)</f>
         <v>51.2820512820513</v>
       </c>
       <c r="K5" s="26" t="n">
-        <f aca="false">J5/D5</f>
+        <f aca="false">IF(D5&gt;0,J5/D5,0)</f>
         <v>93.2400932400932</v>
       </c>
       <c r="L5" s="23" t="n">
-        <f aca="false">K5/C5</f>
+        <f aca="false">IF(C5&gt;0,K5/C5,0)</f>
         <v>621.600621600622</v>
       </c>
       <c r="M5" s="23" t="n">
@@ -9538,7 +9544,7 @@
         <v>98.7525932400932</v>
       </c>
       <c r="P5" s="25" t="n">
-        <f aca="false">O5/$B$22</f>
+        <f aca="false">IF($B$22&gt;0,O5/$B$22,0)</f>
         <v>0.306549069924901</v>
       </c>
     </row>
@@ -9575,19 +9581,19 @@
         <v>0.0891</v>
       </c>
       <c r="I6" s="26" t="n">
-        <f aca="false">B6/F6</f>
+        <f aca="false">IF(F6&gt;0,B6/F6,0)</f>
         <v>60</v>
       </c>
       <c r="J6" s="26" t="n">
-        <f aca="false">I6/E6</f>
+        <f aca="false">IF(E6&gt;0,I6/E6,0)</f>
         <v>66.6666666666667</v>
       </c>
       <c r="K6" s="26" t="n">
-        <f aca="false">J6/D6</f>
+        <f aca="false">IF(D6&gt;0,J6/D6,0)</f>
         <v>111.111111111111</v>
       </c>
       <c r="L6" s="23" t="n">
-        <f aca="false">K6/C6</f>
+        <f aca="false">IF(C6&gt;0,K6/C6,0)</f>
         <v>505.050505050505</v>
       </c>
       <c r="M6" s="23" t="n">
@@ -9603,7 +9609,7 @@
         <v>105.313820018365</v>
       </c>
       <c r="P6" s="25" t="n">
-        <f aca="false">O6/$B$22</f>
+        <f aca="false">IF($B$22&gt;0,O6/$B$22,0)</f>
         <v>0.326916514469427</v>
       </c>
     </row>
@@ -9640,19 +9646,19 @@
         <v>0.0351</v>
       </c>
       <c r="I7" s="26" t="n">
-        <f aca="false">B7/F7</f>
+        <f aca="false">IF(F7&gt;0,B7/F7,0)</f>
         <v>23.0769230769231</v>
       </c>
       <c r="J7" s="26" t="n">
-        <f aca="false">I7/E7</f>
+        <f aca="false">IF(E7&gt;0,I7/E7,0)</f>
         <v>25.6410256410256</v>
       </c>
       <c r="K7" s="26" t="n">
-        <f aca="false">J7/D7</f>
+        <f aca="false">IF(D7&gt;0,J7/D7,0)</f>
         <v>51.2820512820513</v>
       </c>
       <c r="L7" s="23" t="n">
-        <f aca="false">K7/C7</f>
+        <f aca="false">IF(C7&gt;0,K7/C7,0)</f>
         <v>427.350427350427</v>
       </c>
       <c r="M7" s="23" t="n">
@@ -9668,7 +9674,7 @@
         <v>50.2020512820513</v>
       </c>
       <c r="P7" s="25" t="n">
-        <f aca="false">O7/$B$22</f>
+        <f aca="false">IF($B$22&gt;0,O7/$B$22,0)</f>
         <v>0.155837853203707</v>
       </c>
     </row>
@@ -9705,19 +9711,19 @@
         <v>0.026775</v>
       </c>
       <c r="I8" s="26" t="n">
-        <f aca="false">B8/F8</f>
+        <f aca="false">IF(F8&gt;0,B8/F8,0)</f>
         <v>14.2857142857143</v>
       </c>
       <c r="J8" s="26" t="n">
-        <f aca="false">I8/E8</f>
+        <f aca="false">IF(E8&gt;0,I8/E8,0)</f>
         <v>16.8067226890756</v>
       </c>
       <c r="K8" s="26" t="n">
-        <f aca="false">J8/D8</f>
+        <f aca="false">IF(D8&gt;0,J8/D8,0)</f>
         <v>37.3482726423903</v>
       </c>
       <c r="L8" s="23" t="n">
-        <f aca="false">K8/C8</f>
+        <f aca="false">IF(C8&gt;0,K8/C8,0)</f>
         <v>373.482726423903</v>
       </c>
       <c r="M8" s="23" t="n">
@@ -9733,7 +9739,7 @@
         <v>36.4112856736898</v>
       </c>
       <c r="P8" s="25" t="n">
-        <f aca="false">O8/$B$22</f>
+        <f aca="false">IF($B$22&gt;0,O8/$B$22,0)</f>
         <v>0.113028381248704</v>
       </c>
     </row>
@@ -9746,7 +9752,7 @@
         <v>100</v>
       </c>
       <c r="G9" s="28" t="n">
-        <f aca="false">B9/K9</f>
+        <f aca="false">IF(K9&gt;0,B9/K9,0)</f>
         <v>0.341318446212476</v>
       </c>
       <c r="I9" s="29" t="n">
@@ -9770,7 +9776,7 @@
         <v>1610.75413506972</v>
       </c>
       <c r="N9" s="28" t="n">
-        <f aca="false">O9/M9</f>
+        <f aca="false">IF(M9&gt;0,O9/M9,0)</f>
         <v>0.180461899110145</v>
       </c>
       <c r="O9" s="29" t="n">
@@ -9778,7 +9784,7 @@
         <v>290.6797502142</v>
       </c>
       <c r="P9" s="28" t="n">
-        <f aca="false">O9/$B$22</f>
+        <f aca="false">IF($B$22&gt;0,O9/$B$22,0)</f>
         <v>0.90233181884674</v>
       </c>
     </row>
@@ -9869,7 +9875,7 @@
         <v>441</v>
       </c>
       <c r="B21" s="23" t="n">
-        <f aca="false">B17-B13+1</f>
+        <f aca="false">MAX(0,B17-B13+1)</f>
         <v>41</v>
       </c>
     </row>
@@ -9896,7 +9902,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="33" t="n">
-        <f aca="false">B23/B22</f>
+        <f aca="false">IF(B22&gt;0,B23/B22,IF(B23&gt;0,9.99,0))</f>
         <v>0.90233181884674</v>
       </c>
       <c r="C24" s="22" t="str">
@@ -9909,7 +9915,7 @@
         <v>443</v>
       </c>
       <c r="B25" s="25" t="n">
-        <f aca="false">B9/O9</f>
+        <f aca="false">IF(O9&gt;0,Channels!U35/O9,0)</f>
         <v>0.344021212094447</v>
       </c>
     </row>
@@ -9982,7 +9988,7 @@
         <v>56.060915625</v>
       </c>
       <c r="E30" s="34" t="n">
-        <f aca="false">D30/B30</f>
+        <f aca="false">IF(B30&gt;0,D30/B30,0)</f>
         <v>1.8686971875</v>
       </c>
       <c r="F30" s="23" t="n">
@@ -10004,7 +10010,7 @@
         <v>457</v>
       </c>
       <c r="K30" s="34" t="n">
-        <f aca="false">(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30</f>
+        <f aca="false">IF(B30&gt;0,(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30,0)</f>
         <v>1.4825971875</v>
       </c>
     </row>
@@ -10025,7 +10031,7 @@
         <v>145.767375</v>
       </c>
       <c r="E31" s="34" t="n">
-        <f aca="false">D31/B31</f>
+        <f aca="false">IF(B31&gt;0,D31/B31,0)</f>
         <v>3.239275</v>
       </c>
       <c r="F31" s="23" t="n">
@@ -10047,7 +10053,7 @@
         <v>459</v>
       </c>
       <c r="K31" s="34" t="n">
-        <f aca="false">(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31</f>
+        <f aca="false">IF(B31&gt;0,(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31,0)</f>
         <v>3.239275</v>
       </c>
     </row>
@@ -10068,7 +10074,7 @@
         <v>29.9680875</v>
       </c>
       <c r="E32" s="34" t="n">
-        <f aca="false">D32/B32</f>
+        <f aca="false">IF(B32&gt;0,D32/B32,0)</f>
         <v>1.9978725</v>
       </c>
       <c r="F32" s="23" t="n">
@@ -10090,7 +10096,7 @@
         <v>459</v>
       </c>
       <c r="K32" s="34" t="n">
-        <f aca="false">(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32</f>
+        <f aca="false">IF(B32&gt;0,(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32,0)</f>
         <v>1.9978725</v>
       </c>
     </row>
@@ -10111,7 +10117,7 @@
         <v>17.55369</v>
       </c>
       <c r="E33" s="34" t="n">
-        <f aca="false">D33/B33</f>
+        <f aca="false">IF(B33&gt;0,D33/B33,0)</f>
         <v>1.755369</v>
       </c>
       <c r="F33" s="23" t="n">
@@ -10133,7 +10139,7 @@
         <v>459</v>
       </c>
       <c r="K33" s="34" t="n">
-        <f aca="false">(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33</f>
+        <f aca="false">IF(B33&gt;0,(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33,0)</f>
         <v>1.755369</v>
       </c>
     </row>
@@ -10224,11 +10230,11 @@
         <v>290.6797502142</v>
       </c>
       <c r="C42" s="24" t="n">
-        <f aca="false">B42/($B$22)</f>
+        <f aca="false">IF(($B$22)&gt;0,B42/($B$22),IF(B42&gt;0,9.99,0))</f>
         <v>0.90233181884674</v>
       </c>
       <c r="D42" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22/B42*$B$9,MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
+        <f aca="false">MIN($B$9,IF(B42&gt;0,$B$22/B42*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
         <v>100</v>
       </c>
       <c r="E42" s="23" t="n">
@@ -10240,7 +10246,7 @@
         <v>38733.4681977991</v>
       </c>
       <c r="G42" s="24" t="n">
-        <f aca="false">F42/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F42/Budget!$C$7-1,0)</f>
         <v>0</v>
       </c>
       <c r="H42" s="13" t="s">
@@ -10256,11 +10262,11 @@
         <v>415.256786020285</v>
       </c>
       <c r="C43" s="24" t="n">
-        <f aca="false">B43/($B$22)</f>
+        <f aca="false">IF(($B$22)&gt;0,B43/($B$22),IF(B43&gt;0,9.99,0))</f>
         <v>1.28904545549534</v>
       </c>
       <c r="D43" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22/B43*$B$9,MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
+        <f aca="false">MIN($B$9,IF(B43&gt;0,$B$22/B43*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
         <v>77.5767833272977</v>
       </c>
       <c r="E43" s="23" t="n">
@@ -10272,7 +10278,7 @@
         <v>55333.5259968559</v>
       </c>
       <c r="G43" s="24" t="n">
-        <f aca="false">F43/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F43/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H43" s="13" t="s">
@@ -10288,11 +10294,11 @@
         <v>415.256786020285</v>
       </c>
       <c r="C44" s="24" t="n">
-        <f aca="false">B44/($B$22)</f>
+        <f aca="false">IF(($B$22)&gt;0,B44/($B$22),IF(B44&gt;0,9.99,0))</f>
         <v>1.28904545549534</v>
       </c>
       <c r="D44" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22/B44*$B$9,MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
+        <f aca="false">MIN($B$9,IF(B44&gt;0,$B$22/B44*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
         <v>77.5767833272977</v>
       </c>
       <c r="E44" s="23" t="n">
@@ -10304,7 +10310,7 @@
         <v>55333.5259968559</v>
       </c>
       <c r="G44" s="24" t="n">
-        <f aca="false">F44/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F44/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H44" s="13" t="s">
@@ -10320,11 +10326,11 @@
         <v>290.6797502142</v>
       </c>
       <c r="C45" s="24" t="n">
-        <f aca="false">B45/($B$22)</f>
+        <f aca="false">IF(($B$22)&gt;0,B45/($B$22),IF(B45&gt;0,9.99,0))</f>
         <v>0.90233181884674</v>
       </c>
       <c r="D45" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22/B45*$B$9,MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
+        <f aca="false">MIN($B$9,IF(B45&gt;0,$B$22/B45*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
         <v>100</v>
       </c>
       <c r="E45" s="23" t="n">
@@ -10336,7 +10342,7 @@
         <v>55333.5259968559</v>
       </c>
       <c r="G45" s="24" t="n">
-        <f aca="false">F45/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F45/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H45" s="13" t="s">
@@ -10352,11 +10358,11 @@
         <v>290.6797502142</v>
       </c>
       <c r="C46" s="24" t="n">
-        <f aca="false">B46/($B$22)</f>
+        <f aca="false">IF(($B$22)&gt;0,B46/($B$22),IF(B46&gt;0,9.99,0))</f>
         <v>0.90233181884674</v>
       </c>
       <c r="D46" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22/B46*$B$9,MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
+        <f aca="false">MIN($B$9,IF(B46&gt;0,$B$22/B46*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
         <v>100</v>
       </c>
       <c r="E46" s="23" t="n">
@@ -10368,7 +10374,7 @@
         <v>50353.5086571388</v>
       </c>
       <c r="G46" s="24" t="n">
-        <f aca="false">F46/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F46/Budget!$C$7-1,0)</f>
         <v>0.3</v>
       </c>
       <c r="H46" s="13" t="s">
@@ -10384,11 +10390,11 @@
         <v>290.6797502142</v>
       </c>
       <c r="C47" s="24" t="n">
-        <f aca="false">B47/($B$22*(1-$B$40))</f>
+        <f aca="false">IF(($B$22*(1-$B$40))&gt;0,B47/($B$22*(1-$B$40)),IF(B47&gt;0,9.99,0))</f>
         <v>1.28904545549534</v>
       </c>
       <c r="D47" s="32" t="n">
-        <f aca="false">MIN($B$9,$B$22*(1-$B$40)/B47*$B$9,MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
+        <f aca="false">MIN($B$9,IF(B47&gt;0,$B$22*(1-$B$40)/B47*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
         <v>77.5767833272977</v>
       </c>
       <c r="E47" s="23" t="n">
@@ -10400,7 +10406,7 @@
         <v>38733.4681977991</v>
       </c>
       <c r="G47" s="24" t="n">
-        <f aca="false">F47/Budget!$C$7-1</f>
+        <f aca="false">IF(Budget!$C$7&gt;0,F47/Budget!$C$7-1,0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
@@ -10534,7 +10540,7 @@
         <v>53.7525932400932</v>
       </c>
       <c r="H5" s="24" t="n">
-        <f aca="false">G5/F5</f>
+        <f aca="false">IF(F5&gt;0,G5/F5,0)</f>
         <v>0.0943027951580583</v>
       </c>
       <c r="I5" s="23" t="n">
@@ -10542,7 +10548,7 @@
         <v>134.75</v>
       </c>
       <c r="J5" s="24" t="n">
-        <f aca="false">I5/F5</f>
+        <f aca="false">IF(F5&gt;0,I5/F5,0)</f>
         <v>0.23640350877193</v>
       </c>
       <c r="K5" s="2" t="str">
@@ -10579,7 +10585,7 @@
         <v>105.313820018365</v>
       </c>
       <c r="H6" s="24" t="n">
-        <f aca="false">G6/F6</f>
+        <f aca="false">IF(F6&gt;0,G6/F6,0)</f>
         <v>0.054850947926232</v>
       </c>
       <c r="I6" s="23" t="n">
@@ -10587,7 +10593,7 @@
         <v>409.75</v>
       </c>
       <c r="J6" s="24" t="n">
-        <f aca="false">I6/F6</f>
+        <f aca="false">IF(F6&gt;0,I6/F6,0)</f>
         <v>0.213411458333333</v>
       </c>
       <c r="K6" s="2" t="str">
@@ -10624,7 +10630,7 @@
         <v>50.2020512820513</v>
       </c>
       <c r="H7" s="24" t="n">
-        <f aca="false">G7/F7</f>
+        <f aca="false">IF(F7&gt;0,G7/F7,0)</f>
         <v>0.0912764568764569</v>
       </c>
       <c r="I7" s="23" t="n">
@@ -10632,7 +10638,7 @@
         <v>100.7</v>
       </c>
       <c r="J7" s="24" t="n">
-        <f aca="false">I7/F7</f>
+        <f aca="false">IF(F7&gt;0,I7/F7,0)</f>
         <v>0.183090909090909</v>
       </c>
       <c r="K7" s="2" t="str">
@@ -10669,7 +10675,7 @@
         <v>36.4112856736898</v>
       </c>
       <c r="H8" s="24" t="n">
-        <f aca="false">G8/F8</f>
+        <f aca="false">IF(F8&gt;0,G8/F8,0)</f>
         <v>0.165505843971317</v>
       </c>
       <c r="I8" s="23" t="n">
@@ -10677,7 +10683,7 @@
         <v>64.3</v>
       </c>
       <c r="J8" s="24" t="n">
-        <f aca="false">I8/F8</f>
+        <f aca="false">IF(F8&gt;0,I8/F8,0)</f>
         <v>0.292272727272727</v>
       </c>
       <c r="K8" s="2" t="str">
@@ -10916,19 +10922,19 @@
         <v>505</v>
       </c>
       <c r="B11" s="37" t="n">
-        <f aca="false">B10/B7</f>
+        <f aca="false">IF(B7&gt;0,B10/B7,0)</f>
         <v>4.16666666666667</v>
       </c>
       <c r="C11" s="37" t="n">
-        <f aca="false">C10/C7</f>
+        <f aca="false">IF(C7&gt;0,C10/C7,0)</f>
         <v>4.16666666666667</v>
       </c>
       <c r="D11" s="37" t="n">
-        <f aca="false">D10/D7</f>
+        <f aca="false">IF(D7&gt;0,D10/D7,0)</f>
         <v>4.16666666666667</v>
       </c>
       <c r="E11" s="37" t="n">
-        <f aca="false">E10/E7</f>
+        <f aca="false">IF(E7&gt;0,E10/E7,0)</f>
         <v>4.16666666666667</v>
       </c>
       <c r="G11" s="13" t="s">
@@ -11061,19 +11067,19 @@
         <v>512</v>
       </c>
       <c r="B17" s="37" t="n">
-        <f aca="false">B16/B13</f>
+        <f aca="false">IF(B13&gt;0,B16/B13,0)</f>
         <v>166.505625</v>
       </c>
       <c r="C17" s="37" t="n">
-        <f aca="false">C16/C13</f>
+        <f aca="false">IF(C13&gt;0,C16/C13,0)</f>
         <v>209.5875</v>
       </c>
       <c r="D17" s="37" t="n">
-        <f aca="false">D16/D13</f>
+        <f aca="false">IF(D13&gt;0,D16/D13,0)</f>
         <v>151.36875</v>
       </c>
       <c r="E17" s="37" t="n">
-        <f aca="false">E16/E13</f>
+        <f aca="false">IF(E13&gt;0,E16/E13,0)</f>
         <v>138.560625</v>
       </c>
       <c r="G17" s="13" t="s">
@@ -11135,23 +11141,23 @@
         <v>516</v>
       </c>
       <c r="B20" s="35" t="n">
-        <f aca="false">B19/B18</f>
+        <f aca="false">IF(B18&gt;0,B19/B18,0)</f>
         <v>495.49510278823</v>
       </c>
       <c r="C20" s="35" t="n">
-        <f aca="false">C19/C18</f>
+        <f aca="false">IF(C18&gt;0,C19/C18,0)</f>
         <v>438.795593384965</v>
       </c>
       <c r="D20" s="35" t="n">
-        <f aca="false">D19/D18</f>
+        <f aca="false">IF(D18&gt;0,D19/D18,0)</f>
         <v>399.860884810718</v>
       </c>
       <c r="E20" s="35" t="n">
-        <f aca="false">E19/E18</f>
+        <f aca="false">IF(E18&gt;0,E19/E18,0)</f>
         <v>444.036551818795</v>
       </c>
       <c r="F20" s="36" t="n">
-        <f aca="false">F19/F18</f>
+        <f aca="false">IF(F18&gt;0,F19/F18,0)</f>
         <v>450.47833548117</v>
       </c>
     </row>
@@ -11255,7 +11261,7 @@
         <v>528</v>
       </c>
       <c r="B34" s="35" t="n">
-        <f aca="false">(B32+B33)/B31</f>
+        <f aca="false">IF(B31&gt;0,(B32+B33)/B31,0)</f>
         <v>880.600880600881</v>
       </c>
     </row>
@@ -11350,7 +11356,7 @@
         <v>538</v>
       </c>
       <c r="B47" s="23" t="n">
-        <f aca="false">B43/B41/B39</f>
+        <f aca="false">IF(B41*B39&gt;0,B43/B41/B39,0)</f>
         <v>183.654729109275</v>
       </c>
     </row>
@@ -11359,7 +11365,7 @@
         <v>539</v>
       </c>
       <c r="B48" s="35" t="n">
-        <f aca="false">(B47*B38+B46)/B43</f>
+        <f aca="false">IF(B43&gt;0,(B47*B38+B46)/B43,0)</f>
         <v>221.181512090603</v>
       </c>
     </row>
@@ -11451,19 +11457,19 @@
         <v>558</v>
       </c>
       <c r="C54" s="24" t="n">
-        <f aca="false">(Assumptions!$D$55*4/7+Assumptions!$D$56+Assumptions!$D$57*4/7)</f>
-        <v>0.181428571428571</v>
+        <f aca="false">(Assumptions!$D$55*4/7+Assumptions!$D$56+Assumptions!$D$57*3/7)</f>
+        <v>0.152857142857143</v>
       </c>
       <c r="D54" s="35" t="n">
         <f aca="false">B33+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I2-E")*C54</f>
-        <v>2832.85714285714</v>
+        <v>2575.71428571429</v>
       </c>
       <c r="E54" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E")*C54</f>
-        <v>8.16428571428572</v>
+        <v>6.87857142857143</v>
       </c>
       <c r="F54" s="35" t="n">
-        <f aca="false">B27/B28</f>
+        <f aca="false">IF(B28&gt;0,B27/B28,0)</f>
         <v>200</v>
       </c>
       <c r="G54" s="23" t="n">
@@ -11506,7 +11512,7 @@
         <v>7.7432277318641</v>
       </c>
       <c r="F55" s="35" t="n">
-        <f aca="false">B38/B39</f>
+        <f aca="false">IF(B39&gt;0,B38/B39,0)</f>
         <v>88.6363636363636</v>
       </c>
       <c r="G55" s="23" t="n">
@@ -11714,7 +11720,7 @@
         <v/>
       </c>
       <c r="H5" s="37" t="n">
-        <f aca="false">IF(E5="CPC",F5/G5,IF(E5="Slot",F5/G5,F5))</f>
+        <f aca="false">IF(OR(E5="CPC",E5="Slot"),IF(N(G5)&gt;0,F5/G5,0),F5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="24" t="n">
@@ -11722,7 +11728,7 @@
         <v>0.08</v>
       </c>
       <c r="J5" s="23" t="n">
-        <f aca="false">IF(E5="Slot",Assumptions!H112*G5,Assumptions!H112)</f>
+        <f aca="false">IF(AND(OR(E5="CPC",E5="Slot"),NOT(N(G5)&gt;0)),0,IF(E5="Slot",Assumptions!H112*G5,Assumptions!H112))</f>
         <v>150</v>
       </c>
       <c r="K5" s="26" t="n">
@@ -11754,11 +11760,11 @@
         <v>5E-006</v>
       </c>
       <c r="R5" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C5,$Q$5:$Q$34,"&lt;"&amp;Q5)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C5)*($Q$5:$Q$34&lt;Q5))+1</f>
         <v>1</v>
       </c>
       <c r="S5" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C5,$Q$5:$Q$34,"&lt;"&amp;Q5)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C5)*($Q$5:$Q$34&lt;Q5)*$AH$5:$AH$34)</f>
         <v>0</v>
       </c>
       <c r="T5" s="26" t="n">
@@ -11778,7 +11784,7 @@
         <v>150</v>
       </c>
       <c r="X5" s="35" t="n">
-        <f aca="false">IF(E5="Slot",ROUNDUP(W5/G5,0)*F5,W5*H5)</f>
+        <f aca="false">IF(E5="Slot",IF(N(G5)&gt;0,ROUNDUP(W5/G5,0)*F5,0),W5*H5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="35" t="n">
@@ -11798,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q5)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q5))+1</f>
         <v>1</v>
       </c>
       <c r="AD5" s="2" t="str">
@@ -11855,7 +11861,7 @@
         <v/>
       </c>
       <c r="H6" s="37" t="n">
-        <f aca="false">IF(E6="CPC",F6/G6,IF(E6="Slot",F6/G6,F6))</f>
+        <f aca="false">IF(OR(E6="CPC",E6="Slot"),IF(N(G6)&gt;0,F6/G6,0),F6)</f>
         <v>0</v>
       </c>
       <c r="I6" s="24" t="n">
@@ -11863,7 +11869,7 @@
         <v>0.18</v>
       </c>
       <c r="J6" s="23" t="n">
-        <f aca="false">IF(E6="Slot",Assumptions!H113*G6,Assumptions!H113)</f>
+        <f aca="false">IF(AND(OR(E6="CPC",E6="Slot"),NOT(N(G6)&gt;0)),0,IF(E6="Slot",Assumptions!H113*G6,Assumptions!H113))</f>
         <v>200</v>
       </c>
       <c r="K6" s="26" t="n">
@@ -11895,11 +11901,11 @@
         <v>6E-006</v>
       </c>
       <c r="R6" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C6,$Q$5:$Q$34,"&lt;"&amp;Q6)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C6)*($Q$5:$Q$34&lt;Q6))+1</f>
         <v>1</v>
       </c>
       <c r="S6" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C6,$Q$5:$Q$34,"&lt;"&amp;Q6)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C6)*($Q$5:$Q$34&lt;Q6)*$AH$5:$AH$34)</f>
         <v>0</v>
       </c>
       <c r="T6" s="26" t="n">
@@ -11919,7 +11925,7 @@
         <v>200</v>
       </c>
       <c r="X6" s="35" t="n">
-        <f aca="false">IF(E6="Slot",ROUNDUP(W6/G6,0)*F6,W6*H6)</f>
+        <f aca="false">IF(E6="Slot",IF(N(G6)&gt;0,ROUNDUP(W6/G6,0)*F6,0),W6*H6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="35" t="n">
@@ -11939,7 +11945,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q6)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q6))+1</f>
         <v>2</v>
       </c>
       <c r="AD6" s="2" t="str">
@@ -11996,7 +12002,7 @@
         <v/>
       </c>
       <c r="H7" s="37" t="n">
-        <f aca="false">IF(E7="CPC",F7/G7,IF(E7="Slot",F7/G7,F7))</f>
+        <f aca="false">IF(OR(E7="CPC",E7="Slot"),IF(N(G7)&gt;0,F7/G7,0),F7)</f>
         <v>0</v>
       </c>
       <c r="I7" s="24" t="n">
@@ -12004,7 +12010,7 @@
         <v>0.1</v>
       </c>
       <c r="J7" s="23" t="n">
-        <f aca="false">IF(E7="Slot",Assumptions!H114*G7,Assumptions!H114)</f>
+        <f aca="false">IF(AND(OR(E7="CPC",E7="Slot"),NOT(N(G7)&gt;0)),0,IF(E7="Slot",Assumptions!H114*G7,Assumptions!H114))</f>
         <v>80</v>
       </c>
       <c r="K7" s="26" t="n">
@@ -12036,11 +12042,11 @@
         <v>7E-006</v>
       </c>
       <c r="R7" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C7,$Q$5:$Q$34,"&lt;"&amp;Q7)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C7)*($Q$5:$Q$34&lt;Q7))+1</f>
         <v>1</v>
       </c>
       <c r="S7" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C7,$Q$5:$Q$34,"&lt;"&amp;Q7)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C7)*($Q$5:$Q$34&lt;Q7)*$AH$5:$AH$34)</f>
         <v>0</v>
       </c>
       <c r="T7" s="26" t="n">
@@ -12060,7 +12066,7 @@
         <v>80</v>
       </c>
       <c r="X7" s="35" t="n">
-        <f aca="false">IF(E7="Slot",ROUNDUP(W7/G7,0)*F7,W7*H7)</f>
+        <f aca="false">IF(E7="Slot",IF(N(G7)&gt;0,ROUNDUP(W7/G7,0)*F7,0),W7*H7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="35" t="n">
@@ -12080,7 +12086,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q7)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q7))+1</f>
         <v>3</v>
       </c>
       <c r="AD7" s="2" t="str">
@@ -12137,7 +12143,7 @@
         <v/>
       </c>
       <c r="H8" s="37" t="n">
-        <f aca="false">IF(E8="CPC",F8/G8,IF(E8="Slot",F8/G8,F8))</f>
+        <f aca="false">IF(OR(E8="CPC",E8="Slot"),IF(N(G8)&gt;0,F8/G8,0),F8)</f>
         <v>0</v>
       </c>
       <c r="I8" s="24" t="n">
@@ -12145,7 +12151,7 @@
         <v>0.08</v>
       </c>
       <c r="J8" s="23" t="n">
-        <f aca="false">IF(E8="Slot",Assumptions!H115*G8,Assumptions!H115)</f>
+        <f aca="false">IF(AND(OR(E8="CPC",E8="Slot"),NOT(N(G8)&gt;0)),0,IF(E8="Slot",Assumptions!H115*G8,Assumptions!H115))</f>
         <v>60</v>
       </c>
       <c r="K8" s="26" t="n">
@@ -12177,11 +12183,11 @@
         <v>8E-006</v>
       </c>
       <c r="R8" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C8,$Q$5:$Q$34,"&lt;"&amp;Q8)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C8)*($Q$5:$Q$34&lt;Q8))+1</f>
         <v>1</v>
       </c>
       <c r="S8" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C8,$Q$5:$Q$34,"&lt;"&amp;Q8)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C8)*($Q$5:$Q$34&lt;Q8)*$AH$5:$AH$34)</f>
         <v>0</v>
       </c>
       <c r="T8" s="26" t="n">
@@ -12201,7 +12207,7 @@
         <v>60</v>
       </c>
       <c r="X8" s="35" t="n">
-        <f aca="false">IF(E8="Slot",ROUNDUP(W8/G8,0)*F8,W8*H8)</f>
+        <f aca="false">IF(E8="Slot",IF(N(G8)&gt;0,ROUNDUP(W8/G8,0)*F8,0),W8*H8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="35" t="n">
@@ -12221,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="AC8" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q8)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q8))+1</f>
         <v>4</v>
       </c>
       <c r="AD8" s="2" t="str">
@@ -12278,7 +12284,7 @@
         <v>0.035</v>
       </c>
       <c r="H9" s="37" t="n">
-        <f aca="false">IF(E9="CPC",F9/G9,IF(E9="Slot",F9/G9,F9))</f>
+        <f aca="false">IF(OR(E9="CPC",E9="Slot"),IF(N(G9)&gt;0,F9/G9,0),F9)</f>
         <v>57.1428571428571</v>
       </c>
       <c r="I9" s="24" t="n">
@@ -12286,7 +12292,7 @@
         <v>0.12</v>
       </c>
       <c r="J9" s="23" t="n">
-        <f aca="false">IF(E9="Slot",Assumptions!H116*G9,Assumptions!H116)</f>
+        <f aca="false">IF(AND(OR(E9="CPC",E9="Slot"),NOT(N(G9)&gt;0)),0,IF(E9="Slot",Assumptions!H116*G9,Assumptions!H116))</f>
         <v>450</v>
       </c>
       <c r="K9" s="26" t="n">
@@ -12318,11 +12324,11 @@
         <v>1480.00148900148</v>
       </c>
       <c r="R9" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C9,$Q$5:$Q$34,"&lt;"&amp;Q9)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C9)*($Q$5:$Q$34&lt;Q9))+1</f>
         <v>8</v>
       </c>
       <c r="S9" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C9,$Q$5:$Q$34,"&lt;"&amp;Q9)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C9)*($Q$5:$Q$34&lt;Q9)*$AH$5:$AH$34)</f>
         <v>36.864384375</v>
       </c>
       <c r="T9" s="26" t="n">
@@ -12342,7 +12348,7 @@
         <v>13.125</v>
       </c>
       <c r="X9" s="35" t="n">
-        <f aca="false">IF(E9="Slot",ROUNDUP(W9/G9,0)*F9,W9*H9)</f>
+        <f aca="false">IF(E9="Slot",IF(N(G9)&gt;0,ROUNDUP(W9/G9,0)*F9,0),W9*H9)</f>
         <v>750</v>
       </c>
       <c r="Y9" s="35" t="n">
@@ -12362,7 +12368,7 @@
         <v>1480.00148000148</v>
       </c>
       <c r="AC9" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q9)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q9))+1</f>
         <v>29</v>
       </c>
       <c r="AD9" s="2" t="str">
@@ -12419,7 +12425,7 @@
         <v>0.05</v>
       </c>
       <c r="H10" s="37" t="n">
-        <f aca="false">IF(E10="CPC",F10/G10,IF(E10="Slot",F10/G10,F10))</f>
+        <f aca="false">IF(OR(E10="CPC",E10="Slot"),IF(N(G10)&gt;0,F10/G10,0),F10)</f>
         <v>24</v>
       </c>
       <c r="I10" s="24" t="n">
@@ -12427,7 +12433,7 @@
         <v>0.22</v>
       </c>
       <c r="J10" s="23" t="n">
-        <f aca="false">IF(E10="Slot",Assumptions!H117*G10,Assumptions!H117)</f>
+        <f aca="false">IF(AND(OR(E10="CPC",E10="Slot"),NOT(N(G10)&gt;0)),0,IF(E10="Slot",Assumptions!H117*G10,Assumptions!H117))</f>
         <v>600</v>
       </c>
       <c r="K10" s="26" t="n">
@@ -12459,11 +12465,11 @@
         <v>269.360279360269</v>
       </c>
       <c r="R10" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C10,$Q$5:$Q$34,"&lt;"&amp;Q10)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C10)*($Q$5:$Q$34&lt;Q10))+1</f>
         <v>5</v>
       </c>
       <c r="S10" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C10,$Q$5:$Q$34,"&lt;"&amp;Q10)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C10)*($Q$5:$Q$34&lt;Q10)*$AH$5:$AH$34)</f>
         <v>62.226</v>
       </c>
       <c r="T10" s="26" t="n">
@@ -12483,7 +12489,7 @@
         <v>31.25</v>
       </c>
       <c r="X10" s="35" t="n">
-        <f aca="false">IF(E10="Slot",ROUNDUP(W10/G10,0)*F10,W10*H10)</f>
+        <f aca="false">IF(E10="Slot",IF(N(G10)&gt;0,ROUNDUP(W10/G10,0)*F10,0),W10*H10)</f>
         <v>750</v>
       </c>
       <c r="Y10" s="35" t="n">
@@ -12503,7 +12509,7 @@
         <v>269.360269360269</v>
       </c>
       <c r="AC10" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q10)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q10))+1</f>
         <v>11</v>
       </c>
       <c r="AD10" s="2" t="str">
@@ -12560,7 +12566,7 @@
         <v>0.04</v>
       </c>
       <c r="H11" s="37" t="n">
-        <f aca="false">IF(E11="CPC",F11/G11,IF(E11="Slot",F11/G11,F11))</f>
+        <f aca="false">IF(OR(E11="CPC",E11="Slot"),IF(N(G11)&gt;0,F11/G11,0),F11)</f>
         <v>45</v>
       </c>
       <c r="I11" s="24" t="n">
@@ -12568,7 +12574,7 @@
         <v>0.12</v>
       </c>
       <c r="J11" s="23" t="n">
-        <f aca="false">IF(E11="Slot",Assumptions!H118*G11,Assumptions!H118)</f>
+        <f aca="false">IF(AND(OR(E11="CPC",E11="Slot"),NOT(N(G11)&gt;0)),0,IF(E11="Slot",Assumptions!H118*G11,Assumptions!H118))</f>
         <v>250</v>
       </c>
       <c r="K11" s="26" t="n">
@@ -12600,11 +12606,11 @@
         <v>1282.05129305128</v>
       </c>
       <c r="R11" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C11,$Q$5:$Q$34,"&lt;"&amp;Q11)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C11)*($Q$5:$Q$34&lt;Q11))+1</f>
         <v>6</v>
       </c>
       <c r="S11" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C11,$Q$5:$Q$34,"&lt;"&amp;Q11)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C11)*($Q$5:$Q$34&lt;Q11)*$AH$5:$AH$34)</f>
         <v>16.698749025974</v>
       </c>
       <c r="T11" s="26" t="n">
@@ -12624,7 +12630,7 @@
         <v>16.6666666666667</v>
       </c>
       <c r="X11" s="35" t="n">
-        <f aca="false">IF(E11="Slot",ROUNDUP(W11/G11,0)*F11,W11*H11)</f>
+        <f aca="false">IF(E11="Slot",IF(N(G11)&gt;0,ROUNDUP(W11/G11,0)*F11,0),W11*H11)</f>
         <v>750</v>
       </c>
       <c r="Y11" s="35" t="n">
@@ -12644,7 +12650,7 @@
         <v>1282.05128205128</v>
       </c>
       <c r="AC11" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q11)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q11))+1</f>
         <v>26</v>
       </c>
       <c r="AD11" s="2" t="str">
@@ -12701,7 +12707,7 @@
         <v>0.04</v>
       </c>
       <c r="H12" s="37" t="n">
-        <f aca="false">IF(E12="CPC",F12/G12,IF(E12="Slot",F12/G12,F12))</f>
+        <f aca="false">IF(OR(E12="CPC",E12="Slot"),IF(N(G12)&gt;0,F12/G12,0),F12)</f>
         <v>42.5</v>
       </c>
       <c r="I12" s="24" t="n">
@@ -12709,7 +12715,7 @@
         <v>0.1</v>
       </c>
       <c r="J12" s="23" t="n">
-        <f aca="false">IF(E12="Slot",Assumptions!H119*G12,Assumptions!H119)</f>
+        <f aca="false">IF(AND(OR(E12="CPC",E12="Slot"),NOT(N(G12)&gt;0)),0,IF(E12="Slot",Assumptions!H119*G12,Assumptions!H119))</f>
         <v>200</v>
       </c>
       <c r="K12" s="26" t="n">
@@ -12741,11 +12747,11 @@
         <v>1587.30159930159</v>
       </c>
       <c r="R12" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C12,$Q$5:$Q$34,"&lt;"&amp;Q12)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C12)*($Q$5:$Q$34&lt;Q12))+1</f>
         <v>7</v>
       </c>
       <c r="S12" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C12,$Q$5:$Q$34,"&lt;"&amp;Q12)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C12)*($Q$5:$Q$34&lt;Q12)*$AH$5:$AH$34)</f>
         <v>10.5139513636364</v>
       </c>
       <c r="T12" s="26" t="n">
@@ -12765,7 +12771,7 @@
         <v>17.6470588235294</v>
       </c>
       <c r="X12" s="35" t="n">
-        <f aca="false">IF(E12="Slot",ROUNDUP(W12/G12,0)*F12,W12*H12)</f>
+        <f aca="false">IF(E12="Slot",IF(N(G12)&gt;0,ROUNDUP(W12/G12,0)*F12,0),W12*H12)</f>
         <v>750</v>
       </c>
       <c r="Y12" s="35" t="n">
@@ -12785,7 +12791,7 @@
         <v>1587.30158730159</v>
       </c>
       <c r="AC12" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q12)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q12))+1</f>
         <v>30</v>
       </c>
       <c r="AD12" s="2" t="str">
@@ -12842,7 +12848,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="37" t="n">
-        <f aca="false">IF(E13="CPC",F13/G13,IF(E13="Slot",F13/G13,F13))</f>
+        <f aca="false">IF(OR(E13="CPC",E13="Slot"),IF(N(G13)&gt;0,F13/G13,0),F13)</f>
         <v>96.6</v>
       </c>
       <c r="I13" s="24" t="n">
@@ -12850,7 +12856,7 @@
         <v>0.3</v>
       </c>
       <c r="J13" s="23" t="n">
-        <f aca="false">IF(E13="Slot",Assumptions!H120*G13,Assumptions!H120)</f>
+        <f aca="false">IF(AND(OR(E13="CPC",E13="Slot"),NOT(N(G13)&gt;0)),0,IF(E13="Slot",Assumptions!H120*G13,Assumptions!H120))</f>
         <v>45</v>
       </c>
       <c r="K13" s="26" t="n">
@@ -12882,11 +12888,11 @@
         <v>1000.777013777</v>
       </c>
       <c r="R13" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C13,$Q$5:$Q$34,"&lt;"&amp;Q13)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C13)*($Q$5:$Q$34&lt;Q13))+1</f>
         <v>6</v>
       </c>
       <c r="S13" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C13,$Q$5:$Q$34,"&lt;"&amp;Q13)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C13)*($Q$5:$Q$34&lt;Q13)*$AH$5:$AH$34)</f>
         <v>26.756071875</v>
       </c>
       <c r="T13" s="26" t="n">
@@ -12906,7 +12912,7 @@
         <v>9.48086635586635</v>
       </c>
       <c r="X13" s="35" t="n">
-        <f aca="false">IF(E13="Slot",ROUNDUP(W13/G13,0)*F13,W13*H13)</f>
+        <f aca="false">IF(E13="Slot",IF(N(G13)&gt;0,ROUNDUP(W13/G13,0)*F13,0),W13*H13)</f>
         <v>1449</v>
       </c>
       <c r="Y13" s="35" t="n">
@@ -12926,7 +12932,7 @@
         <v>1583.36321262101</v>
       </c>
       <c r="AC13" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q13)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q13))+1</f>
         <v>24</v>
       </c>
       <c r="AD13" s="2" t="str">
@@ -12983,7 +12989,7 @@
         <v>25</v>
       </c>
       <c r="H14" s="37" t="n">
-        <f aca="false">IF(E14="CPC",F14/G14,IF(E14="Slot",F14/G14,F14))</f>
+        <f aca="false">IF(OR(E14="CPC",E14="Slot"),IF(N(G14)&gt;0,F14/G14,0),F14)</f>
         <v>57.96</v>
       </c>
       <c r="I14" s="24" t="n">
@@ -12991,7 +12997,7 @@
         <v>0.35</v>
       </c>
       <c r="J14" s="23" t="n">
-        <f aca="false">IF(E14="Slot",Assumptions!H121*G14,Assumptions!H121)</f>
+        <f aca="false">IF(AND(OR(E14="CPC",E14="Slot"),NOT(N(G14)&gt;0)),0,IF(E14="Slot",Assumptions!H121*G14,Assumptions!H121))</f>
         <v>75</v>
       </c>
       <c r="K14" s="26" t="n">
@@ -13023,11 +13029,11 @@
         <v>408.888902888889</v>
       </c>
       <c r="R14" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C14,$Q$5:$Q$34,"&lt;"&amp;Q14)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C14)*($Q$5:$Q$34&lt;Q14))+1</f>
         <v>7</v>
       </c>
       <c r="S14" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C14,$Q$5:$Q$34,"&lt;"&amp;Q14)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C14)*($Q$5:$Q$34&lt;Q14)*$AH$5:$AH$34)</f>
         <v>120.610431818182</v>
       </c>
       <c r="T14" s="26" t="n">
@@ -13047,7 +13053,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="35" t="n">
-        <f aca="false">IF(E14="Slot",ROUNDUP(W14/G14,0)*F14,W14*H14)</f>
+        <f aca="false">IF(E14="Slot",IF(N(G14)&gt;0,ROUNDUP(W14/G14,0)*F14,0),W14*H14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="35" t="n">
@@ -13067,7 +13073,7 @@
         <v>–</v>
       </c>
       <c r="AC14" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q14)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q14))+1</f>
         <v>13</v>
       </c>
       <c r="AD14" s="2" t="str">
@@ -13124,7 +13130,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="37" t="n">
-        <f aca="false">IF(E15="CPC",F15/G15,IF(E15="Slot",F15/G15,F15))</f>
+        <f aca="false">IF(OR(E15="CPC",E15="Slot"),IF(N(G15)&gt;0,F15/G15,0),F15)</f>
         <v>96.6</v>
       </c>
       <c r="I15" s="24" t="n">
@@ -13132,7 +13138,7 @@
         <v>0.25</v>
       </c>
       <c r="J15" s="23" t="n">
-        <f aca="false">IF(E15="Slot",Assumptions!H122*G15,Assumptions!H122)</f>
+        <f aca="false">IF(AND(OR(E15="CPC",E15="Slot"),NOT(N(G15)&gt;0)),0,IF(E15="Slot",Assumptions!H122*G15,Assumptions!H122))</f>
         <v>30</v>
       </c>
       <c r="K15" s="26" t="n">
@@ -13164,11 +13170,11 @@
         <v>1321.02565602564</v>
       </c>
       <c r="R15" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C15,$Q$5:$Q$34,"&lt;"&amp;Q15)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C15)*($Q$5:$Q$34&lt;Q15))+1</f>
         <v>7</v>
       </c>
       <c r="S15" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C15,$Q$5:$Q$34,"&lt;"&amp;Q15)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C15)*($Q$5:$Q$34&lt;Q15)*$AH$5:$AH$34)</f>
         <v>24.888749025974</v>
       </c>
       <c r="T15" s="26" t="n">
@@ -13188,7 +13194,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="35" t="n">
-        <f aca="false">IF(E15="Slot",ROUNDUP(W15/G15,0)*F15,W15*H15)</f>
+        <f aca="false">IF(E15="Slot",IF(N(G15)&gt;0,ROUNDUP(W15/G15,0)*F15,0),W15*H15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="35" t="n">
@@ -13208,7 +13214,7 @@
         <v>–</v>
       </c>
       <c r="AC15" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q15)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q15))+1</f>
         <v>27</v>
       </c>
       <c r="AD15" s="2" t="str">
@@ -13265,7 +13271,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="37" t="n">
-        <f aca="false">IF(E16="CPC",F16/G16,IF(E16="Slot",F16/G16,F16))</f>
+        <f aca="false">IF(OR(E16="CPC",E16="Slot"),IF(N(G16)&gt;0,F16/G16,0),F16)</f>
         <v>96.6</v>
       </c>
       <c r="I16" s="24" t="n">
@@ -13273,7 +13279,7 @@
         <v>0.25</v>
       </c>
       <c r="J16" s="23" t="n">
-        <f aca="false">IF(E16="Slot",Assumptions!H123*G16,Assumptions!H123)</f>
+        <f aca="false">IF(AND(OR(E16="CPC",E16="Slot"),NOT(N(G16)&gt;0)),0,IF(E16="Slot",Assumptions!H123*G16,Assumptions!H123))</f>
         <v>30</v>
       </c>
       <c r="K16" s="26" t="n">
@@ -13305,11 +13311,11 @@
         <v>1443.13727090196</v>
       </c>
       <c r="R16" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C16,$Q$5:$Q$34,"&lt;"&amp;Q16)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C16)*($Q$5:$Q$34&lt;Q16))+1</f>
         <v>6</v>
       </c>
       <c r="S16" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C16,$Q$5:$Q$34,"&lt;"&amp;Q16)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C16)*($Q$5:$Q$34&lt;Q16)*$AH$5:$AH$34)</f>
         <v>8.50582636363636</v>
       </c>
       <c r="T16" s="26" t="n">
@@ -13329,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="35" t="n">
-        <f aca="false">IF(E16="Slot",ROUNDUP(W16/G16,0)*F16,W16*H16)</f>
+        <f aca="false">IF(E16="Slot",IF(N(G16)&gt;0,ROUNDUP(W16/G16,0)*F16,0),W16*H16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="35" t="n">
@@ -13349,7 +13355,7 @@
         <v>–</v>
       </c>
       <c r="AC16" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q16)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q16))+1</f>
         <v>28</v>
       </c>
       <c r="AD16" s="2" t="str">
@@ -13406,7 +13412,7 @@
         <v>0.08</v>
       </c>
       <c r="H17" s="37" t="n">
-        <f aca="false">IF(E17="CPC",F17/G17,IF(E17="Slot",F17/G17,F17))</f>
+        <f aca="false">IF(OR(E17="CPC",E17="Slot"),IF(N(G17)&gt;0,F17/G17,0),F17)</f>
         <v>43.75</v>
       </c>
       <c r="I17" s="24" t="n">
@@ -13414,7 +13420,7 @@
         <v>0.25</v>
       </c>
       <c r="J17" s="23" t="n">
-        <f aca="false">IF(E17="Slot",Assumptions!H124*G17,Assumptions!H124)</f>
+        <f aca="false">IF(AND(OR(E17="CPC",E17="Slot"),NOT(N(G17)&gt;0)),0,IF(E17="Slot",Assumptions!H124*G17,Assumptions!H124))</f>
         <v>150</v>
       </c>
       <c r="K17" s="26" t="n">
@@ -13446,11 +13452,11 @@
         <v>598.290615290598</v>
       </c>
       <c r="R17" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C17,$Q$5:$Q$34,"&lt;"&amp;Q17)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C17)*($Q$5:$Q$34&lt;Q17))+1</f>
         <v>3</v>
       </c>
       <c r="S17" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C17,$Q$5:$Q$34,"&lt;"&amp;Q17)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C17)*($Q$5:$Q$34&lt;Q17)*$AH$5:$AH$34)</f>
         <v>4.7619</v>
       </c>
       <c r="T17" s="26" t="n">
@@ -13470,7 +13476,7 @@
         <v>117.690023310023</v>
       </c>
       <c r="X17" s="35" t="n">
-        <f aca="false">IF(E17="Slot",ROUNDUP(W17/G17,0)*F17,W17*H17)</f>
+        <f aca="false">IF(E17="Slot",IF(N(G17)&gt;0,ROUNDUP(W17/G17,0)*F17,0),W17*H17)</f>
         <v>5148.93851981352</v>
       </c>
       <c r="Y17" s="35" t="n">
@@ -13490,7 +13496,7 @@
         <v>598.290598290598</v>
       </c>
       <c r="AC17" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q17)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q17))+1</f>
         <v>14</v>
       </c>
       <c r="AD17" s="2" t="str">
@@ -13547,7 +13553,7 @@
         <v>0.08</v>
       </c>
       <c r="H18" s="37" t="n">
-        <f aca="false">IF(E18="CPC",F18/G18,IF(E18="Slot",F18/G18,F18))</f>
+        <f aca="false">IF(OR(E18="CPC",E18="Slot"),IF(N(G18)&gt;0,F18/G18,0),F18)</f>
         <v>43.75</v>
       </c>
       <c r="I18" s="24" t="n">
@@ -13555,7 +13561,7 @@
         <v>0.2</v>
       </c>
       <c r="J18" s="23" t="n">
-        <f aca="false">IF(E18="Slot",Assumptions!H125*G18,Assumptions!H125)</f>
+        <f aca="false">IF(AND(OR(E18="CPC",E18="Slot"),NOT(N(G18)&gt;0)),0,IF(E18="Slot",Assumptions!H125*G18,Assumptions!H125))</f>
         <v>100</v>
       </c>
       <c r="K18" s="26" t="n">
@@ -13587,11 +13593,11 @@
         <v>816.993482052288</v>
       </c>
       <c r="R18" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C18,$Q$5:$Q$34,"&lt;"&amp;Q18)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C18)*($Q$5:$Q$34&lt;Q18))+1</f>
         <v>3</v>
       </c>
       <c r="S18" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C18,$Q$5:$Q$34,"&lt;"&amp;Q18)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C18)*($Q$5:$Q$34&lt;Q18)*$AH$5:$AH$34)</f>
         <v>2.76318</v>
       </c>
       <c r="T18" s="26" t="n">
@@ -13611,7 +13617,7 @@
         <v>100</v>
       </c>
       <c r="X18" s="35" t="n">
-        <f aca="false">IF(E18="Slot",ROUNDUP(W18/G18,0)*F18,W18*H18)</f>
+        <f aca="false">IF(E18="Slot",IF(N(G18)&gt;0,ROUNDUP(W18/G18,0)*F18,0),W18*H18)</f>
         <v>4375</v>
       </c>
       <c r="Y18" s="35" t="n">
@@ -13631,7 +13637,7 @@
         <v>816.993464052288</v>
       </c>
       <c r="AC18" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q18)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q18))+1</f>
         <v>17</v>
       </c>
       <c r="AD18" s="2" t="str">
@@ -13688,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="37" t="n">
-        <f aca="false">IF(E19="CPC",F19/G19,IF(E19="Slot",F19/G19,F19))</f>
+        <f aca="false">IF(OR(E19="CPC",E19="Slot"),IF(N(G19)&gt;0,F19/G19,0),F19)</f>
         <v>18</v>
       </c>
       <c r="I19" s="24" t="n">
@@ -13696,7 +13702,7 @@
         <v>0.05</v>
       </c>
       <c r="J19" s="23" t="n">
-        <f aca="false">IF(E19="Slot",Assumptions!H126*G19,Assumptions!H126)</f>
+        <f aca="false">IF(AND(OR(E19="CPC",E19="Slot"),NOT(N(G19)&gt;0)),0,IF(E19="Slot",Assumptions!H126*G19,Assumptions!H126))</f>
         <v>400</v>
       </c>
       <c r="K19" s="26" t="n">
@@ -13728,11 +13734,11 @@
         <v>1118.88113788112</v>
       </c>
       <c r="R19" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C19,$Q$5:$Q$34,"&lt;"&amp;Q19)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C19)*($Q$5:$Q$34&lt;Q19))+1</f>
         <v>7</v>
       </c>
       <c r="S19" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C19,$Q$5:$Q$34,"&lt;"&amp;Q19)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C19)*($Q$5:$Q$34&lt;Q19)*$AH$5:$AH$34)</f>
         <v>31.099696875</v>
       </c>
       <c r="T19" s="26" t="n">
@@ -13752,7 +13758,7 @@
         <v>41.6666666666667</v>
       </c>
       <c r="X19" s="35" t="n">
-        <f aca="false">IF(E19="Slot",ROUNDUP(W19/G19,0)*F19,W19*H19)</f>
+        <f aca="false">IF(E19="Slot",IF(N(G19)&gt;0,ROUNDUP(W19/G19,0)*F19,0),W19*H19)</f>
         <v>750</v>
       </c>
       <c r="Y19" s="35" t="n">
@@ -13772,7 +13778,7 @@
         <v>1118.88111888112</v>
       </c>
       <c r="AC19" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q19)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q19))+1</f>
         <v>25</v>
       </c>
       <c r="AD19" s="2" t="str">
@@ -13829,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="37" t="n">
-        <f aca="false">IF(E20="CPC",F20/G20,IF(E20="Slot",F20/G20,F20))</f>
+        <f aca="false">IF(OR(E20="CPC",E20="Slot"),IF(N(G20)&gt;0,F20/G20,0),F20)</f>
         <v>12</v>
       </c>
       <c r="I20" s="24" t="n">
@@ -13837,7 +13843,7 @@
         <v>0.12</v>
       </c>
       <c r="J20" s="23" t="n">
-        <f aca="false">IF(E20="Slot",Assumptions!H127*G20,Assumptions!H127)</f>
+        <f aca="false">IF(AND(OR(E20="CPC",E20="Slot"),NOT(N(G20)&gt;0)),0,IF(E20="Slot",Assumptions!H127*G20,Assumptions!H127))</f>
         <v>500</v>
       </c>
       <c r="K20" s="26" t="n">
@@ -13869,11 +13875,11 @@
         <v>246.913600246914</v>
       </c>
       <c r="R20" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C20,$Q$5:$Q$34,"&lt;"&amp;Q20)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C20)*($Q$5:$Q$34&lt;Q20))+1</f>
         <v>4</v>
       </c>
       <c r="S20" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C20,$Q$5:$Q$34,"&lt;"&amp;Q20)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C20)*($Q$5:$Q$34&lt;Q20)*$AH$5:$AH$34)</f>
         <v>40.9635</v>
       </c>
       <c r="T20" s="26" t="n">
@@ -13893,7 +13899,7 @@
         <v>62.5</v>
       </c>
       <c r="X20" s="35" t="n">
-        <f aca="false">IF(E20="Slot",ROUNDUP(W20/G20,0)*F20,W20*H20)</f>
+        <f aca="false">IF(E20="Slot",IF(N(G20)&gt;0,ROUNDUP(W20/G20,0)*F20,0),W20*H20)</f>
         <v>750</v>
       </c>
       <c r="Y20" s="35" t="n">
@@ -13913,7 +13919,7 @@
         <v>246.913580246914</v>
       </c>
       <c r="AC20" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q20)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q20))+1</f>
         <v>10</v>
       </c>
       <c r="AD20" s="2" t="str">
@@ -13970,7 +13976,7 @@
         <v>0.07</v>
       </c>
       <c r="H21" s="37" t="n">
-        <f aca="false">IF(E21="CPC",F21/G21,IF(E21="Slot",F21/G21,F21))</f>
+        <f aca="false">IF(OR(E21="CPC",E21="Slot"),IF(N(G21)&gt;0,F21/G21,0),F21)</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I21" s="24" t="n">
@@ -13978,7 +13984,7 @@
         <v>0.15</v>
       </c>
       <c r="J21" s="23" t="n">
-        <f aca="false">IF(E21="Slot",Assumptions!H128*G21,Assumptions!H128)</f>
+        <f aca="false">IF(AND(OR(E21="CPC",E21="Slot"),NOT(N(G21)&gt;0)),0,IF(E21="Slot",Assumptions!H128*G21,Assumptions!H128))</f>
         <v>80</v>
       </c>
       <c r="K21" s="26" t="n">
@@ -14010,11 +14016,11 @@
         <v>651.200672200651</v>
       </c>
       <c r="R21" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C21,$Q$5:$Q$34,"&lt;"&amp;Q21)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C21)*($Q$5:$Q$34&lt;Q21))+1</f>
         <v>3</v>
       </c>
       <c r="S21" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C21,$Q$5:$Q$34,"&lt;"&amp;Q21)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C21)*($Q$5:$Q$34&lt;Q21)*$AH$5:$AH$34)</f>
         <v>8.30115</v>
       </c>
       <c r="T21" s="26" t="n">
@@ -14034,7 +14040,7 @@
         <v>80</v>
       </c>
       <c r="X21" s="35" t="n">
-        <f aca="false">IF(E21="Slot",ROUNDUP(W21/G21,0)*F21,W21*H21)</f>
+        <f aca="false">IF(E21="Slot",IF(N(G21)&gt;0,ROUNDUP(W21/G21,0)*F21,0),W21*H21)</f>
         <v>2514.28571428571</v>
       </c>
       <c r="Y21" s="35" t="n">
@@ -14054,7 +14060,7 @@
         <v>651.200651200651</v>
       </c>
       <c r="AC21" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q21)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q21))+1</f>
         <v>15</v>
       </c>
       <c r="AD21" s="2" t="str">
@@ -14111,7 +14117,7 @@
         <v>0.07</v>
       </c>
       <c r="H22" s="37" t="n">
-        <f aca="false">IF(E22="CPC",F22/G22,IF(E22="Slot",F22/G22,F22))</f>
+        <f aca="false">IF(OR(E22="CPC",E22="Slot"),IF(N(G22)&gt;0,F22/G22,0),F22)</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I22" s="24" t="n">
@@ -14119,7 +14125,7 @@
         <v>0.25</v>
       </c>
       <c r="J22" s="23" t="n">
-        <f aca="false">IF(E22="Slot",Assumptions!H129*G22,Assumptions!H129)</f>
+        <f aca="false">IF(AND(OR(E22="CPC",E22="Slot"),NOT(N(G22)&gt;0)),0,IF(E22="Slot",Assumptions!H129*G22,Assumptions!H129))</f>
         <v>100</v>
       </c>
       <c r="K22" s="26" t="n">
@@ -14151,11 +14157,11 @@
         <v>310.405665738977</v>
       </c>
       <c r="R22" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C22,$Q$5:$Q$34,"&lt;"&amp;Q22)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C22)*($Q$5:$Q$34&lt;Q22))+1</f>
         <v>6</v>
       </c>
       <c r="S22" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C22,$Q$5:$Q$34,"&lt;"&amp;Q22)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C22)*($Q$5:$Q$34&lt;Q22)*$AH$5:$AH$34)</f>
         <v>112.901625</v>
       </c>
       <c r="T22" s="26" t="n">
@@ -14175,7 +14181,7 @@
         <v>23.8636363636364</v>
       </c>
       <c r="X22" s="35" t="n">
-        <f aca="false">IF(E22="Slot",ROUNDUP(W22/G22,0)*F22,W22*H22)</f>
+        <f aca="false">IF(E22="Slot",IF(N(G22)&gt;0,ROUNDUP(W22/G22,0)*F22,0),W22*H22)</f>
         <v>750</v>
       </c>
       <c r="Y22" s="35" t="n">
@@ -14195,7 +14201,7 @@
         <v>310.405643738977</v>
       </c>
       <c r="AC22" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q22)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q22))+1</f>
         <v>12</v>
       </c>
       <c r="AD22" s="2" t="str">
@@ -14252,7 +14258,7 @@
         <v>0.07</v>
       </c>
       <c r="H23" s="37" t="n">
-        <f aca="false">IF(E23="CPC",F23/G23,IF(E23="Slot",F23/G23,F23))</f>
+        <f aca="false">IF(OR(E23="CPC",E23="Slot"),IF(N(G23)&gt;0,F23/G23,0),F23)</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I23" s="24" t="n">
@@ -14260,7 +14266,7 @@
         <v>0.15</v>
       </c>
       <c r="J23" s="23" t="n">
-        <f aca="false">IF(E23="Slot",Assumptions!H130*G23,Assumptions!H130)</f>
+        <f aca="false">IF(AND(OR(E23="CPC",E23="Slot"),NOT(N(G23)&gt;0)),0,IF(E23="Slot",Assumptions!H130*G23,Assumptions!H130))</f>
         <v>40</v>
       </c>
       <c r="K23" s="26" t="n">
@@ -14292,11 +14298,11 @@
         <v>716.320739320716</v>
       </c>
       <c r="R23" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C23,$Q$5:$Q$34,"&lt;"&amp;Q23)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C23)*($Q$5:$Q$34&lt;Q23))+1</f>
         <v>4</v>
       </c>
       <c r="S23" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C23,$Q$5:$Q$34,"&lt;"&amp;Q23)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C23)*($Q$5:$Q$34&lt;Q23)*$AH$5:$AH$34)</f>
         <v>14.4770785714286</v>
       </c>
       <c r="T23" s="26" t="n">
@@ -14316,7 +14322,7 @@
         <v>23.8636363636364</v>
       </c>
       <c r="X23" s="35" t="n">
-        <f aca="false">IF(E23="Slot",ROUNDUP(W23/G23,0)*F23,W23*H23)</f>
+        <f aca="false">IF(E23="Slot",IF(N(G23)&gt;0,ROUNDUP(W23/G23,0)*F23,0),W23*H23)</f>
         <v>750</v>
       </c>
       <c r="Y23" s="35" t="n">
@@ -14336,7 +14342,7 @@
         <v>716.320716320716</v>
       </c>
       <c r="AC23" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q23)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q23))+1</f>
         <v>16</v>
       </c>
       <c r="AD23" s="2" t="str">
@@ -14393,7 +14399,7 @@
         <v>0.07</v>
       </c>
       <c r="H24" s="37" t="n">
-        <f aca="false">IF(E24="CPC",F24/G24,IF(E24="Slot",F24/G24,F24))</f>
+        <f aca="false">IF(OR(E24="CPC",E24="Slot"),IF(N(G24)&gt;0,F24/G24,0),F24)</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I24" s="24" t="n">
@@ -14401,7 +14407,7 @@
         <v>0.12</v>
       </c>
       <c r="J24" s="23" t="n">
-        <f aca="false">IF(E24="Slot",Assumptions!H131*G24,Assumptions!H131)</f>
+        <f aca="false">IF(AND(OR(E24="CPC",E24="Slot"),NOT(N(G24)&gt;0)),0,IF(E24="Slot",Assumptions!H131*G24,Assumptions!H131))</f>
         <v>30</v>
       </c>
       <c r="K24" s="26" t="n">
@@ -14433,11 +14439,11 @@
         <v>978.169069395936</v>
       </c>
       <c r="R24" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C24,$Q$5:$Q$34,"&lt;"&amp;Q24)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C24)*($Q$5:$Q$34&lt;Q24))+1</f>
         <v>4</v>
       </c>
       <c r="S24" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C24,$Q$5:$Q$34,"&lt;"&amp;Q24)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C24)*($Q$5:$Q$34&lt;Q24)*$AH$5:$AH$34)</f>
         <v>7.20018</v>
       </c>
       <c r="T24" s="26" t="n">
@@ -14457,7 +14463,7 @@
         <v>30</v>
       </c>
       <c r="X24" s="35" t="n">
-        <f aca="false">IF(E24="Slot",ROUNDUP(W24/G24,0)*F24,W24*H24)</f>
+        <f aca="false">IF(E24="Slot",IF(N(G24)&gt;0,ROUNDUP(W24/G24,0)*F24,0),W24*H24)</f>
         <v>942.857142857143</v>
       </c>
       <c r="Y24" s="35" t="n">
@@ -14477,7 +14483,7 @@
         <v>978.169045395936</v>
       </c>
       <c r="AC24" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q24)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q24))+1</f>
         <v>19</v>
       </c>
       <c r="AD24" s="2" t="str">
@@ -14567,11 +14573,11 @@
         <v>22.5217866521964</v>
       </c>
       <c r="R25" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C25,$Q$5:$Q$34,"&lt;"&amp;Q25)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C25)*($Q$5:$Q$34&lt;Q25))+1</f>
         <v>2</v>
       </c>
       <c r="S25" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C25,$Q$5:$Q$34,"&lt;"&amp;Q25)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C25)*($Q$5:$Q$34&lt;Q25)*$AH$5:$AH$34)</f>
         <v>3.861</v>
       </c>
       <c r="T25" s="26" t="n">
@@ -14591,7 +14597,7 @@
         <v>24</v>
       </c>
       <c r="X25" s="35" t="n">
-        <f aca="false">IF(E25="Slot",ROUNDUP(W25/G25,0)*F25,W25*H25)</f>
+        <f aca="false">IF(E25="Slot",IF(N(G25)&gt;0,ROUNDUP(W25/G25,0)*F25,0),W25*H25)</f>
         <v>100</v>
       </c>
       <c r="Y25" s="35" t="n">
@@ -14611,7 +14617,7 @@
         <v>22.5217616521964</v>
       </c>
       <c r="AC25" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q25)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q25))+1</f>
         <v>6</v>
       </c>
       <c r="AD25" s="2" t="str">
@@ -14701,11 +14707,11 @@
         <v>17.8923144236894</v>
       </c>
       <c r="R26" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C26,$Q$5:$Q$34,"&lt;"&amp;Q26)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C26)*($Q$5:$Q$34&lt;Q26))+1</f>
         <v>2</v>
       </c>
       <c r="S26" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C26,$Q$5:$Q$34,"&lt;"&amp;Q26)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C26)*($Q$5:$Q$34&lt;Q26)*$AH$5:$AH$34)</f>
         <v>14.58</v>
       </c>
       <c r="T26" s="26" t="n">
@@ -14725,7 +14731,7 @@
         <v>36</v>
       </c>
       <c r="X26" s="35" t="n">
-        <f aca="false">IF(E26="Slot",ROUNDUP(W26/G26,0)*F26,W26*H26)</f>
+        <f aca="false">IF(E26="Slot",IF(N(G26)&gt;0,ROUNDUP(W26/G26,0)*F26,0),W26*H26)</f>
         <v>150</v>
       </c>
       <c r="Y26" s="35" t="n">
@@ -14745,7 +14751,7 @@
         <v>17.8922884236894</v>
       </c>
       <c r="AC26" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q26)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q26))+1</f>
         <v>5</v>
       </c>
       <c r="AD26" s="2" t="str">
@@ -14835,11 +14841,11 @@
         <v>24.7739648174161</v>
       </c>
       <c r="R27" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C27,$Q$5:$Q$34,"&lt;"&amp;Q27)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C27)*($Q$5:$Q$34&lt;Q27))+1</f>
         <v>2</v>
       </c>
       <c r="S27" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C27,$Q$5:$Q$34,"&lt;"&amp;Q27)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C27)*($Q$5:$Q$34&lt;Q27)*$AH$5:$AH$34)</f>
         <v>2.34</v>
       </c>
       <c r="T27" s="26" t="n">
@@ -14859,7 +14865,7 @@
         <v>14.4</v>
       </c>
       <c r="X27" s="35" t="n">
-        <f aca="false">IF(E27="Slot",ROUNDUP(W27/G27,0)*F27,W27*H27)</f>
+        <f aca="false">IF(E27="Slot",IF(N(G27)&gt;0,ROUNDUP(W27/G27,0)*F27,0),W27*H27)</f>
         <v>60</v>
       </c>
       <c r="Y27" s="35" t="n">
@@ -14879,7 +14885,7 @@
         <v>24.7739378174161</v>
       </c>
       <c r="AC27" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q27)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q27))+1</f>
         <v>7</v>
       </c>
       <c r="AD27" s="2" t="str">
@@ -14969,11 +14975,11 @@
         <v>27.0639936828915</v>
       </c>
       <c r="R28" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C28,$Q$5:$Q$34,"&lt;"&amp;Q28)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C28)*($Q$5:$Q$34&lt;Q28))+1</f>
         <v>2</v>
       </c>
       <c r="S28" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C28,$Q$5:$Q$34,"&lt;"&amp;Q28)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C28)*($Q$5:$Q$34&lt;Q28)*$AH$5:$AH$34)</f>
         <v>1.2852</v>
       </c>
       <c r="T28" s="26" t="n">
@@ -14993,7 +14999,7 @@
         <v>9.6</v>
       </c>
       <c r="X28" s="35" t="n">
-        <f aca="false">IF(E28="Slot",ROUNDUP(W28/G28,0)*F28,W28*H28)</f>
+        <f aca="false">IF(E28="Slot",IF(N(G28)&gt;0,ROUNDUP(W28/G28,0)*F28,0),W28*H28)</f>
         <v>40</v>
       </c>
       <c r="Y28" s="35" t="n">
@@ -15013,7 +15019,7 @@
         <v>27.0639656828915</v>
       </c>
       <c r="AC28" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q28)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q28))+1</f>
         <v>8</v>
       </c>
       <c r="AD28" s="2" t="str">
@@ -15103,11 +15109,11 @@
         <v>1000.000029</v>
       </c>
       <c r="R29" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C29,$Q$5:$Q$34,"&lt;"&amp;Q29)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C29)*($Q$5:$Q$34&lt;Q29))+1</f>
         <v>5</v>
       </c>
       <c r="S29" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C29,$Q$5:$Q$34,"&lt;"&amp;Q29)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C29)*($Q$5:$Q$34&lt;Q29)*$AH$5:$AH$34)</f>
         <v>22.59343125</v>
       </c>
       <c r="T29" s="26" t="n">
@@ -15127,7 +15133,7 @@
         <v>25</v>
       </c>
       <c r="X29" s="35" t="n">
-        <f aca="false">IF(E29="Slot",ROUNDUP(W29/G29,0)*F29,W29*H29)</f>
+        <f aca="false">IF(E29="Slot",IF(N(G29)&gt;0,ROUNDUP(W29/G29,0)*F29,0),W29*H29)</f>
         <v>4162.640625</v>
       </c>
       <c r="Y29" s="35" t="n">
@@ -15147,7 +15153,7 @@
         <v>1000</v>
       </c>
       <c r="AC29" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q29)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q29))+1</f>
         <v>20</v>
       </c>
       <c r="AD29" s="2" t="str">
@@ -15237,11 +15243,11 @@
         <v>1000.00003</v>
       </c>
       <c r="R30" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C30,$Q$5:$Q$34,"&lt;"&amp;Q30)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C30)*($Q$5:$Q$34&lt;Q30))+1</f>
         <v>8</v>
       </c>
       <c r="S30" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C30,$Q$5:$Q$34,"&lt;"&amp;Q30)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C30)*($Q$5:$Q$34&lt;Q30)*$AH$5:$AH$34)</f>
         <v>131.241681818182</v>
       </c>
       <c r="T30" s="26" t="n">
@@ -15261,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="35" t="n">
-        <f aca="false">IF(E30="Slot",ROUNDUP(W30/G30,0)*F30,W30*H30)</f>
+        <f aca="false">IF(E30="Slot",IF(N(G30)&gt;0,ROUNDUP(W30/G30,0)*F30,0),W30*H30)</f>
         <v>0</v>
       </c>
       <c r="Y30" s="35" t="n">
@@ -15281,7 +15287,7 @@
         <v>–</v>
       </c>
       <c r="AC30" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q30)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q30))+1</f>
         <v>21</v>
       </c>
       <c r="AD30" s="2" t="str">
@@ -15371,11 +15377,11 @@
         <v>1000.000031</v>
       </c>
       <c r="R31" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C31,$Q$5:$Q$34,"&lt;"&amp;Q31)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C31)*($Q$5:$Q$34&lt;Q31))+1</f>
         <v>5</v>
       </c>
       <c r="S31" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C31,$Q$5:$Q$34,"&lt;"&amp;Q31)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C31)*($Q$5:$Q$34&lt;Q31)*$AH$5:$AH$34)</f>
         <v>15.185061525974</v>
       </c>
       <c r="T31" s="26" t="n">
@@ -15395,7 +15401,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="35" t="n">
-        <f aca="false">IF(E31="Slot",ROUNDUP(W31/G31,0)*F31,W31*H31)</f>
+        <f aca="false">IF(E31="Slot",IF(N(G31)&gt;0,ROUNDUP(W31/G31,0)*F31,0),W31*H31)</f>
         <v>0</v>
       </c>
       <c r="Y31" s="35" t="n">
@@ -15415,7 +15421,7 @@
         <v>–</v>
       </c>
       <c r="AC31" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q31)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q31))+1</f>
         <v>22</v>
       </c>
       <c r="AD31" s="2" t="str">
@@ -15505,11 +15511,11 @@
         <v>1000.000032</v>
       </c>
       <c r="R32" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C32,$Q$5:$Q$34,"&lt;"&amp;Q32)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C32)*($Q$5:$Q$34&lt;Q32))+1</f>
         <v>5</v>
       </c>
       <c r="S32" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C32,$Q$5:$Q$34,"&lt;"&amp;Q32)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C32)*($Q$5:$Q$34&lt;Q32)*$AH$5:$AH$34)</f>
         <v>7.39734136363636</v>
       </c>
       <c r="T32" s="26" t="n">
@@ -15529,7 +15535,7 @@
         <v>3.21462175852628</v>
       </c>
       <c r="X32" s="35" t="n">
-        <f aca="false">IF(E32="Slot",ROUNDUP(W32/G32,0)*F32,W32*H32)</f>
+        <f aca="false">IF(E32="Slot",IF(N(G32)&gt;0,ROUNDUP(W32/G32,0)*F32,0),W32*H32)</f>
         <v>445.42</v>
       </c>
       <c r="Y32" s="35" t="n">
@@ -15549,7 +15555,7 @@
         <v>1000</v>
       </c>
       <c r="AC32" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q32)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q32))+1</f>
         <v>23</v>
       </c>
       <c r="AD32" s="2" t="str">
@@ -15639,11 +15645,11 @@
         <v>880.600913600881</v>
       </c>
       <c r="R33" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C33,$Q$5:$Q$34,"&lt;"&amp;Q33)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C33)*($Q$5:$Q$34&lt;Q33))+1</f>
         <v>4</v>
       </c>
       <c r="S33" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C33,$Q$5:$Q$34,"&lt;"&amp;Q33)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C33)*($Q$5:$Q$34&lt;Q33)*$AH$5:$AH$34)</f>
         <v>11.01043125</v>
       </c>
       <c r="T33" s="26" t="n">
@@ -15663,7 +15669,7 @@
         <v>300</v>
       </c>
       <c r="X33" s="35" t="n">
-        <f aca="false">IF(E33="Slot",ROUNDUP(W33/G33,0)*F33,W33*H33)</f>
+        <f aca="false">IF(E33="Slot",IF(N(G33)&gt;0,ROUNDUP(W33/G33,0)*F33,0),W33*H33)</f>
         <v>9000</v>
       </c>
       <c r="Y33" s="35" t="n">
@@ -15683,7 +15689,7 @@
         <v>880.600880600881</v>
       </c>
       <c r="AC33" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q33)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q33))+1</f>
         <v>18</v>
       </c>
       <c r="AD33" s="2" t="str">
@@ -15773,11 +15779,11 @@
         <v>221.181546090603</v>
       </c>
       <c r="R34" s="23" t="n">
-        <f aca="false">COUNTIFS($C$5:$C$34,C34,$Q$5:$Q$34,"&lt;"&amp;Q34)+1</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C34)*($Q$5:$Q$34&lt;Q34))+1</f>
         <v>3</v>
       </c>
       <c r="S34" s="26" t="n">
-        <f aca="false">SUMIFS($AH$5:$AH$34,$C$5:$C$34,C34,$Q$5:$Q$34,"&lt;"&amp;Q34)</f>
+        <f aca="false">SUMPRODUCT(($C$5:$C$34=C34)*($Q$5:$Q$34&lt;Q34)*$AH$5:$AH$34)</f>
         <v>22.9635</v>
       </c>
       <c r="T34" s="26" t="n">
@@ -15797,7 +15803,7 @@
         <v>140.785958761165</v>
       </c>
       <c r="X34" s="35" t="n">
-        <f aca="false">IF(E34="Slot",ROUNDUP(W34/G34,0)*F34,W34*H34)</f>
+        <f aca="false">IF(E34="Slot",IF(N(G34)&gt;0,ROUNDUP(W34/G34,0)*F34,0),W34*H34)</f>
         <v>2745.32619584272</v>
       </c>
       <c r="Y34" s="35" t="n">
@@ -15817,7 +15823,7 @@
         <v>227.948091296738</v>
       </c>
       <c r="AC34" s="23" t="n">
-        <f aca="false">COUNTIF($Q$5:$Q$34,"&lt;"&amp;Q34)+1</f>
+        <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q34))+1</f>
         <v>9</v>
       </c>
       <c r="AD34" s="2" t="str">
@@ -16087,7 +16093,7 @@
         <v>618</v>
       </c>
       <c r="C10" s="35" t="n">
-        <f aca="false">C9/(1-Assumptions!$D$48)*Assumptions!$D$48</f>
+        <f aca="false">IF(Assumptions!$D$48&lt;1,C9/(1-Assumptions!$D$48)*Assumptions!$D$48,0)</f>
         <v>6835.31791725867</v>
       </c>
     </row>
@@ -16123,7 +16129,7 @@
         <v>622</v>
       </c>
       <c r="C14" s="41" t="n">
-        <f aca="false">C9/C13</f>
+        <f aca="false">IF(C13&gt;0,C9/C13,0)</f>
         <v>387.334681977991</v>
       </c>
     </row>
@@ -16132,7 +16138,7 @@
         <v>623</v>
       </c>
       <c r="C15" s="35" t="n">
-        <f aca="false">C12/C13</f>
+        <f aca="false">IF(C13&gt;0,C12/C13,0)</f>
         <v>475</v>
       </c>
     </row>
@@ -16141,7 +16147,7 @@
         <v>624</v>
       </c>
       <c r="C16" s="24" t="n">
-        <f aca="false">Weekly!N5/C12</f>
+        <f aca="false">IF(C12&gt;0,Weekly!N5/C12,0)</f>
         <v>0.297811868076705</v>
       </c>
     </row>
@@ -16202,7 +16208,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="35" t="n">
-        <f aca="false">F21/G21</f>
+        <f aca="false">IF(G21&gt;0,F21/G21,0)</f>
         <v>664.197544642857</v>
       </c>
       <c r="I21" s="26" t="n">
@@ -16235,7 +16241,7 @@
         <v>45</v>
       </c>
       <c r="H22" s="35" t="n">
-        <f aca="false">F22/G22</f>
+        <f aca="false">IF(G22&gt;0,F22/G22,0)</f>
         <v>123.229471018727</v>
       </c>
       <c r="I22" s="26" t="n">
@@ -16268,7 +16274,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="35" t="n">
-        <f aca="false">F23/G23</f>
+        <f aca="false">IF(G23&gt;0,F23/G23,0)</f>
         <v>447.262567987568</v>
       </c>
       <c r="I23" s="26" t="n">
@@ -16301,7 +16307,7 @@
         <v>10</v>
       </c>
       <c r="H24" s="35" t="n">
-        <f aca="false">F24/G24</f>
+        <f aca="false">IF(G24&gt;0,F24/G24,0)</f>
         <v>655.327714285714</v>
       </c>
       <c r="I24" s="26" t="n">
@@ -16382,7 +16388,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="24" t="n">
-        <f aca="false">C29/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C29/$C$9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -16403,7 +16409,7 @@
         <v>689.872244283762</v>
       </c>
       <c r="F30" s="24" t="n">
-        <f aca="false">C30/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C30/$C$9,0)</f>
         <v>0.0774523981348633</v>
       </c>
     </row>
@@ -16424,7 +16430,7 @@
         <v>1583.36321262101</v>
       </c>
       <c r="F31" s="24" t="n">
-        <f aca="false">C31/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C31/$C$9,0)</f>
         <v>0.037409508299139</v>
       </c>
     </row>
@@ -16445,7 +16451,7 @@
         <v>682.177632696661</v>
       </c>
       <c r="F32" s="24" t="n">
-        <f aca="false">C32/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C32/$C$9,0)</f>
         <v>0.245883959349519</v>
       </c>
     </row>
@@ -16466,7 +16472,7 @@
         <v>404.551201011378</v>
       </c>
       <c r="F33" s="24" t="n">
-        <f aca="false">C33/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C33/$C$9,0)</f>
         <v>0.0387261990674316</v>
       </c>
     </row>
@@ -16487,7 +16493,7 @@
         <v>598.102911424966</v>
       </c>
       <c r="F34" s="24" t="n">
-        <f aca="false">C34/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C34/$C$9,0)</f>
         <v>0.127980867394274</v>
       </c>
     </row>
@@ -16508,7 +16514,7 @@
         <v>20.9285958167923</v>
       </c>
       <c r="F35" s="24" t="n">
-        <f aca="false">C35/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C35/$C$9,0)</f>
         <v>0.00903611311573405</v>
       </c>
     </row>
@@ -16529,7 +16535,7 @@
         <v>1000</v>
       </c>
       <c r="F36" s="24" t="n">
-        <f aca="false">C36/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C36/$C$9,0)</f>
         <v>0.118968448719029</v>
       </c>
     </row>
@@ -16550,7 +16556,7 @@
         <v>880.600880600881</v>
       </c>
       <c r="F37" s="24" t="n">
-        <f aca="false">C37/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C37/$C$9,0)</f>
         <v>0.263338153658535</v>
       </c>
     </row>
@@ -16571,7 +16577,7 @@
         <v>227.948091296738</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">C38/$C$9</f>
+        <f aca="false">IF($C$9&gt;0,C38/$C$9,0)</f>
         <v>0.0812043522614752</v>
       </c>
     </row>
@@ -16661,7 +16667,7 @@
         <v>100</v>
       </c>
       <c r="I45" s="35" t="n">
-        <f aca="false">C45/H45</f>
+        <f aca="false">IF(H45&gt;0,C45/H45,0)</f>
         <v>475</v>
       </c>
     </row>
@@ -16695,7 +16701,7 @@
         <v>96.8809299857171</v>
       </c>
       <c r="I46" s="35" t="n">
-        <f aca="false">C46/H46</f>
+        <f aca="false">IF(H46&gt;0,C46/H46,0)</f>
         <v>416.748683213016</v>
       </c>
     </row>
@@ -16729,7 +16735,7 @@
         <v>90.6720880966647</v>
       </c>
       <c r="I47" s="35" t="n">
-        <f aca="false">C47/H47</f>
+        <f aca="false">IF(H47&gt;0,C47/H47,0)</f>
         <v>366.706013922967</v>
       </c>
     </row>
@@ -16763,7 +16769,7 @@
         <v>80.2795630966647</v>
       </c>
       <c r="I48" s="35" t="n">
-        <f aca="false">C48/H48</f>
+        <f aca="false">IF(H48&gt;0,C48/H48,0)</f>
         <v>295.841171574422</v>
       </c>
     </row>
@@ -16995,19 +17001,19 @@
         <v>3.861</v>
       </c>
       <c r="J8" s="35" t="n">
-        <f aca="false">MIN(C8,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D8)))</f>
+        <f aca="false">MIN(C8,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D8)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K8" s="35" t="n">
-        <f aca="false">MIN(C8,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D8)))</f>
+        <f aca="false">MIN(C8,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D8)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L8" s="35" t="n">
-        <f aca="false">MIN(C8,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D8)))</f>
+        <f aca="false">MIN(C8,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D8)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M8" s="35" t="n">
-        <f aca="false">MIN(C8,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D8)))</f>
+        <f aca="false">MIN(C8,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D8)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N8" s="35" t="n">
@@ -17053,19 +17059,19 @@
         <v>14.58</v>
       </c>
       <c r="J9" s="35" t="n">
-        <f aca="false">MIN(C9,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D9)))</f>
+        <f aca="false">MIN(C9,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D9)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K9" s="35" t="n">
-        <f aca="false">MIN(C9,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D9)))</f>
+        <f aca="false">MIN(C9,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D9)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L9" s="35" t="n">
-        <f aca="false">MIN(C9,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D9)))</f>
+        <f aca="false">MIN(C9,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D9)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M9" s="35" t="n">
-        <f aca="false">MIN(C9,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D9)))</f>
+        <f aca="false">MIN(C9,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D9)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N9" s="35" t="n">
@@ -17111,19 +17117,19 @@
         <v>2.34</v>
       </c>
       <c r="J10" s="35" t="n">
-        <f aca="false">MIN(C10,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D10)))</f>
+        <f aca="false">MIN(C10,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D10)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K10" s="35" t="n">
-        <f aca="false">MIN(C10,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D10)))</f>
+        <f aca="false">MIN(C10,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D10)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L10" s="35" t="n">
-        <f aca="false">MIN(C10,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D10)))</f>
+        <f aca="false">MIN(C10,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D10)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M10" s="35" t="n">
-        <f aca="false">MIN(C10,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D10)))</f>
+        <f aca="false">MIN(C10,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D10)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N10" s="35" t="n">
@@ -17169,19 +17175,19 @@
         <v>1.2852</v>
       </c>
       <c r="J11" s="35" t="n">
-        <f aca="false">MIN(C11,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D11)))</f>
+        <f aca="false">MIN(C11,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D11)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K11" s="35" t="n">
-        <f aca="false">MIN(C11,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D11)))</f>
+        <f aca="false">MIN(C11,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D11)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L11" s="35" t="n">
-        <f aca="false">MIN(C11,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D11)))</f>
+        <f aca="false">MIN(C11,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D11)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M11" s="35" t="n">
-        <f aca="false">MIN(C11,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D11)))</f>
+        <f aca="false">MIN(C11,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D11)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N11" s="35" t="n">
@@ -17227,19 +17233,19 @@
         <v>0</v>
       </c>
       <c r="J12" s="35" t="n">
-        <f aca="false">MIN(C12,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D12)))</f>
+        <f aca="false">MIN(C12,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D12)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K12" s="35" t="n">
-        <f aca="false">MIN(C12,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D12)))</f>
+        <f aca="false">MIN(C12,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D12)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="L12" s="35" t="n">
-        <f aca="false">MIN(C12,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D12)))</f>
+        <f aca="false">MIN(C12,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D12)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="M12" s="35" t="n">
-        <f aca="false">MIN(C12,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D12)))</f>
+        <f aca="false">MIN(C12,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D12)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="N12" s="35" t="n">
@@ -17285,19 +17291,19 @@
         <v>2.784375</v>
       </c>
       <c r="J13" s="35" t="n">
-        <f aca="false">MIN(C13,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D13)))</f>
+        <f aca="false">MIN(C13,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D13)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K13" s="35" t="n">
-        <f aca="false">MIN(C13,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D13)))</f>
+        <f aca="false">MIN(C13,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D13)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L13" s="35" t="n">
-        <f aca="false">MIN(C13,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D13)))</f>
+        <f aca="false">MIN(C13,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D13)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M13" s="35" t="n">
-        <f aca="false">MIN(C13,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D13)))</f>
+        <f aca="false">MIN(C13,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D13)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N13" s="35" t="n">
@@ -17343,19 +17349,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="35" t="n">
-        <f aca="false">MIN(C14,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D14)))</f>
+        <f aca="false">MIN(C14,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D14)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K14" s="35" t="n">
-        <f aca="false">MIN(C14,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D14)))</f>
+        <f aca="false">MIN(C14,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D14)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="L14" s="35" t="n">
-        <f aca="false">MIN(C14,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D14)))</f>
+        <f aca="false">MIN(C14,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D14)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="M14" s="35" t="n">
-        <f aca="false">MIN(C14,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D14)))</f>
+        <f aca="false">MIN(C14,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D14)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="N14" s="35" t="n">
@@ -17401,19 +17407,19 @@
         <v>0</v>
       </c>
       <c r="J15" s="35" t="n">
-        <f aca="false">MIN(C15,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D15)))</f>
+        <f aca="false">MIN(C15,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D15)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K15" s="35" t="n">
-        <f aca="false">MIN(C15,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D15)))</f>
+        <f aca="false">MIN(C15,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D15)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="L15" s="35" t="n">
-        <f aca="false">MIN(C15,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D15)))</f>
+        <f aca="false">MIN(C15,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D15)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="M15" s="35" t="n">
-        <f aca="false">MIN(C15,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D15)))</f>
+        <f aca="false">MIN(C15,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D15)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="N15" s="35" t="n">
@@ -17459,19 +17465,19 @@
         <v>0</v>
       </c>
       <c r="J16" s="35" t="n">
-        <f aca="false">MIN(C16,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D16)))</f>
+        <f aca="false">MIN(C16,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D16)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K16" s="35" t="n">
-        <f aca="false">MIN(C16,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D16)))</f>
+        <f aca="false">MIN(C16,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D16)*$C$8:$C$37)))</f>
         <v>1449</v>
       </c>
       <c r="L16" s="35" t="n">
-        <f aca="false">MIN(C16,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D16)))</f>
+        <f aca="false">MIN(C16,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D16)*$C$8:$C$37)))</f>
         <v>1449</v>
       </c>
       <c r="M16" s="35" t="n">
-        <f aca="false">MIN(C16,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D16)))</f>
+        <f aca="false">MIN(C16,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D16)*$C$8:$C$37)))</f>
         <v>1449</v>
       </c>
       <c r="N16" s="35" t="n">
@@ -17517,19 +17523,19 @@
         <v>0</v>
       </c>
       <c r="J17" s="35" t="n">
-        <f aca="false">MIN(C17,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D17)))</f>
+        <f aca="false">MIN(C17,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D17)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K17" s="35" t="n">
-        <f aca="false">MIN(C17,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D17)))</f>
+        <f aca="false">MIN(C17,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D17)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L17" s="35" t="n">
-        <f aca="false">MIN(C17,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D17)))</f>
+        <f aca="false">MIN(C17,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D17)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M17" s="35" t="n">
-        <f aca="false">MIN(C17,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D17)))</f>
+        <f aca="false">MIN(C17,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D17)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N17" s="35" t="n">
@@ -17575,19 +17581,19 @@
         <v>0</v>
       </c>
       <c r="J18" s="35" t="n">
-        <f aca="false">MIN(C18,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D18)))</f>
+        <f aca="false">MIN(C18,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D18)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K18" s="35" t="n">
-        <f aca="false">MIN(C18,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D18)))</f>
+        <f aca="false">MIN(C18,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D18)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L18" s="35" t="n">
-        <f aca="false">MIN(C18,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D18)))</f>
+        <f aca="false">MIN(C18,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D18)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M18" s="35" t="n">
-        <f aca="false">MIN(C18,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D18)))</f>
+        <f aca="false">MIN(C18,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D18)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N18" s="35" t="n">
@@ -17633,19 +17639,19 @@
         <v>0</v>
       </c>
       <c r="J19" s="35" t="n">
-        <f aca="false">MIN(C19,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D19)))</f>
+        <f aca="false">MIN(C19,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D19)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K19" s="35" t="n">
-        <f aca="false">MIN(C19,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D19)))</f>
+        <f aca="false">MIN(C19,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D19)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L19" s="35" t="n">
-        <f aca="false">MIN(C19,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D19)))</f>
+        <f aca="false">MIN(C19,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D19)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M19" s="35" t="n">
-        <f aca="false">MIN(C19,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D19)))</f>
+        <f aca="false">MIN(C19,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D19)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N19" s="35" t="n">
@@ -17691,19 +17697,19 @@
         <v>8.60608295454545</v>
       </c>
       <c r="J20" s="35" t="n">
-        <f aca="false">MIN(C20,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D20)))</f>
+        <f aca="false">MIN(C20,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D20)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K20" s="35" t="n">
-        <f aca="false">MIN(C20,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D20)))</f>
+        <f aca="false">MIN(C20,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D20)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L20" s="35" t="n">
-        <f aca="false">MIN(C20,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D20)))</f>
+        <f aca="false">MIN(C20,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D20)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M20" s="35" t="n">
-        <f aca="false">MIN(C20,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D20)))</f>
+        <f aca="false">MIN(C20,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D20)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N20" s="35" t="n">
@@ -17749,19 +17755,19 @@
         <v>5.355</v>
       </c>
       <c r="J21" s="35" t="n">
-        <f aca="false">MIN(C21,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
+        <f aca="false">MIN(C21,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D21)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K21" s="35" t="n">
-        <f aca="false">MIN(C21,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
+        <f aca="false">MIN(C21,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D21)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L21" s="35" t="n">
-        <f aca="false">MIN(C21,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
+        <f aca="false">MIN(C21,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D21)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M21" s="35" t="n">
-        <f aca="false">MIN(C21,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D21)))</f>
+        <f aca="false">MIN(C21,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D21)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N21" s="35" t="n">
@@ -17807,19 +17813,19 @@
         <v>0</v>
       </c>
       <c r="J22" s="35" t="n">
-        <f aca="false">MIN(C22,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D22)))</f>
+        <f aca="false">MIN(C22,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D22)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K22" s="35" t="n">
-        <f aca="false">MIN(C22,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D22)))</f>
+        <f aca="false">MIN(C22,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D22)*$C$8:$C$37)))</f>
         <v>715.718197799099</v>
       </c>
       <c r="L22" s="35" t="n">
-        <f aca="false">MIN(C22,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D22)))</f>
+        <f aca="false">MIN(C22,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D22)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="M22" s="35" t="n">
-        <f aca="false">MIN(C22,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D22)))</f>
+        <f aca="false">MIN(C22,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D22)*$C$8:$C$37)))</f>
         <v>750</v>
       </c>
       <c r="N22" s="35" t="n">
@@ -17865,19 +17871,19 @@
         <v>3.0375</v>
       </c>
       <c r="J23" s="35" t="n">
-        <f aca="false">MIN(C23,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D23)))</f>
+        <f aca="false">MIN(C23,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D23)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K23" s="35" t="n">
-        <f aca="false">MIN(C23,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D23)))</f>
+        <f aca="false">MIN(C23,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D23)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L23" s="35" t="n">
-        <f aca="false">MIN(C23,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D23)))</f>
+        <f aca="false">MIN(C23,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D23)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M23" s="35" t="n">
-        <f aca="false">MIN(C23,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D23)))</f>
+        <f aca="false">MIN(C23,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D23)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N23" s="35" t="n">
@@ -17923,19 +17929,19 @@
         <v>3.861</v>
       </c>
       <c r="J24" s="35" t="n">
-        <f aca="false">MIN(C24,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D24)))</f>
+        <f aca="false">MIN(C24,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D24)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K24" s="35" t="n">
-        <f aca="false">MIN(C24,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D24)))</f>
+        <f aca="false">MIN(C24,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D24)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L24" s="35" t="n">
-        <f aca="false">MIN(C24,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D24)))</f>
+        <f aca="false">MIN(C24,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D24)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M24" s="35" t="n">
-        <f aca="false">MIN(C24,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D24)))</f>
+        <f aca="false">MIN(C24,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D24)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N24" s="35" t="n">
@@ -17981,19 +17987,19 @@
         <v>2.41619318181818</v>
       </c>
       <c r="J25" s="35" t="n">
-        <f aca="false">MIN(C25,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D25)))</f>
+        <f aca="false">MIN(C25,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D25)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K25" s="35" t="n">
-        <f aca="false">MIN(C25,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D25)))</f>
+        <f aca="false">MIN(C25,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D25)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L25" s="35" t="n">
-        <f aca="false">MIN(C25,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D25)))</f>
+        <f aca="false">MIN(C25,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D25)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M25" s="35" t="n">
-        <f aca="false">MIN(C25,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D25)))</f>
+        <f aca="false">MIN(C25,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D25)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N25" s="35" t="n">
@@ -18039,19 +18045,19 @@
         <v>1.04701704545455</v>
       </c>
       <c r="J26" s="35" t="n">
-        <f aca="false">MIN(C26,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D26)))</f>
+        <f aca="false">MIN(C26,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D26)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K26" s="35" t="n">
-        <f aca="false">MIN(C26,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D26)))</f>
+        <f aca="false">MIN(C26,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D26)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L26" s="35" t="n">
-        <f aca="false">MIN(C26,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D26)))</f>
+        <f aca="false">MIN(C26,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D26)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M26" s="35" t="n">
-        <f aca="false">MIN(C26,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D26)))</f>
+        <f aca="false">MIN(C26,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D26)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N26" s="35" t="n">
@@ -18097,19 +18103,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="35" t="n">
-        <f aca="false">MIN(C27,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D27)))</f>
+        <f aca="false">MIN(C27,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D27)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K27" s="35" t="n">
-        <f aca="false">MIN(C27,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D27)))</f>
+        <f aca="false">MIN(C27,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D27)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L27" s="35" t="n">
-        <f aca="false">MIN(C27,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D27)))</f>
+        <f aca="false">MIN(C27,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D27)*$C$8:$C$37)))</f>
         <v>942.857142857143</v>
       </c>
       <c r="M27" s="35" t="n">
-        <f aca="false">MIN(C27,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D27)))</f>
+        <f aca="false">MIN(C27,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D27)*$C$8:$C$37)))</f>
         <v>942.857142857143</v>
       </c>
       <c r="N27" s="35" t="n">
@@ -18155,19 +18161,19 @@
         <v>4.44015</v>
       </c>
       <c r="J28" s="35" t="n">
-        <f aca="false">MIN(C28,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D28)))</f>
+        <f aca="false">MIN(C28,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D28)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K28" s="35" t="n">
-        <f aca="false">MIN(C28,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D28)))</f>
+        <f aca="false">MIN(C28,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D28)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L28" s="35" t="n">
-        <f aca="false">MIN(C28,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D28)))</f>
+        <f aca="false">MIN(C28,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D28)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M28" s="35" t="n">
-        <f aca="false">MIN(C28,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D28)))</f>
+        <f aca="false">MIN(C28,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D28)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N28" s="35" t="n">
@@ -18213,19 +18219,19 @@
         <v>8.3835</v>
       </c>
       <c r="J29" s="35" t="n">
-        <f aca="false">MIN(C29,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D29)))</f>
+        <f aca="false">MIN(C29,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D29)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K29" s="35" t="n">
-        <f aca="false">MIN(C29,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D29)))</f>
+        <f aca="false">MIN(C29,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D29)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L29" s="35" t="n">
-        <f aca="false">MIN(C29,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D29)))</f>
+        <f aca="false">MIN(C29,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D29)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M29" s="35" t="n">
-        <f aca="false">MIN(C29,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D29)))</f>
+        <f aca="false">MIN(C29,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D29)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N29" s="35" t="n">
@@ -18271,19 +18277,19 @@
         <v>2.4219</v>
       </c>
       <c r="J30" s="35" t="n">
-        <f aca="false">MIN(C30,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D30)))</f>
+        <f aca="false">MIN(C30,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D30)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K30" s="35" t="n">
-        <f aca="false">MIN(C30,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D30)))</f>
+        <f aca="false">MIN(C30,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D30)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L30" s="35" t="n">
-        <f aca="false">MIN(C30,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D30)))</f>
+        <f aca="false">MIN(C30,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D30)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M30" s="35" t="n">
-        <f aca="false">MIN(C30,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D30)))</f>
+        <f aca="false">MIN(C30,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D30)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N30" s="35" t="n">
@@ -18329,19 +18335,19 @@
         <v>1.47798</v>
       </c>
       <c r="J31" s="35" t="n">
-        <f aca="false">MIN(C31,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D31)))</f>
+        <f aca="false">MIN(C31,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D31)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K31" s="35" t="n">
-        <f aca="false">MIN(C31,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D31)))</f>
+        <f aca="false">MIN(C31,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D31)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L31" s="35" t="n">
-        <f aca="false">MIN(C31,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D31)))</f>
+        <f aca="false">MIN(C31,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D31)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M31" s="35" t="n">
-        <f aca="false">MIN(C31,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D31)))</f>
+        <f aca="false">MIN(C31,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D31)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N31" s="35" t="n">
@@ -18387,19 +18393,19 @@
         <v>0</v>
       </c>
       <c r="J32" s="35" t="n">
-        <f aca="false">MIN(C32,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
+        <f aca="false">MIN(C32,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D32)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K32" s="35" t="n">
-        <f aca="false">MIN(C32,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
+        <f aca="false">MIN(C32,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D32)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L32" s="35" t="n">
-        <f aca="false">MIN(C32,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
+        <f aca="false">MIN(C32,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D32)*$C$8:$C$37)))</f>
         <v>4162.640625</v>
       </c>
       <c r="M32" s="35" t="n">
-        <f aca="false">MIN(C32,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D32)))</f>
+        <f aca="false">MIN(C32,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D32)*$C$8:$C$37)))</f>
         <v>4162.640625</v>
       </c>
       <c r="N32" s="35" t="n">
@@ -18445,19 +18451,19 @@
         <v>0</v>
       </c>
       <c r="J33" s="35" t="n">
-        <f aca="false">MIN(C33,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D33)))</f>
+        <f aca="false">MIN(C33,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D33)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K33" s="35" t="n">
-        <f aca="false">MIN(C33,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D33)))</f>
+        <f aca="false">MIN(C33,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D33)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L33" s="35" t="n">
-        <f aca="false">MIN(C33,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D33)))</f>
+        <f aca="false">MIN(C33,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D33)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M33" s="35" t="n">
-        <f aca="false">MIN(C33,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D33)))</f>
+        <f aca="false">MIN(C33,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D33)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N33" s="35" t="n">
@@ -18503,19 +18509,19 @@
         <v>0</v>
       </c>
       <c r="J34" s="35" t="n">
-        <f aca="false">MIN(C34,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D34)))</f>
+        <f aca="false">MIN(C34,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D34)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K34" s="35" t="n">
-        <f aca="false">MIN(C34,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D34)))</f>
+        <f aca="false">MIN(C34,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D34)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L34" s="35" t="n">
-        <f aca="false">MIN(C34,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D34)))</f>
+        <f aca="false">MIN(C34,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D34)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M34" s="35" t="n">
-        <f aca="false">MIN(C34,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D34)))</f>
+        <f aca="false">MIN(C34,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D34)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N34" s="35" t="n">
@@ -18561,19 +18567,19 @@
         <v>0</v>
       </c>
       <c r="J35" s="35" t="n">
-        <f aca="false">MIN(C35,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D35)))</f>
+        <f aca="false">MIN(C35,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D35)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K35" s="35" t="n">
-        <f aca="false">MIN(C35,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D35)))</f>
+        <f aca="false">MIN(C35,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D35)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L35" s="35" t="n">
-        <f aca="false">MIN(C35,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D35)))</f>
+        <f aca="false">MIN(C35,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D35)*$C$8:$C$37)))</f>
         <v>445.42</v>
       </c>
       <c r="M35" s="35" t="n">
-        <f aca="false">MIN(C35,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D35)))</f>
+        <f aca="false">MIN(C35,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D35)*$C$8:$C$37)))</f>
         <v>445.42</v>
       </c>
       <c r="N35" s="35" t="n">
@@ -18619,19 +18625,19 @@
         <v>0.584233096664704</v>
       </c>
       <c r="J36" s="35" t="n">
-        <f aca="false">MIN(C36,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
+        <f aca="false">MIN(C36,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D36)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K36" s="35" t="n">
-        <f aca="false">MIN(C36,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
+        <f aca="false">MIN(C36,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D36)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L36" s="35" t="n">
-        <f aca="false">MIN(C36,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
+        <f aca="false">MIN(C36,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D36)*$C$8:$C$37)))</f>
         <v>471.050429941955</v>
       </c>
       <c r="M36" s="35" t="n">
-        <f aca="false">MIN(C36,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D36)))</f>
+        <f aca="false">MIN(C36,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D36)*$C$8:$C$37)))</f>
         <v>8546.05042994196</v>
       </c>
       <c r="N36" s="35" t="n">
@@ -18677,19 +18683,19 @@
         <v>13.7984318181818</v>
       </c>
       <c r="J37" s="35" t="n">
-        <f aca="false">MIN(C37,MAX(0,F$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D37)))</f>
+        <f aca="false">MIN(C37,MAX(0,F$6-SUMPRODUCT(($D$8:$D$37&gt;D37)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="K37" s="35" t="n">
-        <f aca="false">MIN(C37,MAX(0,G$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D37)))</f>
+        <f aca="false">MIN(C37,MAX(0,G$6-SUMPRODUCT(($D$8:$D$37&gt;D37)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="L37" s="35" t="n">
-        <f aca="false">MIN(C37,MAX(0,H$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D37)))</f>
+        <f aca="false">MIN(C37,MAX(0,H$6-SUMPRODUCT(($D$8:$D$37&gt;D37)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="M37" s="35" t="n">
-        <f aca="false">MIN(C37,MAX(0,I$6-SUMIFS($C$8:$C$37,$D$8:$D$37,"&gt;"&amp;D37)))</f>
+        <f aca="false">MIN(C37,MAX(0,I$6-SUMPRODUCT(($D$8:$D$37&gt;D37)*$C$8:$C$37)))</f>
         <v>0</v>
       </c>
       <c r="N37" s="35" t="n">
@@ -18812,19 +18818,19 @@
         <v>629</v>
       </c>
       <c r="F44" s="35" t="n">
-        <f aca="false">F4/F43</f>
+        <f aca="false">IF(F43&gt;0,F4/F43,0)</f>
         <v>475</v>
       </c>
       <c r="G44" s="35" t="n">
-        <f aca="false">G4/G43</f>
+        <f aca="false">IF(G43&gt;0,G4/G43,0)</f>
         <v>416.748683213016</v>
       </c>
       <c r="H44" s="35" t="n">
-        <f aca="false">H4/H43</f>
+        <f aca="false">IF(H43&gt;0,H4/H43,0)</f>
         <v>366.706013922967</v>
       </c>
       <c r="I44" s="35" t="n">
-        <f aca="false">I4/I43</f>
+        <f aca="false">IF(I43&gt;0,I4/I43,0)</f>
         <v>295.841171574422</v>
       </c>
     </row>
@@ -18959,7 +18965,7 @@
         <v>0.03</v>
       </c>
       <c r="E4" s="24" t="n">
-        <f aca="false">IF(B4&lt;=Funnel!$B$20,D4,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B4&lt;=Funnel!$B$20,D4,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0.0394736842105263</v>
       </c>
       <c r="F4" s="24" t="n">
@@ -19015,7 +19021,7 @@
         <v>0.998299142073115</v>
       </c>
       <c r="S4" s="2" t="str">
-        <f aca="false">IF(P4&gt;Q4+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R4&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P4&gt;Q4+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R4&gt;Assumptions!$D$106,"Full",IF(AND(Q4&gt;=Assumptions!$D$107,P4&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v>Full</v>
       </c>
       <c r="T4" s="26" t="n">
@@ -19060,7 +19066,7 @@
         <v>0.05</v>
       </c>
       <c r="E5" s="24" t="n">
-        <f aca="false">IF(B5&lt;=Funnel!$B$20,D5,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B5&lt;=Funnel!$B$20,D5,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0.0657894736842105</v>
       </c>
       <c r="F5" s="24" t="n">
@@ -19116,7 +19122,7 @@
         <v>0.993298679254963</v>
       </c>
       <c r="S5" s="2" t="str">
-        <f aca="false">IF(P5&gt;Q5+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R5&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P5&gt;Q5+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R5&gt;Assumptions!$D$106,"Full",IF(AND(Q5&gt;=Assumptions!$D$107,P5&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v>Full</v>
       </c>
       <c r="T5" s="26" t="n">
@@ -19161,7 +19167,7 @@
         <v>0.2</v>
       </c>
       <c r="E6" s="24" t="n">
-        <f aca="false">IF(B6&lt;=Funnel!$B$20,D6,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B6&lt;=Funnel!$B$20,D6,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0.263157894736842</v>
       </c>
       <c r="F6" s="24" t="n">
@@ -19217,7 +19223,7 @@
         <v>0.956789133298758</v>
       </c>
       <c r="S6" s="2" t="str">
-        <f aca="false">IF(P6&gt;Q6+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R6&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P6&gt;Q6+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R6&gt;Assumptions!$D$106,"Full",IF(AND(Q6&gt;=Assumptions!$D$107,P6&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v>Full</v>
       </c>
       <c r="T6" s="26" t="n">
@@ -19262,7 +19268,7 @@
         <v>0.24</v>
       </c>
       <c r="E7" s="24" t="n">
-        <f aca="false">IF(B7&lt;=Funnel!$B$20,D7,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B7&lt;=Funnel!$B$20,D7,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0.315789473684211</v>
       </c>
       <c r="F7" s="24" t="n">
@@ -19318,7 +19324,7 @@
         <v>0.9190560508676</v>
       </c>
       <c r="S7" s="2" t="str">
-        <f aca="false">IF(P7&gt;Q7+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R7&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P7&gt;Q7+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R7&gt;Assumptions!$D$106,"Full",IF(AND(Q7&gt;=Assumptions!$D$107,P7&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v>Full</v>
       </c>
       <c r="T7" s="26" t="n">
@@ -19363,7 +19369,7 @@
         <v>0.24</v>
       </c>
       <c r="E8" s="24" t="n">
-        <f aca="false">IF(B8&lt;=Funnel!$B$20,D8,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B8&lt;=Funnel!$B$20,D8,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0.315789473684211</v>
       </c>
       <c r="F8" s="24" t="n">
@@ -19419,7 +19425,7 @@
         <v>0.9190560508676</v>
       </c>
       <c r="S8" s="2" t="str">
-        <f aca="false">IF(P8&gt;Q8+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R8&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P8&gt;Q8+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R8&gt;Assumptions!$D$106,"Full",IF(AND(Q8&gt;=Assumptions!$D$107,P8&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v>Full</v>
       </c>
       <c r="T8" s="26" t="n">
@@ -19464,7 +19470,7 @@
         <v>0.24</v>
       </c>
       <c r="E9" s="24" t="n">
-        <f aca="false">IF(B9&lt;=Funnel!$B$20,D9,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B9&lt;=Funnel!$B$20,D9,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F9" s="24" t="n">
@@ -19520,8 +19526,8 @@
         <v>0.783815637475472</v>
       </c>
       <c r="S9" s="2" t="str">
-        <f aca="false">IF(P9&gt;Q9+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R9&gt;Assumptions!$D$106,"Full",""))</f>
-        <v/>
+        <f aca="false">IF(P9&gt;Q9+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R9&gt;Assumptions!$D$106,"Full",IF(AND(Q9&gt;=Assumptions!$D$107,P9&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
+        <v>Under 45 – release reserve</v>
       </c>
       <c r="T9" s="26" t="n">
         <f aca="false">$F$38*(F9*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A9-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A9-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A9-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
@@ -19565,7 +19571,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="24" t="n">
-        <f aca="false">IF(B10&lt;=Funnel!$B$20,D10,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B10&lt;=Funnel!$B$20,D10,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F10" s="24" t="n">
@@ -19621,7 +19627,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="2" t="str">
-        <f aca="false">IF(P10&gt;Q10+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R10&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P10&gt;Q10+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R10&gt;Assumptions!$D$106,"Full",IF(AND(Q10&gt;=Assumptions!$D$107,P10&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v/>
       </c>
       <c r="T10" s="26" t="n">
@@ -19666,7 +19672,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="24" t="n">
-        <f aca="false">IF(B11&lt;=Funnel!$B$20,D11,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B11&lt;=Funnel!$B$20,D11,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="24" t="n">
@@ -19722,7 +19728,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="2" t="str">
-        <f aca="false">IF(P11&gt;Q11+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R11&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P11&gt;Q11+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R11&gt;Assumptions!$D$106,"Full",IF(AND(Q11&gt;=Assumptions!$D$107,P11&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v/>
       </c>
       <c r="T11" s="26" t="n">
@@ -19767,7 +19773,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="24" t="n">
-        <f aca="false">IF(B12&lt;=Funnel!$B$20,D12,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B12&lt;=Funnel!$B$20,D12,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F12" s="24" t="n">
@@ -19823,7 +19829,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="2" t="str">
-        <f aca="false">IF(P12&gt;Q12+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R12&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P12&gt;Q12+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R12&gt;Assumptions!$D$106,"Full",IF(AND(Q12&gt;=Assumptions!$D$107,P12&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v/>
       </c>
       <c r="T12" s="26" t="n">
@@ -19868,7 +19874,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="24" t="n">
-        <f aca="false">IF(B13&lt;=Funnel!$B$20,D13,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B13&lt;=Funnel!$B$20,D13,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F13" s="24" t="n">
@@ -19924,7 +19930,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="2" t="str">
-        <f aca="false">IF(P13&gt;Q13+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R13&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P13&gt;Q13+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R13&gt;Assumptions!$D$106,"Full",IF(AND(Q13&gt;=Assumptions!$D$107,P13&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v/>
       </c>
       <c r="T13" s="26" t="n">
@@ -19969,7 +19975,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="24" t="n">
-        <f aca="false">IF(B14&lt;=Funnel!$B$20,D14,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)</f>
+        <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B14&lt;=Funnel!$B$20,D14,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
         <v>0</v>
       </c>
       <c r="F14" s="24" t="n">
@@ -20025,7 +20031,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="2" t="str">
-        <f aca="false">IF(P14&gt;Q14+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R14&gt;Assumptions!$D$106,"Full",""))</f>
+        <f aca="false">IF(P14&gt;Q14+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R14&gt;Assumptions!$D$106,"Full",IF(AND(Q14&gt;=Assumptions!$D$107,P14&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
         <v/>
       </c>
       <c r="T14" s="26" t="n">
@@ -20110,7 +20116,7 @@
         <v>322.142857142857</v>
       </c>
       <c r="S15" s="2" t="str">
-        <f aca="false">IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan"))))</f>
+        <f aca="false">IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan"))))))</f>
         <v>✓ ties to plan</v>
       </c>
       <c r="T15" s="29" t="n">
@@ -20367,7 +20373,7 @@
         <v>702</v>
       </c>
       <c r="F38" s="24" t="n">
-        <f aca="false">MIN(1,Funnel!B22/Funnel!B23)</f>
+        <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
         <v>1</v>
       </c>
     </row>
@@ -20409,6 +20415,12 @@
         <v>712</v>
       </c>
       <c r="L43" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="M43" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="N43" s="12" t="s">
         <v>432</v>
       </c>
     </row>
@@ -20453,8 +20465,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L44" s="36" t="n">
-        <f aca="false">SUM(C44:K44)</f>
+      <c r="L44" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B44)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N44" s="36" t="n">
+        <f aca="false">SUM(C44:M44)</f>
         <v>0</v>
       </c>
     </row>
@@ -20499,8 +20519,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L45" s="36" t="n">
-        <f aca="false">SUM(C45:K45)</f>
+      <c r="L45" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="36" t="n">
+        <f aca="false">SUM(C45:M45)</f>
         <v>3000</v>
       </c>
     </row>
@@ -20545,8 +20573,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L46" s="36" t="n">
-        <f aca="false">SUM(C46:K46)</f>
+      <c r="L46" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="36" t="n">
+        <f aca="false">SUM(C46:M46)</f>
         <v>1449</v>
       </c>
     </row>
@@ -20591,8 +20627,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L47" s="36" t="n">
-        <f aca="false">SUM(C47:K47)</f>
+      <c r="L47" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N47" s="36" t="n">
+        <f aca="false">SUM(C47:M47)</f>
         <v>9523.93851981352</v>
       </c>
     </row>
@@ -20637,8 +20681,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L48" s="36" t="n">
-        <f aca="false">SUM(C48:K48)</f>
+      <c r="L48" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M48" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N48" s="36" t="n">
+        <f aca="false">SUM(C48:M48)</f>
         <v>1500</v>
       </c>
     </row>
@@ -20683,8 +20735,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L49" s="36" t="n">
-        <f aca="false">SUM(C49:K49)</f>
+      <c r="L49" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="36" t="n">
+        <f aca="false">SUM(C49:M49)</f>
         <v>4957.14285714286</v>
       </c>
     </row>
@@ -20729,8 +20789,16 @@
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B50)*$Y$12</f>
         <v>0</v>
       </c>
-      <c r="L50" s="36" t="n">
-        <f aca="false">SUM(C50:K50)</f>
+      <c r="L50" s="35" t="n">
+        <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B50)*$Y$13</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="35" t="n">
+        <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B50)*$Y$14</f>
+        <v>0</v>
+      </c>
+      <c r="N50" s="36" t="n">
+        <f aca="false">SUM(C50:M50)</f>
         <v>350</v>
       </c>
     </row>
@@ -20775,8 +20843,16 @@
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$12+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$12</f>
         <v>1139.69269736842</v>
       </c>
-      <c r="L51" s="36" t="n">
-        <f aca="false">SUM(C51:K51)</f>
+      <c r="L51" s="35" t="n">
+        <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$13+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$13</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="35" t="n">
+        <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$14+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$14</f>
+        <v>0</v>
+      </c>
+      <c r="N51" s="36" t="n">
+        <f aca="false">SUM(C51:M51)</f>
         <v>4608.060625</v>
       </c>
     </row>
@@ -20821,8 +20897,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L52" s="36" t="n">
-        <f aca="false">SUM(C52:K52)</f>
+      <c r="L52" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="36" t="n">
+        <f aca="false">SUM(C52:M52)</f>
         <v>10200</v>
       </c>
     </row>
@@ -20867,8 +20951,16 @@
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$12+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$12+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$12</f>
         <v>0</v>
       </c>
-      <c r="L53" s="36" t="n">
-        <f aca="false">SUM(C53:K53)</f>
+      <c r="L53" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$13+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$13+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$13</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="35" t="n">
+        <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$14+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$14+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$14</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="36" t="n">
+        <f aca="false">SUM(C53:M53)</f>
         <v>3145.32619584272</v>
       </c>
     </row>
@@ -20914,12 +21006,20 @@
       </c>
       <c r="L54" s="36" t="n">
         <f aca="false">SUM(L44:L53)</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="36" t="n">
+        <f aca="false">SUM(M44:M53)</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="36" t="n">
+        <f aca="false">SUM(N44:N53)</f>
         <v>38733.4681977991</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="2" t="str">
-        <f aca="false">IF(ABS(L54-Budget!C9)&gt;1,"✗ matrix ≠ planned spend","✓ matrix ties to planned spend")</f>
+        <f aca="false">IF(ABS(N54-Budget!C9)&gt;1,"✗ matrix ≠ planned spend","✓ matrix ties to planned spend")</f>
         <v>✓ matrix ties to planned spend</v>
       </c>
     </row>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="760">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -1933,7 +1933,7 @@
     <t xml:space="preserve">Part 2.5 — What a smaller (or bigger) budget buys</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule when money is cut: drop the most expensive cost-per-hire cells first (across roles), including their test tranches and set-up costs; keep the reserve at the same %. Detail on Scenarios tab.</t>
+    <t xml:space="preserve">Rule when money is cut: drop the most expensive cost-per-hire cells first (across roles), including their test tranches and set-up costs; keep the reserve at the same %. If assessment slots bind (Funnel B24 &gt; 100%), hires are capped by slots, and a cut can even raise hires because it removes low-conversion sources: then re-optimise for hires per assessment slot. Detail on Scenarios tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Budget level</t>
@@ -1990,7 +1990,28 @@
     <t xml:space="preserve">Cut @L4</t>
   </si>
   <si>
+    <t xml:space="preserve">Qualified @L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualified @L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualified @L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualified @L4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hires by role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualified applicants (before capacity cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacity factor (assessment slots ÷ qualified, max 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hires by role are scaled by the capacity factor: if a scenario's qualified applicants exceed the assessment slots, only the share that can be assessed turns into hires (same rule as Budget C13).</t>
   </si>
   <si>
     <t xml:space="preserve">Week-by-week plan: cash out, qualified flow vs 55/week, signatures</t>
@@ -3090,12 +3111,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3109,67 +3130,67 @@
         <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5357,7 +5378,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5366,46 +5387,46 @@
         <v>288</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5635,7 +5656,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -16596,7 +16617,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="str">
-        <f aca="false">IF(ABS(C39-C9)&lt;1,"✓ ties to planned spend","✗ check: channel totals ≠ planned spend")</f>
+        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(ABS(C39-C9)&lt;1,"✓ ties to planned spend","✗ check: channel totals ≠ planned spend"))</f>
         <v>✓ ties to planned spend</v>
       </c>
     </row>
@@ -16816,7 +16837,7 @@
     <tabColor rgb="FF8EA9DB"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -16962,6 +16983,18 @@
       <c r="N7" s="12" t="s">
         <v>626</v>
       </c>
+      <c r="O7" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="str">
@@ -17020,6 +17053,22 @@
         <f aca="false">Channels!X5</f>
         <v>0</v>
       </c>
+      <c r="O8" s="26" t="n">
+        <f aca="false">IF(E8&gt;0,F8*Channels!V5/E8,0)</f>
+        <v>12</v>
+      </c>
+      <c r="P8" s="26" t="n">
+        <f aca="false">IF(E8&gt;0,G8*Channels!V5/E8,0)</f>
+        <v>12</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <f aca="false">IF(E8&gt;0,H8*Channels!V5/E8,0)</f>
+        <v>12</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <f aca="false">IF(E8&gt;0,I8*Channels!V5/E8,0)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="str">
@@ -17078,6 +17127,22 @@
         <f aca="false">Channels!X6</f>
         <v>0</v>
       </c>
+      <c r="O9" s="26" t="n">
+        <f aca="false">IF(E9&gt;0,F9*Channels!V6/E9,0)</f>
+        <v>36</v>
+      </c>
+      <c r="P9" s="26" t="n">
+        <f aca="false">IF(E9&gt;0,G9*Channels!V6/E9,0)</f>
+        <v>36</v>
+      </c>
+      <c r="Q9" s="26" t="n">
+        <f aca="false">IF(E9&gt;0,H9*Channels!V6/E9,0)</f>
+        <v>36</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <f aca="false">IF(E9&gt;0,I9*Channels!V6/E9,0)</f>
+        <v>36</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="str">
@@ -17136,6 +17201,22 @@
         <f aca="false">Channels!X7</f>
         <v>0</v>
       </c>
+      <c r="O10" s="26" t="n">
+        <f aca="false">IF(E10&gt;0,F10*Channels!V7/E10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="P10" s="26" t="n">
+        <f aca="false">IF(E10&gt;0,G10*Channels!V7/E10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="Q10" s="26" t="n">
+        <f aca="false">IF(E10&gt;0,H10*Channels!V7/E10,0)</f>
+        <v>8</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <f aca="false">IF(E10&gt;0,I10*Channels!V7/E10,0)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="str">
@@ -17194,6 +17275,22 @@
         <f aca="false">Channels!X8</f>
         <v>0</v>
       </c>
+      <c r="O11" s="26" t="n">
+        <f aca="false">IF(E11&gt;0,F11*Channels!V8/E11,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="P11" s="26" t="n">
+        <f aca="false">IF(E11&gt;0,G11*Channels!V8/E11,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="Q11" s="26" t="n">
+        <f aca="false">IF(E11&gt;0,H11*Channels!V8/E11,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <f aca="false">IF(E11&gt;0,I11*Channels!V8/E11,0)</f>
+        <v>4.8</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="str">
@@ -17252,6 +17349,22 @@
         <f aca="false">Channels!X9</f>
         <v>750</v>
       </c>
+      <c r="O12" s="26" t="n">
+        <f aca="false">IF(E12&gt;0,F12*Channels!V9/E12,0)</f>
+        <v>1.575</v>
+      </c>
+      <c r="P12" s="26" t="n">
+        <f aca="false">IF(E12&gt;0,G12*Channels!V9/E12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="26" t="n">
+        <f aca="false">IF(E12&gt;0,H12*Channels!V9/E12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <f aca="false">IF(E12&gt;0,I12*Channels!V9/E12,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="str">
@@ -17310,6 +17423,22 @@
         <f aca="false">Channels!X10</f>
         <v>750</v>
       </c>
+      <c r="O13" s="26" t="n">
+        <f aca="false">IF(E13&gt;0,F13*Channels!V10/E13,0)</f>
+        <v>6.875</v>
+      </c>
+      <c r="P13" s="26" t="n">
+        <f aca="false">IF(E13&gt;0,G13*Channels!V10/E13,0)</f>
+        <v>6.875</v>
+      </c>
+      <c r="Q13" s="26" t="n">
+        <f aca="false">IF(E13&gt;0,H13*Channels!V10/E13,0)</f>
+        <v>6.875</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <f aca="false">IF(E13&gt;0,I13*Channels!V10/E13,0)</f>
+        <v>6.875</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="str">
@@ -17368,6 +17497,22 @@
         <f aca="false">Channels!X11</f>
         <v>750</v>
       </c>
+      <c r="O14" s="26" t="n">
+        <f aca="false">IF(E14&gt;0,F14*Channels!V11/E14,0)</f>
+        <v>2</v>
+      </c>
+      <c r="P14" s="26" t="n">
+        <f aca="false">IF(E14&gt;0,G14*Channels!V11/E14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="26" t="n">
+        <f aca="false">IF(E14&gt;0,H14*Channels!V11/E14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <f aca="false">IF(E14&gt;0,I14*Channels!V11/E14,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="str">
@@ -17426,6 +17571,22 @@
         <f aca="false">Channels!X12</f>
         <v>750</v>
       </c>
+      <c r="O15" s="26" t="n">
+        <f aca="false">IF(E15&gt;0,F15*Channels!V12/E15,0)</f>
+        <v>1.76470588235294</v>
+      </c>
+      <c r="P15" s="26" t="n">
+        <f aca="false">IF(E15&gt;0,G15*Channels!V12/E15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="26" t="n">
+        <f aca="false">IF(E15&gt;0,H15*Channels!V12/E15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <f aca="false">IF(E15&gt;0,I15*Channels!V12/E15,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="str">
@@ -17484,6 +17645,22 @@
         <f aca="false">Channels!X13</f>
         <v>1449</v>
       </c>
+      <c r="O16" s="26" t="n">
+        <f aca="false">IF(E16&gt;0,F16*Channels!V13/E16,0)</f>
+        <v>2.8442599067599</v>
+      </c>
+      <c r="P16" s="26" t="n">
+        <f aca="false">IF(E16&gt;0,G16*Channels!V13/E16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="26" t="n">
+        <f aca="false">IF(E16&gt;0,H16*Channels!V13/E16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <f aca="false">IF(E16&gt;0,I16*Channels!V13/E16,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="str">
@@ -17542,6 +17719,22 @@
         <f aca="false">Channels!X14</f>
         <v>0</v>
       </c>
+      <c r="O17" s="26" t="n">
+        <f aca="false">IF(E17&gt;0,F17*Channels!V14/E17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="26" t="n">
+        <f aca="false">IF(E17&gt;0,G17*Channels!V14/E17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="26" t="n">
+        <f aca="false">IF(E17&gt;0,H17*Channels!V14/E17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <f aca="false">IF(E17&gt;0,I17*Channels!V14/E17,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="str">
@@ -17600,6 +17793,22 @@
         <f aca="false">Channels!X15</f>
         <v>0</v>
       </c>
+      <c r="O18" s="26" t="n">
+        <f aca="false">IF(E18&gt;0,F18*Channels!V15/E18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="26" t="n">
+        <f aca="false">IF(E18&gt;0,G18*Channels!V15/E18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="26" t="n">
+        <f aca="false">IF(E18&gt;0,H18*Channels!V15/E18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <f aca="false">IF(E18&gt;0,I18*Channels!V15/E18,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="str">
@@ -17658,6 +17867,22 @@
         <f aca="false">Channels!X16</f>
         <v>0</v>
       </c>
+      <c r="O19" s="26" t="n">
+        <f aca="false">IF(E19&gt;0,F19*Channels!V16/E19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="26" t="n">
+        <f aca="false">IF(E19&gt;0,G19*Channels!V16/E19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="26" t="n">
+        <f aca="false">IF(E19&gt;0,H19*Channels!V16/E19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <f aca="false">IF(E19&gt;0,I19*Channels!V16/E19,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="str">
@@ -17716,6 +17941,22 @@
         <f aca="false">Channels!X17</f>
         <v>5148.93851981352</v>
       </c>
+      <c r="O20" s="26" t="n">
+        <f aca="false">IF(E20&gt;0,F20*Channels!V17/E20,0)</f>
+        <v>29.4225058275058</v>
+      </c>
+      <c r="P20" s="26" t="n">
+        <f aca="false">IF(E20&gt;0,G20*Channels!V17/E20,0)</f>
+        <v>29.4225058275058</v>
+      </c>
+      <c r="Q20" s="26" t="n">
+        <f aca="false">IF(E20&gt;0,H20*Channels!V17/E20,0)</f>
+        <v>29.4225058275058</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <f aca="false">IF(E20&gt;0,I20*Channels!V17/E20,0)</f>
+        <v>29.4225058275058</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="str">
@@ -17774,6 +18015,22 @@
         <f aca="false">Channels!X18</f>
         <v>4375</v>
       </c>
+      <c r="O21" s="26" t="n">
+        <f aca="false">IF(E21&gt;0,F21*Channels!V18/E21,0)</f>
+        <v>20</v>
+      </c>
+      <c r="P21" s="26" t="n">
+        <f aca="false">IF(E21&gt;0,G21*Channels!V18/E21,0)</f>
+        <v>20</v>
+      </c>
+      <c r="Q21" s="26" t="n">
+        <f aca="false">IF(E21&gt;0,H21*Channels!V18/E21,0)</f>
+        <v>20</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <f aca="false">IF(E21&gt;0,I21*Channels!V18/E21,0)</f>
+        <v>20</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="str">
@@ -17832,6 +18089,22 @@
         <f aca="false">Channels!X19</f>
         <v>750</v>
       </c>
+      <c r="O22" s="26" t="n">
+        <f aca="false">IF(E22&gt;0,F22*Channels!V19/E22,0)</f>
+        <v>2.08333333333333</v>
+      </c>
+      <c r="P22" s="26" t="n">
+        <f aca="false">IF(E22&gt;0,G22*Channels!V19/E22,0)</f>
+        <v>0.0952272283358373</v>
+      </c>
+      <c r="Q22" s="26" t="n">
+        <f aca="false">IF(E22&gt;0,H22*Channels!V19/E22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <f aca="false">IF(E22&gt;0,I22*Channels!V19/E22,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="str">
@@ -17890,6 +18163,22 @@
         <f aca="false">Channels!X20</f>
         <v>750</v>
       </c>
+      <c r="O23" s="26" t="n">
+        <f aca="false">IF(E23&gt;0,F23*Channels!V20/E23,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="P23" s="26" t="n">
+        <f aca="false">IF(E23&gt;0,G23*Channels!V20/E23,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="Q23" s="26" t="n">
+        <f aca="false">IF(E23&gt;0,H23*Channels!V20/E23,0)</f>
+        <v>7.5</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <f aca="false">IF(E23&gt;0,I23*Channels!V20/E23,0)</f>
+        <v>7.5</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="str">
@@ -17948,6 +18237,22 @@
         <f aca="false">Channels!X21</f>
         <v>2514.28571428571</v>
       </c>
+      <c r="O24" s="26" t="n">
+        <f aca="false">IF(E24&gt;0,F24*Channels!V21/E24,0)</f>
+        <v>12</v>
+      </c>
+      <c r="P24" s="26" t="n">
+        <f aca="false">IF(E24&gt;0,G24*Channels!V21/E24,0)</f>
+        <v>12</v>
+      </c>
+      <c r="Q24" s="26" t="n">
+        <f aca="false">IF(E24&gt;0,H24*Channels!V21/E24,0)</f>
+        <v>12</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <f aca="false">IF(E24&gt;0,I24*Channels!V21/E24,0)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="str">
@@ -18006,6 +18311,22 @@
         <f aca="false">Channels!X22</f>
         <v>750</v>
       </c>
+      <c r="O25" s="26" t="n">
+        <f aca="false">IF(E25&gt;0,F25*Channels!V22/E25,0)</f>
+        <v>5.96590909090909</v>
+      </c>
+      <c r="P25" s="26" t="n">
+        <f aca="false">IF(E25&gt;0,G25*Channels!V22/E25,0)</f>
+        <v>5.96590909090909</v>
+      </c>
+      <c r="Q25" s="26" t="n">
+        <f aca="false">IF(E25&gt;0,H25*Channels!V22/E25,0)</f>
+        <v>5.96590909090909</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <f aca="false">IF(E25&gt;0,I25*Channels!V22/E25,0)</f>
+        <v>5.96590909090909</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="str">
@@ -18064,6 +18385,22 @@
         <f aca="false">Channels!X23</f>
         <v>750</v>
       </c>
+      <c r="O26" s="26" t="n">
+        <f aca="false">IF(E26&gt;0,F26*Channels!V23/E26,0)</f>
+        <v>3.57954545454545</v>
+      </c>
+      <c r="P26" s="26" t="n">
+        <f aca="false">IF(E26&gt;0,G26*Channels!V23/E26,0)</f>
+        <v>3.57954545454545</v>
+      </c>
+      <c r="Q26" s="26" t="n">
+        <f aca="false">IF(E26&gt;0,H26*Channels!V23/E26,0)</f>
+        <v>3.57954545454545</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <f aca="false">IF(E26&gt;0,I26*Channels!V23/E26,0)</f>
+        <v>3.57954545454545</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="str">
@@ -18122,6 +18459,22 @@
         <f aca="false">Channels!X24</f>
         <v>942.857142857143</v>
       </c>
+      <c r="O27" s="26" t="n">
+        <f aca="false">IF(E27&gt;0,F27*Channels!V24/E27,0)</f>
+        <v>3.6</v>
+      </c>
+      <c r="P27" s="26" t="n">
+        <f aca="false">IF(E27&gt;0,G27*Channels!V24/E27,0)</f>
+        <v>3.6</v>
+      </c>
+      <c r="Q27" s="26" t="n">
+        <f aca="false">IF(E27&gt;0,H27*Channels!V24/E27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <f aca="false">IF(E27&gt;0,I27*Channels!V24/E27,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="str">
@@ -18180,6 +18533,22 @@
         <f aca="false">Channels!X25</f>
         <v>100</v>
       </c>
+      <c r="O28" s="26" t="n">
+        <f aca="false">IF(E28&gt;0,F28*Channels!V25/E28,0)</f>
+        <v>12</v>
+      </c>
+      <c r="P28" s="26" t="n">
+        <f aca="false">IF(E28&gt;0,G28*Channels!V25/E28,0)</f>
+        <v>12</v>
+      </c>
+      <c r="Q28" s="26" t="n">
+        <f aca="false">IF(E28&gt;0,H28*Channels!V25/E28,0)</f>
+        <v>12</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <f aca="false">IF(E28&gt;0,I28*Channels!V25/E28,0)</f>
+        <v>12</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="str">
@@ -18238,6 +18607,22 @@
         <f aca="false">Channels!X26</f>
         <v>150</v>
       </c>
+      <c r="O29" s="26" t="n">
+        <f aca="false">IF(E29&gt;0,F29*Channels!V26/E29,0)</f>
+        <v>18</v>
+      </c>
+      <c r="P29" s="26" t="n">
+        <f aca="false">IF(E29&gt;0,G29*Channels!V26/E29,0)</f>
+        <v>18</v>
+      </c>
+      <c r="Q29" s="26" t="n">
+        <f aca="false">IF(E29&gt;0,H29*Channels!V26/E29,0)</f>
+        <v>18</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <f aca="false">IF(E29&gt;0,I29*Channels!V26/E29,0)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="str">
@@ -18296,6 +18681,22 @@
         <f aca="false">Channels!X27</f>
         <v>60</v>
       </c>
+      <c r="O30" s="26" t="n">
+        <f aca="false">IF(E30&gt;0,F30*Channels!V27/E30,0)</f>
+        <v>7.2</v>
+      </c>
+      <c r="P30" s="26" t="n">
+        <f aca="false">IF(E30&gt;0,G30*Channels!V27/E30,0)</f>
+        <v>7.2</v>
+      </c>
+      <c r="Q30" s="26" t="n">
+        <f aca="false">IF(E30&gt;0,H30*Channels!V27/E30,0)</f>
+        <v>7.2</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <f aca="false">IF(E30&gt;0,I30*Channels!V27/E30,0)</f>
+        <v>7.2</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="str">
@@ -18354,6 +18755,22 @@
         <f aca="false">Channels!X28</f>
         <v>40</v>
       </c>
+      <c r="O31" s="26" t="n">
+        <f aca="false">IF(E31&gt;0,F31*Channels!V28/E31,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="P31" s="26" t="n">
+        <f aca="false">IF(E31&gt;0,G31*Channels!V28/E31,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="Q31" s="26" t="n">
+        <f aca="false">IF(E31&gt;0,H31*Channels!V28/E31,0)</f>
+        <v>4.8</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <f aca="false">IF(E31&gt;0,I31*Channels!V28/E31,0)</f>
+        <v>4.8</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="str">
@@ -18412,6 +18829,22 @@
         <f aca="false">Channels!X29</f>
         <v>4162.640625</v>
       </c>
+      <c r="O32" s="26" t="n">
+        <f aca="false">IF(E32&gt;0,F32*Channels!V29/E32,0)</f>
+        <v>11.25</v>
+      </c>
+      <c r="P32" s="26" t="n">
+        <f aca="false">IF(E32&gt;0,G32*Channels!V29/E32,0)</f>
+        <v>11.25</v>
+      </c>
+      <c r="Q32" s="26" t="n">
+        <f aca="false">IF(E32&gt;0,H32*Channels!V29/E32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <f aca="false">IF(E32&gt;0,I32*Channels!V29/E32,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="str">
@@ -18470,6 +18903,22 @@
         <f aca="false">Channels!X30</f>
         <v>0</v>
       </c>
+      <c r="O33" s="26" t="n">
+        <f aca="false">IF(E33&gt;0,F33*Channels!V30/E33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P33" s="26" t="n">
+        <f aca="false">IF(E33&gt;0,G33*Channels!V30/E33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="26" t="n">
+        <f aca="false">IF(E33&gt;0,H33*Channels!V30/E33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <f aca="false">IF(E33&gt;0,I33*Channels!V30/E33,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="str">
@@ -18528,6 +18977,22 @@
         <f aca="false">Channels!X31</f>
         <v>0</v>
       </c>
+      <c r="O34" s="26" t="n">
+        <f aca="false">IF(E34&gt;0,F34*Channels!V31/E34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="26" t="n">
+        <f aca="false">IF(E34&gt;0,G34*Channels!V31/E34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="26" t="n">
+        <f aca="false">IF(E34&gt;0,H34*Channels!V31/E34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <f aca="false">IF(E34&gt;0,I34*Channels!V31/E34,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="str">
@@ -18586,6 +19051,22 @@
         <f aca="false">Channels!X32</f>
         <v>445.42</v>
       </c>
+      <c r="O35" s="26" t="n">
+        <f aca="false">IF(E35&gt;0,F35*Channels!V32/E35,0)</f>
+        <v>1.44657979133683</v>
+      </c>
+      <c r="P35" s="26" t="n">
+        <f aca="false">IF(E35&gt;0,G35*Channels!V32/E35,0)</f>
+        <v>1.44657979133683</v>
+      </c>
+      <c r="Q35" s="26" t="n">
+        <f aca="false">IF(E35&gt;0,H35*Channels!V32/E35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <f aca="false">IF(E35&gt;0,I35*Channels!V32/E35,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="str">
@@ -18644,6 +19125,22 @@
         <f aca="false">Channels!X33</f>
         <v>9000</v>
       </c>
+      <c r="O36" s="26" t="n">
+        <f aca="false">IF(E36&gt;0,F36*Channels!V33/E36,0)</f>
+        <v>45</v>
+      </c>
+      <c r="P36" s="26" t="n">
+        <f aca="false">IF(E36&gt;0,G36*Channels!V33/E36,0)</f>
+        <v>45</v>
+      </c>
+      <c r="Q36" s="26" t="n">
+        <f aca="false">IF(E36&gt;0,H36*Channels!V33/E36,0)</f>
+        <v>42.6447478502902</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <f aca="false">IF(E36&gt;0,I36*Channels!V33/E36,0)</f>
+        <v>2.26974785029022</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="str">
@@ -18702,10 +19199,26 @@
         <f aca="false">Channels!X34</f>
         <v>2745.32619584272</v>
       </c>
+      <c r="O37" s="26" t="n">
+        <f aca="false">IF(E37&gt;0,F37*Channels!V34/E37,0)</f>
+        <v>30.9729109274564</v>
+      </c>
+      <c r="P37" s="26" t="n">
+        <f aca="false">IF(E37&gt;0,G37*Channels!V34/E37,0)</f>
+        <v>30.9729109274564</v>
+      </c>
+      <c r="Q37" s="26" t="n">
+        <f aca="false">IF(E37&gt;0,H37*Channels!V34/E37,0)</f>
+        <v>30.9729109274564</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <f aca="false">IF(E37&gt;0,I37*Channels!V34/E37,0)</f>
+        <v>30.9729109274564</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="22" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18713,19 +19226,19 @@
         <v>50</v>
       </c>
       <c r="F39" s="26" t="n">
-        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E39)</f>
+        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E39)*F$47</f>
         <v>30</v>
       </c>
       <c r="G39" s="26" t="n">
-        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E39)</f>
+        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E39)*G$47</f>
         <v>27.9384299857171</v>
       </c>
       <c r="H39" s="26" t="n">
-        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E39)</f>
+        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E39)*H$47</f>
         <v>23.1389080966647</v>
       </c>
       <c r="I39" s="26" t="n">
-        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E39)</f>
+        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E39)*I$47</f>
         <v>12.7463830966647</v>
       </c>
     </row>
@@ -18734,19 +19247,19 @@
         <v>45</v>
       </c>
       <c r="F40" s="26" t="n">
-        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E40)</f>
+        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E40)*F$47</f>
         <v>45</v>
       </c>
       <c r="G40" s="26" t="n">
-        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E40)</f>
+        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E40)*G$47</f>
         <v>45</v>
       </c>
       <c r="H40" s="26" t="n">
-        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E40)</f>
+        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E40)*H$47</f>
         <v>45</v>
       </c>
       <c r="I40" s="26" t="n">
-        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E40)</f>
+        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E40)*I$47</f>
         <v>45</v>
       </c>
     </row>
@@ -18755,19 +19268,19 @@
         <v>55</v>
       </c>
       <c r="F41" s="26" t="n">
-        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E41)</f>
+        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E41)*F$47</f>
         <v>15</v>
       </c>
       <c r="G41" s="26" t="n">
-        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E41)</f>
+        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E41)*G$47</f>
         <v>14.415</v>
       </c>
       <c r="H41" s="26" t="n">
-        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E41)</f>
+        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E41)*H$47</f>
         <v>14.415</v>
       </c>
       <c r="I41" s="26" t="n">
-        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E41)</f>
+        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E41)*I$47</f>
         <v>14.415</v>
       </c>
     </row>
@@ -18776,19 +19289,19 @@
         <v>57</v>
       </c>
       <c r="F42" s="26" t="n">
-        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E42)</f>
+        <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E42)*F$47</f>
         <v>10</v>
       </c>
       <c r="G42" s="26" t="n">
-        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E42)</f>
+        <f aca="false">SUMIFS(G$8:G$37,$B$8:$B$37,$E42)*G$47</f>
         <v>9.5275</v>
       </c>
       <c r="H42" s="26" t="n">
-        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E42)</f>
+        <f aca="false">SUMIFS(H$8:H$37,$B$8:$B$37,$E42)*H$47</f>
         <v>8.11818</v>
       </c>
       <c r="I42" s="26" t="n">
-        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E42)</f>
+        <f aca="false">SUMIFS(I$8:I$37,$B$8:$B$37,$E42)*I$47</f>
         <v>8.11818</v>
       </c>
     </row>
@@ -18832,6 +19345,53 @@
       <c r="I44" s="35" t="n">
         <f aca="false">IF(I43&gt;0,I4/I43,0)</f>
         <v>295.841171574422</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F46" s="26" t="n">
+        <f aca="false">SUM(O8:O37)</f>
+        <v>290.6797502142</v>
+      </c>
+      <c r="G46" s="26" t="n">
+        <f aca="false">SUM(P8:P37)</f>
+        <v>280.507678320089</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <f aca="false">SUM(Q8:Q37)</f>
+        <v>261.760619150707</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <f aca="false">SUM(R8:R37)</f>
+        <v>221.385619150707</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F47" s="24" t="n">
+        <f aca="false">IF(F46&gt;0,MIN(1,Funnel!$B$22/F46),1)</f>
+        <v>1</v>
+      </c>
+      <c r="G47" s="24" t="n">
+        <f aca="false">IF(G46&gt;0,MIN(1,Funnel!$B$22/G46),1)</f>
+        <v>1</v>
+      </c>
+      <c r="H47" s="24" t="n">
+        <f aca="false">IF(H46&gt;0,MIN(1,Funnel!$B$22/H46),1)</f>
+        <v>1</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <f aca="false">IF(I46&gt;0,MIN(1,Funnel!$B$22/I46),1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -18863,89 +19423,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20116,7 +20676,7 @@
         <v>322.142857142857</v>
       </c>
       <c r="S15" s="2" t="str">
-        <f aca="false">IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan"))))))</f>
+        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan")))))))</f>
         <v>✓ ties to plan</v>
       </c>
       <c r="T15" s="29" t="n">
@@ -20142,7 +20702,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -20194,12 +20754,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="F19" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20208,7 +20768,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="F20" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20217,7 +20777,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="F21" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -20226,7 +20786,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="F22" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20235,7 +20795,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="F23" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20244,7 +20804,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="F24" s="35" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -20253,7 +20813,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="F25" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20262,7 +20822,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="F26" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20271,7 +20831,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="F27" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20280,7 +20840,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="F28" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20289,7 +20849,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="F29" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20298,7 +20858,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="F30" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20307,7 +20867,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="F31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -20316,7 +20876,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20325,7 +20885,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20334,7 +20894,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="F34" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20343,7 +20903,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20352,7 +20912,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="F36" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20361,7 +20921,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="F37" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20370,7 +20930,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="F38" s="24" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -20379,7 +20939,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20388,37 +20948,37 @@
         <v>287</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="N43" s="12" t="s">
         <v>432</v>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -1729,7 +1729,7 @@
     <t xml:space="preserve">Allocation logic: within each role, channels are filled in order of cost per hire (media at full capacity + fixed costs, ÷ hire capacity) up to their capacity until hires = openings. Polish cap enforced in hire capacity. Slots bought in whole 30-day ads.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every paid CPC/CPA cell first gets a test tranche (B2) in weeks 1–2; its applicants and hires are counted (cols AE–AG). The allocation then fills only the remaining need (col T) from remaining capacity (col AH).</t>
+    <t xml:space="preserve">Every paid CPC/CPA cell for a role with openings first gets a test tranche (B2) in weeks 1–2; its applicants and hires are counted (cols AE–AG). The allocation then fills only the remaining need (col T) from remaining capacity (col AH).</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
@@ -11813,7 +11813,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="35" t="n">
-        <f aca="false">IF(AND(D5="Channel",OR(E5="CPC",E5="CPA")),MIN(Assumptions!$D$49,J5*H5),0)</f>
+        <f aca="false">IF(AND(D5="Channel",OR(E5="CPC",E5="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C5,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J5*H5),0)</f>
         <v>0</v>
       </c>
       <c r="AA5" s="35" t="n">
@@ -11954,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="35" t="n">
-        <f aca="false">IF(AND(D6="Channel",OR(E6="CPC",E6="CPA")),MIN(Assumptions!$D$49,J6*H6),0)</f>
+        <f aca="false">IF(AND(D6="Channel",OR(E6="CPC",E6="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C6,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J6*H6),0)</f>
         <v>0</v>
       </c>
       <c r="AA6" s="35" t="n">
@@ -12095,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="35" t="n">
-        <f aca="false">IF(AND(D7="Channel",OR(E7="CPC",E7="CPA")),MIN(Assumptions!$D$49,J7*H7),0)</f>
+        <f aca="false">IF(AND(D7="Channel",OR(E7="CPC",E7="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C7,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J7*H7),0)</f>
         <v>0</v>
       </c>
       <c r="AA7" s="35" t="n">
@@ -12236,7 +12236,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <f aca="false">IF(AND(D8="Channel",OR(E8="CPC",E8="CPA")),MIN(Assumptions!$D$49,J8*H8),0)</f>
+        <f aca="false">IF(AND(D8="Channel",OR(E8="CPC",E8="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C8,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J8*H8),0)</f>
         <v>0</v>
       </c>
       <c r="AA8" s="35" t="n">
@@ -12377,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="35" t="n">
-        <f aca="false">IF(AND(D9="Channel",OR(E9="CPC",E9="CPA")),MIN(Assumptions!$D$49,J9*H9),0)</f>
+        <f aca="false">IF(AND(D9="Channel",OR(E9="CPC",E9="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C9,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J9*H9),0)</f>
         <v>750</v>
       </c>
       <c r="AA9" s="35" t="n">
@@ -12518,7 +12518,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <f aca="false">IF(AND(D10="Channel",OR(E10="CPC",E10="CPA")),MIN(Assumptions!$D$49,J10*H10),0)</f>
+        <f aca="false">IF(AND(D10="Channel",OR(E10="CPC",E10="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C10,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J10*H10),0)</f>
         <v>750</v>
       </c>
       <c r="AA10" s="35" t="n">
@@ -12659,7 +12659,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="35" t="n">
-        <f aca="false">IF(AND(D11="Channel",OR(E11="CPC",E11="CPA")),MIN(Assumptions!$D$49,J11*H11),0)</f>
+        <f aca="false">IF(AND(D11="Channel",OR(E11="CPC",E11="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C11,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J11*H11),0)</f>
         <v>750</v>
       </c>
       <c r="AA11" s="35" t="n">
@@ -12800,7 +12800,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <f aca="false">IF(AND(D12="Channel",OR(E12="CPC",E12="CPA")),MIN(Assumptions!$D$49,J12*H12),0)</f>
+        <f aca="false">IF(AND(D12="Channel",OR(E12="CPC",E12="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C12,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J12*H12),0)</f>
         <v>750</v>
       </c>
       <c r="AA12" s="35" t="n">
@@ -12941,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="35" t="n">
-        <f aca="false">IF(AND(D13="Channel",OR(E13="CPC",E13="CPA")),MIN(Assumptions!$D$49,J13*H13),0)</f>
+        <f aca="false">IF(AND(D13="Channel",OR(E13="CPC",E13="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C13,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J13*H13),0)</f>
         <v>0</v>
       </c>
       <c r="AA13" s="35" t="n">
@@ -13082,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <f aca="false">IF(AND(D14="Channel",OR(E14="CPC",E14="CPA")),MIN(Assumptions!$D$49,J14*H14),0)</f>
+        <f aca="false">IF(AND(D14="Channel",OR(E14="CPC",E14="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C14,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J14*H14),0)</f>
         <v>0</v>
       </c>
       <c r="AA14" s="35" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="35" t="n">
-        <f aca="false">IF(AND(D15="Channel",OR(E15="CPC",E15="CPA")),MIN(Assumptions!$D$49,J15*H15),0)</f>
+        <f aca="false">IF(AND(D15="Channel",OR(E15="CPC",E15="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C15,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J15*H15),0)</f>
         <v>0</v>
       </c>
       <c r="AA15" s="35" t="n">
@@ -13364,7 +13364,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="35" t="n">
-        <f aca="false">IF(AND(D16="Channel",OR(E16="CPC",E16="CPA")),MIN(Assumptions!$D$49,J16*H16),0)</f>
+        <f aca="false">IF(AND(D16="Channel",OR(E16="CPC",E16="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C16,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J16*H16),0)</f>
         <v>0</v>
       </c>
       <c r="AA16" s="35" t="n">
@@ -13505,7 +13505,7 @@
         <v>0</v>
       </c>
       <c r="Z17" s="35" t="n">
-        <f aca="false">IF(AND(D17="Channel",OR(E17="CPC",E17="CPA")),MIN(Assumptions!$D$49,J17*H17),0)</f>
+        <f aca="false">IF(AND(D17="Channel",OR(E17="CPC",E17="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C17,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J17*H17),0)</f>
         <v>750</v>
       </c>
       <c r="AA17" s="35" t="n">
@@ -13646,7 +13646,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="35" t="n">
-        <f aca="false">IF(AND(D18="Channel",OR(E18="CPC",E18="CPA")),MIN(Assumptions!$D$49,J18*H18),0)</f>
+        <f aca="false">IF(AND(D18="Channel",OR(E18="CPC",E18="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C18,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J18*H18),0)</f>
         <v>750</v>
       </c>
       <c r="AA18" s="35" t="n">
@@ -13787,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="35" t="n">
-        <f aca="false">IF(AND(D19="Channel",OR(E19="CPC",E19="CPA")),MIN(Assumptions!$D$49,J19*H19),0)</f>
+        <f aca="false">IF(AND(D19="Channel",OR(E19="CPC",E19="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C19,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J19*H19),0)</f>
         <v>750</v>
       </c>
       <c r="AA19" s="35" t="n">
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="35" t="n">
-        <f aca="false">IF(AND(D20="Channel",OR(E20="CPC",E20="CPA")),MIN(Assumptions!$D$49,J20*H20),0)</f>
+        <f aca="false">IF(AND(D20="Channel",OR(E20="CPC",E20="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C20,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J20*H20),0)</f>
         <v>750</v>
       </c>
       <c r="AA20" s="35" t="n">
@@ -14069,7 +14069,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="35" t="n">
-        <f aca="false">IF(AND(D21="Channel",OR(E21="CPC",E21="CPA")),MIN(Assumptions!$D$49,J21*H21),0)</f>
+        <f aca="false">IF(AND(D21="Channel",OR(E21="CPC",E21="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C21,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J21*H21),0)</f>
         <v>750</v>
       </c>
       <c r="AA21" s="35" t="n">
@@ -14210,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <f aca="false">IF(AND(D22="Channel",OR(E22="CPC",E22="CPA")),MIN(Assumptions!$D$49,J22*H22),0)</f>
+        <f aca="false">IF(AND(D22="Channel",OR(E22="CPC",E22="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C22,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J22*H22),0)</f>
         <v>750</v>
       </c>
       <c r="AA22" s="35" t="n">
@@ -14351,7 +14351,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="35" t="n">
-        <f aca="false">IF(AND(D23="Channel",OR(E23="CPC",E23="CPA")),MIN(Assumptions!$D$49,J23*H23),0)</f>
+        <f aca="false">IF(AND(D23="Channel",OR(E23="CPC",E23="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C23,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J23*H23),0)</f>
         <v>750</v>
       </c>
       <c r="AA23" s="35" t="n">
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="35" t="n">
-        <f aca="false">IF(AND(D24="Channel",OR(E24="CPC",E24="CPA")),MIN(Assumptions!$D$49,J24*H24),0)</f>
+        <f aca="false">IF(AND(D24="Channel",OR(E24="CPC",E24="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C24,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J24*H24),0)</f>
         <v>750</v>
       </c>
       <c r="AA24" s="35" t="n">
@@ -14626,7 +14626,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="35" t="n">
-        <f aca="false">IF(AND(D25="Channel",OR(E25="CPC",E25="CPA")),MIN(Assumptions!$D$49,J25*H25),0)</f>
+        <f aca="false">IF(AND(D25="Channel",OR(E25="CPC",E25="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C25,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J25*H25),0)</f>
         <v>0</v>
       </c>
       <c r="AA25" s="35" t="n">
@@ -14760,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="Z26" s="35" t="n">
-        <f aca="false">IF(AND(D26="Channel",OR(E26="CPC",E26="CPA")),MIN(Assumptions!$D$49,J26*H26),0)</f>
+        <f aca="false">IF(AND(D26="Channel",OR(E26="CPC",E26="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C26,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J26*H26),0)</f>
         <v>0</v>
       </c>
       <c r="AA26" s="35" t="n">
@@ -14894,7 +14894,7 @@
         <v>0</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <f aca="false">IF(AND(D27="Channel",OR(E27="CPC",E27="CPA")),MIN(Assumptions!$D$49,J27*H27),0)</f>
+        <f aca="false">IF(AND(D27="Channel",OR(E27="CPC",E27="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C27,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J27*H27),0)</f>
         <v>0</v>
       </c>
       <c r="AA27" s="35" t="n">
@@ -15028,7 +15028,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="35" t="n">
-        <f aca="false">IF(AND(D28="Channel",OR(E28="CPC",E28="CPA")),MIN(Assumptions!$D$49,J28*H28),0)</f>
+        <f aca="false">IF(AND(D28="Channel",OR(E28="CPC",E28="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C28,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J28*H28),0)</f>
         <v>0</v>
       </c>
       <c r="AA28" s="35" t="n">
@@ -15162,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="Z29" s="35" t="n">
-        <f aca="false">IF(AND(D29="Channel",OR(E29="CPC",E29="CPA")),MIN(Assumptions!$D$49,J29*H29),0)</f>
+        <f aca="false">IF(AND(D29="Channel",OR(E29="CPC",E29="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C29,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J29*H29),0)</f>
         <v>0</v>
       </c>
       <c r="AA29" s="35" t="n">
@@ -15296,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="35" t="n">
-        <f aca="false">IF(AND(D30="Channel",OR(E30="CPC",E30="CPA")),MIN(Assumptions!$D$49,J30*H30),0)</f>
+        <f aca="false">IF(AND(D30="Channel",OR(E30="CPC",E30="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C30,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J30*H30),0)</f>
         <v>0</v>
       </c>
       <c r="AA30" s="35" t="n">
@@ -15430,7 +15430,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <f aca="false">IF(AND(D31="Channel",OR(E31="CPC",E31="CPA")),MIN(Assumptions!$D$49,J31*H31),0)</f>
+        <f aca="false">IF(AND(D31="Channel",OR(E31="CPC",E31="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C31,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J31*H31),0)</f>
         <v>0</v>
       </c>
       <c r="AA31" s="35" t="n">
@@ -15564,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="35" t="n">
-        <f aca="false">IF(AND(D32="Channel",OR(E32="CPC",E32="CPA")),MIN(Assumptions!$D$49,J32*H32),0)</f>
+        <f aca="false">IF(AND(D32="Channel",OR(E32="CPC",E32="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C32,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J32*H32),0)</f>
         <v>0</v>
       </c>
       <c r="AA32" s="35" t="n">
@@ -15698,7 +15698,7 @@
         <v>1200</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <f aca="false">IF(AND(D33="Channel",OR(E33="CPC",E33="CPA")),MIN(Assumptions!$D$49,J33*H33),0)</f>
+        <f aca="false">IF(AND(D33="Channel",OR(E33="CPC",E33="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C33,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J33*H33),0)</f>
         <v>0</v>
       </c>
       <c r="AA33" s="35" t="n">
@@ -15832,7 +15832,7 @@
         <v>400</v>
       </c>
       <c r="Z34" s="35" t="n">
-        <f aca="false">IF(AND(D34="Channel",OR(E34="CPC",E34="CPA")),MIN(Assumptions!$D$49,J34*H34),0)</f>
+        <f aca="false">IF(AND(D34="Channel",OR(E34="CPC",E34="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C34,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J34*H34),0)</f>
         <v>0</v>
       </c>
       <c r="AA34" s="35" t="n">
@@ -15917,7 +15917,7 @@
         <v>38733.4681977991</v>
       </c>
       <c r="AB35" s="36" t="n">
-        <f aca="false">(X35+Y35)/U35</f>
+        <f aca="false">IF(U35&gt;0,(X35+Y35)/U35,0)</f>
         <v>387.334681977991</v>
       </c>
       <c r="AE35" s="27" t="n">
@@ -16132,7 +16132,7 @@
         <v>620</v>
       </c>
       <c r="C12" s="4" t="n">
-        <f aca="false">ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51</f>
+        <f aca="false">IF(Assumptions!$D$51&gt;0,ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51,C11)</f>
         <v>47500</v>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="36" t="n">
-        <f aca="false">F25/G25</f>
+        <f aca="false">IF(G25&gt;0,F25/G25,0)</f>
         <v>387.334681977991</v>
       </c>
       <c r="I25" s="29" t="n">
@@ -20676,7 +20676,7 @@
         <v>322.142857142857</v>
       </c>
       <c r="S15" s="2" t="str">
-        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan")))))))</f>
+        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(AND(F20&gt;0,ABS(E15-1)&gt;0.001),"✗ no spend share falls before the supervisor cut-off (Funnel B20): move weekly shares into weeks 1–5",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan"))))))))</f>
         <v>✓ ties to plan</v>
       </c>
       <c r="T15" s="29" t="n">

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
   <si>
-    <t xml:space="preserve">Everything on this tab is a live link. Inputs live only on the Assumptions tab (blue on yellow).</t>
+    <t xml:space="preserve">Everything on this tab is a live link to the model. Inputs live only on the Assumptions tab (blue on yellow).</t>
   </si>
   <si>
     <t xml:space="preserve">Target: signed contracts by 31 Dec</t>
@@ -52,9 +52,6 @@
     <t xml:space="preserve">Hires the channel plan buys</t>
   </si>
   <si>
-    <t xml:space="preserve">Hires actually possible (≤ 55 assessments/week)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Media cost per hire</t>
   </si>
   <si>
@@ -73,10 +70,7 @@
     <t xml:space="preserve">Last useful application date (Supervisors)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardest role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electricians (see Funnel row 35)</t>
+    <t xml:space="preserve">Hardest role (lowest channel coverage without the unproven I2)</t>
   </si>
   <si>
     <t xml:space="preserve">Most sensitive assumption</t>
@@ -85,6 +79,9 @@
     <t xml:space="preserve">Hires with 30% less budget</t>
   </si>
   <si>
+    <t xml:space="preserve">Input checks</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tabs: Assumptions (all inputs + labels) → Funnel (Part 1) → Pool (sanity) → Channels (Part 2.2–2.3) → Initiatives (Part 3) → Budget (Part 2.4–2.5) → Scenarios → Weekly → Tracker (Part 4, live round).</t>
   </si>
   <si>
@@ -1399,6 +1396,9 @@
     <t xml:space="preserve">Coverage without the unproven I2 initiative</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranking helper (roles with openings)</t>
+  </si>
+  <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
@@ -1411,7 +1411,7 @@
     <t xml:space="preserve">Yes (no recognition gate in brief)</t>
   </si>
   <si>
-    <t xml:space="preserve">Verdict: Electricians. Biggest scarce volume (30); channel coverage ~1.9× openings, but only ~1.5× without the unproven Handwerk→Industrie initiative (K30) – the lowest of any role; no Polish route and no foreign-trained route by 31 Dec; and energy/grid, rail, aerospace, agencies and Tesla's own lines want the same certificate. Supervisors need a bigger share of a smaller pool (G33) and have ~1.8× coverage, but are only 10 hires with an internal-promotion fallback (and the earliest cut-off, B20).</t>
+    <t xml:space="preserve">Verdict (base case; Summary C16 recomputes it live): Electricians. Biggest scarce volume (30); channel coverage ~1.9× openings, but only ~1.5× without the unproven Handwerk→Industrie initiative (K30) – the lowest of any role; no Polish route and no foreign-trained route by 31 Dec; and energy/grid, rail, aerospace, agencies and Tesla's own lines want the same certificate. Supervisors need a bigger share of a smaller pool (G33) and have ~1.8× coverage, but are only 10 hires with an internal-promotion fallback (and the earliest cut-off, B20).</t>
   </si>
   <si>
     <t xml:space="preserve">Sensitivity: each assumption 30% worse (Part 1.4)</t>
@@ -2908,7 +2908,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G21"/>
+  <dimension ref="B1:G22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2972,8 +2972,9 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
-        <v>7</v>
+      <c r="B9" s="2" t="str">
+        <f aca="false">"Hires actually possible (≤ "&amp;Assumptions!$D$9&amp;" assessments/week)"</f>
+        <v>Hires actually possible (≤ 55 assessments/week)</v>
       </c>
       <c r="C9" s="5" t="n">
         <f aca="false">MIN(Budget!C13,Funnel!B26)</f>
@@ -2982,7 +2983,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="4" t="n">
         <f aca="false">Budget!C14</f>
@@ -2991,7 +2992,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="n">
         <f aca="false">Funnel!B23</f>
@@ -3000,7 +3001,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="n">
         <f aca="false">Funnel!B22</f>
@@ -3009,7 +3010,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Funnel!B24</f>
@@ -3018,7 +3019,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
         <f aca="false">Funnel!B19</f>
@@ -3027,7 +3028,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">Funnel!B20</f>
@@ -3036,15 +3037,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="C16" s="8" t="str">
+        <f aca="false">IF(MIN(Funnel!L30:L33)&gt;=1000000000,"–",INDEX(Funnel!A30:A33,MATCH(MIN(Funnel!L30:L33),Funnel!L30:L33,0))&amp;" ("&amp;TEXT(MIN(Funnel!L30:L33),"0.0")&amp;"× coverage; see Funnel row 35)")</f>
+        <v>Electricians (1.5× coverage; see Funnel row 35)</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="8" t="str">
         <f aca="false">Funnel!D49</f>
@@ -3053,34 +3055,43 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">Budget!H47</f>
         <v>90.6720880966647</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="8" t="str">
+        <f aca="false">IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1))+((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0))+SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))+(Assumptions!$D$48&lt;0)+(Assumptions!$D$48&gt;=1)+(Assumptions!$D$20&lt;Assumptions!$D$7)+(Assumptions!$D$20&gt;Assumptions!$D$8)=0,"✓ all inputs valid","✗ invalid input: "&amp;IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1))&gt;0,"a share/rate is outside 0–100%; ","")&amp;IF(((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0))&gt;0,"a count, cost or day value is negative; ","")&amp;IF(SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))&gt;0,"a channel input (Assumptions §7) is out of range; ","")&amp;IF(OR(Assumptions!$D$48&lt;0,Assumptions!$D$48&gt;=1),"reserve share must be 0–99%; ","")&amp;IF(OR(Assumptions!$D$20&lt;Assumptions!$D$7,Assumptions!$D$20&gt;Assumptions!$D$8),"last signing date must fall inside the campaign; ",""))</f>
+        <v>✓ all inputs valid</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B20:G21"/>
+    <mergeCell ref="B21:G22"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3121,13 +3132,13 @@
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>724</v>
@@ -5325,7 +5336,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G35" s="36" t="n">
         <f aca="false">SUM(G5:G34)</f>
@@ -5384,7 +5395,7 @@
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
       <c r="B39" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>746</v>
@@ -5423,7 +5434,7 @@
         <v>757</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P39" s="12" t="s">
         <v>758</v>
@@ -5431,7 +5442,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
@@ -5477,7 +5488,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
@@ -5523,7 +5534,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
@@ -5569,7 +5580,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -5615,7 +5626,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C44" s="29" t="n">
         <f aca="false">SUM(C40:C43)</f>
@@ -5748,17 +5759,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5769,237 +5780,237 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>46315</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>36</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>46387</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G8" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="C10" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="C11" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>51</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>59</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>60</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6010,191 +6021,191 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="C18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="G18" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>64</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="13" t="s">
         <v>66</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>69</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>46374</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G21" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G22" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G23" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>81</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G24" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>84</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G25" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6205,398 +6216,398 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="F28" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="G28" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>97</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>0.55</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>0.45</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>0.65</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>0.65</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D44" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -6607,467 +6618,467 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="C47" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="D47" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="E47" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="F47" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="G47" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B48" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="C48" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="C49" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="D49" s="17" t="n">
         <v>750</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49" s="13" t="s">
         <v>127</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B50" s="13" t="s">
-        <v>130</v>
-      </c>
       <c r="C50" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D51" s="17" t="n">
         <v>2500</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>136</v>
-      </c>
       <c r="C52" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D52" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>139</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B54" s="13" t="s">
-        <v>142</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="C55" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="D55" s="16" t="n">
         <v>0.03</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D56" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D57" s="16" t="n">
         <v>0.2</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B58" s="13" t="s">
-        <v>155</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>158</v>
-      </c>
       <c r="C59" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="13" t="s">
-        <v>160</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="C61" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="13" t="s">
-        <v>166</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="B63" s="13" t="s">
-        <v>168</v>
-      </c>
       <c r="C63" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B64" s="13" t="s">
-        <v>170</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="13" t="s">
-        <v>172</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="B66" s="13" t="s">
-        <v>174</v>
-      </c>
       <c r="C66" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
@@ -7078,306 +7089,306 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="D69" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="E69" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="F69" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="G69" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G69" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="13" t="s">
-        <v>178</v>
-      </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D70" s="15" t="n">
         <v>7000</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G70" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G70" s="13" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D71" s="15" t="n">
         <v>27000</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D72" s="15" t="n">
         <v>2500</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D73" s="15" t="n">
         <v>2000</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B74" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="C74" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D74" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D76" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B78" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B78" s="13" t="s">
-        <v>194</v>
-      </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D78" s="15" t="n">
         <v>150</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F78" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G78" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="G78" s="13" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D79" s="15" t="n">
         <v>300</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G79" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="G79" s="13" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D80" s="15" t="n">
         <v>400</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G80" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="G80" s="13" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D81" s="15" t="n">
         <v>100</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G81" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="G81" s="13" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -7388,582 +7399,582 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="C84" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="D84" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="E84" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="F84" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F84" s="12" t="s">
+      <c r="G84" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="C85" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="D85" s="17" t="n">
         <v>500</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="B86" s="13" t="s">
-        <v>206</v>
-      </c>
       <c r="C86" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D86" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G86" s="13" t="s">
         <v>207</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G86" s="13" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B87" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B87" s="13" t="s">
-        <v>210</v>
-      </c>
       <c r="C87" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="E87" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G87" s="13" t="s">
         <v>211</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G87" s="13" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B88" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="B88" s="13" t="s">
-        <v>214</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B89" s="13" t="s">
-        <v>217</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D89" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B90" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B90" s="13" t="s">
-        <v>220</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D90" s="17" t="n">
         <v>750</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B91" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B91" s="13" t="s">
-        <v>223</v>
-      </c>
       <c r="C91" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D91" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E91" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G91" s="13" t="s">
         <v>224</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G91" s="13" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B92" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B92" s="13" t="s">
-        <v>227</v>
-      </c>
       <c r="C92" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B93" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="C93" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="D93" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B94" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B94" s="13" t="s">
-        <v>234</v>
-      </c>
       <c r="C94" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B95" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B95" s="13" t="s">
-        <v>237</v>
-      </c>
       <c r="C95" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D95" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="B96" s="13" t="s">
-        <v>240</v>
-      </c>
       <c r="C96" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D96" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B97" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="C97" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>0.35</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B98" s="13" t="s">
-        <v>247</v>
-      </c>
       <c r="C98" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="B99" s="13" t="s">
-        <v>250</v>
-      </c>
       <c r="C99" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B100" s="13" t="s">
-        <v>253</v>
-      </c>
       <c r="C100" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B101" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="C101" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D101" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G101" s="13" t="s">
         <v>258</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G101" s="13" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B102" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B102" s="13" t="s">
-        <v>261</v>
-      </c>
       <c r="C102" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D102" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E102" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G102" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G102" s="13" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B103" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="C103" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B104" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>269</v>
-      </c>
       <c r="C104" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B105" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="C105" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B106" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="C106" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B107" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="B107" s="13" t="s">
-        <v>280</v>
-      </c>
       <c r="C107" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D107" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E107" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G107" s="13" t="s">
         <v>281</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G107" s="13" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B108" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B108" s="13" t="s">
-        <v>284</v>
-      </c>
       <c r="C108" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D108" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
@@ -7979,54 +7990,54 @@
     </row>
     <row r="111" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B111" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C111" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C111" s="12" t="s">
+      <c r="D111" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="E111" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="F111" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="F111" s="12" t="s">
+      <c r="G111" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="G111" s="12" t="s">
+      <c r="H111" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="H111" s="12" t="s">
+      <c r="I111" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="I111" s="12" t="s">
+      <c r="J111" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="J111" s="12" t="s">
-        <v>295</v>
-      </c>
       <c r="K111" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="L111" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B112" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="C112" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E112" s="19" t="n">
         <v>0</v>
@@ -8045,24 +8056,24 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L112" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B113" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E113" s="19" t="n">
         <v>0</v>
@@ -8081,24 +8092,24 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L113" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B114" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E114" s="19" t="n">
         <v>0</v>
@@ -8117,24 +8128,24 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L114" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B115" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="E115" s="19" t="n">
         <v>0</v>
@@ -8153,24 +8164,24 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L115" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B116" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="C116" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D116" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="E116" s="19" t="n">
         <v>2</v>
@@ -8191,24 +8202,24 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L116" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B117" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="E117" s="19" t="n">
         <v>1.2</v>
@@ -8229,24 +8240,24 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L117" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B118" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="E118" s="19" t="n">
         <v>1.8</v>
@@ -8267,24 +8278,24 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L118" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B119" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="E119" s="19" t="n">
         <v>1.7</v>
@@ -8305,24 +8316,24 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L119" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B120" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="C120" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E120" s="19" t="n">
         <v>1449</v>
@@ -8343,24 +8354,24 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L120" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B121" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E121" s="19" t="n">
         <v>1449</v>
@@ -8381,24 +8392,24 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L121" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B122" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E122" s="19" t="n">
         <v>1449</v>
@@ -8419,24 +8430,24 @@
         <v>0</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L122" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B123" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E123" s="19" t="n">
         <v>1449</v>
@@ -8457,24 +8468,24 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L123" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B124" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="B124" s="13" t="s">
-        <v>326</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E124" s="19" t="n">
         <v>3.5</v>
@@ -8495,24 +8506,24 @@
         <v>0</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L124" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E125" s="19" t="n">
         <v>3.5</v>
@@ -8533,24 +8544,24 @@
         <v>0</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L125" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B126" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="C126" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="E126" s="19" t="n">
         <v>18</v>
@@ -8569,24 +8580,24 @@
         <v>0</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L126" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B127" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="E127" s="19" t="n">
         <v>12</v>
@@ -8605,24 +8616,24 @@
         <v>0</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L127" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B128" s="13" t="s">
         <v>336</v>
       </c>
-      <c r="B128" s="13" t="s">
-        <v>337</v>
-      </c>
       <c r="C128" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E128" s="19" t="n">
         <v>2.2</v>
@@ -8643,24 +8654,24 @@
         <v>0</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L128" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E129" s="19" t="n">
         <v>2.2</v>
@@ -8681,24 +8692,24 @@
         <v>0</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L129" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E130" s="19" t="n">
         <v>2.2</v>
@@ -8719,24 +8730,24 @@
         <v>0</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L130" s="13" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E131" s="19" t="n">
         <v>2.2</v>
@@ -8757,15 +8768,15 @@
         <v>0</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L131" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
@@ -8776,649 +8787,667 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B134" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="C134" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="D134" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="E134" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E134" s="12" t="s">
+      <c r="F134" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F134" s="12" t="s">
+      <c r="G134" s="12" t="s">
         <v>27</v>
-      </c>
-      <c r="G134" s="12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B135" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="B135" s="13" t="s">
-        <v>345</v>
-      </c>
       <c r="C135" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D135" s="15" t="n">
         <v>200</v>
       </c>
       <c r="E135" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G135" s="13" t="s">
         <v>346</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G135" s="13" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D136" s="15" t="n">
         <v>300</v>
       </c>
       <c r="E136" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G136" s="13" t="s">
         <v>346</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G136" s="13" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D137" s="15" t="n">
         <v>120</v>
       </c>
       <c r="E137" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G137" s="13" t="s">
         <v>346</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G137" s="13" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D138" s="15" t="n">
         <v>80</v>
       </c>
       <c r="E138" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G138" s="13" t="s">
         <v>346</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G138" s="13" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B139" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="B139" s="13" t="s">
-        <v>352</v>
-      </c>
       <c r="C139" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D139" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B140" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="B140" s="13" t="s">
-        <v>355</v>
-      </c>
       <c r="C140" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D140" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B141" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="B141" s="13" t="s">
-        <v>358</v>
-      </c>
       <c r="C141" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D141" s="15" t="n">
         <v>25</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D142" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D143" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D144" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B145" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="B145" s="13" t="s">
-        <v>364</v>
-      </c>
       <c r="C145" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D145" s="16" t="n">
         <v>0.45</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B146" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B146" s="13" t="s">
-        <v>367</v>
-      </c>
       <c r="C146" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D146" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B147" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="B147" s="13" t="s">
-        <v>370</v>
-      </c>
       <c r="C147" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D147" s="17" t="n">
         <v>1000</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B148" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="B148" s="13" t="s">
-        <v>373</v>
-      </c>
       <c r="C148" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D148" s="20" t="n">
         <v>1.15</v>
       </c>
       <c r="E148" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G148" s="13" t="s">
         <v>374</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B149" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="B149" s="13" t="s">
-        <v>377</v>
-      </c>
       <c r="C149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D149" s="15" t="n">
         <v>12000</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B150" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="B150" s="13" t="s">
-        <v>380</v>
-      </c>
       <c r="C150" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D150" s="21" t="n">
         <v>0.025</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B151" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="B151" s="13" t="s">
-        <v>383</v>
-      </c>
       <c r="C151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D151" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B152" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B152" s="13" t="s">
-        <v>386</v>
-      </c>
       <c r="C152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D152" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B153" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="B153" s="13" t="s">
-        <v>389</v>
-      </c>
       <c r="C153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D153" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B154" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="B154" s="13" t="s">
-        <v>392</v>
-      </c>
       <c r="C154" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D154" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B155" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="B155" s="13" t="s">
-        <v>395</v>
-      </c>
       <c r="C155" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D155" s="17" t="n">
         <v>12</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B156" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="B156" s="13" t="s">
-        <v>398</v>
-      </c>
       <c r="C156" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D156" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B157" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="B157" s="13" t="s">
-        <v>401</v>
-      </c>
       <c r="C157" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D157" s="15" t="n">
         <v>450</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B158" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="B158" s="13" t="s">
-        <v>404</v>
-      </c>
       <c r="C158" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D158" s="20" t="n">
         <v>1.1</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B159" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="B159" s="13" t="s">
-        <v>407</v>
-      </c>
       <c r="C159" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D159" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G159" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G159" s="13" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B160" s="13" t="s">
         <v>410</v>
       </c>
-      <c r="B160" s="13" t="s">
-        <v>411</v>
-      </c>
       <c r="C160" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D160" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B161" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="B161" s="13" t="s">
-        <v>414</v>
-      </c>
       <c r="C161" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D161" s="17" t="n">
         <v>400</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation allowBlank="false" error="Enter a share between 0% and 100%." errorStyle="stop" errorTitle="Out of range" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D10 D29:D44 D50 D52:D66 D74:D77 D92:D93 D95 D97:D100 D103:D106 G112:G131 F116:F119 F124:F125 F128:F131 D139:D140 D145 D150 D152 D156" type="decimal">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Reserve must be between 0% and 99%." errorStyle="stop" errorTitle="Out of range" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D48" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0.99</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Enter a number ≥ 0." errorStyle="stop" errorTitle="Out of range" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D9 D11:D15 D19 D21:D25 D49 D51 D70:D73 D78:D81 D85:D91 D94 D96 D101:D102 D107:D108 E112:F115 H112:J131 E116:E131 F120:F123 F126:F127 D135:D138 D141:D144 D146:D149 D151 D153:D155 D157:D161" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" error="Enter a date inside the campaign (20 Oct – 31 Dec 2026)." errorStyle="stop" errorTitle="Out of range" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D20" type="date">
+      <formula1>DATE(2026,10,20)</formula1>
+      <formula2>DATE(2026,12,31)</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9446,67 +9475,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>420</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>422</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>426</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="M4" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>430</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$D$11</f>
@@ -9571,7 +9600,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">Assumptions!$D$12</f>
@@ -9636,7 +9665,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">Assumptions!$D$13</f>
@@ -9701,7 +9730,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">Assumptions!$D$14</f>
@@ -9766,7 +9795,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -9811,17 +9840,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">Assumptions!$D$7+Assumptions!$D$19</f>
@@ -9830,7 +9859,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">Assumptions!$D$20</f>
@@ -9839,7 +9868,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">Assumptions!$D$22+Assumptions!$D$23+Assumptions!$D$24</f>
@@ -9848,7 +9877,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">B15+Assumptions!$D$25</f>
@@ -9857,7 +9886,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B14-B15</f>
@@ -9866,7 +9895,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B18" s="30" t="n">
         <f aca="false">B14-B16</f>
@@ -9875,7 +9904,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="31" t="n">
         <f aca="false">B17-Assumptions!$D$21</f>
@@ -9884,7 +9913,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" s="30" t="n">
         <f aca="false">B18-Assumptions!$D$21</f>
@@ -9893,7 +9922,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">MAX(0,B17-B13+1)</f>
@@ -9902,7 +9931,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">Assumptions!$D$9*B21/7</f>
@@ -9911,7 +9940,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">O9</f>
@@ -9920,7 +9949,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="33" t="n">
         <f aca="false">IF(B22&gt;0,B23/B22,IF(B23&gt;0,9.99,0))</f>
@@ -9933,7 +9962,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">IF(O9&gt;0,Channels!U35/O9,0)</f>
@@ -9942,59 +9971,62 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">B22*B25</f>
         <v>110.823976181854</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="E29" s="12" t="s">
         <v>448</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="F29" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="G29" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="H29" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="I29" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="I29" s="12" t="s">
+      <c r="J29" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="K29" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="L29" s="12" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B5</f>
@@ -10034,10 +10066,14 @@
         <f aca="false">IF(B30&gt;0,(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30,0)</f>
         <v>1.4825971875</v>
       </c>
+      <c r="L30" s="34" t="n">
+        <f aca="false">IF(B30&gt;0,K30,1000000000)</f>
+        <v>1.4825971875</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">B6</f>
@@ -10077,10 +10113,14 @@
         <f aca="false">IF(B31&gt;0,(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31,0)</f>
         <v>3.239275</v>
       </c>
+      <c r="L31" s="34" t="n">
+        <f aca="false">IF(B31&gt;0,K31,1000000000)</f>
+        <v>3.239275</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">B7</f>
@@ -10120,10 +10160,14 @@
         <f aca="false">IF(B32&gt;0,(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32,0)</f>
         <v>1.9978725</v>
       </c>
+      <c r="L32" s="34" t="n">
+        <f aca="false">IF(B32&gt;0,K32,1000000000)</f>
+        <v>1.9978725</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">B8</f>
@@ -10161,6 +10205,10 @@
       </c>
       <c r="K33" s="34" t="n">
         <f aca="false">IF(B33&gt;0,(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33,0)</f>
+        <v>1.755369</v>
+      </c>
+      <c r="L33" s="34" t="n">
+        <f aca="false">IF(B33&gt;0,K33,1000000000)</f>
         <v>1.755369</v>
       </c>
     </row>
@@ -10224,7 +10272,7 @@
         <v>464</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="12" t="s">
         <v>465</v>
@@ -10499,7 +10547,7 @@
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>485</v>
@@ -10534,7 +10582,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$D$70</f>
@@ -10579,7 +10627,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">Assumptions!$D$71</f>
@@ -10624,7 +10672,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">Assumptions!$D$72</f>
@@ -10669,7 +10717,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">Assumptions!$D$73</f>
@@ -10785,19 +10833,19 @@
         <v>498</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11607,19 +11655,19 @@
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>567</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>568</v>
@@ -11631,7 +11679,7 @@
         <v>521</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J4" s="12" t="s">
         <v>520</v>
@@ -11640,7 +11688,7 @@
         <v>570</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>571</v>
@@ -11726,7 +11774,7 @@
         <v>Electricians</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E5" s="2" t="str">
         <f aca="false">Assumptions!D112</f>
@@ -11741,7 +11789,7 @@
         <v/>
       </c>
       <c r="H5" s="37" t="n">
-        <f aca="false">IF(OR(E5="CPC",E5="Slot"),IF(N(G5)&gt;0,F5/G5,0),F5)</f>
+        <f aca="false">MAX(0,IF(OR(E5="CPC",E5="Slot"),IF(N(G5)&gt;0,F5/G5,0),F5))</f>
         <v>0</v>
       </c>
       <c r="I5" s="24" t="n">
@@ -11805,7 +11853,7 @@
         <v>150</v>
       </c>
       <c r="X5" s="35" t="n">
-        <f aca="false">IF(E5="Slot",IF(N(G5)&gt;0,ROUNDUP(W5/G5,0)*F5,0),W5*H5)</f>
+        <f aca="false">IF(E5="Slot",IF(N(G5)&gt;0,ROUNDUP(W5/G5,0)*MAX(0,F5),0),W5*H5)</f>
         <v>0</v>
       </c>
       <c r="Y5" s="35" t="n">
@@ -11813,7 +11861,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="35" t="n">
-        <f aca="false">IF(AND(D5="Channel",OR(E5="CPC",E5="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C5,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J5*H5),0)</f>
+        <f aca="false">IF(AND(D5="Channel",OR(E5="CPC",E5="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C5,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J5*H5,IF(I5*L5&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C5,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C5)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I5*L5)*H5,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA5" s="35" t="n">
@@ -11867,7 +11915,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E6" s="2" t="str">
         <f aca="false">Assumptions!D113</f>
@@ -11882,7 +11930,7 @@
         <v/>
       </c>
       <c r="H6" s="37" t="n">
-        <f aca="false">IF(OR(E6="CPC",E6="Slot"),IF(N(G6)&gt;0,F6/G6,0),F6)</f>
+        <f aca="false">MAX(0,IF(OR(E6="CPC",E6="Slot"),IF(N(G6)&gt;0,F6/G6,0),F6))</f>
         <v>0</v>
       </c>
       <c r="I6" s="24" t="n">
@@ -11946,7 +11994,7 @@
         <v>200</v>
       </c>
       <c r="X6" s="35" t="n">
-        <f aca="false">IF(E6="Slot",IF(N(G6)&gt;0,ROUNDUP(W6/G6,0)*F6,0),W6*H6)</f>
+        <f aca="false">IF(E6="Slot",IF(N(G6)&gt;0,ROUNDUP(W6/G6,0)*MAX(0,F6),0),W6*H6)</f>
         <v>0</v>
       </c>
       <c r="Y6" s="35" t="n">
@@ -11954,7 +12002,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="35" t="n">
-        <f aca="false">IF(AND(D6="Channel",OR(E6="CPC",E6="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C6,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J6*H6),0)</f>
+        <f aca="false">IF(AND(D6="Channel",OR(E6="CPC",E6="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C6,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J6*H6,IF(I6*L6&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C6,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C6)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I6*L6)*H6,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA6" s="35" t="n">
@@ -12008,7 +12056,7 @@
         <v>Automation</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E7" s="2" t="str">
         <f aca="false">Assumptions!D114</f>
@@ -12023,7 +12071,7 @@
         <v/>
       </c>
       <c r="H7" s="37" t="n">
-        <f aca="false">IF(OR(E7="CPC",E7="Slot"),IF(N(G7)&gt;0,F7/G7,0),F7)</f>
+        <f aca="false">MAX(0,IF(OR(E7="CPC",E7="Slot"),IF(N(G7)&gt;0,F7/G7,0),F7))</f>
         <v>0</v>
       </c>
       <c r="I7" s="24" t="n">
@@ -12087,7 +12135,7 @@
         <v>80</v>
       </c>
       <c r="X7" s="35" t="n">
-        <f aca="false">IF(E7="Slot",IF(N(G7)&gt;0,ROUNDUP(W7/G7,0)*F7,0),W7*H7)</f>
+        <f aca="false">IF(E7="Slot",IF(N(G7)&gt;0,ROUNDUP(W7/G7,0)*MAX(0,F7),0),W7*H7)</f>
         <v>0</v>
       </c>
       <c r="Y7" s="35" t="n">
@@ -12095,7 +12143,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="35" t="n">
-        <f aca="false">IF(AND(D7="Channel",OR(E7="CPC",E7="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C7,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J7*H7),0)</f>
+        <f aca="false">IF(AND(D7="Channel",OR(E7="CPC",E7="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C7,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J7*H7,IF(I7*L7&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C7,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C7)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I7*L7)*H7,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA7" s="35" t="n">
@@ -12149,7 +12197,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E8" s="2" t="str">
         <f aca="false">Assumptions!D115</f>
@@ -12164,7 +12212,7 @@
         <v/>
       </c>
       <c r="H8" s="37" t="n">
-        <f aca="false">IF(OR(E8="CPC",E8="Slot"),IF(N(G8)&gt;0,F8/G8,0),F8)</f>
+        <f aca="false">MAX(0,IF(OR(E8="CPC",E8="Slot"),IF(N(G8)&gt;0,F8/G8,0),F8))</f>
         <v>0</v>
       </c>
       <c r="I8" s="24" t="n">
@@ -12228,7 +12276,7 @@
         <v>60</v>
       </c>
       <c r="X8" s="35" t="n">
-        <f aca="false">IF(E8="Slot",IF(N(G8)&gt;0,ROUNDUP(W8/G8,0)*F8,0),W8*H8)</f>
+        <f aca="false">IF(E8="Slot",IF(N(G8)&gt;0,ROUNDUP(W8/G8,0)*MAX(0,F8),0),W8*H8)</f>
         <v>0</v>
       </c>
       <c r="Y8" s="35" t="n">
@@ -12236,7 +12284,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="35" t="n">
-        <f aca="false">IF(AND(D8="Channel",OR(E8="CPC",E8="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C8,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J8*H8),0)</f>
+        <f aca="false">IF(AND(D8="Channel",OR(E8="CPC",E8="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C8,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J8*H8,IF(I8*L8&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C8,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C8)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I8*L8)*H8,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA8" s="35" t="n">
@@ -12290,7 +12338,7 @@
         <v>Electricians</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E9" s="2" t="str">
         <f aca="false">Assumptions!D116</f>
@@ -12305,7 +12353,7 @@
         <v>0.035</v>
       </c>
       <c r="H9" s="37" t="n">
-        <f aca="false">IF(OR(E9="CPC",E9="Slot"),IF(N(G9)&gt;0,F9/G9,0),F9)</f>
+        <f aca="false">MAX(0,IF(OR(E9="CPC",E9="Slot"),IF(N(G9)&gt;0,F9/G9,0),F9))</f>
         <v>57.1428571428571</v>
       </c>
       <c r="I9" s="24" t="n">
@@ -12369,7 +12417,7 @@
         <v>13.125</v>
       </c>
       <c r="X9" s="35" t="n">
-        <f aca="false">IF(E9="Slot",IF(N(G9)&gt;0,ROUNDUP(W9/G9,0)*F9,0),W9*H9)</f>
+        <f aca="false">IF(E9="Slot",IF(N(G9)&gt;0,ROUNDUP(W9/G9,0)*MAX(0,F9),0),W9*H9)</f>
         <v>750</v>
       </c>
       <c r="Y9" s="35" t="n">
@@ -12377,7 +12425,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="35" t="n">
-        <f aca="false">IF(AND(D9="Channel",OR(E9="CPC",E9="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C9,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J9*H9),0)</f>
+        <f aca="false">IF(AND(D9="Channel",OR(E9="CPC",E9="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C9,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J9*H9,IF(I9*L9&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C9,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C9)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I9*L9)*H9,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA9" s="35" t="n">
@@ -12431,7 +12479,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E10" s="2" t="str">
         <f aca="false">Assumptions!D117</f>
@@ -12446,7 +12494,7 @@
         <v>0.05</v>
       </c>
       <c r="H10" s="37" t="n">
-        <f aca="false">IF(OR(E10="CPC",E10="Slot"),IF(N(G10)&gt;0,F10/G10,0),F10)</f>
+        <f aca="false">MAX(0,IF(OR(E10="CPC",E10="Slot"),IF(N(G10)&gt;0,F10/G10,0),F10))</f>
         <v>24</v>
       </c>
       <c r="I10" s="24" t="n">
@@ -12510,7 +12558,7 @@
         <v>31.25</v>
       </c>
       <c r="X10" s="35" t="n">
-        <f aca="false">IF(E10="Slot",IF(N(G10)&gt;0,ROUNDUP(W10/G10,0)*F10,0),W10*H10)</f>
+        <f aca="false">IF(E10="Slot",IF(N(G10)&gt;0,ROUNDUP(W10/G10,0)*MAX(0,F10),0),W10*H10)</f>
         <v>750</v>
       </c>
       <c r="Y10" s="35" t="n">
@@ -12518,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="35" t="n">
-        <f aca="false">IF(AND(D10="Channel",OR(E10="CPC",E10="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C10,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J10*H10),0)</f>
+        <f aca="false">IF(AND(D10="Channel",OR(E10="CPC",E10="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C10,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J10*H10,IF(I10*L10&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C10,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C10)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I10*L10)*H10,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA10" s="35" t="n">
@@ -12572,7 +12620,7 @@
         <v>Automation</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E11" s="2" t="str">
         <f aca="false">Assumptions!D118</f>
@@ -12587,7 +12635,7 @@
         <v>0.04</v>
       </c>
       <c r="H11" s="37" t="n">
-        <f aca="false">IF(OR(E11="CPC",E11="Slot"),IF(N(G11)&gt;0,F11/G11,0),F11)</f>
+        <f aca="false">MAX(0,IF(OR(E11="CPC",E11="Slot"),IF(N(G11)&gt;0,F11/G11,0),F11))</f>
         <v>45</v>
       </c>
       <c r="I11" s="24" t="n">
@@ -12651,7 +12699,7 @@
         <v>16.6666666666667</v>
       </c>
       <c r="X11" s="35" t="n">
-        <f aca="false">IF(E11="Slot",IF(N(G11)&gt;0,ROUNDUP(W11/G11,0)*F11,0),W11*H11)</f>
+        <f aca="false">IF(E11="Slot",IF(N(G11)&gt;0,ROUNDUP(W11/G11,0)*MAX(0,F11),0),W11*H11)</f>
         <v>750</v>
       </c>
       <c r="Y11" s="35" t="n">
@@ -12659,7 +12707,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="35" t="n">
-        <f aca="false">IF(AND(D11="Channel",OR(E11="CPC",E11="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C11,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J11*H11),0)</f>
+        <f aca="false">IF(AND(D11="Channel",OR(E11="CPC",E11="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C11,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J11*H11,IF(I11*L11&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C11,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C11)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I11*L11)*H11,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA11" s="35" t="n">
@@ -12713,7 +12761,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E12" s="2" t="str">
         <f aca="false">Assumptions!D119</f>
@@ -12728,7 +12776,7 @@
         <v>0.04</v>
       </c>
       <c r="H12" s="37" t="n">
-        <f aca="false">IF(OR(E12="CPC",E12="Slot"),IF(N(G12)&gt;0,F12/G12,0),F12)</f>
+        <f aca="false">MAX(0,IF(OR(E12="CPC",E12="Slot"),IF(N(G12)&gt;0,F12/G12,0),F12))</f>
         <v>42.5</v>
       </c>
       <c r="I12" s="24" t="n">
@@ -12792,7 +12840,7 @@
         <v>17.6470588235294</v>
       </c>
       <c r="X12" s="35" t="n">
-        <f aca="false">IF(E12="Slot",IF(N(G12)&gt;0,ROUNDUP(W12/G12,0)*F12,0),W12*H12)</f>
+        <f aca="false">IF(E12="Slot",IF(N(G12)&gt;0,ROUNDUP(W12/G12,0)*MAX(0,F12),0),W12*H12)</f>
         <v>750</v>
       </c>
       <c r="Y12" s="35" t="n">
@@ -12800,7 +12848,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="35" t="n">
-        <f aca="false">IF(AND(D12="Channel",OR(E12="CPC",E12="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C12,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J12*H12),0)</f>
+        <f aca="false">IF(AND(D12="Channel",OR(E12="CPC",E12="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C12,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J12*H12,IF(I12*L12&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C12,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C12)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I12*L12)*H12,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA12" s="35" t="n">
@@ -12854,7 +12902,7 @@
         <v>Electricians</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E13" s="2" t="str">
         <f aca="false">Assumptions!D120</f>
@@ -12869,7 +12917,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="37" t="n">
-        <f aca="false">IF(OR(E13="CPC",E13="Slot"),IF(N(G13)&gt;0,F13/G13,0),F13)</f>
+        <f aca="false">MAX(0,IF(OR(E13="CPC",E13="Slot"),IF(N(G13)&gt;0,F13/G13,0),F13))</f>
         <v>96.6</v>
       </c>
       <c r="I13" s="24" t="n">
@@ -12933,7 +12981,7 @@
         <v>9.48086635586635</v>
       </c>
       <c r="X13" s="35" t="n">
-        <f aca="false">IF(E13="Slot",IF(N(G13)&gt;0,ROUNDUP(W13/G13,0)*F13,0),W13*H13)</f>
+        <f aca="false">IF(E13="Slot",IF(N(G13)&gt;0,ROUNDUP(W13/G13,0)*MAX(0,F13),0),W13*H13)</f>
         <v>1449</v>
       </c>
       <c r="Y13" s="35" t="n">
@@ -12941,7 +12989,7 @@
         <v>0</v>
       </c>
       <c r="Z13" s="35" t="n">
-        <f aca="false">IF(AND(D13="Channel",OR(E13="CPC",E13="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C13,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J13*H13),0)</f>
+        <f aca="false">IF(AND(D13="Channel",OR(E13="CPC",E13="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C13,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J13*H13,IF(I13*L13&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C13,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C13)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I13*L13)*H13,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA13" s="35" t="n">
@@ -12995,7 +13043,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E14" s="2" t="str">
         <f aca="false">Assumptions!D121</f>
@@ -13010,7 +13058,7 @@
         <v>25</v>
       </c>
       <c r="H14" s="37" t="n">
-        <f aca="false">IF(OR(E14="CPC",E14="Slot"),IF(N(G14)&gt;0,F14/G14,0),F14)</f>
+        <f aca="false">MAX(0,IF(OR(E14="CPC",E14="Slot"),IF(N(G14)&gt;0,F14/G14,0),F14))</f>
         <v>57.96</v>
       </c>
       <c r="I14" s="24" t="n">
@@ -13074,7 +13122,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="35" t="n">
-        <f aca="false">IF(E14="Slot",IF(N(G14)&gt;0,ROUNDUP(W14/G14,0)*F14,0),W14*H14)</f>
+        <f aca="false">IF(E14="Slot",IF(N(G14)&gt;0,ROUNDUP(W14/G14,0)*MAX(0,F14),0),W14*H14)</f>
         <v>0</v>
       </c>
       <c r="Y14" s="35" t="n">
@@ -13082,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="Z14" s="35" t="n">
-        <f aca="false">IF(AND(D14="Channel",OR(E14="CPC",E14="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C14,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J14*H14),0)</f>
+        <f aca="false">IF(AND(D14="Channel",OR(E14="CPC",E14="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C14,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J14*H14,IF(I14*L14&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C14,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C14)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I14*L14)*H14,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA14" s="35" t="n">
@@ -13136,7 +13184,7 @@
         <v>Automation</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E15" s="2" t="str">
         <f aca="false">Assumptions!D122</f>
@@ -13151,7 +13199,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="37" t="n">
-        <f aca="false">IF(OR(E15="CPC",E15="Slot"),IF(N(G15)&gt;0,F15/G15,0),F15)</f>
+        <f aca="false">MAX(0,IF(OR(E15="CPC",E15="Slot"),IF(N(G15)&gt;0,F15/G15,0),F15))</f>
         <v>96.6</v>
       </c>
       <c r="I15" s="24" t="n">
@@ -13215,7 +13263,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="35" t="n">
-        <f aca="false">IF(E15="Slot",IF(N(G15)&gt;0,ROUNDUP(W15/G15,0)*F15,0),W15*H15)</f>
+        <f aca="false">IF(E15="Slot",IF(N(G15)&gt;0,ROUNDUP(W15/G15,0)*MAX(0,F15),0),W15*H15)</f>
         <v>0</v>
       </c>
       <c r="Y15" s="35" t="n">
@@ -13223,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="Z15" s="35" t="n">
-        <f aca="false">IF(AND(D15="Channel",OR(E15="CPC",E15="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C15,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J15*H15),0)</f>
+        <f aca="false">IF(AND(D15="Channel",OR(E15="CPC",E15="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C15,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J15*H15,IF(I15*L15&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C15,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C15)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I15*L15)*H15,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA15" s="35" t="n">
@@ -13277,7 +13325,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E16" s="2" t="str">
         <f aca="false">Assumptions!D123</f>
@@ -13292,7 +13340,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="37" t="n">
-        <f aca="false">IF(OR(E16="CPC",E16="Slot"),IF(N(G16)&gt;0,F16/G16,0),F16)</f>
+        <f aca="false">MAX(0,IF(OR(E16="CPC",E16="Slot"),IF(N(G16)&gt;0,F16/G16,0),F16))</f>
         <v>96.6</v>
       </c>
       <c r="I16" s="24" t="n">
@@ -13356,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="X16" s="35" t="n">
-        <f aca="false">IF(E16="Slot",IF(N(G16)&gt;0,ROUNDUP(W16/G16,0)*F16,0),W16*H16)</f>
+        <f aca="false">IF(E16="Slot",IF(N(G16)&gt;0,ROUNDUP(W16/G16,0)*MAX(0,F16),0),W16*H16)</f>
         <v>0</v>
       </c>
       <c r="Y16" s="35" t="n">
@@ -13364,7 +13412,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="35" t="n">
-        <f aca="false">IF(AND(D16="Channel",OR(E16="CPC",E16="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C16,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J16*H16),0)</f>
+        <f aca="false">IF(AND(D16="Channel",OR(E16="CPC",E16="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C16,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J16*H16,IF(I16*L16&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C16,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C16)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I16*L16)*H16,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA16" s="35" t="n">
@@ -13418,7 +13466,7 @@
         <v>Automation</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E17" s="2" t="str">
         <f aca="false">Assumptions!D124</f>
@@ -13433,7 +13481,7 @@
         <v>0.08</v>
       </c>
       <c r="H17" s="37" t="n">
-        <f aca="false">IF(OR(E17="CPC",E17="Slot"),IF(N(G17)&gt;0,F17/G17,0),F17)</f>
+        <f aca="false">MAX(0,IF(OR(E17="CPC",E17="Slot"),IF(N(G17)&gt;0,F17/G17,0),F17))</f>
         <v>43.75</v>
       </c>
       <c r="I17" s="24" t="n">
@@ -13497,7 +13545,7 @@
         <v>117.690023310023</v>
       </c>
       <c r="X17" s="35" t="n">
-        <f aca="false">IF(E17="Slot",IF(N(G17)&gt;0,ROUNDUP(W17/G17,0)*F17,0),W17*H17)</f>
+        <f aca="false">IF(E17="Slot",IF(N(G17)&gt;0,ROUNDUP(W17/G17,0)*MAX(0,F17),0),W17*H17)</f>
         <v>5148.93851981352</v>
       </c>
       <c r="Y17" s="35" t="n">
@@ -13505,7 +13553,7 @@
         <v>0</v>
       </c>
       <c r="Z17" s="35" t="n">
-        <f aca="false">IF(AND(D17="Channel",OR(E17="CPC",E17="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C17,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J17*H17),0)</f>
+        <f aca="false">IF(AND(D17="Channel",OR(E17="CPC",E17="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C17,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J17*H17,IF(I17*L17&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C17,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C17)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I17*L17)*H17,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA17" s="35" t="n">
@@ -13559,7 +13607,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E18" s="2" t="str">
         <f aca="false">Assumptions!D125</f>
@@ -13574,7 +13622,7 @@
         <v>0.08</v>
       </c>
       <c r="H18" s="37" t="n">
-        <f aca="false">IF(OR(E18="CPC",E18="Slot"),IF(N(G18)&gt;0,F18/G18,0),F18)</f>
+        <f aca="false">MAX(0,IF(OR(E18="CPC",E18="Slot"),IF(N(G18)&gt;0,F18/G18,0),F18))</f>
         <v>43.75</v>
       </c>
       <c r="I18" s="24" t="n">
@@ -13638,7 +13686,7 @@
         <v>100</v>
       </c>
       <c r="X18" s="35" t="n">
-        <f aca="false">IF(E18="Slot",IF(N(G18)&gt;0,ROUNDUP(W18/G18,0)*F18,0),W18*H18)</f>
+        <f aca="false">IF(E18="Slot",IF(N(G18)&gt;0,ROUNDUP(W18/G18,0)*MAX(0,F18),0),W18*H18)</f>
         <v>4375</v>
       </c>
       <c r="Y18" s="35" t="n">
@@ -13646,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="35" t="n">
-        <f aca="false">IF(AND(D18="Channel",OR(E18="CPC",E18="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C18,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J18*H18),0)</f>
+        <f aca="false">IF(AND(D18="Channel",OR(E18="CPC",E18="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C18,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J18*H18,IF(I18*L18&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C18,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C18)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I18*L18)*H18,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA18" s="35" t="n">
@@ -13700,7 +13748,7 @@
         <v>Electricians</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E19" s="2" t="str">
         <f aca="false">Assumptions!D126</f>
@@ -13715,7 +13763,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="37" t="n">
-        <f aca="false">IF(OR(E19="CPC",E19="Slot"),IF(N(G19)&gt;0,F19/G19,0),F19)</f>
+        <f aca="false">MAX(0,IF(OR(E19="CPC",E19="Slot"),IF(N(G19)&gt;0,F19/G19,0),F19))</f>
         <v>18</v>
       </c>
       <c r="I19" s="24" t="n">
@@ -13779,7 +13827,7 @@
         <v>41.6666666666667</v>
       </c>
       <c r="X19" s="35" t="n">
-        <f aca="false">IF(E19="Slot",IF(N(G19)&gt;0,ROUNDUP(W19/G19,0)*F19,0),W19*H19)</f>
+        <f aca="false">IF(E19="Slot",IF(N(G19)&gt;0,ROUNDUP(W19/G19,0)*MAX(0,F19),0),W19*H19)</f>
         <v>750</v>
       </c>
       <c r="Y19" s="35" t="n">
@@ -13787,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="35" t="n">
-        <f aca="false">IF(AND(D19="Channel",OR(E19="CPC",E19="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C19,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J19*H19),0)</f>
+        <f aca="false">IF(AND(D19="Channel",OR(E19="CPC",E19="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C19,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J19*H19,IF(I19*L19&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C19,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C19)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I19*L19)*H19,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA19" s="35" t="n">
@@ -13841,7 +13889,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E20" s="2" t="str">
         <f aca="false">Assumptions!D127</f>
@@ -13856,7 +13904,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="37" t="n">
-        <f aca="false">IF(OR(E20="CPC",E20="Slot"),IF(N(G20)&gt;0,F20/G20,0),F20)</f>
+        <f aca="false">MAX(0,IF(OR(E20="CPC",E20="Slot"),IF(N(G20)&gt;0,F20/G20,0),F20))</f>
         <v>12</v>
       </c>
       <c r="I20" s="24" t="n">
@@ -13920,7 +13968,7 @@
         <v>62.5</v>
       </c>
       <c r="X20" s="35" t="n">
-        <f aca="false">IF(E20="Slot",IF(N(G20)&gt;0,ROUNDUP(W20/G20,0)*F20,0),W20*H20)</f>
+        <f aca="false">IF(E20="Slot",IF(N(G20)&gt;0,ROUNDUP(W20/G20,0)*MAX(0,F20),0),W20*H20)</f>
         <v>750</v>
       </c>
       <c r="Y20" s="35" t="n">
@@ -13928,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="35" t="n">
-        <f aca="false">IF(AND(D20="Channel",OR(E20="CPC",E20="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C20,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J20*H20),0)</f>
+        <f aca="false">IF(AND(D20="Channel",OR(E20="CPC",E20="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C20,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J20*H20,IF(I20*L20&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C20,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C20)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I20*L20)*H20,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA20" s="35" t="n">
@@ -13982,7 +14030,7 @@
         <v>Electricians</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E21" s="2" t="str">
         <f aca="false">Assumptions!D128</f>
@@ -13997,7 +14045,7 @@
         <v>0.07</v>
       </c>
       <c r="H21" s="37" t="n">
-        <f aca="false">IF(OR(E21="CPC",E21="Slot"),IF(N(G21)&gt;0,F21/G21,0),F21)</f>
+        <f aca="false">MAX(0,IF(OR(E21="CPC",E21="Slot"),IF(N(G21)&gt;0,F21/G21,0),F21))</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I21" s="24" t="n">
@@ -14061,7 +14109,7 @@
         <v>80</v>
       </c>
       <c r="X21" s="35" t="n">
-        <f aca="false">IF(E21="Slot",IF(N(G21)&gt;0,ROUNDUP(W21/G21,0)*F21,0),W21*H21)</f>
+        <f aca="false">IF(E21="Slot",IF(N(G21)&gt;0,ROUNDUP(W21/G21,0)*MAX(0,F21),0),W21*H21)</f>
         <v>2514.28571428571</v>
       </c>
       <c r="Y21" s="35" t="n">
@@ -14069,7 +14117,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="35" t="n">
-        <f aca="false">IF(AND(D21="Channel",OR(E21="CPC",E21="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C21,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J21*H21),0)</f>
+        <f aca="false">IF(AND(D21="Channel",OR(E21="CPC",E21="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C21,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J21*H21,IF(I21*L21&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C21,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C21)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I21*L21)*H21,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA21" s="35" t="n">
@@ -14123,7 +14171,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E22" s="2" t="str">
         <f aca="false">Assumptions!D129</f>
@@ -14138,7 +14186,7 @@
         <v>0.07</v>
       </c>
       <c r="H22" s="37" t="n">
-        <f aca="false">IF(OR(E22="CPC",E22="Slot"),IF(N(G22)&gt;0,F22/G22,0),F22)</f>
+        <f aca="false">MAX(0,IF(OR(E22="CPC",E22="Slot"),IF(N(G22)&gt;0,F22/G22,0),F22))</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I22" s="24" t="n">
@@ -14202,7 +14250,7 @@
         <v>23.8636363636364</v>
       </c>
       <c r="X22" s="35" t="n">
-        <f aca="false">IF(E22="Slot",IF(N(G22)&gt;0,ROUNDUP(W22/G22,0)*F22,0),W22*H22)</f>
+        <f aca="false">IF(E22="Slot",IF(N(G22)&gt;0,ROUNDUP(W22/G22,0)*MAX(0,F22),0),W22*H22)</f>
         <v>750</v>
       </c>
       <c r="Y22" s="35" t="n">
@@ -14210,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="35" t="n">
-        <f aca="false">IF(AND(D22="Channel",OR(E22="CPC",E22="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C22,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J22*H22),0)</f>
+        <f aca="false">IF(AND(D22="Channel",OR(E22="CPC",E22="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C22,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J22*H22,IF(I22*L22&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C22,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C22)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I22*L22)*H22,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA22" s="35" t="n">
@@ -14264,7 +14312,7 @@
         <v>Automation</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E23" s="2" t="str">
         <f aca="false">Assumptions!D130</f>
@@ -14279,7 +14327,7 @@
         <v>0.07</v>
       </c>
       <c r="H23" s="37" t="n">
-        <f aca="false">IF(OR(E23="CPC",E23="Slot"),IF(N(G23)&gt;0,F23/G23,0),F23)</f>
+        <f aca="false">MAX(0,IF(OR(E23="CPC",E23="Slot"),IF(N(G23)&gt;0,F23/G23,0),F23))</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I23" s="24" t="n">
@@ -14343,7 +14391,7 @@
         <v>23.8636363636364</v>
       </c>
       <c r="X23" s="35" t="n">
-        <f aca="false">IF(E23="Slot",IF(N(G23)&gt;0,ROUNDUP(W23/G23,0)*F23,0),W23*H23)</f>
+        <f aca="false">IF(E23="Slot",IF(N(G23)&gt;0,ROUNDUP(W23/G23,0)*MAX(0,F23),0),W23*H23)</f>
         <v>750</v>
       </c>
       <c r="Y23" s="35" t="n">
@@ -14351,7 +14399,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="35" t="n">
-        <f aca="false">IF(AND(D23="Channel",OR(E23="CPC",E23="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C23,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J23*H23),0)</f>
+        <f aca="false">IF(AND(D23="Channel",OR(E23="CPC",E23="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C23,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J23*H23,IF(I23*L23&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C23,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C23)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I23*L23)*H23,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA23" s="35" t="n">
@@ -14405,7 +14453,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E24" s="2" t="str">
         <f aca="false">Assumptions!D131</f>
@@ -14420,7 +14468,7 @@
         <v>0.07</v>
       </c>
       <c r="H24" s="37" t="n">
-        <f aca="false">IF(OR(E24="CPC",E24="Slot"),IF(N(G24)&gt;0,F24/G24,0),F24)</f>
+        <f aca="false">MAX(0,IF(OR(E24="CPC",E24="Slot"),IF(N(G24)&gt;0,F24/G24,0),F24))</f>
         <v>31.4285714285714</v>
       </c>
       <c r="I24" s="24" t="n">
@@ -14484,7 +14532,7 @@
         <v>30</v>
       </c>
       <c r="X24" s="35" t="n">
-        <f aca="false">IF(E24="Slot",IF(N(G24)&gt;0,ROUNDUP(W24/G24,0)*F24,0),W24*H24)</f>
+        <f aca="false">IF(E24="Slot",IF(N(G24)&gt;0,ROUNDUP(W24/G24,0)*MAX(0,F24),0),W24*H24)</f>
         <v>942.857142857143</v>
       </c>
       <c r="Y24" s="35" t="n">
@@ -14492,7 +14540,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="35" t="n">
-        <f aca="false">IF(AND(D24="Channel",OR(E24="CPC",E24="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C24,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J24*H24),0)</f>
+        <f aca="false">IF(AND(D24="Channel",OR(E24="CPC",E24="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C24,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J24*H24,IF(I24*L24&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C24,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C24)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I24*L24)*H24,0)),0)</f>
         <v>750</v>
       </c>
       <c r="AA24" s="35" t="n">
@@ -14540,13 +14588,13 @@
         <v>595</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F25" s="37" t="n">
         <f aca="false">Initiatives!B11</f>
@@ -14618,7 +14666,7 @@
         <v>24</v>
       </c>
       <c r="X25" s="35" t="n">
-        <f aca="false">IF(E25="Slot",IF(N(G25)&gt;0,ROUNDUP(W25/G25,0)*F25,0),W25*H25)</f>
+        <f aca="false">IF(E25="Slot",IF(N(G25)&gt;0,ROUNDUP(W25/G25,0)*MAX(0,F25),0),W25*H25)</f>
         <v>100</v>
       </c>
       <c r="Y25" s="35" t="n">
@@ -14626,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="35" t="n">
-        <f aca="false">IF(AND(D25="Channel",OR(E25="CPC",E25="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C25,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J25*H25),0)</f>
+        <f aca="false">IF(AND(D25="Channel",OR(E25="CPC",E25="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C25,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J25*H25,IF(I25*L25&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C25,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C25)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I25*L25)*H25,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA25" s="35" t="n">
@@ -14674,13 +14722,13 @@
         <v>595</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">Initiatives!C11</f>
@@ -14752,7 +14800,7 @@
         <v>36</v>
       </c>
       <c r="X26" s="35" t="n">
-        <f aca="false">IF(E26="Slot",IF(N(G26)&gt;0,ROUNDUP(W26/G26,0)*F26,0),W26*H26)</f>
+        <f aca="false">IF(E26="Slot",IF(N(G26)&gt;0,ROUNDUP(W26/G26,0)*MAX(0,F26),0),W26*H26)</f>
         <v>150</v>
       </c>
       <c r="Y26" s="35" t="n">
@@ -14760,7 +14808,7 @@
         <v>0</v>
       </c>
       <c r="Z26" s="35" t="n">
-        <f aca="false">IF(AND(D26="Channel",OR(E26="CPC",E26="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C26,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J26*H26),0)</f>
+        <f aca="false">IF(AND(D26="Channel",OR(E26="CPC",E26="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C26,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J26*H26,IF(I26*L26&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C26,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C26)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I26*L26)*H26,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA26" s="35" t="n">
@@ -14808,13 +14856,13 @@
         <v>595</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">Initiatives!D11</f>
@@ -14886,7 +14934,7 @@
         <v>14.4</v>
       </c>
       <c r="X27" s="35" t="n">
-        <f aca="false">IF(E27="Slot",IF(N(G27)&gt;0,ROUNDUP(W27/G27,0)*F27,0),W27*H27)</f>
+        <f aca="false">IF(E27="Slot",IF(N(G27)&gt;0,ROUNDUP(W27/G27,0)*MAX(0,F27),0),W27*H27)</f>
         <v>60</v>
       </c>
       <c r="Y27" s="35" t="n">
@@ -14894,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="Z27" s="35" t="n">
-        <f aca="false">IF(AND(D27="Channel",OR(E27="CPC",E27="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C27,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J27*H27),0)</f>
+        <f aca="false">IF(AND(D27="Channel",OR(E27="CPC",E27="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C27,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J27*H27,IF(I27*L27&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C27,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C27)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I27*L27)*H27,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA27" s="35" t="n">
@@ -14942,13 +14990,13 @@
         <v>595</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F28" s="37" t="n">
         <f aca="false">Initiatives!E11</f>
@@ -15020,7 +15068,7 @@
         <v>9.6</v>
       </c>
       <c r="X28" s="35" t="n">
-        <f aca="false">IF(E28="Slot",IF(N(G28)&gt;0,ROUNDUP(W28/G28,0)*F28,0),W28*H28)</f>
+        <f aca="false">IF(E28="Slot",IF(N(G28)&gt;0,ROUNDUP(W28/G28,0)*MAX(0,F28),0),W28*H28)</f>
         <v>40</v>
       </c>
       <c r="Y28" s="35" t="n">
@@ -15028,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="35" t="n">
-        <f aca="false">IF(AND(D28="Channel",OR(E28="CPC",E28="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C28,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J28*H28),0)</f>
+        <f aca="false">IF(AND(D28="Channel",OR(E28="CPC",E28="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C28,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J28*H28,IF(I28*L28&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C28,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C28)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I28*L28)*H28,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA28" s="35" t="n">
@@ -15076,13 +15124,13 @@
         <v>600</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F29" s="37" t="n">
         <f aca="false">Initiatives!B17</f>
@@ -15154,7 +15202,7 @@
         <v>25</v>
       </c>
       <c r="X29" s="35" t="n">
-        <f aca="false">IF(E29="Slot",IF(N(G29)&gt;0,ROUNDUP(W29/G29,0)*F29,0),W29*H29)</f>
+        <f aca="false">IF(E29="Slot",IF(N(G29)&gt;0,ROUNDUP(W29/G29,0)*MAX(0,F29),0),W29*H29)</f>
         <v>4162.640625</v>
       </c>
       <c r="Y29" s="35" t="n">
@@ -15162,7 +15210,7 @@
         <v>0</v>
       </c>
       <c r="Z29" s="35" t="n">
-        <f aca="false">IF(AND(D29="Channel",OR(E29="CPC",E29="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C29,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J29*H29),0)</f>
+        <f aca="false">IF(AND(D29="Channel",OR(E29="CPC",E29="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C29,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J29*H29,IF(I29*L29&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C29,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C29)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I29*L29)*H29,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA29" s="35" t="n">
@@ -15210,13 +15258,13 @@
         <v>600</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F30" s="37" t="n">
         <f aca="false">Initiatives!C17</f>
@@ -15288,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="35" t="n">
-        <f aca="false">IF(E30="Slot",IF(N(G30)&gt;0,ROUNDUP(W30/G30,0)*F30,0),W30*H30)</f>
+        <f aca="false">IF(E30="Slot",IF(N(G30)&gt;0,ROUNDUP(W30/G30,0)*MAX(0,F30),0),W30*H30)</f>
         <v>0</v>
       </c>
       <c r="Y30" s="35" t="n">
@@ -15296,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="35" t="n">
-        <f aca="false">IF(AND(D30="Channel",OR(E30="CPC",E30="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C30,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J30*H30),0)</f>
+        <f aca="false">IF(AND(D30="Channel",OR(E30="CPC",E30="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C30,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J30*H30,IF(I30*L30&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C30,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C30)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I30*L30)*H30,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA30" s="35" t="n">
@@ -15344,13 +15392,13 @@
         <v>600</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">Initiatives!D17</f>
@@ -15422,7 +15470,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="35" t="n">
-        <f aca="false">IF(E31="Slot",IF(N(G31)&gt;0,ROUNDUP(W31/G31,0)*F31,0),W31*H31)</f>
+        <f aca="false">IF(E31="Slot",IF(N(G31)&gt;0,ROUNDUP(W31/G31,0)*MAX(0,F31),0),W31*H31)</f>
         <v>0</v>
       </c>
       <c r="Y31" s="35" t="n">
@@ -15430,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="35" t="n">
-        <f aca="false">IF(AND(D31="Channel",OR(E31="CPC",E31="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C31,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J31*H31),0)</f>
+        <f aca="false">IF(AND(D31="Channel",OR(E31="CPC",E31="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C31,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J31*H31,IF(I31*L31&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C31,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C31)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I31*L31)*H31,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA31" s="35" t="n">
@@ -15478,13 +15526,13 @@
         <v>600</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F32" s="37" t="n">
         <f aca="false">Initiatives!E17</f>
@@ -15556,7 +15604,7 @@
         <v>3.21462175852628</v>
       </c>
       <c r="X32" s="35" t="n">
-        <f aca="false">IF(E32="Slot",IF(N(G32)&gt;0,ROUNDUP(W32/G32,0)*F32,0),W32*H32)</f>
+        <f aca="false">IF(E32="Slot",IF(N(G32)&gt;0,ROUNDUP(W32/G32,0)*MAX(0,F32),0),W32*H32)</f>
         <v>445.42</v>
       </c>
       <c r="Y32" s="35" t="n">
@@ -15564,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="35" t="n">
-        <f aca="false">IF(AND(D32="Channel",OR(E32="CPC",E32="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C32,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J32*H32),0)</f>
+        <f aca="false">IF(AND(D32="Channel",OR(E32="CPC",E32="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C32,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J32*H32,IF(I32*L32&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C32,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C32)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I32*L32)*H32,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA32" s="35" t="n">
@@ -15612,13 +15660,13 @@
         <v>605</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F33" s="37" t="n">
         <f aca="false">Initiatives!B27</f>
@@ -15690,7 +15738,7 @@
         <v>300</v>
       </c>
       <c r="X33" s="35" t="n">
-        <f aca="false">IF(E33="Slot",IF(N(G33)&gt;0,ROUNDUP(W33/G33,0)*F33,0),W33*H33)</f>
+        <f aca="false">IF(E33="Slot",IF(N(G33)&gt;0,ROUNDUP(W33/G33,0)*MAX(0,F33),0),W33*H33)</f>
         <v>9000</v>
       </c>
       <c r="Y33" s="35" t="n">
@@ -15698,7 +15746,7 @@
         <v>1200</v>
       </c>
       <c r="Z33" s="35" t="n">
-        <f aca="false">IF(AND(D33="Channel",OR(E33="CPC",E33="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C33,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J33*H33),0)</f>
+        <f aca="false">IF(AND(D33="Channel",OR(E33="CPC",E33="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C33,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J33*H33,IF(I33*L33&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C33,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C33)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I33*L33)*H33,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA33" s="35" t="n">
@@ -15746,13 +15794,13 @@
         <v>607</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>541</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F34" s="37" t="n">
         <f aca="false">Initiatives!B38</f>
@@ -15824,7 +15872,7 @@
         <v>140.785958761165</v>
       </c>
       <c r="X34" s="35" t="n">
-        <f aca="false">IF(E34="Slot",IF(N(G34)&gt;0,ROUNDUP(W34/G34,0)*F34,0),W34*H34)</f>
+        <f aca="false">IF(E34="Slot",IF(N(G34)&gt;0,ROUNDUP(W34/G34,0)*MAX(0,F34),0),W34*H34)</f>
         <v>2745.32619584272</v>
       </c>
       <c r="Y34" s="35" t="n">
@@ -15832,7 +15880,7 @@
         <v>400</v>
       </c>
       <c r="Z34" s="35" t="n">
-        <f aca="false">IF(AND(D34="Channel",OR(E34="CPC",E34="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C34,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J34*H34),0)</f>
+        <f aca="false">IF(AND(D34="Channel",OR(E34="CPC",E34="CPA"),INDEX(Funnel!$B$5:$B$8,MATCH(C34,Funnel!$A$5:$A$8,0))&gt;0),MIN(Assumptions!$D$49,J34*H34,IF(I34*L34&gt;0,INDEX(Funnel!$B$5:$B$8,MATCH(C34,Funnel!$A$5:$A$8,0))/SUMPRODUCT(($C$5:$C$34=C34)*($D$5:$D$34="Channel")*(($E$5:$E$34="CPC")+($E$5:$E$34="CPA")))/(I34*L34)*H34,0)),0)</f>
         <v>0</v>
       </c>
       <c r="AA34" s="35" t="n">
@@ -15874,7 +15922,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J35" s="27" t="n">
         <f aca="false">SUM(J5:J34)</f>
@@ -15945,10 +15993,10 @@
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
       <c r="B38" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>609</v>
@@ -15959,7 +16007,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="23" t="n">
         <f aca="false">Funnel!B5</f>
@@ -15976,7 +16024,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">Funnel!B6</f>
@@ -15993,7 +16041,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">Funnel!B7</f>
@@ -16010,7 +16058,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">Funnel!B8</f>
@@ -16180,7 +16228,7 @@
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>626</v>
@@ -16206,7 +16254,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B21)</f>
@@ -16239,7 +16287,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B22)</f>
@@ -16272,7 +16320,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B23)</f>
@@ -16305,7 +16353,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B24)</f>
@@ -16338,7 +16386,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C25" s="36" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -16377,7 +16425,7 @@
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>585</v>
@@ -16394,7 +16442,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C29" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B29)</f>
@@ -16415,7 +16463,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B30)</f>
@@ -16436,7 +16484,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B31)</f>
@@ -16457,7 +16505,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C32" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B32)</f>
@@ -16478,7 +16526,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C33" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B33)</f>
@@ -16499,7 +16547,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C34" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B34)</f>
@@ -16604,7 +16652,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C39" s="36" t="n">
         <f aca="false">SUM(C29:C38)</f>
@@ -16617,7 +16665,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="str">
-        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(ABS(C39-C9)&lt;1,"✓ ties to planned spend","✗ check: channel totals ≠ planned spend"))</f>
+        <f aca="false">IF(LEFT(Summary!$C$19,1)&lt;&gt;"✓",Summary!$C$19,IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(ABS(C39-C9)&lt;1,"✓ ties to planned spend","✗ check: channel totals ≠ planned spend")))</f>
         <v>✓ ties to planned spend</v>
       </c>
     </row>
@@ -16640,16 +16688,16 @@
         <v>636</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>637</v>
@@ -16942,10 +16990,10 @@
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>643</v>
@@ -19223,7 +19271,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F39" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E39)*F$47</f>
@@ -19244,7 +19292,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F40" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E40)*F$47</f>
@@ -19265,7 +19313,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E41)*F$47</f>
@@ -19286,7 +19334,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F42" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E42)*F$47</f>
@@ -19307,7 +19355,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F43" s="29" t="n">
         <f aca="false">SUM(F39:F42)</f>
@@ -20621,7 +20669,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D15" s="44" t="n">
         <f aca="false">SUM(D4:D14)</f>
@@ -20676,7 +20724,7 @@
         <v>322.142857142857</v>
       </c>
       <c r="S15" s="2" t="str">
-        <f aca="false">IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(AND(F20&gt;0,ABS(E15-1)&gt;0.001),"✗ no spend share falls before the supervisor cut-off (Funnel B20): move weekly shares into weeks 1–5",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan"))))))))</f>
+        <f aca="false">IF(LEFT(Summary!$C$19,1)&lt;&gt;"✓",Summary!$C$19,IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(AND(F20&gt;0,ABS(E15-1)&gt;0.001),"✗ no spend share falls before the supervisor cut-off (Funnel B20): move weekly shares into weeks 1–5",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan")))))))))</f>
         <v>✓ ties to plan</v>
       </c>
       <c r="T15" s="29" t="n">
@@ -20945,7 +20993,7 @@
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>711</v>
@@ -20981,7 +21029,7 @@
         <v>721</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21526,7 +21574,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C54" s="36" t="n">
         <f aca="false">SUM(C44:C53)</f>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -3067,7 +3067,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="8" t="str">
-        <f aca="false">IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1))+((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0))+SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))+(Assumptions!$D$48&lt;0)+(Assumptions!$D$48&gt;=1)+(Assumptions!$D$20&lt;Assumptions!$D$7)+(Assumptions!$D$20&gt;Assumptions!$D$8)=0,"✓ all inputs valid","✗ invalid input: "&amp;IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1))&gt;0,"a share/rate is outside 0–100%; ","")&amp;IF(((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0))&gt;0,"a count, cost or day value is negative; ","")&amp;IF(SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))&gt;0,"a channel input (Assumptions §7) is out of range; ","")&amp;IF(OR(Assumptions!$D$48&lt;0,Assumptions!$D$48&gt;=1),"reserve share must be 0–99%; ","")&amp;IF(OR(Assumptions!$D$20&lt;Assumptions!$D$7,Assumptions!$D$20&gt;Assumptions!$D$8),"last signing date must fall inside the campaign; ",""))</f>
+        <f aca="false">IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))+((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))+SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))+(Assumptions!$D$48&lt;0)+(Assumptions!$D$48&gt;=1)+(Assumptions!$D$20&lt;Assumptions!$D$7)+(Assumptions!$D$20&gt;Assumptions!$D$8)+(Assumptions!$D$8&lt;=Assumptions!$D$7)=0,"✓ all inputs valid","✗ invalid input: "&amp;IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))&gt;0,"a share/rate is outside 0–100%; ","")&amp;IF(((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))&gt;0,"a count, cost or day value is negative; ","")&amp;IF(SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))&gt;0,"a channel input (Assumptions §7) is out of range; ","")&amp;IF(OR(Assumptions!$D$48&lt;0,Assumptions!$D$48&gt;=1),"reserve share must be 0–99%; ","")&amp;IF(OR(Assumptions!$D$20&lt;Assumptions!$D$7,Assumptions!$D$20&gt;Assumptions!$D$8),"last signing date must fall inside the campaign; ","")&amp;IF(Assumptions!$D$8&lt;=Assumptions!$D$7,"campaign end must be after its start; ",""))</f>
         <v>✓ all inputs valid</v>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
         <v/>
       </c>
       <c r="X5" s="2" t="str">
-        <f aca="false">IF(F5=0,"Free – monitor quality",IF(AND(P5&lt;Assumptions!$D$85,Q5&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W5&gt;=Assumptions!$D$89,AND(R5=0,P5&gt;=Assumptions!$D$90,P5/F5&gt;=Assumptions!$D$91),AND(P5&gt;=Assumptions!$D$90,P5/F5&lt;Assumptions!$D$91,Q5&lt;Assumptions!$D$92*P5/D5)),"SWITCH OFF",IF(W5&gt;=Assumptions!$D$88,"CUT 50%",IF(W5&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D5=0,"Free – monitor quality",IF(F5=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P5&lt;Assumptions!$D$85,Q5&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W5&gt;=Assumptions!$D$89,AND(R5=0,P5&gt;=Assumptions!$D$90,P5/F5&gt;=Assumptions!$D$91),AND(P5&gt;=Assumptions!$D$90,P5/F5&lt;Assumptions!$D$91,Q5&lt;Assumptions!$D$92*P5/D5)),"SWITCH OFF",IF(W5&gt;=Assumptions!$D$88,"CUT 50%",IF(W5&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Free – monitor quality</v>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         <v/>
       </c>
       <c r="X6" s="2" t="str">
-        <f aca="false">IF(F6=0,"Free – monitor quality",IF(AND(P6&lt;Assumptions!$D$85,Q6&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W6&gt;=Assumptions!$D$89,AND(R6=0,P6&gt;=Assumptions!$D$90,P6/F6&gt;=Assumptions!$D$91),AND(P6&gt;=Assumptions!$D$90,P6/F6&lt;Assumptions!$D$91,Q6&lt;Assumptions!$D$92*P6/D6)),"SWITCH OFF",IF(W6&gt;=Assumptions!$D$88,"CUT 50%",IF(W6&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D6=0,"Free – monitor quality",IF(F6=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P6&lt;Assumptions!$D$85,Q6&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W6&gt;=Assumptions!$D$89,AND(R6=0,P6&gt;=Assumptions!$D$90,P6/F6&gt;=Assumptions!$D$91),AND(P6&gt;=Assumptions!$D$90,P6/F6&lt;Assumptions!$D$91,Q6&lt;Assumptions!$D$92*P6/D6)),"SWITCH OFF",IF(W6&gt;=Assumptions!$D$88,"CUT 50%",IF(W6&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Free – monitor quality</v>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
         <v/>
       </c>
       <c r="X7" s="2" t="str">
-        <f aca="false">IF(F7=0,"Free – monitor quality",IF(AND(P7&lt;Assumptions!$D$85,Q7&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W7&gt;=Assumptions!$D$89,AND(R7=0,P7&gt;=Assumptions!$D$90,P7/F7&gt;=Assumptions!$D$91),AND(P7&gt;=Assumptions!$D$90,P7/F7&lt;Assumptions!$D$91,Q7&lt;Assumptions!$D$92*P7/D7)),"SWITCH OFF",IF(W7&gt;=Assumptions!$D$88,"CUT 50%",IF(W7&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D7=0,"Free – monitor quality",IF(F7=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P7&lt;Assumptions!$D$85,Q7&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W7&gt;=Assumptions!$D$89,AND(R7=0,P7&gt;=Assumptions!$D$90,P7/F7&gt;=Assumptions!$D$91),AND(P7&gt;=Assumptions!$D$90,P7/F7&lt;Assumptions!$D$91,Q7&lt;Assumptions!$D$92*P7/D7)),"SWITCH OFF",IF(W7&gt;=Assumptions!$D$88,"CUT 50%",IF(W7&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Free – monitor quality</v>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
         <v/>
       </c>
       <c r="X8" s="2" t="str">
-        <f aca="false">IF(F8=0,"Free – monitor quality",IF(AND(P8&lt;Assumptions!$D$85,Q8&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W8&gt;=Assumptions!$D$89,AND(R8=0,P8&gt;=Assumptions!$D$90,P8/F8&gt;=Assumptions!$D$91),AND(P8&gt;=Assumptions!$D$90,P8/F8&lt;Assumptions!$D$91,Q8&lt;Assumptions!$D$92*P8/D8)),"SWITCH OFF",IF(W8&gt;=Assumptions!$D$88,"CUT 50%",IF(W8&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D8=0,"Free – monitor quality",IF(F8=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P8&lt;Assumptions!$D$85,Q8&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W8&gt;=Assumptions!$D$89,AND(R8=0,P8&gt;=Assumptions!$D$90,P8/F8&gt;=Assumptions!$D$91),AND(P8&gt;=Assumptions!$D$90,P8/F8&lt;Assumptions!$D$91,Q8&lt;Assumptions!$D$92*P8/D8)),"SWITCH OFF",IF(W8&gt;=Assumptions!$D$88,"CUT 50%",IF(W8&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Free – monitor quality</v>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="2" t="str">
-        <f aca="false">IF(F9=0,"Free – monitor quality",IF(AND(P9&lt;Assumptions!$D$85,Q9&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W9&gt;=Assumptions!$D$89,AND(R9=0,P9&gt;=Assumptions!$D$90,P9/F9&gt;=Assumptions!$D$91),AND(P9&gt;=Assumptions!$D$90,P9/F9&lt;Assumptions!$D$91,Q9&lt;Assumptions!$D$92*P9/D9)),"SWITCH OFF",IF(W9&gt;=Assumptions!$D$88,"CUT 50%",IF(W9&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D9=0,"Free – monitor quality",IF(F9=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P9&lt;Assumptions!$D$85,Q9&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W9&gt;=Assumptions!$D$89,AND(R9=0,P9&gt;=Assumptions!$D$90,P9/F9&gt;=Assumptions!$D$91),AND(P9&gt;=Assumptions!$D$90,P9/F9&lt;Assumptions!$D$91,Q9&lt;Assumptions!$D$92*P9/D9)),"SWITCH OFF",IF(W9&gt;=Assumptions!$D$88,"CUT 50%",IF(W9&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="2" t="str">
-        <f aca="false">IF(F10=0,"Free – monitor quality",IF(AND(P10&lt;Assumptions!$D$85,Q10&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W10&gt;=Assumptions!$D$89,AND(R10=0,P10&gt;=Assumptions!$D$90,P10/F10&gt;=Assumptions!$D$91),AND(P10&gt;=Assumptions!$D$90,P10/F10&lt;Assumptions!$D$91,Q10&lt;Assumptions!$D$92*P10/D10)),"SWITCH OFF",IF(W10&gt;=Assumptions!$D$88,"CUT 50%",IF(W10&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D10=0,"Free – monitor quality",IF(F10=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P10&lt;Assumptions!$D$85,Q10&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W10&gt;=Assumptions!$D$89,AND(R10=0,P10&gt;=Assumptions!$D$90,P10/F10&gt;=Assumptions!$D$91),AND(P10&gt;=Assumptions!$D$90,P10/F10&lt;Assumptions!$D$91,Q10&lt;Assumptions!$D$92*P10/D10)),"SWITCH OFF",IF(W10&gt;=Assumptions!$D$88,"CUT 50%",IF(W10&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
         <v>1</v>
       </c>
       <c r="X11" s="2" t="str">
-        <f aca="false">IF(F11=0,"Free – monitor quality",IF(AND(P11&lt;Assumptions!$D$85,Q11&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W11&gt;=Assumptions!$D$89,AND(R11=0,P11&gt;=Assumptions!$D$90,P11/F11&gt;=Assumptions!$D$91),AND(P11&gt;=Assumptions!$D$90,P11/F11&lt;Assumptions!$D$91,Q11&lt;Assumptions!$D$92*P11/D11)),"SWITCH OFF",IF(W11&gt;=Assumptions!$D$88,"CUT 50%",IF(W11&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D11=0,"Free – monitor quality",IF(F11=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P11&lt;Assumptions!$D$85,Q11&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W11&gt;=Assumptions!$D$89,AND(R11=0,P11&gt;=Assumptions!$D$90,P11/F11&gt;=Assumptions!$D$91),AND(P11&gt;=Assumptions!$D$90,P11/F11&lt;Assumptions!$D$91,Q11&lt;Assumptions!$D$92*P11/D11)),"SWITCH OFF",IF(W11&gt;=Assumptions!$D$88,"CUT 50%",IF(W11&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="X12" s="2" t="str">
-        <f aca="false">IF(F12=0,"Free – monitor quality",IF(AND(P12&lt;Assumptions!$D$85,Q12&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W12&gt;=Assumptions!$D$89,AND(R12=0,P12&gt;=Assumptions!$D$90,P12/F12&gt;=Assumptions!$D$91),AND(P12&gt;=Assumptions!$D$90,P12/F12&lt;Assumptions!$D$91,Q12&lt;Assumptions!$D$92*P12/D12)),"SWITCH OFF",IF(W12&gt;=Assumptions!$D$88,"CUT 50%",IF(W12&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D12=0,"Free – monitor quality",IF(F12=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P12&lt;Assumptions!$D$85,Q12&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W12&gt;=Assumptions!$D$89,AND(R12=0,P12&gt;=Assumptions!$D$90,P12/F12&gt;=Assumptions!$D$91),AND(P12&gt;=Assumptions!$D$90,P12/F12&lt;Assumptions!$D$91,Q12&lt;Assumptions!$D$92*P12/D12)),"SWITCH OFF",IF(W12&gt;=Assumptions!$D$88,"CUT 50%",IF(W12&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="X13" s="2" t="str">
-        <f aca="false">IF(F13=0,"Free – monitor quality",IF(AND(P13&lt;Assumptions!$D$85,Q13&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W13&gt;=Assumptions!$D$89,AND(R13=0,P13&gt;=Assumptions!$D$90,P13/F13&gt;=Assumptions!$D$91),AND(P13&gt;=Assumptions!$D$90,P13/F13&lt;Assumptions!$D$91,Q13&lt;Assumptions!$D$92*P13/D13)),"SWITCH OFF",IF(W13&gt;=Assumptions!$D$88,"CUT 50%",IF(W13&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D13=0,"Free – monitor quality",IF(F13=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P13&lt;Assumptions!$D$85,Q13&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W13&gt;=Assumptions!$D$89,AND(R13=0,P13&gt;=Assumptions!$D$90,P13/F13&gt;=Assumptions!$D$91),AND(P13&gt;=Assumptions!$D$90,P13/F13&lt;Assumptions!$D$91,Q13&lt;Assumptions!$D$92*P13/D13)),"SWITCH OFF",IF(W13&gt;=Assumptions!$D$88,"CUT 50%",IF(W13&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="2" t="str">
-        <f aca="false">IF(F14=0,"Free – monitor quality",IF(AND(P14&lt;Assumptions!$D$85,Q14&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W14&gt;=Assumptions!$D$89,AND(R14=0,P14&gt;=Assumptions!$D$90,P14/F14&gt;=Assumptions!$D$91),AND(P14&gt;=Assumptions!$D$90,P14/F14&lt;Assumptions!$D$91,Q14&lt;Assumptions!$D$92*P14/D14)),"SWITCH OFF",IF(W14&gt;=Assumptions!$D$88,"CUT 50%",IF(W14&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D14=0,"Free – monitor quality",IF(F14=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P14&lt;Assumptions!$D$85,Q14&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W14&gt;=Assumptions!$D$89,AND(R14=0,P14&gt;=Assumptions!$D$90,P14/F14&gt;=Assumptions!$D$91),AND(P14&gt;=Assumptions!$D$90,P14/F14&lt;Assumptions!$D$91,Q14&lt;Assumptions!$D$92*P14/D14)),"SWITCH OFF",IF(W14&gt;=Assumptions!$D$88,"CUT 50%",IF(W14&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="X15" s="2" t="str">
-        <f aca="false">IF(F15=0,"Free – monitor quality",IF(AND(P15&lt;Assumptions!$D$85,Q15&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W15&gt;=Assumptions!$D$89,AND(R15=0,P15&gt;=Assumptions!$D$90,P15/F15&gt;=Assumptions!$D$91),AND(P15&gt;=Assumptions!$D$90,P15/F15&lt;Assumptions!$D$91,Q15&lt;Assumptions!$D$92*P15/D15)),"SWITCH OFF",IF(W15&gt;=Assumptions!$D$88,"CUT 50%",IF(W15&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D15=0,"Free – monitor quality",IF(F15=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P15&lt;Assumptions!$D$85,Q15&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W15&gt;=Assumptions!$D$89,AND(R15=0,P15&gt;=Assumptions!$D$90,P15/F15&gt;=Assumptions!$D$91),AND(P15&gt;=Assumptions!$D$90,P15/F15&lt;Assumptions!$D$91,Q15&lt;Assumptions!$D$92*P15/D15)),"SWITCH OFF",IF(W15&gt;=Assumptions!$D$88,"CUT 50%",IF(W15&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="X16" s="2" t="str">
-        <f aca="false">IF(F16=0,"Free – monitor quality",IF(AND(P16&lt;Assumptions!$D$85,Q16&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W16&gt;=Assumptions!$D$89,AND(R16=0,P16&gt;=Assumptions!$D$90,P16/F16&gt;=Assumptions!$D$91),AND(P16&gt;=Assumptions!$D$90,P16/F16&lt;Assumptions!$D$91,Q16&lt;Assumptions!$D$92*P16/D16)),"SWITCH OFF",IF(W16&gt;=Assumptions!$D$88,"CUT 50%",IF(W16&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D16=0,"Free – monitor quality",IF(F16=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P16&lt;Assumptions!$D$85,Q16&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W16&gt;=Assumptions!$D$89,AND(R16=0,P16&gt;=Assumptions!$D$90,P16/F16&gt;=Assumptions!$D$91),AND(P16&gt;=Assumptions!$D$90,P16/F16&lt;Assumptions!$D$91,Q16&lt;Assumptions!$D$92*P16/D16)),"SWITCH OFF",IF(W16&gt;=Assumptions!$D$88,"CUT 50%",IF(W16&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="X17" s="2" t="str">
-        <f aca="false">IF(F17=0,"Free – monitor quality",IF(AND(P17&lt;Assumptions!$D$85,Q17&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W17&gt;=Assumptions!$D$89,AND(R17=0,P17&gt;=Assumptions!$D$90,P17/F17&gt;=Assumptions!$D$91),AND(P17&gt;=Assumptions!$D$90,P17/F17&lt;Assumptions!$D$91,Q17&lt;Assumptions!$D$92*P17/D17)),"SWITCH OFF",IF(W17&gt;=Assumptions!$D$88,"CUT 50%",IF(W17&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D17=0,"Free – monitor quality",IF(F17=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P17&lt;Assumptions!$D$85,Q17&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W17&gt;=Assumptions!$D$89,AND(R17=0,P17&gt;=Assumptions!$D$90,P17/F17&gt;=Assumptions!$D$91),AND(P17&gt;=Assumptions!$D$90,P17/F17&lt;Assumptions!$D$91,Q17&lt;Assumptions!$D$92*P17/D17)),"SWITCH OFF",IF(W17&gt;=Assumptions!$D$88,"CUT 50%",IF(W17&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="X18" s="2" t="str">
-        <f aca="false">IF(F18=0,"Free – monitor quality",IF(AND(P18&lt;Assumptions!$D$85,Q18&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W18&gt;=Assumptions!$D$89,AND(R18=0,P18&gt;=Assumptions!$D$90,P18/F18&gt;=Assumptions!$D$91),AND(P18&gt;=Assumptions!$D$90,P18/F18&lt;Assumptions!$D$91,Q18&lt;Assumptions!$D$92*P18/D18)),"SWITCH OFF",IF(W18&gt;=Assumptions!$D$88,"CUT 50%",IF(W18&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D18=0,"Free – monitor quality",IF(F18=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P18&lt;Assumptions!$D$85,Q18&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W18&gt;=Assumptions!$D$89,AND(R18=0,P18&gt;=Assumptions!$D$90,P18/F18&gt;=Assumptions!$D$91),AND(P18&gt;=Assumptions!$D$90,P18/F18&lt;Assumptions!$D$91,Q18&lt;Assumptions!$D$92*P18/D18)),"SWITCH OFF",IF(W18&gt;=Assumptions!$D$88,"CUT 50%",IF(W18&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="X19" s="2" t="str">
-        <f aca="false">IF(F19=0,"Free – monitor quality",IF(AND(P19&lt;Assumptions!$D$85,Q19&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W19&gt;=Assumptions!$D$89,AND(R19=0,P19&gt;=Assumptions!$D$90,P19/F19&gt;=Assumptions!$D$91),AND(P19&gt;=Assumptions!$D$90,P19/F19&lt;Assumptions!$D$91,Q19&lt;Assumptions!$D$92*P19/D19)),"SWITCH OFF",IF(W19&gt;=Assumptions!$D$88,"CUT 50%",IF(W19&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D19=0,"Free – monitor quality",IF(F19=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P19&lt;Assumptions!$D$85,Q19&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W19&gt;=Assumptions!$D$89,AND(R19=0,P19&gt;=Assumptions!$D$90,P19/F19&gt;=Assumptions!$D$91),AND(P19&gt;=Assumptions!$D$90,P19/F19&lt;Assumptions!$D$91,Q19&lt;Assumptions!$D$92*P19/D19)),"SWITCH OFF",IF(W19&gt;=Assumptions!$D$88,"CUT 50%",IF(W19&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
         <v>1</v>
       </c>
       <c r="X20" s="2" t="str">
-        <f aca="false">IF(F20=0,"Free – monitor quality",IF(AND(P20&lt;Assumptions!$D$85,Q20&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W20&gt;=Assumptions!$D$89,AND(R20=0,P20&gt;=Assumptions!$D$90,P20/F20&gt;=Assumptions!$D$91),AND(P20&gt;=Assumptions!$D$90,P20/F20&lt;Assumptions!$D$91,Q20&lt;Assumptions!$D$92*P20/D20)),"SWITCH OFF",IF(W20&gt;=Assumptions!$D$88,"CUT 50%",IF(W20&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D20=0,"Free – monitor quality",IF(F20=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P20&lt;Assumptions!$D$85,Q20&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W20&gt;=Assumptions!$D$89,AND(R20=0,P20&gt;=Assumptions!$D$90,P20/F20&gt;=Assumptions!$D$91),AND(P20&gt;=Assumptions!$D$90,P20/F20&lt;Assumptions!$D$91,Q20&lt;Assumptions!$D$92*P20/D20)),"SWITCH OFF",IF(W20&gt;=Assumptions!$D$88,"CUT 50%",IF(W20&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="X21" s="2" t="str">
-        <f aca="false">IF(F21=0,"Free – monitor quality",IF(AND(P21&lt;Assumptions!$D$85,Q21&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W21&gt;=Assumptions!$D$89,AND(R21=0,P21&gt;=Assumptions!$D$90,P21/F21&gt;=Assumptions!$D$91),AND(P21&gt;=Assumptions!$D$90,P21/F21&lt;Assumptions!$D$91,Q21&lt;Assumptions!$D$92*P21/D21)),"SWITCH OFF",IF(W21&gt;=Assumptions!$D$88,"CUT 50%",IF(W21&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D21=0,"Free – monitor quality",IF(F21=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P21&lt;Assumptions!$D$85,Q21&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W21&gt;=Assumptions!$D$89,AND(R21=0,P21&gt;=Assumptions!$D$90,P21/F21&gt;=Assumptions!$D$91),AND(P21&gt;=Assumptions!$D$90,P21/F21&lt;Assumptions!$D$91,Q21&lt;Assumptions!$D$92*P21/D21)),"SWITCH OFF",IF(W21&gt;=Assumptions!$D$88,"CUT 50%",IF(W21&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="X22" s="2" t="str">
-        <f aca="false">IF(F22=0,"Free – monitor quality",IF(AND(P22&lt;Assumptions!$D$85,Q22&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W22&gt;=Assumptions!$D$89,AND(R22=0,P22&gt;=Assumptions!$D$90,P22/F22&gt;=Assumptions!$D$91),AND(P22&gt;=Assumptions!$D$90,P22/F22&lt;Assumptions!$D$91,Q22&lt;Assumptions!$D$92*P22/D22)),"SWITCH OFF",IF(W22&gt;=Assumptions!$D$88,"CUT 50%",IF(W22&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D22=0,"Free – monitor quality",IF(F22=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P22&lt;Assumptions!$D$85,Q22&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W22&gt;=Assumptions!$D$89,AND(R22=0,P22&gt;=Assumptions!$D$90,P22/F22&gt;=Assumptions!$D$91),AND(P22&gt;=Assumptions!$D$90,P22/F22&lt;Assumptions!$D$91,Q22&lt;Assumptions!$D$92*P22/D22)),"SWITCH OFF",IF(W22&gt;=Assumptions!$D$88,"CUT 50%",IF(W22&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="X23" s="2" t="str">
-        <f aca="false">IF(F23=0,"Free – monitor quality",IF(AND(P23&lt;Assumptions!$D$85,Q23&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W23&gt;=Assumptions!$D$89,AND(R23=0,P23&gt;=Assumptions!$D$90,P23/F23&gt;=Assumptions!$D$91),AND(P23&gt;=Assumptions!$D$90,P23/F23&lt;Assumptions!$D$91,Q23&lt;Assumptions!$D$92*P23/D23)),"SWITCH OFF",IF(W23&gt;=Assumptions!$D$88,"CUT 50%",IF(W23&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D23=0,"Free – monitor quality",IF(F23=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P23&lt;Assumptions!$D$85,Q23&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W23&gt;=Assumptions!$D$89,AND(R23=0,P23&gt;=Assumptions!$D$90,P23/F23&gt;=Assumptions!$D$91),AND(P23&gt;=Assumptions!$D$90,P23/F23&lt;Assumptions!$D$91,Q23&lt;Assumptions!$D$92*P23/D23)),"SWITCH OFF",IF(W23&gt;=Assumptions!$D$88,"CUT 50%",IF(W23&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="2" t="str">
-        <f aca="false">IF(F24=0,"Free – monitor quality",IF(AND(P24&lt;Assumptions!$D$85,Q24&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W24&gt;=Assumptions!$D$89,AND(R24=0,P24&gt;=Assumptions!$D$90,P24/F24&gt;=Assumptions!$D$91),AND(P24&gt;=Assumptions!$D$90,P24/F24&lt;Assumptions!$D$91,Q24&lt;Assumptions!$D$92*P24/D24)),"SWITCH OFF",IF(W24&gt;=Assumptions!$D$88,"CUT 50%",IF(W24&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D24=0,"Free – monitor quality",IF(F24=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P24&lt;Assumptions!$D$85,Q24&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W24&gt;=Assumptions!$D$89,AND(R24=0,P24&gt;=Assumptions!$D$90,P24/F24&gt;=Assumptions!$D$91),AND(P24&gt;=Assumptions!$D$90,P24/F24&lt;Assumptions!$D$91,Q24&lt;Assumptions!$D$92*P24/D24)),"SWITCH OFF",IF(W24&gt;=Assumptions!$D$88,"CUT 50%",IF(W24&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
         <v>1</v>
       </c>
       <c r="X25" s="2" t="str">
-        <f aca="false">IF(F25=0,"Free – monitor quality",IF(AND(P25&lt;Assumptions!$D$85,Q25&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W25&gt;=Assumptions!$D$89,AND(R25=0,P25&gt;=Assumptions!$D$90,P25/F25&gt;=Assumptions!$D$91),AND(P25&gt;=Assumptions!$D$90,P25/F25&lt;Assumptions!$D$91,Q25&lt;Assumptions!$D$92*P25/D25)),"SWITCH OFF",IF(W25&gt;=Assumptions!$D$88,"CUT 50%",IF(W25&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D25=0,"Free – monitor quality",IF(F25=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P25&lt;Assumptions!$D$85,Q25&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W25&gt;=Assumptions!$D$89,AND(R25=0,P25&gt;=Assumptions!$D$90,P25/F25&gt;=Assumptions!$D$91),AND(P25&gt;=Assumptions!$D$90,P25/F25&lt;Assumptions!$D$91,Q25&lt;Assumptions!$D$92*P25/D25)),"SWITCH OFF",IF(W25&gt;=Assumptions!$D$88,"CUT 50%",IF(W25&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="X26" s="2" t="str">
-        <f aca="false">IF(F26=0,"Free – monitor quality",IF(AND(P26&lt;Assumptions!$D$85,Q26&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W26&gt;=Assumptions!$D$89,AND(R26=0,P26&gt;=Assumptions!$D$90,P26/F26&gt;=Assumptions!$D$91),AND(P26&gt;=Assumptions!$D$90,P26/F26&lt;Assumptions!$D$91,Q26&lt;Assumptions!$D$92*P26/D26)),"SWITCH OFF",IF(W26&gt;=Assumptions!$D$88,"CUT 50%",IF(W26&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D26=0,"Free – monitor quality",IF(F26=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P26&lt;Assumptions!$D$85,Q26&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W26&gt;=Assumptions!$D$89,AND(R26=0,P26&gt;=Assumptions!$D$90,P26/F26&gt;=Assumptions!$D$91),AND(P26&gt;=Assumptions!$D$90,P26/F26&lt;Assumptions!$D$91,Q26&lt;Assumptions!$D$92*P26/D26)),"SWITCH OFF",IF(W26&gt;=Assumptions!$D$88,"CUT 50%",IF(W26&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="X27" s="2" t="str">
-        <f aca="false">IF(F27=0,"Free – monitor quality",IF(AND(P27&lt;Assumptions!$D$85,Q27&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W27&gt;=Assumptions!$D$89,AND(R27=0,P27&gt;=Assumptions!$D$90,P27/F27&gt;=Assumptions!$D$91),AND(P27&gt;=Assumptions!$D$90,P27/F27&lt;Assumptions!$D$91,Q27&lt;Assumptions!$D$92*P27/D27)),"SWITCH OFF",IF(W27&gt;=Assumptions!$D$88,"CUT 50%",IF(W27&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D27=0,"Free – monitor quality",IF(F27=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P27&lt;Assumptions!$D$85,Q27&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W27&gt;=Assumptions!$D$89,AND(R27=0,P27&gt;=Assumptions!$D$90,P27/F27&gt;=Assumptions!$D$91),AND(P27&gt;=Assumptions!$D$90,P27/F27&lt;Assumptions!$D$91,Q27&lt;Assumptions!$D$92*P27/D27)),"SWITCH OFF",IF(W27&gt;=Assumptions!$D$88,"CUT 50%",IF(W27&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="X28" s="2" t="str">
-        <f aca="false">IF(F28=0,"Free – monitor quality",IF(AND(P28&lt;Assumptions!$D$85,Q28&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W28&gt;=Assumptions!$D$89,AND(R28=0,P28&gt;=Assumptions!$D$90,P28/F28&gt;=Assumptions!$D$91),AND(P28&gt;=Assumptions!$D$90,P28/F28&lt;Assumptions!$D$91,Q28&lt;Assumptions!$D$92*P28/D28)),"SWITCH OFF",IF(W28&gt;=Assumptions!$D$88,"CUT 50%",IF(W28&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D28=0,"Free – monitor quality",IF(F28=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P28&lt;Assumptions!$D$85,Q28&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W28&gt;=Assumptions!$D$89,AND(R28=0,P28&gt;=Assumptions!$D$90,P28/F28&gt;=Assumptions!$D$91),AND(P28&gt;=Assumptions!$D$90,P28/F28&lt;Assumptions!$D$91,Q28&lt;Assumptions!$D$92*P28/D28)),"SWITCH OFF",IF(W28&gt;=Assumptions!$D$88,"CUT 50%",IF(W28&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="X29" s="2" t="str">
-        <f aca="false">IF(F29=0,"Free – monitor quality",IF(AND(P29&lt;Assumptions!$D$85,Q29&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W29&gt;=Assumptions!$D$89,AND(R29=0,P29&gt;=Assumptions!$D$90,P29/F29&gt;=Assumptions!$D$91),AND(P29&gt;=Assumptions!$D$90,P29/F29&lt;Assumptions!$D$91,Q29&lt;Assumptions!$D$92*P29/D29)),"SWITCH OFF",IF(W29&gt;=Assumptions!$D$88,"CUT 50%",IF(W29&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D29=0,"Free – monitor quality",IF(F29=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P29&lt;Assumptions!$D$85,Q29&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W29&gt;=Assumptions!$D$89,AND(R29=0,P29&gt;=Assumptions!$D$90,P29/F29&gt;=Assumptions!$D$91),AND(P29&gt;=Assumptions!$D$90,P29/F29&lt;Assumptions!$D$91,Q29&lt;Assumptions!$D$92*P29/D29)),"SWITCH OFF",IF(W29&gt;=Assumptions!$D$88,"CUT 50%",IF(W29&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="X30" s="2" t="str">
-        <f aca="false">IF(F30=0,"Free – monitor quality",IF(AND(P30&lt;Assumptions!$D$85,Q30&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W30&gt;=Assumptions!$D$89,AND(R30=0,P30&gt;=Assumptions!$D$90,P30/F30&gt;=Assumptions!$D$91),AND(P30&gt;=Assumptions!$D$90,P30/F30&lt;Assumptions!$D$91,Q30&lt;Assumptions!$D$92*P30/D30)),"SWITCH OFF",IF(W30&gt;=Assumptions!$D$88,"CUT 50%",IF(W30&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D30=0,"Free – monitor quality",IF(F30=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P30&lt;Assumptions!$D$85,Q30&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W30&gt;=Assumptions!$D$89,AND(R30=0,P30&gt;=Assumptions!$D$90,P30/F30&gt;=Assumptions!$D$91),AND(P30&gt;=Assumptions!$D$90,P30/F30&lt;Assumptions!$D$91,Q30&lt;Assumptions!$D$92*P30/D30)),"SWITCH OFF",IF(W30&gt;=Assumptions!$D$88,"CUT 50%",IF(W30&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="X31" s="2" t="str">
-        <f aca="false">IF(F31=0,"Free – monitor quality",IF(AND(P31&lt;Assumptions!$D$85,Q31&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W31&gt;=Assumptions!$D$89,AND(R31=0,P31&gt;=Assumptions!$D$90,P31/F31&gt;=Assumptions!$D$91),AND(P31&gt;=Assumptions!$D$90,P31/F31&lt;Assumptions!$D$91,Q31&lt;Assumptions!$D$92*P31/D31)),"SWITCH OFF",IF(W31&gt;=Assumptions!$D$88,"CUT 50%",IF(W31&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D31=0,"Free – monitor quality",IF(F31=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P31&lt;Assumptions!$D$85,Q31&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W31&gt;=Assumptions!$D$89,AND(R31=0,P31&gt;=Assumptions!$D$90,P31/F31&gt;=Assumptions!$D$91),AND(P31&gt;=Assumptions!$D$90,P31/F31&lt;Assumptions!$D$91,Q31&lt;Assumptions!$D$92*P31/D31)),"SWITCH OFF",IF(W31&gt;=Assumptions!$D$88,"CUT 50%",IF(W31&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="X32" s="2" t="str">
-        <f aca="false">IF(F32=0,"Free – monitor quality",IF(AND(P32&lt;Assumptions!$D$85,Q32&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W32&gt;=Assumptions!$D$89,AND(R32=0,P32&gt;=Assumptions!$D$90,P32/F32&gt;=Assumptions!$D$91),AND(P32&gt;=Assumptions!$D$90,P32/F32&lt;Assumptions!$D$91,Q32&lt;Assumptions!$D$92*P32/D32)),"SWITCH OFF",IF(W32&gt;=Assumptions!$D$88,"CUT 50%",IF(W32&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D32=0,"Free – monitor quality",IF(F32=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P32&lt;Assumptions!$D$85,Q32&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W32&gt;=Assumptions!$D$89,AND(R32=0,P32&gt;=Assumptions!$D$90,P32/F32&gt;=Assumptions!$D$91),AND(P32&gt;=Assumptions!$D$90,P32/F32&lt;Assumptions!$D$91,Q32&lt;Assumptions!$D$92*P32/D32)),"SWITCH OFF",IF(W32&gt;=Assumptions!$D$88,"CUT 50%",IF(W32&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -5259,7 +5259,7 @@
         <v>1</v>
       </c>
       <c r="X33" s="2" t="str">
-        <f aca="false">IF(F33=0,"Free – monitor quality",IF(AND(P33&lt;Assumptions!$D$85,Q33&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W33&gt;=Assumptions!$D$89,AND(R33=0,P33&gt;=Assumptions!$D$90,P33/F33&gt;=Assumptions!$D$91),AND(P33&gt;=Assumptions!$D$90,P33/F33&lt;Assumptions!$D$91,Q33&lt;Assumptions!$D$92*P33/D33)),"SWITCH OFF",IF(W33&gt;=Assumptions!$D$88,"CUT 50%",IF(W33&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D33=0,"Free – monitor quality",IF(F33=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P33&lt;Assumptions!$D$85,Q33&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W33&gt;=Assumptions!$D$89,AND(R33=0,P33&gt;=Assumptions!$D$90,P33/F33&gt;=Assumptions!$D$91),AND(P33&gt;=Assumptions!$D$90,P33/F33&lt;Assumptions!$D$91,Q33&lt;Assumptions!$D$92*P33/D33)),"SWITCH OFF",IF(W33&gt;=Assumptions!$D$88,"CUT 50%",IF(W33&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="X34" s="2" t="str">
-        <f aca="false">IF(F34=0,"Free – monitor quality",IF(AND(P34&lt;Assumptions!$D$85,Q34&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W34&gt;=Assumptions!$D$89,AND(R34=0,P34&gt;=Assumptions!$D$90,P34/F34&gt;=Assumptions!$D$91),AND(P34&gt;=Assumptions!$D$90,P34/F34&lt;Assumptions!$D$91,Q34&lt;Assumptions!$D$92*P34/D34)),"SWITCH OFF",IF(W34&gt;=Assumptions!$D$88,"CUT 50%",IF(W34&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD")))))</f>
+        <f aca="false">IF(D34=0,"Free – monitor quality",IF(F34=0,"SWITCH OFF – plan expects no qualified applicants",IF(AND(P34&lt;Assumptions!$D$85,Q34&lt;Assumptions!$D$86),"Wait – too little data",IF(OR(W34&gt;=Assumptions!$D$89,AND(R34=0,P34&gt;=Assumptions!$D$90,P34/F34&gt;=Assumptions!$D$91),AND(P34&gt;=Assumptions!$D$90,P34/F34&lt;Assumptions!$D$91,Q34&lt;Assumptions!$D$92*P34/D34)),"SWITCH OFF",IF(W34&gt;=Assumptions!$D$88,"CUT 50%",IF(W34&lt;=Assumptions!$D$87,"ADD +"&amp;TEXT(Assumptions!$D$100,"0%")&amp;" (if slots free)","HOLD"))))))</f>
         <v>Wait – too little data</v>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
         <v>322.142857142857</v>
       </c>
       <c r="S15" s="2" t="str">
-        <f aca="false">IF(LEFT(Summary!$C$19,1)&lt;&gt;"✓",Summary!$C$19,IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(AND(F20&gt;0,ABS(E15-1)&gt;0.001),"✗ no spend share falls before the supervisor cut-off (Funnel B20): move weekly shares into weeks 1–5",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan")))))))))</f>
+        <f aca="false">IF(LEFT(Summary!$C$19,1)&lt;&gt;"✓",Summary!$C$19,IF(Assumptions!$D$48&gt;=1,"✗ reserve share must be below 100%",IF(Funnel!B19&lt;Assumptions!$D$7,"✗ no application can sign by the deadline (Funnel B19 is before the campaign starts)",IF(AND(Budget!G24&gt;0,Funnel!B20&lt;Assumptions!$D$7),"✗ supervisors cannot apply in time (Funnel B20 is before the campaign starts)",IF(Funnel!B13&gt;Funnel!B17,"✗ assessments start (Funnel B13) after the last useful assessment day (Funnel B17): no hire can sign in time",IF(SUMPRODUCT(($B$4:$B$14&gt;Funnel!$B$19)*$D$4:$D$14)&gt;0.0001,"✗ a spend share falls after the last useful application (Funnel B19): move shares into weeks 1–6",IF(OR(ABS(D15-1)&gt;0.001,ABS(Y15-1)&gt;0.001),"✗ shares must sum to 100%",IF(AND(F20&gt;0,ABS(E15-1)&gt;0.001),"✗ no spend share falls before the supervisor cut-off (Funnel B20): move weekly shares into weeks 1–5",IF(ABS(M15-Budget!C9)&gt;1,"✗ weeks ≠ planned spend",IF(ABS(P15-Funnel!O9)&gt;0.5,"✗ qualified ≠ plan",IF(ABS(V15-Budget!C13)&gt;0.5,"✗ signatures ≠ expected hires","✓ ties to plan")))))))))))</f>
         <v>✓ ties to plan</v>
       </c>
       <c r="T15" s="29" t="n">

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="761">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">Input checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan / schedule check (Weekly S15)</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs: Assumptions (all inputs + labels) → Funnel (Part 1) → Pool (sanity) → Channels (Part 2.2–2.3) → Initiatives (Part 3) → Budget (Part 2.4–2.5) → Scenarios → Weekly → Tracker (Part 4, live round).</t>
@@ -2908,7 +2911,7 @@
     <tabColor rgb="FF1F3864"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G22"/>
+  <dimension ref="B1:G23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -3067,31 +3070,40 @@
         <v>16</v>
       </c>
       <c r="C19" s="8" t="str">
-        <f aca="false">IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))+((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))+SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))+(Assumptions!$D$48&lt;0)+(Assumptions!$D$48&gt;=1)+(Assumptions!$D$20&lt;Assumptions!$D$7)+(Assumptions!$D$20&gt;Assumptions!$D$8)+(Assumptions!$D$8&lt;=Assumptions!$D$7)=0,"✓ all inputs valid","✗ invalid input: "&amp;IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))&gt;0,"a share/rate is outside 0–100%; ","")&amp;IF(((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))&gt;0,"a count, cost or day value is negative; ","")&amp;IF(SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))&gt;0,"a channel input (Assumptions §7) is out of range; ","")&amp;IF(OR(Assumptions!$D$48&lt;0,Assumptions!$D$48&gt;=1),"reserve share must be 0–99%; ","")&amp;IF(OR(Assumptions!$D$20&lt;Assumptions!$D$7,Assumptions!$D$20&gt;Assumptions!$D$8),"last signing date must fall inside the campaign; ","")&amp;IF(Assumptions!$D$8&lt;=Assumptions!$D$7,"campaign end must be after its start; ",""))</f>
+        <f aca="false">IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))+((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))+SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))+(Assumptions!$D$48&lt;0)+(Assumptions!$D$48&gt;=1)+(Assumptions!$D$20&lt;Assumptions!$D$7)+(Assumptions!$D$20&gt;Assumptions!$D$8)+(Assumptions!$D$8&lt;=Assumptions!$D$7)+(Assumptions!$D$95&gt;=Assumptions!$D$93)+(Assumptions!$D$96&lt;Assumptions!$D$94)=0,"✓ all inputs valid","✗ invalid input: "&amp;IF(((Assumptions!$D$10&lt;0)+(Assumptions!$D$10&gt;1)+(Assumptions!$D$54&lt;0)+(Assumptions!$D$54&gt;1)+(Assumptions!$D$50&lt;0)+(Assumptions!$D$50&gt;1)+(Assumptions!$D$52&lt;0)+(Assumptions!$D$52&gt;1)+(Assumptions!$D$53&lt;0)+(Assumptions!$D$53&gt;1)+(Assumptions!$D$66&lt;0)+(Assumptions!$D$66&gt;1)+(Assumptions!$D$139&lt;0)+(Assumptions!$D$139&gt;1)+(Assumptions!$D$140&lt;0)+(Assumptions!$D$140&gt;1)+(Assumptions!$D$145&lt;0)+(Assumptions!$D$145&gt;1)+(Assumptions!$D$150&lt;0)+(Assumptions!$D$150&gt;1)+(Assumptions!$D$152&lt;0)+(Assumptions!$D$152&gt;1)+(Assumptions!$D$156&lt;0)+(Assumptions!$D$156&gt;1)+(Assumptions!$D$97&lt;0)+(Assumptions!$D$97&gt;1)+(Assumptions!$D$98&lt;0)+(Assumptions!$D$98&gt;1)+(Assumptions!$D$99&lt;0)+(Assumptions!$D$99&gt;1)+(Assumptions!$D$93&lt;0)+(Assumptions!$D$93&gt;1)+(Assumptions!$D$95&lt;0)+(Assumptions!$D$95&gt;1)+(Assumptions!$D$92&lt;0)+(Assumptions!$D$92&gt;1)+(Assumptions!$D$29&lt;0)+(Assumptions!$D$29&gt;1)+(Assumptions!$D$30&lt;0)+(Assumptions!$D$30&gt;1)+(Assumptions!$D$31&lt;0)+(Assumptions!$D$31&gt;1)+(Assumptions!$D$32&lt;0)+(Assumptions!$D$32&gt;1)+(Assumptions!$D$33&lt;0)+(Assumptions!$D$33&gt;1)+(Assumptions!$D$34&lt;0)+(Assumptions!$D$34&gt;1)+(Assumptions!$D$35&lt;0)+(Assumptions!$D$35&gt;1)+(Assumptions!$D$36&lt;0)+(Assumptions!$D$36&gt;1)+(Assumptions!$D$37&lt;0)+(Assumptions!$D$37&gt;1)+(Assumptions!$D$38&lt;0)+(Assumptions!$D$38&gt;1)+(Assumptions!$D$39&lt;0)+(Assumptions!$D$39&gt;1)+(Assumptions!$D$40&lt;0)+(Assumptions!$D$40&gt;1)+(Assumptions!$D$41&lt;0)+(Assumptions!$D$41&gt;1)+(Assumptions!$D$42&lt;0)+(Assumptions!$D$42&gt;1)+(Assumptions!$D$43&lt;0)+(Assumptions!$D$43&gt;1)+(Assumptions!$D$44&lt;0)+(Assumptions!$D$44&gt;1)+(Assumptions!$D$55&lt;0)+(Assumptions!$D$55&gt;1)+(Assumptions!$D$56&lt;0)+(Assumptions!$D$56&gt;1)+(Assumptions!$D$57&lt;0)+(Assumptions!$D$57&gt;1)+(Assumptions!$D$58&lt;0)+(Assumptions!$D$58&gt;1)+(Assumptions!$D$59&lt;0)+(Assumptions!$D$59&gt;1)+(Assumptions!$D$60&lt;0)+(Assumptions!$D$60&gt;1)+(Assumptions!$D$61&lt;0)+(Assumptions!$D$61&gt;1)+(Assumptions!$D$62&lt;0)+(Assumptions!$D$62&gt;1)+(Assumptions!$D$63&lt;0)+(Assumptions!$D$63&gt;1)+(Assumptions!$D$64&lt;0)+(Assumptions!$D$64&gt;1)+(Assumptions!$D$65&lt;0)+(Assumptions!$D$65&gt;1)+(Assumptions!$D$74&lt;0)+(Assumptions!$D$74&gt;1)+(Assumptions!$D$75&lt;0)+(Assumptions!$D$75&gt;1)+(Assumptions!$D$76&lt;0)+(Assumptions!$D$76&gt;1)+(Assumptions!$D$77&lt;0)+(Assumptions!$D$77&gt;1)+(Assumptions!$D$100&lt;0)+(Assumptions!$D$100&gt;1)+(Assumptions!$D$103&lt;0)+(Assumptions!$D$103&gt;1)+(Assumptions!$D$104&lt;0)+(Assumptions!$D$104&gt;1)+(Assumptions!$D$105&lt;0)+(Assumptions!$D$105&gt;1)+(Assumptions!$D$106&lt;0)+(Assumptions!$D$106&gt;1))&gt;0,"a share/rate is outside 0–100%; ","")&amp;IF(((Assumptions!$D$9&lt;0)+(Assumptions!$D$11&lt;0)+(Assumptions!$D$12&lt;0)+(Assumptions!$D$13&lt;0)+(Assumptions!$D$14&lt;0)+(Assumptions!$D$15&lt;0)+(Assumptions!$D$19&lt;0)+(Assumptions!$D$21&lt;0)+(Assumptions!$D$22&lt;0)+(Assumptions!$D$23&lt;0)+(Assumptions!$D$24&lt;0)+(Assumptions!$D$25&lt;0)+(Assumptions!$D$49&lt;0)+(Assumptions!$D$51&lt;0)+(Assumptions!$D$70&lt;0)+(Assumptions!$D$71&lt;0)+(Assumptions!$D$72&lt;0)+(Assumptions!$D$73&lt;0)+(Assumptions!$D$78&lt;0)+(Assumptions!$D$79&lt;0)+(Assumptions!$D$80&lt;0)+(Assumptions!$D$81&lt;0)+(Assumptions!$D$85&lt;0)+(Assumptions!$D$86&lt;0)+(Assumptions!$D$87&lt;0)+(Assumptions!$D$88&lt;0)+(Assumptions!$D$89&lt;0)+(Assumptions!$D$90&lt;0)+(Assumptions!$D$91&lt;0)+(Assumptions!$D$94&lt;0)+(Assumptions!$D$96&lt;0)+(Assumptions!$D$101&lt;0)+(Assumptions!$D$102&lt;0)+(Assumptions!$D$107&lt;0)+(Assumptions!$D$108&lt;0)+(Assumptions!$D$135&lt;0)+(Assumptions!$D$136&lt;0)+(Assumptions!$D$137&lt;0)+(Assumptions!$D$138&lt;0)+(Assumptions!$D$141&lt;0)+(Assumptions!$D$142&lt;0)+(Assumptions!$D$143&lt;0)+(Assumptions!$D$144&lt;0)+(Assumptions!$D$146&lt;0)+(Assumptions!$D$147&lt;0)+(Assumptions!$D$148&lt;0)+(Assumptions!$D$149&lt;0)+(Assumptions!$D$151&lt;0)+(Assumptions!$D$153&lt;0)+(Assumptions!$D$154&lt;0)+(Assumptions!$D$155&lt;0)+(Assumptions!$D$157&lt;0)+(Assumptions!$D$158&lt;0)+(Assumptions!$D$159&lt;0)+(Assumptions!$D$160&lt;0)+(Assumptions!$D$161&lt;0))&gt;0,"a count, cost or day value is negative; ","")&amp;IF(SUMPRODUCT((Assumptions!$E$112:$E$131&lt;0)+(Assumptions!$G$112:$G$131&lt;0)+(Assumptions!$G$112:$G$131&gt;1)+(Assumptions!$H$112:$H$131&lt;0)+(Assumptions!$I$112:$I$131&lt;0)+(Assumptions!$J$112:$J$131&lt;0)+(Assumptions!$F$112:$F$131&lt;0)+((Assumptions!$D$112:$D$131="CPC")*(Assumptions!$F$112:$F$131&gt;1)))&gt;0,"a channel input (Assumptions §7) is out of range; ","")&amp;IF(OR(Assumptions!$D$48&lt;0,Assumptions!$D$48&gt;=1),"reserve share must be 0–99%; ","")&amp;IF(OR(Assumptions!$D$20&lt;Assumptions!$D$7,Assumptions!$D$20&gt;Assumptions!$D$8),"last signing date must fall inside the campaign; ","")&amp;IF(Assumptions!$D$8&lt;=Assumptions!$D$7,"campaign end must be after its start; ","")&amp;IF(OR(Assumptions!$D$95&gt;=Assumptions!$D$93,Assumptions!$D$96&lt;Assumptions!$D$94),"initiative kill thresholds must sit below pass thresholds (TK1 &lt; TP1, TK2 ≥ TP2); ",""))</f>
         <v>✓ all inputs valid</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9"/>
+      <c r="C20" s="8" t="str">
+        <f aca="false">Weekly!S15</f>
+        <v>✓ ties to plan</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
     </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B21:G22"/>
+    <mergeCell ref="B22:G23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3122,86 +3134,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5336,7 +5348,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G35" s="36" t="n">
         <f aca="false">SUM(G5:G34)</f>
@@ -5389,60 +5401,60 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="22" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
       <c r="B39" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
@@ -5488,7 +5500,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
@@ -5534,7 +5546,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
@@ -5580,7 +5592,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -5626,7 +5638,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C44" s="29" t="n">
         <f aca="false">SUM(C40:C43)</f>
@@ -5667,7 +5679,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -5759,17 +5771,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5780,237 +5792,237 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>46315</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>46387</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -6021,191 +6033,191 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>46374</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="15" t="n">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6216,398 +6228,398 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>0.55</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>0.45</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>0.65</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>0.65</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -6618,467 +6630,467 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D49" s="17" t="n">
         <v>750</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51" s="17" t="n">
         <v>2500</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D55" s="16" t="n">
         <v>0.03</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D56" s="16" t="n">
         <v>0.05</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D57" s="16" t="n">
         <v>0.2</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D58" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>0.24</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
@@ -7089,306 +7101,306 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D70" s="15" t="n">
         <v>7000</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D71" s="15" t="n">
         <v>27000</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D72" s="15" t="n">
         <v>2500</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D73" s="15" t="n">
         <v>2000</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D74" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G75" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D76" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G76" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>0.06</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D78" s="15" t="n">
         <v>150</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D79" s="15" t="n">
         <v>300</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D80" s="15" t="n">
         <v>400</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G80" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D81" s="15" t="n">
         <v>100</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G81" s="13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -7399,582 +7411,582 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D85" s="17" t="n">
         <v>500</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D86" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G86" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>0.8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G87" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D88" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G88" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D89" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G89" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D90" s="17" t="n">
         <v>750</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G90" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D91" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G91" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D93" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G93" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D94" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D95" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G95" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D96" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G96" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>0.35</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G98" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G99" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D101" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G101" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D102" s="15" t="n">
         <v>5</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G103" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G106" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D107" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D108" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
@@ -7990,54 +8002,54 @@
     </row>
     <row r="111" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E111" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G111" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H111" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K111" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L111" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E112" s="19" t="n">
         <v>0</v>
@@ -8056,24 +8068,24 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L112" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E113" s="19" t="n">
         <v>0</v>
@@ -8092,24 +8104,24 @@
         <v>0</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L113" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E114" s="19" t="n">
         <v>0</v>
@@ -8128,24 +8140,24 @@
         <v>0</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L114" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E115" s="19" t="n">
         <v>0</v>
@@ -8164,24 +8176,24 @@
         <v>0</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L115" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E116" s="19" t="n">
         <v>2</v>
@@ -8202,24 +8214,24 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L116" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E117" s="19" t="n">
         <v>1.2</v>
@@ -8240,24 +8252,24 @@
         <v>0</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L117" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E118" s="19" t="n">
         <v>1.8</v>
@@ -8278,24 +8290,24 @@
         <v>0</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L118" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E119" s="19" t="n">
         <v>1.7</v>
@@ -8316,24 +8328,24 @@
         <v>0</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L119" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E120" s="19" t="n">
         <v>1449</v>
@@ -8354,24 +8366,24 @@
         <v>0</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L120" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E121" s="19" t="n">
         <v>1449</v>
@@ -8392,24 +8404,24 @@
         <v>0</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L121" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E122" s="19" t="n">
         <v>1449</v>
@@ -8430,24 +8442,24 @@
         <v>0</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L122" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E123" s="19" t="n">
         <v>1449</v>
@@ -8468,24 +8480,24 @@
         <v>0</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L123" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E124" s="19" t="n">
         <v>3.5</v>
@@ -8506,24 +8518,24 @@
         <v>0</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L124" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E125" s="19" t="n">
         <v>3.5</v>
@@ -8544,24 +8556,24 @@
         <v>0</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L125" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E126" s="19" t="n">
         <v>18</v>
@@ -8580,24 +8592,24 @@
         <v>0</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L126" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E127" s="19" t="n">
         <v>12</v>
@@ -8616,24 +8628,24 @@
         <v>0</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L127" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E128" s="19" t="n">
         <v>2.2</v>
@@ -8654,24 +8666,24 @@
         <v>0</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L128" s="13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E129" s="19" t="n">
         <v>2.2</v>
@@ -8692,24 +8704,24 @@
         <v>0</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L129" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E130" s="19" t="n">
         <v>2.2</v>
@@ -8730,24 +8742,24 @@
         <v>0</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L130" s="13" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E131" s="19" t="n">
         <v>2.2</v>
@@ -8768,15 +8780,15 @@
         <v>0</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L131" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
@@ -8787,646 +8799,646 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E134" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G134" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D135" s="15" t="n">
         <v>200</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G135" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D136" s="15" t="n">
         <v>300</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G136" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D137" s="15" t="n">
         <v>120</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G137" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D138" s="15" t="n">
         <v>80</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G138" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D139" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G139" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D140" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G140" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D141" s="15" t="n">
         <v>25</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G141" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D142" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D143" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D144" s="15" t="n">
         <v>8</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D145" s="16" t="n">
         <v>0.45</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G145" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D146" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G146" s="13" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D147" s="17" t="n">
         <v>1000</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D148" s="20" t="n">
         <v>1.15</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G148" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D149" s="15" t="n">
         <v>12000</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G149" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D150" s="21" t="n">
         <v>0.025</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G150" s="13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D151" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G151" s="13" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D152" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D153" s="20" t="n">
         <v>0.8</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G153" s="13" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D154" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G154" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D155" s="17" t="n">
         <v>12</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G155" s="13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D156" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G156" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D157" s="15" t="n">
         <v>450</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G157" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D158" s="20" t="n">
         <v>1.1</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D159" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G159" s="13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D160" s="17" t="n">
         <v>30</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G160" s="13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D161" s="17" t="n">
         <v>400</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -9475,67 +9487,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$D$11</f>
@@ -9600,7 +9612,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">Assumptions!$D$12</f>
@@ -9665,7 +9677,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">Assumptions!$D$13</f>
@@ -9730,7 +9742,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">Assumptions!$D$14</f>
@@ -9795,7 +9807,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -9840,17 +9852,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B13" s="30" t="n">
         <f aca="false">Assumptions!$D$7+Assumptions!$D$19</f>
@@ -9859,7 +9871,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">Assumptions!$D$20</f>
@@ -9868,7 +9880,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B15" s="23" t="n">
         <f aca="false">Assumptions!$D$22+Assumptions!$D$23+Assumptions!$D$24</f>
@@ -9877,7 +9889,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B16" s="23" t="n">
         <f aca="false">B15+Assumptions!$D$25</f>
@@ -9886,7 +9898,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B17" s="30" t="n">
         <f aca="false">B14-B15</f>
@@ -9895,7 +9907,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B18" s="30" t="n">
         <f aca="false">B14-B16</f>
@@ -9922,7 +9934,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">MAX(0,B17-B13+1)</f>
@@ -9940,7 +9952,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B23" s="23" t="n">
         <f aca="false">O9</f>
@@ -9962,7 +9974,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">IF(O9&gt;0,Channels!U35/O9,0)</f>
@@ -9971,62 +9983,62 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">B22*B25</f>
         <v>110.823976181854</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="23" t="n">
         <f aca="false">B5</f>
@@ -10057,10 +10069,10 @@
         <v>1000.777000777</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K30" s="34" t="n">
         <f aca="false">IF(B30&gt;0,(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30,0)</f>
@@ -10073,7 +10085,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B31" s="23" t="n">
         <f aca="false">B6</f>
@@ -10104,10 +10116,10 @@
         <v>221.181512090603</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K31" s="34" t="n">
         <f aca="false">IF(B31&gt;0,(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31,0)</f>
@@ -10120,7 +10132,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="23" t="n">
         <f aca="false">B7</f>
@@ -10151,10 +10163,10 @@
         <v>598.290598290598</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K32" s="34" t="n">
         <f aca="false">IF(B32&gt;0,(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32,0)</f>
@@ -10167,7 +10179,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" s="23" t="n">
         <f aca="false">B8</f>
@@ -10198,10 +10210,10 @@
         <v>1000</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K33" s="34" t="n">
         <f aca="false">IF(B33&gt;0,(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33,0)</f>
@@ -10214,7 +10226,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -10252,12 +10264,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B40" s="24" t="n">
         <f aca="false">Assumptions!$D$66</f>
@@ -10266,33 +10278,33 @@
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B42" s="23" t="n">
         <f aca="false">O9</f>
@@ -10319,12 +10331,12 @@
         <v>0</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B43" s="23" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -10351,12 +10363,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B44" s="23" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -10383,12 +10395,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B45" s="23" t="n">
         <f aca="false">O9</f>
@@ -10415,12 +10427,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B46" s="23" t="n">
         <f aca="false">O9</f>
@@ -10447,12 +10459,12 @@
         <v>0.3</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">O9</f>
@@ -10479,12 +10491,12 @@
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D49" s="8" t="str">
         <f aca="false">INDEX(A43:A47,MATCH(MAX(E43:E47),E43:E47,0))</f>
@@ -10493,7 +10505,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -10542,47 +10554,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$D$70</f>
@@ -10627,7 +10639,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">Assumptions!$D$71</f>
@@ -10672,7 +10684,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">Assumptions!$D$72</f>
@@ -10717,7 +10729,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">Assumptions!$D$73</f>
@@ -10762,7 +10774,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -10820,37 +10832,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B5" s="23" t="n">
         <f aca="false">Assumptions!$D$135</f>
@@ -10875,7 +10887,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B6" s="24" t="n">
         <f aca="false">Assumptions!$D$139</f>
@@ -10896,7 +10908,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">B5*B6</f>
@@ -10921,7 +10933,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B8" s="24" t="n">
         <f aca="false">Assumptions!$D$140</f>
@@ -10942,7 +10954,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B9" s="25" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$148</f>
@@ -10963,7 +10975,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B10" s="35" t="n">
         <f aca="false">B5*Assumptions!$D$146</f>
@@ -10988,7 +11000,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B11" s="37" t="n">
         <f aca="false">IF(B7&gt;0,B10/B7,0)</f>
@@ -11007,12 +11019,12 @@
         <v>4.16666666666667</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B7*B8*B9</f>
@@ -11037,7 +11049,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">Assumptions!$D$141</f>
@@ -11062,7 +11074,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B14" s="24" t="n">
         <f aca="false">Assumptions!$D$145</f>
@@ -11083,7 +11095,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">B13*B14*B9</f>
@@ -11108,7 +11120,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B16" s="35" t="n">
         <f aca="false">B15*Assumptions!$D$147</f>
@@ -11133,7 +11145,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B17" s="37" t="n">
         <f aca="false">IF(B13&gt;0,B16/B13,0)</f>
@@ -11152,12 +11164,12 @@
         <v>138.560625</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B12+B15</f>
@@ -11182,7 +11194,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B19" s="35" t="n">
         <f aca="false">B10+B16</f>
@@ -11207,7 +11219,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B20" s="35" t="n">
         <f aca="false">IF(B18&gt;0,B19/B18,0)</f>
@@ -11232,12 +11244,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B24" s="23" t="n">
         <f aca="false">Assumptions!$D$149</f>
@@ -11246,7 +11258,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">Assumptions!$D$150</f>
@@ -11255,7 +11267,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B26" s="23" t="n">
         <f aca="false">B24*B25</f>
@@ -11264,7 +11276,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B27" s="35" t="n">
         <f aca="false">Assumptions!$D$151</f>
@@ -11273,7 +11285,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B28" s="24" t="n">
         <f aca="false">Assumptions!$D$152</f>
@@ -11282,7 +11294,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B26*B28</f>
@@ -11291,7 +11303,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B30" s="25" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$153</f>
@@ -11300,7 +11312,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B31" s="26" t="n">
         <f aca="false">B29*B30</f>
@@ -11309,7 +11321,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B32" s="35" t="n">
         <f aca="false">B26*B27</f>
@@ -11318,7 +11330,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B33" s="35" t="n">
         <f aca="false">Assumptions!$D$154</f>
@@ -11327,7 +11339,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B34" s="35" t="n">
         <f aca="false">IF(B31&gt;0,(B32+B33)/B31,0)</f>
@@ -11336,12 +11348,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B38" s="37" t="n">
         <f aca="false">B44+B45</f>
@@ -11350,7 +11362,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B39" s="24" t="n">
         <f aca="false">Assumptions!$D$156</f>
@@ -11359,7 +11371,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B40" s="23" t="n">
         <f aca="false">Assumptions!$D$157</f>
@@ -11368,7 +11380,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B41" s="25" t="n">
         <f aca="false">Funnel!$G$6*Assumptions!$D$158</f>
@@ -11377,7 +11389,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">Assumptions!$D$10*Assumptions!$D$12</f>
@@ -11386,7 +11398,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B43" s="26" t="n">
         <f aca="false">MIN(B40*B39*B41,B42)</f>
@@ -11395,7 +11407,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B44" s="37" t="n">
         <f aca="false">Assumptions!$D$155</f>
@@ -11404,7 +11416,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B45" s="37" t="n">
         <f aca="false">Assumptions!$D$159/60*Assumptions!$D$160</f>
@@ -11413,7 +11425,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B46" s="35" t="n">
         <f aca="false">Assumptions!$D$161</f>
@@ -11422,7 +11434,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">IF(B41*B39&gt;0,B43/B41/B39,0)</f>
@@ -11431,7 +11443,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B48" s="35" t="n">
         <f aca="false">IF(B43&gt;0,(B47*B38+B46)/B43,0)</f>
@@ -11440,50 +11452,50 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="22" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C53" s="24" t="n">
         <f aca="false">(Assumptions!$D$97+Assumptions!$D$98)</f>
@@ -11498,32 +11510,32 @@
         <v>32.515726383307</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G53" s="23" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E53*Assumptions!$D$93,0))</f>
         <v>19</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I53" s="23" t="n">
-        <f aca="false">MAX(1,ROUNDUP(E53*Assumptions!$D$95,0))</f>
+        <f aca="false">MIN(G53,MAX(1,ROUNDUP(E53*Assumptions!$D$95,0)))</f>
         <v>10</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C54" s="24" t="n">
         <f aca="false">(Assumptions!$D$55*4/7+Assumptions!$D$56+Assumptions!$D$57*3/7)</f>
@@ -11550,23 +11562,23 @@
         <v>250</v>
       </c>
       <c r="I54" s="23" t="n">
-        <f aca="false">MAX(1,ROUNDUP(E54*Assumptions!$D$95,0))</f>
+        <f aca="false">MIN(G54,MAX(1,ROUNDUP(E54*Assumptions!$D$95,0)))</f>
         <v>3</v>
       </c>
       <c r="J54" s="35" t="n">
-        <f aca="false">ROUND(F54*Assumptions!$D$96/10,0)*10</f>
+        <f aca="false">MAX(H54,ROUND(F54*Assumptions!$D$96/10,0)*10)</f>
         <v>300</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C55" s="24" t="n">
         <f aca="false">(Assumptions!$D$56+Assumptions!$D$57)</f>
@@ -11593,20 +11605,20 @@
         <v>110</v>
       </c>
       <c r="I55" s="23" t="n">
-        <f aca="false">MAX(1,ROUNDUP(E55*Assumptions!$D$95,0))</f>
+        <f aca="false">MIN(G55,MAX(1,ROUNDUP(E55*Assumptions!$D$95,0)))</f>
         <v>3</v>
       </c>
       <c r="J55" s="35" t="n">
-        <f aca="false">ROUND(F55*Assumptions!$D$96/10,0)*10</f>
+        <f aca="false">MAX(H55,ROUND(F55*Assumptions!$D$96/10,0)*10)</f>
         <v>130</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -11640,124 +11652,124 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>520</v>
-      </c>
       <c r="K4" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AI4" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11774,7 +11786,7 @@
         <v>Electricians</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E5" s="2" t="str">
         <f aca="false">Assumptions!D112</f>
@@ -11915,7 +11927,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="2" t="str">
         <f aca="false">Assumptions!D113</f>
@@ -12056,7 +12068,7 @@
         <v>Automation</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E7" s="2" t="str">
         <f aca="false">Assumptions!D114</f>
@@ -12197,7 +12209,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E8" s="2" t="str">
         <f aca="false">Assumptions!D115</f>
@@ -12338,7 +12350,7 @@
         <v>Electricians</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E9" s="2" t="str">
         <f aca="false">Assumptions!D116</f>
@@ -12479,7 +12491,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E10" s="2" t="str">
         <f aca="false">Assumptions!D117</f>
@@ -12620,7 +12632,7 @@
         <v>Automation</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E11" s="2" t="str">
         <f aca="false">Assumptions!D118</f>
@@ -12761,7 +12773,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E12" s="2" t="str">
         <f aca="false">Assumptions!D119</f>
@@ -12902,7 +12914,7 @@
         <v>Electricians</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E13" s="2" t="str">
         <f aca="false">Assumptions!D120</f>
@@ -13043,7 +13055,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E14" s="2" t="str">
         <f aca="false">Assumptions!D121</f>
@@ -13184,7 +13196,7 @@
         <v>Automation</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E15" s="2" t="str">
         <f aca="false">Assumptions!D122</f>
@@ -13325,7 +13337,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E16" s="2" t="str">
         <f aca="false">Assumptions!D123</f>
@@ -13466,7 +13478,7 @@
         <v>Automation</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E17" s="2" t="str">
         <f aca="false">Assumptions!D124</f>
@@ -13607,7 +13619,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E18" s="2" t="str">
         <f aca="false">Assumptions!D125</f>
@@ -13748,7 +13760,7 @@
         <v>Electricians</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E19" s="2" t="str">
         <f aca="false">Assumptions!D126</f>
@@ -13889,7 +13901,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E20" s="2" t="str">
         <f aca="false">Assumptions!D127</f>
@@ -14030,7 +14042,7 @@
         <v>Electricians</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E21" s="2" t="str">
         <f aca="false">Assumptions!D128</f>
@@ -14171,7 +14183,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E22" s="2" t="str">
         <f aca="false">Assumptions!D129</f>
@@ -14312,7 +14324,7 @@
         <v>Automation</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E23" s="2" t="str">
         <f aca="false">Assumptions!D130</f>
@@ -14453,7 +14465,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E24" s="2" t="str">
         <f aca="false">Assumptions!D131</f>
@@ -14582,19 +14594,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F25" s="37" t="n">
         <f aca="false">Initiatives!B11</f>
@@ -14716,19 +14728,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F26" s="37" t="n">
         <f aca="false">Initiatives!C11</f>
@@ -14850,19 +14862,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F27" s="37" t="n">
         <f aca="false">Initiatives!D11</f>
@@ -14984,19 +14996,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F28" s="37" t="n">
         <f aca="false">Initiatives!E11</f>
@@ -15118,19 +15130,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F29" s="37" t="n">
         <f aca="false">Initiatives!B17</f>
@@ -15252,19 +15264,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F30" s="37" t="n">
         <f aca="false">Initiatives!C17</f>
@@ -15386,19 +15398,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">Initiatives!D17</f>
@@ -15520,19 +15532,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F32" s="37" t="n">
         <f aca="false">Initiatives!E17</f>
@@ -15654,19 +15666,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F33" s="37" t="n">
         <f aca="false">Initiatives!B27</f>
@@ -15788,19 +15800,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F34" s="37" t="n">
         <f aca="false">Initiatives!B38</f>
@@ -15922,7 +15934,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J35" s="27" t="n">
         <f aca="false">SUM(J5:J34)</f>
@@ -15987,27 +15999,27 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
       <c r="B38" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="23" t="n">
         <f aca="false">Funnel!B5</f>
@@ -16024,7 +16036,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40" s="23" t="n">
         <f aca="false">Funnel!B6</f>
@@ -16041,7 +16053,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C41" s="23" t="n">
         <f aca="false">Funnel!B7</f>
@@ -16058,7 +16070,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C42" s="23" t="n">
         <f aca="false">Funnel!B8</f>
@@ -16100,12 +16112,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C4" s="35" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Channel")</f>
@@ -16114,7 +16126,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C5" s="35" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Initiative")</f>
@@ -16123,7 +16135,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C6" s="35" t="n">
         <f aca="false">Channels!Y35</f>
@@ -16132,7 +16144,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C7" s="35" t="n">
         <f aca="false">C4+C5+C6</f>
@@ -16141,7 +16153,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C8" s="35" t="n">
         <f aca="false">Channels!Z35</f>
@@ -16150,7 +16162,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C9" s="35" t="n">
         <f aca="false">C7</f>
@@ -16159,7 +16171,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">IF(Assumptions!$D$48&lt;1,C9/(1-Assumptions!$D$48)*Assumptions!$D$48,0)</f>
@@ -16168,7 +16180,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C11" s="35" t="n">
         <f aca="false">C9+C10</f>
@@ -16177,7 +16189,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">IF(Assumptions!$D$51&gt;0,ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51,C11)</f>
@@ -16186,7 +16198,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C13" s="40" t="n">
         <f aca="false">MIN(Channels!U35,Funnel!B26)</f>
@@ -16195,7 +16207,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C14" s="41" t="n">
         <f aca="false">IF(C13&gt;0,C9/C13,0)</f>
@@ -16204,7 +16216,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C15" s="35" t="n">
         <f aca="false">IF(C13&gt;0,C12/C13,0)</f>
@@ -16213,7 +16225,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">IF(C12&gt;0,Weekly!N5/C12,0)</f>
@@ -16222,39 +16234,39 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="22" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B21)</f>
@@ -16287,7 +16299,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C22" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B22)</f>
@@ -16320,7 +16332,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B23)</f>
@@ -16353,7 +16365,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B24)</f>
@@ -16386,7 +16398,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C25" s="36" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -16419,30 +16431,30 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="22" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C29" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B29)</f>
@@ -16463,7 +16475,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B30)</f>
@@ -16484,7 +16496,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B31)</f>
@@ -16505,7 +16517,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C32" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B32)</f>
@@ -16526,7 +16538,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C33" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B33)</f>
@@ -16547,7 +16559,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C34" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B34)</f>
@@ -16568,7 +16580,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C35" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B35)</f>
@@ -16589,7 +16601,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C36" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B36)</f>
@@ -16610,7 +16622,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C37" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B37)</f>
@@ -16631,7 +16643,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C38" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B38)</f>
@@ -16652,7 +16664,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C39" s="36" t="n">
         <f aca="false">SUM(C29:C38)</f>
@@ -16671,39 +16683,39 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="22" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16896,17 +16908,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E3" s="22" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F3" s="42" t="n">
         <f aca="false">1</f>
@@ -16927,7 +16939,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E4" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F4" s="35" t="n">
         <f aca="false">Budget!$C$12*F3</f>
@@ -16948,7 +16960,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E5" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F5" s="35" t="n">
         <f aca="false">F4*(1-Assumptions!$D$48)</f>
@@ -16969,7 +16981,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E6" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F6" s="35" t="n">
         <f aca="false">MAX(0,Budget!$C$9-F5)</f>
@@ -16990,58 +17002,58 @@
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19266,12 +19278,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="22" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F39" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E39)*F$47</f>
@@ -19292,7 +19304,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F40" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E40)*F$47</f>
@@ -19313,7 +19325,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F41" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E41)*F$47</f>
@@ -19334,7 +19346,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F42" s="26" t="n">
         <f aca="false">SUMIFS(F$8:F$37,$B$8:$B$37,$E42)*F$47</f>
@@ -19355,7 +19367,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F43" s="29" t="n">
         <f aca="false">SUM(F39:F42)</f>
@@ -19376,7 +19388,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F44" s="35" t="n">
         <f aca="false">IF(F43&gt;0,F4/F43,0)</f>
@@ -19397,7 +19409,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F46" s="26" t="n">
         <f aca="false">SUM(O8:O37)</f>
@@ -19418,7 +19430,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F47" s="24" t="n">
         <f aca="false">IF(F46&gt;0,MIN(1,Funnel!$B$22/F46),1)</f>
@@ -19439,7 +19451,7 @@
     </row>
     <row r="49" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -19471,89 +19483,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20669,7 +20681,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D15" s="44" t="n">
         <f aca="false">SUM(D4:D14)</f>
@@ -20750,7 +20762,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -20802,12 +20814,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="22" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F19" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20816,7 +20828,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F20" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20825,7 +20837,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F21" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -20834,7 +20846,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F22" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20843,7 +20855,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F23" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20852,7 +20864,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F24" s="35" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -20861,7 +20873,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F25" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20870,7 +20882,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F26" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20879,7 +20891,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F27" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20888,7 +20900,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F28" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20897,7 +20909,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F29" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20906,7 +20918,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F30" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20915,7 +20927,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F31" s="35" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -20924,7 +20936,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20933,7 +20945,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20942,7 +20954,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F34" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20951,7 +20963,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20960,7 +20972,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F36" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -20969,7 +20981,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F37" s="26" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -20978,7 +20990,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F38" s="24" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -20987,49 +20999,49 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21574,7 +21586,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C54" s="36" t="n">
         <f aca="false">SUM(C44:C53)</f>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="755">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -1935,6 +1935,9 @@
   </si>
   <si>
     <t xml:space="preserve">Savings needed €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID (+ to expand)</t>
   </si>
   <si>
     <t xml:space="preserve">Total € (media + fixed)</t>
@@ -9035,15 +9038,19 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AI42"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="20" min="17" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="21" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="29" min="29" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="35" min="31" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13499,7 +13506,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R102"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
@@ -14370,61 +14377,61 @@
     </row>
     <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>22</v>
+        <v>636</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>289</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>621</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L60" s="12" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N60" s="12" t="s">
         <v>619</v>
       </c>
       <c r="O60" s="12" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A61" s="2" t="str">
         <f aca="false">Channels!A5</f>
         <v>C01</v>
@@ -14498,7 +14505,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A62" s="2" t="str">
         <f aca="false">Channels!A6</f>
         <v>C02</v>
@@ -14572,7 +14579,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A63" s="2" t="str">
         <f aca="false">Channels!A7</f>
         <v>C03</v>
@@ -14646,7 +14653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A64" s="2" t="str">
         <f aca="false">Channels!A8</f>
         <v>C04</v>
@@ -14720,7 +14727,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A65" s="2" t="str">
         <f aca="false">Channels!A9</f>
         <v>C05</v>
@@ -14794,7 +14801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A66" s="2" t="str">
         <f aca="false">Channels!A10</f>
         <v>C06</v>
@@ -14868,7 +14875,7 @@
         <v>1.02484472049689</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A67" s="2" t="str">
         <f aca="false">Channels!A11</f>
         <v>C07</v>
@@ -14942,7 +14949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A68" s="2" t="str">
         <f aca="false">Channels!A12</f>
         <v>C08</v>
@@ -15016,7 +15023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A69" s="2" t="str">
         <f aca="false">Channels!A13</f>
         <v>C09</v>
@@ -15090,7 +15097,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A70" s="2" t="str">
         <f aca="false">Channels!A14</f>
         <v>C10</v>
@@ -15164,7 +15171,7 @@
         <v>12.8835134018277</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A71" s="2" t="str">
         <f aca="false">Channels!A15</f>
         <v>C11</v>
@@ -15238,7 +15245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A72" s="2" t="str">
         <f aca="false">Channels!A16</f>
         <v>C12</v>
@@ -15312,7 +15319,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A73" s="2" t="str">
         <f aca="false">Channels!A17</f>
         <v>C13</v>
@@ -15386,7 +15393,7 @@
         <v>30.2675550787611</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A74" s="2" t="str">
         <f aca="false">Channels!A18</f>
         <v>C14</v>
@@ -15460,7 +15467,7 @@
         <v>17.3998206768484</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A75" s="2" t="str">
         <f aca="false">Channels!A19</f>
         <v>C15</v>
@@ -15534,7 +15541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A76" s="2" t="str">
         <f aca="false">Channels!A20</f>
         <v>C16</v>
@@ -15608,7 +15615,7 @@
         <v>1.07142857142857</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A77" s="2" t="str">
         <f aca="false">Channels!A21</f>
         <v>C17</v>
@@ -15682,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A78" s="2" t="str">
         <f aca="false">Channels!A22</f>
         <v>C18</v>
@@ -15756,7 +15763,7 @@
         <v>1.04748603351955</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A79" s="2" t="str">
         <f aca="false">Channels!A23</f>
         <v>C19</v>
@@ -15830,7 +15837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A80" s="2" t="str">
         <f aca="false">Channels!A24</f>
         <v>C20</v>
@@ -15904,7 +15911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A81" s="2" t="str">
         <f aca="false">Channels!A25</f>
         <v>I1a-E</v>
@@ -15978,7 +15985,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A82" s="2" t="str">
         <f aca="false">Channels!A26</f>
         <v>I1a-M</v>
@@ -16052,7 +16059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A83" s="2" t="str">
         <f aca="false">Channels!A27</f>
         <v>I1a-A</v>
@@ -16126,7 +16133,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A84" s="2" t="str">
         <f aca="false">Channels!A28</f>
         <v>I1a-S</v>
@@ -16200,7 +16207,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A85" s="2" t="str">
         <f aca="false">Channels!A29</f>
         <v>I1b-E</v>
@@ -16274,7 +16281,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A86" s="2" t="str">
         <f aca="false">Channels!A30</f>
         <v>I1b-M</v>
@@ -16348,7 +16355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A87" s="2" t="str">
         <f aca="false">Channels!A31</f>
         <v>I1b-A</v>
@@ -16422,7 +16429,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A88" s="2" t="str">
         <f aca="false">Channels!A32</f>
         <v>I1b-S</v>
@@ -16496,7 +16503,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A89" s="2" t="str">
         <f aca="false">Channels!A33</f>
         <v>I2-E</v>
@@ -16570,7 +16577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
       <c r="A90" s="2" t="str">
         <f aca="false">Channels!A34</f>
         <v>I3-M</v>
@@ -16646,7 +16653,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E91" s="24" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16777,7 +16784,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E99" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F99" s="28" t="n">
         <f aca="false">SUM(O61:O90)</f>
@@ -16798,7 +16805,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E100" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F100" s="26" t="n">
         <f aca="false">IF(F99&gt;0,MIN(1,Funnel!$B$22/F99),1)</f>
@@ -16819,7 +16826,7 @@
     </row>
     <row r="102" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -16843,103 +16850,104 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z55"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="1" max="26" min="24" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Z3" s="45" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18184,7 +18192,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -18236,12 +18244,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18250,7 +18258,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18259,7 +18267,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -18268,7 +18276,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18277,7 +18285,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18286,7 +18294,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -18295,7 +18303,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F25" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18304,7 +18312,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F26" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18313,7 +18321,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F27" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18322,7 +18330,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F28" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18331,7 +18339,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F29" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18340,7 +18348,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F30" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18349,7 +18357,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -18358,7 +18366,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18367,7 +18375,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18376,7 +18384,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18385,7 +18393,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18394,7 +18402,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F36" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18403,7 +18411,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18412,7 +18420,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F38" s="26" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -18421,7 +18429,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18430,37 +18438,37 @@
         <v>288</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N43" s="12" t="s">
         <v>426</v>
@@ -19098,12 +19106,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19117,67 +19125,67 @@
         <v>289</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21365,7 +21373,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21374,46 +21382,46 @@
         <v>289</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21643,7 +21651,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="757">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Last useful application date (Supervisors)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardest role (lowest channel coverage without the unproven I2)</t>
+    <t xml:space="preserve">Hardest role (needs the most money; scarcity evidence on Funnel row 35)</t>
   </si>
   <si>
     <t xml:space="preserve">Most sensitive assumption</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">All paid</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: weekly shares solved so qualified arrivals stay at or below the 55 weekly assessments (Weekly cols P vs Q). With W1–W6 = 7%, 11%, 16%, 20.5%, 20.5%, 25% the loads are 37/39, 52/55, 53/55, 54/55, 54/55, 55/55. Weeks 1–2 are low because rediscovery re-applicants and test applicants already use those slots.</t>
+    <t xml:space="preserve">Derivation: weekly shares solved numerically against the real model (iterated finite-difference fit) so qualified arrivals stay at or below the 55 weekly assessments (Weekly col P vs Q). With W1–W6 = 10%, 15.5%, 17.5%, 18%, 18%, 21% the loads are 38/39, 54/55, 54/55, 55/55, 55/55, 53/55. Weeks 1–2 are lower because rediscovery re-applicants (60% arrive in week 1) and the €750 tests already use those slots.</t>
   </si>
   <si>
     <t xml:space="preserve">W2</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">people</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km = all of Berlin + ~60% of Brandenburg (own scaling) ≈ 4,800, up to ~8,600 incl. 2630 Fachkraft → 6,000. Previously: Berlin+Brandenburg hold roughly 7% of German employment (approx. 2.6M of ~35M employees subject to social insurance; own approximation of BA employment statistics, not looked up); assumed ~150–200k industrial electricians in DE, lower industrial density in the East → ~7,000 within 75 km of Grünheide. Order of magnitude only.</t>
+    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 3,417 × 0.6 + 2,708 = 4,758 → 4,800.</t>
   </si>
   <si>
     <t xml:space="preserve">PSM</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 26,400 incl. ~1,000 German/English-speaking Polish border workers (IAB-Regional 1/2020: 825 Polish commuters in machine/vehicle trades in Brandenburg, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf). Previously: Mechatroniker + Industriemechaniker are among the largest metal/electrical trades; ~25k within 75 km + ~2k German/English-speaking in Polish border towns (Słubice, Kostrzyn, Gorzów). 1,000–2,000 Poles already work at the plant (https://www.faire-mobilitaet.de/fachinformationen/brancheninformationen/automobilindustrie/polen-tesla/).</t>
+    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 14,878 × 0.6 + 17,490 = 26,417 → 26,400.</t>
   </si>
   <si>
     <t xml:space="preserve">PSA</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km ≈ 2,000–2,500. Relocators (400) remain own estimate: Smaller local pool, but specialists relocate more: assume ~400 open to moving to Brandenburg in the window (national LinkedIn reach).</t>
+    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,206 × 0.6 + 1,254 = 1,978 → 2,000.</t>
   </si>
   <si>
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment 31.12.2025, Aufsicht codes 2519+2619+2629+2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km ≈ 2,200. Relocators: own estimate. Maintenance Meister/shift leads within 75 km; few relocate for a shift-lead job.</t>
+    <t xml:space="preserve">BA employment statistics 31.12.2025, Aufsicht codes 2519 + 2619 + 2629 + 2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,209 × 0.6 + 1,494 = 2,219 → 2,200.</t>
   </si>
   <si>
     <t xml:space="preserve">PIE</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">Share in-market or persuadable during the 6-week window</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: persuadable share ≈ one year of voluntary leavers = turnover 12% a year × 41% of exits that are resignations = 4.9% ≈ 5% (IAB-Betriebspanel Brandenburg 2024, https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf). Cross-check: Gallup Engagement Index 2024, ~11% actively searching (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf).</t>
+    <t xml:space="preserve">Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year.</t>
   </si>
   <si>
     <t xml:space="preserve">PIM</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">Free</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105.</t>
+    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C02</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158.</t>
+    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C03</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53.</t>
+    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C04</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35.</t>
+    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C05</t>
@@ -941,22 +941,25 @@
     <t xml:space="preserve">CPA</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. </t>
+    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 13.5% qualified = 1,520 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C06</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. </t>
+    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 19.8% qualified = 5,330 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C07</t>
   </si>
   <si>
+    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 13.5% qualified = 630 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C08</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. </t>
+    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 9.0% qualified = 980 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C09</t>
@@ -968,13 +971,13 @@
     <t xml:space="preserve">Slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. </t>
+    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C10</t>
   </si>
   <si>
-    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. </t>
+    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C11</t>
@@ -983,7 +986,7 @@
     <t xml:space="preserve">C12</t>
   </si>
   <si>
-    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. </t>
+    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C13</t>
@@ -992,13 +995,13 @@
     <t xml:space="preserve">LinkedIn (promoted jobs + InMail)</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. </t>
+    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 13.5% qualified = 260 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C14</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. </t>
+    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 9.0% qualified = 410 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C15</t>
@@ -1007,13 +1010,13 @@
     <t xml:space="preserve">Meta social (FB/IG lead ads, 75 km geo)</t>
   </si>
   <si>
-    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.50 = 7.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 400 applications × 7.5% = 30 qualified.</t>
+    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.50 = 7.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 400 applications × 7.5% = 30 qualified. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C16</t>
   </si>
   <si>
-    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.50 = 11.0%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 200 applications × 11.0% = 22 qualified.</t>
+    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.50 = 11.0%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 200 applications × 11.0% = 22 qualified. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C17</t>
@@ -1022,22 +1025,25 @@
     <t xml:space="preserve">Google Search ads (job-intent keywords)</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. </t>
+    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 10.7% qualified = 560 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C18</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. </t>
+    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 15.6% qualified = 1,970 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">C19</t>
   </si>
   <si>
+    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 10.7% qualified = 230 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C20</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. </t>
+    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 7.1% qualified = 360 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
   </si>
   <si>
     <t xml:space="preserve">8. New-initiative inputs (Part 3) — maths on the Initiatives tab</t>
@@ -2950,7 +2956,7 @@
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Budget!C12</f>
-        <v>230000</v>
+        <v>207500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2959,7 +2965,7 @@
       </c>
       <c r="C6" s="4" t="n">
         <f aca="false">Budget!C9</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2968,7 +2974,7 @@
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Budget!C12-Budget!C9</f>
-        <v>36576.3694239383</v>
+        <v>31285.0323244349</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2977,7 +2983,7 @@
       </c>
       <c r="C8" s="5" t="n">
         <f aca="false">Budget!C13</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2987,7 +2993,7 @@
       </c>
       <c r="C9" s="5" t="n">
         <f aca="false">MIN(Budget!C13,Funnel!B26)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2996,7 +3002,7 @@
       </c>
       <c r="C10" s="4" t="n">
         <f aca="false">Budget!C14</f>
-        <v>1958.71420042621</v>
+        <v>1762.14967675565</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3005,7 +3011,7 @@
       </c>
       <c r="C11" s="3" t="n">
         <f aca="false">Funnel!B23</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3023,7 +3029,7 @@
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Funnel!B24</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3049,8 +3055,8 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="str">
-        <f aca="false">IF(MIN(Funnel!L30:L33)&gt;=1000000000,"–",INDEX(Funnel!A30:A33,MATCH(MIN(Funnel!L30:L33),Funnel!L30:L33,0))&amp;" ("&amp;TEXT(MIN(Funnel!L30:L33),"0.0")&amp;"× coverage; see Funnel row 35)")</f>
-        <v>Supervisors (0.9× coverage; see Funnel row 35)</v>
+        <f aca="false">IF(MAX(Budget!F21:F24)&lt;=0,"–",INDEX(Budget!B21:B24,MATCH(MAX(Budget!F21:F24),Budget!F21:F24,0))&amp;" (€"&amp;TEXT(MAX(Budget!F21:F24)/1000,"0.0")&amp;"k"&amp;IF(Budget!C9&gt;0,", "&amp;TEXT(MAX(Budget!F21:F24)/Budget!C9,"0%")&amp;" of planned spend","")&amp;"; see Funnel row 35)")</f>
+        <v>Electricians (€70.7k, 40% of planned spend; see Funnel row 35)</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3068,7 +3074,7 @@
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">Budget!H47</f>
-        <v>89.7588819710332</v>
+        <v>88.0014981476179</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4186,7 +4192,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>143</v>
       </c>
@@ -4197,7 +4203,7 @@
         <v>145</v>
       </c>
       <c r="D55" s="16" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>46</v>
@@ -4209,7 +4215,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>147</v>
       </c>
@@ -4220,7 +4226,7 @@
         <v>145</v>
       </c>
       <c r="D56" s="16" t="n">
-        <v>0.11</v>
+        <v>0.155</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>46</v>
@@ -4232,7 +4238,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>149</v>
       </c>
@@ -4243,7 +4249,7 @@
         <v>145</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>46</v>
@@ -4255,7 +4261,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>151</v>
       </c>
@@ -4266,7 +4272,7 @@
         <v>145</v>
       </c>
       <c r="D58" s="16" t="n">
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>46</v>
@@ -4278,7 +4284,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>153</v>
       </c>
@@ -4289,7 +4295,7 @@
         <v>145</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>46</v>
@@ -4301,7 +4307,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>155</v>
       </c>
@@ -4312,7 +4318,7 @@
         <v>145</v>
       </c>
       <c r="D60" s="16" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>46</v>
@@ -4507,13 +4513,13 @@
         <v>50</v>
       </c>
       <c r="D70" s="15" t="n">
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G70" s="17" t="s">
         <v>175</v>
@@ -4530,13 +4536,13 @@
         <v>45</v>
       </c>
       <c r="D71" s="15" t="n">
-        <v>26000</v>
+        <v>26400</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G71" s="17" t="s">
         <v>177</v>
@@ -4553,13 +4559,13 @@
         <v>55</v>
       </c>
       <c r="D72" s="15" t="n">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G72" s="17" t="s">
         <v>179</v>
@@ -4582,7 +4588,7 @@
         <v>174</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G73" s="17" t="s">
         <v>181</v>
@@ -4599,7 +4605,7 @@
         <v>50</v>
       </c>
       <c r="D74" s="16" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>46</v>
@@ -4622,7 +4628,7 @@
         <v>45</v>
       </c>
       <c r="D75" s="16" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>46</v>
@@ -4645,7 +4651,7 @@
         <v>55</v>
       </c>
       <c r="D76" s="16" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>46</v>
@@ -4668,7 +4674,7 @@
         <v>57</v>
       </c>
       <c r="D77" s="16" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>46</v>
@@ -5577,7 +5583,7 @@
         <v>0.135</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>450</v>
+        <v>1520</v>
       </c>
       <c r="I116" s="22" t="n">
         <v>1</v>
@@ -5613,7 +5619,7 @@
         <v>0.198</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>600</v>
+        <v>5330</v>
       </c>
       <c r="I117" s="22" t="n">
         <v>1</v>
@@ -5649,7 +5655,7 @@
         <v>0.135</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>250</v>
+        <v>630</v>
       </c>
       <c r="I118" s="22" t="n">
         <v>1</v>
@@ -5661,12 +5667,12 @@
         <v>77</v>
       </c>
       <c r="L118" s="17" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B119" s="13" t="s">
         <v>302</v>
@@ -5685,7 +5691,7 @@
         <v>0.09</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>200</v>
+        <v>980</v>
       </c>
       <c r="I119" s="22" t="n">
         <v>1</v>
@@ -5697,21 +5703,21 @@
         <v>77</v>
       </c>
       <c r="L119" s="17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E120" s="20" t="n">
         <v>1449</v>
@@ -5735,21 +5741,21 @@
         <v>77</v>
       </c>
       <c r="L120" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E121" s="20" t="n">
         <v>1449</v>
@@ -5773,21 +5779,21 @@
         <v>77</v>
       </c>
       <c r="L121" s="17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E122" s="20" t="n">
         <v>1449</v>
@@ -5811,21 +5817,21 @@
         <v>77</v>
       </c>
       <c r="L122" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E123" s="20" t="n">
         <v>1449</v>
@@ -5849,15 +5855,15 @@
         <v>77</v>
       </c>
       <c r="L123" s="17" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>55</v>
@@ -5873,7 +5879,7 @@
         <v>0.135</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="I124" s="22" t="n">
         <v>1</v>
@@ -5885,15 +5891,15 @@
         <v>77</v>
       </c>
       <c r="L124" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>57</v>
@@ -5909,7 +5915,7 @@
         <v>0.09</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="I125" s="22" t="n">
         <v>1</v>
@@ -5921,15 +5927,15 @@
         <v>77</v>
       </c>
       <c r="L125" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>50</v>
@@ -5957,15 +5963,15 @@
         <v>77</v>
       </c>
       <c r="L126" s="17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>45</v>
@@ -5993,15 +5999,15 @@
         <v>77</v>
       </c>
       <c r="L127" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>50</v>
@@ -6017,7 +6023,7 @@
         <v>0.1065</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="I128" s="22" t="n">
         <v>1</v>
@@ -6029,15 +6035,15 @@
         <v>77</v>
       </c>
       <c r="L128" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>45</v>
@@ -6053,7 +6059,7 @@
         <v>0.1562</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>100</v>
+        <v>1970</v>
       </c>
       <c r="I129" s="22" t="n">
         <v>1</v>
@@ -6065,15 +6071,15 @@
         <v>77</v>
       </c>
       <c r="L129" s="17" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>55</v>
@@ -6089,7 +6095,7 @@
         <v>0.1065</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="I130" s="22" t="n">
         <v>1</v>
@@ -6101,15 +6107,15 @@
         <v>77</v>
       </c>
       <c r="L130" s="17" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>57</v>
@@ -6125,7 +6131,7 @@
         <v>0.071</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="I131" s="22" t="n">
         <v>1</v>
@@ -6137,12 +6143,12 @@
         <v>77</v>
       </c>
       <c r="L131" s="17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B133" s="11"/>
       <c r="C133" s="11"/>
@@ -6176,10 +6182,10 @@
     </row>
     <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>50</v>
@@ -6188,21 +6194,21 @@
         <v>41</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>45</v>
@@ -6211,21 +6217,21 @@
         <v>61</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>55</v>
@@ -6234,21 +6240,21 @@
         <v>20</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>57</v>
@@ -6257,21 +6263,21 @@
         <v>14</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>31</v>
@@ -6286,15 +6292,15 @@
         <v>77</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>31</v>
@@ -6309,15 +6315,15 @@
         <v>77</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>50</v>
@@ -6332,15 +6338,15 @@
         <v>77</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B142" s="13" t="s">
         <v>354</v>
-      </c>
-      <c r="B142" s="13" t="s">
-        <v>352</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>45</v>
@@ -6355,15 +6361,15 @@
         <v>77</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>55</v>
@@ -6378,15 +6384,15 @@
         <v>77</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>57</v>
@@ -6401,15 +6407,15 @@
         <v>77</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>31</v>
@@ -6424,15 +6430,15 @@
         <v>77</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>31</v>
@@ -6447,15 +6453,15 @@
         <v>70</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>31</v>
@@ -6470,15 +6476,15 @@
         <v>70</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>31</v>
@@ -6487,21 +6493,21 @@
         <v>1.15</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>50</v>
@@ -6516,15 +6522,15 @@
         <v>77</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -6539,15 +6545,15 @@
         <v>77</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>50</v>
@@ -6562,15 +6568,15 @@
         <v>70</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>50</v>
@@ -6585,15 +6591,15 @@
         <v>66</v>
       </c>
       <c r="G152" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B153" s="13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>50</v>
@@ -6602,21 +6608,21 @@
         <v>0.9</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>50</v>
@@ -6631,15 +6637,15 @@
         <v>70</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>45</v>
@@ -6654,15 +6660,15 @@
         <v>77</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>45</v>
@@ -6677,15 +6683,15 @@
         <v>70</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>45</v>
@@ -6700,15 +6706,15 @@
         <v>66</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>45</v>
@@ -6717,21 +6723,21 @@
         <v>1</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>66</v>
       </c>
       <c r="G158" s="13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>45</v>
@@ -6740,21 +6746,21 @@
         <v>15</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>45</v>
@@ -6769,15 +6775,15 @@
         <v>70</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>45</v>
@@ -6792,7 +6798,7 @@
         <v>77</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -6843,14 +6849,14 @@
     <hyperlink ref="G43" r:id="rId22" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Scarce, many counter-offers (car makers, integrators)."/>
     <hyperlink ref="G44" r:id="rId23" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Career step-up helps acceptance; counter-offers from current employer."/>
     <hyperlink ref="G48" r:id="rId24" display="Practice: high-risk projects carry 10–20% contingency (https://mastt.com/blogs/construction-contingency); PMI recommends sizing it to the risk rather than a flat % (https://www.pmi.org/learning/library/safety-numbers-contingency-planning-10120). Risk-based check: the reserve incl. rounding (€17.1k) covers about half of the extra media a 30% miss on share qualified would need (Funnel sensitivity: +€36.6k). Beyond that the binding limit is assessment slots, not money."/>
-    <hyperlink ref="G70" r:id="rId25" display="BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km = all of Berlin + ~60% of Brandenburg (own scaling) ≈ 4,800, up to ~8,600 incl. 2630 Fachkraft → 6,000. Previously: Berlin+Brandenburg hold roughly 7% of German employment (approx. 2.6M of ~35M employees subject to social insurance; own approximation of BA employment statistics, not looked up); assumed ~150–200k industrial electricians in DE, lower industrial density in the East → ~7,000 within 75 km of Grünheide. Order of magnitude only."/>
-    <hyperlink ref="G71" r:id="rId26" display="BA employment 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 26,400 incl. ~1,000 German/English-speaking Polish border workers (IAB-Regional 1/2020: 825 Polish commuters in machine/vehicle trades in Brandenburg, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf). Previously: Mechatroniker + Industriemechaniker are among the largest metal/electrical trades; ~25k within 75 km + ~2k German/English-speaking in Polish border towns (Słubice, Kostrzyn, Gorzów). 1,000–2,000 Poles already work at the plant (https://www.faire-mobilitaet.de/fachinformationen/brancheninformationen/automobilindustrie/polen-tesla/)."/>
-    <hyperlink ref="G72" r:id="rId27" display="BA employment 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km ≈ 2,000–2,500. Relocators (400) remain own estimate: Smaller local pool, but specialists relocate more: assume ~400 open to moving to Brandenburg in the window (national LinkedIn reach)."/>
-    <hyperlink ref="G73" r:id="rId28" display="BA employment 31.12.2025, Aufsicht codes 2519+2619+2629+2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km ≈ 2,200. Relocators: own estimate. Maintenance Meister/shift leads within 75 km; few relocate for a shift-lead job."/>
-    <hyperlink ref="G74" r:id="rId29" display="Derivation: persuadable share ≈ one year of voluntary leavers = turnover 12% a year × 41% of exits that are resignations = 4.9% ≈ 5% (IAB-Betriebspanel Brandenburg 2024, https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf). Cross-check: Gallup Engagement Index 2024, ~11% actively searching (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf)."/>
-    <hyperlink ref="G75" r:id="rId30" display="Derivation: persuadable share ≈ one year of voluntary leavers = turnover 12% a year × 41% of exits that are resignations = 4.9% ≈ 5% (IAB-Betriebspanel Brandenburg 2024, https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf). Cross-check: Gallup Engagement Index 2024, ~11% actively searching (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf)."/>
-    <hyperlink ref="G76" r:id="rId31" display="Derivation: persuadable share ≈ one year of voluntary leavers = turnover 12% a year × 41% of exits that are resignations = 4.9% ≈ 5% (IAB-Betriebspanel Brandenburg 2024, https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf). Cross-check: Gallup Engagement Index 2024, ~11% actively searching (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf)."/>
-    <hyperlink ref="G77" r:id="rId32" display="Derivation: persuadable share ≈ one year of voluntary leavers = turnover 12% a year × 41% of exits that are resignations = 4.9% ≈ 5% (IAB-Betriebspanel Brandenburg 2024, https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf). Cross-check: Gallup Engagement Index 2024, ~11% actively searching (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf)."/>
+    <hyperlink ref="G70" r:id="rId25" display="BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 3,417 × 0.6 + 2,708 = 4,758 → 4,800."/>
+    <hyperlink ref="G71" r:id="rId26" display="BA employment statistics 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 14,878 × 0.6 + 17,490 = 26,417 → 26,400."/>
+    <hyperlink ref="G72" r:id="rId27" display="BA employment statistics 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,206 × 0.6 + 1,254 = 1,978 → 2,000."/>
+    <hyperlink ref="G73" r:id="rId28" display="BA employment statistics 31.12.2025, Aufsicht codes 2519 + 2619 + 2629 + 2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,209 × 0.6 + 1,494 = 2,219 → 2,200."/>
+    <hyperlink ref="G74" r:id="rId29" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
+    <hyperlink ref="G75" r:id="rId30" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
+    <hyperlink ref="G76" r:id="rId31" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
+    <hyperlink ref="G77" r:id="rId32" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
     <hyperlink ref="G78" r:id="rId33" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 124,699 × 0.928 × 0.026 × 6/52 × 0.119 = 41. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
     <hyperlink ref="G79" r:id="rId34" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 84,727 × 0.928 × 0.026 × 6/52 × 0.119 = 28. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
     <hyperlink ref="G80" r:id="rId35" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 49,171 × 0.928 × 0.026 × 6/52 × 0.119 = 16. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
@@ -6865,26 +6871,26 @@
     <hyperlink ref="G100" r:id="rId44" display="Practice: budget rules use +20% ('safe') to +30% ('aggressive') per step (https://roaspig.com/blog/automated-rules-manage-meta-budgets/); Meta warns that large budget edits restart the learning phase (https://www.facebook.com/business/help/112167992830700). +25% once a week also gives Google bidding the 1–2 conversion cycles it needs between changes (https://support.google.com/google-ads/answer/6268637)."/>
     <hyperlink ref="G103" r:id="rId45" display="Display flag only (changes no number). No published standard for 'share of the reachable pool'. Above 1 in 4 of everyone reachable and open to a move, a 30% miss in response rates (the sensitivity test) cannot be absorbed from the same pool. Proxy: BA Engpassanalyse treats fewer than 2 job seekers per vacancy as the tightest band (https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html)."/>
     <hyperlink ref="G105" r:id="rId46" display="Queueing (Kingman / M/M/1): waiting time grows with ρ ÷ (1 − ρ): 4.0× at 80% use, 5.7× at 85%, 9.0× at 90% (https://en.wikipedia.org/wiki/Kingman%27s_formula); 'wait times go up quickly as server utilization exceeds 80%' (https://www.johndcook.com/blog/2009/01/30/server-utilization-joel-on-queuing/). The plan sits at 97%, which is why the client ask is +10–15 slots a week."/>
-    <hyperlink ref="L112" r:id="rId47" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105."/>
-    <hyperlink ref="L113" r:id="rId48" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158."/>
-    <hyperlink ref="L114" r:id="rId49" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53."/>
-    <hyperlink ref="L115" r:id="rId50" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35."/>
-    <hyperlink ref="L116" r:id="rId51" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. "/>
-    <hyperlink ref="L117" r:id="rId52" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. "/>
-    <hyperlink ref="L118" r:id="rId53" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. "/>
-    <hyperlink ref="L119" r:id="rId54" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. "/>
-    <hyperlink ref="L120" r:id="rId55" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. "/>
-    <hyperlink ref="L121" r:id="rId56" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. "/>
-    <hyperlink ref="L122" r:id="rId57" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. "/>
-    <hyperlink ref="L123" r:id="rId58" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. "/>
-    <hyperlink ref="L124" r:id="rId59" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. "/>
-    <hyperlink ref="L125" r:id="rId60" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. "/>
-    <hyperlink ref="L126" r:id="rId61" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.50 = 7.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 400 applications × 7.5% = 30 qualified."/>
-    <hyperlink ref="L127" r:id="rId62" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.50 = 11.0%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 200 applications × 11.0% = 22 qualified."/>
-    <hyperlink ref="L128" r:id="rId63" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. "/>
-    <hyperlink ref="L129" r:id="rId64" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. "/>
-    <hyperlink ref="L130" r:id="rId65" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. "/>
-    <hyperlink ref="L131" r:id="rId66" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. "/>
+    <hyperlink ref="L112" r:id="rId47" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L113" r:id="rId48" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L114" r:id="rId49" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L115" r:id="rId50" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L116" r:id="rId51" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 13.5% qualified = 1,520 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L117" r:id="rId52" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 19.8% qualified = 5,330 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L118" r:id="rId53" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 13.5% qualified = 630 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L119" r:id="rId54" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 9.0% qualified = 980 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L120" r:id="rId55" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L121" r:id="rId56" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.90 = 19.8%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L122" r:id="rId57" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L123" r:id="rId58" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L124" r:id="rId59" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.90 = 13.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 13.5% qualified = 260 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L125" r:id="rId60" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.90 = 9.0%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 9.0% qualified = 410 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L126" r:id="rId61" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.50 = 7.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 400 applications × 7.5% = 30 qualified. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L127" r:id="rId62" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.50 = 11.0%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 200 applications × 11.0% = 22 qualified. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L128" r:id="rId63" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 10.7% qualified = 560 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L129" r:id="rId64" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (22%) × 0.71 = 15.6%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 15.6% qualified = 1,970 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L130" r:id="rId65" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (15%) × 0.71 = 10.7%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 10.7% qualified = 230 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L131" r:id="rId66" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (10%) × 0.71 = 7.1%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 7.1% qualified = 360 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
     <hyperlink ref="G135" r:id="rId67" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 12% turnover (IAB-Betriebspanel Brandenburg 2024) × 5% of staff in maintenance (rule of thumb, https://michelbaudin.com/?p=1454) = 64. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 64 × 2.1 = 135, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
     <hyperlink ref="G136" r:id="rId68" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 12% turnover (IAB-Betriebspanel Brandenburg 2024) × 5% of staff in maintenance (rule of thumb, https://michelbaudin.com/?p=1454) = 64. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 64 × 2.1 = 135, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
     <hyperlink ref="G137" r:id="rId69" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 12% turnover (IAB-Betriebspanel Brandenburg 2024) × 5% of staff in maintenance (rule of thumb, https://michelbaudin.com/?p=1454) = 64. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 64 × 2.1 = 135, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
@@ -6939,12 +6945,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6955,46 +6961,46 @@
         <v>49</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7242,24 +7248,24 @@
       </c>
       <c r="M8" s="25" t="n">
         <f aca="false">SUMIFS(Channels!$W:$W,Channels!$C:$C,A8)</f>
-        <v>384.68</v>
+        <v>437.573507347073</v>
       </c>
       <c r="N8" s="27" t="n">
         <f aca="false">IF(M8&gt;0,O8/M8,0)</f>
-        <v>0.0941951752105646</v>
+        <v>0.0948087716146479</v>
       </c>
       <c r="O8" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V:$V,Channels!$C:$C,A8)</f>
-        <v>36.235</v>
+        <v>41.4858067226891</v>
       </c>
       <c r="P8" s="27" t="n">
         <f aca="false">IF($B$22&gt;0,O8/$B$22,0)</f>
-        <v>0.115293181818182</v>
+        <v>0.132000294117647</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -7287,34 +7293,34 @@
       </c>
       <c r="M9" s="29" t="n">
         <f aca="false">SUM(M5:M8)</f>
-        <v>2360.469219568</v>
+        <v>2413.36272691508</v>
       </c>
       <c r="N9" s="30" t="n">
         <f aca="false">IF(M9&gt;0,O9/M9,0)</f>
-        <v>0.12855379212096</v>
+        <v>0.127912009512784</v>
       </c>
       <c r="O9" s="31" t="n">
         <f aca="false">SUM(O5:O8)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="P9" s="30" t="n">
         <f aca="false">IF($B$22&gt;0,O9/$B$22,0)</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Assumptions!$D$7+Assumptions!$D$19</f>
@@ -7323,7 +7329,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B14" s="32" t="n">
         <f aca="false">Assumptions!$D$20</f>
@@ -7332,7 +7338,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">Assumptions!$D$22+Assumptions!$D$23+Assumptions!$D$24</f>
@@ -7341,7 +7347,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">B15+Assumptions!$D$25</f>
@@ -7350,7 +7356,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">B14-B15</f>
@@ -7359,7 +7365,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">B14-B16</f>
@@ -7386,7 +7392,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">MAX(0,B17-B13+1)</f>
@@ -7404,11 +7410,11 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">O9</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7417,7 +7423,7 @@
       </c>
       <c r="B24" s="35" t="n">
         <f aca="false">IF(B22&gt;0,B23/B22,IF(B23&gt;0,9.99,0))</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
       <c r="C24" s="24" t="str">
         <f aca="false">IF(B24&gt;1,"OVER CAPACITY – plan cannot be assessed",IF(B24&gt;Assumptions!$D$105,"Tight: little headroom","OK"))</f>
@@ -7426,28 +7432,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B25" s="27" t="n">
         <f aca="false">IF(O9&gt;0,Channels!U35/O9,0)</f>
-        <v>0.325428230770329</v>
+        <v>0.323941118353865</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">B22*B25</f>
-        <v>102.277443956389</v>
+        <v>101.810065768358</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7458,34 +7464,34 @@
         <v>49</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7502,37 +7508,37 @@
       </c>
       <c r="D30" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$N:$N,Channels!$C:$C,A30)</f>
-        <v>48.4695225</v>
+        <v>110.0740725</v>
       </c>
       <c r="E30" s="36" t="n">
         <f aca="false">IF(B30&gt;0,D30/B30,0)</f>
-        <v>1.61565075</v>
+        <v>3.66913575</v>
       </c>
       <c r="F30" s="25" t="n">
         <f aca="false">Funnel!F58</f>
-        <v>341</v>
+        <v>569</v>
       </c>
       <c r="G30" s="27" t="n">
         <f aca="false">Funnel!H58</f>
-        <v>0.195070660522273</v>
+        <v>0.116905264038832</v>
       </c>
       <c r="H30" s="37" t="n">
         <f aca="false">_xlfn.MAXIFS(Channels!$P:$P,Channels!$C:$C,A30,Channels!$AI:$AI,"&gt;0")</f>
-        <v>3786.00823045268</v>
+        <v>3786.00823045267</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K30" s="36" t="n">
         <f aca="false">IF(B30&gt;0,(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30,0)</f>
-        <v>1.33215075</v>
+        <v>3.38563575</v>
       </c>
       <c r="L30" s="36" t="n">
         <f aca="false">IF(B30&gt;0,K30,1000000000)</f>
-        <v>1.33215075</v>
+        <v>3.38563575</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7549,37 +7555,37 @@
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$N:$N,Channels!$C:$C,A31)</f>
-        <v>94.323654</v>
+        <v>550.4540265</v>
       </c>
       <c r="E31" s="36" t="n">
         <f aca="false">IF(B31&gt;0,D31/B31,0)</f>
-        <v>2.0960812</v>
+        <v>12.2323117</v>
       </c>
       <c r="F31" s="25" t="n">
         <f aca="false">Funnel!F59</f>
-        <v>1328</v>
+        <v>2932</v>
       </c>
       <c r="G31" s="27" t="n">
         <f aca="false">Funnel!H59</f>
-        <v>0.0893359346476816</v>
+        <v>0.0404632064161396</v>
       </c>
       <c r="H31" s="37" t="n">
         <f aca="false">_xlfn.MAXIFS(Channels!$P:$P,Channels!$C:$C,A31,Channels!$AI:$AI,"&gt;0")</f>
         <v>2056.93296602388</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K31" s="36" t="n">
         <f aca="false">IF(B31&gt;0,(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31,0)</f>
-        <v>2.0960812</v>
+        <v>12.2323117</v>
       </c>
       <c r="L31" s="36" t="n">
         <f aca="false">IF(B31&gt;0,K31,1000000000)</f>
-        <v>2.0960812</v>
+        <v>12.2323117</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7596,37 +7602,37 @@
       </c>
       <c r="D32" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$N:$N,Channels!$C:$C,A32)</f>
-        <v>20.89380825</v>
+        <v>45.38395575</v>
       </c>
       <c r="E32" s="36" t="n">
         <f aca="false">IF(B32&gt;0,D32/B32,0)</f>
-        <v>1.39292055</v>
+        <v>3.02559705</v>
       </c>
       <c r="F32" s="25" t="n">
         <f aca="false">Funnel!F60</f>
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="G32" s="27" t="n">
         <f aca="false">Funnel!H60</f>
-        <v>0.413135340555976</v>
+        <v>0.220572258093445</v>
       </c>
       <c r="H32" s="37" t="n">
         <f aca="false">_xlfn.MAXIFS(Channels!$P:$P,Channels!$C:$C,A32,Channels!$AI:$AI,"&gt;0")</f>
         <v>4206.67581161408</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K32" s="36" t="n">
         <f aca="false">IF(B32&gt;0,(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32,0)</f>
-        <v>1.39292055</v>
+        <v>3.02559705</v>
       </c>
       <c r="L32" s="36" t="n">
         <f aca="false">IF(B32&gt;0,K32,1000000000)</f>
-        <v>1.39292055</v>
+        <v>3.02559705</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7639,47 +7645,47 @@
       </c>
       <c r="C33" s="28" t="n">
         <f aca="false">O8</f>
-        <v>36.235</v>
+        <v>41.4858067226891</v>
       </c>
       <c r="D33" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$N:$N,Channels!$C:$C,A33)</f>
-        <v>8.750308</v>
+        <v>37.674448</v>
       </c>
       <c r="E33" s="36" t="n">
         <f aca="false">IF(B33&gt;0,D33/B33,0)</f>
-        <v>0.8750308</v>
+        <v>3.7674448</v>
       </c>
       <c r="F33" s="25" t="n">
         <f aca="false">Funnel!F61</f>
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="G33" s="27" t="n">
         <f aca="false">Funnel!H61</f>
-        <v>0.317850877192982</v>
+        <v>0.168641490742639</v>
       </c>
       <c r="H33" s="37" t="n">
         <f aca="false">_xlfn.MAXIFS(Channels!$P:$P,Channels!$C:$C,A33,Channels!$AI:$AI,"&gt;0")</f>
-        <v>10592.9695821991</v>
+        <v>4481.79271708684</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K33" s="36" t="n">
         <f aca="false">IF(B33&gt;0,(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33,0)</f>
-        <v>0.8750308</v>
+        <v>3.7674448</v>
       </c>
       <c r="L33" s="36" t="n">
         <f aca="false">IF(B33&gt;0,K33,1000000000)</f>
-        <v>0.8750308</v>
+        <v>3.7674448</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="str">
-        <f aca="false">"Verdict (base case; Summary C16 recomputes it live): Electricians. Biggest scarce volume (30); channel coverage ~"&amp;TEXT(E30,"0.0")&amp;"× openings, but only ~"&amp;TEXT(K30,"0.0")&amp;"× without the unproven Handwerk→Industrie initiative (K30) – the lowest of any role; no Polish route and no foreign-trained route by 31 Dec; and energy/grid, rail, aerospace, agencies and Tesla’s own lines want the same certificate. Supervisors need a bigger share of a smaller pool (G33) and have ~"&amp;TEXT(E33,"0.0")&amp;"× coverage, but are only 10 hires with an internal-promotion fallback (and the earliest cut-off, B20)."</f>
-        <v>Verdict (base case; Summary C16 recomputes it live): Electricians. Biggest scarce volume (30); channel coverage ~1.6× openings, but only ~1.3× without the unproven Handwerk→Industrie initiative (K30) – the lowest of any role; no Polish route and no foreign-trained route by 31 Dec; and energy/grid, rail, aerospace, agencies and Tesla’s own lines want the same certificate. Supervisors need a bigger share of a smaller pool (G33) and have ~0.9× coverage, but are only 10 hires with an internal-promotion fallback (and the earliest cut-off, B20).</v>
+        <f aca="false">"Verdict: "&amp;Summary!C16&amp;". Evidence for electricians in the base case: the scarcest trade in Brandenburg (KOFA 2026: 85.7% of industrial-electrician vacancies have no suitable unemployed candidate, against 41.4% across all occupations, https://www.kofa.de/media/Publikationen/Laendersteckbriefe/Brandenburg.pdf; BA shortage score 2.33); no Polish route and no foreign-trained route by 31 Dec; coverage without the unproven I2 only "&amp;TEXT(K30,"0.0")&amp;"×. Supervisors cost more per hire (€"&amp;TEXT(Budget!H24,"#,##0")&amp;") but are 10 hires with an internal-promotion fallback; automation has the thinnest coverage ("&amp;TEXT(K32,"0.0")&amp;"×) but is 15 hires with a foreign-trained route."</f>
+        <v>Verdict: Electricians (€70.7k, 40% of planned spend; see Funnel row 35). Evidence for electricians in the base case: the scarcest trade in Brandenburg (KOFA 2026: 85.7% of industrial-electrician vacancies have no suitable unemployed candidate, against 41.4% across all occupations, https://www.kofa.de/media/Publikationen/Laendersteckbriefe/Brandenburg.pdf; BA shortage score 2.33); no Polish route and no foreign-trained route by 31 Dec; coverage without the unproven I2 only 3.4×. Supervisors cost more per hire (€3,930) but are 10 hires with an internal-promotion fallback; automation has the thinnest coverage (3.0×) but is 15 hires with a foreign-trained route.</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -7717,12 +7723,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B40" s="26" t="n">
         <f aca="false">Assumptions!$D$66</f>
@@ -7731,225 +7737,225 @@
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B42" s="25" t="n">
         <f aca="false">O9</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="C42" s="26" t="n">
         <f aca="false">IF(($B$22)&gt;0,B42/($B$22),IF(B42&gt;0,9.99,0))</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
       <c r="D42" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B42&gt;0,$B$22/B42*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="E42" s="25" t="n">
         <f aca="false">$B$9-D42</f>
-        <v>1.249692</v>
+        <v>0</v>
       </c>
       <c r="F42" s="37" t="n">
         <f aca="false">Budget!$C$7*1</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="G42" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F42/Budget!$C$7-1,0)</f>
         <v>0</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B43" s="25" t="n">
         <f aca="false">O9/(1-$B$40)</f>
-        <v>433.496099086099</v>
+        <v>440.997251547084</v>
       </c>
       <c r="C43" s="26" t="n">
         <f aca="false">IF(($B$22)&gt;0,B43/($B$22),IF(B43&gt;0,9.99,0))</f>
-        <v>1.37930576981941</v>
+        <v>1.40317307310436</v>
       </c>
       <c r="D43" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B43&gt;0,$B$22/B43*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
-        <v>72.5002404746651</v>
+        <v>71.2670460378503</v>
       </c>
       <c r="E43" s="25" t="n">
         <f aca="false">$B$9-D43</f>
-        <v>27.4997595253349</v>
+        <v>28.7329539621498</v>
       </c>
       <c r="F43" s="37" t="n">
         <f aca="false">Budget!$C$7*1/(1-$B$40)</f>
-        <v>276319.472251517</v>
+        <v>251735.66810795</v>
       </c>
       <c r="G43" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F43/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B44" s="25" t="n">
         <f aca="false">O9/(1-$B$40)</f>
-        <v>433.496099086099</v>
+        <v>440.997251547084</v>
       </c>
       <c r="C44" s="26" t="n">
         <f aca="false">IF(($B$22)&gt;0,B44/($B$22),IF(B44&gt;0,9.99,0))</f>
-        <v>1.37930576981941</v>
+        <v>1.40317307310436</v>
       </c>
       <c r="D44" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B44&gt;0,$B$22/B44*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
-        <v>72.5002404746651</v>
+        <v>71.2670460378503</v>
       </c>
       <c r="E44" s="25" t="n">
         <f aca="false">$B$9-D44</f>
-        <v>27.4997595253349</v>
+        <v>28.7329539621498</v>
       </c>
       <c r="F44" s="37" t="n">
         <f aca="false">Budget!$C$7*1/(1-$B$40)</f>
-        <v>276319.472251517</v>
+        <v>251735.66810795</v>
       </c>
       <c r="G44" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F44/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B45" s="25" t="n">
         <f aca="false">O9</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="C45" s="26" t="n">
         <f aca="false">IF(($B$22)&gt;0,B45/($B$22),IF(B45&gt;0,9.99,0))</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
       <c r="D45" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B45&gt;0,$B$22/B45*$B$9,$B$9),MIN(B5,D30*(1-$B$40))+MIN(B6,D31*(1-$B$40))+MIN(B7,D32*(1-$B$40))+MIN(B8,D33*(1-$B$40)))</f>
-        <v>95.750881375</v>
+        <v>100</v>
       </c>
       <c r="E45" s="25" t="n">
         <f aca="false">$B$9-D45</f>
-        <v>4.24911862499999</v>
+        <v>0</v>
       </c>
       <c r="F45" s="37" t="n">
         <f aca="false">Budget!$C$7*1/(1-$B$40)</f>
-        <v>276319.472251517</v>
+        <v>251735.66810795</v>
       </c>
       <c r="G45" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F45/Budget!$C$7-1,0)</f>
         <v>0.428571428571429</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B46" s="25" t="n">
         <f aca="false">O9</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="C46" s="26" t="n">
         <f aca="false">IF(($B$22)&gt;0,B46/($B$22),IF(B46&gt;0,9.99,0))</f>
-        <v>0.965514038873584</v>
+        <v>0.98222115117305</v>
       </c>
       <c r="D46" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B46&gt;0,$B$22/B46*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="E46" s="25" t="n">
         <f aca="false">$B$9-D46</f>
-        <v>1.249692</v>
+        <v>0</v>
       </c>
       <c r="F46" s="37" t="n">
         <f aca="false">Budget!$C$7*(1+$B$40)</f>
-        <v>251450.71974888</v>
+        <v>229079.457978235</v>
       </c>
       <c r="G46" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F46/Budget!$C$7-1,0)</f>
         <v>0.3</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B47" s="25" t="n">
         <f aca="false">O9</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="C47" s="26" t="n">
         <f aca="false">IF(($B$22*(1-$B$40))&gt;0,B47/($B$22*(1-$B$40)),IF(B47&gt;0,9.99,0))</f>
-        <v>1.37930576981941</v>
+        <v>1.40317307310436</v>
       </c>
       <c r="D47" s="34" t="n">
         <f aca="false">MIN($B$9,IF(B47&gt;0,$B$22*(1-$B$40)/B47*$B$9,$B$9),MIN(B5,D30*1)+MIN(B6,D31*1)+MIN(B7,D32*1)+MIN(B8,D33*1))</f>
-        <v>72.5002404746651</v>
+        <v>71.2670460378503</v>
       </c>
       <c r="E47" s="25" t="n">
         <f aca="false">$B$9-D47</f>
-        <v>27.4997595253349</v>
+        <v>28.7329539621498</v>
       </c>
       <c r="F47" s="37" t="n">
         <f aca="false">Budget!$C$7*1</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="G47" s="26" t="n">
         <f aca="false">IF(Budget!$C$7&gt;0,F47/Budget!$C$7-1,0)</f>
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="24" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D49" s="8" t="str">
         <f aca="false">INDEX(A43:A47,MATCH(MAX(E43:E47),E43:E47,0))</f>
@@ -7958,7 +7964,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -7980,7 +7986,7 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7988,34 +7994,34 @@
         <v>283</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8024,15 +8030,15 @@
       </c>
       <c r="B58" s="25" t="n">
         <f aca="false">Assumptions!$D$70</f>
-        <v>6000</v>
+        <v>4800</v>
       </c>
       <c r="C58" s="26" t="n">
         <f aca="false">Assumptions!$D$74</f>
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="D58" s="25" t="n">
         <f aca="false">B58*C58</f>
-        <v>300</v>
+        <v>528</v>
       </c>
       <c r="E58" s="25" t="n">
         <f aca="false">Assumptions!$D$78</f>
@@ -8040,7 +8046,7 @@
       </c>
       <c r="F58" s="25" t="n">
         <f aca="false">D58+E58</f>
-        <v>341</v>
+        <v>569</v>
       </c>
       <c r="G58" s="25" t="n">
         <f aca="false">Funnel!O5-SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E",Channels!$C:$C,A58)</f>
@@ -8048,19 +8054,19 @@
       </c>
       <c r="H58" s="26" t="n">
         <f aca="false">IF(F58&gt;0,G58/F58,0)</f>
-        <v>0.195070660522273</v>
+        <v>0.116905264038832</v>
       </c>
       <c r="I58" s="25" t="n">
         <f aca="false">SUMIFS(Channels!$K:$K,Channels!$C:$C,A58)-SUMIFS(Channels!$K:$K,Channels!$A:$A,"I2-E",Channels!$C:$C,A58)</f>
-        <v>125.1525</v>
+        <v>320.7225</v>
       </c>
       <c r="J58" s="26" t="n">
         <f aca="false">IF(F58&gt;0,I58/F58,0)</f>
-        <v>0.367016129032258</v>
+        <v>0.56365992970123</v>
       </c>
       <c r="K58" s="2" t="str">
         <f aca="false">IF(H58&gt;Assumptions!$D$103,"Very hard",IF(H58&gt;Assumptions!$D$104,"Tight","Comfortable"))</f>
-        <v>Tight</v>
+        <v>Comfortable</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8069,15 +8075,15 @@
       </c>
       <c r="B59" s="25" t="n">
         <f aca="false">Assumptions!$D$71</f>
-        <v>26000</v>
+        <v>26400</v>
       </c>
       <c r="C59" s="26" t="n">
         <f aca="false">Assumptions!$D$75</f>
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="D59" s="25" t="n">
         <f aca="false">B59*C59</f>
-        <v>1300</v>
+        <v>2904</v>
       </c>
       <c r="E59" s="25" t="n">
         <f aca="false">Assumptions!$D$79</f>
@@ -8085,7 +8091,7 @@
       </c>
       <c r="F59" s="25" t="n">
         <f aca="false">D59+E59</f>
-        <v>1328</v>
+        <v>2932</v>
       </c>
       <c r="G59" s="25" t="n">
         <f aca="false">Funnel!O6-SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E",Channels!$C:$C,A59)</f>
@@ -8093,15 +8099,15 @@
       </c>
       <c r="H59" s="26" t="n">
         <f aca="false">IF(F59&gt;0,G59/F59,0)</f>
-        <v>0.0893359346476816</v>
+        <v>0.0404632064161396</v>
       </c>
       <c r="I59" s="25" t="n">
         <f aca="false">SUMIFS(Channels!$K:$K,Channels!$C:$C,A59)-SUMIFS(Channels!$K:$K,Channels!$A:$A,"I2-E",Channels!$C:$C,A59)</f>
-        <v>252.0116</v>
+        <v>1480.6456</v>
       </c>
       <c r="J59" s="26" t="n">
         <f aca="false">IF(F59&gt;0,I59/F59,0)</f>
-        <v>0.189767771084337</v>
+        <v>0.504995088676671</v>
       </c>
       <c r="K59" s="2" t="str">
         <f aca="false">IF(H59&gt;Assumptions!$D$103,"Very hard",IF(H59&gt;Assumptions!$D$104,"Tight","Comfortable"))</f>
@@ -8114,15 +8120,15 @@
       </c>
       <c r="B60" s="25" t="n">
         <f aca="false">Assumptions!$D$72</f>
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="C60" s="26" t="n">
         <f aca="false">Assumptions!$D$76</f>
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="D60" s="25" t="n">
         <f aca="false">B60*C60</f>
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="E60" s="25" t="n">
         <f aca="false">Assumptions!$D$80</f>
@@ -8130,7 +8136,7 @@
       </c>
       <c r="F60" s="25" t="n">
         <f aca="false">D60+E60</f>
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="G60" s="25" t="n">
         <f aca="false">Funnel!O7-SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E",Channels!$C:$C,A60)</f>
@@ -8138,19 +8144,19 @@
       </c>
       <c r="H60" s="26" t="n">
         <f aca="false">IF(F60&gt;0,G60/F60,0)</f>
-        <v>0.413135340555976</v>
+        <v>0.220572258093445</v>
       </c>
       <c r="I60" s="25" t="n">
         <f aca="false">SUMIFS(Channels!$K:$K,Channels!$C:$C,A60)-SUMIFS(Channels!$K:$K,Channels!$A:$A,"I2-E",Channels!$C:$C,A60)</f>
-        <v>72.8445</v>
+        <v>159.2295</v>
       </c>
       <c r="J60" s="26" t="n">
         <f aca="false">IF(F60&gt;0,I60/F60,0)</f>
-        <v>0.578130952380952</v>
+        <v>0.674701271186441</v>
       </c>
       <c r="K60" s="2" t="str">
         <f aca="false">IF(H60&gt;Assumptions!$D$103,"Very hard",IF(H60&gt;Assumptions!$D$104,"Tight","Comfortable"))</f>
-        <v>Very hard</v>
+        <v>Tight</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8163,11 +8169,11 @@
       </c>
       <c r="C61" s="26" t="n">
         <f aca="false">Assumptions!$D$77</f>
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="D61" s="25" t="n">
         <f aca="false">B61*C61</f>
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="E61" s="25" t="n">
         <f aca="false">Assumptions!$D$81</f>
@@ -8175,32 +8181,32 @@
       </c>
       <c r="F61" s="25" t="n">
         <f aca="false">D61+E61</f>
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="G61" s="25" t="n">
         <f aca="false">Funnel!O8-SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E",Channels!$C:$C,A61)</f>
-        <v>36.235</v>
+        <v>41.4858067226891</v>
       </c>
       <c r="H61" s="26" t="n">
         <f aca="false">IF(F61&gt;0,G61/F61,0)</f>
-        <v>0.317850877192982</v>
+        <v>0.168641490742639</v>
       </c>
       <c r="I61" s="25" t="n">
         <f aca="false">SUMIFS(Channels!$K:$K,Channels!$C:$C,A61)-SUMIFS(Channels!$K:$K,Channels!$A:$A,"I2-E",Channels!$C:$C,A61)</f>
-        <v>36.235</v>
+        <v>157.765</v>
       </c>
       <c r="J61" s="26" t="n">
         <f aca="false">IF(F61&gt;0,I61/F61,0)</f>
-        <v>0.317850877192982</v>
+        <v>0.641321138211382</v>
       </c>
       <c r="K61" s="2" t="str">
         <f aca="false">IF(H61&gt;Assumptions!$D$103,"Very hard",IF(H61&gt;Assumptions!$D$104,"Tight","Comfortable"))</f>
-        <v>Very hard</v>
+        <v>Tight</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -8260,17 +8266,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>50</v>
@@ -8285,12 +8291,12 @@
         <v>57</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B5" s="25" t="n">
         <f aca="false">Assumptions!$D$135</f>
@@ -8315,7 +8321,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B6" s="26" t="n">
         <f aca="false">Assumptions!$D$139</f>
@@ -8336,7 +8342,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">B5*B6</f>
@@ -8361,7 +8367,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B8" s="26" t="n">
         <f aca="false">Assumptions!$D$140</f>
@@ -8382,7 +8388,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$148</f>
@@ -8403,7 +8409,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B10" s="37" t="n">
         <f aca="false">B5*Assumptions!$D$146</f>
@@ -8428,7 +8434,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">IF(B7&gt;0,B10/B7,0)</f>
@@ -8453,7 +8459,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">B7*B8*B9</f>
@@ -8478,7 +8484,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">Assumptions!$D$141</f>
@@ -8503,7 +8509,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B14" s="26" t="n">
         <f aca="false">Assumptions!$D$145</f>
@@ -8524,7 +8530,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">B13*B14*B9</f>
@@ -8549,7 +8555,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B16" s="37" t="n">
         <f aca="false">B15*Assumptions!$D$147</f>
@@ -8574,7 +8580,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(B13&gt;0,B16/B13,0)</f>
@@ -8593,12 +8599,12 @@
         <v>123.165</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">B12+B15</f>
@@ -8623,7 +8629,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B19" s="37" t="n">
         <f aca="false">B10+B16</f>
@@ -8648,7 +8654,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B20" s="37" t="n">
         <f aca="false">IF(B18&gt;0,B19/B18,0)</f>
@@ -8673,12 +8679,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">Assumptions!$D$149</f>
@@ -8687,7 +8693,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B25" s="27" t="n">
         <f aca="false">Assumptions!$D$150</f>
@@ -8696,7 +8702,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B26" s="25" t="n">
         <f aca="false">B24*B25</f>
@@ -8705,7 +8711,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B27" s="37" t="n">
         <f aca="false">Assumptions!$D$151</f>
@@ -8714,7 +8720,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B28" s="26" t="n">
         <f aca="false">Assumptions!$D$152</f>
@@ -8723,7 +8729,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B29" s="28" t="n">
         <f aca="false">B26*B28</f>
@@ -8732,7 +8738,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B30" s="27" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$153</f>
@@ -8741,7 +8747,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B31" s="28" t="n">
         <f aca="false">B29*B30</f>
@@ -8750,7 +8756,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B32" s="37" t="n">
         <f aca="false">B26*B27</f>
@@ -8759,7 +8765,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B33" s="37" t="n">
         <f aca="false">Assumptions!$D$154</f>
@@ -8768,7 +8774,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B34" s="37" t="n">
         <f aca="false">IF(B31&gt;0,(B32+B33)/B31,0)</f>
@@ -8777,12 +8783,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B38" s="39" t="n">
         <f aca="false">B44+B45</f>
@@ -8791,7 +8797,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B39" s="26" t="n">
         <f aca="false">Assumptions!$D$156</f>
@@ -8800,7 +8806,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B40" s="25" t="n">
         <f aca="false">Assumptions!$D$157</f>
@@ -8809,7 +8815,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B41" s="27" t="n">
         <f aca="false">Funnel!$G$6*Assumptions!$D$158</f>
@@ -8818,7 +8824,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B42" s="28" t="n">
         <f aca="false">Assumptions!$D$10*Assumptions!$D$12</f>
@@ -8827,7 +8833,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B43" s="28" t="n">
         <f aca="false">MIN(B40*B39*B41,B42)</f>
@@ -8836,7 +8842,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B44" s="39" t="n">
         <f aca="false">Assumptions!$D$155</f>
@@ -8845,7 +8851,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B45" s="39" t="n">
         <f aca="false">Assumptions!$D$159/60*Assumptions!$D$160</f>
@@ -8854,7 +8860,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B46" s="37" t="n">
         <f aca="false">Assumptions!$D$161</f>
@@ -8863,7 +8869,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B47" s="25" t="n">
         <f aca="false">IF(B41*B39&gt;0,B43/B41/B39,0)</f>
@@ -8872,7 +8878,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B48" s="37" t="n">
         <f aca="false">IF(B43&gt;0,(B47*B38+B46)/B43,0)</f>
@@ -8881,50 +8887,50 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="24" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="24" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C53" s="26" t="n">
         <f aca="false">(Assumptions!$D$97+Assumptions!$D$98)</f>
@@ -8936,47 +8942,47 @@
       </c>
       <c r="E53" s="28" t="n">
         <f aca="false">(SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1a-E")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1a-M")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1a-A")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1a-S"))*(Assumptions!$D$97+Assumptions!$D$98)+(SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1b-E")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1b-M")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1b-A")+SUMIFS(Channels!$V:$V,Channels!$A:$A,"I1b-S"))*(Weekly!$D$4+Weekly!$D$5)</f>
-        <v>12.6084</v>
+        <v>14.8359</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G53" s="25" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E53*Assumptions!$D$93,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I53" s="25" t="n">
         <f aca="false">MIN(G53,MAX(1,ROUNDUP(E53*Assumptions!$D$95,0)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="24" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C54" s="26" t="n">
         <f aca="false">(Weekly!$D$4*4/7+Weekly!$D$5+Weekly!$D$6*3/7)</f>
-        <v>0.218571428571429</v>
+        <v>0.287142857142857</v>
       </c>
       <c r="D54" s="37" t="n">
         <f aca="false">B33+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I2-E")*C54</f>
-        <v>4872</v>
+        <v>6024</v>
       </c>
       <c r="E54" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I2-E")*C54</f>
-        <v>6.55714285714286</v>
+        <v>8.61428571428571</v>
       </c>
       <c r="F54" s="37" t="n">
         <f aca="false">IF(B28&gt;0,B27/B28,0)</f>
@@ -8984,7 +8990,7 @@
       </c>
       <c r="G54" s="25" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E54*Assumptions!$D$93,0))</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H54" s="37" t="n">
         <f aca="false">ROUND(F54*Assumptions!$D$94/10,0)*10</f>
@@ -8992,34 +8998,34 @@
       </c>
       <c r="I54" s="25" t="n">
         <f aca="false">MIN(G54,MAX(1,ROUNDUP(E54*Assumptions!$D$95,0)))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="37" t="n">
         <f aca="false">MAX(H54,ROUND(F54*Assumptions!$D$96/10,0)*10)</f>
         <v>840</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="24" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C55" s="26" t="n">
         <f aca="false">(Weekly!$D$5+Weekly!$D$6)</f>
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="D55" s="37" t="n">
         <f aca="false">B46+SUMIFS(Channels!$X:$X,Channels!$A:$A,"I3-M")*C55</f>
-        <v>2153.24675324675</v>
+        <v>2542.85714285714</v>
       </c>
       <c r="E55" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V:$V,Channels!$A:$A,"I3-M")*C55</f>
-        <v>13.0909090909091</v>
+        <v>16</v>
       </c>
       <c r="F55" s="37" t="n">
         <f aca="false">IF(B39&gt;0,B38/B39,0)</f>
@@ -9027,7 +9033,7 @@
       </c>
       <c r="G55" s="25" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E55*Assumptions!$D$93,0))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H55" s="37" t="n">
         <f aca="false">ROUND(F55*Assumptions!$D$94/10,0)*10</f>
@@ -9035,19 +9041,19 @@
       </c>
       <c r="I55" s="25" t="n">
         <f aca="false">MIN(G55,MAX(1,ROUNDUP(E55*Assumptions!$D$95,0)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="37" t="n">
         <f aca="false">MAX(H55,ROUND(F55*Assumptions!$D$96/10,0)*10)</f>
         <v>200</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -9085,17 +9091,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9109,100 +9115,100 @@
         <v>283</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>284</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>287</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AI4" s="12" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9807,11 +9813,11 @@
       </c>
       <c r="J9" s="25" t="n">
         <f aca="false">IF(AND(OR(E9="CPC",E9="Slot"),NOT(N(G9)&gt;0)),0,IF(E9="Slot",Assumptions!H116*G9,Assumptions!H116))</f>
-        <v>450</v>
+        <v>1520</v>
       </c>
       <c r="K9" s="28" t="n">
         <f aca="false">J9*I9</f>
-        <v>60.75</v>
+        <v>205.2</v>
       </c>
       <c r="L9" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C9,Funnel!$A$5:$A$8,0))*M9</f>
@@ -9823,7 +9829,7 @@
       </c>
       <c r="N9" s="28" t="n">
         <f aca="false">K9*L9</f>
-        <v>19.13625</v>
+        <v>64.638</v>
       </c>
       <c r="O9" s="37" t="n">
         <f aca="false">IF(I9&gt;0,H9/I9,0)</f>
@@ -9831,11 +9837,11 @@
       </c>
       <c r="P9" s="37" t="n">
         <f aca="false">IF(N9&gt;0,(N9/L9/I9*H9+Assumptions!J116)/N9,0)</f>
-        <v>3786.00823045268</v>
+        <v>3786.00823045267</v>
       </c>
       <c r="Q9" s="41" t="n">
         <f aca="false">P9+ROW()/1000000</f>
-        <v>3786.00823945268</v>
+        <v>3786.00823945267</v>
       </c>
       <c r="R9" s="25" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C9)*($Q$5:$Q$34&lt;Q9))+1</f>
@@ -9903,7 +9909,7 @@
       </c>
       <c r="AH9" s="28" t="n">
         <f aca="false">MAX(0,N9-AG9)</f>
-        <v>18.938152173913</v>
+        <v>64.4399021739131</v>
       </c>
       <c r="AI9" s="28" t="n">
         <f aca="false">MIN(AH9,MAX(0,T9-S9))</f>
@@ -9948,11 +9954,11 @@
       </c>
       <c r="J10" s="25" t="n">
         <f aca="false">IF(AND(OR(E10="CPC",E10="Slot"),NOT(N(G10)&gt;0)),0,IF(E10="Slot",Assumptions!H117*G10,Assumptions!H117))</f>
-        <v>600</v>
+        <v>5330</v>
       </c>
       <c r="K10" s="28" t="n">
         <f aca="false">J10*I10</f>
-        <v>118.8</v>
+        <v>1055.34</v>
       </c>
       <c r="L10" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C10,Funnel!$A$5:$A$8,0))*M10</f>
@@ -9964,7 +9970,7 @@
       </c>
       <c r="N10" s="28" t="n">
         <f aca="false">K10*L10</f>
-        <v>44.1045</v>
+        <v>391.794975</v>
       </c>
       <c r="O10" s="37" t="n">
         <f aca="false">IF(I10&gt;0,H10/I10,0)</f>
@@ -10044,7 +10050,7 @@
       </c>
       <c r="AH10" s="28" t="n">
         <f aca="false">MAX(0,N10-AG10)</f>
-        <v>43.762073757764</v>
+        <v>391.452548757764</v>
       </c>
       <c r="AI10" s="28" t="n">
         <f aca="false">MIN(AH10,MAX(0,T10-S10))</f>
@@ -10089,11 +10095,11 @@
       </c>
       <c r="J11" s="25" t="n">
         <f aca="false">IF(AND(OR(E11="CPC",E11="Slot"),NOT(N(G11)&gt;0)),0,IF(E11="Slot",Assumptions!H118*G11,Assumptions!H118))</f>
-        <v>250</v>
+        <v>630</v>
       </c>
       <c r="K11" s="28" t="n">
         <f aca="false">J11*I11</f>
-        <v>33.75</v>
+        <v>85.05</v>
       </c>
       <c r="L11" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C11,Funnel!$A$5:$A$8,0))*M11</f>
@@ -10105,7 +10111,7 @@
       </c>
       <c r="N11" s="28" t="n">
         <f aca="false">K11*L11</f>
-        <v>9.568125</v>
+        <v>24.111675</v>
       </c>
       <c r="O11" s="37" t="n">
         <f aca="false">IF(I11&gt;0,H11/I11,0)</f>
@@ -10125,7 +10131,7 @@
       </c>
       <c r="S11" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C11)*($Q$5:$Q$34&lt;Q11)*$AH$5:$AH$34)</f>
-        <v>9.81896934375</v>
+        <v>14.02894434375</v>
       </c>
       <c r="T11" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C11,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C11)</f>
@@ -10133,19 +10139,19 @@
       </c>
       <c r="U11" s="42" t="n">
         <f aca="false">AG11+AI11</f>
-        <v>4.75552081424581</v>
+        <v>0.545545814245812</v>
       </c>
       <c r="V11" s="28" t="n">
         <f aca="false">IF(L11&gt;0,U11/L11,0)</f>
-        <v>16.7743238597736</v>
+        <v>1.92432385977359</v>
       </c>
       <c r="W11" s="25" t="n">
         <f aca="false">IF(I11&gt;0,V11/I11,0)</f>
-        <v>124.254250813138</v>
+        <v>14.2542508131377</v>
       </c>
       <c r="X11" s="37" t="n">
         <f aca="false">IF(E11="Slot",IF(N(G11)&gt;0,ROUNDUP(W11/G11,0)*MAX(0,F11),0),W11*H11)</f>
-        <v>20004.9343809152</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="Y11" s="37" t="n">
         <f aca="false">IF(U11&gt;0,Assumptions!J118,0)</f>
@@ -10157,7 +10163,7 @@
       </c>
       <c r="AA11" s="37" t="n">
         <f aca="false">X11+Y11</f>
-        <v>20004.9343809152</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="AB11" s="37" t="n">
         <f aca="false">IF(U11&gt;0,(X11+Y11)/U11,"–")</f>
@@ -10185,11 +10191,11 @@
       </c>
       <c r="AH11" s="28" t="n">
         <f aca="false">MAX(0,N11-AG11)</f>
-        <v>9.38983695652174</v>
+        <v>23.9333869565217</v>
       </c>
       <c r="AI11" s="28" t="n">
         <f aca="false">MIN(AH11,MAX(0,T11-S11))</f>
-        <v>4.57723277076755</v>
+        <v>0.367257770767552</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10230,11 +10236,11 @@
       </c>
       <c r="J12" s="25" t="n">
         <f aca="false">IF(AND(OR(E12="CPC",E12="Slot"),NOT(N(G12)&gt;0)),0,IF(E12="Slot",Assumptions!H119*G12,Assumptions!H119))</f>
-        <v>200</v>
+        <v>980</v>
       </c>
       <c r="K12" s="28" t="n">
         <f aca="false">J12*I12</f>
-        <v>18</v>
+        <v>88.2</v>
       </c>
       <c r="L12" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C12,Funnel!$A$5:$A$8,0))*M12</f>
@@ -10246,7 +10252,7 @@
       </c>
       <c r="N12" s="28" t="n">
         <f aca="false">K12*L12</f>
-        <v>4.284</v>
+        <v>20.9916</v>
       </c>
       <c r="O12" s="37" t="n">
         <f aca="false">IF(I12&gt;0,H12/I12,0)</f>
@@ -10266,7 +10272,7 @@
       </c>
       <c r="S12" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C12)*($Q$5:$Q$34&lt;Q12)*$AH$5:$AH$34)</f>
-        <v>3.79202425</v>
+        <v>10.43222425</v>
       </c>
       <c r="T12" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C12,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C12)</f>
@@ -10274,19 +10280,19 @@
       </c>
       <c r="U12" s="42" t="n">
         <f aca="false">AG12+AI12</f>
-        <v>4.284</v>
+        <v>0.0997826086956522</v>
       </c>
       <c r="V12" s="28" t="n">
         <f aca="false">IF(L12&gt;0,U12/L12,0)</f>
-        <v>18</v>
+        <v>0.419254658385093</v>
       </c>
       <c r="W12" s="25" t="n">
         <f aca="false">IF(I12&gt;0,V12/I12,0)</f>
-        <v>200</v>
+        <v>4.6583850931677</v>
       </c>
       <c r="X12" s="37" t="n">
         <f aca="false">IF(E12="Slot",IF(N(G12)&gt;0,ROUNDUP(W12/G12,0)*MAX(0,F12),0),W12*H12)</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="Y12" s="37" t="n">
         <f aca="false">IF(U12&gt;0,Assumptions!J119,0)</f>
@@ -10298,7 +10304,7 @@
       </c>
       <c r="AA12" s="37" t="n">
         <f aca="false">X12+Y12</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="AB12" s="37" t="n">
         <f aca="false">IF(U12&gt;0,(X12+Y12)/U12,"–")</f>
@@ -10310,7 +10316,7 @@
       </c>
       <c r="AD12" s="2" t="str">
         <f aca="false">IF(AND(AH12&gt;0,AI12&gt;=AH12*0.999),"Used to capacity",IF(AI12&gt;0,"Marginal (fills the gap)",IF(Z12&gt;0,"Test only (wk 1–2)","Not used")))</f>
-        <v>Used to capacity</v>
+        <v>Test only (wk 1–2)</v>
       </c>
       <c r="AE12" s="28" t="n">
         <f aca="false">IF(H12&gt;0,Z12/H12,0)</f>
@@ -10326,11 +10332,11 @@
       </c>
       <c r="AH12" s="28" t="n">
         <f aca="false">MAX(0,N12-AG12)</f>
-        <v>4.18421739130435</v>
+        <v>20.8918173913043</v>
       </c>
       <c r="AI12" s="28" t="n">
         <f aca="false">MIN(AH12,MAX(0,T12-S12))</f>
-        <v>4.18421739130435</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10689,7 +10695,7 @@
       </c>
       <c r="S15" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C15)*($Q$5:$Q$34&lt;Q15)*$AH$5:$AH$34)</f>
-        <v>8.90042934375</v>
+        <v>13.11040434375</v>
       </c>
       <c r="T15" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C15,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C15)</f>
@@ -10830,7 +10836,7 @@
       </c>
       <c r="S16" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C16)*($Q$5:$Q$34&lt;Q16)*$AH$5:$AH$34)</f>
-        <v>3.53498425</v>
+        <v>10.17518425</v>
       </c>
       <c r="T16" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C16,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C16)</f>
@@ -10838,19 +10844,19 @@
       </c>
       <c r="U16" s="42" t="n">
         <f aca="false">AG16+AI16</f>
-        <v>0.25704</v>
+        <v>0</v>
       </c>
       <c r="V16" s="28" t="n">
         <f aca="false">IF(L16&gt;0,U16/L16,0)</f>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W16" s="25" t="n">
         <f aca="false">IF(I16&gt;0,V16/I16,0)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X16" s="37" t="n">
         <f aca="false">IF(E16="Slot",IF(N(G16)&gt;0,ROUNDUP(W16/G16,0)*MAX(0,F16),0),W16*H16)</f>
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="37" t="n">
         <f aca="false">IF(U16&gt;0,Assumptions!J123,0)</f>
@@ -10862,11 +10868,11 @@
       </c>
       <c r="AA16" s="37" t="n">
         <f aca="false">X16+Y16</f>
-        <v>1449</v>
-      </c>
-      <c r="AB16" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="37" t="str">
         <f aca="false">IF(U16&gt;0,(X16+Y16)/U16,"–")</f>
-        <v>5637.25490196078</v>
+        <v>–</v>
       </c>
       <c r="AC16" s="25" t="n">
         <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q16))+1</f>
@@ -10874,7 +10880,7 @@
       </c>
       <c r="AD16" s="2" t="str">
         <f aca="false">IF(AND(AH16&gt;0,AI16&gt;=AH16*0.999),"Used to capacity",IF(AI16&gt;0,"Marginal (fills the gap)",IF(Z16&gt;0,"Test only (wk 1–2)","Not used")))</f>
-        <v>Used to capacity</v>
+        <v>Not used</v>
       </c>
       <c r="AE16" s="28" t="n">
         <f aca="false">IF(H16&gt;0,Z16/H16,0)</f>
@@ -10894,7 +10900,7 @@
       </c>
       <c r="AI16" s="28" t="n">
         <f aca="false">MIN(AH16,MAX(0,T16-S16))</f>
-        <v>0.25704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,11 +10941,11 @@
       </c>
       <c r="J17" s="25" t="n">
         <f aca="false">IF(AND(OR(E17="CPC",E17="Slot"),NOT(N(G17)&gt;0)),0,IF(E17="Slot",Assumptions!H124*G17,Assumptions!H124))</f>
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="K17" s="28" t="n">
         <f aca="false">J17*I17</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
       <c r="L17" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C17,Funnel!$A$5:$A$8,0))*M17</f>
@@ -10951,7 +10957,7 @@
       </c>
       <c r="N17" s="28" t="n">
         <f aca="false">K17*L17</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="O17" s="37" t="n">
         <f aca="false">IF(I17&gt;0,H17/I17,0)</f>
@@ -10979,19 +10985,19 @@
       </c>
       <c r="U17" s="42" t="n">
         <f aca="false">AG17+AI17</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="V17" s="28" t="n">
         <f aca="false">IF(L17&gt;0,U17/L17,0)</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
       <c r="W17" s="25" t="n">
         <f aca="false">IF(I17&gt;0,V17/I17,0)</f>
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="X17" s="37" t="n">
         <f aca="false">IF(E17="Slot",IF(N(G17)&gt;0,ROUNDUP(W17/G17,0)*MAX(0,F17),0),W17*H17)</f>
-        <v>14400</v>
+        <v>24960</v>
       </c>
       <c r="Y17" s="37" t="n">
         <f aca="false">IF(U17&gt;0,Assumptions!J124,0)</f>
@@ -11003,7 +11009,7 @@
       </c>
       <c r="AA17" s="37" t="n">
         <f aca="false">X17+Y17</f>
-        <v>14400</v>
+        <v>24960</v>
       </c>
       <c r="AB17" s="37" t="n">
         <f aca="false">IF(U17&gt;0,(X17+Y17)/U17,"–")</f>
@@ -11031,11 +11037,11 @@
       </c>
       <c r="AH17" s="28" t="n">
         <f aca="false">MAX(0,N17-AG17)</f>
-        <v>5.44187109375</v>
+        <v>9.65184609375</v>
       </c>
       <c r="AI17" s="28" t="n">
         <f aca="false">MIN(AH17,MAX(0,T17-S17))</f>
-        <v>5.44187109375</v>
+        <v>9.65184609375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11076,11 +11082,11 @@
       </c>
       <c r="J18" s="25" t="n">
         <f aca="false">IF(AND(OR(E18="CPC",E18="Slot"),NOT(N(G18)&gt;0)),0,IF(E18="Slot",Assumptions!H125*G18,Assumptions!H125))</f>
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="K18" s="28" t="n">
         <f aca="false">J18*I18</f>
-        <v>9</v>
+        <v>36.9</v>
       </c>
       <c r="L18" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C18,Funnel!$A$5:$A$8,0))*M18</f>
@@ -11092,7 +11098,7 @@
       </c>
       <c r="N18" s="28" t="n">
         <f aca="false">K18*L18</f>
-        <v>2.142</v>
+        <v>8.7822</v>
       </c>
       <c r="O18" s="37" t="n">
         <f aca="false">IF(I18&gt;0,H18/I18,0)</f>
@@ -11120,19 +11126,19 @@
       </c>
       <c r="U18" s="42" t="n">
         <f aca="false">AG18+AI18</f>
-        <v>2.142</v>
+        <v>8.2690877153267</v>
       </c>
       <c r="V18" s="28" t="n">
         <f aca="false">IF(L18&gt;0,U18/L18,0)</f>
-        <v>9</v>
+        <v>34.7440660307844</v>
       </c>
       <c r="W18" s="25" t="n">
         <f aca="false">IF(I18&gt;0,V18/I18,0)</f>
-        <v>100</v>
+        <v>386.045178119827</v>
       </c>
       <c r="X18" s="37" t="n">
         <f aca="false">IF(E18="Slot",IF(N(G18)&gt;0,ROUNDUP(W18/G18,0)*MAX(0,F18),0),W18*H18)</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="Y18" s="37" t="n">
         <f aca="false">IF(U18&gt;0,Assumptions!J125,0)</f>
@@ -11144,11 +11150,11 @@
       </c>
       <c r="AA18" s="37" t="n">
         <f aca="false">X18+Y18</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="AB18" s="37" t="n">
         <f aca="false">IF(U18&gt;0,(X18+Y18)/U18,"–")</f>
-        <v>4481.79271708684</v>
+        <v>4481.79271708683</v>
       </c>
       <c r="AC18" s="25" t="n">
         <f aca="false">SUMPRODUCT(--($Q$5:$Q$34&lt;Q18))+1</f>
@@ -11156,7 +11162,7 @@
       </c>
       <c r="AD18" s="2" t="str">
         <f aca="false">IF(AND(AH18&gt;0,AI18&gt;=AH18*0.999),"Used to capacity",IF(AI18&gt;0,"Marginal (fills the gap)",IF(Z18&gt;0,"Test only (wk 1–2)","Not used")))</f>
-        <v>Used to capacity</v>
+        <v>Marginal (fills the gap)</v>
       </c>
       <c r="AE18" s="28" t="n">
         <f aca="false">IF(H18&gt;0,Z18/H18,0)</f>
@@ -11172,11 +11178,11 @@
       </c>
       <c r="AH18" s="28" t="n">
         <f aca="false">MAX(0,N18-AG18)</f>
-        <v>1.97465625</v>
+        <v>8.61485625</v>
       </c>
       <c r="AI18" s="28" t="n">
         <f aca="false">MIN(AH18,MAX(0,T18-S18))</f>
-        <v>1.97465625</v>
+        <v>8.10174396532669</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11499,11 +11505,11 @@
       </c>
       <c r="J21" s="25" t="n">
         <f aca="false">IF(AND(OR(E21="CPC",E21="Slot"),NOT(N(G21)&gt;0)),0,IF(E21="Slot",Assumptions!H128*G21,Assumptions!H128))</f>
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="K21" s="28" t="n">
         <f aca="false">J21*I21</f>
-        <v>8.52</v>
+        <v>59.64</v>
       </c>
       <c r="L21" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C21,Funnel!$A$5:$A$8,0))*M21</f>
@@ -11515,7 +11521,7 @@
       </c>
       <c r="N21" s="28" t="n">
         <f aca="false">K21*L21</f>
-        <v>2.6838</v>
+        <v>18.7866</v>
       </c>
       <c r="O21" s="37" t="n">
         <f aca="false">IF(I21&gt;0,H21/I21,0)</f>
@@ -11535,7 +11541,7 @@
       </c>
       <c r="S21" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C21)*($Q$5:$Q$34&lt;Q21)*$AH$5:$AH$34)</f>
-        <v>45.3766871739131</v>
+        <v>90.8784371739131</v>
       </c>
       <c r="T21" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C21,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C21)</f>
@@ -11595,7 +11601,7 @@
       </c>
       <c r="AH21" s="28" t="n">
         <f aca="false">MAX(0,N21-AG21)</f>
-        <v>2.54323784916201</v>
+        <v>18.646037849162</v>
       </c>
       <c r="AI21" s="28" t="n">
         <f aca="false">MIN(AH21,MAX(0,T21-S21))</f>
@@ -11640,11 +11646,11 @@
       </c>
       <c r="J22" s="25" t="n">
         <f aca="false">IF(AND(OR(E22="CPC",E22="Slot"),NOT(N(G22)&gt;0)),0,IF(E22="Slot",Assumptions!H129*G22,Assumptions!H129))</f>
-        <v>100</v>
+        <v>1970</v>
       </c>
       <c r="K22" s="28" t="n">
         <f aca="false">J22*I22</f>
-        <v>15.62</v>
+        <v>307.714</v>
       </c>
       <c r="L22" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C22,Funnel!$A$5:$A$8,0))*M22</f>
@@ -11656,7 +11662,7 @@
       </c>
       <c r="N22" s="28" t="n">
         <f aca="false">K22*L22</f>
-        <v>5.798925</v>
+        <v>114.2388225</v>
       </c>
       <c r="O22" s="37" t="n">
         <f aca="false">IF(I22&gt;0,H22/I22,0)</f>
@@ -11676,7 +11682,7 @@
       </c>
       <c r="S22" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C22)*($Q$5:$Q$34&lt;Q22)*$AH$5:$AH$34)</f>
-        <v>87.8176822220497</v>
+        <v>435.50815722205</v>
       </c>
       <c r="T22" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C22,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C22)</f>
@@ -11736,7 +11742,7 @@
       </c>
       <c r="AH22" s="28" t="n">
         <f aca="false">MAX(0,N22-AG22)</f>
-        <v>5.55595328212291</v>
+        <v>113.995850782123</v>
       </c>
       <c r="AI22" s="28" t="n">
         <f aca="false">MIN(AH22,MAX(0,T22-S22))</f>
@@ -11781,11 +11787,11 @@
       </c>
       <c r="J23" s="25" t="n">
         <f aca="false">IF(AND(OR(E23="CPC",E23="Slot"),NOT(N(G23)&gt;0)),0,IF(E23="Slot",Assumptions!H130*G23,Assumptions!H130))</f>
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="K23" s="28" t="n">
         <f aca="false">J23*I23</f>
-        <v>4.26</v>
+        <v>24.495</v>
       </c>
       <c r="L23" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C23,Funnel!$A$5:$A$8,0))*M23</f>
@@ -11797,7 +11803,7 @@
       </c>
       <c r="N23" s="28" t="n">
         <f aca="false">K23*L23</f>
-        <v>1.20771</v>
+        <v>6.9443325</v>
       </c>
       <c r="O23" s="37" t="n">
         <f aca="false">IF(I23&gt;0,H23/I23,0)</f>
@@ -11817,7 +11823,7 @@
       </c>
       <c r="S23" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C23)*($Q$5:$Q$34&lt;Q23)*$AH$5:$AH$34)</f>
-        <v>19.2088063002717</v>
+        <v>37.9623313002717</v>
       </c>
       <c r="T23" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C23,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C23)</f>
@@ -11877,7 +11883,7 @@
       </c>
       <c r="AH23" s="28" t="n">
         <f aca="false">MAX(0,N23-AG23)</f>
-        <v>1.08120406424581</v>
+        <v>6.81782656424581</v>
       </c>
       <c r="AI23" s="28" t="n">
         <f aca="false">MIN(AH23,MAX(0,T23-S23))</f>
@@ -11922,11 +11928,11 @@
       </c>
       <c r="J24" s="25" t="n">
         <f aca="false">IF(AND(OR(E24="CPC",E24="Slot"),NOT(N(G24)&gt;0)),0,IF(E24="Slot",Assumptions!H131*G24,Assumptions!H131))</f>
-        <v>30</v>
+        <v>360</v>
       </c>
       <c r="K24" s="28" t="n">
         <f aca="false">J24*I24</f>
-        <v>2.13</v>
+        <v>25.56</v>
       </c>
       <c r="L24" s="27" t="n">
         <f aca="false">INDEX(Funnel!$G$5:$G$8,MATCH(C24,Funnel!$A$5:$A$8,0))*M24</f>
@@ -11938,7 +11944,7 @@
       </c>
       <c r="N24" s="28" t="n">
         <f aca="false">K24*L24</f>
-        <v>0.50694</v>
+        <v>6.08328</v>
       </c>
       <c r="O24" s="37" t="n">
         <f aca="false">IF(I24&gt;0,H24/I24,0)</f>
@@ -11958,7 +11964,7 @@
       </c>
       <c r="S24" s="28" t="n">
         <f aca="false">SUMPRODUCT(($C$5:$C$34=C24)*($Q$5:$Q$34&lt;Q24)*$AH$5:$AH$34)</f>
-        <v>7.97624164130435</v>
+        <v>31.3240416413043</v>
       </c>
       <c r="T24" s="28" t="n">
         <f aca="false">INDEX(Funnel!$B$5:$B$8,MATCH(C24,Funnel!$A$5:$A$8,0))-SUMIFS($AG$5:$AG$34,$C$5:$C$34,C24)</f>
@@ -11966,19 +11972,19 @@
       </c>
       <c r="U24" s="42" t="n">
         <f aca="false">AG24+AI24</f>
-        <v>0.50694</v>
+        <v>0.0708016759776536</v>
       </c>
       <c r="V24" s="28" t="n">
         <f aca="false">IF(L24&gt;0,U24/L24,0)</f>
-        <v>2.13</v>
+        <v>0.297486033519553</v>
       </c>
       <c r="W24" s="25" t="n">
         <f aca="false">IF(I24&gt;0,V24/I24,0)</f>
-        <v>30</v>
+        <v>4.18994413407821</v>
       </c>
       <c r="X24" s="37" t="n">
         <f aca="false">IF(E24="Slot",IF(N(G24)&gt;0,ROUNDUP(W24/G24,0)*MAX(0,F24),0),W24*H24)</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="Y24" s="37" t="n">
         <f aca="false">IF(U24&gt;0,Assumptions!J131,0)</f>
@@ -11990,7 +11996,7 @@
       </c>
       <c r="AA24" s="37" t="n">
         <f aca="false">X24+Y24</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="AB24" s="37" t="n">
         <f aca="false">IF(U24&gt;0,(X24+Y24)/U24,"–")</f>
@@ -12002,7 +12008,7 @@
       </c>
       <c r="AD24" s="2" t="str">
         <f aca="false">IF(AND(AH24&gt;0,AI24&gt;=AH24*0.999),"Used to capacity",IF(AI24&gt;0,"Marginal (fills the gap)",IF(Z24&gt;0,"Test only (wk 1–2)","Not used")))</f>
-        <v>Used to capacity</v>
+        <v>Test only (wk 1–2)</v>
       </c>
       <c r="AE24" s="28" t="n">
         <f aca="false">IF(H24&gt;0,Z24/H24,0)</f>
@@ -12018,25 +12024,25 @@
       </c>
       <c r="AH24" s="28" t="n">
         <f aca="false">MAX(0,N24-AG24)</f>
-        <v>0.436138324022346</v>
+        <v>6.01247832402235</v>
       </c>
       <c r="AI24" s="28" t="n">
         <f aca="false">MIN(AH24,MAX(0,T24-S24))</f>
-        <v>0.436138324022346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>303</v>
@@ -12161,16 +12167,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>303</v>
@@ -12295,16 +12301,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>303</v>
@@ -12429,16 +12435,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>303</v>
@@ -12563,16 +12569,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>303</v>
@@ -12697,16 +12703,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>303</v>
@@ -12831,16 +12837,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>303</v>
@@ -12965,16 +12971,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>303</v>
@@ -13099,16 +13105,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>303</v>
@@ -13233,16 +13239,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>303</v>
@@ -13367,35 +13373,35 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J35" s="29" t="n">
         <f aca="false">SUM(J5:J34)</f>
-        <v>3667.32</v>
+        <v>13917.32</v>
       </c>
       <c r="K35" s="31" t="n">
         <f aca="false">SUM(K5:K34)</f>
-        <v>516.2436</v>
+        <v>2148.3626</v>
       </c>
       <c r="N35" s="31" t="n">
         <f aca="false">SUM(N5:N34)</f>
-        <v>172.43729275</v>
+        <v>743.58650275</v>
       </c>
       <c r="U35" s="31" t="n">
         <f aca="false">SUM(U5:U34)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="V35" s="31" t="n">
         <f aca="false">SUM(V5:V34)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="W35" s="29" t="n">
         <f aca="false">SUM(W5:W34)</f>
-        <v>2360.469219568</v>
+        <v>2413.36272691508</v>
       </c>
       <c r="X35" s="38" t="n">
         <f aca="false">SUM(X5:X34)</f>
-        <v>191823.630576062</v>
+        <v>174614.967675565</v>
       </c>
       <c r="Y35" s="38" t="n">
         <f aca="false">SUM(Y5:Y34)</f>
@@ -13407,11 +13413,11 @@
       </c>
       <c r="AA35" s="38" t="n">
         <f aca="false">SUM(AA5:AA34)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="AB35" s="38" t="n">
         <f aca="false">IF(U35&gt;0,(X35+Y35)/U35,0)</f>
-        <v>1958.71420042621</v>
+        <v>1762.14967675565</v>
       </c>
       <c r="AE35" s="29" t="n">
         <f aca="false">SUM(AE5:AE34)</f>
@@ -13427,12 +13433,12 @@
       </c>
       <c r="AI35" s="31" t="n">
         <f aca="false">SUM(AI5:AI34)</f>
-        <v>96.3089661070919</v>
+        <v>97.5586581070919</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="24" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13444,10 +13450,10 @@
         <v>49</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13511,11 +13517,11 @@
       </c>
       <c r="D42" s="28" t="n">
         <f aca="false">SUMIFS($U$5:$U$34,$C$5:$C$34,B42)</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="E42" s="28" t="n">
         <f aca="false">IF(C42-D42&gt;0.05,C42-D42,0)</f>
-        <v>1.249692</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -13546,21 +13552,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C4" s="37" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Channel")</f>
-        <v>157259.315332555</v>
+        <v>140050.652432059</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Initiative")</f>
@@ -13569,7 +13575,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C6" s="37" t="n">
         <f aca="false">Channels!Y35</f>
@@ -13578,16 +13584,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C7" s="37" t="n">
         <f aca="false">C4+C5+C6</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C8" s="37" t="n">
         <f aca="false">Channels!Z35</f>
@@ -13596,79 +13602,79 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C9" s="37" t="n">
         <f aca="false">C7</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C10" s="37" t="n">
         <f aca="false">IF(Assumptions!$D$48&lt;1,C9/(1-Assumptions!$D$48)*Assumptions!$D$48,0)</f>
-        <v>34133.5818663638</v>
+        <v>31096.7590015703</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C11" s="37" t="n">
         <f aca="false">C9+C10</f>
-        <v>227557.212442426</v>
+        <v>207311.726677135</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">IF(Assumptions!$D$51&gt;0,ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51,C11)</f>
-        <v>230000</v>
+        <v>207500</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C13" s="42" t="n">
         <f aca="false">MIN(Channels!U35,Funnel!B26)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C14" s="43" t="n">
         <f aca="false">IF(C13&gt;0,C9/C13,0)</f>
-        <v>1958.71420042621</v>
+        <v>1762.14967675565</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C15" s="37" t="n">
         <f aca="false">IF(C13&gt;0,C12/C13,0)</f>
-        <v>2329.10665959644</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C16" s="26" t="n">
         <f aca="false">IF(C12&gt;0,Weekly!N5/C12,0)</f>
-        <v>0.228383825776918</v>
+        <v>0.284011526900921</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="24" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13677,25 +13683,25 @@
         <v>283</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13770,7 +13776,7 @@
       </c>
       <c r="C23" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B23)</f>
-        <v>39526.0468809152</v>
+        <v>32376.0468809152</v>
       </c>
       <c r="D23" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$Y$5:$Y$34,Channels!$C$5:$C$34,B23)</f>
@@ -13782,7 +13788,7 @@
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">C23+D23</f>
-        <v>39526.0468809152</v>
+        <v>32376.0468809152</v>
       </c>
       <c r="G23" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$C$5:$C$34,B23)</f>
@@ -13790,7 +13796,7 @@
       </c>
       <c r="H23" s="37" t="n">
         <f aca="false">IF(G23&gt;0,F23/G23,0)</f>
-        <v>2635.06979206101</v>
+        <v>2158.40312539434</v>
       </c>
       <c r="I23" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$C$5:$C$34,B23)</f>
@@ -13803,7 +13809,7 @@
       </c>
       <c r="C24" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B24)</f>
-        <v>49362.19</v>
+        <v>39303.5270995034</v>
       </c>
       <c r="D24" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$Y$5:$Y$34,Channels!$C$5:$C$34,B24)</f>
@@ -13815,28 +13821,28 @@
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">C24+D24</f>
-        <v>49362.19</v>
+        <v>39303.5270995034</v>
       </c>
       <c r="G24" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$C$5:$C$34,B24)</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="H24" s="37" t="n">
         <f aca="false">IF(G24&gt;0,F24/G24,0)</f>
-        <v>5641.19457280818</v>
+        <v>3930.35270995034</v>
       </c>
       <c r="I24" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$C$5:$C$34,B24)</f>
-        <v>36.235</v>
+        <v>41.4858067226891</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C25" s="38" t="n">
         <f aca="false">SUM(C21:C24)</f>
-        <v>191823.630576062</v>
+        <v>174614.967675565</v>
       </c>
       <c r="D25" s="38" t="n">
         <f aca="false">SUM(D21:D24)</f>
@@ -13848,24 +13854,24 @@
       </c>
       <c r="F25" s="38" t="n">
         <f aca="false">SUM(F21:F24)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="G25" s="31" t="n">
         <f aca="false">SUM(G21:G24)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="H25" s="38" t="n">
         <f aca="false">IF(G25&gt;0,F25/G25,0)</f>
-        <v>1958.71420042621</v>
+        <v>1762.14967675565</v>
       </c>
       <c r="I25" s="31" t="n">
         <f aca="false">SUM(I21:I24)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="24" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13874,16 +13880,16 @@
         <v>282</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13913,66 +13919,66 @@
       </c>
       <c r="C30" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B30)</f>
-        <v>65107.8896123105</v>
+        <v>15947.8896123104</v>
       </c>
       <c r="D30" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,B30)</f>
-        <v>12.5919124056439</v>
+        <v>4.1977200143395</v>
       </c>
       <c r="E30" s="37" t="n">
         <f aca="false">IF(D30&gt;0,C30/D30,"–")</f>
-        <v>5170.61170018371</v>
+        <v>3799.17897283099</v>
       </c>
       <c r="F30" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C30/$C$9,0)</f>
-        <v>0.336607732045995</v>
+        <v>0.090502468789556</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C31" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B31)</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,B31)</f>
-        <v>3.96036</v>
+        <v>3.70332</v>
       </c>
       <c r="E31" s="37" t="n">
         <f aca="false">IF(D31&gt;0,C31/D31,"–")</f>
-        <v>2561.13080629034</v>
+        <v>2347.62321376495</v>
       </c>
       <c r="F31" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C31/$C$9,0)</f>
-        <v>0.052439301081216</v>
+        <v>0.0493374661340165</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C32" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B32)</f>
-        <v>24000</v>
+        <v>62020.3370995034</v>
       </c>
       <c r="D32" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,B32)</f>
-        <v>7.882875</v>
+        <v>18.2199377153267</v>
       </c>
       <c r="E32" s="37" t="n">
         <f aca="false">IF(D32&gt;0,C32/D32,"–")</f>
-        <v>3044.5744731459</v>
+        <v>3403.98183948409</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C32/$C$9,0)</f>
-        <v>0.124079978896696</v>
+        <v>0.351958394440653</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B33)</f>
@@ -13988,33 +13994,33 @@
       </c>
       <c r="F33" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C33/$C$9,0)</f>
-        <v>0.260508116666904</v>
+        <v>0.285948613701286</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C34" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B34)</f>
-        <v>7620</v>
+        <v>3000</v>
       </c>
       <c r="D34" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,B34)</f>
-        <v>1.01697980446927</v>
+        <v>0.580841480446927</v>
       </c>
       <c r="E34" s="37" t="n">
         <f aca="false">IF(D34&gt;0,C34/D34,"–")</f>
-        <v>7492.7741598336</v>
+        <v>5164.92038015545</v>
       </c>
       <c r="F34" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C34/$C$9,0)</f>
-        <v>0.0393953932997009</v>
+        <v>0.017024660501731</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C35" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B35)</f>
@@ -14030,12 +14036,12 @@
       </c>
       <c r="F35" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C35/$C$9,0)</f>
-        <v>0.000210935964124383</v>
+        <v>0.000231535382823542</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C36" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B36)</f>
@@ -14051,12 +14057,12 @@
       </c>
       <c r="F36" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C36/$C$9,0)</f>
-        <v>0.0580591353629045</v>
+        <v>0.0637290288000729</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C37" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B37)</f>
@@ -14072,12 +14078,12 @@
       </c>
       <c r="F37" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C37/$C$9,0)</f>
-        <v>0.0930599841725218</v>
+        <v>0.102147963010386</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C38" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B38)</f>
@@ -14093,20 +14099,20 @@
       </c>
       <c r="F38" s="26" t="n">
         <f aca="false">IF($C$9&gt;0,C38/$C$9,0)</f>
-        <v>0.0356394225099383</v>
+        <v>0.0391198692394754</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C39" s="38" t="n">
         <f aca="false">SUM(C29:C38)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">SUM(D29:D38)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14117,21 +14123,21 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="24" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>50</v>
@@ -14146,10 +14152,10 @@
         <v>57</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14159,7 +14165,7 @@
       </c>
       <c r="C45" s="37" t="n">
         <f aca="false">Budget!F57</f>
-        <v>230000</v>
+        <v>207500</v>
       </c>
       <c r="D45" s="28" t="n">
         <f aca="false">Budget!F92</f>
@@ -14175,15 +14181,15 @@
       </c>
       <c r="G45" s="28" t="n">
         <f aca="false">Budget!F95</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="H45" s="31" t="n">
         <f aca="false">SUM(D45:G45)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="I45" s="37" t="n">
         <f aca="false">IF(H45&gt;0,C45/H45,0)</f>
-        <v>2329.10665959644</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14193,11 +14199,11 @@
       </c>
       <c r="C46" s="37" t="n">
         <f aca="false">Budget!G57</f>
-        <v>195500</v>
+        <v>176375</v>
       </c>
       <c r="D46" s="28" t="n">
         <f aca="false">Budget!G92</f>
-        <v>30</v>
+        <v>29.859437849162</v>
       </c>
       <c r="E46" s="28" t="n">
         <f aca="false">Budget!G93</f>
@@ -14205,19 +14211,19 @@
       </c>
       <c r="F46" s="28" t="n">
         <f aca="false">Budget!G94</f>
-        <v>15</v>
+        <v>14.8734940642458</v>
       </c>
       <c r="G46" s="28" t="n">
         <f aca="false">Budget!G95</f>
-        <v>5.33255888857614</v>
+        <v>4.63144714646623</v>
       </c>
       <c r="H46" s="31" t="n">
         <f aca="false">SUM(D46:G46)</f>
-        <v>95.3325588885761</v>
+        <v>94.3643790598741</v>
       </c>
       <c r="I46" s="37" t="n">
         <f aca="false">IF(H46&gt;0,C46/H46,0)</f>
-        <v>2050.71595978556</v>
+        <v>1869.08451851403</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14227,11 +14233,11 @@
       </c>
       <c r="C47" s="37" t="n">
         <f aca="false">Budget!H57</f>
-        <v>161000</v>
+        <v>145250</v>
       </c>
       <c r="D47" s="28" t="n">
         <f aca="false">Budget!H92</f>
-        <v>29.859437849162</v>
+        <v>27.1132218976179</v>
       </c>
       <c r="E47" s="28" t="n">
         <f aca="false">Budget!H93</f>
@@ -14239,7 +14245,7 @@
       </c>
       <c r="F47" s="28" t="n">
         <f aca="false">Budget!H94</f>
-        <v>13.3391161218711</v>
+        <v>14.32794825</v>
       </c>
       <c r="G47" s="28" t="n">
         <f aca="false">Budget!H95</f>
@@ -14247,11 +14253,11 @@
       </c>
       <c r="H47" s="31" t="n">
         <f aca="false">SUM(D47:G47)</f>
-        <v>89.7588819710332</v>
+        <v>88.0014981476179</v>
       </c>
       <c r="I47" s="37" t="n">
         <f aca="false">IF(H47&gt;0,C47/H47,0)</f>
-        <v>1793.69435608565</v>
+        <v>1650.54008235577</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14261,11 +14267,11 @@
       </c>
       <c r="C48" s="37" t="n">
         <f aca="false">Budget!I57</f>
-        <v>115000</v>
+        <v>103750</v>
       </c>
       <c r="D48" s="28" t="n">
         <f aca="false">Budget!I92</f>
-        <v>22.881639103945</v>
+        <v>17.222185978945</v>
       </c>
       <c r="E48" s="28" t="n">
         <f aca="false">Budget!I93</f>
@@ -14273,7 +14279,7 @@
       </c>
       <c r="F48" s="28" t="n">
         <f aca="false">Budget!I94</f>
-        <v>10.11797325</v>
+        <v>14.32794825</v>
       </c>
       <c r="G48" s="28" t="n">
         <f aca="false">Budget!I95</f>
@@ -14281,17 +14287,17 @@
       </c>
       <c r="H48" s="31" t="n">
         <f aca="false">SUM(D48:G48)</f>
-        <v>79.559940353945</v>
+        <v>78.110462228945</v>
       </c>
       <c r="I48" s="37" t="n">
         <f aca="false">IF(H48&gt;0,C48/H48,0)</f>
-        <v>1445.451058515</v>
+        <v>1328.24716484079</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="9" t="str">
         <f aca="false">"Above the recommended budget, extra money can buy at most ~"&amp;TEXT(MAX(0,Funnel!B26-Funnel!B9),"0")&amp;" more hires before 31 Dec (the "&amp;TEXT(MAX(0,Funnel!B22-Funnel!B23),"0")&amp;" spare assessment slots at plan conversion); after that the "&amp;Assumptions!$D$9&amp;"/week limit binds."</f>
-        <v>Above the recommended budget, extra money can buy at most ~2 more hires before 31 Dec (the 11 spare assessment slots at plan conversion); after that the 55/week limit binds.</v>
+        <v>Above the recommended budget, extra money can buy at most ~2 more hires before 31 Dec (the 6 spare assessment slots at plan conversion); after that the 55/week limit binds.</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
@@ -14313,17 +14319,17 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="24" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F56" s="44" t="n">
         <f aca="false">1</f>
@@ -14344,49 +14350,49 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F57" s="37" t="n">
         <f aca="false">Budget!$C$12*F56</f>
-        <v>230000</v>
+        <v>207500</v>
       </c>
       <c r="G57" s="37" t="n">
         <f aca="false">Budget!$C$12*G56</f>
-        <v>195500</v>
+        <v>176375</v>
       </c>
       <c r="H57" s="37" t="n">
         <f aca="false">Budget!$C$12*H56</f>
-        <v>161000</v>
+        <v>145250</v>
       </c>
       <c r="I57" s="37" t="n">
         <f aca="false">Budget!$C$12*I56</f>
-        <v>115000</v>
+        <v>103750</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F58" s="37" t="n">
         <f aca="false">F57*(1-Assumptions!$D$48)</f>
-        <v>195500</v>
+        <v>176375</v>
       </c>
       <c r="G58" s="37" t="n">
         <f aca="false">G57*(1-Assumptions!$D$48)</f>
-        <v>166175</v>
+        <v>149918.75</v>
       </c>
       <c r="H58" s="37" t="n">
         <f aca="false">H57*(1-Assumptions!$D$48)</f>
-        <v>136850</v>
+        <v>123462.5</v>
       </c>
       <c r="I58" s="37" t="n">
         <f aca="false">I57*(1-Assumptions!$D$48)</f>
-        <v>97750</v>
+        <v>88187.5</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F59" s="37" t="n">
         <f aca="false">MAX(0,Budget!$C$9-F58)</f>
@@ -14394,71 +14400,71 @@
       </c>
       <c r="G59" s="37" t="n">
         <f aca="false">MAX(0,Budget!$C$9-G58)</f>
-        <v>27248.6305760617</v>
+        <v>26296.2176755651</v>
       </c>
       <c r="H59" s="37" t="n">
         <f aca="false">MAX(0,Budget!$C$9-H58)</f>
-        <v>56573.6305760617</v>
+        <v>52752.4676755651</v>
       </c>
       <c r="I59" s="37" t="n">
         <f aca="false">MAX(0,Budget!$C$9-I58)</f>
-        <v>95673.6305760617</v>
+        <v>88027.4676755651</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>283</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E60" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="G60" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="H60" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="K60" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="M60" s="12" t="s">
+        <v>648</v>
+      </c>
+      <c r="N60" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="F60" s="12" t="s">
-        <v>639</v>
-      </c>
-      <c r="G60" s="12" t="s">
-        <v>640</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>641</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>643</v>
-      </c>
-      <c r="K60" s="12" t="s">
-        <v>644</v>
-      </c>
-      <c r="L60" s="12" t="s">
-        <v>645</v>
-      </c>
-      <c r="M60" s="12" t="s">
-        <v>646</v>
-      </c>
-      <c r="N60" s="12" t="s">
-        <v>619</v>
-      </c>
       <c r="O60" s="12" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -14788,7 +14794,7 @@
       </c>
       <c r="H65" s="28" t="n">
         <f aca="false">IF(N65&gt;0,E65*MAX(0,N65-MIN(L65,N65))/N65,IF(C65&gt;0,E65*(1-L65/C65),E65))</f>
-        <v>3.20996534916201</v>
+        <v>0.463749397617865</v>
       </c>
       <c r="I65" s="28" t="n">
         <f aca="false">IF(N65&gt;0,E65*MAX(0,N65-MIN(M65,N65))/N65,IF(C65&gt;0,E65*(1-M65/C65),E65))</f>
@@ -14804,7 +14810,7 @@
       </c>
       <c r="L65" s="37" t="n">
         <f aca="false">MIN(C65,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D65)*$C$61:$C$90)))</f>
-        <v>0</v>
+        <v>10397.1961951466</v>
       </c>
       <c r="M65" s="37" t="n">
         <f aca="false">MIN(C65,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D65)*$C$61:$C$90)))</f>
@@ -14824,7 +14830,7 @@
       </c>
       <c r="Q65" s="28" t="n">
         <f aca="false">IF(E65&gt;0,H65*Channels!V9/E65,0)</f>
-        <v>10.1903661878159</v>
+        <v>1.47222030989798</v>
       </c>
       <c r="R65" s="28" t="n">
         <f aca="false">IF(E65&gt;0,I65*Channels!V9/E65,0)</f>
@@ -14916,7 +14922,7 @@
       </c>
       <c r="C67" s="37" t="n">
         <f aca="false">Channels!AA11</f>
-        <v>20004.9343809152</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="D67" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB11),Channels!AB11,0)+ROW()/1000000</f>
@@ -14924,19 +14930,19 @@
       </c>
       <c r="E67" s="28" t="n">
         <f aca="false">Channels!U11</f>
-        <v>4.75552081424581</v>
+        <v>0.545545814245812</v>
       </c>
       <c r="F67" s="28" t="n">
         <f aca="false">IF(N67&gt;0,E67*MAX(0,N67-MIN(J67,N67))/N67,IF(C67&gt;0,E67*(1-J67/C67),E67))</f>
-        <v>4.75552081424581</v>
+        <v>0.545545814245812</v>
       </c>
       <c r="G67" s="28" t="n">
         <f aca="false">IF(N67&gt;0,E67*MAX(0,N67-MIN(K67,N67))/N67,IF(C67&gt;0,E67*(1-K67/C67),E67))</f>
-        <v>4.75552081424581</v>
+        <v>0.545545814245812</v>
       </c>
       <c r="H67" s="28" t="n">
         <f aca="false">IF(N67&gt;0,E67*MAX(0,N67-MIN(L67,N67))/N67,IF(C67&gt;0,E67*(1-L67/C67),E67))</f>
-        <v>3.22114287187114</v>
+        <v>0</v>
       </c>
       <c r="I67" s="28" t="n">
         <f aca="false">IF(N67&gt;0,E67*MAX(0,N67-MIN(M67,N67))/N67,IF(C67&gt;0,E67*(1-M67/C67),E67))</f>
@@ -14952,27 +14958,27 @@
       </c>
       <c r="L67" s="37" t="n">
         <f aca="false">MIN(C67,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D67)*$C$61:$C$90)))</f>
-        <v>6454.63057606173</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="M67" s="37" t="n">
         <f aca="false">MIN(C67,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D67)*$C$61:$C$90)))</f>
-        <v>20004.9343809152</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="N67" s="37" t="n">
         <f aca="false">Channels!X11</f>
-        <v>20004.9343809152</v>
+        <v>2294.93438091517</v>
       </c>
       <c r="O67" s="28" t="n">
         <f aca="false">IF(E67&gt;0,F67*Channels!V11/E67,0)</f>
-        <v>16.7743238597736</v>
+        <v>1.92432385977359</v>
       </c>
       <c r="P67" s="28" t="n">
         <f aca="false">IF(E67&gt;0,G67*Channels!V11/E67,0)</f>
-        <v>16.7743238597736</v>
+        <v>1.92432385977359</v>
       </c>
       <c r="Q67" s="28" t="n">
         <f aca="false">IF(E67&gt;0,H67*Channels!V11/E67,0)</f>
-        <v>11.3620559854361</v>
+        <v>0</v>
       </c>
       <c r="R67" s="28" t="n">
         <f aca="false">IF(E67&gt;0,I67*Channels!V11/E67,0)</f>
@@ -14990,7 +14996,7 @@
       </c>
       <c r="C68" s="37" t="n">
         <f aca="false">Channels!AA12</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="D68" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB12),Channels!AB12,0)+ROW()/1000000</f>
@@ -14998,15 +15004,15 @@
       </c>
       <c r="E68" s="28" t="n">
         <f aca="false">Channels!U12</f>
-        <v>4.284</v>
+        <v>0.0997826086956522</v>
       </c>
       <c r="F68" s="28" t="n">
         <f aca="false">IF(N68&gt;0,E68*MAX(0,N68-MIN(J68,N68))/N68,IF(C68&gt;0,E68*(1-J68/C68),E68))</f>
-        <v>4.284</v>
+        <v>0.0997826086956522</v>
       </c>
       <c r="G68" s="28" t="n">
         <f aca="false">IF(N68&gt;0,E68*MAX(0,N68-MIN(K68,N68))/N68,IF(C68&gt;0,E68*(1-K68/C68),E68))</f>
-        <v>1.37319088857614</v>
+        <v>0</v>
       </c>
       <c r="H68" s="28" t="n">
         <f aca="false">IF(N68&gt;0,E68*MAX(0,N68-MIN(L68,N68))/N68,IF(C68&gt;0,E68*(1-L68/C68),E68))</f>
@@ -15022,27 +15028,27 @@
       </c>
       <c r="K68" s="37" t="n">
         <f aca="false">MIN(C68,MAX(0,G$59-SUMPRODUCT(($D$61:$D$90&gt;D68)*$C$61:$C$90)))</f>
-        <v>21878.6305760617</v>
+        <v>750</v>
       </c>
       <c r="L68" s="37" t="n">
         <f aca="false">MIN(C68,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D68)*$C$61:$C$90)))</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="M68" s="37" t="n">
         <f aca="false">MIN(C68,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D68)*$C$61:$C$90)))</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="N68" s="37" t="n">
         <f aca="false">Channels!X12</f>
-        <v>32200</v>
+        <v>750</v>
       </c>
       <c r="O68" s="28" t="n">
         <f aca="false">IF(E68&gt;0,F68*Channels!V12/E68,0)</f>
-        <v>18</v>
+        <v>0.419254658385093</v>
       </c>
       <c r="P68" s="28" t="n">
         <f aca="false">IF(E68&gt;0,G68*Channels!V12/E68,0)</f>
-        <v>5.76970961586612</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="28" t="n">
         <f aca="false">IF(E68&gt;0,H68*Channels!V12/E68,0)</f>
@@ -15286,23 +15292,23 @@
       </c>
       <c r="C72" s="37" t="n">
         <f aca="false">Channels!AA16</f>
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="D72" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB16),Channels!AB16,0)+ROW()/1000000</f>
-        <v>5637.25497396078</v>
+        <v>7.2E-005</v>
       </c>
       <c r="E72" s="28" t="n">
         <f aca="false">Channels!U16</f>
-        <v>0.25704</v>
+        <v>0</v>
       </c>
       <c r="F72" s="28" t="n">
         <f aca="false">IF(N72&gt;0,E72*MAX(0,N72-MIN(J72,N72))/N72,IF(C72&gt;0,E72*(1-J72/C72),E72))</f>
-        <v>0.25704</v>
+        <v>0</v>
       </c>
       <c r="G72" s="28" t="n">
         <f aca="false">IF(N72&gt;0,E72*MAX(0,N72-MIN(K72,N72))/N72,IF(C72&gt;0,E72*(1-K72/C72),E72))</f>
-        <v>0.25704</v>
+        <v>0</v>
       </c>
       <c r="H72" s="28" t="n">
         <f aca="false">IF(N72&gt;0,E72*MAX(0,N72-MIN(L72,N72))/N72,IF(C72&gt;0,E72*(1-L72/C72),E72))</f>
@@ -15322,23 +15328,23 @@
       </c>
       <c r="L72" s="37" t="n">
         <f aca="false">MIN(C72,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D72)*$C$61:$C$90)))</f>
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="M72" s="37" t="n">
         <f aca="false">MIN(C72,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D72)*$C$61:$C$90)))</f>
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="N72" s="37" t="n">
         <f aca="false">Channels!X16</f>
-        <v>1449</v>
+        <v>0</v>
       </c>
       <c r="O72" s="28" t="n">
         <f aca="false">IF(E72&gt;0,F72*Channels!V16/E72,0)</f>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="P72" s="28" t="n">
         <f aca="false">IF(E72&gt;0,G72*Channels!V16/E72,0)</f>
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="28" t="n">
         <f aca="false">IF(E72&gt;0,H72*Channels!V16/E72,0)</f>
@@ -15360,7 +15366,7 @@
       </c>
       <c r="C73" s="37" t="n">
         <f aca="false">Channels!AA17</f>
-        <v>14400</v>
+        <v>24960</v>
       </c>
       <c r="D73" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB17),Channels!AB17,0)+ROW()/1000000</f>
@@ -15368,23 +15374,23 @@
       </c>
       <c r="E73" s="28" t="n">
         <f aca="false">Channels!U17</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="F73" s="28" t="n">
         <f aca="false">IF(N73&gt;0,E73*MAX(0,N73-MIN(J73,N73))/N73,IF(C73&gt;0,E73*(1-J73/C73),E73))</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="G73" s="28" t="n">
         <f aca="false">IF(N73&gt;0,E73*MAX(0,N73-MIN(K73,N73))/N73,IF(C73&gt;0,E73*(1-K73/C73),E73))</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="H73" s="28" t="n">
         <f aca="false">IF(N73&gt;0,E73*MAX(0,N73-MIN(L73,N73))/N73,IF(C73&gt;0,E73*(1-L73/C73),E73))</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="I73" s="28" t="n">
         <f aca="false">IF(N73&gt;0,E73*MAX(0,N73-MIN(M73,N73))/N73,IF(C73&gt;0,E73*(1-M73/C73),E73))</f>
-        <v>5.740875</v>
+        <v>9.95085</v>
       </c>
       <c r="J73" s="37" t="n">
         <f aca="false">MIN(C73,MAX(0,F$59-SUMPRODUCT(($D$61:$D$90&gt;D73)*$C$61:$C$90)))</f>
@@ -15404,23 +15410,23 @@
       </c>
       <c r="N73" s="37" t="n">
         <f aca="false">Channels!X17</f>
-        <v>14400</v>
+        <v>24960</v>
       </c>
       <c r="O73" s="28" t="n">
         <f aca="false">IF(E73&gt;0,F73*Channels!V17/E73,0)</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
       <c r="P73" s="28" t="n">
         <f aca="false">IF(E73&gt;0,G73*Channels!V17/E73,0)</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
       <c r="Q73" s="28" t="n">
         <f aca="false">IF(E73&gt;0,H73*Channels!V17/E73,0)</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
       <c r="R73" s="28" t="n">
         <f aca="false">IF(E73&gt;0,I73*Channels!V17/E73,0)</f>
-        <v>20.25</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -15434,23 +15440,23 @@
       </c>
       <c r="C74" s="37" t="n">
         <f aca="false">Channels!AA18</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="D74" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB18),Channels!AB18,0)+ROW()/1000000</f>
-        <v>4481.79279108684</v>
+        <v>4481.79279108683</v>
       </c>
       <c r="E74" s="28" t="n">
         <f aca="false">Channels!U18</f>
-        <v>2.142</v>
+        <v>8.2690877153267</v>
       </c>
       <c r="F74" s="28" t="n">
         <f aca="false">IF(N74&gt;0,E74*MAX(0,N74-MIN(J74,N74))/N74,IF(C74&gt;0,E74*(1-J74/C74),E74))</f>
-        <v>2.142</v>
+        <v>8.2690877153267</v>
       </c>
       <c r="G74" s="28" t="n">
         <f aca="false">IF(N74&gt;0,E74*MAX(0,N74-MIN(K74,N74))/N74,IF(C74&gt;0,E74*(1-K74/C74),E74))</f>
-        <v>2.142</v>
+        <v>3.07111914646622</v>
       </c>
       <c r="H74" s="28" t="n">
         <f aca="false">IF(N74&gt;0,E74*MAX(0,N74-MIN(L74,N74))/N74,IF(C74&gt;0,E74*(1-L74/C74),E74))</f>
@@ -15466,27 +15472,27 @@
       </c>
       <c r="K74" s="37" t="n">
         <f aca="false">MIN(C74,MAX(0,G$59-SUMPRODUCT(($D$61:$D$90&gt;D74)*$C$61:$C$90)))</f>
-        <v>0</v>
+        <v>23296.2176755651</v>
       </c>
       <c r="L74" s="37" t="n">
         <f aca="false">MIN(C74,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D74)*$C$61:$C$90)))</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="M74" s="37" t="n">
         <f aca="false">MIN(C74,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D74)*$C$61:$C$90)))</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="N74" s="37" t="n">
         <f aca="false">Channels!X18</f>
-        <v>9600</v>
+        <v>37060.3370995034</v>
       </c>
       <c r="O74" s="28" t="n">
         <f aca="false">IF(E74&gt;0,F74*Channels!V18/E74,0)</f>
-        <v>9</v>
+        <v>34.7440660307844</v>
       </c>
       <c r="P74" s="28" t="n">
         <f aca="false">IF(E74&gt;0,G74*Channels!V18/E74,0)</f>
-        <v>9</v>
+        <v>12.9038619599421</v>
       </c>
       <c r="Q74" s="28" t="n">
         <f aca="false">IF(E74&gt;0,H74*Channels!V18/E74,0)</f>
@@ -15532,7 +15538,7 @@
       </c>
       <c r="I75" s="28" t="n">
         <f aca="false">IF(N75&gt;0,E75*MAX(0,N75-MIN(M75,N75))/N75,IF(C75&gt;0,E75*(1-M75/C75),E75))</f>
-        <v>5.68216660394495</v>
+        <v>0.0227134789449476</v>
       </c>
       <c r="J75" s="37" t="n">
         <f aca="false">MIN(C75,MAX(0,F$59-SUMPRODUCT(($D$61:$D$90&gt;D75)*$C$61:$C$90)))</f>
@@ -15548,7 +15554,7 @@
       </c>
       <c r="M75" s="37" t="n">
         <f aca="false">MIN(C75,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D75)*$C$61:$C$90)))</f>
-        <v>13396.7409637513</v>
+        <v>33519.2409637513</v>
       </c>
       <c r="N75" s="37" t="n">
         <f aca="false">Channels!X19</f>
@@ -15568,7 +15574,7 @@
       </c>
       <c r="R75" s="28" t="n">
         <f aca="false">IF(E75&gt;0,I75*Channels!V19/E75,0)</f>
-        <v>18.0386241395078</v>
+        <v>0.0721062823649131</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -15672,7 +15678,7 @@
       </c>
       <c r="G77" s="28" t="n">
         <f aca="false">IF(N77&gt;0,E77*MAX(0,N77-MIN(K77,N77))/N77,IF(C77&gt;0,E77*(1-K77/C77),E77))</f>
-        <v>0.140562150837989</v>
+        <v>0</v>
       </c>
       <c r="H77" s="28" t="n">
         <f aca="false">IF(N77&gt;0,E77*MAX(0,N77-MIN(L77,N77))/N77,IF(C77&gt;0,E77*(1-L77/C77),E77))</f>
@@ -15688,7 +15694,7 @@
       </c>
       <c r="K77" s="37" t="n">
         <f aca="false">MIN(C77,MAX(0,G$59-SUMPRODUCT(($D$61:$D$90&gt;D77)*$C$61:$C$90)))</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="L77" s="37" t="n">
         <f aca="false">MIN(C77,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D77)*$C$61:$C$90)))</f>
@@ -15708,7 +15714,7 @@
       </c>
       <c r="P77" s="28" t="n">
         <f aca="false">IF(E77&gt;0,G77*Channels!V21/E77,0)</f>
-        <v>0.44622905027933</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="28" t="n">
         <f aca="false">IF(E77&gt;0,H77*Channels!V21/E77,0)</f>
@@ -15820,7 +15826,7 @@
       </c>
       <c r="G79" s="28" t="n">
         <f aca="false">IF(N79&gt;0,E79*MAX(0,N79-MIN(K79,N79))/N79,IF(C79&gt;0,E79*(1-K79/C79),E79))</f>
-        <v>0.12650593575419</v>
+        <v>0</v>
       </c>
       <c r="H79" s="28" t="n">
         <f aca="false">IF(N79&gt;0,E79*MAX(0,N79-MIN(L79,N79))/N79,IF(C79&gt;0,E79*(1-L79/C79),E79))</f>
@@ -15836,7 +15842,7 @@
       </c>
       <c r="K79" s="37" t="n">
         <f aca="false">MIN(C79,MAX(0,G$59-SUMPRODUCT(($D$61:$D$90&gt;D79)*$C$61:$C$90)))</f>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="L79" s="37" t="n">
         <f aca="false">MIN(C79,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D79)*$C$61:$C$90)))</f>
@@ -15856,7 +15862,7 @@
       </c>
       <c r="P79" s="28" t="n">
         <f aca="false">IF(E79&gt;0,G79*Channels!V23/E79,0)</f>
-        <v>0.44622905027933</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="28" t="n">
         <f aca="false">IF(E79&gt;0,H79*Channels!V23/E79,0)</f>
@@ -15878,7 +15884,7 @@
       </c>
       <c r="C80" s="37" t="n">
         <f aca="false">Channels!AA24</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="D80" s="41" t="n">
         <f aca="false">IF(ISNUMBER(Channels!AB24),Channels!AB24,0)+ROW()/1000000</f>
@@ -15886,11 +15892,11 @@
       </c>
       <c r="E80" s="28" t="n">
         <f aca="false">Channels!U24</f>
-        <v>0.50694</v>
+        <v>0.0708016759776536</v>
       </c>
       <c r="F80" s="28" t="n">
         <f aca="false">IF(N80&gt;0,E80*MAX(0,N80-MIN(J80,N80))/N80,IF(C80&gt;0,E80*(1-J80/C80),E80))</f>
-        <v>0.50694</v>
+        <v>0.0708016759776536</v>
       </c>
       <c r="G80" s="28" t="n">
         <f aca="false">IF(N80&gt;0,E80*MAX(0,N80-MIN(K80,N80))/N80,IF(C80&gt;0,E80*(1-K80/C80),E80))</f>
@@ -15910,23 +15916,23 @@
       </c>
       <c r="K80" s="37" t="n">
         <f aca="false">MIN(C80,MAX(0,G$59-SUMPRODUCT(($D$61:$D$90&gt;D80)*$C$61:$C$90)))</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="L80" s="37" t="n">
         <f aca="false">MIN(C80,MAX(0,H$59-SUMPRODUCT(($D$61:$D$90&gt;D80)*$C$61:$C$90)))</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="M80" s="37" t="n">
         <f aca="false">MIN(C80,MAX(0,I$59-SUMPRODUCT(($D$61:$D$90&gt;D80)*$C$61:$C$90)))</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="N80" s="37" t="n">
         <f aca="false">Channels!X24</f>
-        <v>5370</v>
+        <v>750</v>
       </c>
       <c r="O80" s="28" t="n">
         <f aca="false">IF(E80&gt;0,F80*Channels!V24/E80,0)</f>
-        <v>2.13</v>
+        <v>0.297486033519553</v>
       </c>
       <c r="P80" s="28" t="n">
         <f aca="false">IF(E80&gt;0,G80*Channels!V24/E80,0)</f>
@@ -16683,7 +16689,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E91" s="24" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16696,15 +16702,15 @@
       </c>
       <c r="G92" s="28" t="n">
         <f aca="false">SUMIFS(G$61:G$90,$B$61:$B$90,$E92)*G$100</f>
-        <v>30</v>
+        <v>29.859437849162</v>
       </c>
       <c r="H92" s="28" t="n">
         <f aca="false">SUMIFS(H$61:H$90,$B$61:$B$90,$E92)*H$100</f>
-        <v>29.859437849162</v>
+        <v>27.1132218976179</v>
       </c>
       <c r="I92" s="28" t="n">
         <f aca="false">SUMIFS(I$61:I$90,$B$61:$B$90,$E92)*I$100</f>
-        <v>22.881639103945</v>
+        <v>17.222185978945</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16738,15 +16744,15 @@
       </c>
       <c r="G94" s="28" t="n">
         <f aca="false">SUMIFS(G$61:G$90,$B$61:$B$90,$E94)*G$100</f>
-        <v>15</v>
+        <v>14.8734940642458</v>
       </c>
       <c r="H94" s="28" t="n">
         <f aca="false">SUMIFS(H$61:H$90,$B$61:$B$90,$E94)*H$100</f>
-        <v>13.3391161218711</v>
+        <v>14.32794825</v>
       </c>
       <c r="I94" s="28" t="n">
         <f aca="false">SUMIFS(I$61:I$90,$B$61:$B$90,$E94)*I$100</f>
-        <v>10.11797325</v>
+        <v>14.32794825</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16755,11 +16761,11 @@
       </c>
       <c r="F95" s="28" t="n">
         <f aca="false">SUMIFS(F$61:F$90,$B$61:$B$90,$E95)*F$100</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="G95" s="28" t="n">
         <f aca="false">SUMIFS(G$61:G$90,$B$61:$B$90,$E95)*G$100</f>
-        <v>5.33255888857614</v>
+        <v>4.63144714646623</v>
       </c>
       <c r="H95" s="28" t="n">
         <f aca="false">SUMIFS(H$61:H$90,$B$61:$B$90,$E95)*H$100</f>
@@ -16772,70 +16778,70 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E96" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F96" s="31" t="n">
         <f aca="false">SUM(F92:F95)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="G96" s="31" t="n">
         <f aca="false">SUM(G92:G95)</f>
-        <v>95.3325588885761</v>
+        <v>94.3643790598741</v>
       </c>
       <c r="H96" s="31" t="n">
         <f aca="false">SUM(H92:H95)</f>
-        <v>89.7588819710332</v>
+        <v>88.0014981476179</v>
       </c>
       <c r="I96" s="31" t="n">
         <f aca="false">SUM(I92:I95)</f>
-        <v>79.559940353945</v>
+        <v>78.110462228945</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E97" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F97" s="37" t="n">
         <f aca="false">IF(F96&gt;0,F57/F96,0)</f>
-        <v>2329.10665959644</v>
+        <v>2075</v>
       </c>
       <c r="G97" s="37" t="n">
         <f aca="false">IF(G96&gt;0,G57/G96,0)</f>
-        <v>2050.71595978556</v>
+        <v>1869.08451851403</v>
       </c>
       <c r="H97" s="37" t="n">
         <f aca="false">IF(H96&gt;0,H57/H96,0)</f>
-        <v>1793.69435608565</v>
+        <v>1650.54008235577</v>
       </c>
       <c r="I97" s="37" t="n">
         <f aca="false">IF(I96&gt;0,I57/I96,0)</f>
-        <v>1445.451058515</v>
+        <v>1328.24716484079</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E99" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F99" s="28" t="n">
         <f aca="false">SUM(O61:O90)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="G99" s="28" t="n">
         <f aca="false">SUM(P61:P90)</f>
-        <v>289.086978976135</v>
+        <v>285.248673219653</v>
       </c>
       <c r="H99" s="28" t="n">
         <f aca="false">SUM(Q61:Q90)</f>
-        <v>266.932543385373</v>
+        <v>261.702341522019</v>
       </c>
       <c r="I99" s="28" t="n">
         <f aca="false">SUM(R61:R90)</f>
-        <v>233.418745351629</v>
+        <v>230.302227494486</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E100" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="F100" s="26" t="n">
         <f aca="false">IF(F99&gt;0,MIN(1,Funnel!$B$22/F99),1)</f>
@@ -16856,7 +16862,7 @@
     </row>
     <row r="102" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -16892,92 +16898,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="Z3" s="45" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16994,11 +17000,11 @@
       </c>
       <c r="D4" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B4&lt;=Funnel!$B$19,Z4,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B4&lt;=Funnel!$B$20,D4,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
-        <v>0.0933333333333333</v>
+        <v>0.126582278481013</v>
       </c>
       <c r="F4" s="26" t="n">
         <f aca="false">IF(A4-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A4-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
@@ -17010,11 +17016,11 @@
       </c>
       <c r="H4" s="37" t="n">
         <f aca="false">$F$19*D4+$F$20*E4+$F$31*Y4</f>
-        <v>12371.3008611577</v>
+        <v>15554.707385075</v>
       </c>
       <c r="I4" s="37" t="n">
         <f aca="false">IF(A4=1,$F$21,0)</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
       <c r="J4" s="37" t="n">
         <f aca="false">$F$22*F4+$F$23*G4</f>
@@ -17030,19 +17036,19 @@
       </c>
       <c r="M4" s="37" t="n">
         <f aca="false">SUM(H4:L4)</f>
-        <v>27714.3008611577</v>
+        <v>29448.707385075</v>
       </c>
       <c r="N4" s="37" t="n">
         <f aca="false">SUM($M$4:M4)</f>
-        <v>27714.3008611577</v>
+        <v>29448.707385075</v>
       </c>
       <c r="O4" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D4+(Funnel!$M$8-$F$28-$F$35)*E4+($F$27+$F$28)*X4+($F$34+$F$35)*Y4</f>
-        <v>205.15926107728</v>
+        <v>281.303070419468</v>
       </c>
       <c r="P4" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D4+(Funnel!$O$8-$F$26-$F$33)*E4+($F$25+$F$26)*X4+($F$32+$F$33)*Y4</f>
-        <v>28.9504808554256</v>
+        <v>38.3485396476843</v>
       </c>
       <c r="Q4" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C4,Funnel!$B$17)-MAX(B4,Funnel!$B$13)+1)/7</f>
@@ -17050,11 +17056,11 @@
       </c>
       <c r="R4" s="26" t="n">
         <f aca="false">IF(Q4&gt;0,P4/Q4,IF(P4&gt;0,9.99,0))</f>
-        <v>0.736921330865379</v>
+        <v>0.976144645577418</v>
       </c>
       <c r="S4" s="2" t="str">
         <f aca="false">IF(P4&gt;Q4+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R4&gt;Assumptions!$D$106,"Full",IF(AND(Q4&gt;=Assumptions!$D$107,P4&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v/>
+        <v>Full</v>
       </c>
       <c r="T4" s="28" t="n">
         <f aca="false">$F$38*(F4*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A4-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A4-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A4-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
@@ -17082,7 +17088,7 @@
       </c>
       <c r="Z4" s="26" t="n">
         <f aca="false">Assumptions!$D$55</f>
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17099,11 +17105,11 @@
       </c>
       <c r="D5" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B5&lt;=Funnel!$B$19,Z5,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.11</v>
+        <v>0.155</v>
       </c>
       <c r="E5" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B5&lt;=Funnel!$B$20,D5,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
-        <v>0.146666666666667</v>
+        <v>0.19620253164557</v>
       </c>
       <c r="F5" s="26" t="n">
         <f aca="false">IF(A5-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A5-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
@@ -17115,7 +17121,7 @@
       </c>
       <c r="H5" s="37" t="n">
         <f aca="false">$F$19*D5+$F$20*E5+$F$31*Y5</f>
-        <v>19413.9790675335</v>
+        <v>24083.6844468662</v>
       </c>
       <c r="I5" s="37" t="n">
         <f aca="false">IF(A5=1,$F$21,0)</f>
@@ -17135,19 +17141,19 @@
       </c>
       <c r="M5" s="37" t="n">
         <f aca="false">SUM(H5:L5)</f>
-        <v>24813.9790675335</v>
+        <v>29483.6844468662</v>
       </c>
       <c r="N5" s="43" t="n">
         <f aca="false">SUM($M$4:M5)</f>
-        <v>52528.2799286911</v>
+        <v>58932.3918319411</v>
       </c>
       <c r="O5" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D5+(Funnel!$M$8-$F$28-$F$35)*E5+($F$27+$F$28)*X5+($F$34+$F$35)*Y5</f>
-        <v>309.77062569955</v>
+        <v>424.197449954852</v>
       </c>
       <c r="P5" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D5+(Funnel!$O$8-$F$26-$F$33)*E5+($F$25+$F$26)*X5+($F$32+$F$33)*Y5</f>
-        <v>39.9419159012661</v>
+        <v>54.0607686438288</v>
       </c>
       <c r="Q5" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C5,Funnel!$B$17)-MAX(B5,Funnel!$B$13)+1)/7</f>
@@ -17155,11 +17161,11 @@
       </c>
       <c r="R5" s="26" t="n">
         <f aca="false">IF(Q5&gt;0,P5/Q5,IF(P5&gt;0,9.99,0))</f>
-        <v>0.726216652750293</v>
+        <v>0.982923066251432</v>
       </c>
       <c r="S5" s="2" t="str">
         <f aca="false">IF(P5&gt;Q5+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R5&gt;Assumptions!$D$106,"Full",IF(AND(Q5&gt;=Assumptions!$D$107,P5&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v>Under 45 – release reserve</v>
+        <v>Full</v>
       </c>
       <c r="T5" s="28" t="n">
         <f aca="false">$F$38*(F5*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A5-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A5-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A5-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
@@ -17187,7 +17193,7 @@
       </c>
       <c r="Z5" s="26" t="n">
         <f aca="false">Assumptions!$D$56</f>
-        <v>0.11</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17204,11 +17210,11 @@
       </c>
       <c r="D6" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B6&lt;=Funnel!$B$19,Z6,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
       <c r="E6" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B6&lt;=Funnel!$B$20,D6,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
-        <v>0.213333333333333</v>
+        <v>0.221518987341772</v>
       </c>
       <c r="F6" s="26" t="n">
         <f aca="false">IF(A6-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A6-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
@@ -17220,7 +17226,7 @@
       </c>
       <c r="H6" s="37" t="n">
         <f aca="false">$F$19*D6+$F$20*E6+$F$31*Y6</f>
-        <v>28225.7928255032</v>
+        <v>27182.3859238812</v>
       </c>
       <c r="I6" s="37" t="n">
         <f aca="false">IF(A6=1,$F$21,0)</f>
@@ -17240,19 +17246,19 @@
       </c>
       <c r="M6" s="37" t="n">
         <f aca="false">SUM(H6:L6)</f>
-        <v>28225.7928255032</v>
+        <v>27182.3859238812</v>
       </c>
       <c r="N6" s="37" t="n">
         <f aca="false">SUM($M$4:M6)</f>
-        <v>80754.0727541943</v>
+        <v>86114.7777558223</v>
       </c>
       <c r="O6" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D6+(Funnel!$M$8-$F$28-$F$35)*E6+($F$27+$F$28)*X6+($F$34+$F$35)*Y6</f>
-        <v>385.377090676181</v>
+        <v>428.72675139778</v>
       </c>
       <c r="P6" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D6+(Funnel!$O$8-$F$26-$F$33)*E6+($F$25+$F$26)*X6+($F$32+$F$33)*Y6</f>
-        <v>48.6990277800864</v>
+        <v>53.9421710305813</v>
       </c>
       <c r="Q6" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C6,Funnel!$B$17)-MAX(B6,Funnel!$B$13)+1)/7</f>
@@ -17260,11 +17266,11 @@
       </c>
       <c r="R6" s="26" t="n">
         <f aca="false">IF(Q6&gt;0,P6/Q6,IF(P6&gt;0,9.99,0))</f>
-        <v>0.885436868728844</v>
+        <v>0.98076674601057</v>
       </c>
       <c r="S6" s="2" t="str">
         <f aca="false">IF(P6&gt;Q6+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R6&gt;Assumptions!$D$106,"Full",IF(AND(Q6&gt;=Assumptions!$D$107,P6&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v/>
+        <v>Full</v>
       </c>
       <c r="T6" s="28" t="n">
         <f aca="false">$F$38*(F6*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A6-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A6-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A6-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
@@ -17292,7 +17298,7 @@
       </c>
       <c r="Z6" s="26" t="n">
         <f aca="false">Assumptions!$D$57</f>
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17309,15 +17315,15 @@
       </c>
       <c r="D7" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B7&lt;=Funnel!$B$19,Z7,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B7&lt;=Funnel!$B$20,D7,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
-        <v>0.273333333333333</v>
+        <v>0.227848101265823</v>
       </c>
       <c r="F7" s="26" t="n">
         <f aca="false">IF(A7-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A7-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="26" t="n">
         <f aca="false">IF(A7-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A7-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
@@ -17325,7 +17331,7 @@
       </c>
       <c r="H7" s="37" t="n">
         <f aca="false">$F$19*D7+$F$20*E7+$F$31*Y7</f>
-        <v>36158.546807676</v>
+        <v>27954.4092931349</v>
       </c>
       <c r="I7" s="37" t="n">
         <f aca="false">IF(A7=1,$F$21,0)</f>
@@ -17333,7 +17339,7 @@
       </c>
       <c r="J7" s="37" t="n">
         <f aca="false">$F$22*F7+$F$23*G7</f>
-        <v>734.3713125</v>
+        <v>1049.101875</v>
       </c>
       <c r="K7" s="37" t="n">
         <f aca="false">IF(A7=1,Budget!$C$6,0)</f>
@@ -17345,19 +17351,19 @@
       </c>
       <c r="M7" s="37" t="n">
         <f aca="false">SUM(H7:L7)</f>
-        <v>36892.918120176</v>
+        <v>29003.5111681349</v>
       </c>
       <c r="N7" s="37" t="n">
         <f aca="false">SUM($M$4:M7)</f>
-        <v>117646.99087437</v>
+        <v>115118.288923957</v>
       </c>
       <c r="O7" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D7+(Funnel!$M$8-$F$28-$F$35)*E7+($F$27+$F$28)*X7+($F$34+$F$35)*Y7</f>
-        <v>491.464297428856</v>
+        <v>439.129595723431</v>
       </c>
       <c r="P7" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D7+(Funnel!$O$8-$F$26-$F$33)*E7+($F$25+$F$26)*X7+($F$32+$F$33)*Y7</f>
-        <v>61.2455793432357</v>
+        <v>54.5601302028837</v>
       </c>
       <c r="Q7" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C7,Funnel!$B$17)-MAX(B7,Funnel!$B$13)+1)/7</f>
@@ -17365,15 +17371,15 @@
       </c>
       <c r="R7" s="26" t="n">
         <f aca="false">IF(Q7&gt;0,P7/Q7,IF(P7&gt;0,9.99,0))</f>
-        <v>1.11355598805883</v>
+        <v>0.992002367325158</v>
       </c>
       <c r="S7" s="2" t="str">
         <f aca="false">IF(P7&gt;Q7+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R7&gt;Assumptions!$D$106,"Full",IF(AND(Q7&gt;=Assumptions!$D$107,P7&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v>OVER 55/wk – pace down</v>
+        <v>Full</v>
       </c>
       <c r="T7" s="28" t="n">
         <f aca="false">$F$38*(F7*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A7-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A7-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A7-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>8.50195338571749</v>
+        <v>11.0535022824704</v>
       </c>
       <c r="U7" s="28" t="n">
         <f aca="false">$F$38*(G7*(Budget!$G$24-$F$30-$F$37)+IF(A7-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A7-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A7-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
@@ -17381,11 +17387,11 @@
       </c>
       <c r="V7" s="28" t="n">
         <f aca="false">T7+U7</f>
-        <v>8.50195338571749</v>
+        <v>11.0535022824704</v>
       </c>
       <c r="W7" s="28" t="n">
         <f aca="false">SUM($V$4:V7)</f>
-        <v>8.50195338571749</v>
+        <v>11.0535022824704</v>
       </c>
       <c r="X7" s="26" t="n">
         <f aca="false">IF(A7=1,Assumptions!$D$50,IF(A7=2,1-Assumptions!$D$50,0))</f>
@@ -17397,7 +17403,7 @@
       </c>
       <c r="Z7" s="26" t="n">
         <f aca="false">Assumptions!$D$58</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17414,23 +17420,23 @@
       </c>
       <c r="D8" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B8&lt;=Funnel!$B$19,Z8,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="E8" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B8&lt;=Funnel!$B$20,D8,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
-        <v>0.273333333333333</v>
+        <v>0.227848101265823</v>
       </c>
       <c r="F8" s="26" t="n">
         <f aca="false">IF(A8-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A8-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.11</v>
+        <v>0.155</v>
       </c>
       <c r="G8" s="26" t="n">
         <f aca="false">IF(A8-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A8-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
-        <v>0.0933333333333333</v>
+        <v>0.126582278481013</v>
       </c>
       <c r="H8" s="37" t="n">
         <f aca="false">$F$19*D8+$F$20*E8+$F$31*Y8</f>
-        <v>36158.546807676</v>
+        <v>27954.4092931349</v>
       </c>
       <c r="I8" s="37" t="n">
         <f aca="false">IF(A8=1,$F$21,0)</f>
@@ -17438,7 +17444,7 @@
       </c>
       <c r="J8" s="37" t="n">
         <f aca="false">$F$22*F8+$F$23*G8</f>
-        <v>1222.9844625</v>
+        <v>1719.65094422468</v>
       </c>
       <c r="K8" s="37" t="n">
         <f aca="false">IF(A8=1,Budget!$C$6,0)</f>
@@ -17450,19 +17456,19 @@
       </c>
       <c r="M8" s="37" t="n">
         <f aca="false">SUM(H8:L8)</f>
-        <v>37381.531270176</v>
+        <v>29674.0602373596</v>
       </c>
       <c r="N8" s="37" t="n">
         <f aca="false">SUM($M$4:M8)</f>
-        <v>155028.522144546</v>
+        <v>144792.349161317</v>
       </c>
       <c r="O8" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D8+(Funnel!$M$8-$F$28-$F$35)*E8+($F$27+$F$28)*X8+($F$34+$F$35)*Y8</f>
-        <v>491.464297428856</v>
+        <v>439.129595723431</v>
       </c>
       <c r="P8" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D8+(Funnel!$O$8-$F$26-$F$33)*E8+($F$25+$F$26)*X8+($F$32+$F$33)*Y8</f>
-        <v>61.2455793432357</v>
+        <v>54.5601302028837</v>
       </c>
       <c r="Q8" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C8,Funnel!$B$17)-MAX(B8,Funnel!$B$13)+1)/7</f>
@@ -17470,27 +17476,27 @@
       </c>
       <c r="R8" s="26" t="n">
         <f aca="false">IF(Q8&gt;0,P8/Q8,IF(P8&gt;0,9.99,0))</f>
-        <v>1.11355598805883</v>
+        <v>0.992002367325158</v>
       </c>
       <c r="S8" s="2" t="str">
         <f aca="false">IF(P8&gt;Q8+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R8&gt;Assumptions!$D$106,"Full",IF(AND(Q8&gt;=Assumptions!$D$107,P8&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v>OVER 55/wk – pace down</v>
+        <v>Full</v>
       </c>
       <c r="T8" s="28" t="n">
         <f aca="false">$F$38*(F8*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A8-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A8-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A8-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>11.4427649155351</v>
+        <v>15.2700882606645</v>
       </c>
       <c r="U8" s="28" t="n">
         <f aca="false">$F$38*(G8*(Budget!$G$24-$F$30-$F$37)+IF(A8-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A8-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A8-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
-        <v>1.03681339729981</v>
+        <v>1.46706081960688</v>
       </c>
       <c r="V8" s="28" t="n">
         <f aca="false">T8+U8</f>
-        <v>12.4795783128349</v>
+        <v>16.7371490802714</v>
       </c>
       <c r="W8" s="28" t="n">
         <f aca="false">SUM($V$4:V8)</f>
-        <v>20.9815316985524</v>
+        <v>27.7906513627418</v>
       </c>
       <c r="X8" s="26" t="n">
         <f aca="false">IF(A8=1,Assumptions!$D$50,IF(A8=2,1-Assumptions!$D$50,0))</f>
@@ -17502,7 +17508,7 @@
       </c>
       <c r="Z8" s="26" t="n">
         <f aca="false">Assumptions!$D$59</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17519,7 +17525,7 @@
       </c>
       <c r="D9" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14)&gt;0,IF(B9&lt;=Funnel!$B$19,Z9,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$19)*$Z$4:$Z$14),0)</f>
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="E9" s="26" t="n">
         <f aca="false">IF(SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14)&gt;0,IF(B9&lt;=Funnel!$B$20,D9,0)/SUMPRODUCT(($B$4:$B$14&lt;=Funnel!$B$20)*$D$4:$D$14),0)</f>
@@ -17527,15 +17533,15 @@
       </c>
       <c r="F9" s="26" t="n">
         <f aca="false">IF(A9-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A9-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.16</v>
+        <v>0.175</v>
       </c>
       <c r="G9" s="26" t="n">
         <f aca="false">IF(A9-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A9-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
-        <v>0.146666666666667</v>
+        <v>0.19620253164557</v>
       </c>
       <c r="H9" s="37" t="n">
         <f aca="false">$F$19*D9+$F$20*E9+$F$31*Y9</f>
-        <v>29122.4554565154</v>
+        <v>22961.362583473</v>
       </c>
       <c r="I9" s="37" t="n">
         <f aca="false">IF(A9=1,$F$21,0)</f>
@@ -17543,7 +17549,7 @@
       </c>
       <c r="J9" s="37" t="n">
         <f aca="false">$F$22*F9+$F$23*G9</f>
-        <v>1786.9482</v>
+        <v>1980.91999011076</v>
       </c>
       <c r="K9" s="37" t="n">
         <f aca="false">IF(A9=1,Budget!$C$6,0)</f>
@@ -17555,19 +17561,19 @@
       </c>
       <c r="M9" s="37" t="n">
         <f aca="false">SUM(H9:L9)</f>
-        <v>30909.4036565154</v>
+        <v>24942.2825735837</v>
       </c>
       <c r="N9" s="37" t="n">
         <f aca="false">SUM($M$4:M9)</f>
-        <v>185937.925801062</v>
+        <v>169734.631734901</v>
       </c>
       <c r="O9" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D9+(Funnel!$M$8-$F$28-$F$35)*E9+($F$27+$F$28)*X9+($F$34+$F$35)*Y9</f>
-        <v>477.233647257281</v>
+        <v>400.876263696116</v>
       </c>
       <c r="P9" s="25" t="n">
         <f aca="false">(Funnel!$O$5+Funnel!$O$6+Funnel!$O$7-$F$25-$F$32)*D9+(Funnel!$O$8-$F$26-$F$33)*E9+($F$25+$F$26)*X9+($F$32+$F$33)*Y9</f>
-        <v>63.3646861370199</v>
+        <v>53.2263363550967</v>
       </c>
       <c r="Q9" s="25" t="n">
         <f aca="false">Assumptions!$D$9*MAX(0,MIN(C9,Funnel!$B$17)-MAX(B9,Funnel!$B$13)+1)/7</f>
@@ -17575,27 +17581,27 @@
       </c>
       <c r="R9" s="26" t="n">
         <f aca="false">IF(Q9&gt;0,P9/Q9,IF(P9&gt;0,9.99,0))</f>
-        <v>1.15208520249127</v>
+        <v>0.967751570092667</v>
       </c>
       <c r="S9" s="2" t="str">
         <f aca="false">IF(P9&gt;Q9+0.5,"OVER "&amp;Assumptions!$D$9&amp;"/wk – pace down",IF(R9&gt;Assumptions!$D$106,"Full",IF(AND(Q9&gt;=Assumptions!$D$107,P9&lt;Assumptions!$D$107),"Under "&amp;Assumptions!$D$107&amp;" – release reserve","")))</f>
-        <v>OVER 55/wk – pace down</v>
+        <v>Full</v>
       </c>
       <c r="T9" s="28" t="n">
         <f aca="false">$F$38*(F9*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A9-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A9-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A9-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>13.9212059701824</v>
+        <v>15.1969804185589</v>
       </c>
       <c r="U9" s="28" t="n">
         <f aca="false">$F$38*(G9*(Budget!$G$24-$F$30-$F$37)+IF(A9-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A9-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A9-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
-        <v>1.4695260290519</v>
+        <v>2.1200445896972</v>
       </c>
       <c r="V9" s="28" t="n">
         <f aca="false">T9+U9</f>
-        <v>15.3907319992343</v>
+        <v>17.3170250082561</v>
       </c>
       <c r="W9" s="28" t="n">
         <f aca="false">SUM($V$4:V9)</f>
-        <v>36.3722636977867</v>
+        <v>45.1076763709979</v>
       </c>
       <c r="X9" s="26" t="n">
         <f aca="false">IF(A9=1,Assumptions!$D$50,IF(A9=2,1-Assumptions!$D$50,0))</f>
@@ -17607,7 +17613,7 @@
       </c>
       <c r="Z9" s="26" t="n">
         <f aca="false">Assumptions!$D$60</f>
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17632,11 +17638,11 @@
       </c>
       <c r="F10" s="26" t="n">
         <f aca="false">IF(A10-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A10-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="G10" s="26" t="n">
         <f aca="false">IF(A10-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A10-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
-        <v>0.213333333333333</v>
+        <v>0.221518987341772</v>
       </c>
       <c r="H10" s="37" t="n">
         <f aca="false">$F$19*D10+$F$20*E10+$F$31*Y10</f>
@@ -17648,7 +17654,7 @@
       </c>
       <c r="J10" s="37" t="n">
         <f aca="false">$F$22*F10+$F$23*G10</f>
-        <v>2308.31004375</v>
+        <v>2052.0836914557</v>
       </c>
       <c r="K10" s="37" t="n">
         <f aca="false">IF(A10=1,Budget!$C$6,0)</f>
@@ -17660,11 +17666,11 @@
       </c>
       <c r="M10" s="37" t="n">
         <f aca="false">SUM(H10:L10)</f>
-        <v>2308.31004375</v>
+        <v>2052.0836914557</v>
       </c>
       <c r="N10" s="37" t="n">
         <f aca="false">SUM($M$4:M10)</f>
-        <v>188246.235844812</v>
+        <v>171786.715426356</v>
       </c>
       <c r="O10" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D10+(Funnel!$M$8-$F$28-$F$35)*E10+($F$27+$F$28)*X10+($F$34+$F$35)*Y10</f>
@@ -17688,19 +17694,19 @@
       </c>
       <c r="T10" s="28" t="n">
         <f aca="false">$F$38*(F10*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A10-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A10-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A10-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>17.4355841278119</v>
+        <v>15.3092933805177</v>
       </c>
       <c r="U10" s="28" t="n">
         <f aca="false">$F$38*(G10*(Budget!$G$24-$F$30-$F$37)+IF(A10-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A10-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A10-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
-        <v>1.77088389926969</v>
+        <v>2.11469329004072</v>
       </c>
       <c r="V10" s="28" t="n">
         <f aca="false">T10+U10</f>
-        <v>19.2064680270816</v>
+        <v>17.4239866705585</v>
       </c>
       <c r="W10" s="28" t="n">
         <f aca="false">SUM($V$4:V10)</f>
-        <v>55.5787317248683</v>
+        <v>62.5316630415564</v>
       </c>
       <c r="X10" s="26" t="n">
         <f aca="false">IF(A10=1,Assumptions!$D$50,IF(A10=2,1-Assumptions!$D$50,0))</f>
@@ -17737,11 +17743,11 @@
       </c>
       <c r="F11" s="26" t="n">
         <f aca="false">IF(A11-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A11-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.205</v>
+        <v>0.18</v>
       </c>
       <c r="G11" s="26" t="n">
         <f aca="false">IF(A11-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A11-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
-        <v>0.273333333333333</v>
+        <v>0.227848101265823</v>
       </c>
       <c r="H11" s="37" t="n">
         <f aca="false">$F$19*D11+$F$20*E11+$F$31*Y11</f>
@@ -17753,7 +17759,7 @@
       </c>
       <c r="J11" s="37" t="n">
         <f aca="false">$F$22*F11+$F$23*G11</f>
-        <v>2352.64944375</v>
+        <v>2056.76084335443</v>
       </c>
       <c r="K11" s="37" t="n">
         <f aca="false">IF(A11=1,Budget!$C$6,0)</f>
@@ -17765,11 +17771,11 @@
       </c>
       <c r="M11" s="37" t="n">
         <f aca="false">SUM(H11:L11)</f>
-        <v>2352.64944375</v>
+        <v>2056.76084335443</v>
       </c>
       <c r="N11" s="37" t="n">
         <f aca="false">SUM($M$4:M11)</f>
-        <v>190598.885288562</v>
+        <v>173843.476269711</v>
       </c>
       <c r="O11" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D11+(Funnel!$M$8-$F$28-$F$35)*E11+($F$27+$F$28)*X11+($F$34+$F$35)*Y11</f>
@@ -17793,19 +17799,19 @@
       </c>
       <c r="T11" s="28" t="n">
         <f aca="false">$F$38*(F11*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A11-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A11-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A11-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>17.4355841278119</v>
+        <v>15.3092933805177</v>
       </c>
       <c r="U11" s="28" t="n">
         <f aca="false">$F$38*(G11*(Budget!$G$24-$F$30-$F$37)+IF(A11-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A11-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A11-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
-        <v>2.2365423371893</v>
+        <v>2.1491006503276</v>
       </c>
       <c r="V11" s="28" t="n">
         <f aca="false">T11+U11</f>
-        <v>19.6721264650012</v>
+        <v>17.4583940308453</v>
       </c>
       <c r="W11" s="28" t="n">
         <f aca="false">SUM($V$4:V11)</f>
-        <v>75.2508581898694</v>
+        <v>79.9900570724017</v>
       </c>
       <c r="X11" s="26" t="n">
         <f aca="false">IF(A11=1,Assumptions!$D$50,IF(A11=2,1-Assumptions!$D$50,0))</f>
@@ -17842,11 +17848,11 @@
       </c>
       <c r="F12" s="26" t="n">
         <f aca="false">IF(A12-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($D$4:$D$14,A12-ROUNDUP(Funnel!$B$15/7,0)),0)</f>
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="G12" s="26" t="n">
         <f aca="false">IF(A12-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($E$4:$E$14,A12-ROUNDUP(Funnel!$B$16/7,0)),0)</f>
-        <v>0.273333333333333</v>
+        <v>0.227848101265823</v>
       </c>
       <c r="H12" s="37" t="n">
         <f aca="false">$F$19*D12+$F$20*E12+$F$31*Y12</f>
@@ -17858,7 +17864,7 @@
       </c>
       <c r="J12" s="37" t="n">
         <f aca="false">$F$22*F12+$F$23*G12</f>
-        <v>2824.7452875</v>
+        <v>2371.49140585443</v>
       </c>
       <c r="K12" s="37" t="n">
         <f aca="false">IF(A12=1,Budget!$C$6,0)</f>
@@ -17870,11 +17876,11 @@
       </c>
       <c r="M12" s="37" t="n">
         <f aca="false">SUM(H12:L12)</f>
-        <v>2824.7452875</v>
+        <v>2371.49140585443</v>
       </c>
       <c r="N12" s="37" t="n">
         <f aca="false">SUM($M$4:M12)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="O12" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D12+(Funnel!$M$8-$F$28-$F$35)*E12+($F$27+$F$28)*X12+($F$34+$F$35)*Y12</f>
@@ -17898,19 +17904,19 @@
       </c>
       <c r="T12" s="28" t="n">
         <f aca="false">$F$38*(F12*(Budget!$G$21+Budget!$G$22+Budget!$G$23-$F$29-$F$36)+IF(A12-ROUNDUP(Funnel!$B$15/7,0)&gt;=1,INDEX($X$4:$X$14,A12-ROUNDUP(Funnel!$B$15/7,0))*$F$29+INDEX($Y$4:$Y$14,A12-ROUNDUP(Funnel!$B$15/7,0))*$F$36,0))</f>
-        <v>21.2629074729413</v>
+        <v>17.8608422772707</v>
       </c>
       <c r="U12" s="28" t="n">
         <f aca="false">$F$38*(G12*(Budget!$G$24-$F$30-$F$37)+IF(A12-ROUNDUP(Funnel!$B$16/7,0)&gt;=1,INDEX($X$4:$X$14,A12-ROUNDUP(Funnel!$B$16/7,0))*$F$30+INDEX($Y$4:$Y$14,A12-ROUNDUP(Funnel!$B$16/7,0))*$F$37,0))</f>
-        <v>2.2365423371893</v>
+        <v>2.1491006503276</v>
       </c>
       <c r="V12" s="28" t="n">
         <f aca="false">T12+U12</f>
-        <v>23.4994498101306</v>
+        <v>20.0099429275983</v>
       </c>
       <c r="W12" s="28" t="n">
         <f aca="false">SUM($V$4:V12)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="X12" s="26" t="n">
         <f aca="false">IF(A12=1,Assumptions!$D$50,IF(A12=2,1-Assumptions!$D$50,0))</f>
@@ -17979,7 +17985,7 @@
       </c>
       <c r="N13" s="37" t="n">
         <f aca="false">SUM($M$4:M13)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="O13" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D13+(Funnel!$M$8-$F$28-$F$35)*E13+($F$27+$F$28)*X13+($F$34+$F$35)*Y13</f>
@@ -18015,7 +18021,7 @@
       </c>
       <c r="W13" s="28" t="n">
         <f aca="false">SUM($V$4:V13)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="X13" s="26" t="n">
         <f aca="false">IF(A13=1,Assumptions!$D$50,IF(A13=2,1-Assumptions!$D$50,0))</f>
@@ -18084,7 +18090,7 @@
       </c>
       <c r="N14" s="37" t="n">
         <f aca="false">SUM($M$4:M14)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="O14" s="25" t="n">
         <f aca="false">(Funnel!$M$5+Funnel!$M$6+Funnel!$M$7-$F$27-$F$34)*D14+(Funnel!$M$8-$F$28-$F$35)*E14+($F$27+$F$28)*X14+($F$34+$F$35)*Y14</f>
@@ -18120,7 +18126,7 @@
       </c>
       <c r="W14" s="28" t="n">
         <f aca="false">SUM($V$4:V14)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="X14" s="26" t="n">
         <f aca="false">IF(A14=1,Assumptions!$D$50,IF(A14=2,1-Assumptions!$D$50,0))</f>
@@ -18137,7 +18143,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D15" s="47" t="n">
         <f aca="false">SUM(D4:D14)</f>
@@ -18157,11 +18163,11 @@
       </c>
       <c r="H15" s="38" t="n">
         <f aca="false">SUM(H4:H14)</f>
-        <v>161450.621826062</v>
+        <v>145690.958925565</v>
       </c>
       <c r="I15" s="38" t="n">
         <f aca="false">SUM(I4:I14)</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
       <c r="J15" s="38" t="n">
         <f aca="false">SUM(J4:J14)</f>
@@ -18177,15 +18183,15 @@
       </c>
       <c r="M15" s="38" t="n">
         <f aca="false">SUM(M4:M14)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
       <c r="O15" s="31" t="n">
         <f aca="false">SUM(O4:O14)</f>
-        <v>2360.469219568</v>
+        <v>2413.36272691508</v>
       </c>
       <c r="P15" s="31" t="n">
         <f aca="false">SUM(P4:P14)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="Q15" s="31" t="n">
         <f aca="false">SUM(Q4:Q14)</f>
@@ -18201,11 +18207,11 @@
       </c>
       <c r="U15" s="31" t="n">
         <f aca="false">SUM(U4:U14)</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="V15" s="31" t="n">
         <f aca="false">SUM(V4:V14)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="X15" s="47" t="n">
         <f aca="false">SUM(X4:X14)</f>
@@ -18222,7 +18228,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -18274,39 +18280,39 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="F19" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
-        <v>116489.821826062</v>
+        <v>109339.821826062</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="F20" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
-        <v>44920</v>
+        <v>36310.3370995034</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F21" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F22" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18315,7 +18321,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="F23" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18324,7 +18330,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F24" s="37" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -18333,7 +18339,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F25" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18342,7 +18348,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F26" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18351,7 +18357,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F27" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18360,7 +18366,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F28" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18369,7 +18375,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F29" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18378,7 +18384,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="F30" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18387,7 +18393,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F31" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -18396,7 +18402,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18405,7 +18411,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18414,7 +18420,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="F34" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18423,7 +18429,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18432,7 +18438,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F36" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18441,7 +18447,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18450,7 +18456,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="F38" s="26" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -18459,7 +18465,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18468,40 +18474,40 @@
         <v>282</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18565,27 +18571,27 @@
       </c>
       <c r="C45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B45)</f>
-        <v>6281.38560619507</v>
+        <v>2494.78896123104</v>
       </c>
       <c r="D45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$5</f>
-        <v>9785.03452402082</v>
+        <v>3806.92288990812</v>
       </c>
       <c r="E45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$6</f>
-        <v>11614.595671303</v>
+        <v>2265.88068215433</v>
       </c>
       <c r="F45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$7</f>
-        <v>14881.200703857</v>
+        <v>2330.62013021588</v>
       </c>
       <c r="G45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$8</f>
-        <v>14881.200703857</v>
+        <v>2330.62013021588</v>
       </c>
       <c r="H45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$9</f>
-        <v>7664.47240307761</v>
+        <v>2719.05681858519</v>
       </c>
       <c r="I45" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$10+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45,Channels!$C$5:$C$34,"Supervisors"))*$E$10+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B45)*$X$10</f>
@@ -18609,7 +18615,7 @@
       </c>
       <c r="N45" s="38" t="n">
         <f aca="false">SUM(C45:M45)</f>
-        <v>65107.8896123105</v>
+        <v>15947.8896123104</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18619,7 +18625,7 @@
       </c>
       <c r="C46" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B46)</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
       <c r="D46" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B46)*$X$5</f>
@@ -18663,7 +18669,7 @@
       </c>
       <c r="N46" s="38" t="n">
         <f aca="false">SUM(C46:M46)</f>
-        <v>10143</v>
+        <v>8694</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18673,27 +18679,27 @@
       </c>
       <c r="C47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B47)</f>
-        <v>2381.5</v>
+        <v>7617.24520246878</v>
       </c>
       <c r="D47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$5</f>
-        <v>3699.5</v>
+        <v>11776.7300638266</v>
       </c>
       <c r="E47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$6</f>
-        <v>4072</v>
+        <v>12280.1791043204</v>
       </c>
       <c r="F47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$7</f>
-        <v>5217.25</v>
+        <v>12631.0413644438</v>
       </c>
       <c r="G47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$8</f>
-        <v>5217.25</v>
+        <v>12631.0413644438</v>
       </c>
       <c r="H47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$9</f>
-        <v>3412.5</v>
+        <v>5084.1</v>
       </c>
       <c r="I47" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$10+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47,Channels!$C$5:$C$34,"Supervisors"))*$E$10+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B47)*$X$10</f>
@@ -18717,7 +18723,7 @@
       </c>
       <c r="N47" s="38" t="n">
         <f aca="false">SUM(C47:M47)</f>
-        <v>24000</v>
+        <v>62020.3370995034</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18727,27 +18733,27 @@
       </c>
       <c r="C48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B48)</f>
-        <v>4022.18980041714</v>
+        <v>5488.84257202448</v>
       </c>
       <c r="D48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$5</f>
-        <v>6277.72682922693</v>
+        <v>8477.70598663795</v>
       </c>
       <c r="E48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$6</f>
-        <v>7822.14811523917</v>
+        <v>8555.47450104284</v>
       </c>
       <c r="F48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$7</f>
-        <v>10022.1272726502</v>
+        <v>8799.91662964407</v>
       </c>
       <c r="G48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$8</f>
-        <v>10022.1272726502</v>
+        <v>8799.91662964407</v>
       </c>
       <c r="H48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$9</f>
-        <v>12222.1064300612</v>
+        <v>10266.5694012514</v>
       </c>
       <c r="I48" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$10+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48,Channels!$C$5:$C$34,"Supervisors"))*$E$10+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B48)*$X$10</f>
@@ -18781,23 +18787,23 @@
       </c>
       <c r="C49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B49)</f>
-        <v>1631.2</v>
+        <v>1200</v>
       </c>
       <c r="D49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$5</f>
-        <v>2477.6</v>
+        <v>1800</v>
       </c>
       <c r="E49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$6</f>
-        <v>985.6</v>
+        <v>0</v>
       </c>
       <c r="F49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$7</f>
-        <v>1262.8</v>
+        <v>0</v>
       </c>
       <c r="G49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$8</f>
-        <v>1262.8</v>
+        <v>0</v>
       </c>
       <c r="H49" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B49)*$X$9</f>
@@ -18825,7 +18831,7 @@
       </c>
       <c r="N49" s="38" t="n">
         <f aca="false">SUM(C49:M49)</f>
-        <v>7620</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18901,27 +18907,27 @@
       </c>
       <c r="F51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$7+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$7</f>
-        <v>734.3713125</v>
+        <v>1049.101875</v>
       </c>
       <c r="G51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$8+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$8</f>
-        <v>1222.9844625</v>
+        <v>1719.65094422468</v>
       </c>
       <c r="H51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$9+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$9</f>
-        <v>1786.9482</v>
+        <v>1980.91999011076</v>
       </c>
       <c r="I51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$10+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$10</f>
-        <v>2308.31004375</v>
+        <v>2052.0836914557</v>
       </c>
       <c r="J51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$11+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$11</f>
-        <v>2352.64944375</v>
+        <v>2056.76084335443</v>
       </c>
       <c r="K51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$12+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$12</f>
-        <v>2824.7452875</v>
+        <v>2371.49140585443</v>
       </c>
       <c r="L51" s="37" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")*$F$13+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B51,Channels!$C$5:$C$34,"Supervisors")*$G$13</f>
@@ -18943,27 +18949,27 @@
       </c>
       <c r="C52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B52)</f>
-        <v>2376</v>
+        <v>2880</v>
       </c>
       <c r="D52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$5</f>
-        <v>1848</v>
+        <v>2604</v>
       </c>
       <c r="E52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$6</f>
-        <v>2688</v>
+        <v>2940</v>
       </c>
       <c r="F52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$7</f>
-        <v>3444</v>
+        <v>3024</v>
       </c>
       <c r="G52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$8</f>
-        <v>3444</v>
+        <v>3024</v>
       </c>
       <c r="H52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$9</f>
-        <v>4200</v>
+        <v>3528</v>
       </c>
       <c r="I52" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$10+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52,Channels!$C$5:$C$34,"Supervisors"))*$E$10+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B52)*$X$10</f>
@@ -18997,27 +19003,27 @@
       </c>
       <c r="C53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$4+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$4+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$4+SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$E$5:$E$34,"Slot")+SUMIFS(Channels!$Y$5:$Y$34,Channels!$B$5:$B$34,$B53)</f>
-        <v>854.545454545455</v>
+        <v>1049.35064935065</v>
       </c>
       <c r="D53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$5+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$5+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$5</f>
-        <v>714.285714285714</v>
+        <v>1006.49350649351</v>
       </c>
       <c r="E53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$6+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$6+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$6</f>
-        <v>1038.96103896104</v>
+        <v>1136.36363636364</v>
       </c>
       <c r="F53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$7+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$7+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$7</f>
-        <v>1331.16883116883</v>
+        <v>1168.83116883117</v>
       </c>
       <c r="G53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$8+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$8+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$8</f>
-        <v>1331.16883116883</v>
+        <v>1168.83116883117</v>
       </c>
       <c r="H53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$9+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$9+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$9</f>
-        <v>1623.37662337662</v>
+        <v>1363.63636363636</v>
       </c>
       <c r="I53" s="37" t="n">
         <f aca="false">(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"&lt;&gt;Supervisors"))*$D$10+(SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53,Channels!$C$5:$C$34,"Supervisors"))*$E$10+SUMIFS(Channels!$Z$5:$Z$34,Channels!$B$5:$B$34,$B53)*$X$10</f>
@@ -19046,43 +19052,43 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C54" s="38" t="n">
         <f aca="false">SUM(C44:C53)</f>
-        <v>27714.3008611577</v>
+        <v>29448.707385075</v>
       </c>
       <c r="D54" s="38" t="n">
         <f aca="false">SUM(D44:D53)</f>
-        <v>24813.9790675335</v>
+        <v>29483.6844468662</v>
       </c>
       <c r="E54" s="38" t="n">
         <f aca="false">SUM(E44:E53)</f>
-        <v>28225.7928255032</v>
+        <v>27182.3859238812</v>
       </c>
       <c r="F54" s="38" t="n">
         <f aca="false">SUM(F44:F53)</f>
-        <v>36892.918120176</v>
+        <v>29003.5111681349</v>
       </c>
       <c r="G54" s="38" t="n">
         <f aca="false">SUM(G44:G53)</f>
-        <v>37381.531270176</v>
+        <v>29674.0602373596</v>
       </c>
       <c r="H54" s="38" t="n">
         <f aca="false">SUM(H44:H53)</f>
-        <v>30909.4036565154</v>
+        <v>24942.2825735837</v>
       </c>
       <c r="I54" s="38" t="n">
         <f aca="false">SUM(I44:I53)</f>
-        <v>2308.31004375</v>
+        <v>2052.0836914557</v>
       </c>
       <c r="J54" s="38" t="n">
         <f aca="false">SUM(J44:J53)</f>
-        <v>2352.64944375</v>
+        <v>2056.76084335443</v>
       </c>
       <c r="K54" s="38" t="n">
         <f aca="false">SUM(K44:K53)</f>
-        <v>2824.7452875</v>
+        <v>2371.49140585443</v>
       </c>
       <c r="L54" s="38" t="n">
         <f aca="false">SUM(L44:L53)</f>
@@ -19094,7 +19100,7 @@
       </c>
       <c r="N54" s="38" t="n">
         <f aca="false">SUM(N44:N53)</f>
-        <v>193423.630576062</v>
+        <v>176214.967675565</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19136,12 +19142,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19155,67 +19161,67 @@
         <v>283</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21350,7 +21356,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G35" s="38" t="n">
         <f aca="false">SUM(G5:G34)</f>
@@ -21403,7 +21409,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21412,46 +21418,46 @@
         <v>283</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21619,15 +21625,15 @@
       </c>
       <c r="L43" s="27" t="n">
         <f aca="false">IF(Funnel!O8*Funnel!G8&gt;0,I43*Assumptions!$D$40*K43*Budget!G24/(Funnel!O8*Funnel!G8),0)</f>
-        <v>0.241487732854974</v>
+        <v>0.241046294865248</v>
       </c>
       <c r="M43" s="28" t="n">
         <f aca="false">MAX(0,Funnel!O8-C43)</f>
-        <v>36.235</v>
+        <v>41.4858067226891</v>
       </c>
       <c r="N43" s="42" t="n">
         <f aca="false">MIN(O43,G43+(F43-G43)*K43+(E43-F43)*Assumptions!$D$40*K43+(C43-D43)*L43+M43*L43)</f>
-        <v>8.750308</v>
+        <v>10</v>
       </c>
       <c r="O43" s="25" t="n">
         <f aca="false">Funnel!B8</f>
@@ -21635,12 +21641,12 @@
       </c>
       <c r="P43" s="28" t="n">
         <f aca="false">O43-N43</f>
-        <v>1.249692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="24" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C44" s="31" t="n">
         <f aca="false">SUM(C40:C43)</f>
@@ -21664,11 +21670,11 @@
       </c>
       <c r="M44" s="31" t="n">
         <f aca="false">SUM(M40:M43)</f>
-        <v>303.447269360269</v>
+        <v>308.698076082958</v>
       </c>
       <c r="N44" s="31" t="n">
         <f aca="false">SUM(N40:N43)</f>
-        <v>98.750308</v>
+        <v>100</v>
       </c>
       <c r="O44" s="31" t="n">
         <f aca="false">SUM(O40:O43)</f>
@@ -21676,12 +21682,12 @@
       </c>
       <c r="P44" s="31" t="n">
         <f aca="false">SUM(P40:P43)</f>
-        <v>1.249692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Assumptions log = the model's only input sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Label: Given = from the brief; Researched = with link; Own estimate = one line of reasoning; Researched + Own estimate = the researched part (e.g. a price or range) is linked, the rest is reasoned.</t>
+    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Label: Given = from the brief; Researched = with link; Own estimate = derived by the arithmetic or rule written beside it (no unexplained values); Researched + Own estimate = a linked benchmark adapted by stated arithmetic.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Given in the brief</t>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -644,7 +644,7 @@
     <t xml:space="preserve">apps</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: at the plan share qualified (~25%), 30 applications give a standard error of √(0.25 × 0.75 ÷ 30) = 7.9 points (95% range ±15.5 points). n ≥ 30 is the usual minimum for reading a proportion; the Tracker also blends each read with the plan (R8), which narrows it further.</t>
+    <t xml:space="preserve">Statistics: NIST's rule for reading a proportion is min{Np, N(1 − p)} ≥ 5 (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm). At the planned share qualified of ~25%, N × 0.25 ≥ 5 needs N ≥ 20; 30 applications gives N × p = 7.5 and a standard error of √(0.25 × 0.75 ÷ 30) = 7.9 points.</t>
   </si>
   <si>
     <t xml:space="preserve">R3</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">× plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: one-sided 95% test (z = 1.645, the standard α = 5%). At the first judgement (30 applications, R2) the plan-blended share qualified (R8, equal weights) has a relative standard error of 16% (raw √(0.25 × 0.75 ÷ 30) = 7.9 points ÷ 25% = 32%, halved by the blend). Better than plan with 95% confidence = 1 − 1.645 × 0.16 = 0.74 → 0.75.</t>
+    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). One-sided test at α = 5% (z = 1.645). At the first judgement point (30 applications, R2) the plan-blended share qualified (R8, equal weights) has a relative standard error of 16% (raw √(0.25 × 0.75 ÷ 30) = 7.9 points ÷ 25% = 32%, halved by the blend). Better than plan with 95% confidence = 1 − 1.645 × 0.16 = 0.74 → 0.75.</t>
   </si>
   <si>
     <t xml:space="preserve">R4</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">Initiatives</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics convention: 5% significance level (the standard α). Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan reaches the PASS bar with ≥95% probability; one far below plan does not.</t>
+    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). PASS uses α = 5%. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan reaches the PASS bar with ≥95% probability.</t>
   </si>
   <si>
     <t xml:space="preserve">TP2</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">Initiative test: KILL bar significance level (an on-plan initiative falls below the bar with less than this probability)</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics convention: 1% significance level (the standard 'strong evidence' α). Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan falls below the KILL bar with &lt;1% probability, so a result there means the mechanism is not working.</t>
+    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). KILL uses α = 1%, the strictest common level, because killing is irreversible. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan falls below the KILL bar with &lt;1% probability.</t>
   </si>
   <si>
     <t xml:space="preserve">TK2</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">interviews</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: below 10 interviews one result moves the pass rate by more than 10 points (1 ÷ 10). 10 is the smallest sample with n × p ≥ 5 at the ~50% planned pass rate (normal-approximation rule).</t>
+    <t xml:space="preserve">Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the ~50% planned pass rate needs N ≥ 10 interviews.</t>
   </si>
   <si>
     <t xml:space="preserve">R10</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">offers</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: same rule as R9. At the ~70% planned acceptance, n × p ≥ 5 needs 5 ÷ 0.70 = 7.1 offers, so 7. Until then the planned acceptance rate is used.</t>
+    <t xml:space="preserve">Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the 70% planned acceptance: N × 0.70 ≥ 5 needs N ≥ 7.1 → 7 offers (N × 0.30 ≥ 5 would need 17, more offers than exist before the first check, so the Tracker blends with the plan until then).</t>
   </si>
   <si>
     <t xml:space="preserve">F1</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">Funnel / Weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Published standard: occupancy above 85% leads to regular capacity crises (Bagust, Place &amp; Posnett, BMJ 1999, 'Dynamics of bed use in accommodating emergency admissions', https://www.bmj.com/content/319/7203/155), the origin of the widely used 85% utilisation rule. Queueing theory gives the same knee: waiting grows with ρ ÷ (1 − ρ), 5.7× at 85% (https://en.wikipedia.org/wiki/Kingman%27s_formula).</t>
+    <t xml:space="preserve">Bagust, Place &amp; Posnett, BMJ 1999;319:155 (abstract, https://pubmed.ncbi.nlm.nih.gov/10406748/): 'Risks are discernible when average bed occupancy rates exceed about 85%'. Same shape as queueing theory, where waiting grows with ρ ÷ (1 − ρ).</t>
   </si>
   <si>
     <t xml:space="preserve">F4</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">Weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: a week is full when less than one day of assessments is spare: 1 − 1/7 = 86% (slots are counted per calendar day, 55 ÷ 7 = 7.9 a day).</t>
+    <t xml:space="preserve">Bagust, Place &amp; Posnett, BMJ 1999 (https://pubmed.ncbi.nlm.nih.gov/10406748/): 'regular bed shortages and periodic bed crises if average bed occupancy rises to 90% or more'. A week above 90% of its slots is therefore treated as full.</t>
   </si>
   <si>
     <t xml:space="preserve">R13</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">qualified/wk</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: = F4 × G3 = 0.86 × 55 = 47. A week forecast below 'full' has at least one day of slots spare, so reserve is released to the cheapest cells with capacity.</t>
+    <t xml:space="preserve">Derivation: = F4 × G3 = 0.90 × 55 = 49.5 → 50. A week forecast below 'full' has spare slots, so reserve is released to the cheapest cells with capacity.</t>
   </si>
   <si>
     <t xml:space="preserve">R8</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">Weight given to plan when updating qualified share (pseudo-applications)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: beta-binomial (empirical-Bayes) update with a prior worth 30 applications = R2. At the first point a cell may be judged (30 applications), its own data and the plan count equally; after 90 applications the data carry 75% of the weight.</t>
+    <t xml:space="preserve">Derivation: beta-binomial update whose prior is worth exactly R2 = 30 applications, so at the first point a cell may be judged its own data and the plan carry equal weight; after 90 applications the data carry 75%.</t>
   </si>
   <si>
     <t xml:space="preserve">7. Channel × role inputs (Part 2.2). Basis: CPC → CPA = CPC ÷ click-to-apply rate; CPA = bought per application/lead; Slot = fixed-price 30-day ad → CPA = price ÷ apps per ad; Free = no media cost.</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">records</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: maintenance and the campaign's trades (KldB 2513 Wartung/Instandhaltung 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisors 2519/2619/2629 36,989 = 536,520) are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile). Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it.</t>
+    <t xml:space="preserve">Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: the occupations this campaign hires from, KldB 2513 maintenance technicians (Wartung/Instandhaltung) 240,934 + 2625 industrial electricians 124,699 + 2611 mechatronics 84,727 + 2612 automation 49,171 + their supervisor codes 2519/2619/2629 36,989 = 536,520, are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile); 7.3% without the supervisor codes. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it.</t>
   </si>
   <si>
     <t xml:space="preserve">I1RM</t>
@@ -4832,7 +4832,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>202</v>
       </c>
@@ -4851,11 +4851,11 @@
       <c r="F86" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="G86" s="17" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>206</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="F87" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G87" s="13" t="s">
+      <c r="G87" s="17" t="s">
         <v>209</v>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       <c r="F93" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G93" s="13" t="s">
+      <c r="G93" s="17" t="s">
         <v>229</v>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
         <v>233</v>
       </c>
@@ -5058,7 +5058,7 @@
       <c r="F95" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G95" s="13" t="s">
+      <c r="G95" s="17" t="s">
         <v>235</v>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       <c r="F101" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G101" s="17" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       <c r="F102" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G102" s="13" t="s">
+      <c r="G102" s="17" t="s">
         <v>258</v>
       </c>
     </row>
@@ -5303,15 +5303,15 @@
         <v>272</v>
       </c>
       <c r="D106" s="16" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>46</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G106" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G106" s="17" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
         <v>40</v>
       </c>
       <c r="D107" s="15" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>276</v>
@@ -6858,63 +6858,70 @@
     <hyperlink ref="G79" r:id="rId34" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 84,727 × 0.928 × 0.026 × 6/52 × 0.119 = 28. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
     <hyperlink ref="G80" r:id="rId35" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 49,171 × 0.928 × 0.026 × 6/52 × 0.119 = 16. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
     <hyperlink ref="G81" r:id="rId36" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 10,746 × 0.928 × 0.026 × 6/52 × 0.119 = 4. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
-    <hyperlink ref="G88" r:id="rId37" display="Statistics: 1.5× plan is about three standard errors worse (see R3), so the cell is very likely worse than plan. Practice: 'turn off a Meta ad once it has spent 1.5x your target CPA without a single conversion' (https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule); here the response is a 50% cut, the full stop comes at R5."/>
-    <hyperlink ref="G89" r:id="rId38" display="Practice: 'Pause if CPA over 2x target' (https://roaspig.com/blog/automated-rules-manage-meta-budgets/). At 2× plan the same money buys twice the qualified applicants in a cell running at plan."/>
-    <hyperlink ref="G90" r:id="rId39" display="Derivation: equal to the test tranche B2, so the decision falls when the test is spent. Combined with R11 = 3 expected qualified, this matches the practitioner rule 'Spent 3× your target CPA with zero purchases? Kill it' (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework)."/>
-    <hyperlink ref="G91" r:id="rId40" display="Statistics: Poisson P(0 | mean 3) = e^−3 = 5%, so a cell that reaches its test spend with zero qualified is wrong at most 1 time in 20 (with mean 2 it would be 13.5%). Matches the '3× target CPA with zero conversions' practice (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework). Cells expecting fewer than 3 are judged on applications (R12)."/>
-    <hyperlink ref="G96" r:id="rId41" display="Derivation: the same multiple as the channel switch-off rule R5 (2×, 'Pause if CPA over 2x target', https://roaspig.com/blog/automated-rules-manage-meta-budgets/)."/>
-    <hyperlink ref="G97" r:id="rId42" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G98" r:id="rId43" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G99" r:id="rId44" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G100" r:id="rId45" display="Practice: budget rules use +20% ('safe') to +30% ('aggressive') per step (https://roaspig.com/blog/automated-rules-manage-meta-budgets/); Meta warns that large budget edits restart the learning phase (https://www.facebook.com/business/help/112167992830700). +25% once a week also gives Google bidding the 1–2 conversion cycles it needs between changes (https://support.google.com/google-ads/answer/6268637)."/>
-    <hyperlink ref="G103" r:id="rId46" display="Display flag only (changes no number). No published standard for 'share of the reachable pool'. Above 1 in 4 of everyone reachable and open to a move, a 30% miss in response rates (the sensitivity test) cannot be absorbed from the same pool. Proxy: BA Engpassanalyse treats fewer than 2 job seekers per vacancy as the tightest band (https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html)."/>
-    <hyperlink ref="G105" r:id="rId47" display="Published standard: occupancy above 85% leads to regular capacity crises (Bagust, Place &amp; Posnett, BMJ 1999, 'Dynamics of bed use in accommodating emergency admissions', https://www.bmj.com/content/319/7203/155), the origin of the widely used 85% utilisation rule. Queueing theory gives the same knee: waiting grows with ρ ÷ (1 − ρ), 5.7× at 85% (https://en.wikipedia.org/wiki/Kingman%27s_formula)."/>
-    <hyperlink ref="L112" r:id="rId48" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L113" r:id="rId49" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L114" r:id="rId50" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L115" r:id="rId51" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L116" r:id="rId52" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 22.5% qualified = 910 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L117" r:id="rId53" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 22.5% qualified = 4,690 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L118" r:id="rId54" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 22.5% qualified = 380 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L119" r:id="rId55" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 20.7% qualified = 430 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L120" r:id="rId56" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L121" r:id="rId57" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L122" r:id="rId58" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L123" r:id="rId59" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L124" r:id="rId60" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 22.5% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L125" r:id="rId61" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 20.7% qualified = 180 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L126" r:id="rId62" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 20 ÷ 12.5% = 160 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L127" r:id="rId63" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 23 ÷ 12.5% = 180 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L128" r:id="rId64" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 17.8% qualified = 340 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L129" r:id="rId65" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 17.8% qualified = 1,730 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L130" r:id="rId66" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 17.8% qualified = 140 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L131" r:id="rId67" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 16.3% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="G135" r:id="rId68" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: maintenance and the campaign's trades (KldB 2513 Wartung/Instandhaltung 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisors 2519/2619/2629 36,989 = 536,520) are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile). Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G136" r:id="rId69" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: maintenance and the campaign's trades (KldB 2513 Wartung/Instandhaltung 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisors 2519/2619/2629 36,989 = 536,520) are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile). Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G137" r:id="rId70" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: maintenance and the campaign's trades (KldB 2513 Wartung/Instandhaltung 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisors 2519/2619/2629 36,989 = 536,520) are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile). Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G138" r:id="rId71" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: maintenance and the campaign's trades (KldB 2513 Wartung/Instandhaltung 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisors 2519/2619/2629 36,989 = 536,520) are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile). Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G139" r:id="rId72" display="Derivation: geometric mean of the cold automated-email reply rate 4.96% (Pin 2026, https://www.pin.com/blog/recruiting-outreach-benchmark-report/) and the warm enterprise outreach reply rate 29% (Gem, https://www.gem.com/blog/2022-recruiting-benchmarks): √(4.96 × 29) = 12.0%. Past applicants are warm, but re-applying is a stricter step than replying."/>
-    <hyperlink ref="G140" r:id="rId73" display="These people met the hard requirements when they applied (that is how the export is filtered). Forrester: rediscovered candidates 'often remain a 70 percent or more match' (via SHRM, https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages). 50% is set below that 70% because a match is not the same as meeting every requirement again (shifts, availability)."/>
-    <hyperlink ref="G141" r:id="rId74" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
-    <hyperlink ref="G142" r:id="rId75" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
-    <hyperlink ref="G143" r:id="rId76" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
-    <hyperlink ref="G144" r:id="rId77" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
-    <hyperlink ref="G145" r:id="rId78" display="Referred applicants convert to hires 4–11× better than average in US data (Breezy 2026: 'convert at 8%, which is 4x the rate of any major job board', https://breezy.hr/resources/hiring-reports/source-of-hire-report; Gem 2026: 11×) and 1.37× in German employer data (IAB 2025, decisive ÷ used, https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/). 45% = 1.6 × the IAB 28% baseline, inside that range and close to the German figure."/>
-    <hyperlink ref="G146" r:id="rId79" display="Three waves × 1 SMS at €0.075 net (seven.io price list, https://www.seven.io/en/prices/) to €0.112 (Twilio Germany, https://www.twilio.com/en-us/sms/pricing/de) = €0.23–0.34; e-mail is near zero → €0.30 per record."/>
-    <hyperlink ref="G147" r:id="rId80" display="German practice example: €1,000 per referral, €2,000 for hard-to-fill roles (IW Köln/KOFA, https://www.kofa.de/media/Publikationen/Handlungsempfehlungen/Mitarbeiter_werben_Mitarbeiter.pdf)."/>
-    <hyperlink ref="G148" r:id="rId81" display="Published uplift range: referred interviewees are ~40% more likely to get an offer (NY Fed Staff Report 568) and accept 2.7–7.3 points more often (Burks et al., QJE), summarised at https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better. Acceptance alone gives ×1.07 (75.1 ÷ 70); ×1.15 adds a fraction of the offer uplift and stays at the low end of the range."/>
-    <hyperlink ref="G149" r:id="rId82" display="BA employment 31.12.2025, KldB 2621 Bauelektrik: Brandenburg 5,905, Berlin 6,204 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 9,750. Bauelektrik is itself a shortage occupation (BA Engpassanalyse)."/>
-    <hyperlink ref="G150" r:id="rId83" display="Derivation: Redline (181 trade social campaigns) reports a mean of 29.5 qualified applications per Elektroniker campaign (https://redline-grow.de/fachkraeftemangel-handwerk) → 30 ÷ 25% qualified (I2Q) = 120 applications ÷ 10,000 construction electricians in reach = 1.2%."/>
-    <hyperlink ref="G151" r:id="rId84" display="Social-recruiting cost per application, trades (Handwerk) average €84 (TalentBait, 818 campaigns, vendor data, https://www.talentbait.de/social-media-recruiting)."/>
-    <hyperlink ref="G153" r:id="rId85" display="Derivation: construction electricians lack the PLC/automation part, so they face the automation pass rate instead of the electrician one: PA ÷ PE = 45% ÷ 50% = 0.9. Context: closing the PLC gap fully takes a 141-day course (WBS SPS-Techniker, https://www.wbstraining.de/potsdam-weiterbildung-sps-techniker-mit-hwk-abschluss), hence the in-house bridge."/>
-    <hyperlink ref="G154" r:id="rId86" display="Copywriting: €65/hour average freelance rate (freelancermap, https://www.freelancermap.de/freelancer/texterstellung) × ~11 h = €700. Quiz funnel: Perspective Grow €147–184/month (https://www.perspective.co/pricing) × 3 months ≈ €500. Total €1,200."/>
-    <hyperlink ref="G155" r:id="rId87" display="Pracuj.pl 30-day ad 1,499 PLN net ≈ €350 (official package page, https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen) ÷ ~25 applications per ad (own estimate; no published figure) = €14."/>
-    <hyperlink ref="G156" r:id="rId88" display="Eurostat Adult Education Survey 2022, Poland, ages 25–64 with vocational upper-secondary education: 58.7% know a foreign language, of whom 23.6% at a good or proficient level → 58.7% × 23.6% = 13.9% ≈ 14% (https://ec.europa.eu/eurostat/api/dissemination/statistics/1.0/data/edat_aes_l23?geo=PL&amp;time=2022&amp;age=Y25-64). Language is the binding filter for this trade; the pre-screen call checks it."/>
-    <hyperlink ref="G157" r:id="rId89" display="Derivation: the applications needed to reach the 40% Polish cap (given): 18 hires ÷ (14% qualified × 37% qualified → signed) = 347 → 350. Reachable: about 2,000 Polish metal/machine-trade workers already commute into Brandenburg (IAB Regional 1/2020: 825 + 424 in 2019, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf, × 1.59 growth of Polish commuters 2019–23, https://iab-forum.de/immer-mehr-menschen-pendeln-aus-osteuropa-nach-deutschland/); 350 is ~18% of that."/>
-    <hyperlink ref="G158" r:id="rId90" display="Derivation: ×1.0, i.e. no uplift, because no study quantifies one: Pin 2026 and Indeed describe pre-screening only qualitatively ('how selective your pre-interview screening is directly determines your interview-to-offer efficiency', https://www.pin.com/blog/recruitment-funnel-benchmarks; https://www.indeed.com/hire/c/info/what-is-a-phone-screen). The pre-screen's effect is already in I3Q."/>
-    <hyperlink ref="G159" r:id="rId91" display="'A phone screen normally lasts for 15 to 30 minutes' (Indeed, https://www.indeed.com/hire/c/info/what-is-a-phone-screen). 15 minutes = the bottom of the range, for a fixed checklist (certificate, language, shifts, commute)."/>
-    <hyperlink ref="G160" r:id="rId92" display="Freelance recruiter in Poland: 60–80 PLN net per hour, B2B (RocketJobs listing, https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee) → top of range 80 PLN ÷ 4.25 PLN/€ = €19 per hour."/>
-    <hyperlink ref="G161" r:id="rId93" display="German statutory translator fee: €1.95 per started 55 characters (§11 JVEG, https://www.buzer.de/11_JVEG.htm); ~6,000 characters × 2 languages ≈ €430."/>
+    <hyperlink ref="G86" r:id="rId37" display="Statistics: NIST's rule for reading a proportion is min{Np, N(1 − p)} ≥ 5 (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm). At the planned share qualified of ~25%, N × 0.25 ≥ 5 needs N ≥ 20; 30 applications gives N × p = 7.5 and a standard error of √(0.25 × 0.75 ÷ 30) = 7.9 points."/>
+    <hyperlink ref="G87" r:id="rId38" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). One-sided test at α = 5% (z = 1.645). At the first judgement point (30 applications, R2) the plan-blended share qualified (R8, equal weights) has a relative standard error of 16% (raw √(0.25 × 0.75 ÷ 30) = 7.9 points ÷ 25% = 32%, halved by the blend). Better than plan with 95% confidence = 1 − 1.645 × 0.16 = 0.74 → 0.75."/>
+    <hyperlink ref="G88" r:id="rId39" display="Statistics: 1.5× plan is about three standard errors worse (see R3), so the cell is very likely worse than plan. Practice: 'turn off a Meta ad once it has spent 1.5x your target CPA without a single conversion' (https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule); here the response is a 50% cut, the full stop comes at R5."/>
+    <hyperlink ref="G89" r:id="rId40" display="Practice: 'Pause if CPA over 2x target' (https://roaspig.com/blog/automated-rules-manage-meta-budgets/). At 2× plan the same money buys twice the qualified applicants in a cell running at plan."/>
+    <hyperlink ref="G90" r:id="rId41" display="Derivation: equal to the test tranche B2, so the decision falls when the test is spent. Combined with R11 = 3 expected qualified, this matches the practitioner rule 'Spent 3× your target CPA with zero purchases? Kill it' (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework)."/>
+    <hyperlink ref="G91" r:id="rId42" display="Statistics: Poisson P(0 | mean 3) = e^−3 = 5%, so a cell that reaches its test spend with zero qualified is wrong at most 1 time in 20 (with mean 2 it would be 13.5%). Matches the '3× target CPA with zero conversions' practice (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework). Cells expecting fewer than 3 are judged on applications (R12)."/>
+    <hyperlink ref="G93" r:id="rId43" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). PASS uses α = 5%. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan reaches the PASS bar with ≥95% probability."/>
+    <hyperlink ref="G95" r:id="rId44" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). KILL uses α = 1%, the strictest common level, because killing is irreversible. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan falls below the KILL bar with &lt;1% probability."/>
+    <hyperlink ref="G96" r:id="rId45" display="Derivation: the same multiple as the channel switch-off rule R5 (2×, 'Pause if CPA over 2x target', https://roaspig.com/blog/automated-rules-manage-meta-budgets/)."/>
+    <hyperlink ref="G97" r:id="rId46" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
+    <hyperlink ref="G98" r:id="rId47" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
+    <hyperlink ref="G99" r:id="rId48" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
+    <hyperlink ref="G100" r:id="rId49" display="Practice: budget rules use +20% ('safe') to +30% ('aggressive') per step (https://roaspig.com/blog/automated-rules-manage-meta-budgets/); Meta warns that large budget edits restart the learning phase (https://www.facebook.com/business/help/112167992830700). +25% once a week also gives Google bidding the 1–2 conversion cycles it needs between changes (https://support.google.com/google-ads/answer/6268637)."/>
+    <hyperlink ref="G101" r:id="rId50" display="Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the ~50% planned pass rate needs N ≥ 10 interviews."/>
+    <hyperlink ref="G102" r:id="rId51" display="Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the 70% planned acceptance: N × 0.70 ≥ 5 needs N ≥ 7.1 → 7 offers (N × 0.30 ≥ 5 would need 17, more offers than exist before the first check, so the Tracker blends with the plan until then)."/>
+    <hyperlink ref="G103" r:id="rId52" display="Display flag only (changes no number). No published standard for 'share of the reachable pool'. Above 1 in 4 of everyone reachable and open to a move, a 30% miss in response rates (the sensitivity test) cannot be absorbed from the same pool. Proxy: BA Engpassanalyse treats fewer than 2 job seekers per vacancy as the tightest band (https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html)."/>
+    <hyperlink ref="G105" r:id="rId53" display="Bagust, Place &amp; Posnett, BMJ 1999;319:155 (abstract, https://pubmed.ncbi.nlm.nih.gov/10406748/): 'Risks are discernible when average bed occupancy rates exceed about 85%'. Same shape as queueing theory, where waiting grows with ρ ÷ (1 − ρ)."/>
+    <hyperlink ref="G106" r:id="rId54" display="Bagust, Place &amp; Posnett, BMJ 1999 (https://pubmed.ncbi.nlm.nih.gov/10406748/): 'regular bed shortages and periodic bed crises if average bed occupancy rises to 90% or more'. A week above 90% of its slots is therefore treated as full."/>
+    <hyperlink ref="L112" r:id="rId55" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L113" r:id="rId56" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L114" r:id="rId57" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L115" r:id="rId58" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L116" r:id="rId59" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 22.5% qualified = 910 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L117" r:id="rId60" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 22.5% qualified = 4,690 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L118" r:id="rId61" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 22.5% qualified = 380 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L119" r:id="rId62" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 20.7% qualified = 430 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L120" r:id="rId63" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L121" r:id="rId64" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L122" r:id="rId65" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L123" r:id="rId66" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L124" r:id="rId67" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 22.5% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L125" r:id="rId68" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 20.7% qualified = 180 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L126" r:id="rId69" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 20 ÷ 12.5% = 160 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L127" r:id="rId70" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 23 ÷ 12.5% = 180 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L128" r:id="rId71" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 17.8% qualified = 340 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L129" r:id="rId72" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 17.8% qualified = 1,730 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L130" r:id="rId73" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 17.8% qualified = 140 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="L131" r:id="rId74" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 16.3% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
+    <hyperlink ref="G135" r:id="rId75" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: the occupations this campaign hires from, KldB 2513 maintenance technicians (Wartung/Instandhaltung) 240,934 + 2625 industrial electricians 124,699 + 2611 mechatronics 84,727 + 2612 automation 49,171 + their supervisor codes 2519/2619/2629 36,989 = 536,520, are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile); 7.3% without the supervisor codes. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
+    <hyperlink ref="G136" r:id="rId76" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: the occupations this campaign hires from, KldB 2513 maintenance technicians (Wartung/Instandhaltung) 240,934 + 2625 industrial electricians 124,699 + 2611 mechatronics 84,727 + 2612 automation 49,171 + their supervisor codes 2519/2619/2629 36,989 = 536,520, are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile); 7.3% without the supervisor codes. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
+    <hyperlink ref="G137" r:id="rId77" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: the occupations this campaign hires from, KldB 2513 maintenance technicians (Wartung/Instandhaltung) 240,934 + 2625 industrial electricians 124,699 + 2611 mechatronics 84,727 + 2612 automation 49,171 + their supervisor codes 2519/2619/2629 36,989 = 536,520, are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile); 7.3% without the supervisor codes. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
+    <hyperlink ref="G138" r:id="rId78" display="Derivation: German practice keeps rejected applicants' data 6 months, or up to 1 year with talent-pool consent (Haufe: https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html), so the usable pool is ~1 year of runners-up. Maintenance share: the occupations this campaign hires from, KldB 2513 maintenance technicians (Wartung/Instandhaltung) 240,934 + 2625 industrial electricians 124,699 + 2611 mechatronics 84,727 + 2612 automation 49,171 + their supervisor codes 2519/2619/2629 36,989 = 536,520, are 7.8% of all production occupations (KldB 21–29: 6,850,263) in Germany (BA, 31.12.2025, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile); 7.3% without the supervisor codes. Maintenance hires a year ≈ 10,703 staff (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/) × 7.8% × 12% turnover (IAB-Betriebspanel Brandenburg 2024) = 100. Qualified runners-up per hire = 1 ÷ 0.32 qualified → signed − 1 = 2.1. Pool = 100 × 2.1 = 211, split by this campaign's openings (30/45/15/10%). The client's day-1 ATS export replaces it."/>
+    <hyperlink ref="G139" r:id="rId79" display="Derivation: geometric mean of the cold automated-email reply rate 4.96% (Pin 2026, https://www.pin.com/blog/recruiting-outreach-benchmark-report/) and the warm enterprise outreach reply rate 29% (Gem, https://www.gem.com/blog/2022-recruiting-benchmarks): √(4.96 × 29) = 12.0%. Past applicants are warm, but re-applying is a stricter step than replying."/>
+    <hyperlink ref="G140" r:id="rId80" display="These people met the hard requirements when they applied (that is how the export is filtered). Forrester: rediscovered candidates 'often remain a 70 percent or more match' (via SHRM, https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages). 50% is set below that 70% because a match is not the same as meeting every requirement again (shifts, availability)."/>
+    <hyperlink ref="G141" r:id="rId81" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
+    <hyperlink ref="G142" r:id="rId82" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
+    <hyperlink ref="G143" r:id="rId83" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
+    <hyperlink ref="G144" r:id="rId84" display="Derivation: sized so referrals deliver 11% of hires, the CareerPlug 2025 benchmark (referrals 2% of applicants but 11% of hires, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf): 11 hires ÷ (45% qualified × 37% qualified → signed incl. ×1.15) = 66 applications, split by openings. Equals 0.6% of the plant's 10,703 staff referring someone in 6 weeks, far below the 20% quarterly participation that marks a healthy programme (https://www.pin.com/blog/employee-referral-program-guide)."/>
+    <hyperlink ref="G145" r:id="rId85" display="Referred applicants convert to hires 4–11× better than average in US data (Breezy 2026: 'convert at 8%, which is 4x the rate of any major job board', https://breezy.hr/resources/hiring-reports/source-of-hire-report; Gem 2026: 11×) and 1.37× in German employer data (IAB 2025, decisive ÷ used, https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/). 45% = 1.6 × the IAB 28% baseline, inside that range and close to the German figure."/>
+    <hyperlink ref="G146" r:id="rId86" display="Three waves × 1 SMS at €0.075 net (seven.io price list, https://www.seven.io/en/prices/) to €0.112 (Twilio Germany, https://www.twilio.com/en-us/sms/pricing/de) = €0.23–0.34; e-mail is near zero → €0.30 per record."/>
+    <hyperlink ref="G147" r:id="rId87" display="German practice example: €1,000 per referral, €2,000 for hard-to-fill roles (IW Köln/KOFA, https://www.kofa.de/media/Publikationen/Handlungsempfehlungen/Mitarbeiter_werben_Mitarbeiter.pdf)."/>
+    <hyperlink ref="G148" r:id="rId88" display="Published uplift range: referred interviewees are ~40% more likely to get an offer (NY Fed Staff Report 568) and accept 2.7–7.3 points more often (Burks et al., QJE), summarised at https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better. Acceptance alone gives ×1.07 (75.1 ÷ 70); ×1.15 adds a fraction of the offer uplift and stays at the low end of the range."/>
+    <hyperlink ref="G149" r:id="rId89" display="BA employment 31.12.2025, KldB 2621 Bauelektrik: Brandenburg 5,905, Berlin 6,204 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 9,750. Bauelektrik is itself a shortage occupation (BA Engpassanalyse)."/>
+    <hyperlink ref="G150" r:id="rId90" display="Derivation: Redline (181 trade social campaigns) reports a mean of 29.5 qualified applications per Elektroniker campaign (https://redline-grow.de/fachkraeftemangel-handwerk) → 30 ÷ 25% qualified (I2Q) = 120 applications ÷ 10,000 construction electricians in reach = 1.2%."/>
+    <hyperlink ref="G151" r:id="rId91" display="Social-recruiting cost per application, trades (Handwerk) average €84 (TalentBait, 818 campaigns, vendor data, https://www.talentbait.de/social-media-recruiting)."/>
+    <hyperlink ref="G153" r:id="rId92" display="Derivation: construction electricians lack the PLC/automation part, so they face the automation pass rate instead of the electrician one: PA ÷ PE = 45% ÷ 50% = 0.9. Context: closing the PLC gap fully takes a 141-day course (WBS SPS-Techniker, https://www.wbstraining.de/potsdam-weiterbildung-sps-techniker-mit-hwk-abschluss), hence the in-house bridge."/>
+    <hyperlink ref="G154" r:id="rId93" display="Copywriting: €65/hour average freelance rate (freelancermap, https://www.freelancermap.de/freelancer/texterstellung) × ~11 h = €700. Quiz funnel: Perspective Grow €147–184/month (https://www.perspective.co/pricing) × 3 months ≈ €500. Total €1,200."/>
+    <hyperlink ref="G155" r:id="rId94" display="Pracuj.pl 30-day ad 1,499 PLN net ≈ €350 (official package page, https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen) ÷ ~25 applications per ad (own estimate; no published figure) = €14."/>
+    <hyperlink ref="G156" r:id="rId95" display="Eurostat Adult Education Survey 2022, Poland, ages 25–64 with vocational upper-secondary education: 58.7% know a foreign language, of whom 23.6% at a good or proficient level → 58.7% × 23.6% = 13.9% ≈ 14% (https://ec.europa.eu/eurostat/api/dissemination/statistics/1.0/data/edat_aes_l23?geo=PL&amp;time=2022&amp;age=Y25-64). Language is the binding filter for this trade; the pre-screen call checks it."/>
+    <hyperlink ref="G157" r:id="rId96" display="Derivation: the applications needed to reach the 40% Polish cap (given): 18 hires ÷ (14% qualified × 37% qualified → signed) = 347 → 350. Reachable: about 2,000 Polish metal/machine-trade workers already commute into Brandenburg (IAB Regional 1/2020: 825 + 424 in 2019, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf, × 1.59 growth of Polish commuters 2019–23, https://iab-forum.de/immer-mehr-menschen-pendeln-aus-osteuropa-nach-deutschland/); 350 is ~18% of that."/>
+    <hyperlink ref="G158" r:id="rId97" display="Derivation: ×1.0, i.e. no uplift, because no study quantifies one: Pin 2026 and Indeed describe pre-screening only qualitatively ('how selective your pre-interview screening is directly determines your interview-to-offer efficiency', https://www.pin.com/blog/recruitment-funnel-benchmarks; https://www.indeed.com/hire/c/info/what-is-a-phone-screen). The pre-screen's effect is already in I3Q."/>
+    <hyperlink ref="G159" r:id="rId98" display="'A phone screen normally lasts for 15 to 30 minutes' (Indeed, https://www.indeed.com/hire/c/info/what-is-a-phone-screen). 15 minutes = the bottom of the range, for a fixed checklist (certificate, language, shifts, commute)."/>
+    <hyperlink ref="G160" r:id="rId99" display="Freelance recruiter in Poland: 60–80 PLN net per hour, B2B (RocketJobs listing, https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee) → top of range 80 PLN ÷ 4.25 PLN/€ = €19 per hour."/>
+    <hyperlink ref="G161" r:id="rId100" display="German statutory translator fee: €1.95 per started 55 characters (§11 JVEG, https://www.buzer.de/11_JVEG.htm); ~6,000 characters × 2 languages ≈ €430."/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="779">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Assumptions log = the model's only input sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Label: Given = from the brief; Researched = with link; Own estimate = derived by the arithmetic or rule written beside it (no unexplained values); Researched + Own estimate = a linked benchmark adapted by stated arithmetic.</t>
+    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Label: Given = from the brief; Researched = with link; Own estimate = my judgement, with the reason beside it; Researched + Own estimate = a linked benchmark that I adapted. Black (not blue) values are calculated.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Given in the brief</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Given</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: campaign runs Tue 20 Oct – Thu 31 Dec.</t>
+    <t xml:space="preserve">From the brief.</t>
   </si>
   <si>
     <t xml:space="preserve">G2</t>
@@ -140,9 +140,6 @@
     <t xml:space="preserve">Campaign end / hire deadline (signed contract)</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: a hire = contract signed by 31 Dec; start date may be 2027.</t>
-  </si>
-  <si>
     <t xml:space="preserve">G3</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t xml:space="preserve">per week</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: at most 55 qualified applicants a week across all roles.</t>
-  </si>
-  <si>
     <t xml:space="preserve">G4</t>
   </si>
   <si>
@@ -170,7 +164,7 @@
     <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: Polish sources allowed for mechatronics, ≤40% of those hires. Legal basis: EU free movement, no work permit needed ('you can enter Germany without a visa, thanks to the freedom of movement', https://www.make-it-in-germany.com/en/working-in-germany/information-eu-citizens/print). Cross-border commuters are insured in the country of work ('Maßgeblich ist der Staat, in dem gearbeitet wird', TK, https://www.tk.de/firmenkunden/service/fachthemen/ausland/grenzgaenger-grenzpendler-mehrstaater-2101334) and German working days are taxed in Germany (no special commuter rule in the DE–PL treaty). Mechatronics is non-regulated, so no recognition is needed.</t>
+    <t xml:space="preserve">From the brief. Polish hires need no work permit (EU free movement) and are insured and taxed in Germany. https://www.make-it-in-germany.com/en/working-in-germany/information-eu-citizens/print</t>
   </si>
   <si>
     <t xml:space="preserve">G5</t>
@@ -185,9 +179,6 @@
     <t xml:space="preserve">hires</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief, 'What you're given' table.</t>
-  </si>
-  <si>
     <t xml:space="preserve">G6</t>
   </si>
   <si>
@@ -212,7 +203,7 @@
     <t xml:space="preserve">months (min)</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: 2–4 months; the plan follows the brief and buys no foreign-trained electricians. Statutory: decision within three months of a complete file (§6(3) BQFG, https://www.buzer.de/6_BQFG.htm). Upside to raise with the client: industrial electrician (Elektroniker für Betriebstechnik) is a non-regulated profession for employees ('This profession is not regulated in Germany', BIBB, https://www.anerkennung-in-deutschland.de/en/interest/finder/profession/62/profile); recognition is legally needed only for self-employment/Meister. The delay applies where the plant requires formal equivalence, e.g. before appointing someone as an Elektrofachkraft. If the client accepts employer-verified competence, EU-trained electricians become a route before 31 Dec.</t>
+    <t xml:space="preserve">From the brief, so I plan no foreign-trained electricians. Worth raising: for employees the trade is not legally regulated, which could open this route. https://www.anerkennung-in-deutschland.de/en/interest/finder/profession/62/profile</t>
   </si>
   <si>
     <t xml:space="preserve">2. Hiring timeline (sets the last useful application date)</t>
@@ -230,7 +221,7 @@
     <t xml:space="preserve">Own estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: rediscovery wave 1 goes out Wed 21 Oct (campaign day 2) to people screened once before; their re-applications skip the first screen, so assessments start Thu 22 Oct = start + 2 days. New applicants follow T2 (6 days).</t>
+    <t xml:space="preserve">Re-applicants were screened before, so the first assessments can run on day 2.</t>
   </si>
   <si>
     <t xml:space="preserve">T1</t>
@@ -242,7 +233,7 @@
     <t xml:space="preserve">Researched</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Hiring Lab DE: job searches 'fiel an den Feiertagen auf einen Tiefpunkt von 45 % unter den durchschnittlichen Wert vom 1. bis 15. Dezember' (https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/). So the last planned signature is Fri 18 Dec; 21–23 Dec is kept as buffer for slipped signatures, not planned volume.</t>
+    <t xml:space="preserve">Last Friday before Christmas; job searching drops ~45% over the holidays (Indeed Hiring Lab). https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/</t>
   </si>
   <si>
     <t xml:space="preserve">T2</t>
@@ -251,7 +242,7 @@
     <t xml:space="preserve">Days: application → recruiter assessment of a qualified applicant</t>
   </si>
   <si>
-    <t xml:space="preserve">SmartRecruiters Germany 2025 benchmark: median 6 days to review an application (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf).</t>
+    <t xml:space="preserve">German median: 6 days to review an application (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">T3</t>
@@ -263,7 +254,7 @@
     <t xml:space="preserve">Researched + Own estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">SmartRecruiters 2025: median 14 days from application to interview (same PDF) → 14 − 6 = 8. German averages are slower (XING report 2026: 21 days to first interview, 72 days to hire, https://www.socialnet.de/personalblog/wie-lange-dauert-recruiting-wirklich-zahlen-aus-dem-xing-bewerbungsreport-2026.html), so the SmartRecruiters median is the fast-track figure the client must commit to (risk; each extra day removes ~8 slots).</t>
+    <t xml:space="preserve">German median: 14 days from application to interview, minus the 6 above (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">T4</t>
@@ -272,7 +263,7 @@
     <t xml:space="preserve">Days: interview → written offer</t>
   </si>
   <si>
-    <t xml:space="preserve">No published 'final interview → offer' figure (checked SmartRecruiters DE, Gem, SHRM, NACE). Context: German median time-to-hire is 55 days (SmartRecruiters DE 2025, https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf); this plan's whole chain T2+T3+T4+T5 = 24 days, a sprint process. 3 days = the service level the plan requires from the client (written offer within 3 working days of the interview, one of the asks); it is a commitment, not an estimate. Sensitivity: each extra day here moves the last useful application one day earlier and removes ~8 assessment slots (55 ÷ 7).</t>
+    <t xml:space="preserve">My ask to the client: written offer within 3 working days. No public benchmark exists for this step.</t>
   </si>
   <si>
     <t xml:space="preserve">T5</t>
@@ -281,7 +272,7 @@
     <t xml:space="preserve">Days: offer → signed contract</t>
   </si>
   <si>
-    <t xml:space="preserve">NACE 2025: candidates took on average 9 days to decide on an offer (11 in 2023) (https://www.naceweb.org/talent-acquisition/trends-and-predictions/employers-make-more-offers-as-student-acceptance-rate-rises-response-time-shortens). 7 days = a one-week validity on the offer (client ask), which cuts the 9-day average; German acceptance is high (91%, SmartRecruiters DE 2025).</t>
+    <t xml:space="preserve">One-week offer validity; candidates take ~9 days on average to decide (NACE 2025). https://www.naceweb.org/talent-acquisition/trends-and-predictions/employers-make-more-offers-as-student-acceptance-rate-rises-response-time-shortens</t>
   </si>
   <si>
     <t xml:space="preserve">T6</t>
@@ -290,7 +281,7 @@
     <t xml:space="preserve">Extra days for supervisors (second round with plant management)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: supervisors have one extra round (panel with plant management). One round = one more scheduling cycle; the assessment → interview step takes 8 days (T3) including the 1-day test, so +7 days. SHRM 2025 finds no difference in time-to-fill between executive and non-executive hires (https://www.shrm.org/content/dam/en/shrm/research/2025-recruiting-benchmarking-report.pdf), so +7 is the cautious side: setting it to 0 gives supervisors one more week of applications.</t>
+    <t xml:space="preserve">Supervisors have one extra round with plant management (about a week).</t>
   </si>
   <si>
     <t xml:space="preserve">3. Funnel rates by role (Part 1)</t>
@@ -302,7 +293,7 @@
     <t xml:space="preserve">Application → qualified (baseline, all channels)</t>
   </si>
   <si>
-    <t xml:space="preserve">IAB-Stellenerhebung 2/2026 (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/): employers rate about 3 of 12 applications suitable in production occupations (≈25%; 7 of 27 ≈ 26% at firms with 250+ staff) and 23% for specialist/expert roles. Skilled trades (electricians, mechatronics, automation) use 25%; supervisors (Meister/Techniker level) use 23%. Scarcity is modelled through the smaller reachable pools and channel caps (BA Engpassanalyse 2025: supervisors 0.75, electricians 1.20, automation 1.46 job seekers per vacancy, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/arbeitsmarktberichte/fachkraefte-engpassanalyse/fachkraefte-engpassanalyse-dl-0-202512-zip.zip), not by a second discount here.</t>
+    <t xml:space="preserve">About 1 in 4 applications is suitable in production jobs; 23% for specialist roles (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/</t>
   </si>
   <si>
     <t xml:space="preserve">QM</t>
@@ -320,25 +311,19 @@
     <t xml:space="preserve">Qualified → passed assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Pass = practical/technical interview. Qualified on paper ≠ passes (fault-finding on live automation, DGUV V3 Elektrofachkraft). ~half pass.</t>
+    <t xml:space="preserve">About a third of final interviews lead to an offer (Gem 2025); higher here because candidates are pre-qualified. Hardest for automation and supervisors. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">PM</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Most standardised skill set; slightly higher pass rate.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PA</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): PLC/robotics tests are hard to fake; half pass.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PS</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Leadership + technical; lowest pass rate.</t>
+    <t xml:space="preserve">BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
   </si>
   <si>
     <t xml:space="preserve">OE</t>
@@ -347,7 +332,7 @@
     <t xml:space="preserve">Passed → offer made</t>
   </si>
   <si>
-    <t xml:space="preserve">No public rate for 'passed the final interview but no offer' (checked IAB, Gem, SmartRecruiters, HireRight 2026, which publishes no %). The combined passed → signed (offer × acceptance) is 0.90 × 0.70–0.75 = 63–68% (supervisors 0.85 × 0.70 = 60%), below SmartRecruiters' 91% German offer acceptance (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf) and below Königsteiner/StepStone's 71–78%, so the extra 10–15% loss sits inside the published range. Supervisors lose more (approval layers).</t>
+    <t xml:space="preserve">My estimate: ~10% drop out after passing (references, pay, shifts), 15% for supervisors. No public figure exists.</t>
   </si>
   <si>
     <t xml:space="preserve">OM</t>
@@ -365,27 +350,18 @@
     <t xml:space="preserve">Offer → signed contract</t>
   </si>
   <si>
-    <t xml:space="preserve">German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Engpassberuf with counter-offers from energy/grid, rail, aerospace; Tesla shift work and IG Metall disputes are known. Acceptance improves if Tesla's offer beats the Brandenburg trade median (€3,030/month, standardised to 10 years' experience, WSI https://www.lohnspiegel.de/gehaltsinfos/elektroniker_in_fuer_betriebstechnik_26252114.html); client to confirm pay band.</t>
+    <t xml:space="preserve">German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449</t>
   </si>
   <si>
     <t xml:space="preserve">AM</t>
   </si>
   <si>
-    <t xml:space="preserve">German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Bigger pool, fewer counter-offers; German pay vs Polish wages is a strong pull for border commuters.</t>
-  </si>
-  <si>
     <t xml:space="preserve">AA</t>
   </si>
   <si>
-    <t xml:space="preserve">German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Scarce, many counter-offers (car makers, integrators).</t>
-  </si>
-  <si>
     <t xml:space="preserve">AS</t>
   </si>
   <si>
-    <t xml:space="preserve">German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Career step-up helps acceptance; counter-offers from current employer.</t>
-  </si>
-  <si>
     <t xml:space="preserve">4. Budget policy and weekly phasing (Part 2)</t>
   </si>
   <si>
@@ -395,7 +371,7 @@
     <t xml:space="preserve">Reserve held back (share of total budget)</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: high-risk projects carry 10–20% contingency (https://mastt.com/blogs/construction-contingency); PMI recommends sizing it to the risk rather than a flat % (https://www.pmi.org/learning/library/safety-numbers-contingency-planning-10120). Risk-based check: the reserve incl. rounding (€17.1k) covers about half of the extra media a 30% miss on share qualified would need (Funnel sensitivity: +€36.6k). Beyond that the binding limit is assessment slots, not money.</t>
+    <t xml:space="preserve">15% buffer, in the 10–20% range used for risky projects; released only on results. https://mastt.com/blogs/construction-contingency</t>
   </si>
   <si>
     <t xml:space="preserve">B2</t>
@@ -410,7 +386,7 @@
     <t xml:space="preserve">€</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: equal to the switch-off spend R6, so every test reaches a decision point. At the paid cells' plan cost per qualified (€384–1,680), €750 buys 0.5–2.0 qualified: cells expecting ≥2 (R11) are judged on qualified, the rest on applications (R12). 12 tests × €750 = €9,000 ≈ 9% of the budget. Test applicants are real candidates and are counted in hires, slots and spend.</t>
+    <t xml:space="preserve">€750 per paid channel and role in weeks 1–2: enough to see whether it works before spending more.</t>
   </si>
   <si>
     <t xml:space="preserve">B4</t>
@@ -419,7 +395,7 @@
     <t xml:space="preserve">Share of test tranches spent in week 1 (rest in week 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: tests are split in proportion to assessment slots. Week 1 has 39 slots (assessments from Thu 22 Oct), week 2 has 55: 39 ÷ (39 + 55) = 42%, rounded down to 40% because rediscovery re-applicants take week-1 slots first.</t>
+    <t xml:space="preserve">Week 1 has fewer assessment days, so 40% of the test money goes there.</t>
   </si>
   <si>
     <t xml:space="preserve">B5</t>
@@ -428,7 +404,7 @@
     <t xml:space="preserve">Rounding step for the recommended budget</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: €2,500 ≈ 2.5% of the budget, the smallest step that gives a round figure for the client. The model always rounds up (here €100,455 → €102,500), and the €2,045 difference is added to the reserve.</t>
+    <t xml:space="preserve">Rounded up to a clean figure; the difference goes to the reserve.</t>
   </si>
   <si>
     <t xml:space="preserve">B6</t>
@@ -437,7 +413,7 @@
     <t xml:space="preserve">Smaller cut shown in scenarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Presentation choice: the brief asks about a 30% cut (B3); −15% and −50% are shown either side so the client sees the shape of hires against budget (Budget rows 45–48).</t>
+    <t xml:space="preserve">Extra cut level so the client sees the curve (the brief asks about −30%).</t>
   </si>
   <si>
     <t xml:space="preserve">B7</t>
@@ -446,18 +422,12 @@
     <t xml:space="preserve">Deep cut shown in scenarios</t>
   </si>
   <si>
-    <t xml:space="preserve">Presentation choice: see B6. Half budget shows where the curve flattens (mechatronics and automation are protected, electricians fall first).</t>
-  </si>
-  <si>
     <t xml:space="preserve">B3</t>
   </si>
   <si>
     <t xml:space="preserve">Budget cut scenario the client asked about</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief: 'what it would buy with 30% less'.</t>
-  </si>
-  <si>
     <t xml:space="preserve">W1</t>
   </si>
   <si>
@@ -467,7 +437,7 @@
     <t xml:space="preserve">All paid</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: weekly shares solved numerically against the real model (iterated finite-difference fit) so qualified arrivals stay within the 55 weekly assessments (Weekly col P vs Q). With W1–W6 = 9%, 14.5%, 18%, 18%, 18.5%, 22% the loads are 39/39, 54/55, 54/55, 53/55, 54/55, 54/55. Weeks 1–2 are lower because rediscovery re-applicants (60% arrive in week 1) and the €750 tests already use those slots.</t>
+    <t xml:space="preserve">Paced so that no week needs more than the 55 assessments (Weekly tab).</t>
   </si>
   <si>
     <t xml:space="preserve">W2</t>
@@ -506,7 +476,7 @@
     <t xml:space="preserve">Share of media spend in week 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: 0 because the week starts after the last useful application (Funnel B19). Any share typed here is re-spread over earlier weeks automatically (Weekly col D).</t>
+    <t xml:space="preserve">No spend after the last useful application date.</t>
   </si>
   <si>
     <t xml:space="preserve">W8</t>
@@ -539,9 +509,6 @@
     <t xml:space="preserve">Stress size for sensitivity test</t>
   </si>
   <si>
-    <t xml:space="preserve">Brief Part 1.4: 'if it turns out 30% worse'.</t>
-  </si>
-  <si>
     <t xml:space="preserve">5. Talent pool sanity check (Part 2.2)</t>
   </si>
   <si>
@@ -554,34 +521,22 @@
     <t xml:space="preserve">people</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 3,417 × 0.6 + 2,708 = 4,758 → 4,800.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSM</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 14,878 × 0.6 + 17,490 = 26,417 → 26,400.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSA</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,206 × 0.6 + 1,254 = 1,978 → 2,000.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025, Aufsicht codes 2519 + 2619 + 2629 + 2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,209 × 0.6 + 1,494 = 2,219 → 2,200.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PIE</t>
   </si>
   <si>
     <t xml:space="preserve">Share in-market or persuadable during the 6-week window</t>
   </si>
   <si>
-    <t xml:space="preserve">Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year.</t>
+    <t xml:space="preserve">~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">PIM</t>
@@ -599,27 +554,18 @@
     <t xml:space="preserve">Qualified people elsewhere in Germany willing to relocate in the window</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 124,699 × 0.928 × 0.026 × 6/52 × 0.119 = 41. Upper-bound rates used (the all-ages migration rate is 1.19%).</t>
+    <t xml:space="preserve">Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html</t>
   </si>
   <si>
     <t xml:space="preserve">PRM</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 84,727 × 0.928 × 0.026 × 6/52 × 0.119 = 28. Upper-bound rates used (the all-ages migration rate is 1.19%).</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRA</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 49,171 × 0.928 × 0.026 × 6/52 × 0.119 = 16. Upper-bound rates used (the all-ages migration rate is 1.19%).</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRS</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 10,746 × 0.928 × 0.026 × 6/52 × 0.119 = 4. Upper-bound rates used (the all-ages migration rate is 1.19%).</t>
-  </si>
-  <si>
     <t xml:space="preserve">6. Week-by-week money rules (Part 4) — used by the Tracker tab</t>
   </si>
   <si>
@@ -632,7 +578,7 @@
     <t xml:space="preserve">Per cell</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: €500 = two-thirds of the €750 test. With 40% of test spend in week 1 (B4), each test has spent ~€500 by Mon 2 Nov, so the first cut decisions can be taken then rather than waiting for the full tranche.</t>
+    <t xml:space="preserve">Don't judge a channel on less than €500 or 30 applications; too little data.</t>
   </si>
   <si>
     <t xml:space="preserve">R2</t>
@@ -644,9 +590,6 @@
     <t xml:space="preserve">apps</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: NIST's rule for reading a proportion is min{Np, N(1 − p)} ≥ 5 (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm). At the planned share qualified of ~25%, N × 0.25 ≥ 5 needs N ≥ 20; 30 applications gives N × p = 7.5 and a standard error of √(0.25 × 0.75 ÷ 30) = 7.9 points.</t>
-  </si>
-  <si>
     <t xml:space="preserve">R3</t>
   </si>
   <si>
@@ -656,7 +599,7 @@
     <t xml:space="preserve">× plan</t>
   </si>
   <si>
-    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). One-sided test at α = 5% (z = 1.645). At the first judgement point (30 applications, R2) the plan-blended share qualified (R8, equal weights) has a relative standard error of 16% (raw √(0.25 × 0.75 ÷ 30) = 7.9 points ÷ 25% = 32%, halved by the blend). Better than plan with 95% confidence = 1 − 1.645 × 0.16 = 0.74 → 0.75.</t>
+    <t xml:space="preserve">20% cheaper than plan and slots free → scale up.</t>
   </si>
   <si>
     <t xml:space="preserve">R4</t>
@@ -665,7 +608,7 @@
     <t xml:space="preserve">Cut budget 50% when re-forecast cost per qualified ≥ this × plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: 1.5× plan is about three standard errors worse (see R3), so the cell is very likely worse than plan. Practice: 'turn off a Meta ad once it has spent 1.5x your target CPA without a single conversion' (https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule); here the response is a 50% cut, the full stop comes at R5.</t>
+    <t xml:space="preserve">50% dearer than plan → halve the budget (common ad practice). https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule</t>
   </si>
   <si>
     <t xml:space="preserve">R5</t>
@@ -674,7 +617,7 @@
     <t xml:space="preserve">Switch off when cost per qualified ≥ this × plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: 'Pause if CPA over 2x target' (https://roaspig.com/blog/automated-rules-manage-meta-budgets/). At 2× plan the same money buys twice the qualified applicants in a cell running at plan.</t>
+    <t xml:space="preserve">Twice the plan cost → switch off (common ad practice). https://roaspig.com/blog/automated-rules-manage-meta-budgets/</t>
   </si>
   <si>
     <t xml:space="preserve">R6</t>
@@ -683,7 +626,7 @@
     <t xml:space="preserve">…or switch off when spend reaches this with zero qualified</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: equal to the test tranche B2, so the decision falls when the test is spent. Combined with R11 = 3 expected qualified, this matches the practitioner rule 'Spent 3× your target CPA with zero purchases? Kill it' (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework).</t>
+    <t xml:space="preserve">Test fully spent with zero qualified → switch off.</t>
   </si>
   <si>
     <t xml:space="preserve">R11</t>
@@ -695,7 +638,7 @@
     <t xml:space="preserve">qualified</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: Poisson P(0 | mean 3) = e^−3 = 5%, so a cell that reaches its test spend with zero qualified is wrong at most 1 time in 20 (with mean 2 it would be 13.5%). Matches the '3× target CPA with zero conversions' practice (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework). Cells expecting fewer than 3 are judged on applications (R12).</t>
+    <t xml:space="preserve">…but only where at least 3 qualified were expected, so bad luck doesn't kill a good channel.</t>
   </si>
   <si>
     <t xml:space="preserve">R12</t>
@@ -704,19 +647,19 @@
     <t xml:space="preserve">Low-yield cells: switch off at R6 spend if applications are below this share of plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: at full test spend, half the planned applications means the cell's cost per application is 2× plan, the same as the switch-off bar R5.</t>
+    <t xml:space="preserve">Low-volume channels: off if applications are under half of plan once the test is spent.</t>
   </si>
   <si>
     <t xml:space="preserve">TP1</t>
   </si>
   <si>
-    <t xml:space="preserve">Initiative test: PASS bar significance level (an on-plan initiative misses the bar with at most this probability)</t>
+    <t xml:space="preserve">Initiative test: PASS needs at least this share of planned qualified in the window</t>
   </si>
   <si>
     <t xml:space="preserve">Initiatives</t>
   </si>
   <si>
-    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). PASS uses α = 5%. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan reaches the PASS bar with ≥95% probability.</t>
+    <t xml:space="preserve">Two-week test passes if at least 60% of the planned qualified applicants arrive.</t>
   </si>
   <si>
     <t xml:space="preserve">TP2</t>
@@ -725,16 +668,16 @@
     <t xml:space="preserve">Initiative test: PASS needs cost per qualified ≤ this × plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: the same multiple as the channel cut rule R4 (1.5×): an initiative passes on cost if a channel at that cost would not be cut.</t>
+    <t xml:space="preserve">Same cost limit as the channel cut rule (1.5× plan).</t>
   </si>
   <si>
     <t xml:space="preserve">TK1</t>
   </si>
   <si>
-    <t xml:space="preserve">Initiative test: KILL bar significance level (an on-plan initiative falls below the bar with less than this probability)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). KILL uses α = 1%, the strictest common level, because killing is irreversible. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan falls below the KILL bar with &lt;1% probability.</t>
+    <t xml:space="preserve">Initiative test: KILL if qualified below this share of plan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kill the initiative if fewer than 30% of the planned qualified arrive.</t>
   </si>
   <si>
     <t xml:space="preserve">TK2</t>
@@ -743,7 +686,7 @@
     <t xml:space="preserve">Initiative test: KILL if cost per qualified above this × plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: the same multiple as the channel switch-off rule R5 (2×, 'Pause if CPA over 2x target', https://roaspig.com/blog/automated-rules-manage-meta-budgets/).</t>
+    <t xml:space="preserve">Same cost limit as the channel switch-off rule (2× plan).</t>
   </si>
   <si>
     <t xml:space="preserve">I1W1</t>
@@ -755,7 +698,7 @@
     <t xml:space="preserve">Rediscovery</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%.</t>
+    <t xml:space="preserve">Most replies come within a day of each message (Pin 2026), so 60% arrive in week 1. https://www.pin.com/blog/recruiting-outreach-benchmark-report/</t>
   </si>
   <si>
     <t xml:space="preserve">I1W2</t>
@@ -776,7 +719,7 @@
     <t xml:space="preserve">Scale-up step per week</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice: budget rules use +20% ('safe') to +30% ('aggressive') per step (https://roaspig.com/blog/automated-rules-manage-meta-budgets/); Meta warns that large budget edits restart the learning phase (https://www.facebook.com/business/help/112167992830700). +25% once a week also gives Google bidding the 1–2 conversion cycles it needs between changes (https://support.google.com/google-ads/answer/6268637).</t>
+    <t xml:space="preserve">+25% a week: big enough to matter, small enough not to upset ad bidding. https://roaspig.com/blog/automated-rules-manage-meta-budgets/</t>
   </si>
   <si>
     <t xml:space="preserve">R9</t>
@@ -791,7 +734,7 @@
     <t xml:space="preserve">interviews</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the ~50% planned pass rate needs N ≥ 10 interviews.</t>
+    <t xml:space="preserve">Switch to the real pass rate after 10 interviews.</t>
   </si>
   <si>
     <t xml:space="preserve">R10</t>
@@ -803,7 +746,7 @@
     <t xml:space="preserve">offers</t>
   </si>
   <si>
-    <t xml:space="preserve">Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the 70% planned acceptance: N × 0.70 ≥ 5 needs N ≥ 7.1 → 7 offers (N × 0.30 ≥ 5 would need 17, more offers than exist before the first check, so the Tracker blends with the plan until then).</t>
+    <t xml:space="preserve">Switch to the real acceptance rate after 5 offers.</t>
   </si>
   <si>
     <t xml:space="preserve">F1</t>
@@ -815,7 +758,7 @@
     <t xml:space="preserve">Funnel pool check</t>
   </si>
   <si>
-    <t xml:space="preserve">Display flag only (changes no number). No published standard for 'share of the reachable pool'. Above 1 in 4 of everyone reachable and open to a move, a 30% miss in response rates (the sensitivity test) cannot be absorbed from the same pool. Proxy: BA Engpassanalyse treats fewer than 2 job seekers per vacancy as the tightest band (https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html).</t>
+    <t xml:space="preserve">Display flag only: the plan needs over a quarter of everyone reachable.</t>
   </si>
   <si>
     <t xml:space="preserve">F2</t>
@@ -824,7 +767,7 @@
     <t xml:space="preserve">Pool flag: 'tight' above this share</t>
   </si>
   <si>
-    <t xml:space="preserve">Display flag only. Half of F1 (1 in 8 of the reachable pool): the point from which a 30% miss would need more than a quarter of the pool (12% ÷ 0.7 = 17%, × 1.5 for response noise ≈ 25%).</t>
+    <t xml:space="preserve">Display flag only: the plan needs over 1 in 8 of everyone reachable.</t>
   </si>
   <si>
     <t xml:space="preserve">F3</t>
@@ -836,7 +779,7 @@
     <t xml:space="preserve">Funnel / Weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Bagust, Place &amp; Posnett, BMJ 1999;319:155 (abstract, https://pubmed.ncbi.nlm.nih.gov/10406748/): 'Risks are discernible when average bed occupancy rates exceed about 85%'. Same shape as queueing theory, where waiting grows with ρ ÷ (1 − ρ).</t>
+    <t xml:space="preserve">Risk rises once capacity is more than 85% used (Bagust et al., BMJ 1999). https://pubmed.ncbi.nlm.nih.gov/10406748/</t>
   </si>
   <si>
     <t xml:space="preserve">F4</t>
@@ -848,7 +791,7 @@
     <t xml:space="preserve">Weekly</t>
   </si>
   <si>
-    <t xml:space="preserve">Bagust, Place &amp; Posnett, BMJ 1999 (https://pubmed.ncbi.nlm.nih.gov/10406748/): 'regular bed shortages and periodic bed crises if average bed occupancy rises to 90% or more'. A week above 90% of its slots is therefore treated as full.</t>
+    <t xml:space="preserve">Above 90% use, shortages become regular (same study), so the week counts as full. https://pubmed.ncbi.nlm.nih.gov/10406748/</t>
   </si>
   <si>
     <t xml:space="preserve">R13</t>
@@ -860,7 +803,7 @@
     <t xml:space="preserve">qualified/wk</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: = F4 × G3 = 0.90 × 55 = 49.5 → 50. A week forecast below 'full' has spare slots, so reserve is released to the cheapest cells with capacity.</t>
+    <t xml:space="preserve">Next week below 90% of the 55 slots → release reserve to the cheapest working channel.</t>
   </si>
   <si>
     <t xml:space="preserve">R8</t>
@@ -869,10 +812,10 @@
     <t xml:space="preserve">Weight given to plan when updating qualified share (pseudo-applications)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: beta-binomial update whose prior is worth exactly R2 = 30 applications, so at the first point a cell may be judged its own data and the plan carry equal weight; after 90 applications the data carry 75%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6a. Evidence inputs behind channel quality, channel volumes and initiative sizes (the derived cells below are live formulas on these)</t>
+    <t xml:space="preserve">Early results are blended with the plan, so one lucky or unlucky week doesn't swing decisions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6a. Facts behind channel quality and volumes (cells in black below are calculated from these)</t>
   </si>
   <si>
     <t xml:space="preserve">CXB</t>
@@ -887,7 +830,7 @@
     <t xml:space="preserve">×</t>
   </si>
   <si>
-    <t xml:space="preserve">Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. </t>
+    <t xml:space="preserve">How often each channel was decisive for a hire, from IAB's 2025 employer survey. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/</t>
   </si>
   <si>
     <t xml:space="preserve">CXH</t>
@@ -908,7 +851,7 @@
     <t xml:space="preserve">Reach: share of skilled-worker job seekers using Indeed (programmatic cap)</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used.</t>
+    <t xml:space="preserve">36% of skilled-worker job seekers use Indeed (Trendence 2023). https://www.personalwirtschaft.de/?p=157882</t>
   </si>
   <si>
     <t xml:space="preserve">RXL</t>
@@ -917,7 +860,7 @@
     <t xml:space="preserve">Reach: share of skilled-worker job seekers using LinkedIn</t>
   </si>
   <si>
-    <t xml:space="preserve">LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882).</t>
+    <t xml:space="preserve">15% of skilled-worker job seekers use LinkedIn (Trendence 2023). https://www.personalwirtschaft.de/?p=157882</t>
   </si>
   <si>
     <t xml:space="preserve">RXG</t>
@@ -926,7 +869,7 @@
     <t xml:space="preserve">Reach: share of job seekers starting their search on Google</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/).</t>
+    <t xml:space="preserve">10.5% of job seekers start their search on Google (softgarden). https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/</t>
   </si>
   <si>
     <t xml:space="preserve">APV</t>
@@ -938,7 +881,7 @@
     <t xml:space="preserve">Organic</t>
   </si>
   <si>
-    <t xml:space="preserve">IAB-Stellenerhebung 2/2026: 'Große Betriebe mit mindestens 250 Beschäftigten berichten im Durchschnitt 27 Bewerbungen' (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/).</t>
+    <t xml:space="preserve">Firms with 250+ staff get ~27 applications per vacancy (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/</t>
   </si>
   <si>
     <t xml:space="preserve">CPS</t>
@@ -947,7 +890,7 @@
     <t xml:space="preserve">Share of applications that come via the careers page</t>
   </si>
   <si>
-    <t xml:space="preserve">CareerPlug 2025: 'Careers pages bring in just 13% of applicants, but 26% of hires' (https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf).</t>
+    <t xml:space="preserve">13% of applications come through the careers page (CareerPlug 2025). https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">RDE</t>
@@ -959,7 +902,7 @@
     <t xml:space="preserve">Meta electricians</t>
   </si>
   <si>
-    <t xml:space="preserve">Redline, 181 trade social campaigns 2024–26: 'Elektroniker 20 Bewerbungen' (median) (https://redline-grow.de/bewerbungen-pro-stelle).</t>
+    <t xml:space="preserve">Typical social campaign for electricians brings ~20 qualified applications (Redline, 181 campaigns). https://redline-grow.de/bewerbungen-pro-stelle</t>
   </si>
   <si>
     <t xml:space="preserve">RDM</t>
@@ -971,7 +914,7 @@
     <t xml:space="preserve">Meta mechatronics</t>
   </si>
   <si>
-    <t xml:space="preserve">Redline 2024–26: median 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle).</t>
+    <t xml:space="preserve">Typical social campaign for mechatronics brings ~23 qualified applications (Redline). https://redline-grow.de/bewerbungen-pro-stelle</t>
   </si>
   <si>
     <t xml:space="preserve">RD2</t>
@@ -983,7 +926,7 @@
     <t xml:space="preserve">I2</t>
   </si>
   <si>
-    <t xml:space="preserve">Redline 2024–26: mean 29.5 qualified applications per Elektroniker campaign (https://redline-grow.de/fachkraeftemangel-handwerk).</t>
+    <t xml:space="preserve">Average social campaign for electricians brings ~30 qualified applications (Redline). https://redline-grow.de/fachkraeftemangel-handwerk</t>
   </si>
   <si>
     <t xml:space="preserve">SSW</t>
@@ -995,7 +938,7 @@
     <t xml:space="preserve">StepStone</t>
   </si>
   <si>
-    <t xml:space="preserve">StepStone price list: 30-day job ad (https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/).</t>
+    <t xml:space="preserve">A StepStone ad runs 30 days. https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/</t>
   </si>
   <si>
     <t xml:space="preserve">STAFF</t>
@@ -1007,7 +950,7 @@
     <t xml:space="preserve">I1</t>
   </si>
   <si>
-    <t xml:space="preserve">Electrek, Mar 2026: headcount reduced 'from 12,415 to 10,703' (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/).</t>
+    <t xml:space="preserve">Plant headcount (Electrek, March 2026). https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/</t>
   </si>
   <si>
     <t xml:space="preserve">MSH</t>
@@ -1016,7 +959,7 @@
     <t xml:space="preserve">Maintenance trades as share of production occupations</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment statistics 31.12.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile): KldB 2513 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisor codes 2519/2619/2629 36,989 = 536,520 of 6,850,263 in production occupations (KldB 21–29) = 7.8% (7.3% without the supervisor codes).</t>
+    <t xml:space="preserve">Maintenance trades are ~7.8% of production jobs in Germany (BA employment data). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile</t>
   </si>
   <si>
     <t xml:space="preserve">TURN</t>
@@ -1025,7 +968,7 @@
     <t xml:space="preserve">Annual staff turnover, Brandenburg firms</t>
   </si>
   <si>
-    <t xml:space="preserve">IAB-Betriebspanel Brandenburg 2024: turnover 12% a year (https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf).</t>
+    <t xml:space="preserve">Brandenburg firms turn over ~12% of staff a year (IAB-Betriebspanel 2024). https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">REFSH</t>
@@ -1034,7 +977,7 @@
     <t xml:space="preserve">Share of hires that come from referrals</t>
   </si>
   <si>
-    <t xml:space="preserve">CareerPlug 2025: referrals 'account for just 2% of applicants, but 11% of hires' (https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf).</t>
+    <t xml:space="preserve">Referrals bring ~11% of hires (CareerPlug 2025). https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">7. Channel × role inputs (Part 2.2). Basis: CPC → CPA = CPC ÷ click-to-apply rate; CPA = bought per application/lead; Slot = fixed-price 30-day ad → CPA = price ÷ apps per ad; Free = no media cost.</t>
@@ -1076,27 +1019,18 @@
     <t xml:space="preserve">Free</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">Free listings (careers site, BA Jobbörse, Google for Jobs). Volume: ~27 applications per vacancy, 13% via the careers page. https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse</t>
   </si>
   <si>
     <t xml:space="preserve">C02</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C03</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C04</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C05</t>
   </si>
   <si>
@@ -1106,27 +1040,18 @@
     <t xml:space="preserve">CPA</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 22.5% qualified = 910 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/</t>
   </si>
   <si>
     <t xml:space="preserve">C06</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 22.5% qualified = 4,690 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C07</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 22.5% qualified = 380 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C08</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 20.7% qualified = 430 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C09</t>
   </si>
   <si>
@@ -1136,7 +1061,7 @@
     <t xml:space="preserve">Slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/</t>
   </si>
   <si>
     <t xml:space="preserve">C10</t>
@@ -1148,66 +1073,48 @@
     <t xml:space="preserve">C12</t>
   </si>
   <si>
-    <t xml:space="preserve">Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C13</t>
   </si>
   <si>
     <t xml:space="preserve">LinkedIn (promoted jobs + InMail)</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 22.5% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">DACH median €96 per application (TalentBait). Used only for automation and supervisors. https://www.talentbait.de/recruiting-kanaele-uebersicht/</t>
   </si>
   <si>
     <t xml:space="preserve">C14</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 20.7% qualified = 180 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C15</t>
   </si>
   <si>
     <t xml:space="preserve">Meta social (FB/IG lead ads, 75 km geo)</t>
   </si>
   <si>
-    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 20 ÷ 12.5% = 160 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">Social ads for trades ~€84 per application (TalentBait); volume from Redline campaign data. https://www.talentbait.de/social-media-recruiting</t>
   </si>
   <si>
     <t xml:space="preserve">C16</t>
   </si>
   <si>
-    <t xml:space="preserve">Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 23 ÷ 12.5% = 180 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C17</t>
   </si>
   <si>
     <t xml:space="preserve">Google Search ads (job-intent keywords)</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 17.8% qualified = 340 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
+    <t xml:space="preserve">Google Search ads ~€179 per application, low volume (TalentBait). https://www.talentbait.de/recruiting-kanaele-uebersicht/</t>
   </si>
   <si>
     <t xml:space="preserve">C18</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 17.8% qualified = 1,730 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C19</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 17.8% qualified = 140 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">C20</t>
   </si>
   <si>
-    <t xml:space="preserve">DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 16.3% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price.</t>
-  </si>
-  <si>
     <t xml:space="preserve">8. New-initiative inputs (Part 3) — maths on the Initiatives tab</t>
   </si>
   <si>
@@ -1220,7 +1127,7 @@
     <t xml:space="preserve">records</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated (live formula on the evidence inputs in section 6a; black text = formula). Data kept ~1 year with talent-pool consent (Haufe, https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html) → pool = one year of runners-up: STAFF × MSH × TURN = 10,703 × 7.8% × 12% = 100 maintenance hires a year, × this role's share of openings × runners-up per hire (1 ÷ qualified → signed − 1). The client's day-1 ATS export replaces it.</t>
+    <t xml:space="preserve">Calculated: about one year of runners-up in the client's applicant system (data is kept up to a year with consent). Replaced by the real export on day 1.</t>
   </si>
   <si>
     <t xml:space="preserve">I1RM</t>
@@ -1238,7 +1145,7 @@
     <t xml:space="preserve">I1: share of re-contacted past applicants who re-apply</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: geometric mean of the cold automated-email reply rate 4.96% (Pin 2026, https://www.pin.com/blog/recruiting-outreach-benchmark-report/) and the warm enterprise outreach reply rate 29% (Gem, https://www.gem.com/blog/2022-recruiting-benchmarks): √(4.96 × 29) = 12.0%. Past applicants are warm, but re-applying is a stricter step than replying.</t>
+    <t xml:space="preserve">Past applicants respond more than cold contacts (~5%) and less than warm outreach (~29%); I use 12% (Pin 2026, Gem). https://www.pin.com/blog/recruiting-outreach-benchmark-report/</t>
   </si>
   <si>
     <t xml:space="preserve">I1Q</t>
@@ -1247,7 +1154,7 @@
     <t xml:space="preserve">I1: share qualified among re-applicants</t>
   </si>
   <si>
-    <t xml:space="preserve">These people met the hard requirements when they applied (that is how the export is filtered). Forrester: rediscovered candidates 'often remain a 70 percent or more match' (via SHRM, https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages). 50% is set below that 70% because a match is not the same as meeting every requirement again (shifts, availability).</t>
+    <t xml:space="preserve">They met the requirements once; I assume half still do (Forrester via SHRM: most remain a 70%+ match). https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages</t>
   </si>
   <si>
     <t xml:space="preserve">I1FE</t>
@@ -1256,7 +1163,7 @@
     <t xml:space="preserve">I1: employee-referred applications over campaign</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated (live formula on the evidence inputs in section 6a; black text = formula). Referrals sized to deliver REFSH = 11% of this role's hires (CareerPlug 2025): role openings × 11% ÷ (I1FQ × qualified → signed × I1A).</t>
+    <t xml:space="preserve">Calculated: sized so referrals give ~11% of this role's hires.</t>
   </si>
   <si>
     <t xml:space="preserve">I1FM</t>
@@ -1274,7 +1181,7 @@
     <t xml:space="preserve">I1: share qualified among referrals</t>
   </si>
   <si>
-    <t xml:space="preserve">Referred applicants convert to hires 4–11× better than average in US data (Breezy 2026: 'convert at 8%, which is 4x the rate of any major job board', https://breezy.hr/resources/hiring-reports/source-of-hire-report; Gem 2026: 11×) and 1.37× in German employer data (IAB 2025, decisive ÷ used, https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/). 45% = 1.6 × the IAB 28% baseline, inside that range and close to the German figure.</t>
+    <t xml:space="preserve">Referred applicants are better pre-filtered (IAB: referrals are the most decisive channel), so 45% qualify. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/</t>
   </si>
   <si>
     <t xml:space="preserve">I1M</t>
@@ -1283,7 +1190,7 @@
     <t xml:space="preserve">I1: messaging cost per contacted past applicant (email + SMS tool)</t>
   </si>
   <si>
-    <t xml:space="preserve">Three waves × 1 SMS at €0.075 net (seven.io price list, https://www.seven.io/en/prices/) to €0.112 (Twilio Germany, https://www.twilio.com/en-us/sms/pricing/de) = €0.23–0.34; e-mail is near zero → €0.30 per record.</t>
+    <t xml:space="preserve">Three text messages at ~€0.08–0.11 each, plus email. https://www.seven.io/en/prices/</t>
   </si>
   <si>
     <t xml:space="preserve">I1B</t>
@@ -1292,7 +1199,7 @@
     <t xml:space="preserve">I1: referral bonus per signed referred hire (paid from this budget)</t>
   </si>
   <si>
-    <t xml:space="preserve">German practice example: €1,000 per referral, €2,000 for hard-to-fill roles (IW Köln/KOFA, https://www.kofa.de/media/Publikationen/Handlungsempfehlungen/Mitarbeiter_werben_Mitarbeiter.pdf).</t>
+    <t xml:space="preserve">Most German firms pay €501–1,000 per successful referral. https://www.personalwirtschaft.de/?p=166393</t>
   </si>
   <si>
     <t xml:space="preserve">I1A</t>
@@ -1301,7 +1208,7 @@
     <t xml:space="preserve">I1: downstream adjustment (pass/accept better than average)</t>
   </si>
   <si>
-    <t xml:space="preserve">Published uplift range: referred interviewees are ~40% more likely to get an offer (NY Fed Staff Report 568) and accept 2.7–7.3 points more often (Burks et al., QJE), summarised at https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better. Acceptance alone gives ×1.07 (75.1 ÷ 70); ×1.15 adds a fraction of the offer uplift and stays at the low end of the range.</t>
+    <t xml:space="preserve">Referred and known candidates pass and accept a little more often (+15%). https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better</t>
   </si>
   <si>
     <t xml:space="preserve">I2P</t>
@@ -1310,7 +1217,7 @@
     <t xml:space="preserve">I2: construction/Handwerk electricians (Elektroniker Energie- und Gebäudetechnik) within 75 km</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment 31.12.2025, KldB 2621 Bauelektrik: Brandenburg 5,905, Berlin 6,204 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 9,750. Bauelektrik is itself a shortage occupation (BA Engpassanalyse).</t>
+    <t xml:space="preserve">BA employment: ~10,000 construction electricians within 75 km. https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
   </si>
   <si>
     <t xml:space="preserve">I2S</t>
@@ -1319,7 +1226,7 @@
     <t xml:space="preserve">I2: share who apply over the campaign (reachable × persuaded)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated (live formula on the evidence inputs in section 6a; black text = formula). RD2 (Redline mean 29.5 qualified per Elektroniker campaign) ÷ I2Q ÷ I2P (construction electricians in reach).</t>
+    <t xml:space="preserve">Calculated from Redline's average electrician campaign (~30 qualified).</t>
   </si>
   <si>
     <t xml:space="preserve">I2C</t>
@@ -1328,7 +1235,7 @@
     <t xml:space="preserve">I2: cost per application (Meta/Google + 6-question quiz funnel)</t>
   </si>
   <si>
-    <t xml:space="preserve">Social-recruiting cost per application, trades (Handwerk) average €84 (TalentBait, 818 campaigns, vendor data, https://www.talentbait.de/social-media-recruiting).</t>
+    <t xml:space="preserve">Social ads for trades cost ~€84 per application (TalentBait). https://www.talentbait.de/social-media-recruiting</t>
   </si>
   <si>
     <t xml:space="preserve">I2Q</t>
@@ -1337,7 +1244,7 @@
     <t xml:space="preserve">I2: share qualified (only if client accepts EGT + Elektrofachkraft + 2 yrs, with in-house bridge)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated (live formula on the evidence inputs in section 6a; black text = formula). Equal to the electrician baseline QE: the 6-question quiz admits only certified electricians, so the remaining filters are the same; the skills gap is handled by I2A. Set to 0 if the client rejects the profile.</t>
+    <t xml:space="preserve">Calculated: same as electricians (25%), because the quiz admits only certified electricians.</t>
   </si>
   <si>
     <t xml:space="preserve">I2A</t>
@@ -1346,7 +1253,7 @@
     <t xml:space="preserve">I2: downstream adjustment (industrial skills gap)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: construction electricians lack the PLC/automation part, so they face the automation pass rate instead of the electrician one: PA ÷ PE = 45% ÷ 50% = 0.9. Context: closing the PLC gap fully takes a 141-day course (WBS SPS-Techniker, https://www.wbstraining.de/potsdam-weiterbildung-sps-techniker-mit-hwk-abschluss), hence the in-house bridge.</t>
+    <t xml:space="preserve">They lack PLC skills, so they pass like automation candidates: 45% ÷ 50% = 0.9.</t>
   </si>
   <si>
     <t xml:space="preserve">I2F</t>
@@ -1355,7 +1262,7 @@
     <t xml:space="preserve">I2: fixed set-up cost (German copywriter + quiz-funnel tool, 3 months)</t>
   </si>
   <si>
-    <t xml:space="preserve">Copywriting: €65/hour average freelance rate (freelancermap, https://www.freelancermap.de/freelancer/texterstellung) × ~11 h = €700. Quiz funnel: Perspective Grow €147–184/month (https://www.perspective.co/pricing) × 3 months ≈ €500. Total €1,200.</t>
+    <t xml:space="preserve">Copywriter (~11 hours at €65) plus a quiz tool for 3 months. https://www.freelancermap.de/freelancer/texterstellung</t>
   </si>
   <si>
     <t xml:space="preserve">I3C</t>
@@ -1364,7 +1271,7 @@
     <t xml:space="preserve">I3: blended cost per application, Pracuj.pl + OLX Praca + Polish-geo Meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Pracuj.pl 30-day ad 1,499 PLN net ≈ €350 (official package page, https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen) ÷ ~25 applications per ad (own estimate; no published figure) = €14.</t>
+    <t xml:space="preserve">Pracuj.pl ad price divided by expected applications, blended with OLX and Meta. https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen</t>
   </si>
   <si>
     <t xml:space="preserve">I3Q</t>
@@ -1373,7 +1280,7 @@
     <t xml:space="preserve">I3: share qualified after Polish-language pre-screen call</t>
   </si>
   <si>
-    <t xml:space="preserve">Eurostat Adult Education Survey 2022, Poland, ages 25–64 with vocational upper-secondary education: 58.7% know a foreign language, of whom 23.6% at a good or proficient level → 58.7% × 23.6% = 13.9% ≈ 14% (https://ec.europa.eu/eurostat/api/dissemination/statistics/1.0/data/edat_aes_l23?geo=PL&amp;time=2022&amp;age=Y25-64). Language is the binding filter for this trade; the pre-screen call checks it.</t>
+    <t xml:space="preserve">~14% of vocationally trained Poles speak a foreign language well (Eurostat 2022); language is the filter. https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Foreign_language_skills_statistics</t>
   </si>
   <si>
     <t xml:space="preserve">I3X</t>
@@ -1382,7 +1289,7 @@
     <t xml:space="preserve">I3: max applications over campaign</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated (live formula on the evidence inputs in section 6a; black text = formula). Applications needed to reach the 40% Polish cap (given): G4 × G6 ÷ (I3Q × mechatronics qualified → signed × I3A), rounded up to 10. Reachable: ~2,000 Polish metal/machine-trade workers already commute into Brandenburg (IAB Regional 1/2020 825 + 424 in 2019, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf, × 1.59 growth 2019–23, https://iab-forum.de/immer-mehr-menschen-pendeln-aus-osteuropa-nach-deutschland/).</t>
+    <t xml:space="preserve">Calculated: the applications needed to fill the 40% Polish cap.</t>
   </si>
   <si>
     <t xml:space="preserve">I3A</t>
@@ -1391,7 +1298,7 @@
     <t xml:space="preserve">I3: downstream adjustment (pre-screened)</t>
   </si>
   <si>
-    <t xml:space="preserve">Derivation: ×1.0, i.e. no uplift, because no study quantifies one: Pin 2026 and Indeed describe pre-screening only qualitatively ('how selective your pre-interview screening is directly determines your interview-to-offer efficiency', https://www.pin.com/blog/recruitment-funnel-benchmarks; https://www.indeed.com/hire/c/info/what-is-a-phone-screen). The pre-screen's effect is already in I3Q.</t>
+    <t xml:space="preserve">No pass-rate uplift assumed for the pre-screen; none has been measured.</t>
   </si>
   <si>
     <t xml:space="preserve">I3H</t>
@@ -1403,7 +1310,7 @@
     <t xml:space="preserve">minutes</t>
   </si>
   <si>
-    <t xml:space="preserve">'A phone screen normally lasts for 15 to 30 minutes' (Indeed, https://www.indeed.com/hire/c/info/what-is-a-phone-screen). 15 minutes = the bottom of the range, for a fixed checklist (certificate, language, shifts, commute).</t>
+    <t xml:space="preserve">Phone screens take 15–30 minutes (Indeed); a checklist call takes 15. https://www.indeed.com/hire/c/info/what-is-a-phone-screen</t>
   </si>
   <si>
     <t xml:space="preserve">I3W</t>
@@ -1412,7 +1319,7 @@
     <t xml:space="preserve">I3: pre-screener hourly rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Freelance recruiter in Poland: 60–80 PLN net per hour, B2B (RocketJobs listing, https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee) → top of range 80 PLN ÷ 4.25 PLN/€ = €19 per hour.</t>
+    <t xml:space="preserve">Polish freelance recruiters charge ~€14–19 an hour. https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee</t>
   </si>
   <si>
     <t xml:space="preserve">I3T</t>
@@ -1421,7 +1328,7 @@
     <t xml:space="preserve">I3: Polish translation of job ads + landing page</t>
   </si>
   <si>
-    <t xml:space="preserve">German statutory translator fee: €1.95 per started 55 characters (§11 JVEG, https://www.buzer.de/11_JVEG.htm); ~6,000 characters × 2 languages ≈ €430.</t>
+    <t xml:space="preserve">Translation at the German statutory rate per line (JVEG). https://www.gesetze-im-internet.de/jveg/__11.html</t>
   </si>
   <si>
     <t xml:space="preserve">Part 1 — Funnel by role (work back from openings)</t>
@@ -1661,7 +1568,7 @@
     <t xml:space="preserve">Read-out</t>
   </si>
   <si>
-    <t xml:space="preserve">Channel max ÷ pool above 100% means channel capacities overlap (the same people apply via several channels) – capacities are de-duplicated in practice, so treat the higher of the two as optimistic. Electricians' I2 initiative draws on a separate pool (construction electricians, Assumptions I2P), so its applicants are excluded from both plan and channel max here.</t>
+    <t xml:space="preserve">Channel max can exceed the pool because the same people apply via several channels. Construction electricians (I2) are a separate pool and excluded here.</t>
   </si>
   <si>
     <t xml:space="preserve">Part 3 — New sources beyond the usual paid channels (maths feeds the Channels tab)</t>
@@ -1841,7 +1748,7 @@
     <t xml:space="preserve">–</t>
   </si>
   <si>
-    <t xml:space="preserve">Also ≥ a third of the qualified are electricians. All three waves have gone out by day 14, so a kill means no further re-contacts and the I1a share of the plan is re-allocated. Referral bonus stays live: it is paid only on a signed hire (from week 4). A kill mainly signals stale ATS data.</t>
+    <t xml:space="preserve">A kill means no more re-contact waves; the referral bonus stays live (paid only on a signed hire).</t>
   </si>
   <si>
     <t xml:space="preserve">I2 Handwerk → Industrie</t>
@@ -1850,7 +1757,7 @@
     <t xml:space="preserve">Fri 23 Oct – Thu 5 Nov (read Mon 9 Nov)</t>
   </si>
   <si>
-    <t xml:space="preserve">Also kill at once if the client rejects the EGT profile. Week-4 quality check: ≥50% of the first 6 interviewed pass (kill below 40%). Money then moves to Meta, StepStone and programmatic electricians.</t>
+    <t xml:space="preserve">Also stop at once if the client rejects the profile; the money moves to programmatic electricians.</t>
   </si>
   <si>
     <t xml:space="preserve">I3 Polish corridor</t>
@@ -1859,19 +1766,19 @@
     <t xml:space="preserve">Tue 27 Oct – Mon 9 Nov (freelancer starts 27 Oct)</t>
   </si>
   <si>
-    <t xml:space="preserve">Also kill if the pre-screener finds &lt;30% speak German/English. Freelancer is paid hourly, so stopping leaves no sunk cost beyond translation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Who does what: see the deck, Part 3 (all set-up done from Bangalore; client provides ATS export, referral approval, EGT profile sign-off). Test windows start at each initiative's launch, so I2/I3 are read on Mon 9 Nov, I1 on Mon 2 Nov and again on 9 Nov.</t>
+    <t xml:space="preserve">Also stop if far fewer than planned pass the language call. The freelancer is paid hourly, so stopping costs little.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Who does what is on deck slide 7. I2 and I3 are read on Mon 9 Nov, I1 on Mon 2 Nov.</t>
   </si>
   <si>
     <t xml:space="preserve">Part 2 — Channel × role economics and allocation (cheapest cost-per-hire first, until each role's openings are covered)</t>
   </si>
   <si>
-    <t xml:space="preserve">Allocation logic: within each role, channels are filled in order of cost per hire (media at full capacity + fixed costs, ÷ hire capacity) up to their capacity until hires = openings. Polish cap enforced in hire capacity. Slots bought in whole 30-day ads.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every paid CPC/CPA cell for a role with openings first gets a test tranche (B2) in weeks 1–2; its applicants and hires are counted (cols AE–AG). The allocation then fills only the remaining need (col T) from remaining capacity (col AH).</t>
+    <t xml:space="preserve">How hires are bought: within each role, channels are used cheapest cost per hire first, each up to its volume cap, until openings are filled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every paid channel first gets a €750 test in weeks 1–2; its hires count. Then only the remaining need is bought.</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
@@ -2075,7 +1982,7 @@
     <t xml:space="preserve">Part 2.5 — What a smaller (or bigger) budget buys</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule when money is cut: drop the most expensive cost-per-hire cells first (across roles), including their test tranches and set-up costs; keep the reserve at the same %. If assessment slots bind (Funnel B24 &gt; 100%), hires are capped by slots, and a cut can even raise hires because it removes low-conversion sources: then re-optimise for hires per assessment slot. Detail in the scenario calculation below.</t>
+    <t xml:space="preserve">If money is cut: drop the most expensive cost-per-hire cells first and keep the reserve at 15%. If assessment slots run out, hires are capped (scenario detail below).</t>
   </si>
   <si>
     <t xml:space="preserve">Budget level</t>
@@ -2162,7 +2069,7 @@
     <t xml:space="preserve">Week-by-week plan: cash out, qualified flow vs 55/week, signatures</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash timing: test tranches split weeks 1–2 (B4); remaining CPC/CPA media follows the spend share (col D; supervisor cells col E, which stops at their earlier cut-off). StepStone ads and set-up costs fall in week 1. Referral bonuses are paid when the referred hire signs. Rediscovery re-applications follow their own wave profile (col Y). Signatures are scaled down if planned qualified exceed assessment slots (F38). Small approximations: Polish pre-screening starts 27 Oct and StepStone ads expire 18 Nov, but both follow the general profile.</t>
+    <t xml:space="preserve">Cash by week: tests in weeks 1–2, StepStone ads and set-up in week 1, media by the weekly shares, referral bonuses when people sign.</t>
   </si>
   <si>
     <t xml:space="preserve">Week</t>
@@ -2243,7 +2150,7 @@
     <t xml:space="preserve">Input share (Assumptions W1–W11)</t>
   </si>
   <si>
-    <t xml:space="preserve">Weeks 1–2 cash = N5. Planned cells failing the rules are cut from Mon 2 Nov once past the €500 / 30-application minimum; test tranches and the full re-allocation are judged by Mon 9 Nov. The reserve (Budget C10) is released only from week 3. CPC/CPA spend stops after the last useful application date (Funnel B19/B20); referral bonuses keep being paid as hires sign. Week 9 signatures are due by Fri 18 Dec.</t>
+    <t xml:space="preserve">Weak channels are cut from Mon 2 Nov; tests are judged by Mon 9 Nov; the reserve is released only from week 3, on the Tracker rules.</t>
   </si>
   <si>
     <t xml:space="preserve">Helper totals</t>
@@ -2456,7 +2363,7 @@
     <t xml:space="preserve">Gap</t>
   </si>
   <si>
-    <t xml:space="preserve">How to re-plan live: (1) type weeks 1–3 actuals above; (2) for any cell with a confident read, copy 'Actual CPA' and 'Updated Q' into the matching row of Assumptions §7, and the actual pass / offer→signed rates into Assumptions §3; (3) Channels re-ranks and re-allocates, Budget/Weekly/Scenarios update. Gap &gt; 0 = release reserve to the cheapest cells with capacity, or ask the client for more assessment slots.</t>
+    <t xml:space="preserve">Each Monday: type last week's actuals above. Where a channel has enough data, copy its actual cost per application and updated qualified share into Assumptions §7 (real pass and acceptance rates into §3). The plan then re-ranks itself.</t>
   </si>
 </sst>
 </file>
@@ -3412,173 +3319,173 @@
         <v>33</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -3610,12 +3517,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>31</v>
@@ -3624,21 +3531,21 @@
         <v>2</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>31</v>
@@ -3650,18 +3557,18 @@
         <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>31</v>
@@ -3670,21 +3577,21 @@
         <v>6</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>31</v>
@@ -3693,21 +3600,21 @@
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>31</v>
@@ -3716,21 +3623,21 @@
         <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>81</v>
+        <v>74</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>31</v>
@@ -3739,41 +3646,41 @@
         <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>87</v>
+        <v>63</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3807,375 +3714,375 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>0.23</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>0.55</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>0.45</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G40" s="17" t="s">
-        <v>106</v>
+        <v>63</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D44" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -4209,10 +4116,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>31</v>
@@ -4221,67 +4128,67 @@
         <v>0.15</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>0.4</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>31</v>
@@ -4290,21 +4197,21 @@
         <v>2500</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="B52" s="13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>31</v>
@@ -4313,21 +4220,21 @@
         <v>0.15</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>31</v>
@@ -4336,21 +4243,21 @@
         <v>0.5</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>31</v>
@@ -4359,274 +4266,274 @@
         <v>0.3</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D55" s="16" t="n">
         <v>0.09</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D56" s="16" t="n">
         <v>0.145</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D57" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D58" s="16" t="n">
         <v>0.18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>0.185</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G59" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>156</v>
-      </c>
       <c r="C60" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G63" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B65" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B61" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G61" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D62" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>167</v>
-      </c>
       <c r="C65" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>31</v>
@@ -4635,18 +4542,18 @@
         <v>0.3</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
@@ -4680,283 +4587,283 @@
     </row>
     <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D70" s="15" t="n">
         <v>4800</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D71" s="15" t="n">
         <v>26400</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>177</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D72" s="15" t="n">
         <v>2000</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D73" s="15" t="n">
         <v>2200</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D74" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D75" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D76" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D77" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D78" s="15" t="n">
         <v>41</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D79" s="15" t="n">
         <v>28</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D80" s="15" t="n">
         <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D81" s="15" t="n">
         <v>4</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -4988,561 +4895,561 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D85" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D86" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G86" s="17" t="s">
-        <v>205</v>
+        <v>63</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D87" s="19" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G87" s="17" t="s">
-        <v>209</v>
+        <v>63</v>
+      </c>
+      <c r="G87" s="13" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D88" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D89" s="19" t="n">
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D90" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G90" s="17" t="s">
-        <v>218</v>
+        <v>63</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D91" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G91" s="17" t="s">
-        <v>222</v>
+        <v>74</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D92" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G92" s="13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D93" s="16" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G93" s="17" t="s">
-        <v>229</v>
+        <v>63</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D94" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G94" s="13" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D95" s="16" t="n">
-        <v>0.01</v>
+        <v>0.3</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G95" s="17" t="s">
-        <v>235</v>
+        <v>63</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="D96" s="19" t="n">
         <v>2</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G96" s="17" t="s">
-        <v>238</v>
+        <v>63</v>
+      </c>
+      <c r="G96" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="D97" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="D98" s="16" t="n">
         <v>0.29</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="D99" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D100" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="D101" s="15" t="n">
         <v>10</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G101" s="17" t="s">
-        <v>254</v>
+        <v>63</v>
+      </c>
+      <c r="G101" s="13" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="D102" s="15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G102" s="17" t="s">
-        <v>258</v>
+        <v>63</v>
+      </c>
+      <c r="G102" s="13" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="D103" s="16" t="n">
         <v>0.25</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G103" s="17" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="G103" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="D104" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G104" s="13" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="D105" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="D106" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D107" s="15" t="n">
         <v>50</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G107" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D108" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G108" s="13" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
@@ -5576,375 +5483,375 @@
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D113" s="20" t="n">
         <v>0.9</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D114" s="20" t="n">
         <v>0.71</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D115" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D116" s="16" t="n">
         <v>0.36</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D117" s="16" t="n">
         <v>0.15</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D118" s="21" t="n">
         <v>0.105</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D119" s="15" t="n">
         <v>27</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D120" s="16" t="n">
         <v>0.13</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="D121" s="15" t="n">
         <v>20</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="D122" s="15" t="n">
         <v>23</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="D123" s="22" t="n">
         <v>29.5</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="D124" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D125" s="15" t="n">
         <v>10703</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D126" s="21" t="n">
         <v>0.078</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D127" s="16" t="n">
         <v>0.12</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D128" s="16" t="n">
         <v>0.11</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B130" s="11"/>
       <c r="C130" s="11"/>
@@ -5963,31 +5870,31 @@
         <v>22</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="E131" s="12" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="G131" s="12" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="H131" s="12" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="I131" s="12" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="J131" s="12" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="K131" s="12" t="s">
         <v>27</v>
@@ -5998,16 +5905,16 @@
     </row>
     <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E132" s="23" t="n">
         <v>0</v>
@@ -6028,24 +5935,24 @@
         <v>0</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L132" s="17" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E133" s="23" t="n">
         <v>0</v>
@@ -6066,24 +5973,24 @@
         <v>0</v>
       </c>
       <c r="K133" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L133" s="17" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E134" s="23" t="n">
         <v>0</v>
@@ -6104,24 +6011,24 @@
         <v>0</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L134" s="17" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="E135" s="23" t="n">
         <v>0</v>
@@ -6142,24 +6049,24 @@
         <v>0</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L135" s="17" t="s">
-        <v>355</v>
+        <v>330</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E136" s="23" t="n">
         <v>161</v>
@@ -6180,24 +6087,24 @@
         <v>0</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L136" s="17" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E137" s="23" t="n">
         <v>161</v>
@@ -6218,24 +6125,24 @@
         <v>0</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L137" s="17" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E138" s="23" t="n">
         <v>161</v>
@@ -6256,24 +6163,24 @@
         <v>0</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L138" s="17" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E139" s="23" t="n">
         <v>161</v>
@@ -6294,24 +6201,24 @@
         <v>0</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L139" s="17" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="E140" s="23" t="n">
         <v>1449</v>
@@ -6334,24 +6241,24 @@
         <v>0</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L140" s="17" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="E141" s="23" t="n">
         <v>1449</v>
@@ -6374,24 +6281,24 @@
         <v>0</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L141" s="17" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="E142" s="23" t="n">
         <v>1449</v>
@@ -6414,24 +6321,24 @@
         <v>0</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L142" s="17" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="E143" s="23" t="n">
         <v>1449</v>
@@ -6454,24 +6361,24 @@
         <v>0</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L143" s="17" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E144" s="23" t="n">
         <v>96</v>
@@ -6492,24 +6399,24 @@
         <v>0</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L144" s="17" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E145" s="23" t="n">
         <v>96</v>
@@ -6530,24 +6437,24 @@
         <v>0</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L145" s="17" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E146" s="23" t="n">
         <v>84</v>
@@ -6568,24 +6475,24 @@
         <v>0</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L146" s="17" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E147" s="23" t="n">
         <v>84</v>
@@ -6606,24 +6513,24 @@
         <v>0</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L147" s="17" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E148" s="23" t="n">
         <v>179</v>
@@ -6644,24 +6551,24 @@
         <v>0</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L148" s="17" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B149" s="13" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E149" s="23" t="n">
         <v>179</v>
@@ -6682,24 +6589,24 @@
         <v>0</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L149" s="17" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E150" s="23" t="n">
         <v>179</v>
@@ -6720,24 +6627,24 @@
         <v>0</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L150" s="17" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
       <c r="B151" s="13" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="E151" s="23" t="n">
         <v>179</v>
@@ -6758,15 +6665,15 @@
         <v>0</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L151" s="17" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="10" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
@@ -6800,106 +6707,106 @@
     </row>
     <row r="155" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D155" s="26" t="n">
         <f aca="false">IF(AND((Assumptions!$D$33*Assumptions!$D$37*Assumptions!$D$41)&gt;0,SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)&gt;0),ROUND(Assumptions!$D$125*Assumptions!$D$126*Assumptions!$D$127*Assumptions!$D$11/SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)*(1/(Assumptions!$D$33*Assumptions!$D$37*Assumptions!$D$41)-1),0),0)</f>
         <v>65</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G155" s="17" t="s">
-        <v>397</v>
+        <v>74</v>
+      </c>
+      <c r="G155" s="13" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D156" s="26" t="n">
         <f aca="false">IF(AND((Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42)&gt;0,SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)&gt;0),ROUND(Assumptions!$D$125*Assumptions!$D$126*Assumptions!$D$127*Assumptions!$D$12/SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)*(1/(Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42)-1),0),0)</f>
         <v>76</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G156" s="17" t="s">
-        <v>397</v>
+        <v>74</v>
+      </c>
+      <c r="G156" s="13" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>399</v>
+        <v>368</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D157" s="26" t="n">
         <f aca="false">IF(AND((Assumptions!$D$35*Assumptions!$D$39*Assumptions!$D$43)&gt;0,SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)&gt;0),ROUND(Assumptions!$D$125*Assumptions!$D$126*Assumptions!$D$127*Assumptions!$D$13/SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)*(1/(Assumptions!$D$35*Assumptions!$D$39*Assumptions!$D$43)-1),0),0)</f>
         <v>38</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G157" s="17" t="s">
-        <v>397</v>
+        <v>74</v>
+      </c>
+      <c r="G157" s="13" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D158" s="26" t="n">
         <f aca="false">IF(AND((Assumptions!$D$36*Assumptions!$D$40*Assumptions!$D$44)&gt;0,SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)&gt;0),ROUND(Assumptions!$D$125*Assumptions!$D$126*Assumptions!$D$127*Assumptions!$D$14/SUM(Assumptions!$D$11,Assumptions!$D$12,Assumptions!$D$13,Assumptions!$D$14)*(1/(Assumptions!$D$36*Assumptions!$D$40*Assumptions!$D$44)-1),0),0)</f>
         <v>32</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G158" s="17" t="s">
-        <v>397</v>
+        <v>74</v>
+      </c>
+      <c r="G158" s="13" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>401</v>
+        <v>370</v>
       </c>
       <c r="B159" s="13" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>31</v>
@@ -6908,21 +6815,21 @@
         <v>0.12</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>31</v>
@@ -6931,117 +6838,117 @@
         <v>0.5</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="B161" s="13" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D161" s="26" t="n">
         <f aca="false">IF((Assumptions!$D$33*Assumptions!$D$37*Assumptions!$D$41)*Assumptions!$D$165*Assumptions!$D$168&gt;0,ROUND(Assumptions!$D$128*Assumptions!$D$11/(Assumptions!$D$165*(Assumptions!$D$33*Assumptions!$D$37*Assumptions!$D$41)*Assumptions!$D$168),0),0)</f>
         <v>20</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G161" s="13" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D162" s="26" t="n">
         <f aca="false">IF((Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42)*Assumptions!$D$165*Assumptions!$D$168&gt;0,ROUND(Assumptions!$D$128*Assumptions!$D$12/(Assumptions!$D$165*(Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42)*Assumptions!$D$168),0),0)</f>
         <v>26</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G162" s="13" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
       <c r="B163" s="13" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D163" s="26" t="n">
         <f aca="false">IF((Assumptions!$D$35*Assumptions!$D$39*Assumptions!$D$43)*Assumptions!$D$165*Assumptions!$D$168&gt;0,ROUND(Assumptions!$D$128*Assumptions!$D$13/(Assumptions!$D$165*(Assumptions!$D$35*Assumptions!$D$39*Assumptions!$D$43)*Assumptions!$D$168),0),0)</f>
         <v>11</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G163" s="13" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>412</v>
+        <v>381</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D164" s="26" t="n">
         <f aca="false">IF((Assumptions!$D$36*Assumptions!$D$40*Assumptions!$D$44)*Assumptions!$D$165*Assumptions!$D$168&gt;0,ROUND(Assumptions!$D$128*Assumptions!$D$14/(Assumptions!$D$165*(Assumptions!$D$36*Assumptions!$D$40*Assumptions!$D$44)*Assumptions!$D$168),0),0)</f>
         <v>9</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G164" s="13" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>413</v>
+        <v>382</v>
       </c>
       <c r="B165" s="13" t="s">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>31</v>
@@ -7050,21 +6957,21 @@
         <v>0.45</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>416</v>
+        <v>385</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>417</v>
+        <v>386</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>31</v>
@@ -7073,21 +6980,21 @@
         <v>0.3</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>418</v>
+        <v>387</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="B167" s="13" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>31</v>
@@ -7096,21 +7003,21 @@
         <v>1000</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>31</v>
@@ -7119,315 +7026,315 @@
         <v>1.15</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="B169" s="13" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D169" s="15" t="n">
         <v>10000</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G169" s="17" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D170" s="27" t="n">
         <f aca="false">IF(Assumptions!$D$172*Assumptions!$D$169&gt;0,Assumptions!$D$123/Assumptions!$D$172/Assumptions!$D$169,0)</f>
         <v>0.0118</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G170" s="13" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D171" s="18" t="n">
         <v>84</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D172" s="25" t="n">
         <f aca="false">Assumptions!$D$29</f>
         <v>0.25</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G172" s="13" t="s">
-        <v>436</v>
+        <v>405</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D173" s="20" t="n">
         <v>0.9</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G173" s="17" t="s">
-        <v>439</v>
+        <v>63</v>
+      </c>
+      <c r="G173" s="13" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D174" s="18" t="n">
         <v>1200</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D175" s="18" t="n">
         <v>14</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D176" s="16" t="n">
         <v>0.14</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D177" s="26" t="n">
         <f aca="false">IF(Assumptions!$D$176*Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42*Assumptions!$D$178&gt;0,ROUNDUP(Assumptions!$D$10*Assumptions!$D$12/(Assumptions!$D$176*Assumptions!$D$34*Assumptions!$D$38*Assumptions!$D$42*Assumptions!$D$178),-1),0)</f>
         <v>350</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G177" s="17" t="s">
-        <v>451</v>
+        <v>63</v>
+      </c>
+      <c r="G177" s="13" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D178" s="20" t="n">
         <v>1</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G178" s="17" t="s">
-        <v>454</v>
+        <v>63</v>
+      </c>
+      <c r="G178" s="13" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D179" s="15" t="n">
         <v>15</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D180" s="18" t="n">
         <v>19</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D181" s="18" t="n">
         <v>400</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -7454,118 +7361,95 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G10" r:id="rId1" display="Brief: Polish sources allowed for mechatronics, ≤40% of those hires. Legal basis: EU free movement, no work permit needed ('you can enter Germany without a visa, thanks to the freedom of movement', https://www.make-it-in-germany.com/en/working-in-germany/information-eu-citizens/print). Cross-border commuters are insured in the country of work ('Maßgeblich ist der Staat, in dem gearbeitet wird', TK, https://www.tk.de/firmenkunden/service/fachthemen/ausland/grenzgaenger-grenzpendler-mehrstaater-2101334) and German working days are taxed in Germany (no special commuter rule in the DE–PL treaty). Mechatronics is non-regulated, so no recognition is needed."/>
-    <hyperlink ref="G15" r:id="rId2" display="Brief: 2–4 months; the plan follows the brief and buys no foreign-trained electricians. Statutory: decision within three months of a complete file (§6(3) BQFG, https://www.buzer.de/6_BQFG.htm). Upside to raise with the client: industrial electrician (Elektroniker für Betriebstechnik) is a non-regulated profession for employees ('This profession is not regulated in Germany', BIBB, https://www.anerkennung-in-deutschland.de/en/interest/finder/profession/62/profile); recognition is legally needed only for self-employment/Meister. The delay applies where the plant requires formal equivalence, e.g. before appointing someone as an Elektrofachkraft. If the client accepts employer-verified competence, EU-trained electricians become a route before 31 Dec."/>
-    <hyperlink ref="G20" r:id="rId3" display="Indeed Hiring Lab DE: job searches 'fiel an den Feiertagen auf einen Tiefpunkt von 45 % unter den durchschnittlichen Wert vom 1. bis 15. Dezember' (https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/). So the last planned signature is Fri 18 Dec; 21–23 Dec is kept as buffer for slipped signatures, not planned volume."/>
-    <hyperlink ref="G21" r:id="rId4" display="SmartRecruiters Germany 2025 benchmark: median 6 days to review an application (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf)."/>
-    <hyperlink ref="G22" r:id="rId5" display="SmartRecruiters 2025: median 14 days from application to interview (same PDF) → 14 − 6 = 8. German averages are slower (XING report 2026: 21 days to first interview, 72 days to hire, https://www.socialnet.de/personalblog/wie-lange-dauert-recruiting-wirklich-zahlen-aus-dem-xing-bewerbungsreport-2026.html), so the SmartRecruiters median is the fast-track figure the client must commit to (risk; each extra day removes ~8 slots)."/>
-    <hyperlink ref="G23" r:id="rId6" display="No published 'final interview → offer' figure (checked SmartRecruiters DE, Gem, SHRM, NACE). Context: German median time-to-hire is 55 days (SmartRecruiters DE 2025, https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf); this plan's whole chain T2+T3+T4+T5 = 24 days, a sprint process. 3 days = the service level the plan requires from the client (written offer within 3 working days of the interview, one of the asks); it is a commitment, not an estimate. Sensitivity: each extra day here moves the last useful application one day earlier and removes ~8 assessment slots (55 ÷ 7)."/>
-    <hyperlink ref="G24" r:id="rId7" display="NACE 2025: candidates took on average 9 days to decide on an offer (11 in 2023) (https://www.naceweb.org/talent-acquisition/trends-and-predictions/employers-make-more-offers-as-student-acceptance-rate-rises-response-time-shortens). 7 days = a one-week validity on the offer (client ask), which cuts the 9-day average; German acceptance is high (91%, SmartRecruiters DE 2025)."/>
-    <hyperlink ref="G25" r:id="rId8" display="Derivation: supervisors have one extra round (panel with plant management). One round = one more scheduling cycle; the assessment → interview step takes 8 days (T3) including the 1-day test, so +7 days. SHRM 2025 finds no difference in time-to-fill between executive and non-executive hires (https://www.shrm.org/content/dam/en/shrm/research/2025-recruiting-benchmarking-report.pdf), so +7 is the cautious side: setting it to 0 gives supervisors one more week of applications."/>
-    <hyperlink ref="G29" r:id="rId9" display="IAB-Stellenerhebung 2/2026 (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/): employers rate about 3 of 12 applications suitable in production occupations (≈25%; 7 of 27 ≈ 26% at firms with 250+ staff) and 23% for specialist/expert roles. Skilled trades (electricians, mechatronics, automation) use 25%; supervisors (Meister/Techniker level) use 23%. Scarcity is modelled through the smaller reachable pools and channel caps (BA Engpassanalyse 2025: supervisors 0.75, electricians 1.20, automation 1.46 job seekers per vacancy, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/arbeitsmarktberichte/fachkraefte-engpassanalyse/fachkraefte-engpassanalyse-dl-0-202512-zip.zip), not by a second discount here."/>
-    <hyperlink ref="G30" r:id="rId10" display="IAB-Stellenerhebung 2/2026 (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/): employers rate about 3 of 12 applications suitable in production occupations (≈25%; 7 of 27 ≈ 26% at firms with 250+ staff) and 23% for specialist/expert roles. Skilled trades (electricians, mechatronics, automation) use 25%; supervisors (Meister/Techniker level) use 23%. Scarcity is modelled through the smaller reachable pools and channel caps (BA Engpassanalyse 2025: supervisors 0.75, electricians 1.20, automation 1.46 job seekers per vacancy, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/arbeitsmarktberichte/fachkraefte-engpassanalyse/fachkraefte-engpassanalyse-dl-0-202512-zip.zip), not by a second discount here."/>
-    <hyperlink ref="G31" r:id="rId11" display="IAB-Stellenerhebung 2/2026 (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/): employers rate about 3 of 12 applications suitable in production occupations (≈25%; 7 of 27 ≈ 26% at firms with 250+ staff) and 23% for specialist/expert roles. Skilled trades (electricians, mechatronics, automation) use 25%; supervisors (Meister/Techniker level) use 23%. Scarcity is modelled through the smaller reachable pools and channel caps (BA Engpassanalyse 2025: supervisors 0.75, electricians 1.20, automation 1.46 job seekers per vacancy, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/arbeitsmarktberichte/fachkraefte-engpassanalyse/fachkraefte-engpassanalyse-dl-0-202512-zip.zip), not by a second discount here."/>
-    <hyperlink ref="G32" r:id="rId12" display="IAB-Stellenerhebung 2/2026 (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/): employers rate about 3 of 12 applications suitable in production occupations (≈25%; 7 of 27 ≈ 26% at firms with 250+ staff) and 23% for specialist/expert roles. Skilled trades (electricians, mechatronics, automation) use 25%; supervisors (Meister/Techniker level) use 23%. Scarcity is modelled through the smaller reachable pools and channel caps (BA Engpassanalyse 2025: supervisors 0.75, electricians 1.20, automation 1.46 job seekers per vacancy, https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/arbeitsmarktberichte/fachkraefte-engpassanalyse/fachkraefte-engpassanalyse-dl-0-202512-zip.zip), not by a second discount here."/>
-    <hyperlink ref="G33" r:id="rId13" display="Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Pass = practical/technical interview. Qualified on paper ≠ passes (fault-finding on live automation, DGUV V3 Elektrofachkraft). ~half pass."/>
-    <hyperlink ref="G34" r:id="rId14" display="Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Most standardised skill set; slightly higher pass rate."/>
-    <hyperlink ref="G35" r:id="rId15" display="Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): PLC/robotics tests are hard to fake; half pass."/>
-    <hyperlink ref="G36" r:id="rId16" display="Gem 2025 benchmarks: 35% of onsite interviews led to an offer in 2024 (48% in 2021), vendor data, mostly US (https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf); we sit somewhat higher because candidates are pre-qualified (own mapping): Leadership + technical; lowest pass rate."/>
-    <hyperlink ref="G37" r:id="rId17" display="No public rate for 'passed the final interview but no offer' (checked IAB, Gem, SmartRecruiters, HireRight 2026, which publishes no %). The combined passed → signed (offer × acceptance) is 0.90 × 0.70–0.75 = 63–68% (supervisors 0.85 × 0.70 = 60%), below SmartRecruiters' 91% German offer acceptance (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf) and below Königsteiner/StepStone's 71–78%, so the extra 10–15% loss sits inside the published range. Supervisors lose more (approval layers)."/>
-    <hyperlink ref="G38" r:id="rId18" display="No public rate for 'passed the final interview but no offer' (checked IAB, Gem, SmartRecruiters, HireRight 2026, which publishes no %). The combined passed → signed (offer × acceptance) is 0.90 × 0.70–0.75 = 63–68% (supervisors 0.85 × 0.70 = 60%), below SmartRecruiters' 91% German offer acceptance (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf) and below Königsteiner/StepStone's 71–78%, so the extra 10–15% loss sits inside the published range. Supervisors lose more (approval layers)."/>
-    <hyperlink ref="G39" r:id="rId19" display="No public rate for 'passed the final interview but no offer' (checked IAB, Gem, SmartRecruiters, HireRight 2026, which publishes no %). The combined passed → signed (offer × acceptance) is 0.90 × 0.70–0.75 = 63–68% (supervisors 0.85 × 0.70 = 60%), below SmartRecruiters' 91% German offer acceptance (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf) and below Königsteiner/StepStone's 71–78%, so the extra 10–15% loss sits inside the published range. Supervisors lose more (approval layers)."/>
-    <hyperlink ref="G40" r:id="rId20" display="No public rate for 'passed the final interview but no offer' (checked IAB, Gem, SmartRecruiters, HireRight 2026, which publishes no %). The combined passed → signed (offer × acceptance) is 0.90 × 0.70–0.75 = 63–68% (supervisors 0.85 × 0.70 = 60%), below SmartRecruiters' 91% German offer acceptance (https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf) and below Königsteiner/StepStone's 71–78%, so the extra 10–15% loss sits inside the published range. Supervisors lose more (approval layers)."/>
-    <hyperlink ref="G41" r:id="rId21" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Engpassberuf with counter-offers from energy/grid, rail, aerospace; Tesla shift work and IG Metall disputes are known. Acceptance improves if Tesla's offer beats the Brandenburg trade median (€3,030/month, standardised to 10 years' experience, WSI https://www.lohnspiegel.de/gehaltsinfos/elektroniker_in_fuer_betriebstechnik_26252114.html); client to confirm pay band."/>
-    <hyperlink ref="G42" r:id="rId22" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Bigger pool, fewer counter-offers; German pay vs Polish wages is a strong pull for border commuters."/>
-    <hyperlink ref="G43" r:id="rId23" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Scarce, many counter-offers (car makers, integrators)."/>
-    <hyperlink ref="G44" r:id="rId24" display="German offer acceptance ≈71–78%: Königsteiner 2022 (14% declined a ready-to-sign offer vs 47% receiving one ≈77%: https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449); StepStone 29% of skilled workers decline (≈71%: https://www.tageskarte.io/zahlen/detail/arbeitsmarkt-jeder-dritte-bewerber-lehnt-das-vertragsangebot-ab.html); Glassdoor 21.7% declined (≈78%: https://www.business-punk.com/work/studie-zeigt-deutsche-jobsuchende-lehnen-am-ehesten-angebote-ab/). Shortage roles at the low end (70%): Career step-up helps acceptance; counter-offers from current employer."/>
-    <hyperlink ref="G48" r:id="rId25" display="Practice: high-risk projects carry 10–20% contingency (https://mastt.com/blogs/construction-contingency); PMI recommends sizing it to the risk rather than a flat % (https://www.pmi.org/learning/library/safety-numbers-contingency-planning-10120). Risk-based check: the reserve incl. rounding (€17.1k) covers about half of the extra media a 30% miss on share qualified would need (Funnel sensitivity: +€36.6k). Beyond that the binding limit is assessment slots, not money."/>
-    <hyperlink ref="G70" r:id="rId26" display="BA employment statistics 31.12.2025, KldB 2625 elektrische Betriebstechnik + 2622: Brandenburg 3,417, Berlin 2,708 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 3,417 × 0.6 + 2,708 = 4,758 → 4,800."/>
-    <hyperlink ref="G71" r:id="rId27" display="BA employment statistics 31.12.2025, KldB 2611 + 2510 Fachkraft + 2511 + 2513 Fachkraft: Brandenburg 14,878, Berlin 17,490 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 14,878 × 0.6 + 17,490 = 26,417 → 26,400."/>
-    <hyperlink ref="G72" r:id="rId28" display="BA employment statistics 31.12.2025, KldB 2612 Automatisierungstechnik: Brandenburg 1,206, Berlin 1,254 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,206 × 0.6 + 1,254 = 1,978 → 2,000."/>
-    <hyperlink ref="G73" r:id="rId29" display="BA employment statistics 31.12.2025, Aufsicht codes 2519 + 2619 + 2629 + 2639: Brandenburg 1,209, Berlin 1,494 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile; -11- = Berlin). 75 km catchment = all of Berlin + 60% of Brandenburg: BA employees by place of residence, 30.06.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202506/iiia6/beschaeftigung-sozbe-gemband/gemband-dlk-0-202506-xlsx.xlsx): 55% live in districts fully within 75 km of Grünheide, 65% incl. partly-inside districts (Havelland, Potsdam-Mittelmark, Uckermark); midpoint 60%. 1,209 × 0.6 + 1,494 = 2,219 → 2,200."/>
-    <hyperlink ref="G74" r:id="rId30" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
-    <hyperlink ref="G75" r:id="rId31" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
-    <hyperlink ref="G76" r:id="rId32" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
-    <hyperlink ref="G77" r:id="rId33" display="Gallup Engagement Index Deutschland 2024: about 11% of employees are actively looking for a new job (https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf). That is the in-market share at any point in the window. Cross-check: one year of voluntary leavers = 12% turnover × 41% resignations = 4.9% (IAB-Betriebspanel Brandenburg 2024), a lower bound because not every searcher leaves within the year."/>
-    <hyperlink ref="G78" r:id="rId34" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 124,699 × 0.928 × 0.026 × 6/52 × 0.119 = 41. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
-    <hyperlink ref="G79" r:id="rId35" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 84,727 × 0.928 × 0.026 × 6/52 × 0.119 = 28. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
-    <hyperlink ref="G80" r:id="rId36" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 49,171 × 0.928 × 0.026 × 6/52 × 0.119 = 16. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
-    <hyperlink ref="G81" r:id="rId37" display="Derivation: national stock (BA, 31.12.2025, bo-heft Germany: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile) × 92.8% living outside Berlin-Brandenburg × 2.6% changing Bundesland of work a year (IAB Kurzbericht 4/2000, https://doku.iab.de/kurzber/2000/kb0400.pdf) × 6/52 of a year × 11.9% of inter-state movers choosing Berlin or Brandenburg (Destatis Binnenwanderung 2025, https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html). 10,746 × 0.928 × 0.026 × 6/52 × 0.119 = 4. Upper-bound rates used (the all-ages migration rate is 1.19%)."/>
-    <hyperlink ref="G86" r:id="rId38" display="Statistics: NIST's rule for reading a proportion is min{Np, N(1 − p)} ≥ 5 (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm). At the planned share qualified of ~25%, N × 0.25 ≥ 5 needs N ≥ 20; 30 applications gives N × p = 7.5 and a standard error of √(0.25 × 0.75 ÷ 30) = 7.9 points."/>
-    <hyperlink ref="G87" r:id="rId39" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). One-sided test at α = 5% (z = 1.645). At the first judgement point (30 applications, R2) the plan-blended share qualified (R8, equal weights) has a relative standard error of 16% (raw √(0.25 × 0.75 ÷ 30) = 7.9 points ÷ 25% = 32%, halved by the blend). Better than plan with 95% confidence = 1 − 1.645 × 0.16 = 0.74 → 0.75."/>
-    <hyperlink ref="G88" r:id="rId40" display="Statistics: 1.5× plan is about three standard errors worse (see R3), so the cell is very likely worse than plan. Practice: 'turn off a Meta ad once it has spent 1.5x your target CPA without a single conversion' (https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule); here the response is a 50% cut, the full stop comes at R5."/>
-    <hyperlink ref="G89" r:id="rId41" display="Practice: 'Pause if CPA over 2x target' (https://roaspig.com/blog/automated-rules-manage-meta-budgets/). At 2× plan the same money buys twice the qualified applicants in a cell running at plan."/>
-    <hyperlink ref="G90" r:id="rId42" display="Derivation: equal to the test tranche B2, so the decision falls when the test is spent. Combined with R11 = 3 expected qualified, this matches the practitioner rule 'Spent 3× your target CPA with zero purchases? Kill it' (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework)."/>
-    <hyperlink ref="G91" r:id="rId43" display="Statistics: Poisson P(0 | mean 3) = e^−3 = 5%, so a cell that reaches its test spend with zero qualified is wrong at most 1 time in 20 (with mean 2 it would be 13.5%). Matches the '3× target CPA with zero conversions' practice (https://coinis.com/blog/when-to-kill-meta-ads-decision-framework). Cells expecting fewer than 3 are judged on applications (R12)."/>
-    <hyperlink ref="G93" r:id="rId44" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). PASS uses α = 5%. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan reaches the PASS bar with ≥95% probability."/>
-    <hyperlink ref="G95" r:id="rId45" display="NIST/SEMATECH e-Handbook: 'in practice values of 0.1, 0.05, and 0.01 are common' for the significance level α (https://www.itl.nist.gov/div898/handbook/prc/section1/prc131.htm). KILL uses α = 1%, the strictest common level, because killing is irreversible. Each bar is the Poisson quantile of the initiative's planned qualified in its 14-day window (Initiatives col G/I, CRITBINOM with n = 100,000). An initiative running at plan falls below the KILL bar with &lt;1% probability."/>
-    <hyperlink ref="G96" r:id="rId46" display="Derivation: the same multiple as the channel switch-off rule R5 (2×, 'Pause if CPA over 2x target', https://roaspig.com/blog/automated-rules-manage-meta-budgets/)."/>
-    <hyperlink ref="G97" r:id="rId47" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G98" r:id="rId48" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G99" r:id="rId49" display="Derivation from Pin 2026 reply timing (50% of replies within 4 h, 74.8% within 24 h, 93.9% within 7 days) and replies by message step (43.8% / 33.7% / 15.7%) (https://www.pin.com/blog/recruiting-outreach-benchmark-report/). Waves go out on day 2 (Wed 21 Oct), day 7 (Mon 26 Oct) and day 14 (Mon 2 Nov): week 1 = 0.47 × 0.90 + 0.36 × 0.50 = 60%; week 2 = 0.47 × 0.07 + 0.36 × 0.47 + 0.17 × 0.50 = 29%; week 3 = the rest, 11%."/>
-    <hyperlink ref="G100" r:id="rId50" display="Practice: budget rules use +20% ('safe') to +30% ('aggressive') per step (https://roaspig.com/blog/automated-rules-manage-meta-budgets/); Meta warns that large budget edits restart the learning phase (https://www.facebook.com/business/help/112167992830700). +25% once a week also gives Google bidding the 1–2 conversion cycles it needs between changes (https://support.google.com/google-ads/answer/6268637)."/>
-    <hyperlink ref="G101" r:id="rId51" display="Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the ~50% planned pass rate needs N ≥ 10 interviews."/>
-    <hyperlink ref="G102" r:id="rId52" display="Statistics: NIST's min{Np, N(1 − p)} ≥ 5 rule (https://www.itl.nist.gov/div898/handbook/prc/section2/prc24.htm) at the 70% planned acceptance: N × 0.70 ≥ 5 needs N ≥ 7.1 → 7 offers (N × 0.30 ≥ 5 would need 17, more offers than exist before the first check, so the Tracker blends with the plan until then)."/>
-    <hyperlink ref="G103" r:id="rId53" display="Display flag only (changes no number). No published standard for 'share of the reachable pool'. Above 1 in 4 of everyone reachable and open to a move, a 30% miss in response rates (the sensitivity test) cannot be absorbed from the same pool. Proxy: BA Engpassanalyse treats fewer than 2 job seekers per vacancy as the tightest band (https://statistik.arbeitsagentur.de/DE/Navigation/Statistiken/Interaktive-Statistiken/Fachkraeftebedarf/Engpassanalyse-Nav.html)."/>
-    <hyperlink ref="G105" r:id="rId54" display="Bagust, Place &amp; Posnett, BMJ 1999;319:155 (abstract, https://pubmed.ncbi.nlm.nih.gov/10406748/): 'Risks are discernible when average bed occupancy rates exceed about 85%'. Same shape as queueing theory, where waiting grows with ρ ÷ (1 − ρ)."/>
-    <hyperlink ref="G106" r:id="rId55" display="Bagust, Place &amp; Posnett, BMJ 1999 (https://pubmed.ncbi.nlm.nih.gov/10406748/): 'regular bed shortages and periodic bed crises if average bed occupancy rises to 90% or more'. A week above 90% of its slots is therefore treated as full."/>
-    <hyperlink ref="G113" r:id="rId56" display="Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. "/>
-    <hyperlink ref="G114" r:id="rId57" display="Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. "/>
-    <hyperlink ref="G115" r:id="rId58" display="Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. "/>
-    <hyperlink ref="G116" r:id="rId59" display="Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used."/>
-    <hyperlink ref="G117" r:id="rId60" display="LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882)."/>
-    <hyperlink ref="G118" r:id="rId61" display="10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/)."/>
-    <hyperlink ref="G119" r:id="rId62" display="IAB-Stellenerhebung 2/2026: 'Große Betriebe mit mindestens 250 Beschäftigten berichten im Durchschnitt 27 Bewerbungen' (https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/)."/>
-    <hyperlink ref="G120" r:id="rId63" display="CareerPlug 2025: 'Careers pages bring in just 13% of applicants, but 26% of hires' (https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf)."/>
-    <hyperlink ref="G121" r:id="rId64" display="Redline, 181 trade social campaigns 2024–26: 'Elektroniker 20 Bewerbungen' (median) (https://redline-grow.de/bewerbungen-pro-stelle)."/>
-    <hyperlink ref="G122" r:id="rId65" display="Redline 2024–26: median 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle)."/>
-    <hyperlink ref="G123" r:id="rId66" display="Redline 2024–26: mean 29.5 qualified applications per Elektroniker campaign (https://redline-grow.de/fachkraeftemangel-handwerk)."/>
-    <hyperlink ref="G124" r:id="rId67" display="StepStone price list: 30-day job ad (https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/)."/>
-    <hyperlink ref="G125" r:id="rId68" display="Electrek, Mar 2026: headcount reduced 'from 12,415 to 10,703' (https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/)."/>
-    <hyperlink ref="G126" r:id="rId69" display="BA employment statistics 31.12.2025 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile): KldB 2513 240,934 + 2625 124,699 + 2611 84,727 + 2612 49,171 + supervisor codes 2519/2619/2629 36,989 = 536,520 of 6,850,263 in production occupations (KldB 21–29) = 7.8% (7.3% without the supervisor codes)."/>
-    <hyperlink ref="G127" r:id="rId70" display="IAB-Betriebspanel Brandenburg 2024: turnover 12% a year (https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf)."/>
-    <hyperlink ref="G128" r:id="rId71" display="CareerPlug 2025: referrals 'account for just 2% of applicants, but 11% of hires' (https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf)."/>
-    <hyperlink ref="L132" r:id="rId72" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 30 × 27 × 0.13 = 105. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L133" r:id="rId73" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 45 × 27 × 0.13 = 158. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L134" r:id="rId74" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 15 × 27 × 0.13 = 53. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L135" r:id="rId75" display="Free: BA Jobbörse posting is free (https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse); Google for Jobs is free. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume: openings × 27 applications per vacancy at firms with 250+ staff (IAB, https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/) × 13% of applications via the careers page (CareerPlug 2025, https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf) = 10 × 27 × 0.13 = 35. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L136" r:id="rId76" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.36 reach ÷ 22.5% qualified = 910 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L137" r:id="rId77" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.36 reach ÷ 22.5% qualified = 4,690 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L138" r:id="rId78" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.36 reach ÷ 22.5% qualified = 380 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L139" r:id="rId79" display="Indeed Germany bills per started application since 1 Mar 2024 (https://www.personalwirtschaft.de/?p=162207). DACH median cost per application on Indeed: €161 (TalentBait, 2,549 campaigns, 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: Indeed is used by 36% of skilled-worker job seekers ('Indeed mit einem Nutzungsgrad von 36 Prozent an der Spitze', Trendence 2023, n = 42,817, https://www.personalwirtschaft.de/?p=157882); the other programmatic boards overlap with it, so Indeed alone is used. Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.36 reach ÷ 20.7% qualified = 430 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L140" r:id="rId80" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L141" r:id="rId81" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L142" r:id="rId82" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–24 Nov = 36 days → 2 ads. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L143" r:id="rId83" display="Price €1,449 per 30-day ad (official price list, https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/). 12 applications per ad: StepStone Application Quality study 2025, 'durchschnittlich 12 Bewerbungen pro Stelle' (https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern/). Max ads = 30-day ads that fit the application window: 20 Oct–17 Nov = 29 days → 1 ad. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%.  Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L144" r:id="rId84" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.90 = 22.5%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.15 reach ÷ 22.5% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L145" r:id="rId85" display="DACH median cost per application on LinkedIn: €96 (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). LinkedIn job postings count as an online job board. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.90 = 20.7%. Volume cap: LinkedIn is used by 15% of skilled-worker job seekers ('Linkedin kommt mit 15 Prozent erst auf den siebten Rang', Trendence 2023, https://www.personalwirtschaft.de/?p=157882). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.15 reach ÷ 20.7% qualified = 180 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L146" r:id="rId86" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 20 qualified applications per Elektroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 20 ÷ 12.5% = 160 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L147" r:id="rId87" display="Social-recruiting cost per application for trades: €84 (TalentBait, 818 campaigns: https://www.talentbait.de/social-media-recruiting). Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.50 = 12.5%. Volume: Redline (181 trade social campaigns, 2024–26) reports a median of 23 qualified applications per Kfz-Mechatroniker campaign (https://redline-grow.de/bewerbungen-pro-stelle); cap = 23 ÷ 12.5% = 180 applications. Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L148" r:id="rId88" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 569) × 0.105 reach ÷ 17.8% qualified = 340 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L149" r:id="rId89" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 2,932) × 0.105 reach ÷ 17.8% qualified = 1,730 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L150" r:id="rId90" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (25%) × 0.71 = 17.8%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 236) × 0.105 reach ÷ 17.8% qualified = 140 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="L151" r:id="rId91" display="DACH median cost per application from Google Search: €179, 'little volume' (TalentBait 2024–26: https://www.talentbait.de/recruiting-kanaele-uebersicht/). Search ads land on the careers page, so the homepage index applies. Channel quality index from IAB-Stellenerhebung 2025: share of hires where a channel was decisive ÷ share where it was used: job boards 21/57 = 0.37, own homepage 20/70 = 0.29, referrals 27/48 = 0.56 (https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/); scaled so these three average 1 → job boards 0.90, homepage 0.71, referrals 1.37. Social media 7/40 = 0.18 vs job boards 16/51 = 0.31 in 2021 (https://iab-forum.de/iab-stellenerhebung-1-2022-174-millionen-offene-stellen-am-arbeitsmarkt/) → 0.57 × 0.90 = 0.50. Share qualified = role baseline Q (23%) × 0.71 = 16.3%. Volume cap: 10.5% of job seekers start their search on Google (softgarden 2020, n = 6,720, https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/). Cap = reachable in-market qualified pool (Funnel pool check: 246) × 0.105 reach ÷ 16.3% qualified = 160 applications (channels overlap, so caps are not additive; the pool check shows the total against the pool). Downstream adjustment ×1.0 and fixed cost €0: no published evidence of a channel-specific effect once an applicant is qualified, and no set-up fee beyond the media price."/>
-    <hyperlink ref="G155" r:id="rId92" display="Calculated (live formula on the evidence inputs in section 6a; black text = formula). Data kept ~1 year with talent-pool consent (Haufe, https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html) → pool = one year of runners-up: STAFF × MSH × TURN = 10,703 × 7.8% × 12% = 100 maintenance hires a year, × this role's share of openings × runners-up per hire (1 ÷ qualified → signed − 1). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G156" r:id="rId93" display="Calculated (live formula on the evidence inputs in section 6a; black text = formula). Data kept ~1 year with talent-pool consent (Haufe, https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html) → pool = one year of runners-up: STAFF × MSH × TURN = 10,703 × 7.8% × 12% = 100 maintenance hires a year, × this role's share of openings × runners-up per hire (1 ÷ qualified → signed − 1). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G157" r:id="rId94" display="Calculated (live formula on the evidence inputs in section 6a; black text = formula). Data kept ~1 year with talent-pool consent (Haufe, https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html) → pool = one year of runners-up: STAFF × MSH × TURN = 10,703 × 7.8% × 12% = 100 maintenance hires a year, × this role's share of openings × runners-up per hire (1 ÷ qualified → signed − 1). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G158" r:id="rId95" display="Calculated (live formula on the evidence inputs in section 6a; black text = formula). Data kept ~1 year with talent-pool consent (Haufe, https://www.haufe.de/compliance/management-praxis/aufbewahrung-wie-lange-duerfen-bewerberdaten-gespeichert-werden_230130_261218.html) → pool = one year of runners-up: STAFF × MSH × TURN = 10,703 × 7.8% × 12% = 100 maintenance hires a year, × this role's share of openings × runners-up per hire (1 ÷ qualified → signed − 1). The client's day-1 ATS export replaces it."/>
-    <hyperlink ref="G159" r:id="rId96" display="Derivation: geometric mean of the cold automated-email reply rate 4.96% (Pin 2026, https://www.pin.com/blog/recruiting-outreach-benchmark-report/) and the warm enterprise outreach reply rate 29% (Gem, https://www.gem.com/blog/2022-recruiting-benchmarks): √(4.96 × 29) = 12.0%. Past applicants are warm, but re-applying is a stricter step than replying."/>
-    <hyperlink ref="G160" r:id="rId97" display="These people met the hard requirements when they applied (that is how the export is filtered). Forrester: rediscovered candidates 'often remain a 70 percent or more match' (via SHRM, https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages). 50% is set below that 70% because a match is not the same as meeting every requirement again (shifts, availability)."/>
-    <hyperlink ref="G165" r:id="rId98" display="Referred applicants convert to hires 4–11× better than average in US data (Breezy 2026: 'convert at 8%, which is 4x the rate of any major job board', https://breezy.hr/resources/hiring-reports/source-of-hire-report; Gem 2026: 11×) and 1.37× in German employer data (IAB 2025, decisive ÷ used, https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/). 45% = 1.6 × the IAB 28% baseline, inside that range and close to the German figure."/>
-    <hyperlink ref="G166" r:id="rId99" display="Three waves × 1 SMS at €0.075 net (seven.io price list, https://www.seven.io/en/prices/) to €0.112 (Twilio Germany, https://www.twilio.com/en-us/sms/pricing/de) = €0.23–0.34; e-mail is near zero → €0.30 per record."/>
-    <hyperlink ref="G167" r:id="rId100" display="German practice example: €1,000 per referral, €2,000 for hard-to-fill roles (IW Köln/KOFA, https://www.kofa.de/media/Publikationen/Handlungsempfehlungen/Mitarbeiter_werben_Mitarbeiter.pdf)."/>
-    <hyperlink ref="G168" r:id="rId101" display="Published uplift range: referred interviewees are ~40% more likely to get an offer (NY Fed Staff Report 568) and accept 2.7–7.3 points more often (Burks et al., QJE), summarised at https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better. Acceptance alone gives ×1.07 (75.1 ÷ 70); ×1.15 adds a fraction of the offer uplift and stays at the low end of the range."/>
-    <hyperlink ref="G169" r:id="rId102" display="BA employment 31.12.2025, KldB 2621 Bauelektrik: Brandenburg 5,905, Berlin 6,204 (https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile (Brandenburg; -11- Berlin, -d- Germany)); ~75 km scaling ≈ 9,750. Bauelektrik is itself a shortage occupation (BA Engpassanalyse)."/>
-    <hyperlink ref="G171" r:id="rId103" display="Social-recruiting cost per application, trades (Handwerk) average €84 (TalentBait, 818 campaigns, vendor data, https://www.talentbait.de/social-media-recruiting)."/>
-    <hyperlink ref="G173" r:id="rId104" display="Derivation: construction electricians lack the PLC/automation part, so they face the automation pass rate instead of the electrician one: PA ÷ PE = 45% ÷ 50% = 0.9. Context: closing the PLC gap fully takes a 141-day course (WBS SPS-Techniker, https://www.wbstraining.de/potsdam-weiterbildung-sps-techniker-mit-hwk-abschluss), hence the in-house bridge."/>
-    <hyperlink ref="G174" r:id="rId105" display="Copywriting: €65/hour average freelance rate (freelancermap, https://www.freelancermap.de/freelancer/texterstellung) × ~11 h = €700. Quiz funnel: Perspective Grow €147–184/month (https://www.perspective.co/pricing) × 3 months ≈ €500. Total €1,200."/>
-    <hyperlink ref="G175" r:id="rId106" display="Pracuj.pl 30-day ad 1,499 PLN net ≈ €350 (official package page, https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen) ÷ ~25 applications per ad (own estimate; no published figure) = €14."/>
-    <hyperlink ref="G176" r:id="rId107" display="Eurostat Adult Education Survey 2022, Poland, ages 25–64 with vocational upper-secondary education: 58.7% know a foreign language, of whom 23.6% at a good or proficient level → 58.7% × 23.6% = 13.9% ≈ 14% (https://ec.europa.eu/eurostat/api/dissemination/statistics/1.0/data/edat_aes_l23?geo=PL&amp;time=2022&amp;age=Y25-64). Language is the binding filter for this trade; the pre-screen call checks it."/>
-    <hyperlink ref="G177" r:id="rId108" display="Calculated (live formula on the evidence inputs in section 6a; black text = formula). Applications needed to reach the 40% Polish cap (given): G4 × G6 ÷ (I3Q × mechatronics qualified → signed × I3A), rounded up to 10. Reachable: ~2,000 Polish metal/machine-trade workers already commute into Brandenburg (IAB Regional 1/2020 825 + 424 in 2019, https://doku.iab.de/regional/BB/2020/regional_bb_0120.pdf, × 1.59 growth 2019–23, https://iab-forum.de/immer-mehr-menschen-pendeln-aus-osteuropa-nach-deutschland/)."/>
-    <hyperlink ref="G178" r:id="rId109" display="Derivation: ×1.0, i.e. no uplift, because no study quantifies one: Pin 2026 and Indeed describe pre-screening only qualitatively ('how selective your pre-interview screening is directly determines your interview-to-offer efficiency', https://www.pin.com/blog/recruitment-funnel-benchmarks; https://www.indeed.com/hire/c/info/what-is-a-phone-screen). The pre-screen's effect is already in I3Q."/>
-    <hyperlink ref="G179" r:id="rId110" display="'A phone screen normally lasts for 15 to 30 minutes' (Indeed, https://www.indeed.com/hire/c/info/what-is-a-phone-screen). 15 minutes = the bottom of the range, for a fixed checklist (certificate, language, shifts, commute)."/>
-    <hyperlink ref="G180" r:id="rId111" display="Freelance recruiter in Poland: 60–80 PLN net per hour, B2B (RocketJobs listing, https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee) → top of range 80 PLN ÷ 4.25 PLN/€ = €19 per hour."/>
-    <hyperlink ref="G181" r:id="rId112" display="German statutory translator fee: €1.95 per started 55 characters (§11 JVEG, https://www.buzer.de/11_JVEG.htm); ~6,000 characters × 2 languages ≈ €430."/>
+    <hyperlink ref="G10" r:id="rId1" display="From the brief. Polish hires need no work permit (EU free movement) and are insured and taxed in Germany. https://www.make-it-in-germany.com/en/working-in-germany/information-eu-citizens/print"/>
+    <hyperlink ref="G15" r:id="rId2" display="From the brief, so I plan no foreign-trained electricians. Worth raising: for employees the trade is not legally regulated, which could open this route. https://www.anerkennung-in-deutschland.de/en/interest/finder/profession/62/profile"/>
+    <hyperlink ref="G20" r:id="rId3" display="Last Friday before Christmas; job searching drops ~45% over the holidays (Indeed Hiring Lab). https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/"/>
+    <hyperlink ref="G21" r:id="rId4" display="German median: 6 days to review an application (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf"/>
+    <hyperlink ref="G22" r:id="rId5" display="German median: 14 days from application to interview, minus the 6 above (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf"/>
+    <hyperlink ref="G24" r:id="rId6" display="One-week offer validity; candidates take ~9 days on average to decide (NACE 2025). https://www.naceweb.org/talent-acquisition/trends-and-predictions/employers-make-more-offers-as-student-acceptance-rate-rises-response-time-shortens"/>
+    <hyperlink ref="G29" r:id="rId7" display="About 1 in 4 applications is suitable in production jobs; 23% for specialist roles (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/"/>
+    <hyperlink ref="G30" r:id="rId8" display="About 1 in 4 applications is suitable in production jobs; 23% for specialist roles (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/"/>
+    <hyperlink ref="G31" r:id="rId9" display="About 1 in 4 applications is suitable in production jobs; 23% for specialist roles (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/"/>
+    <hyperlink ref="G32" r:id="rId10" display="About 1 in 4 applications is suitable in production jobs; 23% for specialist roles (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/"/>
+    <hyperlink ref="G33" r:id="rId11" display="About a third of final interviews lead to an offer (Gem 2025); higher here because candidates are pre-qualified. Hardest for automation and supervisors. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf"/>
+    <hyperlink ref="G34" r:id="rId12" display="About a third of final interviews lead to an offer (Gem 2025); higher here because candidates are pre-qualified. Hardest for automation and supervisors. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf"/>
+    <hyperlink ref="G35" r:id="rId13" display="About a third of final interviews lead to an offer (Gem 2025); higher here because candidates are pre-qualified. Hardest for automation and supervisors. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf"/>
+    <hyperlink ref="G36" r:id="rId14" display="BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G41" r:id="rId15" display="German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449"/>
+    <hyperlink ref="G42" r:id="rId16" display="German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449"/>
+    <hyperlink ref="G43" r:id="rId17" display="German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449"/>
+    <hyperlink ref="G44" r:id="rId18" display="German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449"/>
+    <hyperlink ref="G48" r:id="rId19" display="15% buffer, in the 10–20% range used for risky projects; released only on results. https://mastt.com/blogs/construction-contingency"/>
+    <hyperlink ref="G70" r:id="rId20" display="BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G71" r:id="rId21" display="BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G72" r:id="rId22" display="BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G73" r:id="rId23" display="BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G74" r:id="rId24" display="~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf"/>
+    <hyperlink ref="G75" r:id="rId25" display="~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf"/>
+    <hyperlink ref="G76" r:id="rId26" display="~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf"/>
+    <hyperlink ref="G77" r:id="rId27" display="~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf"/>
+    <hyperlink ref="G78" r:id="rId28" display="Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html"/>
+    <hyperlink ref="G79" r:id="rId29" display="Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html"/>
+    <hyperlink ref="G80" r:id="rId30" display="Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html"/>
+    <hyperlink ref="G81" r:id="rId31" display="Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html"/>
+    <hyperlink ref="G88" r:id="rId32" display="50% dearer than plan → halve the budget (common ad practice). https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule"/>
+    <hyperlink ref="G89" r:id="rId33" display="Twice the plan cost → switch off (common ad practice). https://roaspig.com/blog/automated-rules-manage-meta-budgets/"/>
+    <hyperlink ref="G97" r:id="rId34" display="Most replies come within a day of each message (Pin 2026), so 60% arrive in week 1. https://www.pin.com/blog/recruiting-outreach-benchmark-report/"/>
+    <hyperlink ref="G98" r:id="rId35" display="Most replies come within a day of each message (Pin 2026), so 60% arrive in week 1. https://www.pin.com/blog/recruiting-outreach-benchmark-report/"/>
+    <hyperlink ref="G99" r:id="rId36" display="Most replies come within a day of each message (Pin 2026), so 60% arrive in week 1. https://www.pin.com/blog/recruiting-outreach-benchmark-report/"/>
+    <hyperlink ref="G100" r:id="rId37" display="+25% a week: big enough to matter, small enough not to upset ad bidding. https://roaspig.com/blog/automated-rules-manage-meta-budgets/"/>
+    <hyperlink ref="G105" r:id="rId38" display="Risk rises once capacity is more than 85% used (Bagust et al., BMJ 1999). https://pubmed.ncbi.nlm.nih.gov/10406748/"/>
+    <hyperlink ref="G106" r:id="rId39" display="Above 90% use, shortages become regular (same study), so the week counts as full. https://pubmed.ncbi.nlm.nih.gov/10406748/"/>
+    <hyperlink ref="G113" r:id="rId40" display="How often each channel was decisive for a hire, from IAB's 2025 employer survey. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/"/>
+    <hyperlink ref="G114" r:id="rId41" display="How often each channel was decisive for a hire, from IAB's 2025 employer survey. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/"/>
+    <hyperlink ref="G115" r:id="rId42" display="How often each channel was decisive for a hire, from IAB's 2025 employer survey. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/"/>
+    <hyperlink ref="G116" r:id="rId43" display="36% of skilled-worker job seekers use Indeed (Trendence 2023). https://www.personalwirtschaft.de/?p=157882"/>
+    <hyperlink ref="G117" r:id="rId44" display="15% of skilled-worker job seekers use LinkedIn (Trendence 2023). https://www.personalwirtschaft.de/?p=157882"/>
+    <hyperlink ref="G118" r:id="rId45" display="10.5% of job seekers start their search on Google (softgarden). https://www.personalwirtschaft.de/news/recruiting/jeder-zehnte-nutzt-google-zur-jobsuche-97400/"/>
+    <hyperlink ref="G119" r:id="rId46" display="Firms with 250+ staff get ~27 applications per vacancy (IAB 2026). https://iab-forum.de/iab-stellenerhebung-2-2026-fast-drei-von-vier-bewerbungen-sind-aus-betrieblicher-sicht-ungeeignet/"/>
+    <hyperlink ref="G120" r:id="rId47" display="13% of applications come through the careers page (CareerPlug 2025). https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf"/>
+    <hyperlink ref="G121" r:id="rId48" display="Typical social campaign for electricians brings ~20 qualified applications (Redline, 181 campaigns). https://redline-grow.de/bewerbungen-pro-stelle"/>
+    <hyperlink ref="G122" r:id="rId49" display="Typical social campaign for mechatronics brings ~23 qualified applications (Redline). https://redline-grow.de/bewerbungen-pro-stelle"/>
+    <hyperlink ref="G123" r:id="rId50" display="Average social campaign for electricians brings ~30 qualified applications (Redline). https://redline-grow.de/fachkraeftemangel-handwerk"/>
+    <hyperlink ref="G124" r:id="rId51" display="A StepStone ad runs 30 days. https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/"/>
+    <hyperlink ref="G125" r:id="rId52" display="Plant headcount (Electrek, March 2026). https://electrek.co/2026/03/04/tesla-giga-berlin-ig-metall-union-vote-collapse/"/>
+    <hyperlink ref="G126" r:id="rId53" display="Maintenance trades are ~7.8% of production jobs in Germany (BA employment data). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G127" r:id="rId54" display="Brandenburg firms turn over ~12% of staff a year (IAB-Betriebspanel 2024). https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf"/>
+    <hyperlink ref="G128" r:id="rId55" display="Referrals bring ~11% of hires (CareerPlug 2025). https://www.careerplug.com/wp-content/uploads/2025/04/Recruiting-Metrics-Report.pdf"/>
+    <hyperlink ref="L132" r:id="rId56" display="Free listings (careers site, BA Jobbörse, Google for Jobs). Volume: ~27 applications per vacancy, 13% via the careers page. https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse"/>
+    <hyperlink ref="L133" r:id="rId57" display="Free listings (careers site, BA Jobbörse, Google for Jobs). Volume: ~27 applications per vacancy, 13% via the careers page. https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse"/>
+    <hyperlink ref="L134" r:id="rId58" display="Free listings (careers site, BA Jobbörse, Google for Jobs). Volume: ~27 applications per vacancy, 13% via the careers page. https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse"/>
+    <hyperlink ref="L135" r:id="rId59" display="Free listings (careers site, BA Jobbörse, Google for Jobs). Volume: ~27 applications per vacancy, 13% via the careers page. https://www.arbeitsagentur.de/faktor-a/mitarbeiter-finden/so-funktioniert-deutschlands-groesste-jobboerse"/>
+    <hyperlink ref="L136" r:id="rId60" display="Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L137" r:id="rId61" display="Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L138" r:id="rId62" display="Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L139" r:id="rId63" display="Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L140" r:id="rId64" display="€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/"/>
+    <hyperlink ref="L141" r:id="rId65" display="€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/"/>
+    <hyperlink ref="L142" r:id="rId66" display="€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/"/>
+    <hyperlink ref="L143" r:id="rId67" display="€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/"/>
+    <hyperlink ref="L144" r:id="rId68" display="DACH median €96 per application (TalentBait). Used only for automation and supervisors. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L145" r:id="rId69" display="DACH median €96 per application (TalentBait). Used only for automation and supervisors. https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L146" r:id="rId70" display="Social ads for trades ~€84 per application (TalentBait); volume from Redline campaign data. https://www.talentbait.de/social-media-recruiting"/>
+    <hyperlink ref="L147" r:id="rId71" display="Social ads for trades ~€84 per application (TalentBait); volume from Redline campaign data. https://www.talentbait.de/social-media-recruiting"/>
+    <hyperlink ref="L148" r:id="rId72" display="Google Search ads ~€179 per application, low volume (TalentBait). https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L149" r:id="rId73" display="Google Search ads ~€179 per application, low volume (TalentBait). https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L150" r:id="rId74" display="Google Search ads ~€179 per application, low volume (TalentBait). https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="L151" r:id="rId75" display="Google Search ads ~€179 per application, low volume (TalentBait). https://www.talentbait.de/recruiting-kanaele-uebersicht/"/>
+    <hyperlink ref="G159" r:id="rId76" display="Past applicants respond more than cold contacts (~5%) and less than warm outreach (~29%); I use 12% (Pin 2026, Gem). https://www.pin.com/blog/recruiting-outreach-benchmark-report/"/>
+    <hyperlink ref="G160" r:id="rId77" display="They met the requirements once; I assume half still do (Forrester via SHRM: most remain a 70%+ match). https://www.shrm.org/mena/topics-tools/news/technology/talent-rediscovery-tools-help-address-labor-shortages"/>
+    <hyperlink ref="G165" r:id="rId78" display="Referred applicants are better pre-filtered (IAB: referrals are the most decisive channel), so 45% qualify. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/"/>
+    <hyperlink ref="G166" r:id="rId79" display="Three text messages at ~€0.08–0.11 each, plus email. https://www.seven.io/en/prices/"/>
+    <hyperlink ref="G167" r:id="rId80" display="Most German firms pay €501–1,000 per successful referral. https://www.personalwirtschaft.de/?p=166393"/>
+    <hyperlink ref="G168" r:id="rId81" display="Referred and known candidates pass and accept a little more often (+15%). https://www.metaview.ai/resources/blog/do-referred-candidates-interview-better"/>
+    <hyperlink ref="G169" r:id="rId82" display="BA employment: ~10,000 construction electricians within 75 km. https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile"/>
+    <hyperlink ref="G171" r:id="rId83" display="Social ads for trades cost ~€84 per application (TalentBait). https://www.talentbait.de/social-media-recruiting"/>
+    <hyperlink ref="G174" r:id="rId84" display="Copywriter (~11 hours at €65) plus a quiz tool for 3 months. https://www.freelancermap.de/freelancer/texterstellung"/>
+    <hyperlink ref="G175" r:id="rId85" display="Pracuj.pl ad price divided by expected applications, blended with OLX and Meta. https://dlafirm.pracuj.pl/cennik-uslug/pakiety-ogloszen"/>
+    <hyperlink ref="G176" r:id="rId86" display="~14% of vocationally trained Poles speak a foreign language well (Eurostat 2022); language is the filter. https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Foreign_language_skills_statistics"/>
+    <hyperlink ref="G179" r:id="rId87" display="Phone screens take 15–30 minutes (Indeed); a checklist call takes 15. https://www.indeed.com/hire/c/info/what-is-a-phone-screen"/>
+    <hyperlink ref="G180" r:id="rId88" display="Polish freelance recruiters charge ~€14–19 an hour. https://rocketjobs.pl/oferta-pracy/intent-tech-recruiter-freelance--warszawa-hr-recruitment-9e0cdcee"/>
+    <hyperlink ref="G181" r:id="rId89" display="Translation at the German statutory rate per line (JVEG). https://www.gesetze-im-internet.de/jveg/__11.html"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7595,67 +7479,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>466</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>467</v>
+        <v>436</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>468</v>
+        <v>437</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>469</v>
+        <v>438</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>472</v>
+        <v>441</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>473</v>
+        <v>442</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>474</v>
+        <v>443</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">Assumptions!$D$11</f>
@@ -7720,7 +7604,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" s="29" t="n">
         <f aca="false">Assumptions!$D$12</f>
@@ -7785,7 +7669,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">Assumptions!$D$13</f>
@@ -7850,7 +7734,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B8" s="29" t="n">
         <f aca="false">Assumptions!$D$14</f>
@@ -7915,7 +7799,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="B9" s="33" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -7960,17 +7844,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>482</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>483</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="B13" s="36" t="n">
         <f aca="false">Assumptions!$D$7+Assumptions!$D$19</f>
@@ -7979,7 +7863,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="B14" s="36" t="n">
         <f aca="false">Assumptions!$D$20</f>
@@ -7988,7 +7872,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="B15" s="29" t="n">
         <f aca="false">Assumptions!$D$22+Assumptions!$D$23+Assumptions!$D$24</f>
@@ -7997,7 +7881,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="B16" s="29" t="n">
         <f aca="false">B15+Assumptions!$D$25</f>
@@ -8006,7 +7890,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="B17" s="36" t="n">
         <f aca="false">B14-B15</f>
@@ -8015,7 +7899,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="B18" s="36" t="n">
         <f aca="false">B14-B16</f>
@@ -8042,7 +7926,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">MAX(0,B17-B13+1)</f>
@@ -8060,7 +7944,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>491</v>
+        <v>460</v>
       </c>
       <c r="B23" s="29" t="n">
         <f aca="false">O9</f>
@@ -8082,7 +7966,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>492</v>
+        <v>461</v>
       </c>
       <c r="B25" s="31" t="n">
         <f aca="false">IF(O9&gt;0,Channels!U35/O9,0)</f>
@@ -8091,62 +7975,62 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="B26" s="38" t="n">
         <f aca="false">B22*B25</f>
         <v>102.049737036446</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>496</v>
+        <v>465</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>497</v>
+        <v>466</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>498</v>
+        <v>467</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>499</v>
+        <v>468</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>500</v>
+        <v>469</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>501</v>
+        <v>470</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>502</v>
+        <v>471</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>505</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B30" s="29" t="n">
         <f aca="false">B5</f>
@@ -8177,10 +8061,10 @@
         <v>2271.6049382716</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="K30" s="40" t="n">
         <f aca="false">IF(B30&gt;0,(D30-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A30))/B30,0)</f>
@@ -8193,7 +8077,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B31" s="29" t="n">
         <f aca="false">B6</f>
@@ -8224,10 +8108,10 @@
         <v>1810.10101010101</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="K31" s="40" t="n">
         <f aca="false">IF(B31&gt;0,(D31-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A31))/B31,0)</f>
@@ -8240,7 +8124,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B32" s="29" t="n">
         <f aca="false">B7</f>
@@ -8271,10 +8155,10 @@
         <v>1504.99706055262</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="K32" s="40" t="n">
         <f aca="false">IF(B32&gt;0,(D32-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A32))/B32,0)</f>
@@ -8287,7 +8171,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B33" s="29" t="n">
         <f aca="false">B8</f>
@@ -8318,10 +8202,10 @@
         <v>1948.60552916819</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="K33" s="40" t="n">
         <f aca="false">IF(B33&gt;0,(D33-SUMIFS(Channels!$N:$N,Channels!$A:$A,"I2-E",Channels!$C:$C,A33))/B33,0)</f>
@@ -8334,8 +8218,8 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="str">
-        <f aca="false">"Verdict: "&amp;Summary!C16&amp;". Evidence for electricians in the base case: the scarcest trade in Brandenburg (KOFA 2026: 85.7% of industrial-electrician vacancies have no suitable unemployed candidate, against 41.4% across all occupations, https://www.kofa.de/media/Publikationen/Laendersteckbriefe/Brandenburg.pdf; BA shortage score 2.33); no Polish route and no foreign-trained route by 31 Dec; coverage without the unproven I2 only "&amp;TEXT(K30,"0.0")&amp;"×. Supervisors cost more per hire (€"&amp;TEXT(Budget!H24,"#,##0")&amp;") but are 10 hires with an internal-promotion fallback; automation has the thinnest coverage ("&amp;TEXT(K32,"0.0")&amp;"×) but is 15 hires with a foreign-trained route."</f>
-        <v>Verdict: Electricians (€38.0k, 38% of planned spend; see Funnel row 35). Evidence for electricians in the base case: the scarcest trade in Brandenburg (KOFA 2026: 85.7% of industrial-electrician vacancies have no suitable unemployed candidate, against 41.4% across all occupations, https://www.kofa.de/media/Publikationen/Laendersteckbriefe/Brandenburg.pdf; BA shortage score 2.33); no Polish route and no foreign-trained route by 31 Dec; coverage without the unproven I2 only 3.4×. Supervisors cost more per hire (€1,550) but are 10 hires with an internal-promotion fallback; automation has the thinnest coverage (3.2×) but is 15 hires with a foreign-trained route.</v>
+        <f aca="false">"Hardest role: "&amp;Summary!C16&amp;". Electricians are the scarcest trade in Brandenburg (KOFA 2026: 85.7% of vacancies have no suitable unemployed candidate, vs 41.4% overall) and have no Polish or foreign-trained route under the brief."</f>
+        <v>Hardest role: Electricians (€38.0k, 38% of planned spend; see Funnel row 35). Electricians are the scarcest trade in Brandenburg (KOFA 2026: 85.7% of vacancies have no suitable unemployed candidate, vs 41.4% overall) and have no Polish or foreign-trained route under the brief.</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -8373,12 +8257,12 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="28" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="B40" s="30" t="n">
         <f aca="false">Assumptions!$D$66</f>
@@ -8387,33 +8271,33 @@
     </row>
     <row r="41" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>517</v>
+        <v>486</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>518</v>
+        <v>487</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>519</v>
+        <v>488</v>
       </c>
       <c r="B42" s="29" t="n">
         <f aca="false">O9</f>
@@ -8440,12 +8324,12 @@
         <v>0</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>521</v>
+        <v>490</v>
       </c>
       <c r="B43" s="29" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -8472,12 +8356,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="B44" s="29" t="n">
         <f aca="false">O9/(1-$B$40)</f>
@@ -8504,12 +8388,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>524</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="B45" s="29" t="n">
         <f aca="false">O9</f>
@@ -8536,12 +8420,12 @@
         <v>0.428571428571429</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>526</v>
+        <v>495</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>527</v>
+        <v>496</v>
       </c>
       <c r="B46" s="29" t="n">
         <f aca="false">O9</f>
@@ -8568,12 +8452,12 @@
         <v>0.3</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>528</v>
+        <v>497</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>529</v>
+        <v>498</v>
       </c>
       <c r="B47" s="29" t="n">
         <f aca="false">O9</f>
@@ -8600,12 +8484,12 @@
         <v>0</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>530</v>
+        <v>499</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="28" t="s">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="D49" s="8" t="str">
         <f aca="false">INDEX(A43:A47,MATCH(MAX(E43:E47),E43:E47,0))</f>
@@ -8614,7 +8498,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>532</v>
+        <v>501</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -8636,47 +8520,47 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>533</v>
+        <v>502</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>534</v>
+        <v>503</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>535</v>
+        <v>504</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>536</v>
+        <v>505</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>537</v>
+        <v>506</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>538</v>
+        <v>507</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>540</v>
+        <v>509</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>542</v>
+        <v>511</v>
       </c>
       <c r="K57" s="12" t="s">
-        <v>543</v>
+        <v>512</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B58" s="29" t="n">
         <f aca="false">Assumptions!$D$70</f>
@@ -8721,7 +8605,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B59" s="29" t="n">
         <f aca="false">Assumptions!$D$71</f>
@@ -8766,7 +8650,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B60" s="29" t="n">
         <f aca="false">Assumptions!$D$72</f>
@@ -8811,7 +8695,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B61" s="29" t="n">
         <f aca="false">Assumptions!$D$73</f>
@@ -8856,7 +8740,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>544</v>
+        <v>513</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -8916,37 +8800,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>545</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>546</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>547</v>
+        <v>516</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>548</v>
+        <v>517</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">Assumptions!$D$155</f>
@@ -8971,7 +8855,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>549</v>
+        <v>518</v>
       </c>
       <c r="B6" s="30" t="n">
         <f aca="false">Assumptions!$D$159</f>
@@ -8992,7 +8876,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>550</v>
+        <v>519</v>
       </c>
       <c r="B7" s="32" t="n">
         <f aca="false">B5*B6</f>
@@ -9017,7 +8901,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>551</v>
+        <v>520</v>
       </c>
       <c r="B8" s="30" t="n">
         <f aca="false">Assumptions!$D$160</f>
@@ -9038,7 +8922,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>552</v>
+        <v>521</v>
       </c>
       <c r="B9" s="31" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$168</f>
@@ -9059,7 +8943,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>553</v>
+        <v>522</v>
       </c>
       <c r="B10" s="41" t="n">
         <f aca="false">B5*Assumptions!$D$166</f>
@@ -9084,7 +8968,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>554</v>
+        <v>523</v>
       </c>
       <c r="B11" s="43" t="n">
         <f aca="false">IF(B7&gt;0,B10/B7,0)</f>
@@ -9109,7 +8993,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>555</v>
+        <v>524</v>
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">B7*B8*B9</f>
@@ -9134,7 +9018,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>556</v>
+        <v>525</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Assumptions!$D$161</f>
@@ -9159,7 +9043,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>557</v>
+        <v>526</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">Assumptions!$D$165</f>
@@ -9180,7 +9064,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>558</v>
+        <v>527</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">B13*B14*B9</f>
@@ -9205,7 +9089,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="B16" s="41" t="n">
         <f aca="false">B15*Assumptions!$D$167</f>
@@ -9230,7 +9114,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>560</v>
+        <v>529</v>
       </c>
       <c r="B17" s="43" t="n">
         <f aca="false">IF(B13&gt;0,B16/B13,0)</f>
@@ -9249,12 +9133,12 @@
         <v>123.165</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>561</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>562</v>
+        <v>531</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">B12+B15</f>
@@ -9279,7 +9163,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>563</v>
+        <v>532</v>
       </c>
       <c r="B19" s="41" t="n">
         <f aca="false">B10+B16</f>
@@ -9304,7 +9188,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>564</v>
+        <v>533</v>
       </c>
       <c r="B20" s="41" t="n">
         <f aca="false">IF(B18&gt;0,B19/B18,0)</f>
@@ -9329,12 +9213,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>565</v>
+        <v>534</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>566</v>
+        <v>535</v>
       </c>
       <c r="B24" s="29" t="n">
         <f aca="false">Assumptions!$D$169</f>
@@ -9343,7 +9227,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="B25" s="31" t="n">
         <f aca="false">Assumptions!$D$170</f>
@@ -9352,7 +9236,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="B26" s="29" t="n">
         <f aca="false">B24*B25</f>
@@ -9361,7 +9245,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
       <c r="B27" s="41" t="n">
         <f aca="false">Assumptions!$D$171</f>
@@ -9370,7 +9254,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>570</v>
+        <v>539</v>
       </c>
       <c r="B28" s="30" t="n">
         <f aca="false">Assumptions!$D$172</f>
@@ -9379,7 +9263,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>571</v>
+        <v>540</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">B26*B28</f>
@@ -9388,7 +9272,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>572</v>
+        <v>541</v>
       </c>
       <c r="B30" s="31" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$173</f>
@@ -9397,7 +9281,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>573</v>
+        <v>542</v>
       </c>
       <c r="B31" s="32" t="n">
         <f aca="false">B29*B30</f>
@@ -9406,7 +9290,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>574</v>
+        <v>543</v>
       </c>
       <c r="B32" s="41" t="n">
         <f aca="false">B26*B27</f>
@@ -9415,7 +9299,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>575</v>
+        <v>544</v>
       </c>
       <c r="B33" s="41" t="n">
         <f aca="false">Assumptions!$D$174</f>
@@ -9424,7 +9308,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>576</v>
+        <v>545</v>
       </c>
       <c r="B34" s="41" t="n">
         <f aca="false">IF(B31&gt;0,(B32+B33)/B31,0)</f>
@@ -9433,12 +9317,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>577</v>
+        <v>546</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>578</v>
+        <v>547</v>
       </c>
       <c r="B38" s="43" t="n">
         <f aca="false">B44+B45</f>
@@ -9447,7 +9331,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>579</v>
+        <v>548</v>
       </c>
       <c r="B39" s="30" t="n">
         <f aca="false">Assumptions!$D$176</f>
@@ -9456,7 +9340,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">Assumptions!$D$177</f>
@@ -9465,7 +9349,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>580</v>
+        <v>549</v>
       </c>
       <c r="B41" s="31" t="n">
         <f aca="false">Funnel!$G$6*Assumptions!$D$178</f>
@@ -9474,7 +9358,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="B42" s="32" t="n">
         <f aca="false">Assumptions!$D$10*Assumptions!$D$12</f>
@@ -9483,7 +9367,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>582</v>
+        <v>551</v>
       </c>
       <c r="B43" s="32" t="n">
         <f aca="false">MIN(B40*B39*B41,B42)</f>
@@ -9492,7 +9376,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>583</v>
+        <v>552</v>
       </c>
       <c r="B44" s="43" t="n">
         <f aca="false">Assumptions!$D$175</f>
@@ -9501,7 +9385,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="B45" s="43" t="n">
         <f aca="false">Assumptions!$D$179/60*Assumptions!$D$180</f>
@@ -9510,7 +9394,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>585</v>
+        <v>554</v>
       </c>
       <c r="B46" s="41" t="n">
         <f aca="false">Assumptions!$D$181</f>
@@ -9519,7 +9403,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>586</v>
+        <v>555</v>
       </c>
       <c r="B47" s="29" t="n">
         <f aca="false">IF(B41*B39&gt;0,B43/B41/B39,0)</f>
@@ -9528,7 +9412,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="B48" s="41" t="n">
         <f aca="false">IF(B43&gt;0,(B47*B38+B46)/B43,0)</f>
@@ -9537,50 +9421,50 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>588</v>
+        <v>557</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>592</v>
+        <v>561</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>594</v>
+        <v>563</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>597</v>
+        <v>566</v>
       </c>
       <c r="J52" s="12" t="s">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>599</v>
+        <v>568</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="28" t="s">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>601</v>
+        <v>570</v>
       </c>
       <c r="C53" s="30" t="n">
         <f aca="false">(Assumptions!$D$97+Assumptions!$D$98)</f>
@@ -9595,32 +9479,32 @@
         <v>18.2469</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>602</v>
+        <v>571</v>
       </c>
       <c r="G53" s="29" t="n">
-        <f aca="false">IF(E53&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E53/100000),MIN(MAX(Assumptions!$D$93,0.000000001),1-0.000000001))),1)</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUNDDOWN(E53*Assumptions!$D$93,0))</f>
+        <v>10</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="I53" s="29" t="n">
-        <f aca="false">MIN(G53,IF(E53&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E53/100000),MIN(MAX(Assumptions!$D$95,0.000000001),1-0.000000001))),1))</f>
-        <v>9</v>
+        <f aca="false">MIN(G53,MAX(1,ROUNDUP(E53*Assumptions!$D$95,0)))</f>
+        <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>603</v>
+        <v>572</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>604</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="s">
-        <v>605</v>
+        <v>574</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>606</v>
+        <v>575</v>
       </c>
       <c r="C54" s="30" t="n">
         <f aca="false">(Weekly!$D$4*4/7+Weekly!$D$5+Weekly!$D$6*3/7)</f>
@@ -9639,7 +9523,7 @@
         <v>336</v>
       </c>
       <c r="G54" s="29" t="n">
-        <f aca="false">IF(E54&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E54/100000),MIN(MAX(Assumptions!$D$93,0.000000001),1-0.000000001))),1)</f>
+        <f aca="false">MAX(1,ROUNDDOWN(E54*Assumptions!$D$93,0))</f>
         <v>4</v>
       </c>
       <c r="H54" s="41" t="n">
@@ -9647,23 +9531,23 @@
         <v>500</v>
       </c>
       <c r="I54" s="29" t="n">
-        <f aca="false">MIN(G54,IF(E54&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E54/100000),MIN(MAX(Assumptions!$D$95,0.000000001),1-0.000000001))),1))</f>
-        <v>2</v>
+        <f aca="false">MIN(G54,MAX(1,ROUNDUP(E54*Assumptions!$D$95,0)))</f>
+        <v>3</v>
       </c>
       <c r="J54" s="41" t="n">
         <f aca="false">MAX(H54,ROUND(F54*Assumptions!$D$96/10,0)*10)</f>
         <v>670</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>607</v>
+        <v>576</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="28" t="s">
-        <v>608</v>
+        <v>577</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="C55" s="30" t="n">
         <f aca="false">(Weekly!$D$5+Weekly!$D$6)</f>
@@ -9682,28 +9566,28 @@
         <v>133.928571428571</v>
       </c>
       <c r="G55" s="29" t="n">
-        <f aca="false">IF(E55&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E55/100000),MIN(MAX(Assumptions!$D$93,0.000000001),1-0.000000001))),1)</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUNDDOWN(E55*Assumptions!$D$93,0))</f>
+        <v>9</v>
       </c>
       <c r="H55" s="41" t="n">
         <f aca="false">ROUND(F55*Assumptions!$D$94/10,0)*10</f>
         <v>200</v>
       </c>
       <c r="I55" s="29" t="n">
-        <f aca="false">MIN(G55,IF(E55&gt;0,MAX(1,CRITBINOM(100000,MIN(1,E55/100000),MIN(MAX(Assumptions!$D$95,0.000000001),1-0.000000001))),1))</f>
-        <v>7</v>
+        <f aca="false">MIN(G55,MAX(1,ROUNDUP(E55*Assumptions!$D$95,0)))</f>
+        <v>5</v>
       </c>
       <c r="J55" s="41" t="n">
         <f aca="false">MAX(H55,ROUND(F55*Assumptions!$D$96/10,0)*10)</f>
         <v>270</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>611</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="13" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -9741,17 +9625,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>614</v>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="369.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="318.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9759,106 +9643,106 @@
         <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>615</v>
+        <v>584</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>616</v>
+        <v>585</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>619</v>
+        <v>588</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>620</v>
+        <v>589</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>622</v>
+        <v>591</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>623</v>
+        <v>592</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>624</v>
+        <v>593</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>625</v>
+        <v>594</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>626</v>
+        <v>595</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>629</v>
+        <v>598</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>630</v>
+        <v>599</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>632</v>
+        <v>601</v>
       </c>
       <c r="AA4" s="12" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>634</v>
+        <v>603</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>635</v>
+        <v>604</v>
       </c>
       <c r="AD4" s="12" t="s">
-        <v>636</v>
+        <v>605</v>
       </c>
       <c r="AE4" s="12" t="s">
-        <v>637</v>
+        <v>606</v>
       </c>
       <c r="AF4" s="12" t="s">
-        <v>638</v>
+        <v>607</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>639</v>
+        <v>608</v>
       </c>
       <c r="AH4" s="12" t="s">
-        <v>640</v>
+        <v>609</v>
       </c>
       <c r="AI4" s="12" t="s">
-        <v>641</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9875,7 +9759,7 @@
         <v>Electricians</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E5" s="2" t="str">
         <f aca="false">Assumptions!D132</f>
@@ -10016,7 +9900,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E6" s="2" t="str">
         <f aca="false">Assumptions!D133</f>
@@ -10157,7 +10041,7 @@
         <v>Automation</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E7" s="2" t="str">
         <f aca="false">Assumptions!D134</f>
@@ -10298,7 +10182,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E8" s="2" t="str">
         <f aca="false">Assumptions!D135</f>
@@ -10439,7 +10323,7 @@
         <v>Electricians</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E9" s="2" t="str">
         <f aca="false">Assumptions!D136</f>
@@ -10580,7 +10464,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="str">
         <f aca="false">Assumptions!D137</f>
@@ -10721,7 +10605,7 @@
         <v>Automation</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E11" s="2" t="str">
         <f aca="false">Assumptions!D138</f>
@@ -10862,7 +10746,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E12" s="2" t="str">
         <f aca="false">Assumptions!D139</f>
@@ -11003,7 +10887,7 @@
         <v>Electricians</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E13" s="2" t="str">
         <f aca="false">Assumptions!D140</f>
@@ -11144,7 +11028,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E14" s="2" t="str">
         <f aca="false">Assumptions!D141</f>
@@ -11285,7 +11169,7 @@
         <v>Automation</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E15" s="2" t="str">
         <f aca="false">Assumptions!D142</f>
@@ -11426,7 +11310,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E16" s="2" t="str">
         <f aca="false">Assumptions!D143</f>
@@ -11567,7 +11451,7 @@
         <v>Automation</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E17" s="2" t="str">
         <f aca="false">Assumptions!D144</f>
@@ -11708,7 +11592,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E18" s="2" t="str">
         <f aca="false">Assumptions!D145</f>
@@ -11849,7 +11733,7 @@
         <v>Electricians</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E19" s="2" t="str">
         <f aca="false">Assumptions!D146</f>
@@ -11990,7 +11874,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E20" s="2" t="str">
         <f aca="false">Assumptions!D147</f>
@@ -12131,7 +12015,7 @@
         <v>Electricians</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E21" s="2" t="str">
         <f aca="false">Assumptions!D148</f>
@@ -12272,7 +12156,7 @@
         <v>Mechatronics</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E22" s="2" t="str">
         <f aca="false">Assumptions!D149</f>
@@ -12413,7 +12297,7 @@
         <v>Automation</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E23" s="2" t="str">
         <f aca="false">Assumptions!D150</f>
@@ -12554,7 +12438,7 @@
         <v>Supervisors</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="E24" s="2" t="str">
         <f aca="false">Assumptions!D151</f>
@@ -12683,19 +12567,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>642</v>
+        <v>611</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F25" s="43" t="n">
         <f aca="false">Initiatives!B11</f>
@@ -12817,19 +12701,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F26" s="43" t="n">
         <f aca="false">Initiatives!C11</f>
@@ -12951,19 +12835,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>645</v>
+        <v>614</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F27" s="43" t="n">
         <f aca="false">Initiatives!D11</f>
@@ -13085,19 +12969,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>646</v>
+        <v>615</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F28" s="43" t="n">
         <f aca="false">Initiatives!E11</f>
@@ -13219,19 +13103,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>647</v>
+        <v>616</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F29" s="43" t="n">
         <f aca="false">Initiatives!B17</f>
@@ -13353,19 +13237,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F30" s="43" t="n">
         <f aca="false">Initiatives!C17</f>
@@ -13487,19 +13371,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>650</v>
+        <v>619</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F31" s="43" t="n">
         <f aca="false">Initiatives!D17</f>
@@ -13621,19 +13505,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>651</v>
+        <v>620</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">Initiatives!E17</f>
@@ -13755,19 +13639,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>652</v>
+        <v>621</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F33" s="43" t="n">
         <f aca="false">Initiatives!B27</f>
@@ -13889,19 +13773,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>654</v>
+        <v>623</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="F34" s="43" t="n">
         <f aca="false">Initiatives!B38</f>
@@ -14023,7 +13907,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="J35" s="33" t="n">
         <f aca="false">SUM(J5:J34)</f>
@@ -14088,27 +13972,27 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>656</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12"/>
       <c r="B38" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>657</v>
+        <v>626</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>658</v>
+        <v>627</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C39" s="29" t="n">
         <f aca="false">Funnel!B5</f>
@@ -14125,7 +14009,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="29" t="n">
         <f aca="false">Funnel!B6</f>
@@ -14142,7 +14026,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C41" s="29" t="n">
         <f aca="false">Funnel!B7</f>
@@ -14159,7 +14043,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C42" s="29" t="n">
         <f aca="false">Funnel!B8</f>
@@ -14202,12 +14086,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>659</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
       <c r="C4" s="41" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Channel")</f>
@@ -14216,7 +14100,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>661</v>
+        <v>630</v>
       </c>
       <c r="C5" s="41" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Initiative")</f>
@@ -14225,7 +14109,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>662</v>
+        <v>631</v>
       </c>
       <c r="C6" s="41" t="n">
         <f aca="false">Channels!Y35</f>
@@ -14234,7 +14118,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>663</v>
+        <v>632</v>
       </c>
       <c r="C7" s="41" t="n">
         <f aca="false">C4+C5+C6</f>
@@ -14243,7 +14127,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>664</v>
+        <v>633</v>
       </c>
       <c r="C8" s="41" t="n">
         <f aca="false">Channels!Z35</f>
@@ -14252,7 +14136,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="C9" s="41" t="n">
         <f aca="false">C7</f>
@@ -14261,7 +14145,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>666</v>
+        <v>635</v>
       </c>
       <c r="C10" s="41" t="n">
         <f aca="false">IF(Assumptions!$D$48&lt;1,C9/(1-Assumptions!$D$48)*Assumptions!$D$48,0)</f>
@@ -14270,7 +14154,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>667</v>
+        <v>636</v>
       </c>
       <c r="C11" s="41" t="n">
         <f aca="false">C9+C10</f>
@@ -14279,7 +14163,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">IF(Assumptions!$D$51&gt;0,ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51,C11)</f>
@@ -14288,7 +14172,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>669</v>
+        <v>638</v>
       </c>
       <c r="C13" s="46" t="n">
         <f aca="false">MIN(Channels!U35,Funnel!B26)</f>
@@ -14297,7 +14181,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>670</v>
+        <v>639</v>
       </c>
       <c r="C14" s="47" t="n">
         <f aca="false">IF(C13&gt;0,C9/C13,0)</f>
@@ -14306,7 +14190,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>671</v>
+        <v>640</v>
       </c>
       <c r="C15" s="41" t="n">
         <f aca="false">IF(C13&gt;0,C12/C13,0)</f>
@@ -14315,7 +14199,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>672</v>
+        <v>641</v>
       </c>
       <c r="C16" s="30" t="n">
         <f aca="false">IF(C12&gt;0,Weekly!N5/C12,0)</f>
@@ -14324,39 +14208,39 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="28" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
       <c r="B20" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>678</v>
+        <v>647</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B21)</f>
@@ -14389,7 +14273,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C22" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B22)</f>
@@ -14422,7 +14306,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C23" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B23)</f>
@@ -14455,7 +14339,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,B24)</f>
@@ -14488,7 +14372,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="C25" s="42" t="n">
         <f aca="false">SUM(C21:C24)</f>
@@ -14521,30 +14405,30 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="28" t="s">
-        <v>679</v>
+        <v>648</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>680</v>
+        <v>649</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C29" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B29)</f>
@@ -14565,7 +14449,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C30" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B30)</f>
@@ -14586,7 +14470,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="C31" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B31)</f>
@@ -14607,7 +14491,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="C32" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B32)</f>
@@ -14628,7 +14512,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="C33" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B33)</f>
@@ -14649,7 +14533,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="C34" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B34)</f>
@@ -14670,7 +14554,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C35" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B35)</f>
@@ -14691,7 +14575,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="C36" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B36)</f>
@@ -14712,7 +14596,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="C37" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B37)</f>
@@ -14733,7 +14617,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="C38" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B38)</f>
@@ -14754,7 +14638,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="C39" s="42" t="n">
         <f aca="false">SUM(C29:C38)</f>
@@ -14773,39 +14657,39 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="28" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="2" t="s">
-        <v>682</v>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="13" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
-        <v>683</v>
+        <v>652</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>684</v>
+        <v>653</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>685</v>
+        <v>654</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14969,17 +14853,17 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>686</v>
+        <v>655</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>687</v>
+        <v>656</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="28" t="s">
-        <v>688</v>
+        <v>657</v>
       </c>
       <c r="F56" s="48" t="n">
         <f aca="false">1</f>
@@ -15000,7 +14884,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="2" t="s">
-        <v>684</v>
+        <v>653</v>
       </c>
       <c r="F57" s="41" t="n">
         <f aca="false">Budget!$C$12*F56</f>
@@ -15021,7 +14905,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E58" s="2" t="s">
-        <v>689</v>
+        <v>658</v>
       </c>
       <c r="F58" s="41" t="n">
         <f aca="false">F57*(1-Assumptions!$D$48)</f>
@@ -15042,7 +14926,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="2" t="s">
-        <v>690</v>
+        <v>659</v>
       </c>
       <c r="F59" s="41" t="n">
         <f aca="false">MAX(0,Budget!$C$9-F58)</f>
@@ -15063,58 +14947,58 @@
     </row>
     <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>691</v>
+        <v>660</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>692</v>
+        <v>661</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>693</v>
+        <v>662</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>694</v>
+        <v>663</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>695</v>
+        <v>664</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>696</v>
+        <v>665</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>697</v>
+        <v>666</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>698</v>
+        <v>667</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>699</v>
+        <v>668</v>
       </c>
       <c r="L60" s="12" t="s">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>701</v>
+        <v>670</v>
       </c>
       <c r="N60" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="O60" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="P60" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q60" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="R60" s="12" t="s">
         <v>674</v>
-      </c>
-      <c r="O60" s="12" t="s">
-        <v>702</v>
-      </c>
-      <c r="P60" s="12" t="s">
-        <v>703</v>
-      </c>
-      <c r="Q60" s="12" t="s">
-        <v>704</v>
-      </c>
-      <c r="R60" s="12" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -17339,12 +17223,12 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E91" s="28" t="s">
-        <v>706</v>
+        <v>675</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E92" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F92" s="32" t="n">
         <f aca="false">SUMIFS(F$61:F$90,$B$61:$B$90,$E92)*F$100</f>
@@ -17365,7 +17249,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E93" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F93" s="32" t="n">
         <f aca="false">SUMIFS(F$61:F$90,$B$61:$B$90,$E93)*F$100</f>
@@ -17386,7 +17270,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E94" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F94" s="32" t="n">
         <f aca="false">SUMIFS(F$61:F$90,$B$61:$B$90,$E94)*F$100</f>
@@ -17407,7 +17291,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E95" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F95" s="32" t="n">
         <f aca="false">SUMIFS(F$61:F$90,$B$61:$B$90,$E95)*F$100</f>
@@ -17428,7 +17312,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E96" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="F96" s="35" t="n">
         <f aca="false">SUM(F92:F95)</f>
@@ -17449,7 +17333,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E97" s="2" t="s">
-        <v>677</v>
+        <v>646</v>
       </c>
       <c r="F97" s="41" t="n">
         <f aca="false">IF(F96&gt;0,F57/F96,0)</f>
@@ -17470,7 +17354,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E99" s="2" t="s">
-        <v>707</v>
+        <v>676</v>
       </c>
       <c r="F99" s="32" t="n">
         <f aca="false">SUM(O61:O90)</f>
@@ -17491,7 +17375,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E100" s="2" t="s">
-        <v>708</v>
+        <v>677</v>
       </c>
       <c r="F100" s="30" t="n">
         <f aca="false">IF(F99&gt;0,MIN(1,Funnel!$B$22/F99),1)</f>
@@ -17512,7 +17396,7 @@
     </row>
     <row r="102" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
-        <v>709</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -17548,92 +17432,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>711</v>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="344" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>680</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>712</v>
+        <v>681</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>713</v>
+        <v>682</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>714</v>
+        <v>683</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>715</v>
+        <v>684</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>716</v>
+        <v>685</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>719</v>
+        <v>688</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>720</v>
+        <v>689</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>721</v>
+        <v>690</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>722</v>
+        <v>691</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>723</v>
+        <v>692</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>724</v>
+        <v>693</v>
       </c>
       <c r="N3" s="12" t="s">
-        <v>725</v>
+        <v>694</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>729</v>
+        <v>698</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>730</v>
+        <v>699</v>
       </c>
       <c r="T3" s="12" t="s">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="Z3" s="49" t="s">
-        <v>737</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18793,7 +18677,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">SUM(D4:D14)</f>
@@ -18878,7 +18762,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -18930,12 +18814,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>739</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="F19" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18944,7 +18828,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>741</v>
+        <v>710</v>
       </c>
       <c r="F20" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18953,7 +18837,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="F21" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -18962,7 +18846,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="F22" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18971,7 +18855,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="F23" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -18980,7 +18864,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="F24" s="41" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -18989,7 +18873,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="F25" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -18998,7 +18882,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>747</v>
+        <v>716</v>
       </c>
       <c r="F26" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19007,7 +18891,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>748</v>
+        <v>717</v>
       </c>
       <c r="F27" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -19016,7 +18900,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>749</v>
+        <v>718</v>
       </c>
       <c r="F28" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19025,7 +18909,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="F29" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -19034,7 +18918,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>751</v>
+        <v>720</v>
       </c>
       <c r="F30" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19043,7 +18927,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>752</v>
+        <v>721</v>
       </c>
       <c r="F31" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -19052,7 +18936,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="F32" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -19061,7 +18945,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>754</v>
+        <v>723</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19070,7 +18954,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>755</v>
+        <v>724</v>
       </c>
       <c r="F34" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -19079,7 +18963,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>756</v>
+        <v>725</v>
       </c>
       <c r="F35" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19088,7 +18972,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>757</v>
+        <v>726</v>
       </c>
       <c r="F36" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -19097,7 +18981,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>758</v>
+        <v>727</v>
       </c>
       <c r="F37" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -19106,7 +18990,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>759</v>
+        <v>728</v>
       </c>
       <c r="F38" s="30" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -19115,49 +18999,49 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>760</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12"/>
       <c r="B43" s="12" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>761</v>
+        <v>730</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>762</v>
+        <v>731</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>764</v>
+        <v>733</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>765</v>
+        <v>734</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>767</v>
+        <v>736</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>768</v>
+        <v>737</v>
       </c>
       <c r="K43" s="12" t="s">
-        <v>769</v>
+        <v>738</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>770</v>
+        <v>739</v>
       </c>
       <c r="M43" s="12" t="s">
-        <v>771</v>
+        <v>740</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19702,7 +19586,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="C54" s="42" t="n">
         <f aca="false">SUM(C44:C53)</f>
@@ -19792,12 +19676,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>772</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>773</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19805,73 +19689,73 @@
         <v>22</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>774</v>
+        <v>743</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>775</v>
+        <v>744</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>776</v>
+        <v>745</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>777</v>
+        <v>746</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>778</v>
+        <v>747</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>779</v>
+        <v>748</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>780</v>
+        <v>749</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>783</v>
+        <v>752</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>784</v>
+        <v>753</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>785</v>
+        <v>754</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>786</v>
+        <v>755</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>787</v>
+        <v>756</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>788</v>
+        <v>757</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>789</v>
+        <v>758</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>790</v>
+        <v>759</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>791</v>
+        <v>760</v>
       </c>
       <c r="V4" s="12" t="s">
-        <v>792</v>
+        <v>761</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>793</v>
+        <v>762</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>794</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22006,7 +21890,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="G35" s="42" t="n">
         <f aca="false">SUM(G5:G34)</f>
@@ -22059,60 +21943,60 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>795</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12"/>
       <c r="B39" s="12" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>796</v>
+        <v>765</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>797</v>
+        <v>766</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>801</v>
+        <v>770</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>802</v>
+        <v>771</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>803</v>
+        <v>772</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>804</v>
+        <v>773</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>805</v>
+        <v>774</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>806</v>
+        <v>775</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>807</v>
+        <v>776</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>808</v>
+        <v>777</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="15"/>
@@ -22158,7 +22042,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
@@ -22204,7 +22088,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="15"/>
@@ -22250,7 +22134,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -22296,7 +22180,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="28" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="C44" s="35" t="n">
         <f aca="false">SUM(C40:C43)</f>
@@ -22337,7 +22221,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>809</v>
+        <v>778</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="758">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">records</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated: about one year of runners-up in the client's applicant system (data is kept up to a year with consent). Replaced by the real export on day 1.</t>
+    <t xml:space="preserve">Calculated: last year's maintenance hires (STAFF × MSH × TURN × this role's share) × qualified runners-up per hire (1 ÷ qualified→signed − 1). Replaced by the real export on day 1.</t>
   </si>
   <si>
     <t xml:space="preserve">I1RM</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">I1: employee-referred applications over campaign</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated: sized so referrals give ~11% of this role's hires.</t>
+    <t xml:space="preserve">Calculated: referrals give REFSH (11%) of this role's hires: REFSH × openings ÷ (I1FQ × qualified→signed × I1A).</t>
   </si>
   <si>
     <t xml:space="preserve">I1FM</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">I2: share who apply over the campaign (reachable × persuaded)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calculated from Redline's average electrician campaign (~30 qualified).</t>
+    <t xml:space="preserve">Calculated: RD2 (Redline, ~30 qualified per electrician campaign) ÷ I2Q ÷ I2P.</t>
   </si>
   <si>
     <t xml:space="preserve">I2C</t>
@@ -1481,16 +1481,13 @@
     <t xml:space="preserve">Pure money: +30% media, no effect on hires if the money is there.</t>
   </si>
   <si>
-    <t xml:space="preserve">Recruiter capacity ×0.7 (≈38/week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fewer slots: hires capped by capacity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Most sensitive assumption (largest hire loss):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Why it matters most: recruiter capacity, not money, is the binding limit. Anything that lowers hires per qualified applicant (pass or acceptance) can't be fixed by spending more; anything upstream (share qualified, CPA) can.</t>
+    <t xml:space="preserve">Recruiter capacity ×0.7 (≈38/week), given in the brief, shown for context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fewer slots: hires capped by capacity. Not ranked: 55/week is given, not assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most sensitive assumption (largest hire loss; capacity excluded as it is given):</t>
   </si>
   <si>
     <t xml:space="preserve">Talent-pool sanity check (Part 2.2): can the channels plausibly deliver the qualified applicants we plan?</t>
@@ -3566,7 +3563,7 @@
         <v>62</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>78</v>
@@ -8317,13 +8314,14 @@
         <v>486</v>
       </c>
       <c r="D49" s="8" t="str">
-        <f aca="false">INDEX(A43:A47,MATCH(MAX(E43:E47),E43:E47,0))</f>
+        <f aca="false">INDEX(A43:A46,MATCH(MAX(E43:E46),E43:E46,0))</f>
         <v>Qualified → signed (assessment pass rate) ×0.7</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>487</v>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="str">
+        <f aca="false">IF(AND(E43&gt;0,ROUND(E43,6)=ROUND(E44,6)),"Pass rate and acceptance tie ("&amp;TEXT(E43,"0")&amp;" hires lost each). I name the pass rate: it depends on this plant’s own test, so it is the least known, and it can only be read after interviews (week-2 check). Acceptance can be protected with fast offers. ","")&amp;"Why it matters: assessment capacity, not money, is the limit, so a lower pass rate or acceptance can’t be fixed by spending more; a lower share qualified or dearer clicks only cost money."</f>
+        <v>Pass rate and acceptance tie (29 hires lost each). I name the pass rate: it depends on this plant’s own test, so it is the least known, and it can only be read after interviews (week-2 check). Acceptance can be protected with fast offers. Why it matters: assessment capacity, not money, is the limit, so a lower pass rate or acceptance can’t be fixed by spending more; a lower share qualified or dearer clicks only cost money.</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -8345,7 +8343,7 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8353,34 +8351,34 @@
         <v>305</v>
       </c>
       <c r="B57" s="12" t="s">
+        <v>488</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="D57" s="12" t="s">
         <v>490</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="E57" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="F57" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="G57" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="H57" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="I57" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="J57" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="K57" s="12" t="s">
         <v>497</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8565,7 +8563,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -8625,22 +8623,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>48</v>
@@ -8660,7 +8658,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B5" s="29" t="n">
         <f aca="false">Assumptions!$D$150</f>
@@ -8685,7 +8683,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B6" s="30" t="n">
         <f aca="false">Assumptions!$D$154</f>
@@ -8706,7 +8704,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B7" s="32" t="n">
         <f aca="false">B5*B6</f>
@@ -8731,7 +8729,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B8" s="30" t="n">
         <f aca="false">Assumptions!$D$155</f>
@@ -8752,7 +8750,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B9" s="31" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$163</f>
@@ -8773,7 +8771,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B10" s="41" t="n">
         <f aca="false">B5*Assumptions!$D$161</f>
@@ -8798,7 +8796,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B11" s="43" t="n">
         <f aca="false">IF(B7&gt;0,B10/B7,0)</f>
@@ -8823,7 +8821,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">B7*B8*B9</f>
@@ -8848,7 +8846,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Assumptions!$D$156</f>
@@ -8873,7 +8871,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B14" s="30" t="n">
         <f aca="false">Assumptions!$D$160</f>
@@ -8894,7 +8892,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">B13*B14*B9</f>
@@ -8919,7 +8917,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B16" s="41" t="n">
         <f aca="false">B15*Assumptions!$D$162</f>
@@ -8944,7 +8942,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B17" s="43" t="n">
         <f aca="false">IF(B13&gt;0,B16/B13,0)</f>
@@ -8963,12 +8961,12 @@
         <v>123.165</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">B12+B15</f>
@@ -8993,7 +8991,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B19" s="41" t="n">
         <f aca="false">B10+B16</f>
@@ -9018,7 +9016,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B20" s="41" t="n">
         <f aca="false">IF(B18&gt;0,B19/B18,0)</f>
@@ -9043,12 +9041,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B24" s="29" t="n">
         <f aca="false">Assumptions!$D$164</f>
@@ -9057,7 +9055,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B25" s="31" t="n">
         <f aca="false">Assumptions!$D$165</f>
@@ -9066,7 +9064,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B26" s="29" t="n">
         <f aca="false">B24*B25</f>
@@ -9075,7 +9073,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B27" s="41" t="n">
         <f aca="false">Assumptions!$D$166</f>
@@ -9084,7 +9082,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B28" s="30" t="n">
         <f aca="false">Assumptions!$D$167</f>
@@ -9093,7 +9091,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">B26*B28</f>
@@ -9102,7 +9100,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B30" s="31" t="n">
         <f aca="false">Funnel!$G$5*Assumptions!$D$168</f>
@@ -9111,7 +9109,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B31" s="32" t="n">
         <f aca="false">B29*B30</f>
@@ -9120,7 +9118,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B32" s="41" t="n">
         <f aca="false">B26*B27</f>
@@ -9129,7 +9127,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B33" s="41" t="n">
         <f aca="false">Assumptions!$D$169</f>
@@ -9138,7 +9136,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B34" s="41" t="n">
         <f aca="false">IF(B31&gt;0,(B32+B33)/B31,0)</f>
@@ -9147,12 +9145,12 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B38" s="43" t="n">
         <f aca="false">B44+B45</f>
@@ -9161,7 +9159,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B39" s="30" t="n">
         <f aca="false">Assumptions!$D$171</f>
@@ -9170,7 +9168,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">Assumptions!$D$172</f>
@@ -9179,7 +9177,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B41" s="31" t="n">
         <f aca="false">Funnel!$G$6*Assumptions!$D$173</f>
@@ -9188,7 +9186,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B42" s="32" t="n">
         <f aca="false">Assumptions!$D$10*Assumptions!$D$12</f>
@@ -9197,7 +9195,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B43" s="32" t="n">
         <f aca="false">MIN(B40*B39*B41,B42)</f>
@@ -9206,7 +9204,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B44" s="43" t="n">
         <f aca="false">Assumptions!$D$170</f>
@@ -9215,7 +9213,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B45" s="43" t="n">
         <f aca="false">Assumptions!$D$174/60*Assumptions!$D$175</f>
@@ -9224,7 +9222,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B46" s="41" t="n">
         <f aca="false">Assumptions!$D$176</f>
@@ -9233,7 +9231,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B47" s="29" t="n">
         <f aca="false">IF(B41*B39&gt;0,B43/B41/B39,0)</f>
@@ -9242,7 +9240,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B48" s="41" t="n">
         <f aca="false">IF(B43&gt;0,(B47*B38+B46)/B43,0)</f>
@@ -9251,50 +9249,50 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="B52" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="C52" s="12" t="s">
         <v>546</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="D52" s="12" t="s">
         <v>547</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="E52" s="12" t="s">
         <v>548</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="F52" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="G52" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="H52" s="12" t="s">
         <v>551</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="I52" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="J52" s="12" t="s">
         <v>553</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="K52" s="12" t="s">
         <v>554</v>
-      </c>
-      <c r="K52" s="12" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="28" t="s">
+        <v>555</v>
+      </c>
+      <c r="B53" s="13" t="s">
         <v>556</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>557</v>
       </c>
       <c r="C53" s="30" t="n">
         <f aca="false">(Assumptions!$D$93+Assumptions!$D$94)</f>
@@ -9309,32 +9307,32 @@
         <v>18.2469</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G53" s="29" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E53*Assumptions!$D$89,0))</f>
         <v>10</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I53" s="29" t="n">
         <f aca="false">MIN(G53,MAX(1,ROUNDUP(E53*Assumptions!$D$91,0)))</f>
         <v>6</v>
       </c>
       <c r="J53" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="K53" s="13" t="s">
         <v>559</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="28" t="s">
+        <v>560</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>561</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>562</v>
       </c>
       <c r="C54" s="30" t="n">
         <f aca="false">(Weekly!$D$4*4/7+Weekly!$D$5+Weekly!$D$6*3/7)</f>
@@ -9369,15 +9367,15 @@
         <v>670</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="28" t="s">
+        <v>563</v>
+      </c>
+      <c r="B55" s="13" t="s">
         <v>564</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>565</v>
       </c>
       <c r="C55" s="30" t="n">
         <f aca="false">(Weekly!$D$5+Weekly!$D$6)</f>
@@ -9412,12 +9410,12 @@
         <v>270</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -9455,17 +9453,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="369.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="318.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9479,100 +9477,100 @@
         <v>305</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>306</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>573</v>
-      </c>
       <c r="H4" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>309</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L4" s="12" t="s">
         <v>426</v>
       </c>
       <c r="M4" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="N4" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>576</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="W4" s="12" t="s">
         <v>584</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="X4" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="X4" s="12" t="s">
+      <c r="Y4" s="12" t="s">
         <v>586</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Z4" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="Z4" s="12" t="s">
+      <c r="AA4" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="AA4" s="12" t="s">
+      <c r="AB4" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="AB4" s="12" t="s">
+      <c r="AC4" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="AC4" s="12" t="s">
+      <c r="AD4" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="AD4" s="12" t="s">
+      <c r="AE4" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="AE4" s="12" t="s">
+      <c r="AF4" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="AF4" s="12" t="s">
+      <c r="AG4" s="12" t="s">
         <v>594</v>
       </c>
-      <c r="AG4" s="12" t="s">
+      <c r="AH4" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="AH4" s="12" t="s">
+      <c r="AI4" s="12" t="s">
         <v>596</v>
-      </c>
-      <c r="AI4" s="12" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12397,16 +12395,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>322</v>
@@ -12531,16 +12529,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>322</v>
@@ -12665,16 +12663,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>322</v>
@@ -12799,16 +12797,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>322</v>
@@ -12933,16 +12931,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>322</v>
@@ -13067,16 +13065,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>322</v>
@@ -13201,16 +13199,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>322</v>
@@ -13335,16 +13333,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>322</v>
@@ -13469,16 +13467,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>48</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>322</v>
@@ -13603,16 +13601,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>322</v>
@@ -13802,7 +13800,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13814,10 +13812,10 @@
         <v>47</v>
       </c>
       <c r="D38" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>613</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13916,7 +13914,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13927,7 +13925,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C4" s="41" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Channel")</f>
@@ -13936,7 +13934,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C5" s="41" t="n">
         <f aca="false">SUMIFS(Channels!X5:X34,Channels!D5:D34,"Initiative")</f>
@@ -13945,7 +13943,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C6" s="41" t="n">
         <f aca="false">Channels!Y35</f>
@@ -13954,7 +13952,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C7" s="41" t="n">
         <f aca="false">C4+C5+C6</f>
@@ -13963,7 +13961,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C8" s="41" t="n">
         <f aca="false">Channels!Z35</f>
@@ -13972,7 +13970,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C9" s="41" t="n">
         <f aca="false">C7</f>
@@ -13981,7 +13979,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C10" s="41" t="n">
         <f aca="false">IF(Assumptions!$D$48&lt;1,C9/(1-Assumptions!$D$48)*Assumptions!$D$48,0)</f>
@@ -13990,7 +13988,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C11" s="41" t="n">
         <f aca="false">C9+C10</f>
@@ -13999,7 +13997,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">IF(Assumptions!$D$51&gt;0,ROUNDUP(C11/Assumptions!$D$51,0)*Assumptions!$D$51,C11)</f>
@@ -14008,7 +14006,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C13" s="46" t="n">
         <f aca="false">MIN(Channels!U35,Funnel!B26)</f>
@@ -14017,7 +14015,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C14" s="47" t="n">
         <f aca="false">IF(C13&gt;0,C9/C13,0)</f>
@@ -14026,7 +14024,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C15" s="41" t="n">
         <f aca="false">IF(C13&gt;0,C12/C13,0)</f>
@@ -14035,7 +14033,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C16" s="30" t="n">
         <f aca="false">IF(C12&gt;0,Weekly!N5/C12,0)</f>
@@ -14044,7 +14042,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="28" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14053,25 +14051,25 @@
         <v>305</v>
       </c>
       <c r="C20" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>587</v>
-      </c>
-      <c r="E20" s="12" t="s">
+      <c r="F20" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="F20" s="12" t="s">
-        <v>589</v>
-      </c>
-      <c r="G20" s="12" t="s">
+      <c r="H20" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="I20" s="12" t="s">
         <v>633</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14241,7 +14239,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="28" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14250,16 +14248,16 @@
         <v>304</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D28" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>633</v>
-      </c>
       <c r="F28" s="12" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14390,7 +14388,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C35" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B35)</f>
@@ -14411,7 +14409,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C36" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B36)</f>
@@ -14432,7 +14430,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C37" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B37)</f>
@@ -14453,7 +14451,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C38" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$AA$5:$AA$34,Channels!$B$5:$B$34,B38)</f>
@@ -14493,7 +14491,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="28" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14505,10 +14503,10 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12"/>
       <c r="B44" s="12" t="s">
+        <v>637</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>638</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>639</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>48</v>
@@ -14523,10 +14521,10 @@
         <v>54</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14599,17 +14597,17 @@
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="28" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F51" s="48" t="n">
         <f aca="false">1</f>
@@ -14622,7 +14620,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F52" s="41" t="n">
         <f aca="false">Budget!$C$12*F51</f>
@@ -14635,7 +14633,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F53" s="41" t="n">
         <f aca="false">F52*(1-Assumptions!$D$48)</f>
@@ -14648,7 +14646,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E54" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F54" s="41" t="n">
         <f aca="false">MAX(0,Budget!$C$9-F53)</f>
@@ -14661,44 +14659,44 @@
     </row>
     <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>305</v>
       </c>
       <c r="C55" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>647</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="E55" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="E55" s="12" t="s">
-        <v>632</v>
-      </c>
-      <c r="F55" s="12" t="s">
+      <c r="G55" s="12" t="s">
         <v>649</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>650</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="12"/>
       <c r="J55" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="K55" s="12" t="s">
         <v>651</v>
-      </c>
-      <c r="K55" s="12" t="s">
-        <v>652</v>
       </c>
       <c r="L55" s="12"/>
       <c r="M55" s="12"/>
       <c r="N55" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O55" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="P55" s="12" t="s">
         <v>653</v>
-      </c>
-      <c r="P55" s="12" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="1" collapsed="false">
@@ -16203,7 +16201,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E86" s="28" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16273,7 +16271,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E92" s="2" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F92" s="41" t="n">
         <f aca="false">IF(F91&gt;0,F52/F91,0)</f>
@@ -16286,7 +16284,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E94" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F94" s="32" t="n">
         <f aca="false">SUM(O56:O85)</f>
@@ -16299,7 +16297,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E95" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F95" s="30" t="n">
         <f aca="false">IF(F94&gt;0,MIN(1,Funnel!$B$22/F94),1)</f>
@@ -16312,7 +16310,7 @@
     </row>
     <row r="97" customFormat="false" ht="407.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -16345,92 +16343,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="344" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>662</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>663</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="J3" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="K3" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="L3" s="12" t="s">
         <v>671</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="M3" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="N3" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="O3" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="P3" s="12" t="s">
         <v>675</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="Q3" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="R3" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="S3" s="12" t="s">
         <v>678</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="T3" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="U3" s="12" t="s">
         <v>680</v>
       </c>
-      <c r="U3" s="12" t="s">
+      <c r="V3" s="12" t="s">
         <v>681</v>
       </c>
-      <c r="V3" s="12" t="s">
+      <c r="W3" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="W3" s="12" t="s">
+      <c r="X3" s="12" t="s">
         <v>683</v>
       </c>
-      <c r="X3" s="12" t="s">
+      <c r="Y3" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="Y3" s="12" t="s">
+      <c r="Z3" s="49" t="s">
         <v>685</v>
-      </c>
-      <c r="Z3" s="49" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17675,7 +17673,7 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -17727,12 +17725,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="28" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F19" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17741,7 +17739,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F20" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$C$5:$C$34,"Supervisors",Channels!$E$5:$E$34,"&lt;&gt;Slot",Channels!$B$5:$B$34,"&lt;&gt;I1b Employee referral sprint (bonus on hire)",Channels!$B$5:$B$34,"&lt;&gt;I1a Talent rediscovery (past applicants in ATS)")-SUMIFS(Channels!$Z$5:$Z$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17750,7 +17748,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F21" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$E$5:$E$34,"Slot")</f>
@@ -17759,7 +17757,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F22" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17768,7 +17766,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F23" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1b Employee referral sprint (bonus on hire)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17777,7 +17775,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F24" s="41" t="n">
         <f aca="false">SUM(Channels!$Z$5:$Z$34)</f>
@@ -17786,7 +17784,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F25" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17795,7 +17793,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F26" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AF$5:$AF$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17804,7 +17802,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F27" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17813,7 +17811,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F28" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AE$5:$AE$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17822,7 +17820,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F29" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17831,7 +17829,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F30" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$AG$5:$AG$34,Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17840,7 +17838,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F31" s="41" t="n">
         <f aca="false">SUMIFS(Channels!$X$5:$X$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)")</f>
@@ -17849,7 +17847,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F32" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17858,7 +17856,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F33" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$V$5:$V$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17867,7 +17865,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F34" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17876,7 +17874,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F35" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$W$5:$W$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17885,7 +17883,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F36" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"&lt;&gt;Supervisors")</f>
@@ -17894,7 +17892,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F37" s="32" t="n">
         <f aca="false">SUMIFS(Channels!$U$5:$U$34,Channels!$B$5:$B$34,"I1a Talent rediscovery (past applicants in ATS)",Channels!$C$5:$C$34,"Supervisors")</f>
@@ -17903,7 +17901,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F38" s="30" t="n">
         <f aca="false">IF(Funnel!B23&gt;0,MIN(1,Funnel!B22/Funnel!B23),1)</f>
@@ -17912,7 +17910,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17921,37 +17919,37 @@
         <v>304</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>711</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="F43" s="12" t="s">
         <v>712</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="G43" s="12" t="s">
         <v>713</v>
       </c>
-      <c r="G43" s="12" t="s">
+      <c r="H43" s="12" t="s">
         <v>714</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="I43" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="J43" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="K43" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="L43" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="L43" s="12" t="s">
+      <c r="M43" s="12" t="s">
         <v>719</v>
-      </c>
-      <c r="M43" s="12" t="s">
-        <v>720</v>
       </c>
       <c r="N43" s="12" t="s">
         <v>436</v>
@@ -18589,12 +18587,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18608,67 +18606,67 @@
         <v>305</v>
       </c>
       <c r="D4" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>724</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>725</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>726</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="I4" s="12" t="s">
         <v>727</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="J4" s="12" t="s">
         <v>728</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>729</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>730</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="M4" s="12" t="s">
         <v>731</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>732</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>733</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>734</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="12" t="s">
         <v>735</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="R4" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="R4" s="12" t="s">
+      <c r="S4" s="12" t="s">
         <v>737</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="T4" s="12" t="s">
         <v>738</v>
       </c>
-      <c r="T4" s="12" t="s">
+      <c r="U4" s="12" t="s">
         <v>739</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>740</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="W4" s="12" t="s">
         <v>741</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="X4" s="12" t="s">
         <v>742</v>
-      </c>
-      <c r="X4" s="12" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20856,7 +20854,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20865,46 +20863,46 @@
         <v>305</v>
       </c>
       <c r="C39" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="E39" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="F39" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="G39" s="12" t="s">
         <v>748</v>
       </c>
-      <c r="G39" s="12" t="s">
+      <c r="H39" s="12" t="s">
         <v>749</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="I39" s="12" t="s">
         <v>750</v>
       </c>
-      <c r="I39" s="12" t="s">
+      <c r="J39" s="12" t="s">
         <v>751</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="K39" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="L39" s="12" t="s">
         <v>753</v>
       </c>
-      <c r="L39" s="12" t="s">
+      <c r="M39" s="12" t="s">
         <v>754</v>
       </c>
-      <c r="M39" s="12" t="s">
+      <c r="N39" s="12" t="s">
         <v>755</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>756</v>
       </c>
       <c r="O39" s="12" t="s">
         <v>47</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21134,7 +21132,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>

--- a/operation_uptime/Operation_Uptime_Model.xlsx
+++ b/operation_uptime/Operation_Uptime_Model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="765">
   <si>
     <t xml:space="preserve">Operation Uptime — model summary (hypothetical Tesla Giga Berlin maintenance hiring)</t>
   </si>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Last useful application date (Supervisors)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardest role (needs the most money; scarcity evidence on Funnel row 35)</t>
+    <t xml:space="preserve">Hardest role (dearest last hire we must buy; reasons on Funnel row 35)</t>
   </si>
   <si>
     <t xml:space="preserve">Most sensitive assumption</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Assumptions log = the model's only input sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Label: Given = from the brief; Researched = with link; Own estimate = my judgement, with the reason beside it; Researched + Own estimate = a linked benchmark that I adapted. Black (not blue) values are calculated.</t>
+    <t xml:space="preserve">Blue cells on yellow are inputs: change them here and every other tab recalculates. Labels: Given = from the brief; Researched = read from, or calculated by stated arithmetic from, the linked source; Own estimate = my judgement, with the reason (and the benchmark it starts from, where there is one). Black (not blue) values are calculated.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Given in the brief</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">Researched</t>
   </si>
   <si>
-    <t xml:space="preserve">Last Friday before Christmas; job searching drops ~45% over the holidays (Indeed Hiring Lab). https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/</t>
+    <t xml:space="preserve">Last Friday before Christmas; job searches hit a low ~45% below normal over the holidays (Indeed Hiring Lab). https://hiringlab.indeed.com/de/blog/2025/02/17/der-stellenmarkt-startet-unausgewogen-in-das-neue-jahr/</t>
   </si>
   <si>
     <t xml:space="preserve">T2</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">Days: application → recruiter assessment of a qualified applicant</t>
   </si>
   <si>
-    <t xml:space="preserve">German median: 6 days to review an application (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
+    <t xml:space="preserve">Global median: 6 days to review an application (SmartRecruiters 2025, Germany edition; German processes run longer, so this assumes the client keeps pace). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">T3</t>
@@ -251,10 +251,7 @@
     <t xml:space="preserve">Days: recruiter assessment → technical interview/test done</t>
   </si>
   <si>
-    <t xml:space="preserve">Researched + Own estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">German median: 14 days from application to interview, minus the 6 above (SmartRecruiters 2025). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
+    <t xml:space="preserve">Global median: 14 days from application to interview, minus the 6 above (SmartRecruiters 2025, Germany edition). https://ta.smartrecruiters.com/rs/664-NIC-529/images/Germany%20Recruiting%20Benchmarks%202025%20Report%20DE.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">T4</t>
@@ -311,19 +308,25 @@
     <t xml:space="preserve">Qualified → passed assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">About a third of final interviews lead to an offer (Gem 2025); higher here because candidates are pre-qualified. Hardest for automation and supervisors. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
+    <t xml:space="preserve">Gem 2025: ~35% of candidates brought onsite get offers (mostly US tech). Set higher (50%) because only pre-qualified people reach this step. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">PM</t>
   </si>
   <si>
+    <t xml:space="preserve">Gem 2025: ~35% of onsite candidates get offers. Set at 55%: most common trade, the assessment is routine for it. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">PA</t>
   </si>
   <si>
+    <t xml:space="preserve">Gem 2025: ~35% of onsite candidates get offers. Set at 45%: PLC skills are tested hard. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">PS</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment for these trades: all of Berlin plus ~60% of Brandenburg (within 75 km). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+    <t xml:space="preserve">Gem 2025: ~35% of onsite candidates get offers. Set at 40%: leadership is assessed on top of trade skills. https://lp.gem.com/rs/972-IVV-330/images/2025%20Recruiting%20Benchmarks%20-%20Gem.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">OE</t>
@@ -350,7 +353,7 @@
     <t xml:space="preserve">Offer → signed contract</t>
   </si>
   <si>
-    <t xml:space="preserve">German offer acceptance is ~71–78% (Königsteiner, StepStone surveys). https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449</t>
+    <t xml:space="preserve">Königsteiner 2022: 47% accepted vs 14% declined after an offer → ~77% acceptance. I use 70–75%: shift work and competing offers. https://www.lebensmittelzeitung.net/handel/karriere/rekrutierung-bewerber-sagen-haeufiger-ab-166449</t>
   </si>
   <si>
     <t xml:space="preserve">AM</t>
@@ -422,7 +425,7 @@
     <t xml:space="preserve">All paid</t>
   </si>
   <si>
-    <t xml:space="preserve">Paced so that no week needs more than the 55 assessments (Weekly tab).</t>
+    <t xml:space="preserve">Paced so each week's qualified applicants fit the slots they can use (assessed 6 days after applying). Week 1 is biggest: it also fills the first assessment days (22–25 Oct). Week 6 is small: only 24 Nov is still useful.</t>
   </si>
   <si>
     <t xml:space="preserve">W2</t>
@@ -506,22 +509,34 @@
     <t xml:space="preserve">people</t>
   </si>
   <si>
+    <t xml:space="preserve">BA employment, KldB 2625 + 2622: Berlin 2,708 + 60% of Brandenburg 3,417 (75 km radius, own scaling) ≈ 4,800. Berlin file: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-11-0-202512-xlsx.xlsx?__blob=publicationFile https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSM</t>
   </si>
   <si>
+    <t xml:space="preserve">BA employment, KldB 2611 + 2510/2511/2513 (skilled level): Berlin 17,490 + 60% of Brandenburg 14,878 (75 km radius, own scaling) ≈ 26,400. Berlin file: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-11-0-202512-xlsx.xlsx?__blob=publicationFile https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSA</t>
   </si>
   <si>
+    <t xml:space="preserve">BA employment, KldB 2612: Berlin 1,254 + 60% of Brandenburg 1,206 (75 km radius, own scaling) ≈ 2,000. Berlin file: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-11-0-202512-xlsx.xlsx?__blob=publicationFile https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSS</t>
   </si>
   <si>
+    <t xml:space="preserve">BA employment, supervisor codes 2519 + 2619 + 2629 + 2639: Berlin 1,494 + 60% of Brandenburg 1,209 (75 km radius, own scaling) ≈ 2,200. Berlin file: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-11-0-202512-xlsx.xlsx?__blob=publicationFile https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+  </si>
+  <si>
     <t xml:space="preserve">PIE</t>
   </si>
   <si>
     <t xml:space="preserve">Share in-market or persuadable during the 6-week window</t>
   </si>
   <si>
-    <t xml:space="preserve">~11% of employees are actively looking for a new job (Gallup 2024). https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf</t>
+    <t xml:space="preserve">Gallup 2024: active job search is 3% / 10% / 23% for high / low / no engagement; weighted by the 9% / 78% / 13% shares ≈ 11%. https://gallup.com/file/de/657716/Engagement-Index-Deutschland-Report-2024.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">PIM</t>
@@ -539,7 +554,7 @@
     <t xml:space="preserve">Qualified people elsewhere in Germany willing to relocate in the window</t>
   </si>
   <si>
-    <t xml:space="preserve">Few trades workers move across Germany for a job: national headcount × yearly move rate × share moving to Berlin-Brandenburg (Destatis, IAB). https://www.destatis.de/DE/Themen/Gesellschaft-Umwelt/Bevoelkerung/Wanderungen/Tabellen/_tabellen-liste-nach-bundeslaendern-jahr.html</t>
+    <t xml:space="preserve">Own sizing: few trades workers move across Germany for a job; national headcount × yearly move rate × share moving to Berlin-Brandenburg.</t>
   </si>
   <si>
     <t xml:space="preserve">PRM</t>
@@ -593,7 +608,7 @@
     <t xml:space="preserve">Cut budget 50% when re-forecast cost per qualified ≥ this × plan</t>
   </si>
   <si>
-    <t xml:space="preserve">50% dearer than plan → halve the budget (common ad practice). https://sparkugc.com/resources/when-to-kill-a-meta-ad-cpa-rule</t>
+    <t xml:space="preserve">A common ad rule is 'reduce if cost is 1.2–2× target' (roaspig); I halve at 1.5×. https://roaspig.com/blog/automated-rules-manage-meta-budgets/</t>
   </si>
   <si>
     <t xml:space="preserve">R5</t>
@@ -683,7 +698,7 @@
     <t xml:space="preserve">Scale-up step per week</t>
   </si>
   <si>
-    <t xml:space="preserve">+25% a week: big enough to matter, small enough not to upset ad bidding. https://roaspig.com/blog/automated-rules-manage-meta-budgets/</t>
+    <t xml:space="preserve">Between the common +20% and +30% scale-up rules (roaspig). https://roaspig.com/blog/automated-rules-manage-meta-budgets/</t>
   </si>
   <si>
     <t xml:space="preserve">R9</t>
@@ -785,7 +800,7 @@
     <t xml:space="preserve">×</t>
   </si>
   <si>
-    <t xml:space="preserve">How often each channel was decisive for a hire, from IAB's 2025 employer survey. https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/</t>
+    <t xml:space="preserve">Derived from IAB 2025: decisive ÷ used for job boards (21% ÷ 57%), relative to the average channel (0.41). https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/</t>
   </si>
   <si>
     <t xml:space="preserve">CXH</t>
@@ -794,12 +809,18 @@
     <t xml:space="preserve">Channel quality index: own careers page (organic, Google Search ads)</t>
   </si>
   <si>
+    <t xml:space="preserve">Derived from IAB 2025: decisive ÷ used for the employer homepage (20% ÷ 70%), relative to the average channel (0.41). https://iab-forum.de/online-medien-sind-bei-der-personalsuche-auf-dem-vormarsch/</t>
+  </si>
+  <si>
     <t xml:space="preserve">CXS</t>
   </si>
   <si>
     <t xml:space="preserve">Channel quality index: social media (Meta)</t>
   </si>
   <si>
+    <t xml:space="preserve">Derived from IAB data (2022): social media was used for 42% of filled jobs but decisive for 1 in 14; (7.1% ÷ 42%) ÷ 0.41 ≈ 0.41. https://ohn.haendlerbund.de/themen/unternehmen-maerkte/139538-social-media-whatsapp-mitarbeitersuche-immer-wichtiger</t>
+  </si>
+  <si>
     <t xml:space="preserve">RXP</t>
   </si>
   <si>
@@ -884,7 +905,7 @@
     <t xml:space="preserve">I2</t>
   </si>
   <si>
-    <t xml:space="preserve">Average social campaign for electricians brings ~30 qualified applications (Redline). https://redline-grow.de/fachkraeftemangel-handwerk</t>
+    <t xml:space="preserve">Redline 2024–26: mean 29.5 qualified applications per Elektroniker campaign (11 campaigns). https://redline-grow.de/bewerbungen-pro-stelle</t>
   </si>
   <si>
     <t xml:space="preserve">SSW</t>
@@ -917,7 +938,7 @@
     <t xml:space="preserve">Maintenance trades as share of production occupations</t>
   </si>
   <si>
-    <t xml:space="preserve">Maintenance trades are ~7.8% of production jobs in Germany (BA employment data). https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+    <t xml:space="preserve">BA employment: maintenance codes 2513 + 2625 + 2611 + 2612 + supervisors (536,520) ÷ production occupations 21–29 (6,850,263) = 7.8%. https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-d-0-202512-xlsx.xlsx?__blob=publicationFile</t>
   </si>
   <si>
     <t xml:space="preserve">TURN</t>
@@ -926,7 +947,7 @@
     <t xml:space="preserve">Annual staff turnover, Brandenburg firms</t>
   </si>
   <si>
-    <t xml:space="preserve">Brandenburg firms turn over ~12% of staff a year (IAB-Betriebspanel 2024). https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf</t>
+    <t xml:space="preserve">IAB-Betriebspanel Brandenburg: ~6% of jobs ended in the first half of 2024 → ~12% a year. https://mweke.brandenburg.de/media/bb1.a.3814.de/Betriebspanel%20Brandenburg%202024%20-%20final.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">REFSH</t>
@@ -998,7 +1019,7 @@
     <t xml:space="preserve">CPA</t>
   </si>
   <si>
-    <t xml:space="preserve">Indeed charges per application in Germany; DACH median €161 (TalentBait). Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/</t>
+    <t xml:space="preserve">Indeed's DACH median is €161 per application (TalentBait, 2,549 campaigns), used as the programmatic proxy. Volume capped by Indeed's reach. https://www.talentbait.de/recruiting-kanaele-uebersicht/</t>
   </si>
   <si>
     <t xml:space="preserve">C06</t>
@@ -1019,7 +1040,7 @@
     <t xml:space="preserve">Slot</t>
   </si>
   <si>
-    <t xml:space="preserve">€1,449 per 30-day ad (StepStone price list); ~12 applications per ad (StepStone study). https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/</t>
+    <t xml:space="preserve">From €1,449 per 30-day ad (StepStone price list); HR teams get ~12 applications per vacancy on average (StepStone), used as applications per ad. https://www.stepstone.de/e-recruiting/stellenanzeige-aufgeben/ https://www.stepstone.de/e-recruiting/hr-wissen/recruiting/bewerberqualitaet-steigern</t>
   </si>
   <si>
     <t xml:space="preserve">C10</t>
@@ -1049,7 +1070,7 @@
     <t xml:space="preserve">Meta social (FB/IG lead ads, 75 km geo)</t>
   </si>
   <si>
-    <t xml:space="preserve">Social ads for trades ~€84 per application (TalentBait); volume from Redline campaign data. https://www.talentbait.de/social-media-recruiting</t>
+    <t xml:space="preserve">TalentBait's trades example: ~€84 per application for social ads; volume from Redline campaign data. https://www.talentbait.de/social-media-recruiting</t>
   </si>
   <si>
     <t xml:space="preserve">C16</t>
@@ -1079,7 +1100,7 @@
     <t xml:space="preserve">I1RE</t>
   </si>
   <si>
-    <t xml:space="preserve">I1: past applicants in client ATS who were qualified but not hired (last 24 months)</t>
+    <t xml:space="preserve">I1: past applicants in client ATS who were qualified but not hired (last 12 months)</t>
   </si>
   <si>
     <t xml:space="preserve">records</t>
@@ -1103,7 +1124,7 @@
     <t xml:space="preserve">I1: share of re-contacted past applicants who re-apply</t>
   </si>
   <si>
-    <t xml:space="preserve">Past applicants respond more than cold contacts (~5%) and less than warm outreach (~29%); I use 12% (Pin 2026, Gem). https://www.pin.com/blog/recruiting-outreach-benchmark-report/</t>
+    <t xml:space="preserve">Cold outreach gets ~5% replies (Pin 2026); past applicants already know the employer, so I assume 12%. https://www.pin.com/blog/recruiting-outreach-benchmark-report/</t>
   </si>
   <si>
     <t xml:space="preserve">I1Q</t>
@@ -1157,7 +1178,7 @@
     <t xml:space="preserve">I1: referral bonus per signed referred hire (paid from this budget)</t>
   </si>
   <si>
-    <t xml:space="preserve">Most German firms pay €501–1,000 per successful referral. https://www.personalwirtschaft.de/?p=166393</t>
+    <t xml:space="preserve">Most firms pay €501–1,000 per successful referral (Radancy survey, 335 firms worldwide). https://www.personalwirtschaft.de/?p=166393</t>
   </si>
   <si>
     <t xml:space="preserve">I1A</t>
@@ -1175,7 +1196,7 @@
     <t xml:space="preserve">I2: construction/Handwerk electricians (Elektroniker Energie- und Gebäudetechnik) within 75 km</t>
   </si>
   <si>
-    <t xml:space="preserve">BA employment: ~10,000 construction electricians within 75 km. https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
+    <t xml:space="preserve">BA employment, KldB 2621 Bauelektrik: Berlin 6,204 + 60% of Brandenburg 5,905 (75 km radius, own scaling) ≈ 10,000. Berlin file: https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-11-0-202512-xlsx.xlsx?__blob=publicationFile https://statistik.arbeitsagentur.de/Statistikdaten/Detail/202512/iiia6/beschaeftigung-sozbe-bo-heft/bo-heft-12-0-202512-xlsx.xlsx?__blob=publicationFile</t>
   </si>
   <si>
     <t xml:space="preserve">I2S</t>
@@ -1193,7 +1214,7 @@
     <t xml:space="preserve">I2: cost per application (Meta/Google + 6-question quiz funnel)</t>
   </si>
   <si>
-    <t xml:space="preserve">Social ads for trades cost ~€84 per application (TalentBait). https://www.talentbait.de/social-media-recruiting</t>
+    <t xml:space="preserve">TalentBait's trades example shows ~€84 per application for social ads. https://www.talentbait.de/social-media-recruiting</t>
   </si>
   <si>
     <t xml:space="preserve">I2Q</t>
@@ -1238,7 +1259,7 @@
     <t xml:space="preserve">I3: share qualified after Polish-language pre-screen call</t>
   </si>
   <si>
-    <t xml:space="preserve">~14% of vocationally trained Poles speak a foreign language well (Eurostat 2022); language is the filter. https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Foreign_language_skills_statistics</t>
+    <t xml:space="preserve">Eurostat AES 2022, Poland, vocational upper-secondary: 58.7% know a foreign language × 23.6% of them good or proficient ≈ 14%. https://ec.europa.eu/eurostat/databrowser/view/edat_aes_l33/default/table</t>
   </si>
   <si>
     <t xml:space="preserve">I3X</t>
@@ -1610,7 +1631,7 @@
     <t xml:space="preserve">Qualified</t>
   </si>
   <si>
-    <t xml:space="preserve">Qualified → signed (electrician × 0.8 adj.)</t>
+    <t xml:space="preserve">Qualified → signed (electrician rate × I2A adjustment)</t>
   </si>
   <si>
     <t xml:space="preserve">Expected hires if fully used</t>
@@ -1634,7 +1655,7 @@
     <t xml:space="preserve">Share qualified after pre-screen</t>
   </si>
   <si>
-    <t xml:space="preserve">Qualified → signed (mechatronics × 1.1 adj.)</t>
+    <t xml:space="preserve">Qualified → signed (mechatronics rate × I3A adjustment)</t>
   </si>
   <si>
     <t xml:space="preserve">Hire cap from the 40% rule</t>
@@ -2976,7 +2997,7 @@
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">Budget!C12</f>
-        <v>117500</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2985,7 +3006,7 @@
       </c>
       <c r="C6" s="4" t="n">
         <f aca="false">Budget!C9</f>
-        <v>99787.7142048161</v>
+        <v>101667.57387493</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2994,7 +3015,7 @@
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">Budget!C12-Budget!C9</f>
-        <v>17712.2857951839</v>
+        <v>18332.4261250701</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3022,7 +3043,7 @@
       </c>
       <c r="C10" s="4" t="n">
         <f aca="false">Budget!C14</f>
-        <v>997.877142048161</v>
+        <v>1016.6757387493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3075,8 +3096,8 @@
         <v>13</v>
       </c>
       <c r="C16" s="8" t="str">
-        <f aca="false">IF(MAX(Budget!F21:F24)&lt;=0,"–",INDEX(Budget!B21:B24,MATCH(MAX(Budget!F21:F24),Budget!F21:F24,0))&amp;" (€"&amp;TEXT(MAX(Budget!F21:F24)/1000,"0.0")&amp;"k"&amp;IF(Budget!C9&gt;0,", "&amp;TEXT(MAX(Budget!F21:F24)/Budget!C9,"0%")&amp;" of planned spend","")&amp;"; see Funnel row 35)")</f>
-        <v>Electricians (€38.0k, 38% of planned spend; see Funnel row 35)</v>
+        <f aca="false">IF(MAX(Funnel!H30:H33)&lt;=0,"–",INDEX(Funnel!A30:A33,MATCH(MAX(Funnel!H30:H33),Funnel!H30:H33,0))&amp;" (last hire costs €"&amp;TEXT(MAX(Funnel!H30:H33),"#,##0")&amp;")")</f>
+        <v>Electricians (last hire costs €2,272)</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3094,7 +3115,7 @@
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">Budget!H46</f>
-        <v>86.6379696262294</v>
+        <v>86.977613550255</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3540,18 +3561,18 @@
         <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G22" s="17" t="s">
         <v>74</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>77</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>31</v>
@@ -3566,15 +3587,15 @@
         <v>63</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>79</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>31</v>
@@ -3586,18 +3607,18 @@
         <v>62</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>83</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>54</v>
@@ -3612,12 +3633,12 @@
         <v>63</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3651,10 +3672,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>48</v>
@@ -3666,18 +3687,18 @@
         <v>44</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>43</v>
@@ -3689,18 +3710,18 @@
         <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>52</v>
@@ -3712,18 +3733,18 @@
         <v>44</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>54</v>
@@ -3735,18 +3756,18 @@
         <v>44</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>92</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>48</v>
@@ -3758,18 +3779,18 @@
         <v>44</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
@@ -3781,10 +3802,10 @@
         <v>44</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3792,7 +3813,7 @@
         <v>96</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>52</v>
@@ -3804,18 +3825,18 @@
         <v>44</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>54</v>
@@ -3827,18 +3848,18 @@
         <v>44</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>48</v>
@@ -3853,15 +3874,15 @@
         <v>63</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>43</v>
@@ -3876,15 +3897,15 @@
         <v>63</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>52</v>
@@ -3899,15 +3920,15 @@
         <v>63</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>54</v>
@@ -3922,15 +3943,15 @@
         <v>63</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>48</v>
@@ -3942,18 +3963,18 @@
         <v>44</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>43</v>
@@ -3965,18 +3986,18 @@
         <v>44</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>52</v>
@@ -3988,18 +4009,18 @@
         <v>44</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>54</v>
@@ -4011,15 +4032,15 @@
         <v>44</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -4053,10 +4074,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>31</v>
@@ -4068,44 +4089,44 @@
         <v>44</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>750</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>0.4</v>
@@ -4117,15 +4138,15 @@
         <v>63</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>31</v>
@@ -4134,21 +4155,21 @@
         <v>2500</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>31</v>
@@ -4166,18 +4187,18 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D53" s="16" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>44</v>
@@ -4186,18 +4207,18 @@
         <v>63</v>
       </c>
       <c r="G53" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D54" s="16" t="n">
         <v>0.145</v>
@@ -4209,21 +4230,21 @@
         <v>63</v>
       </c>
       <c r="G54" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D55" s="16" t="n">
-        <v>0.18</v>
+        <v>0.185</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>44</v>
@@ -4232,21 +4253,21 @@
         <v>63</v>
       </c>
       <c r="G55" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D56" s="16" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>44</v>
@@ -4255,21 +4276,21 @@
         <v>63</v>
       </c>
       <c r="G56" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D57" s="16" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>44</v>
@@ -4278,21 +4299,21 @@
         <v>63</v>
       </c>
       <c r="G57" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D58" s="16" t="n">
-        <v>0.22</v>
+        <v>0.03</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>44</v>
@@ -4301,18 +4322,18 @@
         <v>63</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" s="16" t="n">
         <v>0</v>
@@ -4324,18 +4345,18 @@
         <v>63</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D60" s="16" t="n">
         <v>0</v>
@@ -4347,18 +4368,18 @@
         <v>63</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D61" s="16" t="n">
         <v>0</v>
@@ -4370,18 +4391,18 @@
         <v>63</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D62" s="16" t="n">
         <v>0</v>
@@ -4393,18 +4414,18 @@
         <v>63</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D63" s="16" t="n">
         <v>0</v>
@@ -4416,15 +4437,15 @@
         <v>63</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>31</v>
@@ -4444,7 +4465,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -4478,10 +4499,10 @@
     </row>
     <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>48</v>
@@ -4490,21 +4511,21 @@
         <v>4800</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>43</v>
@@ -4513,21 +4534,21 @@
         <v>26400</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>52</v>
@@ -4536,21 +4557,21 @@
         <v>2000</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>54</v>
@@ -4559,21 +4580,21 @@
         <v>2200</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>67</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>48</v>
@@ -4588,15 +4609,15 @@
         <v>67</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>43</v>
@@ -4611,15 +4632,15 @@
         <v>67</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>52</v>
@@ -4634,15 +4655,15 @@
         <v>67</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>54</v>
@@ -4657,15 +4678,15 @@
         <v>67</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>48</v>
@@ -4674,21 +4695,21 @@
         <v>41</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>170</v>
+        <v>63</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>43</v>
@@ -4697,21 +4718,21 @@
         <v>28</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G77" s="17" t="s">
-        <v>170</v>
+        <v>63</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>52</v>
@@ -4720,21 +4741,21 @@
         <v>16</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G78" s="17" t="s">
-        <v>170</v>
+        <v>63</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>54</v>
@@ -4743,18 +4764,18 @@
         <v>4</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G79" s="17" t="s">
-        <v>170</v>
+        <v>63</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B81" s="11"/>
       <c r="C81" s="11"/>
@@ -4788,151 +4809,151 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D83" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G83" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D84" s="15" t="n">
         <v>30</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G84" s="13" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="B85" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D85" s="19" t="n">
         <v>0.8</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>63</v>
       </c>
       <c r="G85" s="13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v